--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="118">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,120 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
+    <t>UEFA Nations League</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
+    <t>Internacional de Bogotá</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>Bosnia</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Faroe Islands</t>
+  </si>
+  <si>
+    <t>Goias</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Moldova</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Armenia</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Northern Ireland</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>2026-09-30 01:26:25</t>
   </si>
 </sst>
 </file>
@@ -585,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +942,3152 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2">
+        <v>1.67</v>
+      </c>
+      <c r="G2">
+        <v>1.78</v>
+      </c>
+      <c r="H2">
+        <v>5.7</v>
+      </c>
+      <c r="I2">
+        <v>6.8</v>
+      </c>
+      <c r="J2">
+        <v>3.55</v>
+      </c>
+      <c r="K2">
+        <v>4.6</v>
+      </c>
+      <c r="L2">
+        <v>1.47</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>3.15</v>
+      </c>
+      <c r="O2">
+        <v>1.42</v>
+      </c>
+      <c r="P2">
+        <v>1.67</v>
+      </c>
+      <c r="Q2">
+        <v>2.2</v>
+      </c>
+      <c r="R2">
+        <v>1.24</v>
+      </c>
+      <c r="S2">
+        <v>4.1</v>
+      </c>
+      <c r="T2">
+        <v>2.12</v>
+      </c>
+      <c r="U2">
+        <v>1.68</v>
+      </c>
+      <c r="V2">
+        <v>1.17</v>
+      </c>
+      <c r="W2">
+        <v>2.28</v>
+      </c>
+      <c r="X2">
+        <v>970</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>7.2</v>
+      </c>
+      <c r="AC2">
+        <v>970</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>970</v>
+      </c>
+      <c r="AG2">
+        <v>970</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>26</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>970</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.7</v>
+      </c>
+      <c r="AQ2">
+        <v>1.93</v>
+      </c>
+      <c r="AR2">
+        <v>1.93</v>
+      </c>
+      <c r="AS2">
+        <v>1.93</v>
+      </c>
+      <c r="AT2">
+        <v>6</v>
+      </c>
+      <c r="AU2">
+        <v>7</v>
+      </c>
+      <c r="AV2">
+        <v>1.93</v>
+      </c>
+      <c r="AW2">
+        <v>1.93</v>
+      </c>
+      <c r="AX2">
+        <v>7.4</v>
+      </c>
+      <c r="AY2">
+        <v>7.4</v>
+      </c>
+      <c r="AZ2">
+        <v>1.93</v>
+      </c>
+      <c r="BA2">
+        <v>1.93</v>
+      </c>
+      <c r="BB2">
+        <v>1.93</v>
+      </c>
+      <c r="BC2">
+        <v>1.79</v>
+      </c>
+      <c r="BD2">
+        <v>1.93</v>
+      </c>
+      <c r="BE2">
+        <v>1.93</v>
+      </c>
+      <c r="BF2">
+        <v>9</v>
+      </c>
+      <c r="BG2">
+        <v>1.93</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.29</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.43</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3">
+        <v>2.98</v>
+      </c>
+      <c r="G3">
+        <v>3.15</v>
+      </c>
+      <c r="H3">
+        <v>2.78</v>
+      </c>
+      <c r="I3">
+        <v>2.94</v>
+      </c>
+      <c r="J3">
+        <v>3.05</v>
+      </c>
+      <c r="K3">
+        <v>3.2</v>
+      </c>
+      <c r="L3">
+        <v>1.02</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>3.5</v>
+      </c>
+      <c r="O3">
+        <v>1.36</v>
+      </c>
+      <c r="P3">
+        <v>1.83</v>
+      </c>
+      <c r="Q3">
+        <v>2.04</v>
+      </c>
+      <c r="R3">
+        <v>1.3</v>
+      </c>
+      <c r="S3">
+        <v>3.4</v>
+      </c>
+      <c r="T3">
+        <v>1.69</v>
+      </c>
+      <c r="U3">
+        <v>2.04</v>
+      </c>
+      <c r="V3">
+        <v>1.51</v>
+      </c>
+      <c r="W3">
+        <v>1.46</v>
+      </c>
+      <c r="X3">
+        <v>23</v>
+      </c>
+      <c r="Y3">
+        <v>11.5</v>
+      </c>
+      <c r="Z3">
+        <v>21</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>24</v>
+      </c>
+      <c r="AC3">
+        <v>7.6</v>
+      </c>
+      <c r="AD3">
+        <v>29</v>
+      </c>
+      <c r="AE3">
+        <v>40</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>18</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>44</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>42</v>
+      </c>
+      <c r="AO3">
+        <v>36</v>
+      </c>
+      <c r="AP3">
+        <v>1.99</v>
+      </c>
+      <c r="AQ3">
+        <v>1.83</v>
+      </c>
+      <c r="AR3">
+        <v>1.97</v>
+      </c>
+      <c r="AS3">
+        <v>2.16</v>
+      </c>
+      <c r="AT3">
+        <v>2</v>
+      </c>
+      <c r="AU3">
+        <v>5.2</v>
+      </c>
+      <c r="AV3">
+        <v>10.5</v>
+      </c>
+      <c r="AW3">
+        <v>2.06</v>
+      </c>
+      <c r="AX3">
+        <v>16</v>
+      </c>
+      <c r="AY3">
+        <v>2.16</v>
+      </c>
+      <c r="AZ3">
+        <v>1.94</v>
+      </c>
+      <c r="BA3">
+        <v>2.16</v>
+      </c>
+      <c r="BB3">
+        <v>2.16</v>
+      </c>
+      <c r="BC3">
+        <v>2.06</v>
+      </c>
+      <c r="BD3">
+        <v>2.16</v>
+      </c>
+      <c r="BE3">
+        <v>2.16</v>
+      </c>
+      <c r="BF3">
+        <v>2.06</v>
+      </c>
+      <c r="BG3">
+        <v>2.04</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.84</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>1.62</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.84</v>
+      </c>
+      <c r="BN3">
+        <v>8</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
+        <v>32</v>
+      </c>
+      <c r="BQ3">
+        <v>1.74</v>
+      </c>
+      <c r="BR3">
+        <v>50</v>
+      </c>
+      <c r="BS3">
+        <v>1.78</v>
+      </c>
+      <c r="BT3">
+        <v>7.6</v>
+      </c>
+      <c r="BU3">
+        <v>3.85</v>
+      </c>
+      <c r="BV3">
+        <v>30</v>
+      </c>
+      <c r="BW3">
+        <v>1.74</v>
+      </c>
+      <c r="BX3">
+        <v>50</v>
+      </c>
+      <c r="BY3">
+        <v>1.78</v>
+      </c>
+      <c r="BZ3">
+        <v>46</v>
+      </c>
+      <c r="CA3">
+        <v>1.77</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4">
+        <v>1.55</v>
+      </c>
+      <c r="G4">
+        <v>1.59</v>
+      </c>
+      <c r="H4">
+        <v>5.6</v>
+      </c>
+      <c r="I4">
+        <v>6.2</v>
+      </c>
+      <c r="J4">
+        <v>5.2</v>
+      </c>
+      <c r="K4">
+        <v>5.4</v>
+      </c>
+      <c r="L4">
+        <v>1.2</v>
+      </c>
+      <c r="M4">
+        <v>1.02</v>
+      </c>
+      <c r="N4">
+        <v>7.6</v>
+      </c>
+      <c r="O4">
+        <v>1.14</v>
+      </c>
+      <c r="P4">
+        <v>3.2</v>
+      </c>
+      <c r="Q4">
+        <v>1.41</v>
+      </c>
+      <c r="R4">
+        <v>1.9</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4">
+        <v>1.54</v>
+      </c>
+      <c r="U4">
+        <v>2.66</v>
+      </c>
+      <c r="V4">
+        <v>1.2</v>
+      </c>
+      <c r="W4">
+        <v>2.7</v>
+      </c>
+      <c r="X4">
+        <v>38</v>
+      </c>
+      <c r="Y4">
+        <v>38</v>
+      </c>
+      <c r="Z4">
+        <v>360</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>15.5</v>
+      </c>
+      <c r="AC4">
+        <v>13.5</v>
+      </c>
+      <c r="AD4">
+        <v>24</v>
+      </c>
+      <c r="AE4">
+        <v>70</v>
+      </c>
+      <c r="AF4">
+        <v>14</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
+        <v>17</v>
+      </c>
+      <c r="AI4">
+        <v>65</v>
+      </c>
+      <c r="AJ4">
+        <v>17</v>
+      </c>
+      <c r="AK4">
+        <v>14.5</v>
+      </c>
+      <c r="AL4">
+        <v>23</v>
+      </c>
+      <c r="AM4">
+        <v>420</v>
+      </c>
+      <c r="AN4">
+        <v>4.9</v>
+      </c>
+      <c r="AO4">
+        <v>44</v>
+      </c>
+      <c r="AP4">
+        <v>24</v>
+      </c>
+      <c r="AQ4">
+        <v>21</v>
+      </c>
+      <c r="AR4">
+        <v>28</v>
+      </c>
+      <c r="AS4">
+        <v>42</v>
+      </c>
+      <c r="AT4">
+        <v>14</v>
+      </c>
+      <c r="AU4">
+        <v>11.5</v>
+      </c>
+      <c r="AV4">
+        <v>21</v>
+      </c>
+      <c r="AW4">
+        <v>42</v>
+      </c>
+      <c r="AX4">
+        <v>12.5</v>
+      </c>
+      <c r="AY4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4">
+        <v>15.5</v>
+      </c>
+      <c r="BA4">
+        <v>32</v>
+      </c>
+      <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
+        <v>12.5</v>
+      </c>
+      <c r="BD4">
+        <v>19.5</v>
+      </c>
+      <c r="BE4">
+        <v>36</v>
+      </c>
+      <c r="BF4">
+        <v>4.5</v>
+      </c>
+      <c r="BG4">
+        <v>25</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>4.3</v>
+      </c>
+      <c r="BJ4">
+        <v>10.5</v>
+      </c>
+      <c r="BK4">
+        <v>6.8</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>21</v>
+      </c>
+      <c r="BN4">
+        <v>5.6</v>
+      </c>
+      <c r="BO4">
+        <v>3.8</v>
+      </c>
+      <c r="BP4">
+        <v>11</v>
+      </c>
+      <c r="BQ4">
+        <v>7</v>
+      </c>
+      <c r="BR4">
+        <v>23</v>
+      </c>
+      <c r="BS4">
+        <v>12.5</v>
+      </c>
+      <c r="BT4">
+        <v>11.5</v>
+      </c>
+      <c r="BU4">
+        <v>7.4</v>
+      </c>
+      <c r="BV4">
+        <v>50</v>
+      </c>
+      <c r="BW4">
+        <v>21</v>
+      </c>
+      <c r="BX4">
+        <v>48</v>
+      </c>
+      <c r="BY4">
+        <v>21</v>
+      </c>
+      <c r="BZ4">
+        <v>13</v>
+      </c>
+      <c r="CA4">
+        <v>6.4</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5">
+        <v>1.7</v>
+      </c>
+      <c r="G5">
+        <v>1.79</v>
+      </c>
+      <c r="H5">
+        <v>5.7</v>
+      </c>
+      <c r="I5">
+        <v>6.6</v>
+      </c>
+      <c r="J5">
+        <v>3.7</v>
+      </c>
+      <c r="K5">
+        <v>4.1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.77</v>
+      </c>
+      <c r="Q5">
+        <v>2.1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6">
+        <v>4.5</v>
+      </c>
+      <c r="G6">
+        <v>5.1</v>
+      </c>
+      <c r="H6">
+        <v>1.9</v>
+      </c>
+      <c r="I6">
+        <v>1.99</v>
+      </c>
+      <c r="J6">
+        <v>3.6</v>
+      </c>
+      <c r="K6">
+        <v>3.7</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.71</v>
+      </c>
+      <c r="Q6">
+        <v>2.22</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7">
+        <v>2.34</v>
+      </c>
+      <c r="G7">
+        <v>2.38</v>
+      </c>
+      <c r="H7">
+        <v>3.4</v>
+      </c>
+      <c r="I7">
+        <v>3.5</v>
+      </c>
+      <c r="J7">
+        <v>3.45</v>
+      </c>
+      <c r="K7">
+        <v>3.5</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.78</v>
+      </c>
+      <c r="Q7">
+        <v>2.24</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1.89</v>
+      </c>
+      <c r="U7">
+        <v>2.02</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>12.5</v>
+      </c>
+      <c r="Y7">
+        <v>12</v>
+      </c>
+      <c r="Z7">
+        <v>27</v>
+      </c>
+      <c r="AA7">
+        <v>80</v>
+      </c>
+      <c r="AB7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC7">
+        <v>7.8</v>
+      </c>
+      <c r="AD7">
+        <v>15.5</v>
+      </c>
+      <c r="AE7">
+        <v>55</v>
+      </c>
+      <c r="AF7">
+        <v>14</v>
+      </c>
+      <c r="AG7">
+        <v>12</v>
+      </c>
+      <c r="AH7">
+        <v>22</v>
+      </c>
+      <c r="AI7">
+        <v>65</v>
+      </c>
+      <c r="AJ7">
+        <v>38</v>
+      </c>
+      <c r="AK7">
+        <v>29</v>
+      </c>
+      <c r="AL7">
+        <v>55</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>24</v>
+      </c>
+      <c r="AO7">
+        <v>55</v>
+      </c>
+      <c r="AP7">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7">
+        <v>10.5</v>
+      </c>
+      <c r="AR7">
+        <v>20</v>
+      </c>
+      <c r="AS7">
+        <v>8.6</v>
+      </c>
+      <c r="AT7">
+        <v>8</v>
+      </c>
+      <c r="AU7">
+        <v>7</v>
+      </c>
+      <c r="AV7">
+        <v>13</v>
+      </c>
+      <c r="AW7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX7">
+        <v>12.5</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>17</v>
+      </c>
+      <c r="BA7">
+        <v>8.4</v>
+      </c>
+      <c r="BB7">
+        <v>7.4</v>
+      </c>
+      <c r="BC7">
+        <v>19.5</v>
+      </c>
+      <c r="BD7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE7">
+        <v>9</v>
+      </c>
+      <c r="BF7">
+        <v>19.5</v>
+      </c>
+      <c r="BG7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8">
+        <v>1.44</v>
+      </c>
+      <c r="G8">
+        <v>1.45</v>
+      </c>
+      <c r="H8">
+        <v>7.8</v>
+      </c>
+      <c r="I8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J8">
+        <v>5.4</v>
+      </c>
+      <c r="K8">
+        <v>5.6</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1.03</v>
+      </c>
+      <c r="N8">
+        <v>6.6</v>
+      </c>
+      <c r="O8">
+        <v>1.16</v>
+      </c>
+      <c r="P8">
+        <v>2.96</v>
+      </c>
+      <c r="Q8">
+        <v>1.5</v>
+      </c>
+      <c r="R8">
+        <v>1.78</v>
+      </c>
+      <c r="S8">
+        <v>2.22</v>
+      </c>
+      <c r="T8">
+        <v>1.69</v>
+      </c>
+      <c r="U8">
+        <v>2.44</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>34</v>
+      </c>
+      <c r="Y8">
+        <v>38</v>
+      </c>
+      <c r="Z8">
+        <v>75</v>
+      </c>
+      <c r="AA8">
+        <v>240</v>
+      </c>
+      <c r="AB8">
+        <v>13</v>
+      </c>
+      <c r="AC8">
+        <v>13</v>
+      </c>
+      <c r="AD8">
+        <v>30</v>
+      </c>
+      <c r="AE8">
+        <v>95</v>
+      </c>
+      <c r="AF8">
+        <v>11.5</v>
+      </c>
+      <c r="AG8">
+        <v>10.5</v>
+      </c>
+      <c r="AH8">
+        <v>21</v>
+      </c>
+      <c r="AI8">
+        <v>75</v>
+      </c>
+      <c r="AJ8">
+        <v>14.5</v>
+      </c>
+      <c r="AK8">
+        <v>14</v>
+      </c>
+      <c r="AL8">
+        <v>27</v>
+      </c>
+      <c r="AM8">
+        <v>80</v>
+      </c>
+      <c r="AN8">
+        <v>4.8</v>
+      </c>
+      <c r="AO8">
+        <v>90</v>
+      </c>
+      <c r="AP8">
+        <v>10</v>
+      </c>
+      <c r="AQ8">
+        <v>10.5</v>
+      </c>
+      <c r="AR8">
+        <v>11</v>
+      </c>
+      <c r="AS8">
+        <v>12</v>
+      </c>
+      <c r="AT8">
+        <v>11.5</v>
+      </c>
+      <c r="AU8">
+        <v>11.5</v>
+      </c>
+      <c r="AV8">
+        <v>20</v>
+      </c>
+      <c r="AW8">
+        <v>11</v>
+      </c>
+      <c r="AX8">
+        <v>10</v>
+      </c>
+      <c r="AY8">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8">
+        <v>17.5</v>
+      </c>
+      <c r="BA8">
+        <v>11</v>
+      </c>
+      <c r="BB8">
+        <v>12.5</v>
+      </c>
+      <c r="BC8">
+        <v>12</v>
+      </c>
+      <c r="BD8">
+        <v>21</v>
+      </c>
+      <c r="BE8">
+        <v>11</v>
+      </c>
+      <c r="BF8">
+        <v>4.5</v>
+      </c>
+      <c r="BG8">
+        <v>11</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>3.9</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>7</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>3.5</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>6.2</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>7.8</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9">
+        <v>2.14</v>
+      </c>
+      <c r="G9">
+        <v>2.22</v>
+      </c>
+      <c r="H9">
+        <v>3.8</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <v>3.6</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1.09</v>
+      </c>
+      <c r="N9">
+        <v>3.3</v>
+      </c>
+      <c r="O9">
+        <v>1.39</v>
+      </c>
+      <c r="P9">
+        <v>1.79</v>
+      </c>
+      <c r="Q9">
+        <v>2.22</v>
+      </c>
+      <c r="R9">
+        <v>1.29</v>
+      </c>
+      <c r="S9">
+        <v>4.1</v>
+      </c>
+      <c r="T9">
+        <v>1.95</v>
+      </c>
+      <c r="U9">
+        <v>1.99</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>14</v>
+      </c>
+      <c r="Y9">
+        <v>13</v>
+      </c>
+      <c r="Z9">
+        <v>29</v>
+      </c>
+      <c r="AA9">
+        <v>110</v>
+      </c>
+      <c r="AB9">
+        <v>8.6</v>
+      </c>
+      <c r="AC9">
+        <v>8</v>
+      </c>
+      <c r="AD9">
+        <v>16</v>
+      </c>
+      <c r="AE9">
+        <v>70</v>
+      </c>
+      <c r="AF9">
+        <v>13</v>
+      </c>
+      <c r="AG9">
+        <v>11</v>
+      </c>
+      <c r="AH9">
+        <v>25</v>
+      </c>
+      <c r="AI9">
+        <v>75</v>
+      </c>
+      <c r="AJ9">
+        <v>29</v>
+      </c>
+      <c r="AK9">
+        <v>28</v>
+      </c>
+      <c r="AL9">
+        <v>48</v>
+      </c>
+      <c r="AM9">
+        <v>150</v>
+      </c>
+      <c r="AN9">
+        <v>25</v>
+      </c>
+      <c r="AO9">
+        <v>75</v>
+      </c>
+      <c r="AP9">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9">
+        <v>11</v>
+      </c>
+      <c r="AR9">
+        <v>18</v>
+      </c>
+      <c r="AS9">
+        <v>8.6</v>
+      </c>
+      <c r="AT9">
+        <v>7.6</v>
+      </c>
+      <c r="AU9">
+        <v>7</v>
+      </c>
+      <c r="AV9">
+        <v>14</v>
+      </c>
+      <c r="AW9">
+        <v>8</v>
+      </c>
+      <c r="AX9">
+        <v>11</v>
+      </c>
+      <c r="AY9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9">
+        <v>17.5</v>
+      </c>
+      <c r="BA9">
+        <v>8.4</v>
+      </c>
+      <c r="BB9">
+        <v>23</v>
+      </c>
+      <c r="BC9">
+        <v>19.5</v>
+      </c>
+      <c r="BD9">
+        <v>34</v>
+      </c>
+      <c r="BE9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF9">
+        <v>17</v>
+      </c>
+      <c r="BG9">
+        <v>42</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>2.64</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>7.2</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>3.85</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>10</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>5.4</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10">
+        <v>1.59</v>
+      </c>
+      <c r="G10">
+        <v>1.6</v>
+      </c>
+      <c r="H10">
+        <v>6.4</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <v>4.3</v>
+      </c>
+      <c r="K10">
+        <v>4.5</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>4.1</v>
+      </c>
+      <c r="O10">
+        <v>1.29</v>
+      </c>
+      <c r="P10">
+        <v>2.08</v>
+      </c>
+      <c r="Q10">
+        <v>1.86</v>
+      </c>
+      <c r="R10">
+        <v>1.41</v>
+      </c>
+      <c r="S10">
+        <v>3.2</v>
+      </c>
+      <c r="T10">
+        <v>1.96</v>
+      </c>
+      <c r="U10">
+        <v>1.97</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>16.5</v>
+      </c>
+      <c r="Y10">
+        <v>22</v>
+      </c>
+      <c r="Z10">
+        <v>65</v>
+      </c>
+      <c r="AA10">
+        <v>210</v>
+      </c>
+      <c r="AB10">
+        <v>8.4</v>
+      </c>
+      <c r="AC10">
+        <v>10</v>
+      </c>
+      <c r="AD10">
+        <v>25</v>
+      </c>
+      <c r="AE10">
+        <v>110</v>
+      </c>
+      <c r="AF10">
+        <v>9.4</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+      <c r="AH10">
+        <v>23</v>
+      </c>
+      <c r="AI10">
+        <v>100</v>
+      </c>
+      <c r="AJ10">
+        <v>15</v>
+      </c>
+      <c r="AK10">
+        <v>17</v>
+      </c>
+      <c r="AL10">
+        <v>42</v>
+      </c>
+      <c r="AM10">
+        <v>140</v>
+      </c>
+      <c r="AN10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO10">
+        <v>140</v>
+      </c>
+      <c r="AP10">
+        <v>14.5</v>
+      </c>
+      <c r="AQ10">
+        <v>19</v>
+      </c>
+      <c r="AR10">
+        <v>12.5</v>
+      </c>
+      <c r="AS10">
+        <v>14</v>
+      </c>
+      <c r="AT10">
+        <v>7.6</v>
+      </c>
+      <c r="AU10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV10">
+        <v>21</v>
+      </c>
+      <c r="AW10">
+        <v>13.5</v>
+      </c>
+      <c r="AX10">
+        <v>8.6</v>
+      </c>
+      <c r="AY10">
+        <v>9</v>
+      </c>
+      <c r="AZ10">
+        <v>19</v>
+      </c>
+      <c r="BA10">
+        <v>13</v>
+      </c>
+      <c r="BB10">
+        <v>13.5</v>
+      </c>
+      <c r="BC10">
+        <v>15</v>
+      </c>
+      <c r="BD10">
+        <v>10.5</v>
+      </c>
+      <c r="BE10">
+        <v>13.5</v>
+      </c>
+      <c r="BF10">
+        <v>7.8</v>
+      </c>
+      <c r="BG10">
+        <v>13.5</v>
+      </c>
+      <c r="BH10">
+        <v>4</v>
+      </c>
+      <c r="BI10">
+        <v>3</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>7.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>3.4</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>7.2</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>7</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11">
+        <v>1.97</v>
+      </c>
+      <c r="G11">
+        <v>1.99</v>
+      </c>
+      <c r="H11">
+        <v>4.6</v>
+      </c>
+      <c r="I11">
+        <v>4.8</v>
+      </c>
+      <c r="J11">
+        <v>3.55</v>
+      </c>
+      <c r="K11">
+        <v>3.6</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.1</v>
+      </c>
+      <c r="N11">
+        <v>2.94</v>
+      </c>
+      <c r="O11">
+        <v>1.48</v>
+      </c>
+      <c r="P11">
+        <v>1.66</v>
+      </c>
+      <c r="Q11">
+        <v>2.42</v>
+      </c>
+      <c r="R11">
+        <v>1.24</v>
+      </c>
+      <c r="S11">
+        <v>4.9</v>
+      </c>
+      <c r="T11">
+        <v>2.16</v>
+      </c>
+      <c r="U11">
+        <v>1.79</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>11</v>
+      </c>
+      <c r="Y11">
+        <v>13</v>
+      </c>
+      <c r="Z11">
+        <v>36</v>
+      </c>
+      <c r="AA11">
+        <v>140</v>
+      </c>
+      <c r="AB11">
+        <v>7</v>
+      </c>
+      <c r="AC11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11">
+        <v>19</v>
+      </c>
+      <c r="AE11">
+        <v>85</v>
+      </c>
+      <c r="AF11">
+        <v>10.5</v>
+      </c>
+      <c r="AG11">
+        <v>11</v>
+      </c>
+      <c r="AH11">
+        <v>26</v>
+      </c>
+      <c r="AI11">
+        <v>90</v>
+      </c>
+      <c r="AJ11">
+        <v>24</v>
+      </c>
+      <c r="AK11">
+        <v>26</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>210</v>
+      </c>
+      <c r="AN11">
+        <v>21</v>
+      </c>
+      <c r="AO11">
+        <v>130</v>
+      </c>
+      <c r="AP11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11">
+        <v>11</v>
+      </c>
+      <c r="AR11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS11">
+        <v>12</v>
+      </c>
+      <c r="AT11">
+        <v>6.2</v>
+      </c>
+      <c r="AU11">
+        <v>7.2</v>
+      </c>
+      <c r="AV11">
+        <v>17</v>
+      </c>
+      <c r="AW11">
+        <v>11.5</v>
+      </c>
+      <c r="AX11">
+        <v>9.4</v>
+      </c>
+      <c r="AY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11">
+        <v>21</v>
+      </c>
+      <c r="BA11">
+        <v>11.5</v>
+      </c>
+      <c r="BB11">
+        <v>20</v>
+      </c>
+      <c r="BC11">
+        <v>21</v>
+      </c>
+      <c r="BD11">
+        <v>10.5</v>
+      </c>
+      <c r="BE11">
+        <v>12.5</v>
+      </c>
+      <c r="BF11">
+        <v>18.5</v>
+      </c>
+      <c r="BG11">
+        <v>12</v>
+      </c>
+      <c r="BH11">
+        <v>3.1</v>
+      </c>
+      <c r="BI11">
+        <v>2.48</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>8</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>3.7</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>5.8</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.01</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12">
+        <v>3.35</v>
+      </c>
+      <c r="G12">
+        <v>3.45</v>
+      </c>
+      <c r="H12">
+        <v>2.22</v>
+      </c>
+      <c r="I12">
+        <v>2.28</v>
+      </c>
+      <c r="J12">
+        <v>3.7</v>
+      </c>
+      <c r="K12">
+        <v>3.8</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1.05</v>
+      </c>
+      <c r="N12">
+        <v>4.5</v>
+      </c>
+      <c r="O12">
+        <v>1.26</v>
+      </c>
+      <c r="P12">
+        <v>2.1</v>
+      </c>
+      <c r="Q12">
+        <v>1.8</v>
+      </c>
+      <c r="R12">
+        <v>1.46</v>
+      </c>
+      <c r="S12">
+        <v>3</v>
+      </c>
+      <c r="T12">
+        <v>1.69</v>
+      </c>
+      <c r="U12">
+        <v>2.34</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>18.5</v>
+      </c>
+      <c r="Y12">
+        <v>12</v>
+      </c>
+      <c r="Z12">
+        <v>15.5</v>
+      </c>
+      <c r="AA12">
+        <v>30</v>
+      </c>
+      <c r="AB12">
+        <v>15.5</v>
+      </c>
+      <c r="AC12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12">
+        <v>11.5</v>
+      </c>
+      <c r="AE12">
+        <v>23</v>
+      </c>
+      <c r="AF12">
+        <v>27</v>
+      </c>
+      <c r="AG12">
+        <v>15</v>
+      </c>
+      <c r="AH12">
+        <v>17</v>
+      </c>
+      <c r="AI12">
+        <v>40</v>
+      </c>
+      <c r="AJ12">
+        <v>70</v>
+      </c>
+      <c r="AK12">
+        <v>44</v>
+      </c>
+      <c r="AL12">
+        <v>46</v>
+      </c>
+      <c r="AM12">
+        <v>95</v>
+      </c>
+      <c r="AN12">
+        <v>34</v>
+      </c>
+      <c r="AO12">
+        <v>14.5</v>
+      </c>
+      <c r="AP12">
+        <v>16</v>
+      </c>
+      <c r="AQ12">
+        <v>10.5</v>
+      </c>
+      <c r="AR12">
+        <v>13.5</v>
+      </c>
+      <c r="AS12">
+        <v>20</v>
+      </c>
+      <c r="AT12">
+        <v>13</v>
+      </c>
+      <c r="AU12">
+        <v>7.6</v>
+      </c>
+      <c r="AV12">
+        <v>10</v>
+      </c>
+      <c r="AW12">
+        <v>19</v>
+      </c>
+      <c r="AX12">
+        <v>21</v>
+      </c>
+      <c r="AY12">
+        <v>12.5</v>
+      </c>
+      <c r="AZ12">
+        <v>14.5</v>
+      </c>
+      <c r="BA12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB12">
+        <v>9.4</v>
+      </c>
+      <c r="BC12">
+        <v>30</v>
+      </c>
+      <c r="BD12">
+        <v>36</v>
+      </c>
+      <c r="BE12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG12">
+        <v>12</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>3.1</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>6.4</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>5.2</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>4.2</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13">
+        <v>1.51</v>
+      </c>
+      <c r="G13">
+        <v>1.53</v>
+      </c>
+      <c r="H13">
+        <v>6.2</v>
+      </c>
+      <c r="I13">
+        <v>6.8</v>
+      </c>
+      <c r="J13">
+        <v>5.1</v>
+      </c>
+      <c r="K13">
+        <v>5.3</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.02</v>
+      </c>
+      <c r="N13">
+        <v>6.6</v>
+      </c>
+      <c r="O13">
+        <v>1.16</v>
+      </c>
+      <c r="P13">
+        <v>2.92</v>
+      </c>
+      <c r="Q13">
+        <v>1.48</v>
+      </c>
+      <c r="R13">
+        <v>1.77</v>
+      </c>
+      <c r="S13">
+        <v>2.24</v>
+      </c>
+      <c r="T13">
+        <v>1.64</v>
+      </c>
+      <c r="U13">
+        <v>2.48</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>34</v>
+      </c>
+      <c r="Y13">
+        <v>34</v>
+      </c>
+      <c r="Z13">
+        <v>75</v>
+      </c>
+      <c r="AA13">
+        <v>190</v>
+      </c>
+      <c r="AB13">
+        <v>13.5</v>
+      </c>
+      <c r="AC13">
+        <v>13</v>
+      </c>
+      <c r="AD13">
+        <v>25</v>
+      </c>
+      <c r="AE13">
+        <v>85</v>
+      </c>
+      <c r="AF13">
+        <v>12</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+      <c r="AH13">
+        <v>20</v>
+      </c>
+      <c r="AI13">
+        <v>70</v>
+      </c>
+      <c r="AJ13">
+        <v>15.5</v>
+      </c>
+      <c r="AK13">
+        <v>14.5</v>
+      </c>
+      <c r="AL13">
+        <v>26</v>
+      </c>
+      <c r="AM13">
+        <v>85</v>
+      </c>
+      <c r="AN13">
+        <v>5.2</v>
+      </c>
+      <c r="AO13">
+        <v>65</v>
+      </c>
+      <c r="AP13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR13">
+        <v>10.5</v>
+      </c>
+      <c r="AS13">
+        <v>11.5</v>
+      </c>
+      <c r="AT13">
+        <v>11.5</v>
+      </c>
+      <c r="AU13">
+        <v>11.5</v>
+      </c>
+      <c r="AV13">
+        <v>20</v>
+      </c>
+      <c r="AW13">
+        <v>11</v>
+      </c>
+      <c r="AX13">
+        <v>10.5</v>
+      </c>
+      <c r="AY13">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13">
+        <v>16.5</v>
+      </c>
+      <c r="BA13">
+        <v>10.5</v>
+      </c>
+      <c r="BB13">
+        <v>14</v>
+      </c>
+      <c r="BC13">
+        <v>13</v>
+      </c>
+      <c r="BD13">
+        <v>20</v>
+      </c>
+      <c r="BE13">
+        <v>11</v>
+      </c>
+      <c r="BF13">
+        <v>4.8</v>
+      </c>
+      <c r="BG13">
+        <v>10.5</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>3.95</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>6.8</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>3.65</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>6.4</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>11</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>7.4</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>6.6</v>
+      </c>
+      <c r="H14">
+        <v>1.66</v>
+      </c>
+      <c r="I14">
+        <v>1.69</v>
+      </c>
+      <c r="J14">
+        <v>4.1</v>
+      </c>
+      <c r="K14">
+        <v>4.2</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.64</v>
+      </c>
+      <c r="Q14">
+        <v>2.4</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>2.32</v>
+      </c>
+      <c r="U14">
+        <v>1.65</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>10.5</v>
+      </c>
+      <c r="Y14">
+        <v>6.2</v>
+      </c>
+      <c r="Z14">
+        <v>8.6</v>
+      </c>
+      <c r="AA14">
+        <v>17</v>
+      </c>
+      <c r="AB14">
+        <v>16.5</v>
+      </c>
+      <c r="AC14">
+        <v>10.5</v>
+      </c>
+      <c r="AD14">
+        <v>11</v>
+      </c>
+      <c r="AE14">
+        <v>26</v>
+      </c>
+      <c r="AF14">
+        <v>60</v>
+      </c>
+      <c r="AG14">
+        <v>34</v>
+      </c>
+      <c r="AH14">
+        <v>42</v>
+      </c>
+      <c r="AI14">
+        <v>75</v>
+      </c>
+      <c r="AJ14">
+        <v>290</v>
+      </c>
+      <c r="AK14">
+        <v>150</v>
+      </c>
+      <c r="AL14">
+        <v>160</v>
+      </c>
+      <c r="AM14">
+        <v>270</v>
+      </c>
+      <c r="AN14">
+        <v>300</v>
+      </c>
+      <c r="AO14">
+        <v>16</v>
+      </c>
+      <c r="AP14">
+        <v>9</v>
+      </c>
+      <c r="AQ14">
+        <v>5.4</v>
+      </c>
+      <c r="AR14">
+        <v>7.4</v>
+      </c>
+      <c r="AS14">
+        <v>14.5</v>
+      </c>
+      <c r="AT14">
+        <v>13.5</v>
+      </c>
+      <c r="AU14">
+        <v>7.8</v>
+      </c>
+      <c r="AV14">
+        <v>9.4</v>
+      </c>
+      <c r="AW14">
+        <v>19</v>
+      </c>
+      <c r="AX14">
+        <v>8.6</v>
+      </c>
+      <c r="AY14">
+        <v>19.5</v>
+      </c>
+      <c r="AZ14">
+        <v>21</v>
+      </c>
+      <c r="BA14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC14">
+        <v>9.4</v>
+      </c>
+      <c r="BD14">
+        <v>9.6</v>
+      </c>
+      <c r="BE14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG14">
+        <v>13.5</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="124">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,12 @@
     <t>Brazilian Serie B</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
@@ -292,6 +298,12 @@
     <t>Novorizontino</t>
   </si>
   <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>Cayman Islands</t>
+  </si>
+  <si>
     <t>Internacional de Bogotá</t>
   </si>
   <si>
@@ -307,12 +319,12 @@
     <t>Cyprus</t>
   </si>
   <si>
+    <t>Hungary</t>
+  </si>
+  <si>
     <t>France</t>
   </si>
   <si>
-    <t>Hungary</t>
-  </si>
-  <si>
     <t>Poland</t>
   </si>
   <si>
@@ -331,6 +343,12 @@
     <t>Goias</t>
   </si>
   <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
     <t>Once Caldas</t>
   </si>
   <si>
@@ -346,12 +364,12 @@
     <t>Armenia</t>
   </si>
   <si>
+    <t>Georgia</t>
+  </si>
+  <si>
     <t>Italy</t>
   </si>
   <si>
-    <t>Georgia</t>
-  </si>
-  <si>
     <t>Romania</t>
   </si>
   <si>
@@ -367,7 +385,7 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>2026-09-30 01:26:25</t>
+    <t>2026-09-30 03:37:03</t>
   </si>
 </sst>
 </file>
@@ -699,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -949,40 +967,40 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>6.8</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>3.15</v>
@@ -994,196 +1012,196 @@
         <v>1.67</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC2">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF2">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP2">
-        <v>1.7</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>1.93</v>
+        <v>14.5</v>
       </c>
       <c r="AR2">
-        <v>1.93</v>
+        <v>36</v>
       </c>
       <c r="AS2">
-        <v>1.93</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>6</v>
       </c>
       <c r="AU2">
+        <v>7.6</v>
+      </c>
+      <c r="AV2">
+        <v>17.5</v>
+      </c>
+      <c r="AW2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX2">
+        <v>8</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>18.5</v>
+      </c>
+      <c r="BA2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB2">
+        <v>14.5</v>
+      </c>
+      <c r="BC2">
+        <v>18</v>
+      </c>
+      <c r="BD2">
+        <v>34</v>
+      </c>
+      <c r="BE2">
+        <v>10</v>
+      </c>
+      <c r="BF2">
+        <v>12</v>
+      </c>
+      <c r="BG2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH2">
+        <v>3.4</v>
+      </c>
+      <c r="BI2">
+        <v>2.78</v>
+      </c>
+      <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>4.9</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>7.6</v>
+      </c>
+      <c r="BN2">
+        <v>4.2</v>
+      </c>
+      <c r="BO2">
+        <v>3.6</v>
+      </c>
+      <c r="BP2">
+        <v>14</v>
+      </c>
+      <c r="BQ2">
+        <v>5.2</v>
+      </c>
+      <c r="BR2">
+        <v>38</v>
+      </c>
+      <c r="BS2">
+        <v>6.4</v>
+      </c>
+      <c r="BT2">
+        <v>10</v>
+      </c>
+      <c r="BU2">
+        <v>4.5</v>
+      </c>
+      <c r="BV2">
+        <v>70</v>
+      </c>
+      <c r="BW2">
         <v>7</v>
       </c>
-      <c r="AV2">
-        <v>1.93</v>
-      </c>
-      <c r="AW2">
-        <v>1.93</v>
-      </c>
-      <c r="AX2">
-        <v>7.4</v>
-      </c>
-      <c r="AY2">
-        <v>7.4</v>
-      </c>
-      <c r="AZ2">
-        <v>1.93</v>
-      </c>
-      <c r="BA2">
-        <v>1.93</v>
-      </c>
-      <c r="BB2">
-        <v>1.93</v>
-      </c>
-      <c r="BC2">
-        <v>1.79</v>
-      </c>
-      <c r="BD2">
-        <v>1.93</v>
-      </c>
-      <c r="BE2">
-        <v>1.93</v>
-      </c>
-      <c r="BF2">
-        <v>9</v>
-      </c>
-      <c r="BG2">
-        <v>1.93</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.29</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.01</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.43</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.01</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.01</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
-      <c r="BU2">
-        <v>1.01</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.01</v>
-      </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1191,241 +1209,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>2.52</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="O3">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
         <v>21</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB3">
+        <v>19</v>
+      </c>
+      <c r="AC3">
+        <v>11</v>
+      </c>
+      <c r="AD3">
+        <v>13.5</v>
+      </c>
+      <c r="AE3">
+        <v>26</v>
+      </c>
+      <c r="AF3">
+        <v>28</v>
+      </c>
+      <c r="AG3">
+        <v>16</v>
+      </c>
+      <c r="AH3">
+        <v>17.5</v>
+      </c>
+      <c r="AI3">
+        <v>36</v>
+      </c>
+      <c r="AJ3">
+        <v>55</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>40</v>
+      </c>
+      <c r="AM3">
+        <v>70</v>
+      </c>
+      <c r="AN3">
         <v>24</v>
       </c>
-      <c r="AC3">
-        <v>7.6</v>
-      </c>
-      <c r="AD3">
-        <v>29</v>
-      </c>
-      <c r="AE3">
-        <v>40</v>
-      </c>
-      <c r="AF3">
-        <v>1000</v>
-      </c>
-      <c r="AG3">
-        <v>1000</v>
-      </c>
-      <c r="AH3">
-        <v>18</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>44</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>42</v>
-      </c>
       <c r="AO3">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="AP3">
-        <v>1.99</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>1.83</v>
+        <v>12</v>
       </c>
       <c r="AR3">
-        <v>1.97</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="AT3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AU3">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>2.06</v>
+        <v>19.5</v>
       </c>
       <c r="AX3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AY3">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>1.94</v>
+        <v>13</v>
       </c>
       <c r="BA3">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="BB3">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="BC3">
-        <v>2.06</v>
+        <v>4.5</v>
       </c>
       <c r="BD3">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="BE3">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="BF3">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="BG3">
-        <v>2.04</v>
+        <v>3.85</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1433,241 +1451,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F4">
-        <v>1.55</v>
+        <v>13.5</v>
       </c>
       <c r="G4">
-        <v>1.59</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>1.15</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J4">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="K4">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>4.7</v>
+      </c>
+      <c r="O4">
         <v>1.2</v>
       </c>
-      <c r="M4">
-        <v>1.02</v>
-      </c>
-      <c r="N4">
-        <v>7.6</v>
-      </c>
-      <c r="O4">
-        <v>1.14</v>
-      </c>
       <c r="P4">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="R4">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="T4">
-        <v>1.54</v>
+        <v>2.54</v>
       </c>
       <c r="U4">
-        <v>2.66</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="W4">
-        <v>2.7</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Y4">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>15.5</v>
+        <v>75</v>
       </c>
       <c r="AC4">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AD4">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
+        <v>17</v>
+      </c>
+      <c r="AF4">
+        <v>380</v>
+      </c>
+      <c r="AG4">
+        <v>130</v>
+      </c>
+      <c r="AH4">
+        <v>65</v>
+      </c>
+      <c r="AI4">
         <v>70</v>
       </c>
-      <c r="AF4">
-        <v>14</v>
-      </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
-        <v>17</v>
-      </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>23</v>
+        <v>580</v>
       </c>
       <c r="AM4">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="AN4">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>44</v>
+        <v>4.4</v>
       </c>
       <c r="AP4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AQ4">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AR4">
-        <v>28</v>
+        <v>5.3</v>
       </c>
       <c r="AS4">
-        <v>42</v>
+        <v>5.9</v>
       </c>
       <c r="AT4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AU4">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AV4">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="AX4">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="BA4">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BC4">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BD4">
-        <v>19.5</v>
+        <v>9</v>
       </c>
       <c r="BE4">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>25</v>
+        <v>3.15</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1675,518 +1693,518 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
         <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F5">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="G5">
+        <v>3.15</v>
+      </c>
+      <c r="H5">
+        <v>2.74</v>
+      </c>
+      <c r="I5">
+        <v>2.88</v>
+      </c>
+      <c r="J5">
+        <v>3.05</v>
+      </c>
+      <c r="K5">
+        <v>3.25</v>
+      </c>
+      <c r="L5">
+        <v>1.02</v>
+      </c>
+      <c r="M5">
+        <v>1.09</v>
+      </c>
+      <c r="N5">
+        <v>3.4</v>
+      </c>
+      <c r="O5">
+        <v>1.37</v>
+      </c>
+      <c r="P5">
+        <v>1.82</v>
+      </c>
+      <c r="Q5">
+        <v>2.06</v>
+      </c>
+      <c r="R5">
+        <v>1.32</v>
+      </c>
+      <c r="S5">
+        <v>3.65</v>
+      </c>
+      <c r="T5">
         <v>1.79</v>
       </c>
-      <c r="H5">
-        <v>5.7</v>
-      </c>
-      <c r="I5">
+      <c r="U5">
+        <v>2.12</v>
+      </c>
+      <c r="V5">
+        <v>1.53</v>
+      </c>
+      <c r="W5">
+        <v>1.46</v>
+      </c>
+      <c r="X5">
+        <v>14</v>
+      </c>
+      <c r="Y5">
+        <v>11</v>
+      </c>
+      <c r="Z5">
+        <v>19</v>
+      </c>
+      <c r="AA5">
+        <v>50</v>
+      </c>
+      <c r="AB5">
+        <v>13.5</v>
+      </c>
+      <c r="AC5">
+        <v>7.2</v>
+      </c>
+      <c r="AD5">
+        <v>14.5</v>
+      </c>
+      <c r="AE5">
+        <v>34</v>
+      </c>
+      <c r="AF5">
+        <v>24</v>
+      </c>
+      <c r="AG5">
+        <v>15.5</v>
+      </c>
+      <c r="AH5">
+        <v>17.5</v>
+      </c>
+      <c r="AI5">
+        <v>55</v>
+      </c>
+      <c r="AJ5">
+        <v>60</v>
+      </c>
+      <c r="AK5">
+        <v>38</v>
+      </c>
+      <c r="AL5">
+        <v>60</v>
+      </c>
+      <c r="AM5">
+        <v>110</v>
+      </c>
+      <c r="AN5">
+        <v>40</v>
+      </c>
+      <c r="AO5">
+        <v>32</v>
+      </c>
+      <c r="AP5">
+        <v>10</v>
+      </c>
+      <c r="AQ5">
+        <v>9.6</v>
+      </c>
+      <c r="AR5">
+        <v>15.5</v>
+      </c>
+      <c r="AS5">
+        <v>6.4</v>
+      </c>
+      <c r="AT5">
+        <v>10.5</v>
+      </c>
+      <c r="AU5">
+        <v>6.2</v>
+      </c>
+      <c r="AV5">
+        <v>11</v>
+      </c>
+      <c r="AW5">
+        <v>6</v>
+      </c>
+      <c r="AX5">
+        <v>17</v>
+      </c>
+      <c r="AY5">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5">
+        <v>14.5</v>
+      </c>
+      <c r="BA5">
         <v>6.6</v>
       </c>
-      <c r="J5">
-        <v>3.7</v>
-      </c>
-      <c r="K5">
-        <v>4.1</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="BB5">
+        <v>6.6</v>
+      </c>
+      <c r="BC5">
+        <v>6.2</v>
+      </c>
+      <c r="BD5">
+        <v>6.6</v>
+      </c>
+      <c r="BE5">
+        <v>7</v>
+      </c>
+      <c r="BF5">
+        <v>6.2</v>
+      </c>
+      <c r="BG5">
+        <v>6</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.84</v>
+      </c>
+      <c r="BJ5">
+        <v>13.5</v>
+      </c>
+      <c r="BK5">
+        <v>1.62</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.84</v>
+      </c>
+      <c r="BN5">
+        <v>8</v>
+      </c>
+      <c r="BO5">
+        <v>4.3</v>
+      </c>
+      <c r="BP5">
+        <v>32</v>
+      </c>
+      <c r="BQ5">
+        <v>1.74</v>
+      </c>
+      <c r="BR5">
+        <v>50</v>
+      </c>
+      <c r="BS5">
+        <v>1.78</v>
+      </c>
+      <c r="BT5">
+        <v>7.6</v>
+      </c>
+      <c r="BU5">
+        <v>3.85</v>
+      </c>
+      <c r="BV5">
+        <v>30</v>
+      </c>
+      <c r="BW5">
+        <v>1.74</v>
+      </c>
+      <c r="BX5">
+        <v>50</v>
+      </c>
+      <c r="BY5">
+        <v>1.78</v>
+      </c>
+      <c r="BZ5">
+        <v>46</v>
+      </c>
+      <c r="CA5">
         <v>1.77</v>
       </c>
-      <c r="Q5">
-        <v>2.1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5">
-        <v>0</v>
-      </c>
-      <c r="BE5">
-        <v>0</v>
-      </c>
-      <c r="BF5">
-        <v>0</v>
-      </c>
-      <c r="BG5">
-        <v>0</v>
-      </c>
-      <c r="BH5">
-        <v>0</v>
-      </c>
-      <c r="BI5">
-        <v>0</v>
-      </c>
-      <c r="BJ5">
-        <v>0</v>
-      </c>
-      <c r="BK5">
-        <v>0</v>
-      </c>
-      <c r="BL5">
-        <v>0</v>
-      </c>
-      <c r="BM5">
-        <v>0</v>
-      </c>
-      <c r="BN5">
-        <v>0</v>
-      </c>
-      <c r="BO5">
-        <v>0</v>
-      </c>
-      <c r="BP5">
-        <v>0</v>
-      </c>
-      <c r="BQ5">
-        <v>0</v>
-      </c>
-      <c r="BR5">
-        <v>0</v>
-      </c>
-      <c r="BS5">
-        <v>0</v>
-      </c>
-      <c r="BT5">
-        <v>0</v>
-      </c>
-      <c r="BU5">
-        <v>0</v>
-      </c>
-      <c r="BV5">
-        <v>0</v>
-      </c>
-      <c r="BW5">
-        <v>0</v>
-      </c>
-      <c r="BX5">
-        <v>0</v>
-      </c>
-      <c r="BY5">
-        <v>0</v>
-      </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
       <c r="CB5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
         <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F6">
+        <v>1.55</v>
+      </c>
+      <c r="G6">
+        <v>1.58</v>
+      </c>
+      <c r="H6">
+        <v>5.8</v>
+      </c>
+      <c r="I6">
+        <v>6.2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5.4</v>
+      </c>
+      <c r="L6">
+        <v>1.23</v>
+      </c>
+      <c r="M6">
+        <v>1.02</v>
+      </c>
+      <c r="N6">
+        <v>7.8</v>
+      </c>
+      <c r="O6">
+        <v>1.14</v>
+      </c>
+      <c r="P6">
+        <v>3.25</v>
+      </c>
+      <c r="Q6">
+        <v>1.41</v>
+      </c>
+      <c r="R6">
+        <v>1.92</v>
+      </c>
+      <c r="S6">
+        <v>2.02</v>
+      </c>
+      <c r="T6">
+        <v>1.54</v>
+      </c>
+      <c r="U6">
+        <v>2.68</v>
+      </c>
+      <c r="V6">
+        <v>1.19</v>
+      </c>
+      <c r="W6">
+        <v>2.7</v>
+      </c>
+      <c r="X6">
+        <v>38</v>
+      </c>
+      <c r="Y6">
+        <v>38</v>
+      </c>
+      <c r="Z6">
+        <v>360</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>15.5</v>
+      </c>
+      <c r="AC6">
+        <v>13.5</v>
+      </c>
+      <c r="AD6">
+        <v>24</v>
+      </c>
+      <c r="AE6">
+        <v>75</v>
+      </c>
+      <c r="AF6">
+        <v>14</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>17</v>
+      </c>
+      <c r="AI6">
+        <v>65</v>
+      </c>
+      <c r="AJ6">
+        <v>17</v>
+      </c>
+      <c r="AK6">
+        <v>14.5</v>
+      </c>
+      <c r="AL6">
+        <v>23</v>
+      </c>
+      <c r="AM6">
+        <v>420</v>
+      </c>
+      <c r="AN6">
+        <v>4.8</v>
+      </c>
+      <c r="AO6">
+        <v>44</v>
+      </c>
+      <c r="AP6">
+        <v>24</v>
+      </c>
+      <c r="AQ6">
+        <v>21</v>
+      </c>
+      <c r="AR6">
+        <v>28</v>
+      </c>
+      <c r="AS6">
+        <v>42</v>
+      </c>
+      <c r="AT6">
+        <v>14</v>
+      </c>
+      <c r="AU6">
+        <v>11.5</v>
+      </c>
+      <c r="AV6">
+        <v>21</v>
+      </c>
+      <c r="AW6">
+        <v>40</v>
+      </c>
+      <c r="AX6">
+        <v>12.5</v>
+      </c>
+      <c r="AY6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>15.5</v>
+      </c>
+      <c r="BA6">
+        <v>32</v>
+      </c>
+      <c r="BB6">
+        <v>15</v>
+      </c>
+      <c r="BC6">
+        <v>12.5</v>
+      </c>
+      <c r="BD6">
+        <v>19.5</v>
+      </c>
+      <c r="BE6">
+        <v>36</v>
+      </c>
+      <c r="BF6">
         <v>4.5</v>
       </c>
-      <c r="G6">
-        <v>5.1</v>
-      </c>
-      <c r="H6">
-        <v>1.9</v>
-      </c>
-      <c r="I6">
-        <v>1.99</v>
-      </c>
-      <c r="J6">
-        <v>3.6</v>
-      </c>
-      <c r="K6">
-        <v>3.7</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>1.71</v>
-      </c>
-      <c r="Q6">
-        <v>2.22</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6">
-        <v>0</v>
-      </c>
-      <c r="BE6">
-        <v>0</v>
-      </c>
-      <c r="BF6">
-        <v>0</v>
-      </c>
       <c r="BG6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="G7">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="H7">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="I7">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2201,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q7">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2213,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2225,112 +2243,112 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AO7">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ7">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AT7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV7">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AW7">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX7">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA7">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BB7">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BC7">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD7">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BH7">
         <v>0</v>
@@ -2393,72 +2411,72 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F8">
-        <v>1.44</v>
+        <v>4.6</v>
       </c>
       <c r="G8">
-        <v>1.45</v>
+        <v>5.1</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>1.89</v>
       </c>
       <c r="I8">
-        <v>8.199999999999999</v>
+        <v>1.94</v>
       </c>
       <c r="J8">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>2.96</v>
+        <v>1.71</v>
       </c>
       <c r="Q8">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2467,240 +2485,240 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BG8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI8">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ8">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU8">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F9">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="G9">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="H9">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="J9">
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q9">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T9">
         <v>1.95</v>
       </c>
       <c r="U9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2709,240 +2727,240 @@
         <v>0</v>
       </c>
       <c r="X9">
+        <v>12.5</v>
+      </c>
+      <c r="Y9">
+        <v>12</v>
+      </c>
+      <c r="Z9">
+        <v>26</v>
+      </c>
+      <c r="AA9">
+        <v>80</v>
+      </c>
+      <c r="AB9">
+        <v>9</v>
+      </c>
+      <c r="AC9">
+        <v>7.8</v>
+      </c>
+      <c r="AD9">
+        <v>15.5</v>
+      </c>
+      <c r="AE9">
+        <v>55</v>
+      </c>
+      <c r="AF9">
         <v>14</v>
       </c>
-      <c r="Y9">
-        <v>13</v>
-      </c>
-      <c r="Z9">
+      <c r="AG9">
+        <v>12</v>
+      </c>
+      <c r="AH9">
+        <v>21</v>
+      </c>
+      <c r="AI9">
+        <v>65</v>
+      </c>
+      <c r="AJ9">
+        <v>38</v>
+      </c>
+      <c r="AK9">
         <v>29</v>
       </c>
-      <c r="AA9">
-        <v>110</v>
-      </c>
-      <c r="AB9">
-        <v>8.6</v>
-      </c>
-      <c r="AC9">
-        <v>8</v>
-      </c>
-      <c r="AD9">
-        <v>16</v>
-      </c>
-      <c r="AE9">
-        <v>70</v>
-      </c>
-      <c r="AF9">
-        <v>13</v>
-      </c>
-      <c r="AG9">
-        <v>11</v>
-      </c>
-      <c r="AH9">
-        <v>25</v>
-      </c>
-      <c r="AI9">
-        <v>75</v>
-      </c>
-      <c r="AJ9">
-        <v>29</v>
-      </c>
-      <c r="AK9">
-        <v>28</v>
-      </c>
       <c r="AL9">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN9">
         <v>25</v>
       </c>
       <c r="AO9">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP9">
         <v>10.5</v>
       </c>
       <c r="AQ9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU9">
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW9">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BC9">
         <v>19.5</v>
       </c>
       <c r="BD9">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="BE9">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF9">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI9">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK9">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO9">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU9">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F10">
-        <v>1.59</v>
+        <v>2.14</v>
       </c>
       <c r="G10">
-        <v>1.6</v>
+        <v>2.22</v>
       </c>
       <c r="H10">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
+        <v>3.35</v>
+      </c>
+      <c r="O10">
+        <v>1.39</v>
+      </c>
+      <c r="P10">
+        <v>1.81</v>
+      </c>
+      <c r="Q10">
+        <v>2.18</v>
+      </c>
+      <c r="R10">
+        <v>1.3</v>
+      </c>
+      <c r="S10">
         <v>4.1</v>
       </c>
-      <c r="O10">
-        <v>1.29</v>
-      </c>
-      <c r="P10">
-        <v>2.08</v>
-      </c>
-      <c r="Q10">
-        <v>1.86</v>
-      </c>
-      <c r="R10">
-        <v>1.41</v>
-      </c>
-      <c r="S10">
-        <v>3.2</v>
-      </c>
       <c r="T10">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U10">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2951,124 +2969,124 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y10">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AA10">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="AB10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD10">
+        <v>16</v>
+      </c>
+      <c r="AE10">
+        <v>70</v>
+      </c>
+      <c r="AF10">
+        <v>13</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
         <v>25</v>
       </c>
-      <c r="AE10">
-        <v>110</v>
-      </c>
-      <c r="AF10">
-        <v>9.4</v>
-      </c>
-      <c r="AG10">
-        <v>10</v>
-      </c>
-      <c r="AH10">
-        <v>23</v>
-      </c>
       <c r="AI10">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AK10">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AL10">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM10">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN10">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AO10">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AP10">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AR10">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AS10">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AT10">
         <v>7.6</v>
       </c>
       <c r="AU10">
+        <v>7</v>
+      </c>
+      <c r="AV10">
+        <v>14</v>
+      </c>
+      <c r="AW10">
+        <v>8.6</v>
+      </c>
+      <c r="AX10">
+        <v>11</v>
+      </c>
+      <c r="AY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>17.5</v>
+      </c>
+      <c r="BA10">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV10">
-        <v>21</v>
-      </c>
-      <c r="AW10">
-        <v>13.5</v>
-      </c>
-      <c r="AX10">
-        <v>8.6</v>
-      </c>
-      <c r="AY10">
-        <v>9</v>
-      </c>
-      <c r="AZ10">
-        <v>19</v>
-      </c>
-      <c r="BA10">
-        <v>13</v>
-      </c>
       <c r="BB10">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BC10">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BE10">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF10">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BG10">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="BH10">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3080,13 +3098,13 @@
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3098,7 +3116,7 @@
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3119,198 +3137,198 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11">
+        <v>1.44</v>
+      </c>
+      <c r="G11">
+        <v>1.45</v>
+      </c>
+      <c r="H11">
+        <v>7.8</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>5.4</v>
+      </c>
+      <c r="K11">
+        <v>5.6</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.03</v>
+      </c>
+      <c r="N11">
+        <v>6.6</v>
+      </c>
+      <c r="O11">
+        <v>1.16</v>
+      </c>
+      <c r="P11">
+        <v>2.9</v>
+      </c>
+      <c r="Q11">
+        <v>1.51</v>
+      </c>
+      <c r="R11">
+        <v>1.78</v>
+      </c>
+      <c r="S11">
+        <v>2.22</v>
+      </c>
+      <c r="T11">
+        <v>1.69</v>
+      </c>
+      <c r="U11">
+        <v>2.44</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>34</v>
+      </c>
+      <c r="Y11">
+        <v>36</v>
+      </c>
+      <c r="Z11">
+        <v>75</v>
+      </c>
+      <c r="AA11">
+        <v>240</v>
+      </c>
+      <c r="AB11">
+        <v>13</v>
+      </c>
+      <c r="AC11">
+        <v>13</v>
+      </c>
+      <c r="AD11">
+        <v>30</v>
+      </c>
+      <c r="AE11">
+        <v>95</v>
+      </c>
+      <c r="AF11">
+        <v>11.5</v>
+      </c>
+      <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
+        <v>21</v>
+      </c>
+      <c r="AI11">
+        <v>75</v>
+      </c>
+      <c r="AJ11">
+        <v>14.5</v>
+      </c>
+      <c r="AK11">
+        <v>14</v>
+      </c>
+      <c r="AL11">
+        <v>27</v>
+      </c>
+      <c r="AM11">
+        <v>80</v>
+      </c>
+      <c r="AN11">
+        <v>4.9</v>
+      </c>
+      <c r="AO11">
         <v>90</v>
       </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11">
-        <v>1.97</v>
-      </c>
-      <c r="G11">
-        <v>1.99</v>
-      </c>
-      <c r="H11">
-        <v>4.6</v>
-      </c>
-      <c r="I11">
-        <v>4.8</v>
-      </c>
-      <c r="J11">
-        <v>3.55</v>
-      </c>
-      <c r="K11">
-        <v>3.6</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>1.1</v>
-      </c>
-      <c r="N11">
-        <v>2.94</v>
-      </c>
-      <c r="O11">
-        <v>1.48</v>
-      </c>
-      <c r="P11">
-        <v>1.66</v>
-      </c>
-      <c r="Q11">
-        <v>2.42</v>
-      </c>
-      <c r="R11">
-        <v>1.24</v>
-      </c>
-      <c r="S11">
-        <v>4.9</v>
-      </c>
-      <c r="T11">
-        <v>2.16</v>
-      </c>
-      <c r="U11">
-        <v>1.79</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>11</v>
-      </c>
-      <c r="Y11">
-        <v>13</v>
-      </c>
-      <c r="Z11">
-        <v>36</v>
-      </c>
-      <c r="AA11">
-        <v>140</v>
-      </c>
-      <c r="AB11">
-        <v>7</v>
-      </c>
-      <c r="AC11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11">
-        <v>19</v>
-      </c>
-      <c r="AE11">
-        <v>85</v>
-      </c>
-      <c r="AF11">
+      <c r="AP11">
+        <v>10</v>
+      </c>
+      <c r="AQ11">
+        <v>10</v>
+      </c>
+      <c r="AR11">
         <v>10.5</v>
-      </c>
-      <c r="AG11">
-        <v>11</v>
-      </c>
-      <c r="AH11">
-        <v>26</v>
-      </c>
-      <c r="AI11">
-        <v>90</v>
-      </c>
-      <c r="AJ11">
-        <v>24</v>
-      </c>
-      <c r="AK11">
-        <v>26</v>
-      </c>
-      <c r="AL11">
-        <v>55</v>
-      </c>
-      <c r="AM11">
-        <v>210</v>
-      </c>
-      <c r="AN11">
-        <v>21</v>
-      </c>
-      <c r="AO11">
-        <v>130</v>
-      </c>
-      <c r="AP11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ11">
-        <v>11</v>
-      </c>
-      <c r="AR11">
-        <v>9.800000000000001</v>
       </c>
       <c r="AS11">
         <v>12</v>
       </c>
       <c r="AT11">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AV11">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="AW11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
         <v>9.4</v>
       </c>
-      <c r="AY11">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ11">
+        <v>17.5</v>
+      </c>
+      <c r="BA11">
+        <v>10.5</v>
+      </c>
+      <c r="BB11">
+        <v>12.5</v>
+      </c>
+      <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
         <v>21</v>
       </c>
-      <c r="BA11">
-        <v>11.5</v>
-      </c>
-      <c r="BB11">
-        <v>20</v>
-      </c>
-      <c r="BC11">
-        <v>21</v>
-      </c>
-      <c r="BD11">
+      <c r="BE11">
         <v>10.5</v>
       </c>
-      <c r="BE11">
-        <v>12.5</v>
-      </c>
       <c r="BF11">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH11">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3322,13 +3340,13 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BR11">
         <v>1000</v>
@@ -3340,7 +3358,7 @@
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3361,314 +3379,314 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F12">
-        <v>3.35</v>
+        <v>1.59</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="H12">
-        <v>2.22</v>
+        <v>6.4</v>
       </c>
       <c r="I12">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q12">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S12">
+        <v>3.2</v>
+      </c>
+      <c r="T12">
+        <v>1.96</v>
+      </c>
+      <c r="U12">
+        <v>1.97</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>17</v>
+      </c>
+      <c r="Y12">
+        <v>22</v>
+      </c>
+      <c r="Z12">
+        <v>60</v>
+      </c>
+      <c r="AA12">
+        <v>210</v>
+      </c>
+      <c r="AB12">
+        <v>8.4</v>
+      </c>
+      <c r="AC12">
+        <v>10</v>
+      </c>
+      <c r="AD12">
+        <v>26</v>
+      </c>
+      <c r="AE12">
+        <v>110</v>
+      </c>
+      <c r="AF12">
+        <v>9.4</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+      <c r="AH12">
+        <v>23</v>
+      </c>
+      <c r="AI12">
+        <v>100</v>
+      </c>
+      <c r="AJ12">
+        <v>15</v>
+      </c>
+      <c r="AK12">
+        <v>17</v>
+      </c>
+      <c r="AL12">
+        <v>42</v>
+      </c>
+      <c r="AM12">
+        <v>140</v>
+      </c>
+      <c r="AN12">
+        <v>8.6</v>
+      </c>
+      <c r="AO12">
+        <v>140</v>
+      </c>
+      <c r="AP12">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12">
+        <v>19</v>
+      </c>
+      <c r="AR12">
+        <v>12</v>
+      </c>
+      <c r="AS12">
+        <v>14.5</v>
+      </c>
+      <c r="AT12">
+        <v>7.6</v>
+      </c>
+      <c r="AU12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV12">
+        <v>21</v>
+      </c>
+      <c r="AW12">
+        <v>13.5</v>
+      </c>
+      <c r="AX12">
+        <v>8.4</v>
+      </c>
+      <c r="AY12">
+        <v>9</v>
+      </c>
+      <c r="AZ12">
+        <v>19</v>
+      </c>
+      <c r="BA12">
+        <v>13.5</v>
+      </c>
+      <c r="BB12">
+        <v>13</v>
+      </c>
+      <c r="BC12">
+        <v>15</v>
+      </c>
+      <c r="BD12">
+        <v>10.5</v>
+      </c>
+      <c r="BE12">
+        <v>14</v>
+      </c>
+      <c r="BF12">
+        <v>7.8</v>
+      </c>
+      <c r="BG12">
+        <v>14</v>
+      </c>
+      <c r="BH12">
+        <v>4</v>
+      </c>
+      <c r="BI12">
         <v>3</v>
       </c>
-      <c r="T12">
-        <v>1.69</v>
-      </c>
-      <c r="U12">
-        <v>2.34</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>18.5</v>
-      </c>
-      <c r="Y12">
-        <v>12</v>
-      </c>
-      <c r="Z12">
-        <v>15.5</v>
-      </c>
-      <c r="AA12">
-        <v>30</v>
-      </c>
-      <c r="AB12">
-        <v>15.5</v>
-      </c>
-      <c r="AC12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12">
-        <v>11.5</v>
-      </c>
-      <c r="AE12">
-        <v>23</v>
-      </c>
-      <c r="AF12">
-        <v>27</v>
-      </c>
-      <c r="AG12">
-        <v>15</v>
-      </c>
-      <c r="AH12">
-        <v>17</v>
-      </c>
-      <c r="AI12">
-        <v>40</v>
-      </c>
-      <c r="AJ12">
-        <v>70</v>
-      </c>
-      <c r="AK12">
-        <v>44</v>
-      </c>
-      <c r="AL12">
-        <v>46</v>
-      </c>
-      <c r="AM12">
-        <v>95</v>
-      </c>
-      <c r="AN12">
-        <v>34</v>
-      </c>
-      <c r="AO12">
-        <v>14.5</v>
-      </c>
-      <c r="AP12">
-        <v>16</v>
-      </c>
-      <c r="AQ12">
-        <v>10.5</v>
-      </c>
-      <c r="AR12">
-        <v>13.5</v>
-      </c>
-      <c r="AS12">
-        <v>20</v>
-      </c>
-      <c r="AT12">
-        <v>13</v>
-      </c>
-      <c r="AU12">
-        <v>7.6</v>
-      </c>
-      <c r="AV12">
-        <v>10</v>
-      </c>
-      <c r="AW12">
-        <v>19</v>
-      </c>
-      <c r="AX12">
-        <v>21</v>
-      </c>
-      <c r="AY12">
-        <v>12.5</v>
-      </c>
-      <c r="AZ12">
-        <v>14.5</v>
-      </c>
-      <c r="BA12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB12">
-        <v>9.4</v>
-      </c>
-      <c r="BC12">
-        <v>30</v>
-      </c>
-      <c r="BD12">
-        <v>36</v>
-      </c>
-      <c r="BE12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG12">
-        <v>12</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>3.1</v>
-      </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F13">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="G13">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="H13">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="I13">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J13">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="N13">
-        <v>6.6</v>
+        <v>2.98</v>
       </c>
       <c r="O13">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="P13">
-        <v>2.92</v>
+        <v>1.66</v>
       </c>
       <c r="Q13">
-        <v>1.48</v>
+        <v>2.44</v>
       </c>
       <c r="R13">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="S13">
-        <v>2.24</v>
+        <v>4.9</v>
       </c>
       <c r="T13">
-        <v>1.64</v>
+        <v>2.16</v>
       </c>
       <c r="U13">
-        <v>2.48</v>
+        <v>1.81</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3677,417 +3695,901 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="Y13">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="Z13">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AA13">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AB13">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE13">
         <v>85</v>
       </c>
       <c r="AF13">
+        <v>10.5</v>
+      </c>
+      <c r="AG13">
+        <v>11</v>
+      </c>
+      <c r="AH13">
+        <v>26</v>
+      </c>
+      <c r="AI13">
+        <v>90</v>
+      </c>
+      <c r="AJ13">
+        <v>24</v>
+      </c>
+      <c r="AK13">
+        <v>25</v>
+      </c>
+      <c r="AL13">
+        <v>55</v>
+      </c>
+      <c r="AM13">
+        <v>210</v>
+      </c>
+      <c r="AN13">
+        <v>21</v>
+      </c>
+      <c r="AO13">
+        <v>130</v>
+      </c>
+      <c r="AP13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ13">
+        <v>11</v>
+      </c>
+      <c r="AR13">
+        <v>10</v>
+      </c>
+      <c r="AS13">
+        <v>12.5</v>
+      </c>
+      <c r="AT13">
+        <v>6.2</v>
+      </c>
+      <c r="AU13">
+        <v>7.2</v>
+      </c>
+      <c r="AV13">
+        <v>17</v>
+      </c>
+      <c r="AW13">
+        <v>11.5</v>
+      </c>
+      <c r="AX13">
+        <v>9.4</v>
+      </c>
+      <c r="AY13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13">
+        <v>21</v>
+      </c>
+      <c r="BA13">
         <v>12</v>
       </c>
-      <c r="AG13">
-        <v>10</v>
-      </c>
-      <c r="AH13">
+      <c r="BB13">
         <v>20</v>
       </c>
-      <c r="AI13">
-        <v>70</v>
-      </c>
-      <c r="AJ13">
-        <v>15.5</v>
-      </c>
-      <c r="AK13">
-        <v>14.5</v>
-      </c>
-      <c r="AL13">
-        <v>26</v>
-      </c>
-      <c r="AM13">
-        <v>85</v>
-      </c>
-      <c r="AN13">
-        <v>5.2</v>
-      </c>
-      <c r="AO13">
-        <v>65</v>
-      </c>
-      <c r="AP13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR13">
-        <v>10.5</v>
-      </c>
-      <c r="AS13">
-        <v>11.5</v>
-      </c>
-      <c r="AT13">
-        <v>11.5</v>
-      </c>
-      <c r="AU13">
-        <v>11.5</v>
-      </c>
-      <c r="AV13">
-        <v>20</v>
-      </c>
-      <c r="AW13">
+      <c r="BC13">
+        <v>21</v>
+      </c>
+      <c r="BD13">
         <v>11</v>
       </c>
-      <c r="AX13">
-        <v>10.5</v>
-      </c>
-      <c r="AY13">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13">
-        <v>16.5</v>
-      </c>
-      <c r="BA13">
-        <v>10.5</v>
-      </c>
-      <c r="BB13">
-        <v>14</v>
-      </c>
-      <c r="BC13">
+      <c r="BE13">
         <v>13</v>
       </c>
-      <c r="BD13">
-        <v>20</v>
-      </c>
-      <c r="BE13">
-        <v>11</v>
-      </c>
       <c r="BF13">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
       <c r="BG13">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI13">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14">
+        <v>3.3</v>
+      </c>
+      <c r="G14">
+        <v>3.45</v>
+      </c>
+      <c r="H14">
+        <v>2.24</v>
+      </c>
+      <c r="I14">
+        <v>2.32</v>
+      </c>
+      <c r="J14">
+        <v>3.7</v>
+      </c>
+      <c r="K14">
+        <v>3.8</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.05</v>
+      </c>
+      <c r="N14">
+        <v>4.5</v>
+      </c>
+      <c r="O14">
+        <v>1.26</v>
+      </c>
+      <c r="P14">
+        <v>2.18</v>
+      </c>
+      <c r="Q14">
+        <v>1.79</v>
+      </c>
+      <c r="R14">
+        <v>1.46</v>
+      </c>
+      <c r="S14">
+        <v>2.98</v>
+      </c>
+      <c r="T14">
+        <v>1.68</v>
+      </c>
+      <c r="U14">
+        <v>2.38</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>18.5</v>
+      </c>
+      <c r="Y14">
+        <v>12</v>
+      </c>
+      <c r="Z14">
+        <v>16</v>
+      </c>
+      <c r="AA14">
+        <v>32</v>
+      </c>
+      <c r="AB14">
+        <v>15.5</v>
+      </c>
+      <c r="AC14">
+        <v>8.6</v>
+      </c>
+      <c r="AD14">
+        <v>11.5</v>
+      </c>
+      <c r="AE14">
+        <v>23</v>
+      </c>
+      <c r="AF14">
+        <v>27</v>
+      </c>
+      <c r="AG14">
+        <v>15</v>
+      </c>
+      <c r="AH14">
+        <v>17</v>
+      </c>
+      <c r="AI14">
+        <v>38</v>
+      </c>
+      <c r="AJ14">
+        <v>70</v>
+      </c>
+      <c r="AK14">
+        <v>42</v>
+      </c>
+      <c r="AL14">
+        <v>46</v>
+      </c>
+      <c r="AM14">
         <v>90</v>
       </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14">
-        <v>6</v>
-      </c>
-      <c r="G14">
-        <v>6.6</v>
-      </c>
-      <c r="H14">
-        <v>1.66</v>
-      </c>
-      <c r="I14">
-        <v>1.69</v>
-      </c>
-      <c r="J14">
-        <v>4.1</v>
-      </c>
-      <c r="K14">
-        <v>4.2</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>1.64</v>
-      </c>
-      <c r="Q14">
-        <v>2.4</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>2.32</v>
-      </c>
-      <c r="U14">
-        <v>1.65</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
+      <c r="AN14">
+        <v>34</v>
+      </c>
+      <c r="AO14">
+        <v>15</v>
+      </c>
+      <c r="AP14">
+        <v>16</v>
+      </c>
+      <c r="AQ14">
         <v>10.5</v>
       </c>
-      <c r="Y14">
-        <v>6.2</v>
-      </c>
-      <c r="Z14">
-        <v>8.6</v>
-      </c>
-      <c r="AA14">
-        <v>17</v>
-      </c>
-      <c r="AB14">
-        <v>16.5</v>
-      </c>
-      <c r="AC14">
-        <v>10.5</v>
-      </c>
-      <c r="AD14">
-        <v>11</v>
-      </c>
-      <c r="AE14">
-        <v>26</v>
-      </c>
-      <c r="AF14">
-        <v>60</v>
-      </c>
-      <c r="AG14">
-        <v>34</v>
-      </c>
-      <c r="AH14">
-        <v>42</v>
-      </c>
-      <c r="AI14">
-        <v>75</v>
-      </c>
-      <c r="AJ14">
-        <v>290</v>
-      </c>
-      <c r="AK14">
-        <v>150</v>
-      </c>
-      <c r="AL14">
-        <v>160</v>
-      </c>
-      <c r="AM14">
-        <v>270</v>
-      </c>
-      <c r="AN14">
-        <v>300</v>
-      </c>
-      <c r="AO14">
-        <v>16</v>
-      </c>
-      <c r="AP14">
-        <v>9</v>
-      </c>
-      <c r="AQ14">
-        <v>5.4</v>
-      </c>
       <c r="AR14">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS14">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AT14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU14">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14">
         <v>19</v>
       </c>
       <c r="AX14">
+        <v>21</v>
+      </c>
+      <c r="AY14">
+        <v>12.5</v>
+      </c>
+      <c r="AZ14">
+        <v>14.5</v>
+      </c>
+      <c r="BA14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC14">
+        <v>8.4</v>
+      </c>
+      <c r="BD14">
         <v>8.6</v>
       </c>
-      <c r="AY14">
+      <c r="BE14">
+        <v>9.6</v>
+      </c>
+      <c r="BF14">
+        <v>8</v>
+      </c>
+      <c r="BG14">
+        <v>13</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>3.1</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>6.4</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>5.2</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>4.2</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15">
+        <v>1.51</v>
+      </c>
+      <c r="G15">
+        <v>1.53</v>
+      </c>
+      <c r="H15">
+        <v>6.4</v>
+      </c>
+      <c r="I15">
+        <v>6.8</v>
+      </c>
+      <c r="J15">
+        <v>5.1</v>
+      </c>
+      <c r="K15">
+        <v>5.3</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.02</v>
+      </c>
+      <c r="N15">
+        <v>6.6</v>
+      </c>
+      <c r="O15">
+        <v>1.16</v>
+      </c>
+      <c r="P15">
+        <v>2.92</v>
+      </c>
+      <c r="Q15">
+        <v>1.48</v>
+      </c>
+      <c r="R15">
+        <v>1.77</v>
+      </c>
+      <c r="S15">
+        <v>2.24</v>
+      </c>
+      <c r="T15">
+        <v>1.64</v>
+      </c>
+      <c r="U15">
+        <v>2.48</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>34</v>
+      </c>
+      <c r="Y15">
+        <v>34</v>
+      </c>
+      <c r="Z15">
+        <v>75</v>
+      </c>
+      <c r="AA15">
+        <v>190</v>
+      </c>
+      <c r="AB15">
+        <v>13.5</v>
+      </c>
+      <c r="AC15">
+        <v>13</v>
+      </c>
+      <c r="AD15">
+        <v>25</v>
+      </c>
+      <c r="AE15">
+        <v>85</v>
+      </c>
+      <c r="AF15">
+        <v>12</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+      <c r="AH15">
+        <v>20</v>
+      </c>
+      <c r="AI15">
+        <v>70</v>
+      </c>
+      <c r="AJ15">
+        <v>15.5</v>
+      </c>
+      <c r="AK15">
+        <v>14.5</v>
+      </c>
+      <c r="AL15">
+        <v>26</v>
+      </c>
+      <c r="AM15">
+        <v>85</v>
+      </c>
+      <c r="AN15">
+        <v>5.2</v>
+      </c>
+      <c r="AO15">
+        <v>65</v>
+      </c>
+      <c r="AP15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15">
+        <v>10.5</v>
+      </c>
+      <c r="AS15">
+        <v>11.5</v>
+      </c>
+      <c r="AT15">
+        <v>11.5</v>
+      </c>
+      <c r="AU15">
+        <v>11.5</v>
+      </c>
+      <c r="AV15">
+        <v>20</v>
+      </c>
+      <c r="AW15">
+        <v>11</v>
+      </c>
+      <c r="AX15">
+        <v>10.5</v>
+      </c>
+      <c r="AY15">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15">
+        <v>16.5</v>
+      </c>
+      <c r="BA15">
+        <v>10.5</v>
+      </c>
+      <c r="BB15">
+        <v>14</v>
+      </c>
+      <c r="BC15">
+        <v>13</v>
+      </c>
+      <c r="BD15">
+        <v>20</v>
+      </c>
+      <c r="BE15">
+        <v>11</v>
+      </c>
+      <c r="BF15">
+        <v>4.8</v>
+      </c>
+      <c r="BG15">
+        <v>10.5</v>
+      </c>
+      <c r="BH15">
+        <v>5.8</v>
+      </c>
+      <c r="BI15">
+        <v>4.5</v>
+      </c>
+      <c r="BJ15">
+        <v>11.5</v>
+      </c>
+      <c r="BK15">
+        <v>8.4</v>
+      </c>
+      <c r="BL15">
+        <v>95</v>
+      </c>
+      <c r="BM15">
+        <v>55</v>
+      </c>
+      <c r="BN15">
+        <v>4.5</v>
+      </c>
+      <c r="BO15">
+        <v>4.2</v>
+      </c>
+      <c r="BP15">
+        <v>11</v>
+      </c>
+      <c r="BQ15">
+        <v>8</v>
+      </c>
+      <c r="BR15">
+        <v>22</v>
+      </c>
+      <c r="BS15">
+        <v>13</v>
+      </c>
+      <c r="BT15">
+        <v>12.5</v>
+      </c>
+      <c r="BU15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BV15">
+        <v>55</v>
+      </c>
+      <c r="BW15">
+        <v>30</v>
+      </c>
+      <c r="BX15">
+        <v>50</v>
+      </c>
+      <c r="BY15">
+        <v>29</v>
+      </c>
+      <c r="BZ15">
+        <v>13</v>
+      </c>
+      <c r="CA15">
+        <v>8</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <v>6.6</v>
+      </c>
+      <c r="H16">
+        <v>1.66</v>
+      </c>
+      <c r="I16">
+        <v>1.69</v>
+      </c>
+      <c r="J16">
+        <v>4.1</v>
+      </c>
+      <c r="K16">
+        <v>4.2</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.65</v>
+      </c>
+      <c r="Q16">
+        <v>2.32</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>2.3</v>
+      </c>
+      <c r="U16">
+        <v>1.66</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>11</v>
+      </c>
+      <c r="Y16">
+        <v>6.2</v>
+      </c>
+      <c r="Z16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA16">
+        <v>25</v>
+      </c>
+      <c r="AB16">
+        <v>16.5</v>
+      </c>
+      <c r="AC16">
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
+        <v>11</v>
+      </c>
+      <c r="AE16">
+        <v>26</v>
+      </c>
+      <c r="AF16">
+        <v>60</v>
+      </c>
+      <c r="AG16">
+        <v>32</v>
+      </c>
+      <c r="AH16">
+        <v>42</v>
+      </c>
+      <c r="AI16">
+        <v>75</v>
+      </c>
+      <c r="AJ16">
+        <v>290</v>
+      </c>
+      <c r="AK16">
+        <v>160</v>
+      </c>
+      <c r="AL16">
+        <v>160</v>
+      </c>
+      <c r="AM16">
+        <v>270</v>
+      </c>
+      <c r="AN16">
+        <v>290</v>
+      </c>
+      <c r="AO16">
+        <v>15.5</v>
+      </c>
+      <c r="AP16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ16">
+        <v>5.4</v>
+      </c>
+      <c r="AR16">
+        <v>7.4</v>
+      </c>
+      <c r="AS16">
+        <v>14.5</v>
+      </c>
+      <c r="AT16">
+        <v>13.5</v>
+      </c>
+      <c r="AU16">
+        <v>8</v>
+      </c>
+      <c r="AV16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW16">
+        <v>19</v>
+      </c>
+      <c r="AX16">
+        <v>8.6</v>
+      </c>
+      <c r="AY16">
         <v>19.5</v>
       </c>
-      <c r="AZ14">
+      <c r="AZ16">
         <v>21</v>
       </c>
-      <c r="BA14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB14">
+      <c r="BA16">
+        <v>8.6</v>
+      </c>
+      <c r="BB16">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC14">
+      <c r="BC16">
         <v>9.4</v>
       </c>
-      <c r="BD14">
+      <c r="BD16">
+        <v>9.4</v>
+      </c>
+      <c r="BE16">
         <v>9.6</v>
       </c>
-      <c r="BE14">
+      <c r="BF16">
         <v>9.800000000000001</v>
       </c>
-      <c r="BF14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG14">
-        <v>13.5</v>
-      </c>
-      <c r="BH14">
-        <v>0</v>
-      </c>
-      <c r="BI14">
-        <v>0</v>
-      </c>
-      <c r="BJ14">
-        <v>0</v>
-      </c>
-      <c r="BK14">
-        <v>0</v>
-      </c>
-      <c r="BL14">
-        <v>0</v>
-      </c>
-      <c r="BM14">
-        <v>0</v>
-      </c>
-      <c r="BN14">
-        <v>0</v>
-      </c>
-      <c r="BO14">
-        <v>0</v>
-      </c>
-      <c r="BP14">
-        <v>0</v>
-      </c>
-      <c r="BQ14">
-        <v>0</v>
-      </c>
-      <c r="BR14">
-        <v>0</v>
-      </c>
-      <c r="BS14">
-        <v>0</v>
-      </c>
-      <c r="BT14">
-        <v>0</v>
-      </c>
-      <c r="BU14">
-        <v>0</v>
-      </c>
-      <c r="BV14">
-        <v>0</v>
-      </c>
-      <c r="BW14">
-        <v>0</v>
-      </c>
-      <c r="BX14">
-        <v>0</v>
-      </c>
-      <c r="BY14">
-        <v>0</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
-      <c r="CA14">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>117</v>
+      <c r="BG16">
+        <v>13</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -385,7 +385,7 @@
     <t>Slovakia</t>
   </si>
   <si>
-    <t>2026-09-30 03:37:03</t>
+    <t>2026-09-30 05:48:49</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
         <v>6</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>3.65</v>
@@ -1006,19 +1006,19 @@
         <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
         <v>1.67</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
         <v>2.16</v>
@@ -1027,7 +1027,7 @@
         <v>1.76</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
         <v>2.3</v>
@@ -1036,13 +1036,13 @@
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB2">
         <v>6.8</v>
@@ -1057,7 +1057,7 @@
         <v>130</v>
       </c>
       <c r="AF2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1084,7 +1084,7 @@
         <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP2">
         <v>10</v>
@@ -1096,7 +1096,7 @@
         <v>36</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1105,10 +1105,10 @@
         <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AW2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX2">
         <v>8</v>
@@ -1120,25 +1120,25 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
       </c>
       <c r="BC2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1221,7 +1221,7 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="G3">
         <v>3.2</v>
@@ -1230,7 +1230,7 @@
         <v>2.28</v>
       </c>
       <c r="I3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J3">
         <v>3.75</v>
@@ -1263,13 +1263,13 @@
         <v>2.58</v>
       </c>
       <c r="T3">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
         <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W3">
         <v>1.45</v>
@@ -1463,64 +1463,64 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="G4">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="H4">
+        <v>1.11</v>
+      </c>
+      <c r="I4">
         <v>1.15</v>
       </c>
-      <c r="I4">
-        <v>1.2</v>
-      </c>
       <c r="J4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K4">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q4">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="R4">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="S4">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="T4">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="U4">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V4">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -1529,28 +1529,28 @@
         <v>8</v>
       </c>
       <c r="AB4">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AF4">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AH4">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AI4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
@@ -1559,31 +1559,31 @@
         <v>1000</v>
       </c>
       <c r="AL4">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="AP4">
         <v>19</v>
       </c>
       <c r="AQ4">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS4">
         <v>5.9</v>
       </c>
       <c r="AT4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
         <v>15</v>
@@ -1595,34 +1595,34 @@
         <v>12.5</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1705,13 +1705,13 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G5">
         <v>3.15</v>
       </c>
       <c r="H5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I5">
         <v>2.88</v>
@@ -1720,7 +1720,7 @@
         <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L5">
         <v>1.02</v>
@@ -1729,10 +1729,10 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
         <v>1.82</v>
@@ -1744,13 +1744,13 @@
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T5">
         <v>1.79</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
         <v>1.53</v>
@@ -1888,7 +1888,7 @@
         <v>8</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP5">
         <v>32</v>
@@ -1900,7 +1900,7 @@
         <v>50</v>
       </c>
       <c r="BS5">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BT5">
         <v>7.6</v>
@@ -1918,13 +1918,13 @@
         <v>50</v>
       </c>
       <c r="BY5">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BZ5">
         <v>46</v>
       </c>
       <c r="CA5">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CB5" t="s">
         <v>123</v>
@@ -1950,10 +1950,10 @@
         <v>1.55</v>
       </c>
       <c r="G6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I6">
         <v>6.2</v>
@@ -1962,7 +1962,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
         <v>1.23</v>
@@ -1992,22 +1992,22 @@
         <v>1.54</v>
       </c>
       <c r="U6">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
         <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X6">
         <v>38</v>
       </c>
       <c r="Y6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z6">
-        <v>360</v>
+        <v>520</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>24</v>
       </c>
       <c r="AE6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -2046,10 +2046,10 @@
         <v>23</v>
       </c>
       <c r="AM6">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="AN6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO6">
         <v>44</v>
@@ -2058,13 +2058,13 @@
         <v>24</v>
       </c>
       <c r="AQ6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR6">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AS6">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AT6">
         <v>14</v>
@@ -2076,7 +2076,7 @@
         <v>21</v>
       </c>
       <c r="AW6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AX6">
         <v>12.5</v>
@@ -2085,7 +2085,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA6">
         <v>32</v>
@@ -2112,7 +2112,7 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
@@ -2124,7 +2124,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>21</v>
+        <v>2.58</v>
       </c>
       <c r="BN6">
         <v>5.6</v>
@@ -2142,7 +2142,7 @@
         <v>23</v>
       </c>
       <c r="BS6">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="BT6">
         <v>11.5</v>
@@ -2154,19 +2154,19 @@
         <v>50</v>
       </c>
       <c r="BW6">
-        <v>21</v>
+        <v>2.52</v>
       </c>
       <c r="BX6">
         <v>48</v>
       </c>
       <c r="BY6">
-        <v>21</v>
+        <v>2.52</v>
       </c>
       <c r="BZ6">
         <v>13</v>
       </c>
       <c r="CA6">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="CB6" t="s">
         <v>123</v>
@@ -2198,10 +2198,10 @@
         <v>5.7</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
         <v>4.1</v>
@@ -2437,10 +2437,10 @@
         <v>5.1</v>
       </c>
       <c r="H8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I8">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J8">
         <v>3.6</v>
@@ -2787,7 +2787,7 @@
         <v>10</v>
       </c>
       <c r="AR9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS9">
         <v>9</v>
@@ -2829,7 +2829,7 @@
         <v>9.6</v>
       </c>
       <c r="BF9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG9">
         <v>8.6</v>
@@ -2918,7 +2918,7 @@
         <v>2.14</v>
       </c>
       <c r="G10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H10">
         <v>3.75</v>
@@ -2945,22 +2945,22 @@
         <v>1.39</v>
       </c>
       <c r="P10">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
         <v>1.3</v>
       </c>
       <c r="S10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T10">
         <v>1.94</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>14</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -2990,7 +2990,7 @@
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10">
         <v>13</v>
@@ -3017,7 +3017,7 @@
         <v>150</v>
       </c>
       <c r="AN10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO10">
         <v>75</v>
@@ -3032,7 +3032,7 @@
         <v>18</v>
       </c>
       <c r="AS10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10">
         <v>7.6</v>
@@ -3044,7 +3044,7 @@
         <v>14</v>
       </c>
       <c r="AW10">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10">
         <v>11</v>
@@ -3056,10 +3056,10 @@
         <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BC10">
         <v>19.5</v>
@@ -3068,13 +3068,13 @@
         <v>34</v>
       </c>
       <c r="BE10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF10">
         <v>17</v>
       </c>
       <c r="BG10">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3163,13 +3163,13 @@
         <v>1.45</v>
       </c>
       <c r="H11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I11">
         <v>8</v>
       </c>
       <c r="J11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K11">
         <v>5.6</v>
@@ -3202,7 +3202,7 @@
         <v>1.69</v>
       </c>
       <c r="U11">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3319,64 +3319,64 @@
         <v>11</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI11">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BQ11">
+        <v>5.4</v>
+      </c>
+      <c r="BR11">
+        <v>19.5</v>
+      </c>
+      <c r="BS11">
+        <v>8</v>
+      </c>
+      <c r="BT11">
+        <v>11.5</v>
+      </c>
+      <c r="BU11">
+        <v>6.4</v>
+      </c>
+      <c r="BV11">
+        <v>55</v>
+      </c>
+      <c r="BW11">
+        <v>11</v>
+      </c>
+      <c r="BX11">
+        <v>48</v>
+      </c>
+      <c r="BY11">
+        <v>10.5</v>
+      </c>
+      <c r="BZ11">
+        <v>11</v>
+      </c>
+      <c r="CA11">
         <v>6.2</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.01</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>7.8</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.01</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>1.01</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>123</v>
@@ -3414,7 +3414,7 @@
         <v>4.3</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
         <v>1.29</v>
@@ -3432,19 +3432,19 @@
         <v>2.08</v>
       </c>
       <c r="Q12">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
         <v>1.96</v>
       </c>
       <c r="U12">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3465,25 +3465,25 @@
         <v>210</v>
       </c>
       <c r="AB12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC12">
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE12">
         <v>110</v>
       </c>
       <c r="AF12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG12">
         <v>10</v>
       </c>
       <c r="AH12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI12">
         <v>100</v>
@@ -3495,13 +3495,13 @@
         <v>17</v>
       </c>
       <c r="AL12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM12">
         <v>140</v>
       </c>
       <c r="AN12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO12">
         <v>140</v>
@@ -3513,13 +3513,13 @@
         <v>19</v>
       </c>
       <c r="AR12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU12">
         <v>8.800000000000001</v>
@@ -3540,7 +3540,7 @@
         <v>19</v>
       </c>
       <c r="BA12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB12">
         <v>13</v>
@@ -3549,16 +3549,16 @@
         <v>15</v>
       </c>
       <c r="BD12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH12">
         <v>4</v>
@@ -3644,7 +3644,7 @@
         <v>1.97</v>
       </c>
       <c r="G13">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H13">
         <v>4.6</v>
@@ -3656,16 +3656,16 @@
         <v>3.55</v>
       </c>
       <c r="K13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="O13">
         <v>1.48</v>
@@ -3677,7 +3677,7 @@
         <v>2.44</v>
       </c>
       <c r="R13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S13">
         <v>4.9</v>
@@ -3686,7 +3686,7 @@
         <v>2.16</v>
       </c>
       <c r="U13">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>36</v>
       </c>
       <c r="AA13">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB13">
         <v>7</v>
@@ -3713,7 +3713,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE13">
         <v>85</v>
@@ -3755,10 +3755,10 @@
         <v>11</v>
       </c>
       <c r="AR13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT13">
         <v>6.2</v>
@@ -3782,7 +3782,7 @@
         <v>21</v>
       </c>
       <c r="BA13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB13">
         <v>20</v>
@@ -3791,16 +3791,16 @@
         <v>21</v>
       </c>
       <c r="BD13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF13">
         <v>18.5</v>
       </c>
       <c r="BG13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH13">
         <v>3.1</v>
@@ -3883,7 +3883,7 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G14">
         <v>3.45</v>
@@ -3892,7 +3892,7 @@
         <v>2.24</v>
       </c>
       <c r="I14">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J14">
         <v>3.7</v>
@@ -3922,7 +3922,7 @@
         <v>1.46</v>
       </c>
       <c r="S14">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T14">
         <v>1.68</v>
@@ -4021,19 +4021,19 @@
         <v>12.5</v>
       </c>
       <c r="AZ14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA14">
         <v>8.199999999999999</v>
       </c>
       <c r="BB14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC14">
         <v>8.4</v>
       </c>
       <c r="BD14">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BE14">
         <v>9.6</v>
@@ -4131,7 +4131,7 @@
         <v>1.53</v>
       </c>
       <c r="H15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I15">
         <v>6.8</v>
@@ -4170,7 +4170,7 @@
         <v>1.64</v>
       </c>
       <c r="U15">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4296,13 +4296,13 @@
         <v>11.5</v>
       </c>
       <c r="BK15">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="BL15">
         <v>95</v>
       </c>
       <c r="BM15">
-        <v>55</v>
+        <v>5.3</v>
       </c>
       <c r="BN15">
         <v>4.5</v>
@@ -4320,31 +4320,31 @@
         <v>22</v>
       </c>
       <c r="BS15">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="BT15">
         <v>12.5</v>
       </c>
       <c r="BU15">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BV15">
         <v>55</v>
       </c>
       <c r="BW15">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="BX15">
         <v>50</v>
       </c>
       <c r="BY15">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="BZ15">
         <v>13</v>
       </c>
       <c r="CA15">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="CB15" t="s">
         <v>123</v>
@@ -4367,16 +4367,16 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G16">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H16">
         <v>1.66</v>
       </c>
       <c r="I16">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J16">
         <v>4.1</v>
@@ -4397,22 +4397,22 @@
         <v>0</v>
       </c>
       <c r="P16">
+        <v>1.64</v>
+      </c>
+      <c r="Q16">
+        <v>2.34</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>2.32</v>
+      </c>
+      <c r="U16">
         <v>1.65</v>
-      </c>
-      <c r="Q16">
-        <v>2.32</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>2.3</v>
-      </c>
-      <c r="U16">
-        <v>1.66</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA16">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AB16">
         <v>16.5</v>
@@ -4442,16 +4442,16 @@
         <v>11</v>
       </c>
       <c r="AE16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF16">
         <v>60</v>
       </c>
       <c r="AG16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH16">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AI16">
         <v>75</v>
@@ -4475,10 +4475,10 @@
         <v>15.5</v>
       </c>
       <c r="AP16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR16">
         <v>7.4</v>
@@ -4490,7 +4490,7 @@
         <v>13.5</v>
       </c>
       <c r="AU16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16">
         <v>9.199999999999999</v>
@@ -4499,7 +4499,7 @@
         <v>19</v>
       </c>
       <c r="AX16">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY16">
         <v>19.5</v>
@@ -4508,22 +4508,22 @@
         <v>21</v>
       </c>
       <c r="BA16">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC16">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD16">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE16">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG16">
         <v>13</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -325,7 +325,7 @@
     <t>Kumamoto</t>
   </si>
   <si>
-    <t>2026-09-30 07:58:21</t>
+    <t>2026-09-30 10:09:30</t>
   </si>
 </sst>
 </file>
@@ -919,7 +919,7 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G2">
         <v>1.76</v>
@@ -931,28 +931,28 @@
         <v>6.6</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
         <v>1.66</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
         <v>1.25</v>
@@ -967,7 +967,7 @@
         <v>1.76</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
         <v>2.3</v>
@@ -985,7 +985,7 @@
         <v>240</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
@@ -1003,7 +1003,7 @@
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1027,7 +1027,7 @@
         <v>220</v>
       </c>
       <c r="AP2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
         <v>14</v>
@@ -1036,7 +1036,7 @@
         <v>38</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1045,10 +1045,10 @@
         <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
         <v>8</v>
@@ -1060,7 +1060,7 @@
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
@@ -1069,16 +1069,16 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1090,13 +1090,13 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
         <v>4.5</v>
@@ -1108,10 +1108,10 @@
         <v>12.5</v>
       </c>
       <c r="BQ2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS2">
         <v>5.5</v>
@@ -1120,25 +1120,25 @@
         <v>11.5</v>
       </c>
       <c r="BU2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BW2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2">
         <v>30</v>
       </c>
       <c r="CA2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB2" t="s">
         <v>103</v>
@@ -1164,19 +1164,19 @@
         <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1185,49 +1185,49 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O3">
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S3">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X3">
         <v>26</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA3">
         <v>36</v>
       </c>
       <c r="AB3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC3">
         <v>11</v>
@@ -1236,13 +1236,13 @@
         <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
         <v>17.5</v>
@@ -1278,13 +1278,13 @@
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
         <v>10</v>
@@ -1302,19 +1302,19 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB3">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC3">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD3">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE3">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="BF3">
         <v>18</v>
@@ -1326,61 +1326,61 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>103</v>
@@ -1403,73 +1403,73 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>65</v>
       </c>
       <c r="H4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
         <v>1.12</v>
       </c>
       <c r="J4">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="K4">
         <v>14.5</v>
       </c>
       <c r="L4">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="O4">
         <v>1.14</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="Q4">
         <v>1.42</v>
       </c>
       <c r="R4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="T4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
         <v>1.35</v>
       </c>
       <c r="V4">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W4">
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AA4">
         <v>7.6</v>
       </c>
       <c r="AB4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AC4">
         <v>36</v>
@@ -1484,7 +1484,7 @@
         <v>1000</v>
       </c>
       <c r="AG4">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AH4">
         <v>120</v>
@@ -1511,7 +1511,7 @@
         <v>3.05</v>
       </c>
       <c r="AP4">
-        <v>26</v>
+        <v>5.9</v>
       </c>
       <c r="AQ4">
         <v>8.199999999999999</v>
@@ -1520,46 +1520,46 @@
         <v>5.6</v>
       </c>
       <c r="AS4">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>23</v>
+        <v>5.8</v>
       </c>
       <c r="AV4">
         <v>14.5</v>
       </c>
       <c r="AW4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG4">
         <v>2.34</v>
@@ -1648,73 +1648,73 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I5">
+        <v>2.9</v>
+      </c>
+      <c r="J5">
         <v>3</v>
-      </c>
-      <c r="J5">
-        <v>2.82</v>
       </c>
       <c r="K5">
         <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
         <v>3.7</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD5">
         <v>14.5</v>
@@ -1723,7 +1723,7 @@
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG5">
         <v>15.5</v>
@@ -1732,22 +1732,22 @@
         <v>19</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO5">
         <v>36</v>
@@ -1756,25 +1756,25 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>2.28</v>
+        <v>5.5</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>1.96</v>
+        <v>11</v>
       </c>
       <c r="AW5">
-        <v>2.16</v>
+        <v>5.3</v>
       </c>
       <c r="AX5">
         <v>17</v>
@@ -1783,88 +1783,88 @@
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>2.14</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>2.28</v>
+        <v>5.6</v>
       </c>
       <c r="BB5">
-        <v>2.28</v>
+        <v>5.6</v>
       </c>
       <c r="BC5">
-        <v>2.28</v>
+        <v>5.4</v>
       </c>
       <c r="BD5">
-        <v>2.28</v>
+        <v>5.6</v>
       </c>
       <c r="BE5">
-        <v>2.24</v>
+        <v>5.9</v>
       </c>
       <c r="BF5">
-        <v>2.28</v>
+        <v>5.4</v>
       </c>
       <c r="BG5">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB5" t="s">
         <v>103</v>
@@ -1896,13 +1896,13 @@
         <v>5.8</v>
       </c>
       <c r="I6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.23</v>
@@ -1920,13 +1920,13 @@
         <v>3.25</v>
       </c>
       <c r="Q6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R6">
         <v>1.91</v>
       </c>
       <c r="S6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T6">
         <v>1.55</v>
@@ -2129,22 +2129,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H7">
         <v>1.1</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J7">
         <v>1.12</v>
       </c>
       <c r="K7">
-        <v>880</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2153,7 +2153,7 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>3.55</v>
       </c>
       <c r="O7">
         <v>1.01</v>
@@ -2162,19 +2162,19 @@
         <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="R7">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2237,52 +2237,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2294,61 +2294,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>103</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
   <si>
     <t>League</t>
   </si>
@@ -286,6 +286,9 @@
     <t>01:30:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>10:00:00</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
     <t>Mio Biwako Shiga</t>
   </si>
   <si>
@@ -322,10 +328,13 @@
     <t>Kansas City</t>
   </si>
   <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
     <t>Kumamoto</t>
   </si>
   <si>
-    <t>2026-09-30 10:09:30</t>
+    <t>2026-09-30 12:19:18</t>
   </si>
 </sst>
 </file>
@@ -657,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -913,10 +922,10 @@
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F2">
         <v>1.71</v>
@@ -934,7 +943,7 @@
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -943,7 +952,7 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O2">
         <v>1.4</v>
@@ -997,7 +1006,7 @@
         <v>130</v>
       </c>
       <c r="AF2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1009,7 +1018,7 @@
         <v>140</v>
       </c>
       <c r="AJ2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
         <v>25</v>
@@ -1036,7 +1045,7 @@
         <v>38</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1048,7 +1057,7 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX2">
         <v>8</v>
@@ -1072,13 +1081,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1090,16 +1099,16 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
         <v>3.6</v>
@@ -1108,40 +1117,40 @@
         <v>12.5</v>
       </c>
       <c r="BQ2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BT2">
         <v>11.5</v>
       </c>
       <c r="BU2">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>75</v>
       </c>
       <c r="BW2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2">
         <v>30</v>
       </c>
       <c r="CA2">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="CB2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1155,28 +1164,28 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F3">
         <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3">
         <v>2.24</v>
       </c>
       <c r="I3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J3">
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1194,7 +1203,7 @@
         <v>2.38</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R3">
         <v>1.56</v>
@@ -1206,10 +1215,10 @@
         <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W3">
         <v>1.44</v>
@@ -1233,22 +1242,22 @@
         <v>11</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
         <v>23</v>
       </c>
       <c r="AF3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG3">
         <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
         <v>60</v>
@@ -1266,7 +1275,7 @@
         <v>25</v>
       </c>
       <c r="AO3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP3">
         <v>19</v>
@@ -1278,7 +1287,7 @@
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1302,19 +1311,19 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB3">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC3">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
         <v>18</v>
@@ -1383,7 +1392,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1397,10 +1406,10 @@
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F4">
         <v>27</v>
@@ -1439,13 +1448,13 @@
         <v>1.42</v>
       </c>
       <c r="R4">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S4">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="U4">
         <v>1.35</v>
@@ -1562,7 +1571,7 @@
         <v>7</v>
       </c>
       <c r="BG4">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1625,7 +1634,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1639,10 +1648,10 @@
         <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1651,7 +1660,7 @@
         <v>3.15</v>
       </c>
       <c r="H5">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="I5">
         <v>2.9</v>
@@ -1660,16 +1669,16 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
         <v>1.36</v>
@@ -1678,25 +1687,25 @@
         <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R5">
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
         <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1717,19 +1726,19 @@
         <v>7</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE5">
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG5">
         <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -1750,7 +1759,7 @@
         <v>40</v>
       </c>
       <c r="AO5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1762,7 +1771,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1774,49 +1783,49 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC5">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI5">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1828,13 +1837,13 @@
         <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
         <v>27</v>
       </c>
       <c r="BQ5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR5">
         <v>44</v>
@@ -1846,7 +1855,7 @@
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV5">
         <v>25</v>
@@ -1861,13 +1870,13 @@
         <v>5.1</v>
       </c>
       <c r="BZ5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA5">
         <v>5</v>
       </c>
       <c r="CB5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1881,10 +1890,10 @@
         <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F6">
         <v>1.55</v>
@@ -1899,7 +1908,7 @@
         <v>6.4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
         <v>5.4</v>
@@ -1911,7 +1920,7 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O6">
         <v>1.14</v>
@@ -1920,13 +1929,13 @@
         <v>3.25</v>
       </c>
       <c r="Q6">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R6">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T6">
         <v>1.55</v>
@@ -1947,7 +1956,7 @@
         <v>36</v>
       </c>
       <c r="Z6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -1959,10 +1968,10 @@
         <v>13</v>
       </c>
       <c r="AD6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE6">
-        <v>740</v>
+        <v>690</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -1974,7 +1983,7 @@
         <v>17.5</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
         <v>17</v>
@@ -1986,7 +1995,7 @@
         <v>23</v>
       </c>
       <c r="AM6">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="AN6">
         <v>4.8</v>
@@ -1995,19 +2004,19 @@
         <v>46</v>
       </c>
       <c r="AP6">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AQ6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AR6">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AS6">
         <v>42</v>
       </c>
       <c r="AT6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU6">
         <v>11.5</v>
@@ -2016,7 +2025,7 @@
         <v>21</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AX6">
         <v>12</v>
@@ -2040,81 +2049,81 @@
         <v>19.5</v>
       </c>
       <c r="BE6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG6">
         <v>30</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI6">
-        <v>1.45</v>
+        <v>4.9</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK6">
-        <v>1.67</v>
+        <v>8</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM6">
-        <v>1.87</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO6">
-        <v>1.39</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>1.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS6">
-        <v>1.87</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU6">
-        <v>1.87</v>
+        <v>7.4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW6">
-        <v>1.87</v>
+        <v>12</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY6">
-        <v>1.87</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA6">
-        <v>1.87</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
         <v>86</v>
@@ -2123,16 +2132,16 @@
         <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H7">
         <v>1.1</v>
@@ -2141,7 +2150,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2153,16 +2162,16 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P7">
         <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R7">
         <v>1.18</v>
@@ -2294,64 +2303,306 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>103</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8">
+        <v>1.12</v>
+      </c>
+      <c r="G8">
+        <v>990</v>
+      </c>
+      <c r="H8">
+        <v>1.1</v>
+      </c>
+      <c r="I8">
+        <v>990</v>
+      </c>
+      <c r="J8">
+        <v>1.12</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>3.55</v>
+      </c>
+      <c r="O8">
+        <v>1.01</v>
+      </c>
+      <c r="P8">
+        <v>1.24</v>
+      </c>
+      <c r="Q8">
+        <v>1.29</v>
+      </c>
+      <c r="R8">
+        <v>1.18</v>
+      </c>
+      <c r="S8">
+        <v>1.3</v>
+      </c>
+      <c r="T8">
+        <v>1.11</v>
+      </c>
+      <c r="U8">
+        <v>1.11</v>
+      </c>
+      <c r="V8">
+        <v>1.02</v>
+      </c>
+      <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.04</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.04</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.04</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.04</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.04</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.04</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.04</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.04</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.04</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.04</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="125">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,15 @@
     <t>Japanese J League 3</t>
   </si>
   <si>
+    <t>Danish 2nd Division</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
     <t>2026-10-02</t>
   </si>
   <si>
@@ -292,6 +301,9 @@
     <t>10:00:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
@@ -313,6 +325,27 @@
     <t>Mio Biwako Shiga</t>
   </si>
   <si>
+    <t>Fremad Amager</t>
+  </si>
+  <si>
+    <t>VSK Aarhus FC</t>
+  </si>
+  <si>
+    <t>Naestved</t>
+  </si>
+  <si>
+    <t>Ranheim IL</t>
+  </si>
+  <si>
+    <t>Karlbergs BK</t>
+  </si>
+  <si>
+    <t>Kristianstads</t>
+  </si>
+  <si>
+    <t>Lunds BK</t>
+  </si>
+  <si>
     <t>Goias</t>
   </si>
   <si>
@@ -334,7 +367,28 @@
     <t>Kumamoto</t>
   </si>
   <si>
-    <t>2026-09-30 12:19:18</t>
+    <t>B93 Copenhagen</t>
+  </si>
+  <si>
+    <t>Brabrand</t>
+  </si>
+  <si>
+    <t>Nykobing FC</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Sollentuna FF</t>
+  </si>
+  <si>
+    <t>Ariana FC</t>
+  </si>
+  <si>
+    <t>Laholms</t>
+  </si>
+  <si>
+    <t>2026-09-30 14:31:07</t>
   </si>
 </sst>
 </file>
@@ -666,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -916,19 +970,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G2">
         <v>1.76</v>
@@ -952,13 +1006,13 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q2">
         <v>2.28</v>
@@ -1099,16 +1153,16 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
         <v>3.6</v>
@@ -1117,16 +1171,16 @@
         <v>12.5</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BT2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
         <v>5.8</v>
@@ -1135,22 +1189,22 @@
         <v>75</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ2">
         <v>30</v>
       </c>
       <c r="CA2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1158,28 +1212,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F3">
         <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
         <v>2.24</v>
       </c>
       <c r="I3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J3">
         <v>3.8</v>
@@ -1203,7 +1257,7 @@
         <v>2.38</v>
       </c>
       <c r="Q3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
         <v>1.56</v>
@@ -1227,7 +1281,7 @@
         <v>26</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z3">
         <v>18</v>
@@ -1287,7 +1341,7 @@
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1311,13 +1365,13 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
         <v>6.6</v>
       </c>
       <c r="BC3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD3">
         <v>6.4</v>
@@ -1392,7 +1446,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1400,19 +1454,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>65</v>
@@ -1454,7 +1508,7 @@
         <v>2.08</v>
       </c>
       <c r="T4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="U4">
         <v>1.35</v>
@@ -1547,7 +1601,7 @@
         <v>7</v>
       </c>
       <c r="AY4">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>6.6</v>
@@ -1634,7 +1688,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1642,34 +1696,34 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G5">
         <v>3.15</v>
       </c>
       <c r="H5">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I5">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.39</v>
@@ -1687,22 +1741,22 @@
         <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
         <v>1.46</v>
@@ -1720,7 +1774,7 @@
         <v>50</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
         <v>7</v>
@@ -1747,16 +1801,16 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO5">
         <v>34</v>
@@ -1765,25 +1819,25 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR5">
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX5">
         <v>17.5</v>
@@ -1795,25 +1849,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
+        <v>6.2</v>
+      </c>
+      <c r="BB5">
+        <v>6.2</v>
+      </c>
+      <c r="BC5">
         <v>6</v>
       </c>
-      <c r="BB5">
-        <v>6</v>
-      </c>
-      <c r="BC5">
+      <c r="BD5">
+        <v>6.2</v>
+      </c>
+      <c r="BE5">
+        <v>6.6</v>
+      </c>
+      <c r="BF5">
+        <v>5.9</v>
+      </c>
+      <c r="BG5">
         <v>5.8</v>
-      </c>
-      <c r="BD5">
-        <v>6</v>
-      </c>
-      <c r="BE5">
-        <v>6.2</v>
-      </c>
-      <c r="BF5">
-        <v>5.7</v>
-      </c>
-      <c r="BG5">
-        <v>5.5</v>
       </c>
       <c r="BH5">
         <v>3.6</v>
@@ -1876,7 +1930,7 @@
         <v>5</v>
       </c>
       <c r="CB5" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1884,16 +1938,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F6">
         <v>1.55</v>
@@ -1905,13 +1959,13 @@
         <v>5.8</v>
       </c>
       <c r="I6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L6">
         <v>1.23</v>
@@ -1923,25 +1977,25 @@
         <v>7.8</v>
       </c>
       <c r="O6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q6">
         <v>1.41</v>
       </c>
       <c r="R6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S6">
         <v>2.02</v>
       </c>
       <c r="T6">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V6">
         <v>1.19</v>
@@ -1950,28 +2004,28 @@
         <v>2.74</v>
       </c>
       <c r="X6">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Y6">
         <v>36</v>
       </c>
       <c r="Z6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD6">
         <v>24</v>
       </c>
       <c r="AE6">
-        <v>690</v>
+        <v>95</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -1992,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="AL6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM6">
         <v>270</v>
@@ -2004,16 +2058,16 @@
         <v>46</v>
       </c>
       <c r="AP6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AR6">
         <v>44</v>
       </c>
       <c r="AS6">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AT6">
         <v>14</v>
@@ -2040,7 +2094,7 @@
         <v>32</v>
       </c>
       <c r="BB6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC6">
         <v>12.5</v>
@@ -2118,7 +2172,7 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2126,241 +2180,241 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="I7">
-        <v>990</v>
+        <v>1.74</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q7">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>2.98</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2368,16 +2422,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F8">
         <v>1.12</v>
@@ -2410,7 +2464,7 @@
         <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q8">
         <v>1.29</v>
@@ -2602,7 +2656,1701 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9">
+        <v>1.1</v>
+      </c>
+      <c r="G9">
+        <v>990</v>
+      </c>
+      <c r="H9">
+        <v>1.1</v>
+      </c>
+      <c r="I9">
+        <v>990</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>2.02</v>
+      </c>
+      <c r="O9">
+        <v>1.02</v>
+      </c>
+      <c r="P9">
+        <v>1.61</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>1.37</v>
+      </c>
+      <c r="S9">
+        <v>2.06</v>
+      </c>
+      <c r="T9">
+        <v>1.11</v>
+      </c>
+      <c r="U9">
+        <v>1.11</v>
+      </c>
+      <c r="V9">
+        <v>1.47</v>
+      </c>
+      <c r="W9">
+        <v>1.35</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9">
+        <v>1.03</v>
+      </c>
+      <c r="AR9">
+        <v>1.03</v>
+      </c>
+      <c r="AS9">
+        <v>1.03</v>
+      </c>
+      <c r="AT9">
+        <v>1.03</v>
+      </c>
+      <c r="AU9">
+        <v>1.03</v>
+      </c>
+      <c r="AV9">
+        <v>1.03</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>1.03</v>
+      </c>
+      <c r="AY9">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9">
+        <v>1.03</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>1.03</v>
+      </c>
+      <c r="BC9">
+        <v>1.03</v>
+      </c>
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.03</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.04</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.04</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.04</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.04</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.04</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.04</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.04</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10">
+        <v>1.1</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+      <c r="H10">
+        <v>1.1</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1.1</v>
+      </c>
+      <c r="K10">
+        <v>950</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.25</v>
+      </c>
+      <c r="O10">
+        <v>1.01</v>
+      </c>
+      <c r="P10">
+        <v>1.26</v>
+      </c>
+      <c r="Q10">
+        <v>1.02</v>
+      </c>
+      <c r="R10">
+        <v>1.25</v>
+      </c>
+      <c r="S10">
+        <v>1.05</v>
+      </c>
+      <c r="T10">
+        <v>1.11</v>
+      </c>
+      <c r="U10">
+        <v>1.11</v>
+      </c>
+      <c r="V10">
+        <v>1.01</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10">
+        <v>1.03</v>
+      </c>
+      <c r="AR10">
+        <v>1.03</v>
+      </c>
+      <c r="AS10">
+        <v>1.03</v>
+      </c>
+      <c r="AT10">
+        <v>1.03</v>
+      </c>
+      <c r="AU10">
+        <v>1.03</v>
+      </c>
+      <c r="AV10">
+        <v>1.03</v>
+      </c>
+      <c r="AW10">
+        <v>1.03</v>
+      </c>
+      <c r="AX10">
+        <v>1.03</v>
+      </c>
+      <c r="AY10">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10">
+        <v>1.03</v>
+      </c>
+      <c r="BA10">
+        <v>1.03</v>
+      </c>
+      <c r="BB10">
+        <v>1.03</v>
+      </c>
+      <c r="BC10">
+        <v>1.03</v>
+      </c>
+      <c r="BD10">
+        <v>1.03</v>
+      </c>
+      <c r="BE10">
+        <v>1.03</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.04</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.04</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.04</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.04</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.04</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.04</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.04</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.04</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11">
+        <v>2.36</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>2.24</v>
+      </c>
+      <c r="I11">
+        <v>2.94</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>7.6</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>3.6</v>
+      </c>
+      <c r="O11">
+        <v>1.02</v>
+      </c>
+      <c r="P11">
+        <v>2.14</v>
+      </c>
+      <c r="Q11">
+        <v>1.44</v>
+      </c>
+      <c r="R11">
+        <v>1.42</v>
+      </c>
+      <c r="S11">
+        <v>2.02</v>
+      </c>
+      <c r="T11">
+        <v>1.11</v>
+      </c>
+      <c r="U11">
+        <v>1.11</v>
+      </c>
+      <c r="V11">
+        <v>1.51</v>
+      </c>
+      <c r="W11">
+        <v>1.33</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11">
+        <v>1.03</v>
+      </c>
+      <c r="AR11">
+        <v>1.03</v>
+      </c>
+      <c r="AS11">
+        <v>1.03</v>
+      </c>
+      <c r="AT11">
+        <v>1.03</v>
+      </c>
+      <c r="AU11">
+        <v>1.03</v>
+      </c>
+      <c r="AV11">
+        <v>1.03</v>
+      </c>
+      <c r="AW11">
+        <v>1.03</v>
+      </c>
+      <c r="AX11">
+        <v>1.03</v>
+      </c>
+      <c r="AY11">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11">
+        <v>1.03</v>
+      </c>
+      <c r="BA11">
+        <v>1.03</v>
+      </c>
+      <c r="BB11">
+        <v>1.03</v>
+      </c>
+      <c r="BC11">
+        <v>1.03</v>
+      </c>
+      <c r="BD11">
+        <v>1.03</v>
+      </c>
+      <c r="BE11">
+        <v>1.03</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.04</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.04</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.04</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.04</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.04</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.04</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.04</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
         <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>2.04</v>
+      </c>
+      <c r="G12">
+        <v>2.22</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>3.4</v>
+      </c>
+      <c r="J12">
+        <v>4.3</v>
+      </c>
+      <c r="K12">
+        <v>5.1</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.02</v>
+      </c>
+      <c r="N12">
+        <v>6.8</v>
+      </c>
+      <c r="O12">
+        <v>1.09</v>
+      </c>
+      <c r="P12">
+        <v>3.3</v>
+      </c>
+      <c r="Q12">
+        <v>1.34</v>
+      </c>
+      <c r="R12">
+        <v>1.9</v>
+      </c>
+      <c r="S12">
+        <v>1.89</v>
+      </c>
+      <c r="T12">
+        <v>1.35</v>
+      </c>
+      <c r="U12">
+        <v>2.74</v>
+      </c>
+      <c r="V12">
+        <v>1.41</v>
+      </c>
+      <c r="W12">
+        <v>1.81</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>34</v>
+      </c>
+      <c r="Z12">
+        <v>40</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>19.5</v>
+      </c>
+      <c r="AE12">
+        <v>36</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>17.5</v>
+      </c>
+      <c r="AI12">
+        <v>34</v>
+      </c>
+      <c r="AJ12">
+        <v>36</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>8.6</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>19</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>38</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>20</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>10.5</v>
+      </c>
+      <c r="BA12">
+        <v>20</v>
+      </c>
+      <c r="BB12">
+        <v>21</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>16</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>5.4</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.01</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.01</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13">
+        <v>2.1</v>
+      </c>
+      <c r="G13">
+        <v>2.6</v>
+      </c>
+      <c r="H13">
+        <v>2.8</v>
+      </c>
+      <c r="I13">
+        <v>3.8</v>
+      </c>
+      <c r="J13">
+        <v>3.4</v>
+      </c>
+      <c r="K13">
+        <v>6</v>
+      </c>
+      <c r="L13">
+        <v>1.27</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>3.25</v>
+      </c>
+      <c r="O13">
+        <v>1.01</v>
+      </c>
+      <c r="P13">
+        <v>1.94</v>
+      </c>
+      <c r="Q13">
+        <v>1.72</v>
+      </c>
+      <c r="R13">
+        <v>1.36</v>
+      </c>
+      <c r="S13">
+        <v>2.78</v>
+      </c>
+      <c r="T13">
+        <v>1.01</v>
+      </c>
+      <c r="U13">
+        <v>1.01</v>
+      </c>
+      <c r="V13">
+        <v>1.36</v>
+      </c>
+      <c r="W13">
+        <v>1.62</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14">
+        <v>2.82</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>1.81</v>
+      </c>
+      <c r="I14">
+        <v>2.36</v>
+      </c>
+      <c r="J14">
+        <v>3.1</v>
+      </c>
+      <c r="K14">
+        <v>480</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>3.75</v>
+      </c>
+      <c r="O14">
+        <v>1.01</v>
+      </c>
+      <c r="P14">
+        <v>2</v>
+      </c>
+      <c r="Q14">
+        <v>1.51</v>
+      </c>
+      <c r="R14">
+        <v>1.4</v>
+      </c>
+      <c r="S14">
+        <v>2.26</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.01</v>
+      </c>
+      <c r="V14">
+        <v>1.73</v>
+      </c>
+      <c r="W14">
+        <v>1.14</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15">
+        <v>1.29</v>
+      </c>
+      <c r="G15">
+        <v>1.63</v>
+      </c>
+      <c r="H15">
+        <v>6.4</v>
+      </c>
+      <c r="I15">
+        <v>870</v>
+      </c>
+      <c r="J15">
+        <v>3.75</v>
+      </c>
+      <c r="K15">
+        <v>17</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.66</v>
+      </c>
+      <c r="O15">
+        <v>1.01</v>
+      </c>
+      <c r="P15">
+        <v>2.16</v>
+      </c>
+      <c r="Q15">
+        <v>1.41</v>
+      </c>
+      <c r="R15">
+        <v>1.43</v>
+      </c>
+      <c r="S15">
+        <v>1.85</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.01</v>
+      </c>
+      <c r="W15">
+        <v>2.58</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
   <si>
     <t>League</t>
   </si>
@@ -274,13 +274,25 @@
     <t>Japanese J League 3</t>
   </si>
   <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
     <t>Danish 2nd Division</t>
   </si>
   <si>
-    <t>Norwegian 1st Division</t>
-  </si>
-  <si>
-    <t>Swedish Division 1</t>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Irish Division 1</t>
+  </si>
+  <si>
+    <t>Irish Premier Division</t>
+  </si>
+  <si>
+    <t>Dutch Eerste Divisie</t>
   </si>
   <si>
     <t>2026-10-02</t>
@@ -304,6 +316,15 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
@@ -325,25 +346,49 @@
     <t>Mio Biwako Shiga</t>
   </si>
   <si>
+    <t>Lunds BK</t>
+  </si>
+  <si>
+    <t>Kristianstads</t>
+  </si>
+  <si>
+    <t>Karlbergs BK</t>
+  </si>
+  <si>
+    <t>Ranheim IL</t>
+  </si>
+  <si>
+    <t>Naestved</t>
+  </si>
+  <si>
+    <t>VSK Aarhus FC</t>
+  </si>
+  <si>
     <t>Fremad Amager</t>
   </si>
   <si>
-    <t>VSK Aarhus FC</t>
-  </si>
-  <si>
-    <t>Naestved</t>
-  </si>
-  <si>
-    <t>Ranheim IL</t>
-  </si>
-  <si>
-    <t>Karlbergs BK</t>
-  </si>
-  <si>
-    <t>Kristianstads</t>
-  </si>
-  <si>
-    <t>Lunds BK</t>
+    <t>Eldense</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
   </si>
   <si>
     <t>Goias</t>
@@ -367,28 +412,52 @@
     <t>Kumamoto</t>
   </si>
   <si>
+    <t>Laholms</t>
+  </si>
+  <si>
+    <t>Ariana FC</t>
+  </si>
+  <si>
+    <t>Sollentuna FF</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Nykobing FC</t>
+  </si>
+  <si>
+    <t>Brabrand</t>
+  </si>
+  <si>
     <t>B93 Copenhagen</t>
   </si>
   <si>
-    <t>Brabrand</t>
-  </si>
-  <si>
-    <t>Nykobing FC</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Sollentuna FF</t>
-  </si>
-  <si>
-    <t>Ariana FC</t>
-  </si>
-  <si>
-    <t>Laholms</t>
-  </si>
-  <si>
-    <t>2026-09-30 14:31:07</t>
+    <t>Oviedo</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Longford</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Heracles</t>
+  </si>
+  <si>
+    <t>2026-09-30 16:43:55</t>
   </si>
 </sst>
 </file>
@@ -720,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -970,22 +1039,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F2">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -997,7 +1066,7 @@
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1006,7 +1075,7 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O2">
         <v>1.42</v>
@@ -1033,7 +1102,7 @@
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
         <v>11.5</v>
@@ -1084,7 +1153,7 @@
         <v>230</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
         <v>220</v>
@@ -1099,7 +1168,7 @@
         <v>38</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1135,13 +1204,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1204,7 +1273,7 @@
         <v>5.7</v>
       </c>
       <c r="CB2" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1212,34 +1281,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H3">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I3">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J3">
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1254,28 +1323,28 @@
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R3">
         <v>1.56</v>
       </c>
       <c r="S3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
         <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X3">
         <v>26</v>
@@ -1284,16 +1353,16 @@
         <v>14</v>
       </c>
       <c r="Z3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
         <v>12</v>
@@ -1302,7 +1371,7 @@
         <v>23</v>
       </c>
       <c r="AF3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG3">
         <v>14.5</v>
@@ -1311,7 +1380,7 @@
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AJ3">
         <v>60</v>
@@ -1332,7 +1401,7 @@
         <v>13</v>
       </c>
       <c r="AP3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3">
         <v>12</v>
@@ -1341,13 +1410,13 @@
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
         <v>10</v>
@@ -1365,22 +1434,22 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BC3">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD3">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BG3">
         <v>11</v>
@@ -1446,7 +1515,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1454,16 +1523,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>26</v>
@@ -1532,7 +1601,7 @@
         <v>7.6</v>
       </c>
       <c r="AB4">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="AC4">
         <v>36</v>
@@ -1547,10 +1616,10 @@
         <v>1000</v>
       </c>
       <c r="AG4">
-        <v>220</v>
+        <v>950</v>
       </c>
       <c r="AH4">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>120</v>
@@ -1601,7 +1670,7 @@
         <v>7</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AZ4">
         <v>6.6</v>
@@ -1688,7 +1757,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1696,34 +1765,34 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
         <v>2.76</v>
       </c>
       <c r="I5">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
         <v>1.39</v>
@@ -1732,7 +1801,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>1.36</v>
@@ -1741,25 +1810,25 @@
         <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T5">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1930,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="CB5" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1938,22 +2007,22 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H6">
         <v>5.8</v>
@@ -1962,13 +2031,13 @@
         <v>6.2</v>
       </c>
       <c r="J6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M6">
         <v>1.02</v>
@@ -2001,16 +2070,16 @@
         <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X6">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Y6">
         <v>36</v>
       </c>
       <c r="Z6">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2019,13 +2088,13 @@
         <v>16</v>
       </c>
       <c r="AC6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE6">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -2034,7 +2103,7 @@
         <v>11</v>
       </c>
       <c r="AH6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI6">
         <v>60</v>
@@ -2049,28 +2118,28 @@
         <v>22</v>
       </c>
       <c r="AM6">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AN6">
         <v>4.8</v>
       </c>
       <c r="AO6">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AP6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AQ6">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AR6">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AS6">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AT6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU6">
         <v>11.5</v>
@@ -2079,7 +2148,7 @@
         <v>21</v>
       </c>
       <c r="AW6">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX6">
         <v>12</v>
@@ -2088,10 +2157,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BB6">
         <v>15.5</v>
@@ -2103,13 +2172,13 @@
         <v>19.5</v>
       </c>
       <c r="BE6">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BF6">
         <v>4.5</v>
       </c>
       <c r="BG6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BH6">
         <v>5.4</v>
@@ -2172,7 +2241,7 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2180,34 +2249,34 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="G7">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="H7">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="I7">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="J7">
         <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2216,142 +2285,142 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
         <v>1.92</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U7">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="V7">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AA7">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AB7">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AC7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AF7">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AG7">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI7">
         <v>48</v>
       </c>
       <c r="AJ7">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AK7">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AL7">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AM7">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN7">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AO7">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP7">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AQ7">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AR7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS7">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT7">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU7">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AV7">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AW7">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX7">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7">
+        <v>6.4</v>
+      </c>
+      <c r="AZ7">
         <v>6.2</v>
-      </c>
-      <c r="AZ7">
-        <v>5.5</v>
       </c>
       <c r="BA7">
         <v>9</v>
       </c>
       <c r="BB7">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF7">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2414,7 +2483,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2422,16 +2491,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="F8">
         <v>1.12</v>
@@ -2464,7 +2533,7 @@
         <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>1.29</v>
@@ -2482,10 +2551,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2656,7 +2725,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2664,34 +2733,34 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>1.63</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2700,22 +2769,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="O9">
         <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S9">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2724,10 +2793,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.35</v>
+        <v>2.58</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2898,7 +2967,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2906,34 +2975,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>2.82</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2942,22 +3011,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="Q10">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S10">
-        <v>1.05</v>
+        <v>2.26</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -2966,10 +3035,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3026,52 +3095,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3140,7 +3209,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3148,58 +3217,58 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="H11">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="I11">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
         <v>1.02</v>
       </c>
       <c r="P11">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q11">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="R11">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S11">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3208,10 +3277,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3268,52 +3337,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3382,7 +3451,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3390,22 +3459,22 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F12">
         <v>2.04</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -3426,10 +3495,10 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P12">
         <v>3.3</v>
@@ -3438,7 +3507,7 @@
         <v>1.34</v>
       </c>
       <c r="R12">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="S12">
         <v>1.89</v>
@@ -3453,13 +3522,13 @@
         <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X12">
         <v>1000</v>
       </c>
       <c r="Y12">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Z12">
         <v>40</v>
@@ -3510,121 +3579,121 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12">
         <v>19</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AS12">
-        <v>38</v>
+        <v>1.58</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AW12">
-        <v>20</v>
+        <v>1.51</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AZ12">
         <v>10.5</v>
       </c>
       <c r="BA12">
-        <v>20</v>
+        <v>1.51</v>
       </c>
       <c r="BB12">
-        <v>21</v>
+        <v>1.51</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BD12">
         <v>16</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BF12">
         <v>5.4</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3632,70 +3701,70 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="G13">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="I13">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="J13">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="L13">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="R13">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>2.02</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3752,52 +3821,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -3809,64 +3878,64 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3874,70 +3943,70 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>2.82</v>
+        <v>1.6</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>2.1</v>
       </c>
       <c r="H14">
-        <v>1.81</v>
+        <v>3.55</v>
       </c>
       <c r="I14">
-        <v>2.36</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K14">
-        <v>480</v>
+        <v>12</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.75</v>
+        <v>2.72</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="Q14">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S14">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.9</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4051,64 +4120,64 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4116,241 +4185,2177 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15">
+        <v>2.42</v>
+      </c>
+      <c r="G15">
+        <v>3.85</v>
+      </c>
+      <c r="H15">
+        <v>2.1</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>9</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>3.55</v>
+      </c>
+      <c r="O15">
+        <v>1.02</v>
+      </c>
+      <c r="P15">
+        <v>2.02</v>
+      </c>
+      <c r="Q15">
+        <v>1.42</v>
+      </c>
+      <c r="R15">
+        <v>1.38</v>
+      </c>
+      <c r="S15">
+        <v>2.06</v>
+      </c>
+      <c r="T15">
+        <v>1.11</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.5</v>
+      </c>
+      <c r="W15">
+        <v>1.36</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15">
+        <v>1.03</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>1.03</v>
+      </c>
+      <c r="AU15">
+        <v>1.03</v>
+      </c>
+      <c r="AV15">
+        <v>1.03</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>1.03</v>
+      </c>
+      <c r="AY15">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15">
+        <v>1.03</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>1.03</v>
+      </c>
+      <c r="BC15">
+        <v>1.03</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.04</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
         <v>89</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16">
+        <v>2.84</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>2.82</v>
+      </c>
+      <c r="I16">
+        <v>2.98</v>
+      </c>
+      <c r="J16">
+        <v>3.15</v>
+      </c>
+      <c r="K16">
+        <v>3.25</v>
+      </c>
+      <c r="L16">
+        <v>1.47</v>
+      </c>
+      <c r="M16">
+        <v>1.07</v>
+      </c>
+      <c r="N16">
+        <v>2.64</v>
+      </c>
+      <c r="O16">
+        <v>1.43</v>
+      </c>
+      <c r="P16">
+        <v>1.57</v>
+      </c>
+      <c r="Q16">
+        <v>2.5</v>
+      </c>
+      <c r="R16">
+        <v>1.19</v>
+      </c>
+      <c r="S16">
+        <v>4.5</v>
+      </c>
+      <c r="T16">
+        <v>1.92</v>
+      </c>
+      <c r="U16">
+        <v>1.79</v>
+      </c>
+      <c r="V16">
+        <v>1.51</v>
+      </c>
+      <c r="W16">
+        <v>1.5</v>
+      </c>
+      <c r="X16">
+        <v>9.6</v>
+      </c>
+      <c r="Y16">
+        <v>10</v>
+      </c>
+      <c r="Z16">
+        <v>18</v>
+      </c>
+      <c r="AA16">
+        <v>55</v>
+      </c>
+      <c r="AB16">
+        <v>9.4</v>
+      </c>
+      <c r="AC16">
+        <v>7.4</v>
+      </c>
+      <c r="AD16">
+        <v>14</v>
+      </c>
+      <c r="AE16">
+        <v>46</v>
+      </c>
+      <c r="AF16">
+        <v>18</v>
+      </c>
+      <c r="AG16">
+        <v>14.5</v>
+      </c>
+      <c r="AH16">
+        <v>24</v>
+      </c>
+      <c r="AI16">
+        <v>75</v>
+      </c>
+      <c r="AJ16">
+        <v>60</v>
+      </c>
+      <c r="AK16">
+        <v>46</v>
+      </c>
+      <c r="AL16">
+        <v>75</v>
+      </c>
+      <c r="AM16">
+        <v>200</v>
+      </c>
+      <c r="AN16">
+        <v>55</v>
+      </c>
+      <c r="AO16">
+        <v>55</v>
+      </c>
+      <c r="AP16">
+        <v>7.8</v>
+      </c>
+      <c r="AQ16">
+        <v>7.2</v>
+      </c>
+      <c r="AR16">
+        <v>14.5</v>
+      </c>
+      <c r="AS16">
+        <v>40</v>
+      </c>
+      <c r="AT16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU16">
+        <v>6.6</v>
+      </c>
+      <c r="AV16">
+        <v>12</v>
+      </c>
+      <c r="AW16">
+        <v>30</v>
+      </c>
+      <c r="AX16">
+        <v>14.5</v>
+      </c>
+      <c r="AY16">
+        <v>12</v>
+      </c>
+      <c r="AZ16">
+        <v>19.5</v>
+      </c>
+      <c r="BA16">
+        <v>40</v>
+      </c>
+      <c r="BB16">
+        <v>38</v>
+      </c>
+      <c r="BC16">
+        <v>32</v>
+      </c>
+      <c r="BD16">
+        <v>42</v>
+      </c>
+      <c r="BE16">
+        <v>9</v>
+      </c>
+      <c r="BF16">
+        <v>34</v>
+      </c>
+      <c r="BG16">
+        <v>34</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>2.48</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>6.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.41</v>
+      </c>
+      <c r="BN16">
+        <v>8.4</v>
+      </c>
+      <c r="BO16">
+        <v>4</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.41</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.41</v>
+      </c>
+      <c r="BT16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU16">
+        <v>4</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.41</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.41</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.41</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17">
+        <v>1.69</v>
+      </c>
+      <c r="G17">
+        <v>1.88</v>
+      </c>
+      <c r="H17">
+        <v>4.1</v>
+      </c>
+      <c r="I17">
+        <v>5.8</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>6.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>2.4</v>
+      </c>
+      <c r="O17">
+        <v>1.18</v>
+      </c>
+      <c r="P17">
+        <v>2.4</v>
+      </c>
+      <c r="Q17">
+        <v>1.52</v>
+      </c>
+      <c r="R17">
+        <v>1.55</v>
+      </c>
+      <c r="S17">
+        <v>2.2</v>
+      </c>
+      <c r="T17">
+        <v>1.53</v>
+      </c>
+      <c r="U17">
+        <v>1.11</v>
+      </c>
+      <c r="V17">
+        <v>1.21</v>
+      </c>
+      <c r="W17">
+        <v>2.12</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17">
+        <v>1.01</v>
+      </c>
+      <c r="AR17">
+        <v>1.01</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
+        <v>1.01</v>
+      </c>
+      <c r="AU17">
+        <v>1.01</v>
+      </c>
+      <c r="AV17">
+        <v>1.01</v>
+      </c>
+      <c r="AW17">
+        <v>1.01</v>
+      </c>
+      <c r="AX17">
+        <v>1.01</v>
+      </c>
+      <c r="AY17">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17">
+        <v>1.01</v>
+      </c>
+      <c r="BA17">
+        <v>1.01</v>
+      </c>
+      <c r="BB17">
+        <v>1.01</v>
+      </c>
+      <c r="BC17">
+        <v>1.01</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.01</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.04</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.04</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.04</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.04</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.04</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.04</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.04</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.04</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.04</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.04</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18">
+        <v>2.68</v>
+      </c>
+      <c r="G18">
+        <v>3.35</v>
+      </c>
+      <c r="H18">
+        <v>2.14</v>
+      </c>
+      <c r="I18">
+        <v>2.56</v>
+      </c>
+      <c r="J18">
+        <v>3.65</v>
+      </c>
+      <c r="K18">
+        <v>5.9</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>3.9</v>
+      </c>
+      <c r="O18">
+        <v>1.2</v>
+      </c>
+      <c r="P18">
+        <v>2.2</v>
+      </c>
+      <c r="Q18">
+        <v>1.58</v>
+      </c>
+      <c r="R18">
+        <v>1.47</v>
+      </c>
+      <c r="S18">
+        <v>2.48</v>
+      </c>
+      <c r="T18">
+        <v>1.55</v>
+      </c>
+      <c r="U18">
+        <v>2.28</v>
+      </c>
+      <c r="V18">
+        <v>1.64</v>
+      </c>
+      <c r="W18">
+        <v>1.43</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18">
+        <v>1.03</v>
+      </c>
+      <c r="AR18">
+        <v>1.03</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>1.03</v>
+      </c>
+      <c r="AU18">
+        <v>1.03</v>
+      </c>
+      <c r="AV18">
+        <v>1.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.03</v>
+      </c>
+      <c r="AX18">
+        <v>1.03</v>
+      </c>
+      <c r="AY18">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18">
+        <v>1.03</v>
+      </c>
+      <c r="BA18">
+        <v>1.03</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>1.03</v>
+      </c>
+      <c r="BD18">
+        <v>1.03</v>
+      </c>
+      <c r="BE18">
+        <v>1.03</v>
+      </c>
+      <c r="BF18">
+        <v>11.5</v>
+      </c>
+      <c r="BG18">
+        <v>8.6</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.04</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.04</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.04</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.04</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.04</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.04</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.04</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.04</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.04</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.04</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19">
+        <v>3.25</v>
+      </c>
+      <c r="G19">
+        <v>4.6</v>
+      </c>
+      <c r="H19">
+        <v>1.86</v>
+      </c>
+      <c r="I19">
+        <v>2.2</v>
+      </c>
+      <c r="J19">
+        <v>3.65</v>
+      </c>
+      <c r="K19">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.02</v>
+      </c>
+      <c r="N19">
+        <v>4.1</v>
+      </c>
+      <c r="O19">
+        <v>1.25</v>
+      </c>
+      <c r="P19">
+        <v>2</v>
+      </c>
+      <c r="Q19">
+        <v>1.7</v>
+      </c>
+      <c r="R19">
+        <v>1.4</v>
+      </c>
+      <c r="S19">
+        <v>2.72</v>
+      </c>
+      <c r="T19">
+        <v>1.67</v>
+      </c>
+      <c r="U19">
+        <v>2.06</v>
+      </c>
+      <c r="V19">
+        <v>1.83</v>
+      </c>
+      <c r="W19">
+        <v>1.28</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19">
+        <v>1.03</v>
+      </c>
+      <c r="AR19">
+        <v>1.03</v>
+      </c>
+      <c r="AS19">
+        <v>1.03</v>
+      </c>
+      <c r="AT19">
+        <v>1.03</v>
+      </c>
+      <c r="AU19">
+        <v>1.03</v>
+      </c>
+      <c r="AV19">
+        <v>1.03</v>
+      </c>
+      <c r="AW19">
+        <v>1.03</v>
+      </c>
+      <c r="AX19">
+        <v>1.03</v>
+      </c>
+      <c r="AY19">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19">
+        <v>1.03</v>
+      </c>
+      <c r="BA19">
+        <v>1.03</v>
+      </c>
+      <c r="BB19">
+        <v>1.03</v>
+      </c>
+      <c r="BC19">
+        <v>1.03</v>
+      </c>
+      <c r="BD19">
+        <v>1.03</v>
+      </c>
+      <c r="BE19">
+        <v>1.03</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>7.6</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.04</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.04</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.04</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.04</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.04</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.04</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.04</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.04</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.04</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.04</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20">
+        <v>1.9</v>
+      </c>
+      <c r="G20">
+        <v>2.08</v>
+      </c>
+      <c r="H20">
+        <v>3.7</v>
+      </c>
+      <c r="I20">
+        <v>4.7</v>
+      </c>
+      <c r="J20">
+        <v>3.85</v>
+      </c>
+      <c r="K20">
+        <v>4.2</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>2.4</v>
+      </c>
+      <c r="O20">
+        <v>1.23</v>
+      </c>
+      <c r="P20">
+        <v>2.02</v>
+      </c>
+      <c r="Q20">
+        <v>1.74</v>
+      </c>
+      <c r="R20">
+        <v>1.39</v>
+      </c>
+      <c r="S20">
+        <v>2.74</v>
+      </c>
+      <c r="T20">
+        <v>1.11</v>
+      </c>
+      <c r="U20">
+        <v>1.11</v>
+      </c>
+      <c r="V20">
+        <v>1.27</v>
+      </c>
+      <c r="W20">
+        <v>1.92</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20">
+        <v>1.03</v>
+      </c>
+      <c r="AR20">
+        <v>1.03</v>
+      </c>
+      <c r="AS20">
+        <v>1.03</v>
+      </c>
+      <c r="AT20">
+        <v>1.03</v>
+      </c>
+      <c r="AU20">
+        <v>1.03</v>
+      </c>
+      <c r="AV20">
+        <v>1.03</v>
+      </c>
+      <c r="AW20">
+        <v>1.03</v>
+      </c>
+      <c r="AX20">
+        <v>1.03</v>
+      </c>
+      <c r="AY20">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20">
+        <v>1.03</v>
+      </c>
+      <c r="BA20">
+        <v>1.03</v>
+      </c>
+      <c r="BB20">
+        <v>1.03</v>
+      </c>
+      <c r="BC20">
+        <v>1.03</v>
+      </c>
+      <c r="BD20">
+        <v>1.03</v>
+      </c>
+      <c r="BE20">
+        <v>1.03</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>2.92</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.04</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.04</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.04</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.04</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.04</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.04</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.04</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.04</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21">
+        <v>3.2</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>2.04</v>
+      </c>
+      <c r="I21">
+        <v>2.3</v>
+      </c>
+      <c r="J21">
+        <v>3.65</v>
+      </c>
+      <c r="K21">
+        <v>4.9</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>4.8</v>
+      </c>
+      <c r="O21">
+        <v>1.18</v>
+      </c>
+      <c r="P21">
+        <v>2.34</v>
+      </c>
+      <c r="Q21">
+        <v>1.56</v>
+      </c>
+      <c r="R21">
+        <v>1.54</v>
+      </c>
+      <c r="S21">
+        <v>2.4</v>
+      </c>
+      <c r="T21">
+        <v>1.51</v>
+      </c>
+      <c r="U21">
+        <v>2.46</v>
+      </c>
+      <c r="V21">
+        <v>1.76</v>
+      </c>
+      <c r="W21">
+        <v>1.34</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>15</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>17.5</v>
+      </c>
+      <c r="AP21">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21">
+        <v>1.01</v>
+      </c>
+      <c r="AR21">
+        <v>1.01</v>
+      </c>
+      <c r="AS21">
+        <v>1.03</v>
+      </c>
+      <c r="AT21">
+        <v>1.01</v>
+      </c>
+      <c r="AU21">
+        <v>1.01</v>
+      </c>
+      <c r="AV21">
+        <v>1.01</v>
+      </c>
+      <c r="AW21">
+        <v>1.01</v>
+      </c>
+      <c r="AX21">
+        <v>1.03</v>
+      </c>
+      <c r="AY21">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21">
+        <v>1.01</v>
+      </c>
+      <c r="BA21">
+        <v>1.03</v>
+      </c>
+      <c r="BB21">
+        <v>1.03</v>
+      </c>
+      <c r="BC21">
+        <v>1.03</v>
+      </c>
+      <c r="BD21">
+        <v>1.03</v>
+      </c>
+      <c r="BE21">
+        <v>1.03</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.04</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.04</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.04</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.04</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.04</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.04</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.04</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.04</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.04</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.04</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22">
+        <v>3.55</v>
+      </c>
+      <c r="G22">
+        <v>3.85</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2.08</v>
+      </c>
+      <c r="J22">
+        <v>3.95</v>
+      </c>
+      <c r="K22">
+        <v>4.3</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>5.1</v>
+      </c>
+      <c r="O22">
+        <v>1.21</v>
+      </c>
+      <c r="P22">
+        <v>2.44</v>
+      </c>
+      <c r="Q22">
+        <v>1.6</v>
+      </c>
+      <c r="R22">
+        <v>1.59</v>
+      </c>
+      <c r="S22">
+        <v>2.5</v>
+      </c>
+      <c r="T22">
+        <v>1.59</v>
+      </c>
+      <c r="U22">
+        <v>2.48</v>
+      </c>
+      <c r="V22">
+        <v>1.92</v>
+      </c>
+      <c r="W22">
+        <v>1.35</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>16</v>
+      </c>
+      <c r="AD22">
+        <v>22</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>34</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>36</v>
+      </c>
+      <c r="AJ22">
+        <v>85</v>
+      </c>
+      <c r="AK22">
+        <v>42</v>
+      </c>
+      <c r="AL22">
+        <v>44</v>
+      </c>
+      <c r="AM22">
+        <v>80</v>
+      </c>
+      <c r="AN22">
+        <v>34</v>
+      </c>
+      <c r="AO22">
+        <v>17</v>
+      </c>
+      <c r="AP22">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22">
+        <v>1.03</v>
+      </c>
+      <c r="AR22">
+        <v>1.03</v>
+      </c>
+      <c r="AS22">
+        <v>16.5</v>
+      </c>
+      <c r="AT22">
+        <v>1.03</v>
+      </c>
+      <c r="AU22">
+        <v>8.6</v>
+      </c>
+      <c r="AV22">
+        <v>1.03</v>
+      </c>
+      <c r="AW22">
+        <v>1.03</v>
+      </c>
+      <c r="AX22">
+        <v>20</v>
+      </c>
+      <c r="AY22">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22">
+        <v>1.03</v>
+      </c>
+      <c r="BA22">
+        <v>19</v>
+      </c>
+      <c r="BB22">
+        <v>1.03</v>
+      </c>
+      <c r="BC22">
+        <v>1.03</v>
+      </c>
+      <c r="BD22">
+        <v>1.03</v>
+      </c>
+      <c r="BE22">
+        <v>1.03</v>
+      </c>
+      <c r="BF22">
+        <v>19</v>
+      </c>
+      <c r="BG22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH22">
+        <v>5.1</v>
+      </c>
+      <c r="BI22">
+        <v>3.35</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.52</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.51</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.52</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.51</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.51</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.26</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.51</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.51</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.51</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23">
+        <v>6.6</v>
+      </c>
+      <c r="G23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H23">
+        <v>1.44</v>
+      </c>
+      <c r="I23">
+        <v>1.52</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
+      <c r="K23">
+        <v>5.9</v>
+      </c>
+      <c r="L23">
+        <v>1.18</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>6</v>
+      </c>
+      <c r="O23">
+        <v>1.15</v>
+      </c>
+      <c r="P23">
+        <v>2.78</v>
+      </c>
+      <c r="Q23">
+        <v>1.47</v>
+      </c>
+      <c r="R23">
+        <v>1.73</v>
+      </c>
+      <c r="S23">
+        <v>2.14</v>
+      </c>
+      <c r="T23">
+        <v>1.66</v>
+      </c>
+      <c r="U23">
+        <v>2.26</v>
+      </c>
+      <c r="V23">
+        <v>2.92</v>
+      </c>
+      <c r="W23">
+        <v>1.14</v>
+      </c>
+      <c r="X23">
+        <v>36</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>38</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>11.5</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>34</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>34</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>100</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
         <v>95</v>
       </c>
-      <c r="D15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15">
-        <v>1.29</v>
-      </c>
-      <c r="G15">
-        <v>1.63</v>
-      </c>
-      <c r="H15">
-        <v>6.4</v>
-      </c>
-      <c r="I15">
-        <v>870</v>
-      </c>
-      <c r="J15">
-        <v>3.75</v>
-      </c>
-      <c r="K15">
-        <v>17</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>2.66</v>
-      </c>
-      <c r="O15">
-        <v>1.01</v>
-      </c>
-      <c r="P15">
-        <v>2.16</v>
-      </c>
-      <c r="Q15">
-        <v>1.41</v>
-      </c>
-      <c r="R15">
-        <v>1.43</v>
-      </c>
-      <c r="S15">
-        <v>1.85</v>
-      </c>
-      <c r="T15">
-        <v>1.01</v>
-      </c>
-      <c r="U15">
-        <v>1.01</v>
-      </c>
-      <c r="V15">
-        <v>1.01</v>
-      </c>
-      <c r="W15">
-        <v>2.58</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15">
-        <v>1.01</v>
-      </c>
-      <c r="AR15">
-        <v>1.01</v>
-      </c>
-      <c r="AS15">
-        <v>1.01</v>
-      </c>
-      <c r="AT15">
-        <v>1.01</v>
-      </c>
-      <c r="AU15">
-        <v>1.01</v>
-      </c>
-      <c r="AV15">
-        <v>1.01</v>
-      </c>
-      <c r="AW15">
-        <v>1.01</v>
-      </c>
-      <c r="AX15">
-        <v>1.01</v>
-      </c>
-      <c r="AY15">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15">
-        <v>1.01</v>
-      </c>
-      <c r="BA15">
-        <v>1.01</v>
-      </c>
-      <c r="BB15">
-        <v>1.01</v>
-      </c>
-      <c r="BC15">
-        <v>1.01</v>
-      </c>
-      <c r="BD15">
-        <v>1.01</v>
-      </c>
-      <c r="BE15">
-        <v>1.01</v>
-      </c>
-      <c r="BF15">
-        <v>1.01</v>
-      </c>
-      <c r="BG15">
-        <v>1.01</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.01</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.01</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.01</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.01</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.01</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>1.01</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>1.01</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>1.01</v>
-      </c>
-      <c r="BZ15">
-        <v>1000</v>
-      </c>
-      <c r="CA15">
-        <v>1.01</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>124</v>
+      <c r="AN23">
+        <v>85</v>
+      </c>
+      <c r="AO23">
+        <v>5.3</v>
+      </c>
+      <c r="AP23">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23">
+        <v>10.5</v>
+      </c>
+      <c r="AR23">
+        <v>7.6</v>
+      </c>
+      <c r="AS23">
+        <v>9</v>
+      </c>
+      <c r="AT23">
+        <v>1.01</v>
+      </c>
+      <c r="AU23">
+        <v>10.5</v>
+      </c>
+      <c r="AV23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW23">
+        <v>9.4</v>
+      </c>
+      <c r="AX23">
+        <v>1.01</v>
+      </c>
+      <c r="AY23">
+        <v>19</v>
+      </c>
+      <c r="AZ23">
+        <v>16</v>
+      </c>
+      <c r="BA23">
+        <v>19</v>
+      </c>
+      <c r="BB23">
+        <v>95</v>
+      </c>
+      <c r="BC23">
+        <v>1.01</v>
+      </c>
+      <c r="BD23">
+        <v>1.01</v>
+      </c>
+      <c r="BE23">
+        <v>1.01</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>4.2</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.01</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>3</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -373,12 +373,12 @@
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Wexford F.C</t>
   </si>
   <si>
@@ -439,12 +439,12 @@
     <t>Cobh Ramblers</t>
   </si>
   <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Kerry FC</t>
-  </si>
-  <si>
     <t>Longford</t>
   </si>
   <si>
@@ -457,7 +457,7 @@
     <t>Heracles</t>
   </si>
   <si>
-    <t>2026-09-30 16:43:55</t>
+    <t>2026-09-30 18:55:38</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1054,7 @@
         <v>1.71</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -1063,10 +1063,10 @@
         <v>6.6</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1075,13 +1075,13 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
         <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
         <v>2.28</v>
@@ -1093,16 +1093,16 @@
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
         <v>11.5</v>
@@ -1114,7 +1114,7 @@
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB2">
         <v>6.8</v>
@@ -1123,28 +1123,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE2">
         <v>130</v>
       </c>
       <c r="AF2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
         <v>17.5</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL2">
         <v>60</v>
@@ -1156,7 +1156,7 @@
         <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AP2">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>38</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1180,7 +1180,7 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX2">
         <v>8</v>
@@ -1192,7 +1192,7 @@
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
@@ -1201,16 +1201,16 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1222,34 +1222,34 @@
         <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BN2">
         <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
         <v>12.5</v>
       </c>
       <c r="BQ2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU2">
         <v>5.8</v>
@@ -1258,19 +1258,19 @@
         <v>75</v>
       </c>
       <c r="BW2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="s">
         <v>147</v>
@@ -1299,7 +1299,7 @@
         <v>3.35</v>
       </c>
       <c r="H3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I3">
         <v>2.36</v>
@@ -1308,7 +1308,7 @@
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1320,7 +1320,7 @@
         <v>5</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
         <v>2.36</v>
@@ -1335,19 +1335,19 @@
         <v>2.6</v>
       </c>
       <c r="T3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U3">
         <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W3">
         <v>1.42</v>
       </c>
       <c r="X3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y3">
         <v>14</v>
@@ -1401,7 +1401,7 @@
         <v>13</v>
       </c>
       <c r="AP3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
         <v>12</v>
@@ -1410,7 +1410,7 @@
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1434,19 +1434,19 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB3">
+        <v>8.4</v>
+      </c>
+      <c r="BC3">
         <v>8</v>
       </c>
-      <c r="BC3">
-        <v>7.8</v>
-      </c>
       <c r="BD3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BF3">
         <v>16.5</v>
@@ -1535,13 +1535,13 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I4">
         <v>1.12</v>
@@ -1550,37 +1550,37 @@
         <v>11</v>
       </c>
       <c r="K4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="L4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O4">
         <v>1.14</v>
       </c>
       <c r="P4">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="Q4">
         <v>1.42</v>
       </c>
       <c r="R4">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="S4">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="T4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
         <v>9.199999999999999</v>
@@ -1598,10 +1598,10 @@
         <v>7.4</v>
       </c>
       <c r="AA4">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
         <v>36</v>
@@ -1619,10 +1619,10 @@
         <v>950</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
@@ -1640,61 +1640,61 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AP4">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS4">
         <v>5.7</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU4">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW4">
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AY4">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC4">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF4">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG4">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1780,19 +1780,19 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
         <v>2.76</v>
       </c>
       <c r="I5">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.39</v>
@@ -1801,7 +1801,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
         <v>1.36</v>
@@ -1810,25 +1810,25 @@
         <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1888,7 +1888,7 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
         <v>15.5</v>
@@ -2019,10 +2019,10 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H6">
         <v>5.8</v>
@@ -2031,10 +2031,10 @@
         <v>6.2</v>
       </c>
       <c r="J6">
+        <v>5.1</v>
+      </c>
+      <c r="K6">
         <v>5.3</v>
-      </c>
-      <c r="K6">
-        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.22</v>
@@ -2070,7 +2070,7 @@
         <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="Z6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2100,7 +2100,7 @@
         <v>14</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
         <v>17</v>
@@ -2261,10 +2261,10 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H7">
         <v>1.56</v>
@@ -2273,7 +2273,7 @@
         <v>1.65</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
         <v>4.6</v>
@@ -2309,10 +2309,10 @@
         <v>1.86</v>
       </c>
       <c r="V7">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
         <v>15.5</v>
@@ -2327,7 +2327,7 @@
         <v>15.5</v>
       </c>
       <c r="AB7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AC7">
         <v>9.800000000000001</v>
@@ -2393,10 +2393,10 @@
         <v>5.8</v>
       </c>
       <c r="AX7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ7">
         <v>6.2</v>
@@ -2509,13 +2509,13 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2527,7 +2527,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.55</v>
+        <v>1.28</v>
       </c>
       <c r="O8">
         <v>1.01</v>
@@ -2536,7 +2536,7 @@
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R8">
         <v>1.18</v>
@@ -2551,10 +2551,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2787,10 +2787,10 @@
         <v>2.26</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V9">
         <v>1.01</v>
@@ -2853,52 +2853,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3002,7 +3002,7 @@
         <v>3.1</v>
       </c>
       <c r="K10">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3271,10 +3271,10 @@
         <v>2.78</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V11">
         <v>1.36</v>
@@ -3474,7 +3474,7 @@
         <v>2.04</v>
       </c>
       <c r="G12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -3498,7 +3498,7 @@
         <v>7.2</v>
       </c>
       <c r="O12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
         <v>3.3</v>
@@ -3522,7 +3522,7 @@
         <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3600,7 +3600,7 @@
         <v>1.46</v>
       </c>
       <c r="AW12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AX12">
         <v>1.58</v>
@@ -3615,7 +3615,7 @@
         <v>1.51</v>
       </c>
       <c r="BB12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BC12">
         <v>1.58</v>
@@ -3719,7 +3719,7 @@
         <v>4</v>
       </c>
       <c r="H13">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="I13">
         <v>2.94</v>
@@ -3728,7 +3728,7 @@
         <v>3</v>
       </c>
       <c r="K13">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3737,10 +3737,10 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P13">
         <v>2.14</v>
@@ -3752,7 +3752,7 @@
         <v>1.42</v>
       </c>
       <c r="S13">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3764,7 +3764,7 @@
         <v>1.51</v>
       </c>
       <c r="W13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3821,52 +3821,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -3961,7 +3961,7 @@
         <v>2.1</v>
       </c>
       <c r="H14">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="I14">
         <v>7.2</v>
@@ -3970,7 +3970,7 @@
         <v>3.45</v>
       </c>
       <c r="K14">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="L14">
         <v>1.27</v>
@@ -4305,52 +4305,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4439,7 +4439,7 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -4448,46 +4448,46 @@
         <v>2.82</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <v>3.15</v>
       </c>
       <c r="K16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L16">
         <v>1.47</v>
       </c>
       <c r="M16">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O16">
         <v>1.43</v>
       </c>
       <c r="P16">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Q16">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R16">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>1.92</v>
       </c>
       <c r="U16">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.5</v>
@@ -4508,13 +4508,13 @@
         <v>9.4</v>
       </c>
       <c r="AC16">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD16">
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF16">
         <v>18</v>
@@ -4526,31 +4526,31 @@
         <v>24</v>
       </c>
       <c r="AI16">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL16">
         <v>75</v>
       </c>
       <c r="AM16">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AN16">
         <v>55</v>
       </c>
       <c r="AO16">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP16">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR16">
         <v>14.5</v>
@@ -4565,7 +4565,7 @@
         <v>6.6</v>
       </c>
       <c r="AV16">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AW16">
         <v>30</v>
@@ -4592,7 +4592,7 @@
         <v>42</v>
       </c>
       <c r="BE16">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF16">
         <v>34</v>
@@ -4714,10 +4714,10 @@
         <v>2.4</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S17">
         <v>2.2</v>
@@ -4923,64 +4923,64 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="G18">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="H18">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="I18">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K18">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O18">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P18">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="T18">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="W18">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="X18">
         <v>1000</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z18">
         <v>1000</v>
@@ -4992,7 +4992,7 @@
         <v>1000</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD18">
         <v>1000</v>
@@ -5031,58 +5031,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BF18">
-        <v>11.5</v>
+        <v>1.11</v>
       </c>
       <c r="BG18">
-        <v>8.6</v>
+        <v>1.11</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5165,58 +5165,58 @@
         <v>142</v>
       </c>
       <c r="F19">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="G19">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="H19">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="I19">
+        <v>2.56</v>
+      </c>
+      <c r="J19">
+        <v>3.7</v>
+      </c>
+      <c r="K19">
+        <v>5.9</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>3.9</v>
+      </c>
+      <c r="O19">
+        <v>1.2</v>
+      </c>
+      <c r="P19">
         <v>2.2</v>
       </c>
-      <c r="J19">
-        <v>3.65</v>
-      </c>
-      <c r="K19">
-        <v>110</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.02</v>
-      </c>
-      <c r="N19">
-        <v>4.1</v>
-      </c>
-      <c r="O19">
-        <v>1.25</v>
-      </c>
-      <c r="P19">
-        <v>2</v>
-      </c>
       <c r="Q19">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="R19">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S19">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="T19">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="U19">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="W19">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5234,7 +5234,7 @@
         <v>1000</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5273,58 +5273,58 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG19">
-        <v>7.6</v>
+        <v>1.05</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5425,7 +5425,7 @@
         <v>4.2</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M20">
         <v>1.01</v>
@@ -5449,10 +5449,10 @@
         <v>2.74</v>
       </c>
       <c r="T20">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U20">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V20">
         <v>1.27</v>
@@ -5515,52 +5515,52 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5718,7 +5718,7 @@
         <v>1000</v>
       </c>
       <c r="AC21">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AD21">
         <v>1000</v>
@@ -5754,61 +5754,61 @@
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5894,13 +5894,13 @@
         <v>3.55</v>
       </c>
       <c r="G22">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H22">
         <v>2</v>
       </c>
       <c r="I22">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J22">
         <v>3.95</v>
@@ -5909,7 +5909,7 @@
         <v>4.3</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M22">
         <v>1.01</v>
@@ -5918,28 +5918,28 @@
         <v>5.1</v>
       </c>
       <c r="O22">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
         <v>2.44</v>
       </c>
       <c r="Q22">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R22">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S22">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T22">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="U22">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="V22">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W22">
         <v>1.35</v>
@@ -5960,10 +5960,10 @@
         <v>1000</v>
       </c>
       <c r="AC22">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AD22">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE22">
         <v>1000</v>
@@ -5996,61 +5996,61 @@
         <v>34</v>
       </c>
       <c r="AO22">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AS22">
         <v>16.5</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AU22">
         <v>8.6</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AX22">
         <v>20</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BA22">
         <v>19</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BF22">
         <v>19</v>
       </c>
       <c r="BG22">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="BH22">
         <v>5.1</v>
@@ -6154,7 +6154,7 @@
         <v>1.18</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
         <v>6</v>
@@ -6175,7 +6175,7 @@
         <v>2.14</v>
       </c>
       <c r="T23">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U23">
         <v>2.26</v>
@@ -6187,7 +6187,7 @@
         <v>1.14</v>
       </c>
       <c r="X23">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Y23">
         <v>1000</v>
@@ -6199,13 +6199,13 @@
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AC23">
         <v>1000</v>
       </c>
       <c r="AD23">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE23">
         <v>1000</v>
@@ -6214,7 +6214,7 @@
         <v>1000</v>
       </c>
       <c r="AG23">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AH23">
         <v>1000</v>
@@ -6238,22 +6238,22 @@
         <v>85</v>
       </c>
       <c r="AO23">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AQ23">
         <v>10.5</v>
       </c>
       <c r="AR23">
-        <v>7.6</v>
+        <v>1.77</v>
       </c>
       <c r="AS23">
-        <v>9</v>
+        <v>1.77</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AU23">
         <v>10.5</v>
@@ -6262,10 +6262,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW23">
-        <v>9.4</v>
+        <v>1.77</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AY23">
         <v>19</v>
@@ -6277,19 +6277,19 @@
         <v>19</v>
       </c>
       <c r="BB23">
-        <v>95</v>
+        <v>1.77</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BG23">
         <v>4.2</v>
@@ -6298,61 +6298,61 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>147</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="150">
   <si>
     <t>League</t>
   </si>
@@ -352,33 +352,33 @@
     <t>Kristianstads</t>
   </si>
   <si>
+    <t>Ranheim IL</t>
+  </si>
+  <si>
     <t>Karlbergs BK</t>
   </si>
   <si>
-    <t>Ranheim IL</t>
+    <t>VSK Aarhus FC</t>
+  </si>
+  <si>
+    <t>Fremad Amager</t>
   </si>
   <si>
     <t>Naestved</t>
   </si>
   <si>
-    <t>VSK Aarhus FC</t>
-  </si>
-  <si>
-    <t>Fremad Amager</t>
-  </si>
-  <si>
     <t>Eldense</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
     <t>Wexford F.C</t>
   </si>
   <si>
@@ -388,6 +388,9 @@
     <t>Dundalk</t>
   </si>
   <si>
+    <t>St Lucia</t>
+  </si>
+  <si>
     <t>Helmond Sport</t>
   </si>
   <si>
@@ -418,33 +421,33 @@
     <t>Ariana FC</t>
   </si>
   <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Sollentuna FF</t>
   </si>
   <si>
-    <t>Egersund</t>
+    <t>Brabrand</t>
+  </si>
+  <si>
+    <t>B93 Copenhagen</t>
   </si>
   <si>
     <t>Nykobing FC</t>
   </si>
   <si>
-    <t>Brabrand</t>
-  </si>
-  <si>
-    <t>B93 Copenhagen</t>
-  </si>
-  <si>
     <t>Oviedo</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
+    <t>UCD</t>
+  </si>
+  <si>
     <t>Kerry FC</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Longford</t>
   </si>
   <si>
@@ -454,10 +457,13 @@
     <t>Bohemians</t>
   </si>
   <si>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
     <t>Heracles</t>
   </si>
   <si>
-    <t>2026-09-30 18:55:38</t>
+    <t>2026-09-30 21:08:44</t>
   </si>
 </sst>
 </file>
@@ -789,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1048,28 +1054,28 @@
         <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F2">
         <v>1.71</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.09</v>
@@ -1078,64 +1084,64 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
         <v>2.3</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2">
         <v>230</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>9.199999999999999</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>130</v>
@@ -1144,46 +1150,46 @@
         <v>17.5</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>230</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
         <v>14</v>
       </c>
       <c r="AR2">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
@@ -1192,46 +1198,46 @@
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BJ2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
         <v>3.65</v>
@@ -1240,40 +1246,40 @@
         <v>12.5</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
         <v>10</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BY2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2">
         <v>29</v>
       </c>
       <c r="CA2">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1290,28 +1296,28 @@
         <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I3">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="J3">
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M3">
         <v>1.04</v>
@@ -1329,19 +1335,19 @@
         <v>1.64</v>
       </c>
       <c r="R3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V3">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W3">
         <v>1.42</v>
@@ -1353,7 +1359,7 @@
         <v>14</v>
       </c>
       <c r="Z3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA3">
         <v>34</v>
@@ -1365,10 +1371,10 @@
         <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF3">
         <v>25</v>
@@ -1380,7 +1386,7 @@
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
         <v>60</v>
@@ -1389,10 +1395,10 @@
         <v>36</v>
       </c>
       <c r="AL3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN3">
         <v>25</v>
@@ -1410,7 +1416,7 @@
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1434,19 +1440,19 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BB3">
+        <v>23</v>
+      </c>
+      <c r="BC3">
         <v>8.4</v>
       </c>
-      <c r="BC3">
-        <v>8</v>
-      </c>
       <c r="BD3">
-        <v>8.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="BE3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BF3">
         <v>16.5</v>
@@ -1515,7 +1521,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1532,25 +1538,25 @@
         <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F4">
         <v>36</v>
       </c>
       <c r="G4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>1.09</v>
       </c>
       <c r="I4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="J4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="K4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="L4">
         <v>1.19</v>
@@ -1565,7 +1571,7 @@
         <v>1.14</v>
       </c>
       <c r="P4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q4">
         <v>1.42</v>
@@ -1577,13 +1583,13 @@
         <v>2.02</v>
       </c>
       <c r="T4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U4">
         <v>1.33</v>
       </c>
       <c r="V4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>1.01</v>
@@ -1601,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC4">
         <v>36</v>
@@ -1619,7 +1625,7 @@
         <v>950</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>130</v>
@@ -1646,7 +1652,7 @@
         <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4">
         <v>6.2</v>
@@ -1655,28 +1661,28 @@
         <v>5.7</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AV4">
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AZ4">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BB4">
         <v>8.4</v>
@@ -1757,7 +1763,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1774,19 +1780,19 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
         <v>2.76</v>
       </c>
       <c r="I5">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -1798,16 +1804,16 @@
         <v>1.39</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
         <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
         <v>2.14</v>
@@ -1816,10 +1822,10 @@
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
         <v>2.16</v>
@@ -1870,7 +1876,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL5">
         <v>55</v>
@@ -1879,10 +1885,10 @@
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1906,7 +1912,7 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX5">
         <v>17.5</v>
@@ -1918,25 +1924,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC5">
         <v>6</v>
       </c>
       <c r="BD5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
+        <v>6</v>
+      </c>
+      <c r="BG5">
         <v>5.9</v>
-      </c>
-      <c r="BG5">
-        <v>5.8</v>
       </c>
       <c r="BH5">
         <v>3.6</v>
@@ -1978,7 +1984,7 @@
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
         <v>25</v>
@@ -1999,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="CB5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2016,13 +2022,13 @@
         <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H6">
         <v>5.8</v>
@@ -2031,7 +2037,7 @@
         <v>6.2</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>5.3</v>
@@ -2064,13 +2070,13 @@
         <v>1.53</v>
       </c>
       <c r="U6">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V6">
         <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -2079,7 +2085,7 @@
         <v>36</v>
       </c>
       <c r="Z6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2106,10 +2112,10 @@
         <v>17</v>
       </c>
       <c r="AI6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK6">
         <v>14</v>
@@ -2127,7 +2133,7 @@
         <v>38</v>
       </c>
       <c r="AP6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ6">
         <v>32</v>
@@ -2151,7 +2157,7 @@
         <v>50</v>
       </c>
       <c r="AX6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>9.800000000000001</v>
@@ -2172,13 +2178,13 @@
         <v>19.5</v>
       </c>
       <c r="BE6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF6">
         <v>4.5</v>
       </c>
       <c r="BG6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH6">
         <v>5.4</v>
@@ -2187,7 +2193,7 @@
         <v>4.9</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6">
         <v>8</v>
@@ -2196,7 +2202,7 @@
         <v>90</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN6">
         <v>4.9</v>
@@ -2226,13 +2232,13 @@
         <v>38</v>
       </c>
       <c r="BW6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
         <v>34</v>
       </c>
       <c r="BY6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>9.6</v>
@@ -2241,7 +2247,7 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2258,169 +2264,169 @@
         <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F7">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="G7">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H7">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="I7">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
         <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
         <v>1.92</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T7">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U7">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
         <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB7">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AC7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
       </c>
       <c r="AE7">
+        <v>40</v>
+      </c>
+      <c r="AF7">
+        <v>65</v>
+      </c>
+      <c r="AG7">
         <v>55</v>
       </c>
-      <c r="AF7">
-        <v>70</v>
-      </c>
-      <c r="AG7">
-        <v>85</v>
-      </c>
       <c r="AH7">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AI7">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AJ7">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="AK7">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AL7">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AM7">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN7">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AO7">
         <v>12</v>
       </c>
       <c r="AP7">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AQ7">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AR7">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AS7">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AT7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AU7">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AW7">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="AX7">
+        <v>32</v>
+      </c>
+      <c r="AY7">
+        <v>20</v>
+      </c>
+      <c r="AZ7">
+        <v>20</v>
+      </c>
+      <c r="BA7">
+        <v>8</v>
+      </c>
+      <c r="BB7">
         <v>9.4</v>
       </c>
-      <c r="AY7">
-        <v>6.6</v>
-      </c>
-      <c r="AZ7">
-        <v>6.2</v>
-      </c>
-      <c r="BA7">
+      <c r="BC7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD7">
         <v>9</v>
       </c>
-      <c r="BB7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC7">
-        <v>8</v>
-      </c>
-      <c r="BD7">
-        <v>8</v>
-      </c>
       <c r="BE7">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BF7">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2483,7 +2489,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2500,7 +2506,7 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F8">
         <v>1.12</v>
@@ -2509,13 +2515,13 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2527,7 +2533,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
         <v>1.01</v>
@@ -2536,7 +2542,7 @@
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R8">
         <v>1.18</v>
@@ -2725,7 +2731,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2742,16 +2748,16 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F9">
         <v>1.33</v>
       </c>
       <c r="G9">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I9">
         <v>990</v>
@@ -2760,7 +2766,7 @@
         <v>3.75</v>
       </c>
       <c r="K9">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2796,7 +2802,7 @@
         <v>1.01</v>
       </c>
       <c r="W9">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2967,7 +2973,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2984,7 +2990,7 @@
         <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F10">
         <v>2.82</v>
@@ -3209,12 +3215,12 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
@@ -3226,70 +3232,70 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F11">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G11">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="H11">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="O11">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="P11">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="Q11">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="R11">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="S11">
-        <v>2.78</v>
+        <v>1.87</v>
       </c>
       <c r="T11">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="U11">
-        <v>1.12</v>
+        <v>2.74</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3301,10 +3307,10 @@
         <v>1000</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF11">
         <v>1000</v>
@@ -3313,13 +3319,13 @@
         <v>1000</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK11">
         <v>1000</v>
@@ -3328,67 +3334,67 @@
         <v>1000</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3451,12 +3457,12 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>93</v>
@@ -3468,70 +3474,70 @@
         <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F12">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G12">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I12">
+        <v>3.8</v>
+      </c>
+      <c r="J12">
         <v>3.4</v>
       </c>
-      <c r="J12">
-        <v>4.3</v>
-      </c>
       <c r="K12">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>3.25</v>
+      </c>
+      <c r="O12">
         <v>1.02</v>
       </c>
-      <c r="N12">
-        <v>7.2</v>
-      </c>
-      <c r="O12">
-        <v>1.09</v>
-      </c>
       <c r="P12">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q12">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="S12">
-        <v>1.89</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="U12">
-        <v>2.74</v>
+        <v>1.12</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="X12">
         <v>1000</v>
       </c>
       <c r="Y12">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3543,10 +3549,10 @@
         <v>1000</v>
       </c>
       <c r="AD12">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
         <v>1000</v>
@@ -3555,13 +3561,13 @@
         <v>1000</v>
       </c>
       <c r="AH12">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
         <v>1000</v>
@@ -3573,64 +3579,64 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3693,7 +3699,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3710,49 +3716,49 @@
         <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F13">
-        <v>2.36</v>
+        <v>1.6</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="H13">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="I13">
-        <v>2.94</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K13">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>2.72</v>
       </c>
       <c r="O13">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="Q13">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="R13">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S13">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3761,10 +3767,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="W13">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3935,7 +3941,7 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3952,49 +3958,49 @@
         <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="G14">
+        <v>3.85</v>
+      </c>
+      <c r="H14">
         <v>2.1</v>
       </c>
-      <c r="H14">
-        <v>4.2</v>
-      </c>
       <c r="I14">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="O14">
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="R14">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S14">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4003,10 +4009,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4177,7 +4183,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4194,25 +4200,25 @@
         <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F15">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G15">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J15">
         <v>3</v>
       </c>
       <c r="K15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4221,22 +4227,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="O15">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P15">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q15">
+        <v>1.44</v>
+      </c>
+      <c r="R15">
         <v>1.42</v>
       </c>
-      <c r="R15">
-        <v>1.38</v>
-      </c>
       <c r="S15">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4245,10 +4251,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4419,7 +4425,7 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4436,7 +4442,7 @@
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F16">
         <v>2.86</v>
@@ -4445,7 +4451,7 @@
         <v>3</v>
       </c>
       <c r="H16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I16">
         <v>3</v>
@@ -4460,25 +4466,25 @@
         <v>1.47</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N16">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="O16">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="P16">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q16">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T16">
         <v>1.92</v>
@@ -4496,10 +4502,10 @@
         <v>9.6</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA16">
         <v>55</v>
@@ -4514,43 +4520,43 @@
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG16">
         <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI16">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ16">
         <v>55</v>
       </c>
       <c r="AK16">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL16">
         <v>75</v>
       </c>
       <c r="AM16">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN16">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO16">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ16">
         <v>8.4</v>
-      </c>
-      <c r="AQ16">
-        <v>7.6</v>
       </c>
       <c r="AR16">
         <v>14.5</v>
@@ -4559,43 +4565,43 @@
         <v>40</v>
       </c>
       <c r="AT16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
         <v>6.6</v>
       </c>
       <c r="AV16">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW16">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX16">
         <v>14.5</v>
       </c>
       <c r="AY16">
+        <v>12.5</v>
+      </c>
+      <c r="AZ16">
+        <v>18.5</v>
+      </c>
+      <c r="BA16">
+        <v>50</v>
+      </c>
+      <c r="BB16">
+        <v>42</v>
+      </c>
+      <c r="BC16">
+        <v>34</v>
+      </c>
+      <c r="BD16">
+        <v>50</v>
+      </c>
+      <c r="BE16">
         <v>12</v>
       </c>
-      <c r="AZ16">
-        <v>19.5</v>
-      </c>
-      <c r="BA16">
-        <v>40</v>
-      </c>
-      <c r="BB16">
-        <v>38</v>
-      </c>
-      <c r="BC16">
-        <v>32</v>
-      </c>
-      <c r="BD16">
-        <v>42</v>
-      </c>
-      <c r="BE16">
-        <v>9.6</v>
-      </c>
       <c r="BF16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG16">
         <v>34</v>
@@ -4661,7 +4667,7 @@
         <v>1.41</v>
       </c>
       <c r="CB16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4678,7 +4684,7 @@
         <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F17">
         <v>1.69</v>
@@ -4903,7 +4909,7 @@
         <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4920,80 +4926,80 @@
         <v>119</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F18">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="G18">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="H18">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="I18">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="J18">
         <v>3.7</v>
       </c>
       <c r="K18">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="R18">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S18">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="T18">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="U18">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="W18">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="X18">
         <v>1000</v>
       </c>
       <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
         <v>950</v>
       </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>970</v>
-      </c>
       <c r="AD18">
         <v>1000</v>
       </c>
@@ -5031,58 +5037,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AQ18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AR18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AS18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AT18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AU18">
+        <v>1.01</v>
+      </c>
+      <c r="AV18">
         <v>1.05</v>
       </c>
-      <c r="AV18">
-        <v>1.11</v>
-      </c>
       <c r="AW18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AX18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AY18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AZ18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BA18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BB18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BC18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BD18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BE18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BF18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BG18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5145,7 +5151,7 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5162,67 +5168,67 @@
         <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F19">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="G19">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="H19">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="I19">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="J19">
         <v>3.7</v>
       </c>
       <c r="K19">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O19">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q19">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="R19">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S19">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="T19">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="W19">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="X19">
         <v>1000</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z19">
         <v>1000</v>
@@ -5234,7 +5240,7 @@
         <v>1000</v>
       </c>
       <c r="AC19">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5273,58 +5279,58 @@
         <v>1000</v>
       </c>
       <c r="AP19">
+        <v>1.11</v>
+      </c>
+      <c r="AQ19">
+        <v>1.06</v>
+      </c>
+      <c r="AR19">
+        <v>1.11</v>
+      </c>
+      <c r="AS19">
+        <v>1.11</v>
+      </c>
+      <c r="AT19">
+        <v>1.11</v>
+      </c>
+      <c r="AU19">
         <v>1.05</v>
       </c>
-      <c r="AQ19">
-        <v>1.05</v>
-      </c>
-      <c r="AR19">
-        <v>1.05</v>
-      </c>
-      <c r="AS19">
-        <v>1.05</v>
-      </c>
-      <c r="AT19">
-        <v>1.05</v>
-      </c>
-      <c r="AU19">
-        <v>1.01</v>
-      </c>
       <c r="AV19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AW19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AX19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AY19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AZ19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BA19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BB19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BC19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BD19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BE19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BF19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BG19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5387,7 +5393,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5404,7 +5410,7 @@
         <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F20">
         <v>1.9</v>
@@ -5434,7 +5440,7 @@
         <v>2.4</v>
       </c>
       <c r="O20">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P20">
         <v>2.02</v>
@@ -5443,7 +5449,7 @@
         <v>1.74</v>
       </c>
       <c r="R20">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
         <v>2.74</v>
@@ -5629,7 +5635,7 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5646,7 +5652,7 @@
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F21">
         <v>3.2</v>
@@ -5871,7 +5877,7 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5888,10 +5894,10 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F22">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G22">
         <v>3.9</v>
@@ -5900,13 +5906,13 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L22">
         <v>1.25</v>
@@ -5915,34 +5921,34 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P22">
         <v>2.44</v>
       </c>
       <c r="Q22">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="R22">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S22">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="T22">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U22">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V22">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W22">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -5963,13 +5969,13 @@
         <v>970</v>
       </c>
       <c r="AD22">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE22">
         <v>1000</v>
       </c>
       <c r="AF22">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
         <v>1000</v>
@@ -5978,115 +5984,115 @@
         <v>1000</v>
       </c>
       <c r="AI22">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
         <v>970</v>
       </c>
       <c r="AP22">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AR22">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AS22">
-        <v>16.5</v>
+        <v>1.21</v>
       </c>
       <c r="AT22">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AU22">
-        <v>8.6</v>
+        <v>1.21</v>
       </c>
       <c r="AV22">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AW22">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AX22">
-        <v>20</v>
+        <v>1.21</v>
       </c>
       <c r="AY22">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AZ22">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="BA22">
-        <v>19</v>
+        <v>1.21</v>
       </c>
       <c r="BB22">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="BC22">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="BD22">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="BE22">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="BF22">
-        <v>19</v>
+        <v>1.21</v>
       </c>
       <c r="BG22">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="BH22">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
@@ -6098,27 +6104,27 @@
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
         <v>93</v>
@@ -6130,232 +6136,474 @@
         <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F23">
-        <v>6.6</v>
+        <v>2.96</v>
       </c>
       <c r="G23">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="H23">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="I23">
-        <v>1.52</v>
+        <v>2.38</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="K23">
         <v>5.9</v>
       </c>
       <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>4.7</v>
+      </c>
+      <c r="O23">
+        <v>1.16</v>
+      </c>
+      <c r="P23">
+        <v>2.28</v>
+      </c>
+      <c r="Q23">
+        <v>1.56</v>
+      </c>
+      <c r="R23">
+        <v>1.6</v>
+      </c>
+      <c r="S23">
+        <v>2.38</v>
+      </c>
+      <c r="T23">
+        <v>1.11</v>
+      </c>
+      <c r="U23">
+        <v>1.11</v>
+      </c>
+      <c r="V23">
+        <v>1.73</v>
+      </c>
+      <c r="W23">
+        <v>1.36</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>1000</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>1000</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23">
+        <v>1.01</v>
+      </c>
+      <c r="AR23">
+        <v>1.01</v>
+      </c>
+      <c r="AS23">
+        <v>1.01</v>
+      </c>
+      <c r="AT23">
+        <v>1.01</v>
+      </c>
+      <c r="AU23">
+        <v>1.01</v>
+      </c>
+      <c r="AV23">
+        <v>1.01</v>
+      </c>
+      <c r="AW23">
+        <v>1.01</v>
+      </c>
+      <c r="AX23">
+        <v>1.01</v>
+      </c>
+      <c r="AY23">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23">
+        <v>1.01</v>
+      </c>
+      <c r="BA23">
+        <v>1.01</v>
+      </c>
+      <c r="BB23">
+        <v>1.01</v>
+      </c>
+      <c r="BC23">
+        <v>1.01</v>
+      </c>
+      <c r="BD23">
+        <v>1.01</v>
+      </c>
+      <c r="BE23">
+        <v>1.01</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.04</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.04</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.04</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.04</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.04</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.04</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.04</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.04</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24">
+        <v>6.8</v>
+      </c>
+      <c r="G24">
+        <v>8.6</v>
+      </c>
+      <c r="H24">
+        <v>1.44</v>
+      </c>
+      <c r="I24">
+        <v>1.52</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
+      </c>
+      <c r="K24">
+        <v>5.8</v>
+      </c>
+      <c r="L24">
         <v>1.18</v>
       </c>
-      <c r="M23">
-        <v>1.03</v>
-      </c>
-      <c r="N23">
+      <c r="M24">
+        <v>1.02</v>
+      </c>
+      <c r="N24">
         <v>6</v>
       </c>
-      <c r="O23">
-        <v>1.15</v>
-      </c>
-      <c r="P23">
-        <v>2.78</v>
-      </c>
-      <c r="Q23">
+      <c r="O24">
+        <v>1.16</v>
+      </c>
+      <c r="P24">
+        <v>2.8</v>
+      </c>
+      <c r="Q24">
         <v>1.47</v>
       </c>
-      <c r="R23">
-        <v>1.73</v>
-      </c>
-      <c r="S23">
-        <v>2.14</v>
-      </c>
-      <c r="T23">
-        <v>1.67</v>
-      </c>
-      <c r="U23">
-        <v>2.26</v>
-      </c>
-      <c r="V23">
+      <c r="R24">
+        <v>1.72</v>
+      </c>
+      <c r="S24">
+        <v>2.1</v>
+      </c>
+      <c r="T24">
+        <v>1.69</v>
+      </c>
+      <c r="U24">
+        <v>2.24</v>
+      </c>
+      <c r="V24">
         <v>2.92</v>
       </c>
-      <c r="W23">
-        <v>1.14</v>
-      </c>
-      <c r="X23">
-        <v>950</v>
-      </c>
-      <c r="Y23">
-        <v>1000</v>
-      </c>
-      <c r="Z23">
-        <v>1000</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>950</v>
-      </c>
-      <c r="AC23">
-        <v>1000</v>
-      </c>
-      <c r="AD23">
-        <v>970</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
-        <v>1000</v>
-      </c>
-      <c r="AG23">
-        <v>950</v>
-      </c>
-      <c r="AH23">
-        <v>1000</v>
-      </c>
-      <c r="AI23">
+      <c r="W24">
+        <v>1.13</v>
+      </c>
+      <c r="X24">
+        <v>38</v>
+      </c>
+      <c r="Y24">
+        <v>14</v>
+      </c>
+      <c r="Z24">
+        <v>12</v>
+      </c>
+      <c r="AA24">
+        <v>14.5</v>
+      </c>
+      <c r="AB24">
+        <v>38</v>
+      </c>
+      <c r="AC24">
+        <v>14</v>
+      </c>
+      <c r="AD24">
+        <v>11.5</v>
+      </c>
+      <c r="AE24">
+        <v>15</v>
+      </c>
+      <c r="AF24">
+        <v>75</v>
+      </c>
+      <c r="AG24">
         <v>34</v>
       </c>
-      <c r="AJ23">
-        <v>1000</v>
-      </c>
-      <c r="AK23">
+      <c r="AH24">
+        <v>24</v>
+      </c>
+      <c r="AI24">
+        <v>34</v>
+      </c>
+      <c r="AJ24">
+        <v>210</v>
+      </c>
+      <c r="AK24">
         <v>100</v>
       </c>
-      <c r="AL23">
-        <v>1000</v>
-      </c>
-      <c r="AM23">
+      <c r="AL24">
+        <v>80</v>
+      </c>
+      <c r="AM24">
         <v>95</v>
       </c>
-      <c r="AN23">
+      <c r="AN24">
         <v>85</v>
       </c>
-      <c r="AO23">
-        <v>5.2</v>
-      </c>
-      <c r="AP23">
-        <v>1.69</v>
-      </c>
-      <c r="AQ23">
-        <v>10.5</v>
-      </c>
-      <c r="AR23">
-        <v>1.77</v>
-      </c>
-      <c r="AS23">
-        <v>1.77</v>
-      </c>
-      <c r="AT23">
-        <v>1.69</v>
-      </c>
-      <c r="AU23">
-        <v>10.5</v>
-      </c>
-      <c r="AV23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW23">
-        <v>1.77</v>
-      </c>
-      <c r="AX23">
-        <v>1.77</v>
-      </c>
-      <c r="AY23">
+      <c r="AO24">
+        <v>4.9</v>
+      </c>
+      <c r="AP24">
+        <v>8.4</v>
+      </c>
+      <c r="AQ24">
+        <v>11</v>
+      </c>
+      <c r="AR24">
+        <v>10</v>
+      </c>
+      <c r="AS24">
+        <v>12</v>
+      </c>
+      <c r="AT24">
+        <v>8.4</v>
+      </c>
+      <c r="AU24">
+        <v>11</v>
+      </c>
+      <c r="AV24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW24">
+        <v>12</v>
+      </c>
+      <c r="AX24">
+        <v>7.8</v>
+      </c>
+      <c r="AY24">
         <v>19</v>
       </c>
-      <c r="AZ23">
-        <v>16</v>
-      </c>
-      <c r="BA23">
-        <v>19</v>
-      </c>
-      <c r="BB23">
-        <v>1.77</v>
-      </c>
-      <c r="BC23">
-        <v>1.74</v>
-      </c>
-      <c r="BD23">
-        <v>1.77</v>
-      </c>
-      <c r="BE23">
-        <v>1.74</v>
-      </c>
-      <c r="BF23">
-        <v>1.73</v>
-      </c>
-      <c r="BG23">
-        <v>4.2</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.04</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>1.04</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.04</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.04</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.04</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.04</v>
-      </c>
-      <c r="BT23">
-        <v>1000</v>
-      </c>
-      <c r="BU23">
-        <v>1.04</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.04</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.04</v>
-      </c>
-      <c r="BZ23">
-        <v>1000</v>
-      </c>
-      <c r="CA23">
-        <v>1.04</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>147</v>
+      <c r="AZ24">
+        <v>17.5</v>
+      </c>
+      <c r="BA24">
+        <v>7.8</v>
+      </c>
+      <c r="BB24">
+        <v>8.4</v>
+      </c>
+      <c r="BC24">
+        <v>8</v>
+      </c>
+      <c r="BD24">
+        <v>7.8</v>
+      </c>
+      <c r="BE24">
+        <v>7.8</v>
+      </c>
+      <c r="BF24">
+        <v>7.8</v>
+      </c>
+      <c r="BG24">
+        <v>4.1</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.04</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.04</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.04</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.04</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.04</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.04</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.04</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.04</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -463,7 +463,7 @@
     <t>Heracles</t>
   </si>
   <si>
-    <t>2026-09-30 21:08:44</t>
+    <t>2026-09-30 23:19:46</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1060,7 @@
         <v>1.71</v>
       </c>
       <c r="G2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -1084,13 +1084,13 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R2">
         <v>1.27</v>
@@ -1108,7 +1108,7 @@
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
         <v>12</v>
@@ -1159,7 +1159,7 @@
         <v>230</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO2">
         <v>190</v>
@@ -1174,7 +1174,7 @@
         <v>24</v>
       </c>
       <c r="AS2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1210,16 +1210,16 @@
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH2">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
         <v>2.84</v>
@@ -1234,7 +1234,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
@@ -1252,7 +1252,7 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
         <v>10</v>
@@ -1264,19 +1264,19 @@
         <v>70</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>100</v>
       </c>
       <c r="BY2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA2">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>149</v>
@@ -1302,22 +1302,22 @@
         <v>3.15</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J3">
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.04</v>
@@ -1347,25 +1347,25 @@
         <v>2.48</v>
       </c>
       <c r="V3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X3">
         <v>24</v>
       </c>
       <c r="Y3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z3">
         <v>17</v>
       </c>
       <c r="AA3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC3">
         <v>9.6</v>
@@ -1374,10 +1374,10 @@
         <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG3">
         <v>14.5</v>
@@ -1401,10 +1401,10 @@
         <v>65</v>
       </c>
       <c r="AN3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP3">
         <v>18</v>
@@ -1416,7 +1416,7 @@
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1428,7 +1428,7 @@
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX3">
         <v>21</v>
@@ -1440,16 +1440,16 @@
         <v>13</v>
       </c>
       <c r="BA3">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="BB3">
         <v>23</v>
       </c>
       <c r="BC3">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BE3">
         <v>27</v>
@@ -1458,7 +1458,7 @@
         <v>16.5</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1541,7 +1541,7 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G4">
         <v>60</v>
@@ -1571,7 +1571,7 @@
         <v>1.14</v>
       </c>
       <c r="P4">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q4">
         <v>1.42</v>
@@ -1586,7 +1586,7 @@
         <v>3.45</v>
       </c>
       <c r="U4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -1616,7 +1616,7 @@
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF4">
         <v>1000</v>
@@ -1649,7 +1649,7 @@
         <v>2.92</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
         <v>9.199999999999999</v>
@@ -1661,28 +1661,28 @@
         <v>5.7</v>
       </c>
       <c r="AT4">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AU4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV4">
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX4">
         <v>8.4</v>
       </c>
       <c r="AY4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="BA4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BB4">
         <v>8.4</v>
@@ -1789,16 +1789,16 @@
         <v>3.2</v>
       </c>
       <c r="H5">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I5">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
         <v>1.39</v>
@@ -1813,10 +1813,10 @@
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
         <v>1.32</v>
@@ -1825,13 +1825,13 @@
         <v>3.95</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
         <v>1.46</v>
@@ -1840,7 +1840,7 @@
         <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
         <v>22</v>
@@ -1855,7 +1855,7 @@
         <v>7</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
         <v>38</v>
@@ -1864,10 +1864,10 @@
         <v>22</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -1885,7 +1885,7 @@
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO5">
         <v>32</v>
@@ -1894,13 +1894,13 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR5">
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
@@ -1912,7 +1912,7 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX5">
         <v>17.5</v>
@@ -1924,25 +1924,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB5">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD5">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE5">
+        <v>7.8</v>
+      </c>
+      <c r="BF5">
+        <v>7</v>
+      </c>
+      <c r="BG5">
         <v>6.8</v>
-      </c>
-      <c r="BF5">
-        <v>6</v>
-      </c>
-      <c r="BG5">
-        <v>5.9</v>
       </c>
       <c r="BH5">
         <v>3.6</v>
@@ -2037,7 +2037,7 @@
         <v>6.2</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
         <v>5.3</v>
@@ -2058,7 +2058,7 @@
         <v>3.3</v>
       </c>
       <c r="Q6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R6">
         <v>1.93</v>
@@ -2067,13 +2067,13 @@
         <v>2.02</v>
       </c>
       <c r="T6">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
         <v>2.72</v>
@@ -2085,7 +2085,7 @@
         <v>36</v>
       </c>
       <c r="Z6">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2112,10 +2112,10 @@
         <v>17</v>
       </c>
       <c r="AI6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK6">
         <v>14</v>
@@ -2124,7 +2124,7 @@
         <v>22</v>
       </c>
       <c r="AM6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN6">
         <v>4.8</v>
@@ -2133,7 +2133,7 @@
         <v>38</v>
       </c>
       <c r="AP6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ6">
         <v>32</v>
@@ -2175,10 +2175,10 @@
         <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF6">
         <v>4.5</v>
@@ -2193,19 +2193,19 @@
         <v>4.9</v>
       </c>
       <c r="BJ6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK6">
         <v>8</v>
       </c>
       <c r="BL6">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="BM6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO6">
         <v>4.4</v>
@@ -2226,19 +2226,19 @@
         <v>10</v>
       </c>
       <c r="BU6">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV6">
         <v>38</v>
       </c>
       <c r="BW6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
         <v>34</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>9.6</v>
@@ -2270,13 +2270,13 @@
         <v>5.9</v>
       </c>
       <c r="G7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H7">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="I7">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2285,40 +2285,40 @@
         <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R7">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
         <v>3.4</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V7">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
         <v>15.5</v>
@@ -2327,13 +2327,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AA7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
@@ -2342,7 +2342,7 @@
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF7">
         <v>65</v>
@@ -2351,10 +2351,10 @@
         <v>55</v>
       </c>
       <c r="AH7">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AI7">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AJ7">
         <v>220</v>
@@ -2393,7 +2393,7 @@
         <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AW7">
         <v>15</v>
@@ -2408,22 +2408,22 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BB7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC7">
         <v>9.199999999999999</v>
       </c>
       <c r="BD7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7">
+        <v>46</v>
+      </c>
+      <c r="BF7">
         <v>9.4</v>
-      </c>
-      <c r="BF7">
-        <v>9.199999999999999</v>
       </c>
       <c r="BG7">
         <v>7.6</v>
@@ -2515,13 +2515,13 @@
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2557,10 +2557,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2757,16 +2757,16 @@
         <v>1.61</v>
       </c>
       <c r="H9">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>3.75</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2799,7 +2799,7 @@
         <v>1.12</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W9">
         <v>2.62</v>
@@ -3002,7 +3002,7 @@
         <v>1.81</v>
       </c>
       <c r="I10">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J10">
         <v>3.1</v>
@@ -3041,7 +3041,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W10">
         <v>1.27</v>
@@ -3743,7 +3743,7 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="O13">
         <v>1.02</v>
@@ -3964,7 +3964,7 @@
         <v>2.42</v>
       </c>
       <c r="G14">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="H14">
         <v>2.1</v>
@@ -3985,7 +3985,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O14">
         <v>1.02</v>
@@ -3994,10 +3994,10 @@
         <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="R14">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S14">
         <v>2.06</v>
@@ -4012,7 +4012,7 @@
         <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4448,7 +4448,7 @@
         <v>2.86</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H16">
         <v>2.84</v>
@@ -4472,7 +4472,7 @@
         <v>2.84</v>
       </c>
       <c r="O16">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P16">
         <v>1.63</v>
@@ -4487,10 +4487,10 @@
         <v>4.9</v>
       </c>
       <c r="T16">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U16">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="V16">
         <v>1.5</v>
@@ -4553,7 +4553,7 @@
         <v>46</v>
       </c>
       <c r="AP16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16">
         <v>8.4</v>
@@ -4565,7 +4565,7 @@
         <v>40</v>
       </c>
       <c r="AT16">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16">
         <v>6.6</v>
@@ -4687,166 +4687,166 @@
         <v>141</v>
       </c>
       <c r="F17">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G17">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H17">
         <v>4.1</v>
       </c>
       <c r="I17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="O17">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
         <v>2.4</v>
       </c>
       <c r="Q17">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R17">
         <v>1.56</v>
       </c>
       <c r="S17">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T17">
         <v>1.53</v>
       </c>
       <c r="U17">
+        <v>2.38</v>
+      </c>
+      <c r="V17">
+        <v>1.22</v>
+      </c>
+      <c r="W17">
+        <v>2.14</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>970</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>970</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.18</v>
+      </c>
+      <c r="AQ17">
+        <v>1.18</v>
+      </c>
+      <c r="AR17">
+        <v>1.18</v>
+      </c>
+      <c r="AS17">
+        <v>1.18</v>
+      </c>
+      <c r="AT17">
+        <v>1.18</v>
+      </c>
+      <c r="AU17">
         <v>1.11</v>
       </c>
-      <c r="V17">
-        <v>1.21</v>
-      </c>
-      <c r="W17">
-        <v>2.12</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17">
-        <v>1.01</v>
-      </c>
-      <c r="AR17">
-        <v>1.01</v>
-      </c>
-      <c r="AS17">
-        <v>1.01</v>
-      </c>
-      <c r="AT17">
-        <v>1.01</v>
-      </c>
-      <c r="AU17">
-        <v>1.01</v>
-      </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4932,13 +4932,13 @@
         <v>2.68</v>
       </c>
       <c r="G18">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H18">
         <v>2.08</v>
       </c>
       <c r="I18">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J18">
         <v>3.7</v>
@@ -4977,7 +4977,7 @@
         <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
         <v>1.41</v>
@@ -5180,13 +5180,13 @@
         <v>1.88</v>
       </c>
       <c r="I19">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="J19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5219,7 +5219,7 @@
         <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="W19">
         <v>1.28</v>
@@ -5276,58 +5276,58 @@
         <v>1000</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP19">
+        <v>1.16</v>
+      </c>
+      <c r="AQ19">
         <v>1.11</v>
       </c>
-      <c r="AQ19">
-        <v>1.06</v>
-      </c>
       <c r="AR19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AS19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AU19">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AV19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AW19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AX19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AY19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AZ19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BA19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BB19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BC19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BD19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BE19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG19">
         <v>1.11</v>
@@ -5897,19 +5897,19 @@
         <v>146</v>
       </c>
       <c r="F22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G22">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H22">
         <v>2</v>
       </c>
       <c r="I22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
         <v>4.4</v>
@@ -5921,202 +5921,202 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="O22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
         <v>2.44</v>
       </c>
       <c r="Q22">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="R22">
+        <v>1.58</v>
+      </c>
+      <c r="S22">
+        <v>2.52</v>
+      </c>
+      <c r="T22">
+        <v>1.59</v>
+      </c>
+      <c r="U22">
+        <v>2.48</v>
+      </c>
+      <c r="V22">
+        <v>1.9</v>
+      </c>
+      <c r="W22">
+        <v>1.35</v>
+      </c>
+      <c r="X22">
+        <v>25</v>
+      </c>
+      <c r="Y22">
+        <v>14</v>
+      </c>
+      <c r="Z22">
+        <v>16.5</v>
+      </c>
+      <c r="AA22">
+        <v>26</v>
+      </c>
+      <c r="AB22">
+        <v>23</v>
+      </c>
+      <c r="AC22">
+        <v>10.5</v>
+      </c>
+      <c r="AD22">
+        <v>11.5</v>
+      </c>
+      <c r="AE22">
+        <v>24</v>
+      </c>
+      <c r="AF22">
+        <v>32</v>
+      </c>
+      <c r="AG22">
+        <v>19</v>
+      </c>
+      <c r="AH22">
+        <v>19</v>
+      </c>
+      <c r="AI22">
+        <v>34</v>
+      </c>
+      <c r="AJ22">
+        <v>80</v>
+      </c>
+      <c r="AK22">
+        <v>40</v>
+      </c>
+      <c r="AL22">
+        <v>42</v>
+      </c>
+      <c r="AM22">
+        <v>75</v>
+      </c>
+      <c r="AN22">
+        <v>34</v>
+      </c>
+      <c r="AO22">
+        <v>10.5</v>
+      </c>
+      <c r="AP22">
+        <v>19.5</v>
+      </c>
+      <c r="AQ22">
+        <v>11.5</v>
+      </c>
+      <c r="AR22">
+        <v>13</v>
+      </c>
+      <c r="AS22">
+        <v>20</v>
+      </c>
+      <c r="AT22">
+        <v>16</v>
+      </c>
+      <c r="AU22">
+        <v>8.4</v>
+      </c>
+      <c r="AV22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW22">
+        <v>16</v>
+      </c>
+      <c r="AX22">
+        <v>21</v>
+      </c>
+      <c r="AY22">
+        <v>13.5</v>
+      </c>
+      <c r="AZ22">
+        <v>13.5</v>
+      </c>
+      <c r="BA22">
+        <v>20</v>
+      </c>
+      <c r="BB22">
+        <v>6.6</v>
+      </c>
+      <c r="BC22">
+        <v>6.2</v>
+      </c>
+      <c r="BD22">
+        <v>6.2</v>
+      </c>
+      <c r="BE22">
+        <v>6.6</v>
+      </c>
+      <c r="BF22">
+        <v>19.5</v>
+      </c>
+      <c r="BG22">
+        <v>9</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.17</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
         <v>1.52</v>
       </c>
-      <c r="S22">
-        <v>2.38</v>
-      </c>
-      <c r="T22">
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.17</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
         <v>1.52</v>
       </c>
-      <c r="U22">
-        <v>2.36</v>
-      </c>
-      <c r="V22">
-        <v>1.88</v>
-      </c>
-      <c r="W22">
-        <v>1.36</v>
-      </c>
-      <c r="X22">
-        <v>1000</v>
-      </c>
-      <c r="Y22">
-        <v>1000</v>
-      </c>
-      <c r="Z22">
-        <v>1000</v>
-      </c>
-      <c r="AA22">
-        <v>1000</v>
-      </c>
-      <c r="AB22">
-        <v>1000</v>
-      </c>
-      <c r="AC22">
-        <v>970</v>
-      </c>
-      <c r="AD22">
-        <v>970</v>
-      </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>1000</v>
-      </c>
-      <c r="AH22">
-        <v>1000</v>
-      </c>
-      <c r="AI22">
-        <v>1000</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
-        <v>970</v>
-      </c>
-      <c r="AP22">
-        <v>1.21</v>
-      </c>
-      <c r="AQ22">
-        <v>1.23</v>
-      </c>
-      <c r="AR22">
-        <v>1.23</v>
-      </c>
-      <c r="AS22">
-        <v>1.21</v>
-      </c>
-      <c r="AT22">
-        <v>1.23</v>
-      </c>
-      <c r="AU22">
-        <v>1.21</v>
-      </c>
-      <c r="AV22">
-        <v>1.23</v>
-      </c>
-      <c r="AW22">
-        <v>1.23</v>
-      </c>
-      <c r="AX22">
-        <v>1.21</v>
-      </c>
-      <c r="AY22">
-        <v>1.23</v>
-      </c>
-      <c r="AZ22">
-        <v>1.23</v>
-      </c>
-      <c r="BA22">
-        <v>1.21</v>
-      </c>
-      <c r="BB22">
-        <v>1.21</v>
-      </c>
-      <c r="BC22">
-        <v>1.21</v>
-      </c>
-      <c r="BD22">
-        <v>1.21</v>
-      </c>
-      <c r="BE22">
-        <v>1.21</v>
-      </c>
-      <c r="BF22">
-        <v>1.21</v>
-      </c>
-      <c r="BG22">
-        <v>1.21</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.04</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.04</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.04</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.04</v>
-      </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="CB22" t="s">
         <v>149</v>
@@ -6142,19 +6142,19 @@
         <v>2.96</v>
       </c>
       <c r="G23">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="H23">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="I23">
         <v>2.38</v>
       </c>
       <c r="J23">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K23">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6163,22 +6163,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P23">
         <v>2.28</v>
       </c>
       <c r="Q23">
+        <v>1.5</v>
+      </c>
+      <c r="R23">
         <v>1.56</v>
       </c>
-      <c r="R23">
-        <v>1.6</v>
-      </c>
       <c r="S23">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="T23">
         <v>1.11</v>
@@ -6187,10 +6187,10 @@
         <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="W23">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6390,13 +6390,13 @@
         <v>1.44</v>
       </c>
       <c r="I24">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>1.18</v>
@@ -6420,7 +6420,7 @@
         <v>1.72</v>
       </c>
       <c r="S24">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T24">
         <v>1.69</v>
@@ -6429,10 +6429,10 @@
         <v>2.24</v>
       </c>
       <c r="V24">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>38</v>
@@ -6489,7 +6489,7 @@
         <v>4.9</v>
       </c>
       <c r="AP24">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ24">
         <v>11</v>
@@ -6501,7 +6501,7 @@
         <v>12</v>
       </c>
       <c r="AT24">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU24">
         <v>11</v>
@@ -6522,7 +6522,7 @@
         <v>17.5</v>
       </c>
       <c r="BA24">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB24">
         <v>8.4</v>
@@ -6582,7 +6582,7 @@
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BV24">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="176">
   <si>
     <t>League</t>
   </si>
@@ -277,12 +277,12 @@
     <t>Swedish Division 1</t>
   </si>
   <si>
+    <t>Danish 2nd Division</t>
+  </si>
+  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
-    <t>Danish 2nd Division</t>
-  </si>
-  <si>
     <t>Spanish Segunda Division</t>
   </si>
   <si>
@@ -295,6 +295,18 @@
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
     <t>2026-10-02</t>
   </si>
   <si>
@@ -325,6 +337,24 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:15:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
+    <t>23:45:00</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
@@ -352,24 +382,33 @@
     <t>Kristianstads</t>
   </si>
   <si>
+    <t>Karlbergs BK</t>
+  </si>
+  <si>
+    <t>VSK Aarhus FC</t>
+  </si>
+  <si>
+    <t>Naestved</t>
+  </si>
+  <si>
+    <t>Fremad Amager</t>
+  </si>
+  <si>
     <t>Ranheim IL</t>
   </si>
   <si>
-    <t>Karlbergs BK</t>
-  </si>
-  <si>
-    <t>VSK Aarhus FC</t>
-  </si>
-  <si>
-    <t>Fremad Amager</t>
-  </si>
-  <si>
-    <t>Naestved</t>
-  </si>
-  <si>
     <t>Eldense</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
@@ -379,21 +418,36 @@
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Wexford F.C</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>St Lucia</t>
   </si>
   <si>
     <t>Helmond Sport</t>
   </si>
   <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>Atletico FC Cali</t>
+  </si>
+  <si>
+    <t>CA Independiente</t>
+  </si>
+  <si>
+    <t>Sao Bernardo</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
+    <t>Univ Concepcion</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Goias</t>
   </si>
   <si>
@@ -421,24 +475,33 @@
     <t>Ariana FC</t>
   </si>
   <si>
+    <t>Sollentuna FF</t>
+  </si>
+  <si>
+    <t>Brabrand</t>
+  </si>
+  <si>
+    <t>Nykobing FC</t>
+  </si>
+  <si>
+    <t>B93 Copenhagen</t>
+  </si>
+  <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>Sollentuna FF</t>
-  </si>
-  <si>
-    <t>Brabrand</t>
-  </si>
-  <si>
-    <t>B93 Copenhagen</t>
-  </si>
-  <si>
-    <t>Nykobing FC</t>
-  </si>
-  <si>
     <t>Oviedo</t>
   </si>
   <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Longford</t>
+  </si>
+  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
@@ -448,22 +511,37 @@
     <t>Kerry FC</t>
   </si>
   <si>
-    <t>Longford</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>Guadeloupe</t>
   </si>
   <si>
     <t>Heracles</t>
   </si>
   <si>
-    <t>2026-09-30 23:19:46</t>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Real Soacha Cundinamarca FC</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
+    <t>Criciuma</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>2026-10-01 01:31:06</t>
   </si>
 </sst>
 </file>
@@ -795,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1045,16 +1123,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F2">
         <v>1.71</v>
@@ -1075,25 +1153,25 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
         <v>4.3</v>
@@ -1120,7 +1198,7 @@
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB2">
         <v>7</v>
@@ -1141,7 +1219,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2">
         <v>130</v>
@@ -1156,7 +1234,7 @@
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN2">
         <v>14</v>
@@ -1186,7 +1264,7 @@
         <v>20</v>
       </c>
       <c r="AW2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX2">
         <v>8.199999999999999</v>
@@ -1198,7 +1276,7 @@
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB2">
         <v>15</v>
@@ -1222,7 +1300,7 @@
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1252,7 +1330,7 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
         <v>10</v>
@@ -1261,13 +1339,13 @@
         <v>7.2</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW2">
         <v>10</v>
       </c>
       <c r="BX2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BY2">
         <v>10</v>
@@ -1276,10 +1354,10 @@
         <v>28</v>
       </c>
       <c r="CA2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1287,40 +1365,40 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="F3">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H3">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="I3">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
         <v>5</v>
@@ -1329,94 +1407,94 @@
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S3">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T3">
         <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V3">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="X3">
         <v>24</v>
       </c>
       <c r="Y3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AB3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AK3">
         <v>36</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM3">
         <v>65</v>
       </c>
       <c r="AN3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1425,10 +1503,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW3">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AX3">
         <v>21</v>
@@ -1437,28 +1515,28 @@
         <v>12</v>
       </c>
       <c r="AZ3">
+        <v>12</v>
+      </c>
+      <c r="BA3">
+        <v>6.6</v>
+      </c>
+      <c r="BB3">
+        <v>22</v>
+      </c>
+      <c r="BC3">
         <v>13</v>
       </c>
-      <c r="BA3">
-        <v>13.5</v>
-      </c>
-      <c r="BB3">
-        <v>23</v>
-      </c>
-      <c r="BC3">
-        <v>15</v>
-      </c>
       <c r="BD3">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BF3">
         <v>16.5</v>
       </c>
       <c r="BG3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1521,7 +1599,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1529,22 +1607,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H4">
         <v>1.09</v>
@@ -1553,37 +1631,37 @@
         <v>1.11</v>
       </c>
       <c r="J4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="L4">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>1.14</v>
       </c>
       <c r="P4">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
         <v>1.42</v>
       </c>
       <c r="R4">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S4">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="U4">
         <v>1.34</v>
@@ -1604,19 +1682,19 @@
         <v>7.4</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AB4">
         <v>950</v>
       </c>
       <c r="AC4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AD4">
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF4">
         <v>1000</v>
@@ -1646,61 +1724,61 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AQ4">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AR4">
+        <v>4</v>
+      </c>
+      <c r="AS4">
+        <v>3.85</v>
+      </c>
+      <c r="AT4">
+        <v>8.4</v>
+      </c>
+      <c r="AU4">
+        <v>7.2</v>
+      </c>
+      <c r="AV4">
         <v>6.2</v>
       </c>
-      <c r="AS4">
-        <v>5.7</v>
-      </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>28</v>
-      </c>
-      <c r="AV4">
-        <v>17</v>
-      </c>
       <c r="AW4">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="AX4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY4">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4">
         <v>8.4</v>
       </c>
-      <c r="AY4">
-        <v>16</v>
-      </c>
-      <c r="AZ4">
-        <v>8</v>
-      </c>
       <c r="BA4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
-        <v>8.4</v>
+        <v>2.18</v>
       </c>
       <c r="BC4">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE4">
-        <v>8.4</v>
+        <v>2.18</v>
       </c>
       <c r="BF4">
-        <v>8.4</v>
+        <v>2.18</v>
       </c>
       <c r="BG4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1763,7 +1841,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1771,43 +1849,43 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
         <v>2.8</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J5">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>3.2</v>
       </c>
       <c r="L5">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M5">
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
         <v>1.37</v>
@@ -1816,7 +1894,7 @@
         <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.32</v>
@@ -1825,13 +1903,13 @@
         <v>3.95</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
         <v>1.46</v>
@@ -1849,7 +1927,7 @@
         <v>50</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC5">
         <v>7</v>
@@ -1864,7 +1942,7 @@
         <v>22</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
         <v>16.5</v>
@@ -1900,7 +1978,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
@@ -1912,7 +1990,7 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX5">
         <v>17.5</v>
@@ -1924,25 +2002,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
+        <v>7.6</v>
+      </c>
+      <c r="BB5">
+        <v>7.6</v>
+      </c>
+      <c r="BC5">
         <v>7.4</v>
       </c>
-      <c r="BB5">
-        <v>7.4</v>
-      </c>
-      <c r="BC5">
-        <v>7</v>
-      </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH5">
         <v>3.6</v>
@@ -2005,7 +2083,7 @@
         <v>5</v>
       </c>
       <c r="CB5" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2013,19 +2091,19 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="F6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G6">
         <v>1.58</v>
@@ -2037,13 +2115,13 @@
         <v>6.2</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>5.3</v>
       </c>
       <c r="L6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M6">
         <v>1.02</v>
@@ -2067,16 +2145,16 @@
         <v>2.02</v>
       </c>
       <c r="T6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U6">
         <v>2.76</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -2097,7 +2175,7 @@
         <v>13</v>
       </c>
       <c r="AD6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE6">
         <v>60</v>
@@ -2202,7 +2280,7 @@
         <v>65</v>
       </c>
       <c r="BM6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
@@ -2220,34 +2298,34 @@
         <v>17</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU6">
         <v>8.800000000000001</v>
       </c>
       <c r="BV6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX6">
         <v>34</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
         <v>9.6</v>
       </c>
       <c r="CA6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2255,178 +2333,178 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F7">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="I7">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
+        <v>1.84</v>
+      </c>
+      <c r="R7">
+        <v>1.44</v>
+      </c>
+      <c r="S7">
+        <v>3.1</v>
+      </c>
+      <c r="T7">
+        <v>1.94</v>
+      </c>
+      <c r="U7">
         <v>1.93</v>
       </c>
-      <c r="R7">
-        <v>1.35</v>
-      </c>
-      <c r="S7">
-        <v>3.4</v>
-      </c>
-      <c r="T7">
-        <v>1.97</v>
-      </c>
-      <c r="U7">
-        <v>1.88</v>
-      </c>
       <c r="V7">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="Y7">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA7">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AB7">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AC7">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="AF7">
+        <v>75</v>
+      </c>
+      <c r="AG7">
         <v>65</v>
       </c>
-      <c r="AG7">
+      <c r="AH7">
         <v>55</v>
       </c>
-      <c r="AH7">
-        <v>29</v>
-      </c>
       <c r="AI7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ7">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="AK7">
+        <v>140</v>
+      </c>
+      <c r="AL7">
         <v>120</v>
       </c>
-      <c r="AL7">
-        <v>110</v>
-      </c>
       <c r="AM7">
+        <v>160</v>
+      </c>
+      <c r="AN7">
         <v>170</v>
       </c>
-      <c r="AN7">
-        <v>150</v>
-      </c>
       <c r="AO7">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AP7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AU7">
+        <v>9.6</v>
+      </c>
+      <c r="AV7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW7">
+        <v>13.5</v>
+      </c>
+      <c r="AX7">
         <v>8.4</v>
       </c>
-      <c r="AV7">
-        <v>9</v>
-      </c>
-      <c r="AW7">
-        <v>15</v>
-      </c>
-      <c r="AX7">
-        <v>32</v>
-      </c>
       <c r="AY7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BB7">
         <v>9.6</v>
       </c>
       <c r="BC7">
+        <v>9.6</v>
+      </c>
+      <c r="BD7">
+        <v>42</v>
+      </c>
+      <c r="BE7">
+        <v>9</v>
+      </c>
+      <c r="BF7">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE7">
-        <v>46</v>
-      </c>
-      <c r="BF7">
-        <v>9.4</v>
-      </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2489,7 +2567,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2497,19 +2575,19 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="F8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G8">
         <v>990</v>
@@ -2731,7 +2809,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2739,16 +2817,16 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="F9">
         <v>1.33</v>
@@ -2757,7 +2835,7 @@
         <v>1.61</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="I9">
         <v>8.800000000000001</v>
@@ -2766,7 +2844,7 @@
         <v>3.75</v>
       </c>
       <c r="K9">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2973,7 +3051,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2981,16 +3059,16 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="F10">
         <v>2.82</v>
@@ -3215,87 +3293,87 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F11">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G11">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I11">
+        <v>3.8</v>
+      </c>
+      <c r="J11">
         <v>3.4</v>
       </c>
-      <c r="J11">
-        <v>4.3</v>
-      </c>
       <c r="K11">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>3.25</v>
+      </c>
+      <c r="O11">
         <v>1.02</v>
       </c>
-      <c r="N11">
-        <v>6.8</v>
-      </c>
-      <c r="O11">
-        <v>1.09</v>
-      </c>
       <c r="P11">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q11">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="R11">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="S11">
-        <v>1.87</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="U11">
-        <v>2.74</v>
+        <v>1.12</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3307,10 +3385,10 @@
         <v>1000</v>
       </c>
       <c r="AD11">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
         <v>1000</v>
@@ -3319,13 +3397,13 @@
         <v>1000</v>
       </c>
       <c r="AH11">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
         <v>1000</v>
@@ -3334,67 +3412,67 @@
         <v>1000</v>
       </c>
       <c r="AM11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3457,42 +3535,42 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="F12">
+        <v>1.6</v>
+      </c>
+      <c r="G12">
         <v>2.1</v>
       </c>
-      <c r="G12">
-        <v>2.54</v>
-      </c>
       <c r="H12">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="I12">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="L12">
         <v>1.27</v>
@@ -3501,34 +3579,34 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O12">
         <v>1.02</v>
       </c>
       <c r="P12">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="R12">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="T12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="W12">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3699,66 +3777,66 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="F13">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="G13">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="I13">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="J13">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="L13">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P13">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="Q13">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="R13">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S13">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3767,10 +3845,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3941,24 +4019,24 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="F14">
         <v>2.42</v>
@@ -4183,7 +4261,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4191,179 +4269,179 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F15">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="H15">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
+        <v>4.9</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.02</v>
+      </c>
+      <c r="N15">
+        <v>6.8</v>
+      </c>
+      <c r="O15">
+        <v>1.09</v>
+      </c>
+      <c r="P15">
+        <v>3.3</v>
+      </c>
+      <c r="Q15">
+        <v>1.35</v>
+      </c>
+      <c r="R15">
+        <v>1.81</v>
+      </c>
+      <c r="S15">
+        <v>1.72</v>
+      </c>
+      <c r="T15">
+        <v>1.35</v>
+      </c>
+      <c r="U15">
+        <v>2.74</v>
+      </c>
+      <c r="V15">
+        <v>1.41</v>
+      </c>
+      <c r="W15">
+        <v>1.8</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>950</v>
+      </c>
+      <c r="Z15">
+        <v>40</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>19.5</v>
+      </c>
+      <c r="AE15">
+        <v>36</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>17.5</v>
+      </c>
+      <c r="AI15">
+        <v>34</v>
+      </c>
+      <c r="AJ15">
+        <v>36</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>42</v>
+      </c>
+      <c r="AN15">
+        <v>8.6</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.64</v>
+      </c>
+      <c r="AQ15">
+        <v>1.56</v>
+      </c>
+      <c r="AR15">
+        <v>1.58</v>
+      </c>
+      <c r="AS15">
+        <v>1.64</v>
+      </c>
+      <c r="AT15">
+        <v>17</v>
+      </c>
+      <c r="AU15">
+        <v>1.64</v>
+      </c>
+      <c r="AV15">
+        <v>1.51</v>
+      </c>
+      <c r="AW15">
+        <v>1.58</v>
+      </c>
+      <c r="AX15">
+        <v>17</v>
+      </c>
+      <c r="AY15">
+        <v>1.64</v>
+      </c>
+      <c r="AZ15">
+        <v>10.5</v>
+      </c>
+      <c r="BA15">
+        <v>1.58</v>
+      </c>
+      <c r="BB15">
+        <v>1.58</v>
+      </c>
+      <c r="BC15">
+        <v>1.64</v>
+      </c>
+      <c r="BD15">
+        <v>16</v>
+      </c>
+      <c r="BE15">
+        <v>1.58</v>
+      </c>
+      <c r="BF15">
+        <v>5.4</v>
+      </c>
+      <c r="BG15">
         <v>11</v>
       </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>4.6</v>
-      </c>
-      <c r="O15">
-        <v>1.2</v>
-      </c>
-      <c r="P15">
-        <v>2.14</v>
-      </c>
-      <c r="Q15">
-        <v>1.44</v>
-      </c>
-      <c r="R15">
-        <v>1.42</v>
-      </c>
-      <c r="S15">
-        <v>2.44</v>
-      </c>
-      <c r="T15">
-        <v>1.11</v>
-      </c>
-      <c r="U15">
-        <v>1.11</v>
-      </c>
-      <c r="V15">
-        <v>1.51</v>
-      </c>
-      <c r="W15">
-        <v>1.34</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15">
-        <v>1.01</v>
-      </c>
-      <c r="AR15">
-        <v>1.01</v>
-      </c>
-      <c r="AS15">
-        <v>1.01</v>
-      </c>
-      <c r="AT15">
-        <v>1.01</v>
-      </c>
-      <c r="AU15">
-        <v>1.01</v>
-      </c>
-      <c r="AV15">
-        <v>1.01</v>
-      </c>
-      <c r="AW15">
-        <v>1.01</v>
-      </c>
-      <c r="AX15">
-        <v>1.01</v>
-      </c>
-      <c r="AY15">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15">
-        <v>1.01</v>
-      </c>
-      <c r="BA15">
-        <v>1.01</v>
-      </c>
-      <c r="BB15">
-        <v>1.01</v>
-      </c>
-      <c r="BC15">
-        <v>1.01</v>
-      </c>
-      <c r="BD15">
-        <v>1.01</v>
-      </c>
-      <c r="BE15">
-        <v>1.01</v>
-      </c>
-      <c r="BF15">
-        <v>1.01</v>
-      </c>
-      <c r="BG15">
-        <v>1.01</v>
-      </c>
       <c r="BH15">
         <v>1000</v>
       </c>
@@ -4425,7 +4503,7 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4433,16 +4511,16 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="F16">
         <v>2.86</v>
@@ -4454,7 +4532,7 @@
         <v>2.84</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J16">
         <v>3.15</v>
@@ -4472,10 +4550,10 @@
         <v>2.84</v>
       </c>
       <c r="O16">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P16">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q16">
         <v>2.5</v>
@@ -4493,7 +4571,7 @@
         <v>1.86</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
         <v>1.5</v>
@@ -4553,7 +4631,7 @@
         <v>46</v>
       </c>
       <c r="AP16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16">
         <v>8.4</v>
@@ -4565,7 +4643,7 @@
         <v>40</v>
       </c>
       <c r="AT16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
         <v>6.6</v>
@@ -4622,7 +4700,7 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="BN16">
         <v>8.4</v>
@@ -4634,13 +4712,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="BT16">
         <v>8.199999999999999</v>
@@ -4652,22 +4730,22 @@
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.41</v>
+        <v>2.48</v>
       </c>
       <c r="CB16" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4675,70 +4753,70 @@
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="F17">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="G17">
-        <v>1.87</v>
+        <v>3.9</v>
       </c>
       <c r="H17">
-        <v>4.1</v>
+        <v>2.04</v>
       </c>
       <c r="I17">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J17">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K17">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P17">
+        <v>2.34</v>
+      </c>
+      <c r="Q17">
+        <v>1.56</v>
+      </c>
+      <c r="R17">
+        <v>1.54</v>
+      </c>
+      <c r="S17">
         <v>2.4</v>
       </c>
-      <c r="Q17">
-        <v>1.55</v>
-      </c>
-      <c r="R17">
-        <v>1.56</v>
-      </c>
-      <c r="S17">
-        <v>2.28</v>
-      </c>
       <c r="T17">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U17">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V17">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4789,64 +4867,64 @@
         <v>1000</v>
       </c>
       <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
         <v>970</v>
       </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
       <c r="AP17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AQ17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AS17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AT17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AU17">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AV17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AW17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AX17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AY17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AZ17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BA17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BB17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BC17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BD17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BE17">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BF17">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BG17">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4909,249 +4987,249 @@
         <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F18">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="G18">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="H18">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I18">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="J18">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K18">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="O18">
         <v>1.2</v>
       </c>
       <c r="P18">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q18">
+        <v>1.6</v>
+      </c>
+      <c r="R18">
         <v>1.58</v>
       </c>
-      <c r="R18">
-        <v>1.5</v>
-      </c>
       <c r="S18">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T18">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="V18">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="W18">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC18">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP18">
-        <v>1.05</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18">
-        <v>1.05</v>
+        <v>11.5</v>
       </c>
       <c r="AR18">
-        <v>1.05</v>
+        <v>13</v>
       </c>
       <c r="AS18">
-        <v>1.05</v>
+        <v>20</v>
       </c>
       <c r="AT18">
-        <v>1.05</v>
+        <v>16</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV18">
-        <v>1.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>1.05</v>
+        <v>16</v>
       </c>
       <c r="AX18">
-        <v>1.05</v>
+        <v>21</v>
       </c>
       <c r="AY18">
-        <v>1.05</v>
+        <v>13.5</v>
       </c>
       <c r="AZ18">
-        <v>1.05</v>
+        <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>1.05</v>
+        <v>20</v>
       </c>
       <c r="BB18">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="BC18">
-        <v>1.05</v>
+        <v>6.8</v>
       </c>
       <c r="BD18">
-        <v>1.05</v>
+        <v>6.8</v>
       </c>
       <c r="BE18">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="BF18">
-        <v>1.05</v>
+        <v>21</v>
       </c>
       <c r="BG18">
-        <v>1.05</v>
+        <v>9</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="CB18" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5159,76 +5237,76 @@
         <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="F19">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="G19">
-        <v>4.6</v>
+        <v>2.08</v>
       </c>
       <c r="H19">
-        <v>1.88</v>
+        <v>3.7</v>
       </c>
       <c r="I19">
-        <v>2.12</v>
+        <v>4.8</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="O19">
         <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
         <v>1.4</v>
       </c>
       <c r="S19">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T19">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="U19">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="V19">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="W19">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="X19">
         <v>1000</v>
       </c>
       <c r="Y19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
         <v>1000</v>
@@ -5240,7 +5318,7 @@
         <v>1000</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5276,67 +5354,67 @@
         <v>1000</v>
       </c>
       <c r="AO19">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5393,7 +5471,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5401,70 +5479,70 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="F20">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G20">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="H20">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="I20">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="L20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
+        <v>4.5</v>
+      </c>
+      <c r="O20">
+        <v>1.19</v>
+      </c>
+      <c r="P20">
         <v>2.4</v>
       </c>
-      <c r="O20">
-        <v>1.25</v>
-      </c>
-      <c r="P20">
-        <v>2.02</v>
-      </c>
       <c r="Q20">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="R20">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="S20">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="T20">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="U20">
-        <v>1.12</v>
+        <v>2.38</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W20">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5482,7 +5560,7 @@
         <v>1000</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD20">
         <v>1000</v>
@@ -5515,70 +5593,70 @@
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO20">
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
@@ -5635,7 +5713,7 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5643,70 +5721,70 @@
         <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="F21">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="H21">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I21">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="J21">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K21">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M21">
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P21">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
+        <v>1.58</v>
+      </c>
+      <c r="R21">
+        <v>1.51</v>
+      </c>
+      <c r="S21">
+        <v>2.42</v>
+      </c>
+      <c r="T21">
         <v>1.56</v>
       </c>
-      <c r="R21">
-        <v>1.54</v>
-      </c>
-      <c r="S21">
-        <v>2.4</v>
-      </c>
-      <c r="T21">
-        <v>1.51</v>
-      </c>
       <c r="U21">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="V21">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5724,7 +5802,7 @@
         <v>1000</v>
       </c>
       <c r="AC21">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD21">
         <v>1000</v>
@@ -5760,61 +5838,61 @@
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AQ21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AR21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AS21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AT21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AU21">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AW21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AX21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AY21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AZ21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BA21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BB21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BC21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BD21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BE21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BF21">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5877,249 +5955,249 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F22">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="G22">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="I22">
         <v>2.12</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.02</v>
+      </c>
+      <c r="N22">
+        <v>4.1</v>
+      </c>
+      <c r="O22">
         <v>1.25</v>
       </c>
-      <c r="M22">
-        <v>1.01</v>
-      </c>
-      <c r="N22">
-        <v>5.2</v>
-      </c>
-      <c r="O22">
-        <v>1.2</v>
-      </c>
       <c r="P22">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="Q22">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="R22">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="S22">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="T22">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="U22">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="V22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W22">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X22">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="Z22">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>970</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
         <v>23</v>
       </c>
-      <c r="AC22">
-        <v>10.5</v>
-      </c>
-      <c r="AD22">
-        <v>11.5</v>
-      </c>
-      <c r="AE22">
-        <v>24</v>
-      </c>
-      <c r="AF22">
-        <v>32</v>
-      </c>
-      <c r="AG22">
-        <v>19</v>
-      </c>
-      <c r="AH22">
-        <v>19</v>
-      </c>
-      <c r="AI22">
-        <v>34</v>
-      </c>
-      <c r="AJ22">
-        <v>80</v>
-      </c>
-      <c r="AK22">
-        <v>40</v>
-      </c>
-      <c r="AL22">
-        <v>42</v>
-      </c>
-      <c r="AM22">
-        <v>75</v>
-      </c>
-      <c r="AN22">
-        <v>34</v>
-      </c>
-      <c r="AO22">
-        <v>10.5</v>
-      </c>
       <c r="AP22">
-        <v>19.5</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22">
-        <v>11.5</v>
+        <v>1.11</v>
       </c>
       <c r="AR22">
-        <v>13</v>
+        <v>1.16</v>
       </c>
       <c r="AS22">
-        <v>20</v>
+        <v>1.16</v>
       </c>
       <c r="AT22">
-        <v>16</v>
+        <v>1.16</v>
       </c>
       <c r="AU22">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="AV22">
-        <v>9.800000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="AW22">
-        <v>16</v>
+        <v>1.16</v>
       </c>
       <c r="AX22">
-        <v>21</v>
+        <v>1.16</v>
       </c>
       <c r="AY22">
-        <v>13.5</v>
+        <v>1.16</v>
       </c>
       <c r="AZ22">
-        <v>13.5</v>
+        <v>1.16</v>
       </c>
       <c r="BA22">
-        <v>20</v>
+        <v>1.16</v>
       </c>
       <c r="BB22">
-        <v>6.6</v>
+        <v>1.16</v>
       </c>
       <c r="BC22">
-        <v>6.2</v>
+        <v>1.16</v>
       </c>
       <c r="BD22">
-        <v>6.2</v>
+        <v>1.16</v>
       </c>
       <c r="BE22">
-        <v>6.6</v>
+        <v>1.16</v>
       </c>
       <c r="BF22">
-        <v>19.5</v>
+        <v>1.16</v>
       </c>
       <c r="BG22">
-        <v>9</v>
+        <v>1.11</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6127,34 +6205,34 @@
         <v>82</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="F23">
         <v>2.96</v>
       </c>
       <c r="G23">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H23">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="I23">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J23">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="K23">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6175,10 +6253,10 @@
         <v>1.5</v>
       </c>
       <c r="R23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S23">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="T23">
         <v>1.11</v>
@@ -6187,10 +6265,10 @@
         <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="W23">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6361,7 +6439,7 @@
         <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6369,16 +6447,16 @@
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="F24">
         <v>6.8</v>
@@ -6396,22 +6474,22 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L24">
         <v>1.18</v>
       </c>
       <c r="M24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N24">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="O24">
         <v>1.16</v>
       </c>
       <c r="P24">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q24">
         <v>1.47</v>
@@ -6420,25 +6498,25 @@
         <v>1.72</v>
       </c>
       <c r="S24">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T24">
         <v>1.69</v>
       </c>
       <c r="U24">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V24">
         <v>3</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z24">
         <v>12</v>
@@ -6450,7 +6528,7 @@
         <v>38</v>
       </c>
       <c r="AC24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD24">
         <v>11.5</v>
@@ -6486,10 +6564,10 @@
         <v>85</v>
       </c>
       <c r="AO24">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AP24">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ24">
         <v>11</v>
@@ -6501,7 +6579,7 @@
         <v>12</v>
       </c>
       <c r="AT24">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AU24">
         <v>11</v>
@@ -6522,13 +6600,13 @@
         <v>17.5</v>
       </c>
       <c r="BA24">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BB24">
         <v>8.4</v>
       </c>
       <c r="BC24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD24">
         <v>7.8</v>
@@ -6540,7 +6618,7 @@
         <v>7.8</v>
       </c>
       <c r="BG24">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6603,7 +6681,1943 @@
         <v>1.04</v>
       </c>
       <c r="CB24" t="s">
-        <v>149</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25">
+        <v>1.1</v>
+      </c>
+      <c r="G25">
+        <v>150</v>
+      </c>
+      <c r="H25">
+        <v>1.1</v>
+      </c>
+      <c r="I25">
+        <v>150</v>
+      </c>
+      <c r="J25">
+        <v>1.1</v>
+      </c>
+      <c r="K25">
+        <v>950</v>
+      </c>
+      <c r="L25">
+        <v>1.36</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>1.25</v>
+      </c>
+      <c r="O25">
+        <v>1.28</v>
+      </c>
+      <c r="P25">
+        <v>1.25</v>
+      </c>
+      <c r="Q25">
+        <v>1.28</v>
+      </c>
+      <c r="R25">
+        <v>1.18</v>
+      </c>
+      <c r="S25">
+        <v>1.28</v>
+      </c>
+      <c r="T25">
+        <v>1.01</v>
+      </c>
+      <c r="U25">
+        <v>1.01</v>
+      </c>
+      <c r="V25">
+        <v>1.01</v>
+      </c>
+      <c r="W25">
+        <v>1.01</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25">
+        <v>1.03</v>
+      </c>
+      <c r="AR25">
+        <v>1.03</v>
+      </c>
+      <c r="AS25">
+        <v>1.03</v>
+      </c>
+      <c r="AT25">
+        <v>1.03</v>
+      </c>
+      <c r="AU25">
+        <v>1.03</v>
+      </c>
+      <c r="AV25">
+        <v>1.03</v>
+      </c>
+      <c r="AW25">
+        <v>1.03</v>
+      </c>
+      <c r="AX25">
+        <v>1.03</v>
+      </c>
+      <c r="AY25">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25">
+        <v>1.03</v>
+      </c>
+      <c r="BA25">
+        <v>1.03</v>
+      </c>
+      <c r="BB25">
+        <v>1.03</v>
+      </c>
+      <c r="BC25">
+        <v>1.03</v>
+      </c>
+      <c r="BD25">
+        <v>1.03</v>
+      </c>
+      <c r="BE25">
+        <v>1.03</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>168</v>
+      </c>
+      <c r="F26">
+        <v>3.85</v>
+      </c>
+      <c r="G26">
+        <v>5.1</v>
+      </c>
+      <c r="H26">
+        <v>1.92</v>
+      </c>
+      <c r="I26">
+        <v>2.16</v>
+      </c>
+      <c r="J26">
+        <v>3.3</v>
+      </c>
+      <c r="K26">
+        <v>4.6</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>3.2</v>
+      </c>
+      <c r="O26">
+        <v>1.35</v>
+      </c>
+      <c r="P26">
+        <v>1.72</v>
+      </c>
+      <c r="Q26">
+        <v>2.04</v>
+      </c>
+      <c r="R26">
+        <v>1.13</v>
+      </c>
+      <c r="S26">
+        <v>2.98</v>
+      </c>
+      <c r="T26">
+        <v>1.12</v>
+      </c>
+      <c r="U26">
+        <v>1.12</v>
+      </c>
+      <c r="V26">
+        <v>1.87</v>
+      </c>
+      <c r="W26">
+        <v>1.24</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>1000</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>1000</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26">
+        <v>1.01</v>
+      </c>
+      <c r="AR26">
+        <v>1.01</v>
+      </c>
+      <c r="AS26">
+        <v>1.01</v>
+      </c>
+      <c r="AT26">
+        <v>1.01</v>
+      </c>
+      <c r="AU26">
+        <v>1.01</v>
+      </c>
+      <c r="AV26">
+        <v>1.01</v>
+      </c>
+      <c r="AW26">
+        <v>1.01</v>
+      </c>
+      <c r="AX26">
+        <v>1.01</v>
+      </c>
+      <c r="AY26">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26">
+        <v>1.01</v>
+      </c>
+      <c r="BA26">
+        <v>1.01</v>
+      </c>
+      <c r="BB26">
+        <v>1.01</v>
+      </c>
+      <c r="BC26">
+        <v>1.01</v>
+      </c>
+      <c r="BD26">
+        <v>1.01</v>
+      </c>
+      <c r="BE26">
+        <v>1.01</v>
+      </c>
+      <c r="BF26">
+        <v>1.01</v>
+      </c>
+      <c r="BG26">
+        <v>1.01</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.04</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.04</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.04</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.04</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.04</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.04</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.04</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.04</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.04</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>1.04</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27">
+        <v>2.38</v>
+      </c>
+      <c r="G27">
+        <v>2.54</v>
+      </c>
+      <c r="H27">
+        <v>3.45</v>
+      </c>
+      <c r="I27">
+        <v>3.7</v>
+      </c>
+      <c r="J27">
+        <v>3.1</v>
+      </c>
+      <c r="K27">
+        <v>3.3</v>
+      </c>
+      <c r="L27">
+        <v>1.55</v>
+      </c>
+      <c r="M27">
+        <v>1.13</v>
+      </c>
+      <c r="N27">
+        <v>2.6</v>
+      </c>
+      <c r="O27">
+        <v>1.54</v>
+      </c>
+      <c r="P27">
+        <v>1.56</v>
+      </c>
+      <c r="Q27">
+        <v>2.68</v>
+      </c>
+      <c r="R27">
+        <v>1.21</v>
+      </c>
+      <c r="S27">
+        <v>5.3</v>
+      </c>
+      <c r="T27">
+        <v>2.04</v>
+      </c>
+      <c r="U27">
+        <v>1.75</v>
+      </c>
+      <c r="V27">
+        <v>1.37</v>
+      </c>
+      <c r="W27">
+        <v>1.64</v>
+      </c>
+      <c r="X27">
+        <v>8.6</v>
+      </c>
+      <c r="Y27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z27">
+        <v>24</v>
+      </c>
+      <c r="AA27">
+        <v>110</v>
+      </c>
+      <c r="AB27">
+        <v>7.4</v>
+      </c>
+      <c r="AC27">
+        <v>7.6</v>
+      </c>
+      <c r="AD27">
+        <v>16.5</v>
+      </c>
+      <c r="AE27">
+        <v>65</v>
+      </c>
+      <c r="AF27">
+        <v>13.5</v>
+      </c>
+      <c r="AG27">
+        <v>12.5</v>
+      </c>
+      <c r="AH27">
+        <v>28</v>
+      </c>
+      <c r="AI27">
+        <v>100</v>
+      </c>
+      <c r="AJ27">
+        <v>48</v>
+      </c>
+      <c r="AK27">
+        <v>34</v>
+      </c>
+      <c r="AL27">
+        <v>70</v>
+      </c>
+      <c r="AM27">
+        <v>210</v>
+      </c>
+      <c r="AN27">
+        <v>36</v>
+      </c>
+      <c r="AO27">
+        <v>95</v>
+      </c>
+      <c r="AP27">
+        <v>7.6</v>
+      </c>
+      <c r="AQ27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27">
+        <v>20</v>
+      </c>
+      <c r="AS27">
+        <v>12</v>
+      </c>
+      <c r="AT27">
+        <v>6.6</v>
+      </c>
+      <c r="AU27">
+        <v>6.8</v>
+      </c>
+      <c r="AV27">
+        <v>15</v>
+      </c>
+      <c r="AW27">
+        <v>11</v>
+      </c>
+      <c r="AX27">
+        <v>12</v>
+      </c>
+      <c r="AY27">
+        <v>11</v>
+      </c>
+      <c r="AZ27">
+        <v>21</v>
+      </c>
+      <c r="BA27">
+        <v>11.5</v>
+      </c>
+      <c r="BB27">
+        <v>10</v>
+      </c>
+      <c r="BC27">
+        <v>9.6</v>
+      </c>
+      <c r="BD27">
+        <v>11</v>
+      </c>
+      <c r="BE27">
+        <v>12.5</v>
+      </c>
+      <c r="BF27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG27">
+        <v>11.5</v>
+      </c>
+      <c r="BH27">
+        <v>3.15</v>
+      </c>
+      <c r="BI27">
+        <v>2.24</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>2.72</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>2.26</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>3.55</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>2.26</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>2.26</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>4.3</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>2.26</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>2.26</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>2.26</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28">
+        <v>2.42</v>
+      </c>
+      <c r="G28">
+        <v>2.58</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>3.25</v>
+      </c>
+      <c r="J28">
+        <v>3.3</v>
+      </c>
+      <c r="K28">
+        <v>3.9</v>
+      </c>
+      <c r="L28">
+        <v>1.39</v>
+      </c>
+      <c r="M28">
+        <v>1.03</v>
+      </c>
+      <c r="N28">
+        <v>3.6</v>
+      </c>
+      <c r="O28">
+        <v>1.32</v>
+      </c>
+      <c r="P28">
+        <v>1.86</v>
+      </c>
+      <c r="Q28">
+        <v>1.85</v>
+      </c>
+      <c r="R28">
+        <v>1.33</v>
+      </c>
+      <c r="S28">
+        <v>3.3</v>
+      </c>
+      <c r="T28">
+        <v>1.66</v>
+      </c>
+      <c r="U28">
+        <v>2.14</v>
+      </c>
+      <c r="V28">
+        <v>1.45</v>
+      </c>
+      <c r="W28">
+        <v>1.64</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>950</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>12</v>
+      </c>
+      <c r="AC28">
+        <v>8.4</v>
+      </c>
+      <c r="AD28">
+        <v>950</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>18.5</v>
+      </c>
+      <c r="AG28">
+        <v>950</v>
+      </c>
+      <c r="AH28">
+        <v>18.5</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>1.74</v>
+      </c>
+      <c r="AQ28">
+        <v>8.6</v>
+      </c>
+      <c r="AR28">
+        <v>17.5</v>
+      </c>
+      <c r="AS28">
+        <v>1.74</v>
+      </c>
+      <c r="AT28">
+        <v>9.4</v>
+      </c>
+      <c r="AU28">
+        <v>5.9</v>
+      </c>
+      <c r="AV28">
+        <v>1.66</v>
+      </c>
+      <c r="AW28">
+        <v>1.74</v>
+      </c>
+      <c r="AX28">
+        <v>1.59</v>
+      </c>
+      <c r="AY28">
+        <v>10</v>
+      </c>
+      <c r="AZ28">
+        <v>1.59</v>
+      </c>
+      <c r="BA28">
+        <v>1.74</v>
+      </c>
+      <c r="BB28">
+        <v>1.74</v>
+      </c>
+      <c r="BC28">
+        <v>1.74</v>
+      </c>
+      <c r="BD28">
+        <v>1.74</v>
+      </c>
+      <c r="BE28">
+        <v>1.74</v>
+      </c>
+      <c r="BF28">
+        <v>17.5</v>
+      </c>
+      <c r="BG28">
+        <v>1.74</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.15</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.66</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.15</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.38</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.15</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.15</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.15</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.15</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.15</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.15</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29">
+        <v>2.12</v>
+      </c>
+      <c r="G29">
+        <v>2.22</v>
+      </c>
+      <c r="H29">
+        <v>3.75</v>
+      </c>
+      <c r="I29">
+        <v>3.95</v>
+      </c>
+      <c r="J29">
+        <v>3.45</v>
+      </c>
+      <c r="K29">
+        <v>3.65</v>
+      </c>
+      <c r="L29">
+        <v>1.4</v>
+      </c>
+      <c r="M29">
+        <v>1.08</v>
+      </c>
+      <c r="N29">
+        <v>3.35</v>
+      </c>
+      <c r="O29">
+        <v>1.37</v>
+      </c>
+      <c r="P29">
+        <v>1.8</v>
+      </c>
+      <c r="Q29">
+        <v>2.1</v>
+      </c>
+      <c r="R29">
+        <v>1.31</v>
+      </c>
+      <c r="S29">
+        <v>3.85</v>
+      </c>
+      <c r="T29">
+        <v>1.86</v>
+      </c>
+      <c r="U29">
+        <v>2.02</v>
+      </c>
+      <c r="V29">
+        <v>1.34</v>
+      </c>
+      <c r="W29">
+        <v>1.82</v>
+      </c>
+      <c r="X29">
+        <v>13</v>
+      </c>
+      <c r="Y29">
+        <v>13.5</v>
+      </c>
+      <c r="Z29">
+        <v>32</v>
+      </c>
+      <c r="AA29">
+        <v>95</v>
+      </c>
+      <c r="AB29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC29">
+        <v>8</v>
+      </c>
+      <c r="AD29">
+        <v>16.5</v>
+      </c>
+      <c r="AE29">
+        <v>60</v>
+      </c>
+      <c r="AF29">
+        <v>13.5</v>
+      </c>
+      <c r="AG29">
+        <v>11</v>
+      </c>
+      <c r="AH29">
+        <v>19</v>
+      </c>
+      <c r="AI29">
+        <v>75</v>
+      </c>
+      <c r="AJ29">
+        <v>32</v>
+      </c>
+      <c r="AK29">
+        <v>25</v>
+      </c>
+      <c r="AL29">
+        <v>44</v>
+      </c>
+      <c r="AM29">
+        <v>130</v>
+      </c>
+      <c r="AN29">
+        <v>20</v>
+      </c>
+      <c r="AO29">
+        <v>70</v>
+      </c>
+      <c r="AP29">
+        <v>11</v>
+      </c>
+      <c r="AQ29">
+        <v>11.5</v>
+      </c>
+      <c r="AR29">
+        <v>19</v>
+      </c>
+      <c r="AS29">
+        <v>10.5</v>
+      </c>
+      <c r="AT29">
+        <v>7.8</v>
+      </c>
+      <c r="AU29">
+        <v>7</v>
+      </c>
+      <c r="AV29">
+        <v>14.5</v>
+      </c>
+      <c r="AW29">
+        <v>34</v>
+      </c>
+      <c r="AX29">
+        <v>11.5</v>
+      </c>
+      <c r="AY29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29">
+        <v>16.5</v>
+      </c>
+      <c r="BA29">
+        <v>10</v>
+      </c>
+      <c r="BB29">
+        <v>20</v>
+      </c>
+      <c r="BC29">
+        <v>21</v>
+      </c>
+      <c r="BD29">
+        <v>34</v>
+      </c>
+      <c r="BE29">
+        <v>10</v>
+      </c>
+      <c r="BF29">
+        <v>16.5</v>
+      </c>
+      <c r="BG29">
+        <v>10</v>
+      </c>
+      <c r="BH29">
+        <v>3.85</v>
+      </c>
+      <c r="BI29">
+        <v>2.62</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>2.34</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>2.62</v>
+      </c>
+      <c r="BN29">
+        <v>950</v>
+      </c>
+      <c r="BO29">
+        <v>3.4</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>2.62</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>2.62</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>4.6</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>2.62</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>2.62</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>2.62</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30">
+        <v>2.06</v>
+      </c>
+      <c r="G30">
+        <v>2.26</v>
+      </c>
+      <c r="H30">
+        <v>3.45</v>
+      </c>
+      <c r="I30">
+        <v>3.95</v>
+      </c>
+      <c r="J30">
+        <v>3.55</v>
+      </c>
+      <c r="K30">
+        <v>3.95</v>
+      </c>
+      <c r="L30">
+        <v>1.33</v>
+      </c>
+      <c r="M30">
+        <v>1.03</v>
+      </c>
+      <c r="N30">
+        <v>3.9</v>
+      </c>
+      <c r="O30">
+        <v>1.24</v>
+      </c>
+      <c r="P30">
+        <v>1.93</v>
+      </c>
+      <c r="Q30">
+        <v>1.85</v>
+      </c>
+      <c r="R30">
+        <v>1.37</v>
+      </c>
+      <c r="S30">
+        <v>2.92</v>
+      </c>
+      <c r="T30">
+        <v>1.66</v>
+      </c>
+      <c r="U30">
+        <v>2.08</v>
+      </c>
+      <c r="V30">
+        <v>1.33</v>
+      </c>
+      <c r="W30">
+        <v>1.79</v>
+      </c>
+      <c r="X30">
+        <v>1000</v>
+      </c>
+      <c r="Y30">
+        <v>1000</v>
+      </c>
+      <c r="Z30">
+        <v>1000</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>950</v>
+      </c>
+      <c r="AC30">
+        <v>970</v>
+      </c>
+      <c r="AD30">
+        <v>1000</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
+        <v>34</v>
+      </c>
+      <c r="AG30">
+        <v>950</v>
+      </c>
+      <c r="AH30">
+        <v>1000</v>
+      </c>
+      <c r="AI30">
+        <v>1000</v>
+      </c>
+      <c r="AJ30">
+        <v>1000</v>
+      </c>
+      <c r="AK30">
+        <v>1000</v>
+      </c>
+      <c r="AL30">
+        <v>1000</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>34</v>
+      </c>
+      <c r="AO30">
+        <v>1000</v>
+      </c>
+      <c r="AP30">
+        <v>1.31</v>
+      </c>
+      <c r="AQ30">
+        <v>1.31</v>
+      </c>
+      <c r="AR30">
+        <v>1.31</v>
+      </c>
+      <c r="AS30">
+        <v>1.31</v>
+      </c>
+      <c r="AT30">
+        <v>7.6</v>
+      </c>
+      <c r="AU30">
+        <v>6.2</v>
+      </c>
+      <c r="AV30">
+        <v>1.31</v>
+      </c>
+      <c r="AW30">
+        <v>1.31</v>
+      </c>
+      <c r="AX30">
+        <v>1.26</v>
+      </c>
+      <c r="AY30">
+        <v>7.8</v>
+      </c>
+      <c r="AZ30">
+        <v>1.31</v>
+      </c>
+      <c r="BA30">
+        <v>1.31</v>
+      </c>
+      <c r="BB30">
+        <v>1.31</v>
+      </c>
+      <c r="BC30">
+        <v>1.31</v>
+      </c>
+      <c r="BD30">
+        <v>1.31</v>
+      </c>
+      <c r="BE30">
+        <v>1.31</v>
+      </c>
+      <c r="BF30">
+        <v>9</v>
+      </c>
+      <c r="BG30">
+        <v>1.31</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>1.17</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.04</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.04</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>1.33</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.04</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.04</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.17</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.04</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.04</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.04</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31">
+        <v>3.1</v>
+      </c>
+      <c r="G31">
+        <v>3.3</v>
+      </c>
+      <c r="H31">
+        <v>2.52</v>
+      </c>
+      <c r="I31">
+        <v>2.72</v>
+      </c>
+      <c r="J31">
+        <v>3.2</v>
+      </c>
+      <c r="K31">
+        <v>3.35</v>
+      </c>
+      <c r="L31">
+        <v>1.46</v>
+      </c>
+      <c r="M31">
+        <v>1.1</v>
+      </c>
+      <c r="N31">
+        <v>2.98</v>
+      </c>
+      <c r="O31">
+        <v>1.4</v>
+      </c>
+      <c r="P31">
+        <v>1.59</v>
+      </c>
+      <c r="Q31">
+        <v>2.28</v>
+      </c>
+      <c r="R31">
+        <v>1.23</v>
+      </c>
+      <c r="S31">
+        <v>4.4</v>
+      </c>
+      <c r="T31">
+        <v>1.87</v>
+      </c>
+      <c r="U31">
+        <v>1.83</v>
+      </c>
+      <c r="V31">
+        <v>1.58</v>
+      </c>
+      <c r="W31">
+        <v>1.43</v>
+      </c>
+      <c r="X31">
+        <v>970</v>
+      </c>
+      <c r="Y31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z31">
+        <v>1000</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>970</v>
+      </c>
+      <c r="AC31">
+        <v>970</v>
+      </c>
+      <c r="AD31">
+        <v>1000</v>
+      </c>
+      <c r="AE31">
+        <v>1000</v>
+      </c>
+      <c r="AF31">
+        <v>1000</v>
+      </c>
+      <c r="AG31">
+        <v>15.5</v>
+      </c>
+      <c r="AH31">
+        <v>1000</v>
+      </c>
+      <c r="AI31">
+        <v>1000</v>
+      </c>
+      <c r="AJ31">
+        <v>1000</v>
+      </c>
+      <c r="AK31">
+        <v>46</v>
+      </c>
+      <c r="AL31">
+        <v>1000</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>1000</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>1.64</v>
+      </c>
+      <c r="AQ31">
+        <v>7.4</v>
+      </c>
+      <c r="AR31">
+        <v>1.8</v>
+      </c>
+      <c r="AS31">
+        <v>1.8</v>
+      </c>
+      <c r="AT31">
+        <v>1.64</v>
+      </c>
+      <c r="AU31">
+        <v>5.5</v>
+      </c>
+      <c r="AV31">
+        <v>1.8</v>
+      </c>
+      <c r="AW31">
+        <v>1.8</v>
+      </c>
+      <c r="AX31">
+        <v>16.5</v>
+      </c>
+      <c r="AY31">
+        <v>1.61</v>
+      </c>
+      <c r="AZ31">
+        <v>1.8</v>
+      </c>
+      <c r="BA31">
+        <v>1.8</v>
+      </c>
+      <c r="BB31">
+        <v>1.8</v>
+      </c>
+      <c r="BC31">
+        <v>1.74</v>
+      </c>
+      <c r="BD31">
+        <v>1.8</v>
+      </c>
+      <c r="BE31">
+        <v>1.8</v>
+      </c>
+      <c r="BF31">
+        <v>1.8</v>
+      </c>
+      <c r="BG31">
+        <v>1.71</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.04</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.04</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.04</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.04</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.04</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.04</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.48</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.04</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.04</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.04</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32">
+        <v>1.84</v>
+      </c>
+      <c r="G32">
+        <v>1.9</v>
+      </c>
+      <c r="H32">
+        <v>5.3</v>
+      </c>
+      <c r="I32">
+        <v>5.7</v>
+      </c>
+      <c r="J32">
+        <v>3.4</v>
+      </c>
+      <c r="K32">
+        <v>3.55</v>
+      </c>
+      <c r="L32">
+        <v>1.53</v>
+      </c>
+      <c r="M32">
+        <v>1.07</v>
+      </c>
+      <c r="N32">
+        <v>2.78</v>
+      </c>
+      <c r="O32">
+        <v>1.49</v>
+      </c>
+      <c r="P32">
+        <v>1.6</v>
+      </c>
+      <c r="Q32">
+        <v>2.46</v>
+      </c>
+      <c r="R32">
+        <v>1.21</v>
+      </c>
+      <c r="S32">
+        <v>4.4</v>
+      </c>
+      <c r="T32">
+        <v>2.08</v>
+      </c>
+      <c r="U32">
+        <v>1.66</v>
+      </c>
+      <c r="V32">
+        <v>1.21</v>
+      </c>
+      <c r="W32">
+        <v>2.1</v>
+      </c>
+      <c r="X32">
+        <v>970</v>
+      </c>
+      <c r="Y32">
+        <v>17</v>
+      </c>
+      <c r="Z32">
+        <v>55</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>8</v>
+      </c>
+      <c r="AC32">
+        <v>9.6</v>
+      </c>
+      <c r="AD32">
+        <v>950</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>11.5</v>
+      </c>
+      <c r="AG32">
+        <v>13.5</v>
+      </c>
+      <c r="AH32">
+        <v>950</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>25</v>
+      </c>
+      <c r="AK32">
+        <v>30</v>
+      </c>
+      <c r="AL32">
+        <v>85</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>25</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>3</v>
+      </c>
+      <c r="AQ32">
+        <v>10</v>
+      </c>
+      <c r="AR32">
+        <v>3.5</v>
+      </c>
+      <c r="AS32">
+        <v>3.75</v>
+      </c>
+      <c r="AT32">
+        <v>5.1</v>
+      </c>
+      <c r="AU32">
+        <v>6.2</v>
+      </c>
+      <c r="AV32">
+        <v>16.5</v>
+      </c>
+      <c r="AW32">
+        <v>3.75</v>
+      </c>
+      <c r="AX32">
+        <v>7.2</v>
+      </c>
+      <c r="AY32">
+        <v>8</v>
+      </c>
+      <c r="AZ32">
+        <v>18.5</v>
+      </c>
+      <c r="BA32">
+        <v>3.75</v>
+      </c>
+      <c r="BB32">
+        <v>14.5</v>
+      </c>
+      <c r="BC32">
+        <v>17.5</v>
+      </c>
+      <c r="BD32">
+        <v>3.6</v>
+      </c>
+      <c r="BE32">
+        <v>3.75</v>
+      </c>
+      <c r="BF32">
+        <v>14</v>
+      </c>
+      <c r="BG32">
+        <v>3.75</v>
+      </c>
+      <c r="BH32">
+        <v>3.35</v>
+      </c>
+      <c r="BI32">
+        <v>2.3</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.95</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.95</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>3.1</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.95</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.95</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.95</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.95</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.95</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.95</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="180">
   <si>
     <t>League</t>
   </si>
@@ -274,13 +274,16 @@
     <t>Japanese J League 3</t>
   </si>
   <si>
+    <t>Danish 2nd Division</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
     <t>Swedish Division 1</t>
   </si>
   <si>
-    <t>Danish 2nd Division</t>
-  </si>
-  <si>
-    <t>Norwegian 1st Division</t>
+    <t>Moroccan Botola Pro 1</t>
   </si>
   <si>
     <t>Spanish Segunda Division</t>
@@ -328,6 +331,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>18:30:00</t>
   </si>
   <si>
@@ -376,48 +382,51 @@
     <t>Mio Biwako Shiga</t>
   </si>
   <si>
+    <t>Fremad Amager</t>
+  </si>
+  <si>
+    <t>VSK Aarhus FC</t>
+  </si>
+  <si>
+    <t>Naestved</t>
+  </si>
+  <si>
+    <t>Ranheim IL</t>
+  </si>
+  <si>
+    <t>Karlbergs BK</t>
+  </si>
+  <si>
+    <t>Kristianstads</t>
+  </si>
+  <si>
     <t>Lunds BK</t>
   </si>
   <si>
-    <t>Kristianstads</t>
-  </si>
-  <si>
-    <t>Karlbergs BK</t>
-  </si>
-  <si>
-    <t>VSK Aarhus FC</t>
-  </si>
-  <si>
-    <t>Naestved</t>
-  </si>
-  <si>
-    <t>Fremad Amager</t>
-  </si>
-  <si>
-    <t>Ranheim IL</t>
+    <t>Widad Temara</t>
   </si>
   <si>
     <t>Eldense</t>
   </si>
   <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
     <t>Athlone Town</t>
   </si>
   <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Wexford F.C</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>St Lucia</t>
   </si>
   <si>
@@ -469,48 +478,51 @@
     <t>Kumamoto</t>
   </si>
   <si>
+    <t>B93 Copenhagen</t>
+  </si>
+  <si>
+    <t>Brabrand</t>
+  </si>
+  <si>
+    <t>Nykobing FC</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Sollentuna FF</t>
+  </si>
+  <si>
+    <t>Ariana FC</t>
+  </si>
+  <si>
     <t>Laholms</t>
   </si>
   <si>
-    <t>Ariana FC</t>
-  </si>
-  <si>
-    <t>Sollentuna FF</t>
-  </si>
-  <si>
-    <t>Brabrand</t>
-  </si>
-  <si>
-    <t>Nykobing FC</t>
-  </si>
-  <si>
-    <t>B93 Copenhagen</t>
-  </si>
-  <si>
-    <t>Egersund</t>
+    <t>Union de Touarga</t>
   </si>
   <si>
     <t>Oviedo</t>
   </si>
   <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Longford</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Longford</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Kerry FC</t>
-  </si>
-  <si>
     <t>Guadeloupe</t>
   </si>
   <si>
@@ -541,7 +553,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 01:31:06</t>
+    <t>2026-10-01 03:43:34</t>
   </si>
 </sst>
 </file>
@@ -873,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1123,22 +1135,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -1147,52 +1159,52 @@
         <v>6.4</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
         <v>55</v>
@@ -1201,7 +1213,7 @@
         <v>220</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
@@ -1219,40 +1231,40 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
         <v>17.5</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
         <v>14</v>
       </c>
       <c r="AR2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1273,7 +1285,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA2">
         <v>11</v>
@@ -1282,7 +1294,7 @@
         <v>15</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1291,16 +1303,16 @@
         <v>11</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1330,7 +1342,7 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
         <v>10</v>
@@ -1342,7 +1354,7 @@
         <v>65</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
         <v>75</v>
@@ -1351,13 +1363,13 @@
         <v>10</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1365,91 +1377,91 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G3">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I3">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S3">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="T3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U3">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="W3">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE3">
         <v>20</v>
@@ -1458,43 +1470,43 @@
         <v>32</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI3">
         <v>60</v>
       </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL3">
         <v>44</v>
       </c>
       <c r="AM3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AN3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1503,7 +1515,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3">
         <v>17</v>
@@ -1515,22 +1527,22 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BF3">
         <v>16.5</v>
@@ -1539,13 +1551,13 @@
         <v>11.5</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK3">
         <v>1.04</v>
@@ -1557,13 +1569,13 @@
         <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ3">
         <v>1.04</v>
@@ -1575,31 +1587,31 @@
         <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW3">
         <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY3">
         <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1607,25 +1619,25 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>75</v>
       </c>
       <c r="H4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I4">
         <v>1.11</v>
@@ -1634,7 +1646,7 @@
         <v>12</v>
       </c>
       <c r="K4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="L4">
         <v>1.23</v>
@@ -1658,13 +1670,13 @@
         <v>1.83</v>
       </c>
       <c r="S4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T4">
         <v>3.55</v>
       </c>
       <c r="U4">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -1727,7 +1739,7 @@
         <v>2.88</v>
       </c>
       <c r="AP4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ4">
         <v>4.9</v>
@@ -1751,7 +1763,7 @@
         <v>6.2</v>
       </c>
       <c r="AX4">
-        <v>8.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="AY4">
         <v>8.6</v>
@@ -1766,10 +1778,10 @@
         <v>2.18</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>2.18</v>
       </c>
       <c r="BD4">
-        <v>8.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="BE4">
         <v>2.18</v>
@@ -1781,13 +1793,13 @@
         <v>2.38</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BK4">
         <v>1.04</v>
@@ -1799,7 +1811,7 @@
         <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BO4">
         <v>1.04</v>
@@ -1817,31 +1829,31 @@
         <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4">
         <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1849,16 +1861,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1870,7 +1882,7 @@
         <v>2.8</v>
       </c>
       <c r="I5">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -1885,10 +1897,10 @@
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
         <v>1.82</v>
@@ -1900,7 +1912,7 @@
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
         <v>1.79</v>
@@ -1909,43 +1921,43 @@
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y5">
         <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5">
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -1954,16 +1966,16 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO5">
         <v>32</v>
@@ -1978,7 +1990,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
@@ -1990,10 +2002,10 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
@@ -2002,25 +2014,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC5">
+        <v>7</v>
+      </c>
+      <c r="BD5">
         <v>7.4</v>
       </c>
-      <c r="BD5">
-        <v>7.6</v>
-      </c>
       <c r="BE5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH5">
         <v>3.6</v>
@@ -2029,61 +2041,61 @@
         <v>2.68</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK5">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BN5">
+        <v>6.2</v>
+      </c>
+      <c r="BO5">
+        <v>5.1</v>
+      </c>
+      <c r="BP5">
+        <v>25</v>
+      </c>
+      <c r="BQ5">
+        <v>6.2</v>
+      </c>
+      <c r="BR5">
+        <v>40</v>
+      </c>
+      <c r="BS5">
+        <v>7</v>
+      </c>
+      <c r="BT5">
+        <v>5.9</v>
+      </c>
+      <c r="BU5">
+        <v>4.8</v>
+      </c>
+      <c r="BV5">
+        <v>22</v>
+      </c>
+      <c r="BW5">
+        <v>6</v>
+      </c>
+      <c r="BX5">
+        <v>38</v>
+      </c>
+      <c r="BY5">
         <v>6.8</v>
       </c>
-      <c r="BO5">
-        <v>4.7</v>
-      </c>
-      <c r="BP5">
-        <v>27</v>
-      </c>
-      <c r="BQ5">
-        <v>4.8</v>
-      </c>
-      <c r="BR5">
-        <v>44</v>
-      </c>
-      <c r="BS5">
-        <v>5.1</v>
-      </c>
-      <c r="BT5">
-        <v>6.4</v>
-      </c>
-      <c r="BU5">
-        <v>4.5</v>
-      </c>
-      <c r="BV5">
-        <v>25</v>
-      </c>
-      <c r="BW5">
-        <v>4.7</v>
-      </c>
-      <c r="BX5">
-        <v>42</v>
-      </c>
-      <c r="BY5">
-        <v>5.1</v>
-      </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CA5">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2091,25 +2103,25 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F6">
+        <v>1.55</v>
+      </c>
+      <c r="G6">
         <v>1.57</v>
       </c>
-      <c r="G6">
-        <v>1.58</v>
-      </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I6">
         <v>6.2</v>
@@ -2154,7 +2166,7 @@
         <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -2166,7 +2178,7 @@
         <v>60</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB6">
         <v>16</v>
@@ -2256,13 +2268,13 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF6">
         <v>4.5</v>
       </c>
       <c r="BG6">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BH6">
         <v>5.4</v>
@@ -2325,7 +2337,7 @@
         <v>6.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2333,151 +2345,151 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H7">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="I7">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>1.37</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O7">
         <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T7">
         <v>1.94</v>
       </c>
       <c r="U7">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V7">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="Y7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AA7">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AB7">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE7">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AF7">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AG7">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AH7">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AI7">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AK7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
         <v>160</v>
-      </c>
-      <c r="AN7">
-        <v>170</v>
       </c>
       <c r="AO7">
         <v>8.6</v>
       </c>
       <c r="AP7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
         <v>7.8</v>
       </c>
       <c r="AS7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AU7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX7">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="AY7">
         <v>21</v>
@@ -2489,31 +2501,31 @@
         <v>27</v>
       </c>
       <c r="BB7">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD7">
         <v>42</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="BF7">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG7">
         <v>6.6</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
         <v>1.04</v>
@@ -2525,7 +2537,7 @@
         <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO7">
         <v>1.04</v>
@@ -2543,13 +2555,13 @@
         <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW7">
         <v>1.04</v>
@@ -2567,7 +2579,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2575,16 +2587,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F8">
         <v>1.13</v>
@@ -2599,7 +2611,7 @@
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2635,10 +2647,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2809,7 +2821,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2817,34 +2829,34 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F9">
-        <v>1.33</v>
+        <v>2.42</v>
       </c>
       <c r="G9">
-        <v>1.61</v>
+        <v>3.7</v>
       </c>
       <c r="H9">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="I9">
-        <v>8.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2853,34 +2865,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.66</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
         <v>1.02</v>
       </c>
       <c r="P9">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="R9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="T9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>2.62</v>
+        <v>1.37</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3051,7 +3063,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3059,58 +3071,58 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F10">
-        <v>2.82</v>
+        <v>1.6</v>
       </c>
       <c r="G10">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="H10">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
-        <v>2.32</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="O10">
         <v>1.02</v>
       </c>
       <c r="P10">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="Q10">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="R10">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S10">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3119,10 +3131,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="W10">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3293,7 +3305,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3301,70 +3313,70 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F11">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="G11">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="I11">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L11">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P11">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="Q11">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="R11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S11">
-        <v>2.78</v>
+        <v>2.02</v>
       </c>
       <c r="T11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3535,7 +3547,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3543,178 +3555,178 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F12">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="H12">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J12">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="O12">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="P12">
-        <v>1.86</v>
+        <v>3.3</v>
       </c>
       <c r="Q12">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="R12">
-        <v>1.32</v>
+        <v>1.92</v>
       </c>
       <c r="S12">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="V12">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3777,78 +3789,78 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F13">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="H13">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="I13">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q13">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="R13">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4019,42 +4031,42 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F14">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="G14">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="H14">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K14">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4063,22 +4075,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4087,10 +4099,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W14">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4261,7 +4273,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4269,79 +4281,79 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F15">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="G15">
-        <v>2.24</v>
+        <v>1.61</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="I15">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.66</v>
+      </c>
+      <c r="O15">
         <v>1.02</v>
       </c>
-      <c r="N15">
-        <v>6.8</v>
-      </c>
-      <c r="O15">
-        <v>1.09</v>
-      </c>
       <c r="P15">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q15">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="R15">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="S15">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="T15">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="U15">
-        <v>2.74</v>
+        <v>1.12</v>
       </c>
       <c r="V15">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="W15">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="X15">
         <v>1000</v>
       </c>
       <c r="Y15">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -4353,10 +4365,10 @@
         <v>1000</v>
       </c>
       <c r="AD15">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
         <v>1000</v>
@@ -4365,13 +4377,13 @@
         <v>1000</v>
       </c>
       <c r="AH15">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
         <v>1000</v>
@@ -4380,67 +4392,67 @@
         <v>1000</v>
       </c>
       <c r="AM15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4503,7 +4515,7 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4511,241 +4523,241 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F16">
-        <v>2.86</v>
+        <v>1.1</v>
       </c>
       <c r="G16">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="H16">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="J16">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="K16">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.84</v>
+        <v>1.24</v>
       </c>
       <c r="O16">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="R16">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="T16">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4753,241 +4765,241 @@
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F17">
+        <v>2.86</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>2.82</v>
+      </c>
+      <c r="I17">
+        <v>2.94</v>
+      </c>
+      <c r="J17">
+        <v>3.15</v>
+      </c>
+      <c r="K17">
         <v>3.2</v>
       </c>
-      <c r="G17">
-        <v>3.9</v>
-      </c>
-      <c r="H17">
-        <v>2.04</v>
-      </c>
-      <c r="I17">
+      <c r="L17">
+        <v>1.47</v>
+      </c>
+      <c r="M17">
+        <v>1.11</v>
+      </c>
+      <c r="N17">
+        <v>2.86</v>
+      </c>
+      <c r="O17">
+        <v>1.48</v>
+      </c>
+      <c r="P17">
+        <v>1.64</v>
+      </c>
+      <c r="Q17">
+        <v>2.46</v>
+      </c>
+      <c r="R17">
+        <v>1.23</v>
+      </c>
+      <c r="S17">
+        <v>4.9</v>
+      </c>
+      <c r="T17">
+        <v>2.02</v>
+      </c>
+      <c r="U17">
+        <v>1.86</v>
+      </c>
+      <c r="V17">
+        <v>1.51</v>
+      </c>
+      <c r="W17">
+        <v>1.5</v>
+      </c>
+      <c r="X17">
+        <v>9.6</v>
+      </c>
+      <c r="Y17">
+        <v>9.4</v>
+      </c>
+      <c r="Z17">
+        <v>17.5</v>
+      </c>
+      <c r="AA17">
+        <v>44</v>
+      </c>
+      <c r="AB17">
+        <v>9.4</v>
+      </c>
+      <c r="AC17">
+        <v>7.2</v>
+      </c>
+      <c r="AD17">
+        <v>14</v>
+      </c>
+      <c r="AE17">
+        <v>42</v>
+      </c>
+      <c r="AF17">
+        <v>17.5</v>
+      </c>
+      <c r="AG17">
+        <v>14.5</v>
+      </c>
+      <c r="AH17">
+        <v>22</v>
+      </c>
+      <c r="AI17">
+        <v>65</v>
+      </c>
+      <c r="AJ17">
+        <v>55</v>
+      </c>
+      <c r="AK17">
+        <v>40</v>
+      </c>
+      <c r="AL17">
+        <v>75</v>
+      </c>
+      <c r="AM17">
+        <v>150</v>
+      </c>
+      <c r="AN17">
+        <v>46</v>
+      </c>
+      <c r="AO17">
+        <v>46</v>
+      </c>
+      <c r="AP17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ17">
+        <v>8.4</v>
+      </c>
+      <c r="AR17">
+        <v>14.5</v>
+      </c>
+      <c r="AS17">
+        <v>22</v>
+      </c>
+      <c r="AT17">
+        <v>8.4</v>
+      </c>
+      <c r="AU17">
+        <v>6.6</v>
+      </c>
+      <c r="AV17">
+        <v>12</v>
+      </c>
+      <c r="AW17">
+        <v>34</v>
+      </c>
+      <c r="AX17">
+        <v>14.5</v>
+      </c>
+      <c r="AY17">
+        <v>12.5</v>
+      </c>
+      <c r="AZ17">
+        <v>18.5</v>
+      </c>
+      <c r="BA17">
+        <v>50</v>
+      </c>
+      <c r="BB17">
+        <v>42</v>
+      </c>
+      <c r="BC17">
+        <v>34</v>
+      </c>
+      <c r="BD17">
+        <v>50</v>
+      </c>
+      <c r="BE17">
+        <v>12.5</v>
+      </c>
+      <c r="BF17">
+        <v>36</v>
+      </c>
+      <c r="BG17">
+        <v>36</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>2.48</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>6.4</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
         <v>2.3</v>
       </c>
-      <c r="J17">
-        <v>3.8</v>
-      </c>
-      <c r="K17">
-        <v>4.8</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>4.8</v>
-      </c>
-      <c r="O17">
-        <v>1.18</v>
-      </c>
-      <c r="P17">
-        <v>2.34</v>
-      </c>
-      <c r="Q17">
-        <v>1.56</v>
-      </c>
-      <c r="R17">
-        <v>1.54</v>
-      </c>
-      <c r="S17">
-        <v>2.4</v>
-      </c>
-      <c r="T17">
-        <v>1.51</v>
-      </c>
-      <c r="U17">
-        <v>2.46</v>
-      </c>
-      <c r="V17">
-        <v>1.77</v>
-      </c>
-      <c r="W17">
-        <v>1.35</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>970</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>970</v>
-      </c>
-      <c r="AP17">
-        <v>1.14</v>
-      </c>
-      <c r="AQ17">
-        <v>1.14</v>
-      </c>
-      <c r="AR17">
-        <v>1.14</v>
-      </c>
-      <c r="AS17">
-        <v>1.14</v>
-      </c>
-      <c r="AT17">
-        <v>1.14</v>
-      </c>
-      <c r="AU17">
-        <v>1.06</v>
-      </c>
-      <c r="AV17">
-        <v>1.14</v>
-      </c>
-      <c r="AW17">
-        <v>1.14</v>
-      </c>
-      <c r="AX17">
-        <v>1.14</v>
-      </c>
-      <c r="AY17">
-        <v>1.14</v>
-      </c>
-      <c r="AZ17">
-        <v>1.14</v>
-      </c>
-      <c r="BA17">
-        <v>1.14</v>
-      </c>
-      <c r="BB17">
-        <v>1.14</v>
-      </c>
-      <c r="BC17">
-        <v>1.14</v>
-      </c>
-      <c r="BD17">
-        <v>1.14</v>
-      </c>
-      <c r="BE17">
-        <v>1.14</v>
-      </c>
-      <c r="BF17">
-        <v>1.14</v>
-      </c>
-      <c r="BG17">
-        <v>1.07</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.04</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>1.04</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.04</v>
-      </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="CB17" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4995,312 +5007,312 @@
         <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F18">
-        <v>3.35</v>
+        <v>1.66</v>
       </c>
       <c r="G18">
-        <v>3.75</v>
+        <v>1.74</v>
       </c>
       <c r="H18">
-        <v>2.02</v>
+        <v>4.6</v>
       </c>
       <c r="I18">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="L18">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="O18">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P18">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="R18">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="T18">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="U18">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.84</v>
+        <v>1.22</v>
       </c>
       <c r="W18">
-        <v>1.36</v>
+        <v>2.34</v>
       </c>
       <c r="X18">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AH18">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AO18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>19.5</v>
+        <v>1.26</v>
       </c>
       <c r="AQ18">
-        <v>11.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR18">
-        <v>13</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
-        <v>20</v>
+        <v>1.26</v>
       </c>
       <c r="AT18">
-        <v>16</v>
+        <v>1.26</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>1.18</v>
       </c>
       <c r="AV18">
-        <v>9.800000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="AW18">
-        <v>16</v>
+        <v>1.26</v>
       </c>
       <c r="AX18">
-        <v>21</v>
+        <v>1.26</v>
       </c>
       <c r="AY18">
-        <v>13.5</v>
+        <v>1.18</v>
       </c>
       <c r="AZ18">
-        <v>13.5</v>
+        <v>1.26</v>
       </c>
       <c r="BA18">
-        <v>20</v>
+        <v>1.26</v>
       </c>
       <c r="BB18">
-        <v>7.4</v>
+        <v>1.26</v>
       </c>
       <c r="BC18">
-        <v>6.8</v>
+        <v>1.26</v>
       </c>
       <c r="BD18">
-        <v>6.8</v>
+        <v>1.26</v>
       </c>
       <c r="BE18">
-        <v>7.4</v>
+        <v>1.26</v>
       </c>
       <c r="BF18">
-        <v>21</v>
+        <v>1.12</v>
       </c>
       <c r="BG18">
-        <v>9</v>
+        <v>1.26</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F19">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="G19">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="H19">
+        <v>2.1</v>
+      </c>
+      <c r="I19">
+        <v>2.5</v>
+      </c>
+      <c r="J19">
         <v>3.7</v>
       </c>
-      <c r="I19">
-        <v>4.8</v>
-      </c>
-      <c r="J19">
-        <v>3.85</v>
-      </c>
       <c r="K19">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="L19">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P19">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="R19">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S19">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="T19">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="U19">
-        <v>1.12</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>1.92</v>
+        <v>1.43</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5318,7 +5330,7 @@
         <v>1000</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD19">
         <v>1000</v>
@@ -5357,64 +5369,64 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU19">
         <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5471,42 +5483,42 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F20">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="G20">
-        <v>1.87</v>
+        <v>4.6</v>
       </c>
       <c r="H20">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="I20">
-        <v>5.7</v>
+        <v>2.12</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5515,40 +5527,40 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O20">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="R20">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="S20">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="T20">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="U20">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="V20">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="W20">
-        <v>2.14</v>
+        <v>1.28</v>
       </c>
       <c r="X20">
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z20">
         <v>1000</v>
@@ -5563,7 +5575,7 @@
         <v>970</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE20">
         <v>1000</v>
@@ -5593,64 +5605,64 @@
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AQ20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AR20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AS20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AT20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AU20">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AV20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AW20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AX20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AY20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AZ20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BA20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BB20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BD20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BE20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BF20">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="BG20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5713,78 +5725,78 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E21" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F21">
-        <v>2.68</v>
+        <v>1.88</v>
       </c>
       <c r="G21">
-        <v>3.55</v>
+        <v>2.08</v>
       </c>
       <c r="H21">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="I21">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="J21">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="L21">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N21">
         <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q21">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="R21">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S21">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="T21">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="U21">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="W21">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5799,10 +5811,10 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC21">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
         <v>1000</v>
@@ -5847,25 +5859,25 @@
         <v>1.05</v>
       </c>
       <c r="AR21">
+        <v>1.06</v>
+      </c>
+      <c r="AS21">
+        <v>1.06</v>
+      </c>
+      <c r="AT21">
+        <v>1.01</v>
+      </c>
+      <c r="AU21">
         <v>1.05</v>
-      </c>
-      <c r="AS21">
-        <v>1.05</v>
-      </c>
-      <c r="AT21">
-        <v>1.05</v>
-      </c>
-      <c r="AU21">
-        <v>1.01</v>
       </c>
       <c r="AV21">
         <v>1.05</v>
       </c>
       <c r="AW21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AX21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AY21">
         <v>1.05</v>
@@ -5874,31 +5886,31 @@
         <v>1.05</v>
       </c>
       <c r="BA21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BB21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BC21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BD21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BE21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BF21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5955,84 +5967,84 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G22">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="H22">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="I22">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="J22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K22">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O22">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="Q22">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="R22">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="S22">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="T22">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="V22">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="W22">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X22">
         <v>1000</v>
       </c>
       <c r="Y22">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
         <v>1000</v>
@@ -6080,61 +6092,61 @@
         <v>1000</v>
       </c>
       <c r="AO22">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AP22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AR22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AS22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AT22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AU22">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AV22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AW22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AX22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AY22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AZ22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BA22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BB22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BD22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BE22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BF22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG22">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6197,428 +6209,428 @@
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E23" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F23">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="G23">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="H23">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="I23">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="J23">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M23">
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O23">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="P23">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q23">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S23">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="W23">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="CB23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F24">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="G24">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="H24">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="I24">
+        <v>2.3</v>
+      </c>
+      <c r="J24">
+        <v>3.7</v>
+      </c>
+      <c r="K24">
+        <v>4.7</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>4.3</v>
+      </c>
+      <c r="O24">
+        <v>1.18</v>
+      </c>
+      <c r="P24">
+        <v>2.38</v>
+      </c>
+      <c r="Q24">
         <v>1.5</v>
       </c>
-      <c r="J24">
-        <v>5</v>
-      </c>
-      <c r="K24">
-        <v>5.9</v>
-      </c>
-      <c r="L24">
-        <v>1.18</v>
-      </c>
-      <c r="M24">
-        <v>1.03</v>
-      </c>
-      <c r="N24">
-        <v>5.2</v>
-      </c>
-      <c r="O24">
-        <v>1.16</v>
-      </c>
-      <c r="P24">
-        <v>2.74</v>
-      </c>
-      <c r="Q24">
-        <v>1.47</v>
-      </c>
       <c r="R24">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="S24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T24">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="U24">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="X24">
+        <v>30</v>
+      </c>
+      <c r="Y24">
+        <v>17</v>
+      </c>
+      <c r="Z24">
+        <v>20</v>
+      </c>
+      <c r="AA24">
+        <v>32</v>
+      </c>
+      <c r="AB24">
+        <v>24</v>
+      </c>
+      <c r="AC24">
+        <v>12</v>
+      </c>
+      <c r="AD24">
+        <v>14</v>
+      </c>
+      <c r="AE24">
+        <v>24</v>
+      </c>
+      <c r="AF24">
         <v>36</v>
       </c>
-      <c r="Y24">
-        <v>13.5</v>
-      </c>
-      <c r="Z24">
-        <v>12</v>
-      </c>
-      <c r="AA24">
-        <v>14.5</v>
-      </c>
-      <c r="AB24">
-        <v>38</v>
-      </c>
-      <c r="AC24">
-        <v>13.5</v>
-      </c>
-      <c r="AD24">
-        <v>11.5</v>
-      </c>
-      <c r="AE24">
-        <v>15</v>
-      </c>
-      <c r="AF24">
-        <v>75</v>
-      </c>
       <c r="AG24">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AH24">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AI24">
         <v>34</v>
       </c>
       <c r="AJ24">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="AK24">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AL24">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AM24">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AN24">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AO24">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AP24">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6660,7 +6672,7 @@
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
@@ -6681,320 +6693,320 @@
         <v>1.04</v>
       </c>
       <c r="CB24" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F25">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="G25">
-        <v>150</v>
+        <v>8.6</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="I25">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="J25">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L25">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>2.74</v>
       </c>
       <c r="Q25">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>2.16</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F26">
-        <v>3.85</v>
+        <v>2.34</v>
       </c>
       <c r="G26">
-        <v>5.1</v>
+        <v>2.72</v>
       </c>
       <c r="H26">
-        <v>1.92</v>
+        <v>2.86</v>
       </c>
       <c r="I26">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="K26">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P26">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q26">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="R26">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S26">
-        <v>2.98</v>
+        <v>2.1</v>
       </c>
       <c r="T26">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7051,52 +7063,52 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF26">
         <v>1.01</v>
@@ -7108,64 +7120,64 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7173,725 +7185,725 @@
         <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F27">
-        <v>2.38</v>
+        <v>3.85</v>
       </c>
       <c r="G27">
-        <v>2.54</v>
+        <v>5.1</v>
       </c>
       <c r="H27">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="I27">
-        <v>3.7</v>
+        <v>2.16</v>
       </c>
       <c r="J27">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K27">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="L27">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>3.2</v>
+      </c>
+      <c r="O27">
+        <v>1.35</v>
+      </c>
+      <c r="P27">
+        <v>1.72</v>
+      </c>
+      <c r="Q27">
+        <v>2.04</v>
+      </c>
+      <c r="R27">
         <v>1.13</v>
       </c>
-      <c r="N27">
-        <v>2.6</v>
-      </c>
-      <c r="O27">
-        <v>1.54</v>
-      </c>
-      <c r="P27">
-        <v>1.56</v>
-      </c>
-      <c r="Q27">
-        <v>2.68</v>
-      </c>
-      <c r="R27">
-        <v>1.21</v>
-      </c>
       <c r="S27">
-        <v>5.3</v>
+        <v>2.98</v>
       </c>
       <c r="T27">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="U27">
-        <v>1.75</v>
+        <v>1.12</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="W27">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="X27">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F28">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G28">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="I28">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="J28">
+        <v>3.1</v>
+      </c>
+      <c r="K28">
         <v>3.3</v>
       </c>
-      <c r="K28">
-        <v>3.9</v>
-      </c>
       <c r="L28">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="M28">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="N28">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="P28">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="Q28">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="R28">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S28">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="T28">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="U28">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y28">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB28">
+        <v>7.4</v>
+      </c>
+      <c r="AC28">
+        <v>7.6</v>
+      </c>
+      <c r="AD28">
+        <v>16.5</v>
+      </c>
+      <c r="AE28">
+        <v>65</v>
+      </c>
+      <c r="AF28">
+        <v>13.5</v>
+      </c>
+      <c r="AG28">
+        <v>12.5</v>
+      </c>
+      <c r="AH28">
+        <v>28</v>
+      </c>
+      <c r="AI28">
+        <v>100</v>
+      </c>
+      <c r="AJ28">
+        <v>48</v>
+      </c>
+      <c r="AK28">
+        <v>34</v>
+      </c>
+      <c r="AL28">
+        <v>70</v>
+      </c>
+      <c r="AM28">
+        <v>210</v>
+      </c>
+      <c r="AN28">
+        <v>36</v>
+      </c>
+      <c r="AO28">
+        <v>95</v>
+      </c>
+      <c r="AP28">
+        <v>7.6</v>
+      </c>
+      <c r="AQ28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR28">
+        <v>20</v>
+      </c>
+      <c r="AS28">
         <v>12</v>
       </c>
-      <c r="AC28">
-        <v>8.4</v>
-      </c>
-      <c r="AD28">
-        <v>950</v>
-      </c>
-      <c r="AE28">
-        <v>1000</v>
-      </c>
-      <c r="AF28">
-        <v>18.5</v>
-      </c>
-      <c r="AG28">
-        <v>950</v>
-      </c>
-      <c r="AH28">
-        <v>18.5</v>
-      </c>
-      <c r="AI28">
-        <v>1000</v>
-      </c>
-      <c r="AJ28">
-        <v>1000</v>
-      </c>
-      <c r="AK28">
-        <v>1000</v>
-      </c>
-      <c r="AL28">
-        <v>1000</v>
-      </c>
-      <c r="AM28">
-        <v>1000</v>
-      </c>
-      <c r="AN28">
-        <v>1000</v>
-      </c>
-      <c r="AO28">
-        <v>1000</v>
-      </c>
-      <c r="AP28">
-        <v>1.74</v>
-      </c>
-      <c r="AQ28">
-        <v>8.6</v>
-      </c>
-      <c r="AR28">
-        <v>17.5</v>
-      </c>
-      <c r="AS28">
-        <v>1.74</v>
-      </c>
       <c r="AT28">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU28">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV28">
-        <v>1.66</v>
+        <v>15</v>
       </c>
       <c r="AW28">
-        <v>1.74</v>
+        <v>11</v>
       </c>
       <c r="AX28">
-        <v>1.59</v>
+        <v>12</v>
       </c>
       <c r="AY28">
+        <v>11</v>
+      </c>
+      <c r="AZ28">
+        <v>21</v>
+      </c>
+      <c r="BA28">
+        <v>11.5</v>
+      </c>
+      <c r="BB28">
         <v>10</v>
       </c>
-      <c r="AZ28">
-        <v>1.59</v>
-      </c>
-      <c r="BA28">
-        <v>1.74</v>
-      </c>
-      <c r="BB28">
-        <v>1.74</v>
-      </c>
       <c r="BC28">
-        <v>1.74</v>
+        <v>9.6</v>
       </c>
       <c r="BD28">
-        <v>1.74</v>
+        <v>11</v>
       </c>
       <c r="BE28">
-        <v>1.74</v>
+        <v>12.5</v>
       </c>
       <c r="BF28">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG28">
-        <v>1.74</v>
+        <v>11.5</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI28">
-        <v>1.15</v>
+        <v>2.24</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.66</v>
+        <v>2.72</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.38</v>
+        <v>3.55</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.15</v>
+        <v>4.3</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="CB28" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F29">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="G29">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="H29">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="J29">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K29">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M29">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="O29">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P29">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q29">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="R29">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S29">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="T29">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="U29">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="W29">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="X29">
+        <v>17</v>
+      </c>
+      <c r="Y29">
         <v>13</v>
       </c>
-      <c r="Y29">
-        <v>13.5</v>
-      </c>
       <c r="Z29">
+        <v>25</v>
+      </c>
+      <c r="AA29">
+        <v>60</v>
+      </c>
+      <c r="AB29">
+        <v>11.5</v>
+      </c>
+      <c r="AC29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD29">
+        <v>15.5</v>
+      </c>
+      <c r="AE29">
+        <v>40</v>
+      </c>
+      <c r="AF29">
+        <v>18</v>
+      </c>
+      <c r="AG29">
+        <v>12.5</v>
+      </c>
+      <c r="AH29">
+        <v>17.5</v>
+      </c>
+      <c r="AI29">
+        <v>55</v>
+      </c>
+      <c r="AJ29">
+        <v>42</v>
+      </c>
+      <c r="AK29">
         <v>32</v>
       </c>
-      <c r="AA29">
-        <v>95</v>
-      </c>
-      <c r="AB29">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC29">
-        <v>8</v>
-      </c>
-      <c r="AD29">
-        <v>16.5</v>
-      </c>
-      <c r="AE29">
-        <v>60</v>
-      </c>
-      <c r="AF29">
-        <v>13.5</v>
-      </c>
-      <c r="AG29">
+      <c r="AL29">
+        <v>46</v>
+      </c>
+      <c r="AM29">
+        <v>100</v>
+      </c>
+      <c r="AN29">
+        <v>25</v>
+      </c>
+      <c r="AO29">
+        <v>34</v>
+      </c>
+      <c r="AP29">
+        <v>12.5</v>
+      </c>
+      <c r="AQ29">
         <v>11</v>
       </c>
-      <c r="AH29">
-        <v>19</v>
-      </c>
-      <c r="AI29">
-        <v>75</v>
-      </c>
-      <c r="AJ29">
+      <c r="AR29">
+        <v>18.5</v>
+      </c>
+      <c r="AS29">
+        <v>38</v>
+      </c>
+      <c r="AT29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU29">
+        <v>7.2</v>
+      </c>
+      <c r="AV29">
+        <v>11.5</v>
+      </c>
+      <c r="AW29">
+        <v>6.4</v>
+      </c>
+      <c r="AX29">
+        <v>14</v>
+      </c>
+      <c r="AY29">
+        <v>10.5</v>
+      </c>
+      <c r="AZ29">
+        <v>14.5</v>
+      </c>
+      <c r="BA29">
         <v>32</v>
       </c>
-      <c r="AK29">
-        <v>25</v>
-      </c>
-      <c r="AL29">
-        <v>44</v>
-      </c>
-      <c r="AM29">
-        <v>130</v>
-      </c>
-      <c r="AN29">
-        <v>20</v>
-      </c>
-      <c r="AO29">
-        <v>70</v>
-      </c>
-      <c r="AP29">
-        <v>11</v>
-      </c>
-      <c r="AQ29">
-        <v>11.5</v>
-      </c>
-      <c r="AR29">
-        <v>19</v>
-      </c>
-      <c r="AS29">
-        <v>10.5</v>
-      </c>
-      <c r="AT29">
-        <v>7.8</v>
-      </c>
-      <c r="AU29">
+      <c r="BB29">
+        <v>6.4</v>
+      </c>
+      <c r="BC29">
+        <v>6</v>
+      </c>
+      <c r="BD29">
+        <v>6.4</v>
+      </c>
+      <c r="BE29">
         <v>7</v>
       </c>
-      <c r="AV29">
-        <v>14.5</v>
-      </c>
-      <c r="AW29">
-        <v>34</v>
-      </c>
-      <c r="AX29">
-        <v>11.5</v>
-      </c>
-      <c r="AY29">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ29">
-        <v>16.5</v>
-      </c>
-      <c r="BA29">
-        <v>10</v>
-      </c>
-      <c r="BB29">
-        <v>20</v>
-      </c>
-      <c r="BC29">
-        <v>21</v>
-      </c>
-      <c r="BD29">
-        <v>34</v>
-      </c>
-      <c r="BE29">
-        <v>10</v>
-      </c>
       <c r="BF29">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BH29">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BN29">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>3.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>4.6</v>
+        <v>1.15</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="CB29" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7899,318 +7911,318 @@
         <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F30">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G30">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H30">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="I30">
         <v>3.95</v>
       </c>
       <c r="J30">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K30">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L30">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M30">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N30">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O30">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="P30">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="Q30">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S30">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="T30">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="U30">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
         <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC30">
+        <v>8</v>
+      </c>
+      <c r="AD30">
+        <v>16.5</v>
+      </c>
+      <c r="AE30">
+        <v>60</v>
+      </c>
+      <c r="AF30">
+        <v>13.5</v>
+      </c>
+      <c r="AG30">
+        <v>11</v>
+      </c>
+      <c r="AH30">
+        <v>19</v>
+      </c>
+      <c r="AI30">
+        <v>75</v>
+      </c>
+      <c r="AJ30">
+        <v>32</v>
+      </c>
+      <c r="AK30">
+        <v>25</v>
+      </c>
+      <c r="AL30">
+        <v>44</v>
+      </c>
+      <c r="AM30">
+        <v>130</v>
+      </c>
+      <c r="AN30">
+        <v>20</v>
+      </c>
+      <c r="AO30">
+        <v>70</v>
+      </c>
+      <c r="AP30">
+        <v>11</v>
+      </c>
+      <c r="AQ30">
+        <v>11.5</v>
+      </c>
+      <c r="AR30">
+        <v>19</v>
+      </c>
+      <c r="AS30">
+        <v>10.5</v>
+      </c>
+      <c r="AT30">
+        <v>7.8</v>
+      </c>
+      <c r="AU30">
+        <v>7</v>
+      </c>
+      <c r="AV30">
+        <v>14.5</v>
+      </c>
+      <c r="AW30">
+        <v>34</v>
+      </c>
+      <c r="AX30">
+        <v>11.5</v>
+      </c>
+      <c r="AY30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30">
+        <v>16.5</v>
+      </c>
+      <c r="BA30">
+        <v>10</v>
+      </c>
+      <c r="BB30">
+        <v>20</v>
+      </c>
+      <c r="BC30">
+        <v>21</v>
+      </c>
+      <c r="BD30">
+        <v>34</v>
+      </c>
+      <c r="BE30">
+        <v>10</v>
+      </c>
+      <c r="BF30">
+        <v>16.5</v>
+      </c>
+      <c r="BG30">
+        <v>10</v>
+      </c>
+      <c r="BH30">
+        <v>3.85</v>
+      </c>
+      <c r="BI30">
+        <v>2.62</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>2.34</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>2.62</v>
+      </c>
+      <c r="BN30">
         <v>950</v>
       </c>
-      <c r="AC30">
-        <v>970</v>
-      </c>
-      <c r="AD30">
-        <v>1000</v>
-      </c>
-      <c r="AE30">
-        <v>1000</v>
-      </c>
-      <c r="AF30">
-        <v>34</v>
-      </c>
-      <c r="AG30">
-        <v>950</v>
-      </c>
-      <c r="AH30">
-        <v>1000</v>
-      </c>
-      <c r="AI30">
-        <v>1000</v>
-      </c>
-      <c r="AJ30">
-        <v>1000</v>
-      </c>
-      <c r="AK30">
-        <v>1000</v>
-      </c>
-      <c r="AL30">
-        <v>1000</v>
-      </c>
-      <c r="AM30">
-        <v>1000</v>
-      </c>
-      <c r="AN30">
-        <v>34</v>
-      </c>
-      <c r="AO30">
-        <v>1000</v>
-      </c>
-      <c r="AP30">
-        <v>1.31</v>
-      </c>
-      <c r="AQ30">
-        <v>1.31</v>
-      </c>
-      <c r="AR30">
-        <v>1.31</v>
-      </c>
-      <c r="AS30">
-        <v>1.31</v>
-      </c>
-      <c r="AT30">
-        <v>7.6</v>
-      </c>
-      <c r="AU30">
-        <v>6.2</v>
-      </c>
-      <c r="AV30">
-        <v>1.31</v>
-      </c>
-      <c r="AW30">
-        <v>1.31</v>
-      </c>
-      <c r="AX30">
-        <v>1.26</v>
-      </c>
-      <c r="AY30">
-        <v>7.8</v>
-      </c>
-      <c r="AZ30">
-        <v>1.31</v>
-      </c>
-      <c r="BA30">
-        <v>1.31</v>
-      </c>
-      <c r="BB30">
-        <v>1.31</v>
-      </c>
-      <c r="BC30">
-        <v>1.31</v>
-      </c>
-      <c r="BD30">
-        <v>1.31</v>
-      </c>
-      <c r="BE30">
-        <v>1.31</v>
-      </c>
-      <c r="BF30">
-        <v>9</v>
-      </c>
-      <c r="BG30">
-        <v>1.31</v>
-      </c>
-      <c r="BH30">
-        <v>1000</v>
-      </c>
-      <c r="BI30">
-        <v>1.17</v>
-      </c>
-      <c r="BJ30">
-        <v>1000</v>
-      </c>
-      <c r="BK30">
-        <v>1.04</v>
-      </c>
-      <c r="BL30">
-        <v>1000</v>
-      </c>
-      <c r="BM30">
-        <v>1.04</v>
-      </c>
-      <c r="BN30">
-        <v>1000</v>
-      </c>
       <c r="BO30">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>1.17</v>
+        <v>4.6</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="CB30" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F31">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="G31">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="H31">
-        <v>2.52</v>
+        <v>3.45</v>
       </c>
       <c r="I31">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="J31">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K31">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="L31">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="M31">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N31">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="O31">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="P31">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="Q31">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="R31">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S31">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="T31">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="U31">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="V31">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="X31">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
         <v>1000</v>
@@ -8219,7 +8231,7 @@
         <v>1000</v>
       </c>
       <c r="AB31">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AC31">
         <v>970</v>
@@ -8231,10 +8243,10 @@
         <v>1000</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG31">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AH31">
         <v>1000</v>
@@ -8246,7 +8258,7 @@
         <v>1000</v>
       </c>
       <c r="AK31">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
         <v>1000</v>
@@ -8255,70 +8267,70 @@
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO31">
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AQ31">
-        <v>7.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AS31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AT31">
-        <v>1.64</v>
+        <v>7.6</v>
       </c>
       <c r="AU31">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AW31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AX31">
-        <v>16.5</v>
+        <v>1.26</v>
       </c>
       <c r="AY31">
-        <v>1.61</v>
+        <v>7.8</v>
       </c>
       <c r="AZ31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="BA31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="BB31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="BC31">
-        <v>1.74</v>
+        <v>1.31</v>
       </c>
       <c r="BD31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="BE31">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="BF31">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="BG31">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="BH31">
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
@@ -8336,7 +8348,7 @@
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="BP31">
         <v>1000</v>
@@ -8354,7 +8366,7 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8375,7 +8387,7 @@
         <v>1.04</v>
       </c>
       <c r="CB31" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8383,241 +8395,483 @@
         <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F32">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="G32">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="H32">
-        <v>5.3</v>
+        <v>2.52</v>
       </c>
       <c r="I32">
-        <v>5.7</v>
+        <v>2.72</v>
       </c>
       <c r="J32">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K32">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L32">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="M32">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N32">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="O32">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="P32">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q32">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R32">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S32">
         <v>4.4</v>
       </c>
       <c r="T32">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="U32">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="V32">
+        <v>1.58</v>
+      </c>
+      <c r="W32">
+        <v>1.43</v>
+      </c>
+      <c r="X32">
+        <v>12</v>
+      </c>
+      <c r="Y32">
+        <v>9</v>
+      </c>
+      <c r="Z32">
+        <v>16.5</v>
+      </c>
+      <c r="AA32">
+        <v>44</v>
+      </c>
+      <c r="AB32">
+        <v>12</v>
+      </c>
+      <c r="AC32">
+        <v>7.6</v>
+      </c>
+      <c r="AD32">
+        <v>13</v>
+      </c>
+      <c r="AE32">
+        <v>40</v>
+      </c>
+      <c r="AF32">
+        <v>24</v>
+      </c>
+      <c r="AG32">
+        <v>15</v>
+      </c>
+      <c r="AH32">
+        <v>24</v>
+      </c>
+      <c r="AI32">
+        <v>65</v>
+      </c>
+      <c r="AJ32">
+        <v>70</v>
+      </c>
+      <c r="AK32">
+        <v>46</v>
+      </c>
+      <c r="AL32">
+        <v>75</v>
+      </c>
+      <c r="AM32">
+        <v>170</v>
+      </c>
+      <c r="AN32">
+        <v>60</v>
+      </c>
+      <c r="AO32">
+        <v>40</v>
+      </c>
+      <c r="AP32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ32">
+        <v>7.6</v>
+      </c>
+      <c r="AR32">
+        <v>13.5</v>
+      </c>
+      <c r="AS32">
+        <v>6.4</v>
+      </c>
+      <c r="AT32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU32">
+        <v>6.4</v>
+      </c>
+      <c r="AV32">
+        <v>10.5</v>
+      </c>
+      <c r="AW32">
+        <v>6.2</v>
+      </c>
+      <c r="AX32">
+        <v>17</v>
+      </c>
+      <c r="AY32">
+        <v>12.5</v>
+      </c>
+      <c r="AZ32">
+        <v>17.5</v>
+      </c>
+      <c r="BA32">
+        <v>6.6</v>
+      </c>
+      <c r="BB32">
+        <v>6.8</v>
+      </c>
+      <c r="BC32">
+        <v>32</v>
+      </c>
+      <c r="BD32">
+        <v>6.8</v>
+      </c>
+      <c r="BE32">
+        <v>7.2</v>
+      </c>
+      <c r="BF32">
+        <v>38</v>
+      </c>
+      <c r="BG32">
+        <v>6.2</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.04</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.04</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.04</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.04</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.04</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.04</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.48</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.04</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.04</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.04</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33">
+        <v>1.84</v>
+      </c>
+      <c r="G33">
+        <v>1.88</v>
+      </c>
+      <c r="H33">
+        <v>5.5</v>
+      </c>
+      <c r="I33">
+        <v>5.9</v>
+      </c>
+      <c r="J33">
+        <v>3.4</v>
+      </c>
+      <c r="K33">
+        <v>3.65</v>
+      </c>
+      <c r="L33">
+        <v>1.53</v>
+      </c>
+      <c r="M33">
+        <v>1.11</v>
+      </c>
+      <c r="N33">
+        <v>2.86</v>
+      </c>
+      <c r="O33">
+        <v>1.5</v>
+      </c>
+      <c r="P33">
+        <v>1.62</v>
+      </c>
+      <c r="Q33">
+        <v>2.44</v>
+      </c>
+      <c r="R33">
+        <v>1.22</v>
+      </c>
+      <c r="S33">
+        <v>4.7</v>
+      </c>
+      <c r="T33">
+        <v>2.22</v>
+      </c>
+      <c r="U33">
+        <v>1.72</v>
+      </c>
+      <c r="V33">
         <v>1.21</v>
       </c>
-      <c r="W32">
-        <v>2.1</v>
-      </c>
-      <c r="X32">
-        <v>970</v>
-      </c>
-      <c r="Y32">
-        <v>17</v>
-      </c>
-      <c r="Z32">
-        <v>55</v>
-      </c>
-      <c r="AA32">
-        <v>1000</v>
-      </c>
-      <c r="AB32">
-        <v>8</v>
-      </c>
-      <c r="AC32">
+      <c r="W33">
+        <v>2.12</v>
+      </c>
+      <c r="X33">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y33">
+        <v>15</v>
+      </c>
+      <c r="Z33">
+        <v>48</v>
+      </c>
+      <c r="AA33">
+        <v>240</v>
+      </c>
+      <c r="AB33">
+        <v>6.6</v>
+      </c>
+      <c r="AC33">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33">
+        <v>25</v>
+      </c>
+      <c r="AE33">
+        <v>140</v>
+      </c>
+      <c r="AF33">
         <v>9.6</v>
       </c>
-      <c r="AD32">
-        <v>950</v>
-      </c>
-      <c r="AE32">
-        <v>1000</v>
-      </c>
-      <c r="AF32">
+      <c r="AG33">
         <v>11.5</v>
       </c>
-      <c r="AG32">
-        <v>13.5</v>
-      </c>
-      <c r="AH32">
-        <v>950</v>
-      </c>
-      <c r="AI32">
-        <v>1000</v>
-      </c>
-      <c r="AJ32">
+      <c r="AH33">
+        <v>28</v>
+      </c>
+      <c r="AI33">
+        <v>150</v>
+      </c>
+      <c r="AJ33">
+        <v>21</v>
+      </c>
+      <c r="AK33">
         <v>25</v>
       </c>
-      <c r="AK32">
+      <c r="AL33">
+        <v>60</v>
+      </c>
+      <c r="AM33">
+        <v>270</v>
+      </c>
+      <c r="AN33">
+        <v>19.5</v>
+      </c>
+      <c r="AO33">
+        <v>240</v>
+      </c>
+      <c r="AP33">
+        <v>8.6</v>
+      </c>
+      <c r="AQ33">
+        <v>12.5</v>
+      </c>
+      <c r="AR33">
         <v>30</v>
       </c>
-      <c r="AL32">
-        <v>85</v>
-      </c>
-      <c r="AM32">
-        <v>1000</v>
-      </c>
-      <c r="AN32">
-        <v>25</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>3</v>
-      </c>
-      <c r="AQ32">
+      <c r="AS33">
+        <v>10.5</v>
+      </c>
+      <c r="AT33">
+        <v>5.7</v>
+      </c>
+      <c r="AU33">
+        <v>7.2</v>
+      </c>
+      <c r="AV33">
+        <v>21</v>
+      </c>
+      <c r="AW33">
         <v>10</v>
       </c>
-      <c r="AR32">
-        <v>3.5</v>
-      </c>
-      <c r="AS32">
-        <v>3.75</v>
-      </c>
-      <c r="AT32">
-        <v>5.1</v>
-      </c>
-      <c r="AU32">
-        <v>6.2</v>
-      </c>
-      <c r="AV32">
-        <v>16.5</v>
-      </c>
-      <c r="AW32">
-        <v>3.75</v>
-      </c>
-      <c r="AX32">
-        <v>7.2</v>
-      </c>
-      <c r="AY32">
-        <v>8</v>
-      </c>
-      <c r="AZ32">
+      <c r="AX33">
+        <v>8.4</v>
+      </c>
+      <c r="AY33">
+        <v>9.4</v>
+      </c>
+      <c r="AZ33">
         <v>18.5</v>
       </c>
-      <c r="BA32">
-        <v>3.75</v>
-      </c>
-      <c r="BB32">
-        <v>14.5</v>
-      </c>
-      <c r="BC32">
+      <c r="BA33">
+        <v>10</v>
+      </c>
+      <c r="BB33">
         <v>17.5</v>
       </c>
-      <c r="BD32">
-        <v>3.6</v>
-      </c>
-      <c r="BE32">
-        <v>3.75</v>
-      </c>
-      <c r="BF32">
-        <v>14</v>
-      </c>
-      <c r="BG32">
-        <v>3.75</v>
-      </c>
-      <c r="BH32">
+      <c r="BC33">
+        <v>21</v>
+      </c>
+      <c r="BD33">
+        <v>34</v>
+      </c>
+      <c r="BE33">
+        <v>10.5</v>
+      </c>
+      <c r="BF33">
+        <v>15.5</v>
+      </c>
+      <c r="BG33">
+        <v>10.5</v>
+      </c>
+      <c r="BH33">
         <v>3.35</v>
       </c>
-      <c r="BI32">
+      <c r="BI33">
         <v>2.3</v>
       </c>
-      <c r="BJ32">
-        <v>1000</v>
-      </c>
-      <c r="BK32">
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
         <v>1.95</v>
       </c>
-      <c r="BL32">
-        <v>1000</v>
-      </c>
-      <c r="BM32">
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
         <v>1.95</v>
       </c>
-      <c r="BN32">
-        <v>1000</v>
-      </c>
-      <c r="BO32">
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
         <v>3.1</v>
       </c>
-      <c r="BP32">
-        <v>1000</v>
-      </c>
-      <c r="BQ32">
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
         <v>1.95</v>
       </c>
-      <c r="BR32">
-        <v>1000</v>
-      </c>
-      <c r="BS32">
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
         <v>1.95</v>
       </c>
-      <c r="BT32">
-        <v>1000</v>
-      </c>
-      <c r="BU32">
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
         <v>1.95</v>
       </c>
-      <c r="BV32">
-        <v>1000</v>
-      </c>
-      <c r="BW32">
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
         <v>1.95</v>
       </c>
-      <c r="BX32">
-        <v>1000</v>
-      </c>
-      <c r="BY32">
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
         <v>1.95</v>
       </c>
-      <c r="BZ32">
-        <v>1000</v>
-      </c>
-      <c r="CA32">
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
         <v>1.95</v>
       </c>
-      <c r="CB32" t="s">
-        <v>175</v>
+      <c r="CB33" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -553,7 +553,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 03:43:34</t>
+    <t>2026-10-01 05:55:51</t>
   </si>
 </sst>
 </file>
@@ -1147,94 +1147,94 @@
         <v>147</v>
       </c>
       <c r="F2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G2">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H2">
         <v>5.9</v>
       </c>
       <c r="I2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z2">
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>25</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
         <v>17.5</v>
@@ -1246,28 +1246,28 @@
         <v>46</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO2">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS2">
         <v>11.5</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
@@ -1276,10 +1276,10 @@
         <v>20</v>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
@@ -1288,85 +1288,85 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BB2">
         <v>15</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="BE2">
+        <v>11.5</v>
+      </c>
+      <c r="BF2">
+        <v>10</v>
+      </c>
+      <c r="BG2">
         <v>11</v>
       </c>
-      <c r="BF2">
-        <v>11</v>
-      </c>
-      <c r="BG2">
+      <c r="BH2">
+        <v>3.3</v>
+      </c>
+      <c r="BI2">
+        <v>2.94</v>
+      </c>
+      <c r="BJ2">
         <v>11.5</v>
       </c>
-      <c r="BH2">
-        <v>3.2</v>
-      </c>
-      <c r="BI2">
-        <v>2.82</v>
-      </c>
-      <c r="BJ2">
-        <v>12</v>
-      </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BV2">
+        <v>70</v>
+      </c>
+      <c r="BW2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX2">
+        <v>80</v>
+      </c>
+      <c r="BY2">
+        <v>9</v>
+      </c>
+      <c r="BZ2">
+        <v>26</v>
+      </c>
+      <c r="CA2">
         <v>7.2</v>
-      </c>
-      <c r="BV2">
-        <v>65</v>
-      </c>
-      <c r="BW2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX2">
-        <v>75</v>
-      </c>
-      <c r="BY2">
-        <v>10</v>
-      </c>
-      <c r="BZ2">
-        <v>27</v>
-      </c>
-      <c r="CA2">
-        <v>8</v>
       </c>
       <c r="CB2" t="s">
         <v>179</v>
@@ -1389,19 +1389,19 @@
         <v>148</v>
       </c>
       <c r="F3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G3">
         <v>3.65</v>
       </c>
       <c r="H3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I3">
         <v>2.16</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>4.1</v>
@@ -1416,28 +1416,28 @@
         <v>4.9</v>
       </c>
       <c r="O3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
         <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S3">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T3">
         <v>1.61</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W3">
         <v>1.37</v>
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AA3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC3">
         <v>9.6</v>
@@ -1464,40 +1464,40 @@
         <v>10.5</v>
       </c>
       <c r="AE3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF3">
         <v>32</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AJ3">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AK3">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AL3">
         <v>44</v>
       </c>
       <c r="AM3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
@@ -1506,7 +1506,7 @@
         <v>13</v>
       </c>
       <c r="AS3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AT3">
         <v>14.5</v>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
       <c r="AX3">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AY3">
         <v>12</v>
@@ -1530,28 +1530,28 @@
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BD3">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BF3">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="BG3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
         <v>3.25</v>
@@ -1560,13 +1560,13 @@
         <v>9</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
         <v>7</v>
@@ -1578,13 +1578,13 @@
         <v>26</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>5.3</v>
@@ -1596,19 +1596,19 @@
         <v>14.5</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
         <v>18.5</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>179</v>
@@ -1631,82 +1631,82 @@
         <v>149</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I4">
         <v>1.11</v>
       </c>
       <c r="J4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M4">
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
         <v>1.42</v>
       </c>
       <c r="R4">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="S4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T4">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="U4">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z4">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AB4">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AC4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE4">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AF4">
         <v>1000</v>
@@ -1715,10 +1715,10 @@
         <v>950</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="AI4">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
@@ -1736,121 +1736,121 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AP4">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AR4">
+        <v>6.8</v>
+      </c>
+      <c r="AS4">
+        <v>6</v>
+      </c>
+      <c r="AT4">
+        <v>10</v>
+      </c>
+      <c r="AU4">
+        <v>27</v>
+      </c>
+      <c r="AV4">
+        <v>15.5</v>
+      </c>
+      <c r="AW4">
+        <v>15</v>
+      </c>
+      <c r="AX4">
+        <v>7.8</v>
+      </c>
+      <c r="AY4">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4">
+        <v>9</v>
+      </c>
+      <c r="BA4">
+        <v>9</v>
+      </c>
+      <c r="BB4">
+        <v>7.8</v>
+      </c>
+      <c r="BC4">
+        <v>7.8</v>
+      </c>
+      <c r="BD4">
+        <v>7.8</v>
+      </c>
+      <c r="BE4">
+        <v>7.8</v>
+      </c>
+      <c r="BF4">
+        <v>7.8</v>
+      </c>
+      <c r="BG4">
+        <v>2.3</v>
+      </c>
+      <c r="BH4">
+        <v>5.9</v>
+      </c>
+      <c r="BI4">
+        <v>4.5</v>
+      </c>
+      <c r="BJ4">
+        <v>22</v>
+      </c>
+      <c r="BK4">
+        <v>7.2</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10.5</v>
+      </c>
+      <c r="BN4">
+        <v>36</v>
+      </c>
+      <c r="BO4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>10.5</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>10</v>
+      </c>
+      <c r="BT4">
+        <v>3.75</v>
+      </c>
+      <c r="BU4">
+        <v>2.98</v>
+      </c>
+      <c r="BV4">
+        <v>5.3</v>
+      </c>
+      <c r="BW4">
         <v>4</v>
       </c>
-      <c r="AS4">
-        <v>3.85</v>
-      </c>
-      <c r="AT4">
-        <v>8.4</v>
-      </c>
-      <c r="AU4">
-        <v>7.2</v>
-      </c>
-      <c r="AV4">
-        <v>6.2</v>
-      </c>
-      <c r="AW4">
-        <v>6.2</v>
-      </c>
-      <c r="AX4">
-        <v>2.18</v>
-      </c>
-      <c r="AY4">
-        <v>8.6</v>
-      </c>
-      <c r="AZ4">
-        <v>8.4</v>
-      </c>
-      <c r="BA4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB4">
-        <v>2.18</v>
-      </c>
-      <c r="BC4">
-        <v>2.18</v>
-      </c>
-      <c r="BD4">
-        <v>2.18</v>
-      </c>
-      <c r="BE4">
-        <v>2.18</v>
-      </c>
-      <c r="BF4">
-        <v>2.18</v>
-      </c>
-      <c r="BG4">
-        <v>2.38</v>
-      </c>
-      <c r="BH4">
-        <v>5.6</v>
-      </c>
-      <c r="BI4">
-        <v>4.3</v>
-      </c>
-      <c r="BJ4">
-        <v>27</v>
-      </c>
-      <c r="BK4">
-        <v>1.04</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.04</v>
-      </c>
-      <c r="BN4">
-        <v>44</v>
-      </c>
-      <c r="BO4">
-        <v>1.04</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.04</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.04</v>
-      </c>
-      <c r="BT4">
-        <v>3.55</v>
-      </c>
-      <c r="BU4">
-        <v>2.82</v>
-      </c>
-      <c r="BV4">
-        <v>5.1</v>
-      </c>
-      <c r="BW4">
-        <v>3.9</v>
-      </c>
       <c r="BX4">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CA4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB4" t="s">
         <v>179</v>
@@ -1876,16 +1876,16 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H5">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I5">
         <v>2.94</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
         <v>3.2</v>
@@ -1906,7 +1906,7 @@
         <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
         <v>1.32</v>
@@ -1921,7 +1921,7 @@
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
         <v>1.47</v>
@@ -1933,10 +1933,10 @@
         <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AA5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB5">
         <v>12.5</v>
@@ -1966,7 +1966,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -1978,7 +1978,7 @@
         <v>36</v>
       </c>
       <c r="AO5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1990,19 +1990,19 @@
         <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX5">
         <v>17</v>
@@ -2014,25 +2014,25 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BC5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>3.6</v>
@@ -2041,58 +2041,58 @@
         <v>2.68</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BN5">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
+        <v>27</v>
+      </c>
+      <c r="BQ5">
+        <v>4.8</v>
+      </c>
+      <c r="BR5">
+        <v>44</v>
+      </c>
+      <c r="BS5">
+        <v>5.2</v>
+      </c>
+      <c r="BT5">
+        <v>6.4</v>
+      </c>
+      <c r="BU5">
+        <v>4.5</v>
+      </c>
+      <c r="BV5">
         <v>25</v>
       </c>
-      <c r="BQ5">
-        <v>6.2</v>
-      </c>
-      <c r="BR5">
-        <v>40</v>
-      </c>
-      <c r="BS5">
-        <v>7</v>
-      </c>
-      <c r="BT5">
-        <v>5.9</v>
-      </c>
-      <c r="BU5">
+      <c r="BW5">
         <v>4.8</v>
-      </c>
-      <c r="BV5">
-        <v>22</v>
-      </c>
-      <c r="BW5">
-        <v>6</v>
       </c>
       <c r="BX5">
         <v>38</v>
       </c>
       <c r="BY5">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BZ5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA5">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="s">
         <v>179</v>
@@ -2115,19 +2115,19 @@
         <v>151</v>
       </c>
       <c r="F6">
+        <v>1.53</v>
+      </c>
+      <c r="G6">
         <v>1.55</v>
       </c>
-      <c r="G6">
-        <v>1.57</v>
-      </c>
       <c r="H6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
         <v>5.3</v>
@@ -2139,46 +2139,46 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>1.13</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q6">
         <v>1.4</v>
       </c>
       <c r="R6">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U6">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W6">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X6">
         <v>38</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
         <v>16</v>
@@ -2196,16 +2196,16 @@
         <v>14</v>
       </c>
       <c r="AG6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH6">
         <v>17</v>
       </c>
       <c r="AI6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK6">
         <v>14</v>
@@ -2217,10 +2217,10 @@
         <v>55</v>
       </c>
       <c r="AN6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AO6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP6">
         <v>32</v>
@@ -2229,7 +2229,7 @@
         <v>32</v>
       </c>
       <c r="AR6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS6">
         <v>42</v>
@@ -2238,7 +2238,7 @@
         <v>14.5</v>
       </c>
       <c r="AU6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV6">
         <v>21</v>
@@ -2259,7 +2259,7 @@
         <v>42</v>
       </c>
       <c r="BB6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC6">
         <v>12.5</v>
@@ -2268,13 +2268,13 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH6">
         <v>5.4</v>
@@ -2292,7 +2292,7 @@
         <v>65</v>
       </c>
       <c r="BM6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
@@ -2301,37 +2301,37 @@
         <v>4.4</v>
       </c>
       <c r="BP6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR6">
         <v>17</v>
       </c>
       <c r="BS6">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU6">
         <v>8.800000000000001</v>
       </c>
       <c r="BV6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
         <v>34</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CA6">
         <v>6.4</v>
@@ -2360,7 +2360,7 @@
         <v>6.8</v>
       </c>
       <c r="G7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H7">
         <v>1.54</v>
@@ -2369,10 +2369,10 @@
         <v>1.59</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2399,7 +2399,7 @@
         <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U7">
         <v>1.96</v>
@@ -2417,13 +2417,13 @@
         <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA7">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AB7">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
@@ -2432,16 +2432,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE7">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AF7">
         <v>120</v>
       </c>
       <c r="AG7">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AI7">
         <v>70</v>
@@ -2468,37 +2468,37 @@
         <v>15</v>
       </c>
       <c r="AQ7">
+        <v>7.6</v>
+      </c>
+      <c r="AR7">
+        <v>8.4</v>
+      </c>
+      <c r="AS7">
+        <v>12.5</v>
+      </c>
+      <c r="AT7">
         <v>7.8</v>
-      </c>
-      <c r="AR7">
-        <v>7.8</v>
-      </c>
-      <c r="AS7">
-        <v>11.5</v>
-      </c>
-      <c r="AT7">
-        <v>16</v>
       </c>
       <c r="AU7">
         <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7">
         <v>14.5</v>
       </c>
       <c r="AX7">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
         <v>10.5</v>
@@ -2507,22 +2507,22 @@
         <v>10</v>
       </c>
       <c r="BD7">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="BE7">
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH7">
         <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7">
         <v>11</v>
@@ -2558,7 +2558,7 @@
         <v>4.1</v>
       </c>
       <c r="BU7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BV7">
         <v>9.800000000000001</v>
@@ -2573,7 +2573,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA7">
         <v>1.04</v>
@@ -2599,19 +2599,19 @@
         <v>153</v>
       </c>
       <c r="F8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2632,7 +2632,7 @@
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R8">
         <v>1.18</v>
@@ -2841,22 +2841,22 @@
         <v>154</v>
       </c>
       <c r="F9">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H9">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2865,22 +2865,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
         <v>1.02</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q9">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S9">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2889,10 +2889,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3083,22 +3083,22 @@
         <v>155</v>
       </c>
       <c r="F10">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G10">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L10">
         <v>1.27</v>
@@ -3107,22 +3107,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="O10">
         <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q10">
         <v>1.62</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3134,7 +3134,7 @@
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3325,22 +3325,22 @@
         <v>156</v>
       </c>
       <c r="F11">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H11">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="I11">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K11">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3355,16 +3355,16 @@
         <v>1.01</v>
       </c>
       <c r="P11">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R11">
         <v>1.42</v>
       </c>
       <c r="S11">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3373,10 +3373,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W11">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3567,22 +3567,22 @@
         <v>157</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G12">
         <v>2.22</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J12">
         <v>4.3</v>
       </c>
       <c r="K12">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3591,34 +3591,34 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q12">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R12">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="T12">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="U12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X12">
         <v>48</v>
@@ -3633,13 +3633,13 @@
         <v>65</v>
       </c>
       <c r="AB12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC12">
         <v>14.5</v>
       </c>
       <c r="AD12">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE12">
         <v>30</v>
@@ -3675,55 +3675,55 @@
         <v>16</v>
       </c>
       <c r="AP12">
+        <v>6.6</v>
+      </c>
+      <c r="AQ12">
         <v>6</v>
       </c>
-      <c r="AQ12">
-        <v>5.5</v>
-      </c>
       <c r="AR12">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS12">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT12">
         <v>18</v>
       </c>
       <c r="AU12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV12">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AX12">
         <v>18</v>
       </c>
       <c r="AY12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BB12">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BC12">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD12">
         <v>19</v>
       </c>
       <c r="BE12">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG12">
         <v>12</v>
@@ -3809,52 +3809,52 @@
         <v>158</v>
       </c>
       <c r="F13">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G13">
         <v>2.52</v>
       </c>
       <c r="H13">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="I13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J13">
         <v>3.4</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
         <v>1.02</v>
       </c>
       <c r="P13">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T13">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>1.36</v>
@@ -4051,22 +4051,22 @@
         <v>159</v>
       </c>
       <c r="F14">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G14">
         <v>4.7</v>
       </c>
       <c r="H14">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="I14">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K14">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4075,22 +4075,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q14">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
         <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4099,7 +4099,7 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W14">
         <v>1.27</v>
@@ -4293,22 +4293,22 @@
         <v>160</v>
       </c>
       <c r="F15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G15">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>8.800000000000001</v>
+        <v>990</v>
       </c>
       <c r="J15">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K15">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4317,34 +4317,34 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O15">
         <v>1.02</v>
       </c>
       <c r="P15">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R15">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="T15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
         <v>1.13</v>
       </c>
       <c r="W15">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4535,22 +4535,22 @@
         <v>161</v>
       </c>
       <c r="F16">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H16">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J16">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>3</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4559,34 +4559,34 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="O16">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="R16">
         <v>1.18</v>
       </c>
       <c r="S16">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4655,10 +4655,10 @@
         <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
         <v>1.03</v>
@@ -4777,16 +4777,16 @@
         <v>162</v>
       </c>
       <c r="F17">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H17">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I17">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J17">
         <v>3.15</v>
@@ -4801,40 +4801,40 @@
         <v>1.11</v>
       </c>
       <c r="N17">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O17">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P17">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q17">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S17">
         <v>4.9</v>
       </c>
       <c r="T17">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U17">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V17">
         <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X17">
         <v>9.6</v>
       </c>
       <c r="Y17">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>17.5</v>
@@ -4870,31 +4870,31 @@
         <v>55</v>
       </c>
       <c r="AK17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM17">
         <v>150</v>
       </c>
       <c r="AN17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR17">
         <v>14.5</v>
       </c>
       <c r="AS17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT17">
         <v>8.4</v>
@@ -4909,7 +4909,7 @@
         <v>34</v>
       </c>
       <c r="AX17">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY17">
         <v>12.5</v>
@@ -4921,7 +4921,7 @@
         <v>50</v>
       </c>
       <c r="BB17">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BC17">
         <v>34</v>
@@ -4930,13 +4930,13 @@
         <v>50</v>
       </c>
       <c r="BE17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4948,49 +4948,49 @@
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BN17">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>4</v>
+        <v>2.06</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BT17">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
@@ -5019,22 +5019,22 @@
         <v>163</v>
       </c>
       <c r="F18">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="G18">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="H18">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I18">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K18">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5049,10 +5049,10 @@
         <v>1.19</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q18">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R18">
         <v>1.56</v>
@@ -5061,16 +5061,16 @@
         <v>2.28</v>
       </c>
       <c r="T18">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V18">
         <v>1.22</v>
       </c>
       <c r="W18">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5085,7 +5085,7 @@
         <v>1000</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC18">
         <v>970</v>
@@ -5127,58 +5127,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AQ18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AS18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AT18">
         <v>1.26</v>
       </c>
       <c r="AU18">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AV18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AW18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AX18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AY18">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AZ18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BA18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BB18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BC18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BD18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BE18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BF18">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5261,22 +5261,22 @@
         <v>164</v>
       </c>
       <c r="F19">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G19">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H19">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I19">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J19">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="L19">
         <v>1.31</v>
@@ -5285,22 +5285,22 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q19">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R19">
         <v>1.48</v>
       </c>
       <c r="S19">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="T19">
         <v>1.56</v>
@@ -5309,7 +5309,7 @@
         <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W19">
         <v>1.43</v>
@@ -5330,11 +5330,11 @@
         <v>1000</v>
       </c>
       <c r="AC19">
+        <v>970</v>
+      </c>
+      <c r="AD19">
         <v>950</v>
       </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
       <c r="AE19">
         <v>1000</v>
       </c>
@@ -5366,61 +5366,61 @@
         <v>1000</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AQ19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AR19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AS19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AT19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AW19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AX19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AY19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AZ19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BA19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BB19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BC19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BD19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BE19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BF19">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BG19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5503,55 +5503,55 @@
         <v>165</v>
       </c>
       <c r="F20">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="G20">
         <v>4.6</v>
       </c>
       <c r="H20">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="I20">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K20">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q20">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="R20">
         <v>1.4</v>
       </c>
       <c r="S20">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T20">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U20">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="W20">
         <v>1.28</v>
@@ -5560,10 +5560,10 @@
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA20">
         <v>1000</v>
@@ -5611,58 +5611,58 @@
         <v>23</v>
       </c>
       <c r="AP20">
+        <v>1.31</v>
+      </c>
+      <c r="AQ20">
         <v>1.22</v>
       </c>
-      <c r="AQ20">
-        <v>1.16</v>
-      </c>
       <c r="AR20">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AS20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AT20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AU20">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AV20">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AW20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AX20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AY20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AZ20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BA20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BB20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BC20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BD20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BE20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BF20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BG20">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5745,13 +5745,13 @@
         <v>166</v>
       </c>
       <c r="F21">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G21">
         <v>2.08</v>
       </c>
       <c r="H21">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I21">
         <v>4.7</v>
@@ -5763,31 +5763,31 @@
         <v>5.1</v>
       </c>
       <c r="L21">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
         <v>1.02</v>
       </c>
       <c r="N21">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O21">
         <v>1.26</v>
       </c>
       <c r="P21">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q21">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R21">
         <v>1.38</v>
       </c>
       <c r="S21">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T21">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U21">
         <v>2.06</v>
@@ -5796,7 +5796,7 @@
         <v>1.27</v>
       </c>
       <c r="W21">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5811,10 +5811,10 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD21">
         <v>1000</v>
@@ -5853,64 +5853,64 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AQ21">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AR21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AS21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU21">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="AV21">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AW21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AX21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AY21">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="AZ21">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BA21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BB21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BC21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BD21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BE21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BF21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BG21">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5990,16 +5990,16 @@
         <v>3.2</v>
       </c>
       <c r="G22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H22">
         <v>2.04</v>
       </c>
       <c r="I22">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
         <v>4.8</v>
@@ -6017,7 +6017,7 @@
         <v>1.18</v>
       </c>
       <c r="P22">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q22">
         <v>1.56</v>
@@ -6026,25 +6026,25 @@
         <v>1.54</v>
       </c>
       <c r="S22">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T22">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U22">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V22">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X22">
         <v>1000</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22">
         <v>1000</v>
@@ -6059,7 +6059,7 @@
         <v>970</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE22">
         <v>1000</v>
@@ -6095,58 +6095,58 @@
         <v>970</v>
       </c>
       <c r="AP22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AR22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AS22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AU22">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AV22">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AW22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AX22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AY22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AZ22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BA22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BB22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BC22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BD22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BE22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BF22">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG22">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6229,7 +6229,7 @@
         <v>168</v>
       </c>
       <c r="F23">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G23">
         <v>3.75</v>
@@ -6238,46 +6238,46 @@
         <v>2.02</v>
       </c>
       <c r="I23">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J23">
         <v>3.9</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O23">
         <v>1.2</v>
       </c>
       <c r="P23">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q23">
         <v>1.6</v>
       </c>
       <c r="R23">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S23">
         <v>2.5</v>
       </c>
       <c r="T23">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U23">
         <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W23">
         <v>1.36</v>
@@ -6289,13 +6289,13 @@
         <v>14</v>
       </c>
       <c r="Z23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA23">
         <v>26</v>
       </c>
       <c r="AB23">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -6304,13 +6304,13 @@
         <v>11.5</v>
       </c>
       <c r="AE23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AF23">
         <v>32</v>
       </c>
       <c r="AG23">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH23">
         <v>16.5</v>
@@ -6322,10 +6322,10 @@
         <v>75</v>
       </c>
       <c r="AK23">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AL23">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM23">
         <v>75</v>
@@ -6337,7 +6337,7 @@
         <v>10.5</v>
       </c>
       <c r="AP23">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ23">
         <v>11.5</v>
@@ -6346,7 +6346,7 @@
         <v>13</v>
       </c>
       <c r="AS23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT23">
         <v>16</v>
@@ -6358,7 +6358,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX23">
         <v>21</v>
@@ -6373,34 +6373,34 @@
         <v>20</v>
       </c>
       <c r="BB23">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC23">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD23">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE23">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23">
         <v>21</v>
       </c>
       <c r="BG23">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6412,7 +6412,7 @@
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="BP23">
         <v>1000</v>
@@ -6430,13 +6430,13 @@
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="BX23">
         <v>1000</v>
@@ -6474,10 +6474,10 @@
         <v>3.1</v>
       </c>
       <c r="G24">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H24">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="I24">
         <v>2.3</v>
@@ -6486,16 +6486,16 @@
         <v>3.7</v>
       </c>
       <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
         <v>4.7</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.01</v>
-      </c>
-      <c r="N24">
-        <v>4.3</v>
       </c>
       <c r="O24">
         <v>1.18</v>
@@ -6504,13 +6504,13 @@
         <v>2.38</v>
       </c>
       <c r="Q24">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R24">
         <v>1.56</v>
       </c>
       <c r="S24">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T24">
         <v>1.51</v>
@@ -6522,13 +6522,13 @@
         <v>1.76</v>
       </c>
       <c r="W24">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X24">
         <v>30</v>
       </c>
       <c r="Y24">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z24">
         <v>20</v>
@@ -6540,10 +6540,10 @@
         <v>24</v>
       </c>
       <c r="AC24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD24">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE24">
         <v>24</v>
@@ -6552,10 +6552,10 @@
         <v>36</v>
       </c>
       <c r="AG24">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH24">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI24">
         <v>34</v>
@@ -6579,58 +6579,58 @@
         <v>12.5</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6713,10 +6713,10 @@
         <v>170</v>
       </c>
       <c r="F25">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>1.44</v>
@@ -6725,19 +6725,19 @@
         <v>1.5</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K25">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L25">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O25">
         <v>1.16</v>
@@ -6746,16 +6746,16 @@
         <v>2.74</v>
       </c>
       <c r="Q25">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S25">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T25">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U25">
         <v>2.22</v>
@@ -6764,7 +6764,7 @@
         <v>3</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
         <v>36</v>
@@ -6785,25 +6785,25 @@
         <v>13.5</v>
       </c>
       <c r="AD25">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE25">
         <v>15</v>
       </c>
       <c r="AF25">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG25">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AH25">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI25">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ25">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AK25">
         <v>100</v>
@@ -6818,22 +6818,22 @@
         <v>85</v>
       </c>
       <c r="AO25">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AP25">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT25">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU25">
         <v>11</v>
@@ -6845,34 +6845,34 @@
         <v>12</v>
       </c>
       <c r="AX25">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY25">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ25">
         <v>17.5</v>
       </c>
       <c r="BA25">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BB25">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC25">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD25">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BE25">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BF25">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG25">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6884,31 +6884,31 @@
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BT25">
         <v>1000</v>
@@ -6920,19 +6920,19 @@
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="CB25" t="s">
         <v>179</v>
@@ -6958,163 +6958,163 @@
         <v>2.34</v>
       </c>
       <c r="G26">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H26">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I26">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J26">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="K26">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L26">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O26">
         <v>1.31</v>
       </c>
       <c r="P26">
+        <v>1.84</v>
+      </c>
+      <c r="Q26">
         <v>1.87</v>
       </c>
-      <c r="Q26">
-        <v>1.88</v>
-      </c>
       <c r="R26">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S26">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V26">
         <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP26">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ26">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR26">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS26">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT26">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU26">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV26">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW26">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY26">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ26">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA26">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD26">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE26">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7206,7 +7206,7 @@
         <v>1.92</v>
       </c>
       <c r="I27">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J27">
         <v>3.3</v>
@@ -7227,7 +7227,7 @@
         <v>1.35</v>
       </c>
       <c r="P27">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
         <v>2.04</v>
@@ -7236,13 +7236,13 @@
         <v>1.13</v>
       </c>
       <c r="S27">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V27">
         <v>1.87</v>
@@ -7442,7 +7442,7 @@
         <v>2.38</v>
       </c>
       <c r="G28">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H28">
         <v>3.45</v>
@@ -7460,16 +7460,16 @@
         <v>1.59</v>
       </c>
       <c r="M28">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O28">
         <v>1.57</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q28">
         <v>2.68</v>
@@ -7478,7 +7478,7 @@
         <v>1.2</v>
       </c>
       <c r="S28">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T28">
         <v>2.16</v>
@@ -7490,7 +7490,7 @@
         <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X28">
         <v>8.6</v>
@@ -7523,10 +7523,10 @@
         <v>12.5</v>
       </c>
       <c r="AH28">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI28">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ28">
         <v>48</v>
@@ -7544,7 +7544,7 @@
         <v>36</v>
       </c>
       <c r="AO28">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP28">
         <v>7.6</v>
@@ -7568,7 +7568,7 @@
         <v>15</v>
       </c>
       <c r="AW28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX28">
         <v>12</v>
@@ -7580,28 +7580,28 @@
         <v>21</v>
       </c>
       <c r="BA28">
+        <v>12</v>
+      </c>
+      <c r="BB28">
+        <v>10.5</v>
+      </c>
+      <c r="BC28">
+        <v>10</v>
+      </c>
+      <c r="BD28">
         <v>11.5</v>
       </c>
-      <c r="BB28">
+      <c r="BE28">
+        <v>13</v>
+      </c>
+      <c r="BF28">
         <v>10</v>
       </c>
-      <c r="BC28">
-        <v>9.6</v>
-      </c>
-      <c r="BD28">
-        <v>11</v>
-      </c>
-      <c r="BE28">
-        <v>12.5</v>
-      </c>
-      <c r="BF28">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH28">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
         <v>2.24</v>
@@ -7610,55 +7610,55 @@
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>2.72</v>
+        <v>1.48</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>3.55</v>
+        <v>1.89</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>2.26</v>
+        <v>1.48</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>179</v>
@@ -7759,13 +7759,13 @@
         <v>40</v>
       </c>
       <c r="AF29">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG29">
         <v>12.5</v>
       </c>
       <c r="AH29">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI29">
         <v>55</v>
@@ -7786,7 +7786,7 @@
         <v>25</v>
       </c>
       <c r="AO29">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP29">
         <v>12.5</v>
@@ -7798,7 +7798,7 @@
         <v>18.5</v>
       </c>
       <c r="AS29">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="AT29">
         <v>9.800000000000001</v>
@@ -7810,7 +7810,7 @@
         <v>11.5</v>
       </c>
       <c r="AW29">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX29">
         <v>14</v>
@@ -7822,19 +7822,19 @@
         <v>14.5</v>
       </c>
       <c r="BA29">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BB29">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC29">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BD29">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE29">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF29">
         <v>18</v>
@@ -7932,10 +7932,10 @@
         <v>3.75</v>
       </c>
       <c r="I30">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K30">
         <v>3.65</v>
@@ -7950,10 +7950,10 @@
         <v>3.35</v>
       </c>
       <c r="O30">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P30">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q30">
         <v>2.1</v>
@@ -7962,7 +7962,7 @@
         <v>1.31</v>
       </c>
       <c r="S30">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T30">
         <v>1.86</v>
@@ -7989,7 +7989,7 @@
         <v>95</v>
       </c>
       <c r="AB30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -8019,7 +8019,7 @@
         <v>25</v>
       </c>
       <c r="AL30">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM30">
         <v>130</v>
@@ -8037,22 +8037,22 @@
         <v>11.5</v>
       </c>
       <c r="AR30">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="AS30">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU30">
         <v>7</v>
       </c>
       <c r="AV30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW30">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8067,25 +8067,25 @@
         <v>10</v>
       </c>
       <c r="BB30">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC30">
         <v>21</v>
       </c>
       <c r="BD30">
-        <v>34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE30">
         <v>10</v>
       </c>
       <c r="BF30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG30">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH30">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
         <v>2.62</v>
@@ -8103,10 +8103,10 @@
         <v>2.62</v>
       </c>
       <c r="BN30">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="BP30">
         <v>1000</v>
@@ -8124,7 +8124,7 @@
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>4.6</v>
+        <v>2.06</v>
       </c>
       <c r="BV30">
         <v>1000</v>
@@ -8165,7 +8165,7 @@
         <v>176</v>
       </c>
       <c r="F31">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="G31">
         <v>2.26</v>
@@ -8189,28 +8189,28 @@
         <v>1.03</v>
       </c>
       <c r="N31">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O31">
         <v>1.26</v>
       </c>
       <c r="P31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q31">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R31">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S31">
         <v>2.92</v>
       </c>
       <c r="T31">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U31">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V31">
         <v>1.33</v>
@@ -8407,13 +8407,13 @@
         <v>177</v>
       </c>
       <c r="F32">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G32">
         <v>3.3</v>
       </c>
       <c r="H32">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I32">
         <v>2.72</v>
@@ -8422,7 +8422,7 @@
         <v>3.2</v>
       </c>
       <c r="K32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L32">
         <v>1.46</v>
@@ -8431,7 +8431,7 @@
         <v>1.1</v>
       </c>
       <c r="N32">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O32">
         <v>1.45</v>
@@ -8440,16 +8440,16 @@
         <v>1.64</v>
       </c>
       <c r="Q32">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R32">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S32">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T32">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="U32">
         <v>1.89</v>
@@ -8467,10 +8467,10 @@
         <v>9</v>
       </c>
       <c r="Z32">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA32">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB32">
         <v>12</v>
@@ -8500,7 +8500,7 @@
         <v>70</v>
       </c>
       <c r="AK32">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AL32">
         <v>75</v>
@@ -8524,7 +8524,7 @@
         <v>13.5</v>
       </c>
       <c r="AS32">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT32">
         <v>8.800000000000001</v>
@@ -8536,7 +8536,7 @@
         <v>10.5</v>
       </c>
       <c r="AW32">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX32">
         <v>17</v>
@@ -8548,25 +8548,25 @@
         <v>17.5</v>
       </c>
       <c r="BA32">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB32">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC32">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="BD32">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE32">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF32">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="BG32">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8673,16 +8673,16 @@
         <v>1.11</v>
       </c>
       <c r="N33">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O33">
         <v>1.5</v>
       </c>
       <c r="P33">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q33">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R33">
         <v>1.22</v>
@@ -8751,7 +8751,7 @@
         <v>270</v>
       </c>
       <c r="AN33">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO33">
         <v>240</v>
@@ -8763,7 +8763,7 @@
         <v>12.5</v>
       </c>
       <c r="AR33">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS33">
         <v>10.5</v>
@@ -8778,7 +8778,7 @@
         <v>21</v>
       </c>
       <c r="AW33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX33">
         <v>8.4</v>
@@ -8787,10 +8787,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ33">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="BA33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB33">
         <v>17.5</v>
@@ -8799,7 +8799,7 @@
         <v>21</v>
       </c>
       <c r="BD33">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="BE33">
         <v>10.5</v>
@@ -8811,64 +8811,64 @@
         <v>10.5</v>
       </c>
       <c r="BH33">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="CB33" t="s">
         <v>179</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="183">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Japanese J League 3</t>
   </si>
   <si>
+    <t>Moroccan Botola Pro 1</t>
+  </si>
+  <si>
     <t>Danish 2nd Division</t>
   </si>
   <si>
@@ -283,9 +286,6 @@
     <t>Swedish Division 1</t>
   </si>
   <si>
-    <t>Moroccan Botola Pro 1</t>
-  </si>
-  <si>
     <t>Spanish Segunda Division</t>
   </si>
   <si>
@@ -328,6 +328,9 @@
     <t>10:00:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -382,6 +385,9 @@
     <t>Mio Biwako Shiga</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Fremad Amager</t>
   </si>
   <si>
@@ -478,6 +484,9 @@
     <t>Kumamoto</t>
   </si>
   <si>
+    <t>US Amal Tiznit</t>
+  </si>
+  <si>
     <t>B93 Copenhagen</t>
   </si>
   <si>
@@ -553,7 +562,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 05:55:51</t>
+    <t>2026-10-01 08:08:20</t>
   </si>
 </sst>
 </file>
@@ -885,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1141,10 +1150,10 @@
         <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F2">
         <v>1.69</v>
@@ -1165,13 +1174,13 @@
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.37</v>
@@ -1186,13 +1195,13 @@
         <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
         <v>1.19</v>
@@ -1201,22 +1210,22 @@
         <v>2.38</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
         <v>25</v>
@@ -1225,13 +1234,13 @@
         <v>110</v>
       </c>
       <c r="AF2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>110</v>
@@ -1240,13 +1249,13 @@
         <v>17.5</v>
       </c>
       <c r="AK2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN2">
         <v>12.5</v>
@@ -1258,28 +1267,28 @@
         <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
@@ -1288,55 +1297,55 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="BM2">
         <v>9.6</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
         <v>12</v>
       </c>
       <c r="BQ2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
         <v>34</v>
@@ -1345,10 +1354,10 @@
         <v>7.8</v>
       </c>
       <c r="BT2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BU2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BV2">
         <v>70</v>
@@ -1357,19 +1366,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA2">
         <v>7.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1383,208 +1392,208 @@
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>3.5</v>
       </c>
       <c r="G3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J3">
         <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
         <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S3">
         <v>2.74</v>
       </c>
       <c r="T3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U3">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W3">
         <v>1.37</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y3">
         <v>12.5</v>
       </c>
       <c r="Z3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD3">
         <v>10.5</v>
       </c>
       <c r="AE3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF3">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AG3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH3">
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ3">
+        <v>75</v>
+      </c>
+      <c r="AK3">
         <v>65</v>
       </c>
-      <c r="AK3">
+      <c r="AL3">
         <v>70</v>
       </c>
-      <c r="AL3">
-        <v>44</v>
-      </c>
       <c r="AM3">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AT3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV3">
+        <v>9.4</v>
+      </c>
+      <c r="AW3">
+        <v>16.5</v>
+      </c>
+      <c r="AX3">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW3">
-        <v>17</v>
-      </c>
-      <c r="AX3">
-        <v>14.5</v>
-      </c>
       <c r="AY3">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3">
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="BD3">
-        <v>19.5</v>
+        <v>9.6</v>
       </c>
       <c r="BE3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BF3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO3">
         <v>5.5</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
         <v>5.3</v>
@@ -1593,25 +1602,25 @@
         <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX3">
         <v>24</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1625,19 +1634,19 @@
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
         <v>1.11</v>
@@ -1649,7 +1658,7 @@
         <v>15</v>
       </c>
       <c r="L4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M4">
         <v>1.02</v>
@@ -1667,34 +1676,34 @@
         <v>1.42</v>
       </c>
       <c r="R4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T4">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="U4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>1.02</v>
       </c>
       <c r="X4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AB4">
         <v>120</v>
@@ -1706,7 +1715,7 @@
         <v>20</v>
       </c>
       <c r="AE4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF4">
         <v>1000</v>
@@ -1715,10 +1724,10 @@
         <v>950</v>
       </c>
       <c r="AH4">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
@@ -1739,112 +1748,112 @@
         <v>2.8</v>
       </c>
       <c r="AP4">
+        <v>7.4</v>
+      </c>
+      <c r="AQ4">
+        <v>10</v>
+      </c>
+      <c r="AR4">
         <v>6.6</v>
       </c>
-      <c r="AQ4">
-        <v>9.6</v>
-      </c>
-      <c r="AR4">
-        <v>6.8</v>
-      </c>
       <c r="AS4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AU4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AY4">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB4">
         <v>9</v>
       </c>
-      <c r="BA4">
+      <c r="BC4">
         <v>9</v>
       </c>
-      <c r="BB4">
-        <v>7.8</v>
-      </c>
-      <c r="BC4">
-        <v>7.8</v>
-      </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG4">
         <v>2.3</v>
       </c>
       <c r="BH4">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BI4">
         <v>4.5</v>
       </c>
       <c r="BJ4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BO4">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BU4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BV4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BW4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BX4">
         <v>29</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>6</v>
@@ -1853,7 +1862,7 @@
         <v>4.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1867,34 +1876,34 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G5">
         <v>3.1</v>
       </c>
       <c r="H5">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I5">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L5">
         <v>1.44</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
         <v>3.55</v>
@@ -1903,25 +1912,25 @@
         <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
         <v>1.79</v>
       </c>
       <c r="U5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
         <v>1.47</v>
@@ -1933,16 +1942,16 @@
         <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB5">
         <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD5">
         <v>13</v>
@@ -1954,28 +1963,28 @@
         <v>24</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO5">
         <v>34</v>
@@ -1987,22 +1996,22 @@
         <v>10</v>
       </c>
       <c r="AR5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AT5">
         <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="AX5">
         <v>17</v>
@@ -2011,67 +2020,67 @@
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC5">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE5">
+        <v>8.6</v>
+      </c>
+      <c r="BF5">
         <v>7.6</v>
       </c>
-      <c r="BF5">
-        <v>6.6</v>
-      </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI5">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU5">
         <v>4.5</v>
@@ -2083,19 +2092,19 @@
         <v>4.8</v>
       </c>
       <c r="BX5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CA5">
         <v>5.1</v>
       </c>
       <c r="CB5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2109,10 +2118,10 @@
         <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>1.53</v>
@@ -2139,28 +2148,28 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O6">
         <v>1.13</v>
       </c>
       <c r="P6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
         <v>1.4</v>
       </c>
       <c r="R6">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T6">
         <v>1.55</v>
       </c>
       <c r="U6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
         <v>1.18</v>
@@ -2178,19 +2187,19 @@
         <v>65</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB6">
         <v>16</v>
       </c>
       <c r="AC6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -2241,22 +2250,22 @@
         <v>12</v>
       </c>
       <c r="AV6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB6">
         <v>15</v>
@@ -2268,10 +2277,10 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG6">
         <v>36</v>
@@ -2283,16 +2292,16 @@
         <v>4.9</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL6">
         <v>65</v>
       </c>
       <c r="BM6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
@@ -2313,31 +2322,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU6">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BV6">
         <v>38</v>
       </c>
       <c r="BW6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY6">
         <v>12</v>
       </c>
       <c r="BZ6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CA6">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2351,13 +2360,13 @@
         <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>7.6</v>
@@ -2366,13 +2375,13 @@
         <v>1.54</v>
       </c>
       <c r="I7">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="J7">
         <v>4.4</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2381,10 +2390,10 @@
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P7">
         <v>2.1</v>
@@ -2393,19 +2402,19 @@
         <v>1.85</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S7">
         <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="W7">
         <v>1.15</v>
@@ -2420,64 +2429,64 @@
         <v>9.4</v>
       </c>
       <c r="AA7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AB7">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AF7">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AG7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AH7">
         <v>44</v>
       </c>
       <c r="AI7">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AJ7">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AK7">
         <v>130</v>
       </c>
       <c r="AL7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM7">
         <v>150</v>
       </c>
       <c r="AN7">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AO7">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP7">
         <v>15</v>
       </c>
       <c r="AQ7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT7">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AU7">
         <v>9.199999999999999</v>
@@ -2489,40 +2498,40 @@
         <v>14.5</v>
       </c>
       <c r="AX7">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AY7">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BA7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BD7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE7">
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH7">
         <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ7">
         <v>11</v>
@@ -2537,7 +2546,7 @@
         <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BO7">
         <v>1.04</v>
@@ -2561,7 +2570,7 @@
         <v>3.15</v>
       </c>
       <c r="BV7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BW7">
         <v>1.04</v>
@@ -2573,13 +2582,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2593,64 +2602,64 @@
         <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F8">
-        <v>1.15</v>
+        <v>2.66</v>
       </c>
       <c r="G8">
-        <v>990</v>
+        <v>3.3</v>
       </c>
       <c r="H8">
-        <v>1.16</v>
+        <v>2.4</v>
       </c>
       <c r="I8">
-        <v>990</v>
+        <v>2.86</v>
       </c>
       <c r="J8">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>3.65</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>2.86</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V8">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2821,7 +2830,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2835,28 +2844,28 @@
         <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F9">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="G9">
-        <v>3.6</v>
+        <v>1.96</v>
       </c>
       <c r="H9">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
-        <v>2.96</v>
+        <v>9.4</v>
       </c>
       <c r="J9">
         <v>3.1</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2865,264 +2874,264 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="P9">
+        <v>1.53</v>
+      </c>
+      <c r="Q9">
         <v>2.04</v>
       </c>
-      <c r="Q9">
-        <v>1.55</v>
-      </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="S9">
+        <v>2.96</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.12</v>
+      </c>
+      <c r="W9">
+        <v>2.04</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>3.6</v>
+      </c>
+      <c r="BI9">
         <v>2.34</v>
       </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
-      <c r="U9">
-        <v>1.11</v>
-      </c>
-      <c r="V9">
-        <v>1.51</v>
-      </c>
-      <c r="W9">
-        <v>1.39</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>1000</v>
-      </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
-        <v>1000</v>
-      </c>
-      <c r="AC9">
-        <v>1000</v>
-      </c>
-      <c r="AD9">
-        <v>1000</v>
-      </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
-        <v>1000</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>1000</v>
-      </c>
-      <c r="AI9">
-        <v>1000</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>1000</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1000</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9">
-        <v>1.01</v>
-      </c>
-      <c r="AR9">
-        <v>1.01</v>
-      </c>
-      <c r="AS9">
-        <v>1.01</v>
-      </c>
-      <c r="AT9">
-        <v>1.01</v>
-      </c>
-      <c r="AU9">
-        <v>1.01</v>
-      </c>
-      <c r="AV9">
-        <v>1.01</v>
-      </c>
-      <c r="AW9">
-        <v>1.01</v>
-      </c>
-      <c r="AX9">
-        <v>1.01</v>
-      </c>
-      <c r="AY9">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9">
-        <v>1.01</v>
-      </c>
-      <c r="BA9">
-        <v>1.01</v>
-      </c>
-      <c r="BB9">
-        <v>1.01</v>
-      </c>
-      <c r="BC9">
-        <v>1.01</v>
-      </c>
-      <c r="BD9">
-        <v>1.01</v>
-      </c>
-      <c r="BE9">
-        <v>1.01</v>
-      </c>
-      <c r="BF9">
-        <v>1.01</v>
-      </c>
-      <c r="BG9">
-        <v>1.01</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.04</v>
-      </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
         <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F10">
-        <v>1.58</v>
+        <v>2.46</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="H10">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>2.92</v>
       </c>
       <c r="J10">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="O10">
         <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="Q10">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S10">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3131,10 +3140,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="W10">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3305,186 +3314,186 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
         <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F11">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="G11">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="H11">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
+        <v>4.2</v>
+      </c>
+      <c r="L11">
+        <v>1.28</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>2.86</v>
+      </c>
+      <c r="O11">
+        <v>1.02</v>
+      </c>
+      <c r="P11">
+        <v>1.65</v>
+      </c>
+      <c r="Q11">
+        <v>1.87</v>
+      </c>
+      <c r="R11">
+        <v>1.26</v>
+      </c>
+      <c r="S11">
+        <v>2.68</v>
+      </c>
+      <c r="T11">
+        <v>1.12</v>
+      </c>
+      <c r="U11">
+        <v>1.12</v>
+      </c>
+      <c r="V11">
+        <v>1.17</v>
+      </c>
+      <c r="W11">
+        <v>2.02</v>
+      </c>
+      <c r="X11">
+        <v>16</v>
+      </c>
+      <c r="Y11">
+        <v>20</v>
+      </c>
+      <c r="Z11">
+        <v>50</v>
+      </c>
+      <c r="AA11">
+        <v>170</v>
+      </c>
+      <c r="AB11">
         <v>8.4</v>
       </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>4.5</v>
-      </c>
-      <c r="O11">
-        <v>1.01</v>
-      </c>
-      <c r="P11">
-        <v>2.16</v>
-      </c>
-      <c r="Q11">
-        <v>1.46</v>
-      </c>
-      <c r="R11">
-        <v>1.42</v>
-      </c>
-      <c r="S11">
-        <v>2.46</v>
-      </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
-      <c r="U11">
-        <v>1.11</v>
-      </c>
-      <c r="V11">
-        <v>1.47</v>
-      </c>
-      <c r="W11">
-        <v>1.41</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>1000</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>1000</v>
-      </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3547,7 +3556,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3558,175 +3567,175 @@
         <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F12">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>3.35</v>
       </c>
       <c r="H12">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="I12">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="K12">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="Q12">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="T12">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
+        <v>1.5</v>
+      </c>
+      <c r="W12">
         <v>1.42</v>
       </c>
-      <c r="W12">
-        <v>1.82</v>
-      </c>
       <c r="X12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3789,7 +3798,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3800,297 +3809,297 @@
         <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G13">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="H13">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I13">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="J13">
+        <v>4.4</v>
+      </c>
+      <c r="K13">
+        <v>4.7</v>
+      </c>
+      <c r="L13">
+        <v>1.18</v>
+      </c>
+      <c r="M13">
+        <v>1.02</v>
+      </c>
+      <c r="N13">
+        <v>8</v>
+      </c>
+      <c r="O13">
+        <v>1.11</v>
+      </c>
+      <c r="P13">
         <v>3.4</v>
       </c>
-      <c r="K13">
-        <v>5.2</v>
-      </c>
-      <c r="L13">
-        <v>1.28</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>3.4</v>
-      </c>
-      <c r="O13">
-        <v>1.02</v>
-      </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>1.36</v>
+      </c>
+      <c r="R13">
         <v>1.98</v>
       </c>
-      <c r="Q13">
-        <v>1.75</v>
-      </c>
-      <c r="R13">
-        <v>1.35</v>
-      </c>
       <c r="S13">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F14">
+        <v>2.14</v>
+      </c>
+      <c r="G14">
+        <v>2.6</v>
+      </c>
+      <c r="H14">
         <v>2.86</v>
       </c>
-      <c r="G14">
-        <v>4.7</v>
-      </c>
-      <c r="H14">
-        <v>1.86</v>
-      </c>
       <c r="I14">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O14">
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q14">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S14">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4099,10 +4108,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4273,42 +4282,42 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
         <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F15">
-        <v>1.34</v>
+        <v>2.86</v>
       </c>
       <c r="G15">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>1.86</v>
       </c>
       <c r="I15">
-        <v>990</v>
+        <v>2.3</v>
       </c>
       <c r="J15">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K15">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4317,22 +4326,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="O15">
         <v>1.02</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S15">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4341,10 +4350,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.13</v>
+        <v>1.76</v>
       </c>
       <c r="W15">
-        <v>2.66</v>
+        <v>1.28</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4515,7 +4524,7 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4529,52 +4538,52 @@
         <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F16">
-        <v>2.8</v>
+        <v>1.42</v>
       </c>
       <c r="G16">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="H16">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>3.45</v>
+        <v>8.6</v>
       </c>
       <c r="J16">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="K16">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.34</v>
+        <v>5.7</v>
       </c>
       <c r="O16">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>1.37</v>
+        <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>2.86</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="S16">
-        <v>2.86</v>
+        <v>2.28</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4583,186 +4592,186 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="W16">
-        <v>1.42</v>
+        <v>2.92</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="CB16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
         <v>98</v>
@@ -4771,240 +4780,240 @@
         <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F17">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="G17">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="I17">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="J17">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="K17">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L17">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N17">
-        <v>2.82</v>
+        <v>2.38</v>
       </c>
       <c r="O17">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="P17">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="Q17">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="T17">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U17">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X17">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z17">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AA17">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AB17">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE17">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AF17">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG17">
         <v>14.5</v>
       </c>
       <c r="AH17">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AI17">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AJ17">
+        <v>60</v>
+      </c>
+      <c r="AK17">
         <v>55</v>
       </c>
-      <c r="AK17">
-        <v>42</v>
-      </c>
       <c r="AL17">
+        <v>90</v>
+      </c>
+      <c r="AM17">
+        <v>250</v>
+      </c>
+      <c r="AN17">
         <v>70</v>
       </c>
-      <c r="AM17">
-        <v>150</v>
-      </c>
-      <c r="AN17">
-        <v>48</v>
-      </c>
       <c r="AO17">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AP17">
-        <v>8.6</v>
+        <v>3.95</v>
       </c>
       <c r="AQ17">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="AR17">
-        <v>14.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS17">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="AT17">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="AU17">
+        <v>3.6</v>
+      </c>
+      <c r="AV17">
+        <v>5</v>
+      </c>
+      <c r="AW17">
+        <v>6.4</v>
+      </c>
+      <c r="AX17">
+        <v>5.3</v>
+      </c>
+      <c r="AY17">
+        <v>4.8</v>
+      </c>
+      <c r="AZ17">
+        <v>5.8</v>
+      </c>
+      <c r="BA17">
+        <v>6.8</v>
+      </c>
+      <c r="BB17">
+        <v>6.4</v>
+      </c>
+      <c r="BC17">
+        <v>6.4</v>
+      </c>
+      <c r="BD17">
         <v>6.6</v>
       </c>
-      <c r="AV17">
-        <v>12</v>
-      </c>
-      <c r="AW17">
-        <v>34</v>
-      </c>
-      <c r="AX17">
-        <v>15.5</v>
-      </c>
-      <c r="AY17">
-        <v>12.5</v>
-      </c>
-      <c r="AZ17">
-        <v>18.5</v>
-      </c>
-      <c r="BA17">
-        <v>50</v>
-      </c>
-      <c r="BB17">
-        <v>26</v>
-      </c>
-      <c r="BC17">
-        <v>34</v>
-      </c>
-      <c r="BD17">
-        <v>50</v>
-      </c>
       <c r="BE17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BF17">
-        <v>38</v>
+        <v>6.6</v>
       </c>
       <c r="BG17">
-        <v>38</v>
+        <v>6.6</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
         <v>98</v>
@@ -5013,235 +5022,235 @@
         <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F18">
-        <v>1.71</v>
+        <v>2.86</v>
       </c>
       <c r="G18">
+        <v>2.98</v>
+      </c>
+      <c r="H18">
+        <v>2.86</v>
+      </c>
+      <c r="I18">
+        <v>2.96</v>
+      </c>
+      <c r="J18">
+        <v>3.15</v>
+      </c>
+      <c r="K18">
+        <v>3.2</v>
+      </c>
+      <c r="L18">
+        <v>1.48</v>
+      </c>
+      <c r="M18">
+        <v>1.11</v>
+      </c>
+      <c r="N18">
+        <v>2.88</v>
+      </c>
+      <c r="O18">
+        <v>1.49</v>
+      </c>
+      <c r="P18">
+        <v>1.6</v>
+      </c>
+      <c r="Q18">
+        <v>2.54</v>
+      </c>
+      <c r="R18">
+        <v>1.22</v>
+      </c>
+      <c r="S18">
+        <v>5</v>
+      </c>
+      <c r="T18">
+        <v>2.06</v>
+      </c>
+      <c r="U18">
         <v>1.86</v>
       </c>
-      <c r="H18">
-        <v>4.3</v>
-      </c>
-      <c r="I18">
-        <v>5.5</v>
-      </c>
-      <c r="J18">
-        <v>4.3</v>
-      </c>
-      <c r="K18">
-        <v>4.8</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.02</v>
-      </c>
-      <c r="N18">
-        <v>4.5</v>
-      </c>
-      <c r="O18">
-        <v>1.19</v>
-      </c>
-      <c r="P18">
-        <v>2.42</v>
-      </c>
-      <c r="Q18">
-        <v>1.52</v>
-      </c>
-      <c r="R18">
-        <v>1.56</v>
-      </c>
-      <c r="S18">
-        <v>2.28</v>
-      </c>
-      <c r="T18">
-        <v>1.57</v>
-      </c>
-      <c r="U18">
-        <v>2.36</v>
-      </c>
       <c r="V18">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="W18">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB18">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="AC18">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG18">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN18">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP18">
-        <v>1.32</v>
+        <v>8.6</v>
       </c>
       <c r="AQ18">
-        <v>1.32</v>
+        <v>8</v>
       </c>
       <c r="AR18">
-        <v>1.32</v>
+        <v>14.5</v>
       </c>
       <c r="AS18">
-        <v>1.32</v>
+        <v>23</v>
       </c>
       <c r="AT18">
-        <v>1.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18">
-        <v>1.23</v>
+        <v>6.6</v>
       </c>
       <c r="AV18">
-        <v>1.32</v>
+        <v>12</v>
       </c>
       <c r="AW18">
-        <v>1.32</v>
+        <v>10.5</v>
       </c>
       <c r="AX18">
-        <v>1.32</v>
+        <v>15</v>
       </c>
       <c r="AY18">
-        <v>1.23</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18">
-        <v>1.32</v>
+        <v>19</v>
       </c>
       <c r="BA18">
-        <v>1.32</v>
+        <v>50</v>
       </c>
       <c r="BB18">
-        <v>1.32</v>
+        <v>42</v>
       </c>
       <c r="BC18">
-        <v>1.32</v>
+        <v>34</v>
       </c>
       <c r="BD18">
-        <v>1.32</v>
+        <v>50</v>
       </c>
       <c r="BE18">
-        <v>1.32</v>
+        <v>12.5</v>
       </c>
       <c r="BF18">
-        <v>1.17</v>
+        <v>38</v>
       </c>
       <c r="BG18">
-        <v>1.32</v>
+        <v>36</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="CB18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5252,67 +5261,67 @@
         <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F19">
-        <v>2.74</v>
+        <v>1.69</v>
       </c>
       <c r="G19">
-        <v>3.35</v>
+        <v>1.81</v>
       </c>
       <c r="H19">
-        <v>2.14</v>
+        <v>4.6</v>
       </c>
       <c r="I19">
-        <v>2.46</v>
+        <v>5.2</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O19">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P19">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R19">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="S19">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="T19">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U19">
         <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="W19">
-        <v>1.43</v>
+        <v>2.22</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5327,22 +5336,22 @@
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC19">
         <v>970</v>
       </c>
       <c r="AD19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
         <v>1000</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH19">
         <v>1000</v>
@@ -5363,64 +5372,64 @@
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO19">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AQ19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AR19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AS19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AT19">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AU19">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AV19">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AW19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AX19">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AY19">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AZ19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BA19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BB19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BC19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BD19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BE19">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="BF19">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BG19">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5483,7 +5492,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5494,76 +5503,76 @@
         <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F20">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="G20">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="H20">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="O20">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="P20">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q20">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="R20">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S20">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="T20">
+        <v>1.55</v>
+      </c>
+      <c r="U20">
+        <v>2.28</v>
+      </c>
+      <c r="V20">
         <v>1.69</v>
       </c>
-      <c r="U20">
-        <v>2.1</v>
-      </c>
-      <c r="V20">
-        <v>2</v>
-      </c>
       <c r="W20">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="X20">
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
         <v>1000</v>
@@ -5608,61 +5617,61 @@
         <v>1000</v>
       </c>
       <c r="AO20">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AP20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AR20">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AS20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AU20">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AV20">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AW20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AX20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AY20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AZ20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BA20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BB20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BC20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BD20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BE20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BF20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BG20">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5725,7 +5734,7 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5736,88 +5745,88 @@
         <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F21">
-        <v>1.86</v>
+        <v>3.6</v>
       </c>
       <c r="G21">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="H21">
-        <v>3.6</v>
+        <v>1.88</v>
       </c>
       <c r="I21">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J21">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K21">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O21">
         <v>1.26</v>
       </c>
       <c r="P21">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R21">
         <v>1.38</v>
       </c>
       <c r="S21">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T21">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U21">
         <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="W21">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="X21">
         <v>1000</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA21">
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
         <v>970</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE21">
         <v>1000</v>
@@ -5850,61 +5859,61 @@
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AQ21">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AR21">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AS21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AT21">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AU21">
-        <v>6.4</v>
+        <v>1.18</v>
       </c>
       <c r="AV21">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AW21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AX21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AY21">
-        <v>7.4</v>
+        <v>1.28</v>
       </c>
       <c r="AZ21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BA21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BB21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BC21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BD21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BE21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BF21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BG21">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5967,7 +5976,7 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5978,73 +5987,73 @@
         <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F22">
-        <v>3.2</v>
+        <v>1.89</v>
       </c>
       <c r="G22">
-        <v>3.95</v>
+        <v>2.04</v>
       </c>
       <c r="H22">
+        <v>3.9</v>
+      </c>
+      <c r="I22">
+        <v>4.4</v>
+      </c>
+      <c r="J22">
+        <v>3.85</v>
+      </c>
+      <c r="K22">
+        <v>4.2</v>
+      </c>
+      <c r="L22">
+        <v>1.31</v>
+      </c>
+      <c r="M22">
+        <v>1.02</v>
+      </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
+      <c r="O22">
+        <v>1.26</v>
+      </c>
+      <c r="P22">
         <v>2.04</v>
       </c>
-      <c r="I22">
-        <v>2.28</v>
-      </c>
-      <c r="J22">
-        <v>3.7</v>
-      </c>
-      <c r="K22">
-        <v>4.8</v>
-      </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.01</v>
-      </c>
-      <c r="N22">
-        <v>4.8</v>
-      </c>
-      <c r="O22">
-        <v>1.18</v>
-      </c>
-      <c r="P22">
-        <v>2.36</v>
-      </c>
       <c r="Q22">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="R22">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S22">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="T22">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="U22">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="V22">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="W22">
-        <v>1.34</v>
+        <v>1.96</v>
       </c>
       <c r="X22">
         <v>1000</v>
       </c>
       <c r="Y22">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
         <v>1000</v>
@@ -6053,23 +6062,23 @@
         <v>1000</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC22">
         <v>970</v>
       </c>
       <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
         <v>950</v>
       </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>1000</v>
-      </c>
       <c r="AH22">
         <v>1000</v>
       </c>
@@ -6092,61 +6101,61 @@
         <v>1000</v>
       </c>
       <c r="AO22">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AR22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AS22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AT22">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AU22">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AV22">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AW22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AX22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AY22">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AZ22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BA22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BB22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BC22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BD22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BE22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BF22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BG22">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6209,153 +6218,153 @@
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
         <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F23">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="G23">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I23">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M23">
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O23">
         <v>1.2</v>
       </c>
       <c r="P23">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q23">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R23">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S23">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T23">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U23">
         <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="W23">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X23">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y23">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z23">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA23">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AB23">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD23">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE23">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG23">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH23">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI23">
         <v>34</v>
       </c>
       <c r="AJ23">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK23">
+        <v>40</v>
+      </c>
+      <c r="AL23">
         <v>44</v>
       </c>
-      <c r="AL23">
-        <v>48</v>
-      </c>
       <c r="AM23">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ23">
         <v>11.5</v>
       </c>
       <c r="AR23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU23">
         <v>8.4</v>
       </c>
       <c r="AV23">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW23">
         <v>16.5</v>
@@ -6364,99 +6373,99 @@
         <v>21</v>
       </c>
       <c r="AY23">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB23">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BC23">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD23">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE23">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BF23">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>98</v>
@@ -6465,414 +6474,414 @@
         <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F24">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G24">
         <v>3.9</v>
       </c>
       <c r="H24">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="I24">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="J24">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O24">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="Q24">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="R24">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S24">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="T24">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="U24">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V24">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="W24">
         <v>1.35</v>
       </c>
       <c r="X24">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Y24">
+        <v>14</v>
+      </c>
+      <c r="Z24">
         <v>15.5</v>
       </c>
-      <c r="Z24">
-        <v>20</v>
-      </c>
       <c r="AA24">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB24">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF24">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG24">
         <v>17</v>
       </c>
       <c r="AH24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI24">
         <v>34</v>
       </c>
       <c r="AJ24">
+        <v>80</v>
+      </c>
+      <c r="AK24">
+        <v>44</v>
+      </c>
+      <c r="AL24">
+        <v>50</v>
+      </c>
+      <c r="AM24">
         <v>75</v>
       </c>
-      <c r="AK24">
-        <v>42</v>
-      </c>
-      <c r="AL24">
-        <v>46</v>
-      </c>
-      <c r="AM24">
-        <v>70</v>
-      </c>
       <c r="AN24">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AO24">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AP24">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="AQ24">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="AR24">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="AS24">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="AT24">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="AU24">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV24">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW24">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AX24">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="AY24">
-        <v>3.8</v>
+        <v>13.5</v>
       </c>
       <c r="AZ24">
-        <v>3.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA24">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BB24">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BC24">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD24">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE24">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BF24">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="BG24">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="CB24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
         <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>2.78</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="H25">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="I25">
-        <v>1.5</v>
+        <v>2.56</v>
       </c>
       <c r="J25">
+        <v>3.35</v>
+      </c>
+      <c r="K25">
+        <v>4.4</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>4.9</v>
+      </c>
+      <c r="O25">
+        <v>1.19</v>
+      </c>
+      <c r="P25">
+        <v>2.42</v>
+      </c>
+      <c r="Q25">
+        <v>1.56</v>
+      </c>
+      <c r="R25">
+        <v>1.53</v>
+      </c>
+      <c r="S25">
+        <v>2.36</v>
+      </c>
+      <c r="T25">
+        <v>1.51</v>
+      </c>
+      <c r="U25">
+        <v>2.42</v>
+      </c>
+      <c r="V25">
+        <v>1.64</v>
+      </c>
+      <c r="W25">
+        <v>1.43</v>
+      </c>
+      <c r="X25">
+        <v>25</v>
+      </c>
+      <c r="Y25">
+        <v>16.5</v>
+      </c>
+      <c r="Z25">
+        <v>20</v>
+      </c>
+      <c r="AA25">
+        <v>38</v>
+      </c>
+      <c r="AB25">
+        <v>18.5</v>
+      </c>
+      <c r="AC25">
+        <v>10.5</v>
+      </c>
+      <c r="AD25">
+        <v>13.5</v>
+      </c>
+      <c r="AE25">
+        <v>27</v>
+      </c>
+      <c r="AF25">
+        <v>30</v>
+      </c>
+      <c r="AG25">
+        <v>15</v>
+      </c>
+      <c r="AH25">
+        <v>16</v>
+      </c>
+      <c r="AI25">
+        <v>38</v>
+      </c>
+      <c r="AJ25">
+        <v>60</v>
+      </c>
+      <c r="AK25">
+        <v>36</v>
+      </c>
+      <c r="AL25">
+        <v>38</v>
+      </c>
+      <c r="AM25">
+        <v>70</v>
+      </c>
+      <c r="AN25">
+        <v>24</v>
+      </c>
+      <c r="AO25">
+        <v>15.5</v>
+      </c>
+      <c r="AP25">
+        <v>4.5</v>
+      </c>
+      <c r="AQ25">
+        <v>4.1</v>
+      </c>
+      <c r="AR25">
+        <v>4.3</v>
+      </c>
+      <c r="AS25">
+        <v>4.8</v>
+      </c>
+      <c r="AT25">
+        <v>4.2</v>
+      </c>
+      <c r="AU25">
+        <v>3.6</v>
+      </c>
+      <c r="AV25">
+        <v>3.9</v>
+      </c>
+      <c r="AW25">
+        <v>4.5</v>
+      </c>
+      <c r="AX25">
+        <v>4.6</v>
+      </c>
+      <c r="AY25">
+        <v>4</v>
+      </c>
+      <c r="AZ25">
+        <v>4.1</v>
+      </c>
+      <c r="BA25">
+        <v>4.8</v>
+      </c>
+      <c r="BB25">
+        <v>5</v>
+      </c>
+      <c r="BC25">
+        <v>4.8</v>
+      </c>
+      <c r="BD25">
+        <v>4.8</v>
+      </c>
+      <c r="BE25">
         <v>5.1</v>
       </c>
-      <c r="K25">
-        <v>5.7</v>
-      </c>
-      <c r="L25">
-        <v>1.01</v>
-      </c>
-      <c r="M25">
-        <v>1.03</v>
-      </c>
-      <c r="N25">
-        <v>6.2</v>
-      </c>
-      <c r="O25">
-        <v>1.16</v>
-      </c>
-      <c r="P25">
-        <v>2.74</v>
-      </c>
-      <c r="Q25">
-        <v>1.48</v>
-      </c>
-      <c r="R25">
-        <v>1.71</v>
-      </c>
-      <c r="S25">
-        <v>2.22</v>
-      </c>
-      <c r="T25">
-        <v>1.69</v>
-      </c>
-      <c r="U25">
-        <v>2.22</v>
-      </c>
-      <c r="V25">
-        <v>3</v>
-      </c>
-      <c r="W25">
-        <v>1.15</v>
-      </c>
-      <c r="X25">
-        <v>36</v>
-      </c>
-      <c r="Y25">
-        <v>13.5</v>
-      </c>
-      <c r="Z25">
-        <v>12</v>
-      </c>
-      <c r="AA25">
-        <v>14.5</v>
-      </c>
-      <c r="AB25">
-        <v>38</v>
-      </c>
-      <c r="AC25">
-        <v>13.5</v>
-      </c>
-      <c r="AD25">
-        <v>11</v>
-      </c>
-      <c r="AE25">
-        <v>15</v>
-      </c>
-      <c r="AF25">
-        <v>80</v>
-      </c>
-      <c r="AG25">
-        <v>29</v>
-      </c>
-      <c r="AH25">
-        <v>22</v>
-      </c>
-      <c r="AI25">
-        <v>29</v>
-      </c>
-      <c r="AJ25">
-        <v>220</v>
-      </c>
-      <c r="AK25">
-        <v>100</v>
-      </c>
-      <c r="AL25">
-        <v>80</v>
-      </c>
-      <c r="AM25">
-        <v>95</v>
-      </c>
-      <c r="AN25">
-        <v>85</v>
-      </c>
-      <c r="AO25">
-        <v>5</v>
-      </c>
-      <c r="AP25">
-        <v>7.8</v>
-      </c>
-      <c r="AQ25">
-        <v>10.5</v>
-      </c>
-      <c r="AR25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS25">
-        <v>11.5</v>
-      </c>
-      <c r="AT25">
-        <v>7.8</v>
-      </c>
-      <c r="AU25">
-        <v>11</v>
-      </c>
-      <c r="AV25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW25">
-        <v>12</v>
-      </c>
-      <c r="AX25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY25">
-        <v>21</v>
-      </c>
-      <c r="AZ25">
-        <v>17.5</v>
-      </c>
-      <c r="BA25">
-        <v>20</v>
-      </c>
-      <c r="BB25">
-        <v>8.6</v>
-      </c>
-      <c r="BC25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD25">
-        <v>25</v>
-      </c>
-      <c r="BE25">
-        <v>27</v>
-      </c>
       <c r="BF25">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="BG25">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6884,63 +6893,63 @@
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
         <v>98</v>
@@ -6949,482 +6958,482 @@
         <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F26">
-        <v>2.34</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>2.68</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H26">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="I26">
-        <v>3.6</v>
+        <v>1.51</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="K26">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="O26">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q26">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="R26">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="S26">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="T26">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U26">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V26">
-        <v>1.41</v>
+        <v>2.96</v>
       </c>
       <c r="W26">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="Y26">
+        <v>13.5</v>
+      </c>
+      <c r="Z26">
+        <v>13</v>
+      </c>
+      <c r="AA26">
         <v>14.5</v>
       </c>
-      <c r="Z26">
-        <v>25</v>
-      </c>
-      <c r="AA26">
-        <v>60</v>
-      </c>
       <c r="AB26">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="AC26">
+        <v>13.5</v>
+      </c>
+      <c r="AD26">
+        <v>11.5</v>
+      </c>
+      <c r="AE26">
+        <v>14.5</v>
+      </c>
+      <c r="AF26">
+        <v>80</v>
+      </c>
+      <c r="AG26">
+        <v>32</v>
+      </c>
+      <c r="AH26">
+        <v>22</v>
+      </c>
+      <c r="AI26">
+        <v>32</v>
+      </c>
+      <c r="AJ26">
+        <v>220</v>
+      </c>
+      <c r="AK26">
+        <v>100</v>
+      </c>
+      <c r="AL26">
+        <v>80</v>
+      </c>
+      <c r="AM26">
+        <v>95</v>
+      </c>
+      <c r="AN26">
+        <v>85</v>
+      </c>
+      <c r="AO26">
+        <v>5.4</v>
+      </c>
+      <c r="AP26">
+        <v>8.4</v>
+      </c>
+      <c r="AQ26">
+        <v>11</v>
+      </c>
+      <c r="AR26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS26">
+        <v>11.5</v>
+      </c>
+      <c r="AT26">
+        <v>9.6</v>
+      </c>
+      <c r="AU26">
+        <v>11</v>
+      </c>
+      <c r="AV26">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD26">
-        <v>16</v>
-      </c>
-      <c r="AE26">
-        <v>42</v>
-      </c>
-      <c r="AF26">
-        <v>19.5</v>
-      </c>
-      <c r="AG26">
-        <v>13.5</v>
-      </c>
-      <c r="AH26">
-        <v>19.5</v>
-      </c>
-      <c r="AI26">
-        <v>55</v>
-      </c>
-      <c r="AJ26">
-        <v>42</v>
-      </c>
-      <c r="AK26">
-        <v>32</v>
-      </c>
-      <c r="AL26">
-        <v>46</v>
-      </c>
-      <c r="AM26">
-        <v>110</v>
-      </c>
-      <c r="AN26">
-        <v>25</v>
-      </c>
-      <c r="AO26">
-        <v>38</v>
-      </c>
-      <c r="AP26">
-        <v>3.95</v>
-      </c>
-      <c r="AQ26">
-        <v>3.8</v>
-      </c>
-      <c r="AR26">
-        <v>4.2</v>
-      </c>
-      <c r="AS26">
-        <v>4.7</v>
-      </c>
-      <c r="AT26">
-        <v>3.65</v>
-      </c>
-      <c r="AU26">
-        <v>3.3</v>
-      </c>
-      <c r="AV26">
-        <v>3.9</v>
-      </c>
       <c r="AW26">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AX26">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AY26">
-        <v>3.7</v>
+        <v>21</v>
       </c>
       <c r="AZ26">
-        <v>4</v>
+        <v>17.5</v>
       </c>
       <c r="BA26">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BB26">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC26">
-        <v>4.4</v>
+        <v>27</v>
       </c>
       <c r="BD26">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BE26">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BF26">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG26">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
         <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F27">
-        <v>3.85</v>
+        <v>2.18</v>
       </c>
       <c r="G27">
-        <v>5.1</v>
+        <v>2.46</v>
       </c>
       <c r="H27">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="I27">
-        <v>2.14</v>
+        <v>3.7</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N27">
+        <v>3.65</v>
+      </c>
+      <c r="O27">
+        <v>1.31</v>
+      </c>
+      <c r="P27">
+        <v>1.91</v>
+      </c>
+      <c r="Q27">
+        <v>1.87</v>
+      </c>
+      <c r="R27">
+        <v>1.35</v>
+      </c>
+      <c r="S27">
         <v>3.2</v>
       </c>
-      <c r="O27">
-        <v>1.35</v>
-      </c>
-      <c r="P27">
-        <v>1.73</v>
-      </c>
-      <c r="Q27">
-        <v>2.04</v>
-      </c>
-      <c r="R27">
-        <v>1.13</v>
-      </c>
-      <c r="S27">
-        <v>3</v>
-      </c>
       <c r="T27">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U27">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V27">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
         <v>98</v>
@@ -7433,184 +7442,184 @@
         <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F28">
-        <v>2.38</v>
+        <v>3.9</v>
       </c>
       <c r="G28">
-        <v>2.52</v>
+        <v>5.1</v>
       </c>
       <c r="H28">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="I28">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="J28">
+        <v>3.25</v>
+      </c>
+      <c r="K28">
+        <v>4.4</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.04</v>
+      </c>
+      <c r="N28">
         <v>3.1</v>
       </c>
-      <c r="K28">
-        <v>3.3</v>
-      </c>
-      <c r="L28">
-        <v>1.59</v>
-      </c>
-      <c r="M28">
-        <v>1.12</v>
-      </c>
-      <c r="N28">
-        <v>2.58</v>
-      </c>
       <c r="O28">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P28">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="Q28">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="R28">
         <v>1.2</v>
       </c>
       <c r="S28">
-        <v>5.4</v>
+        <v>2.92</v>
       </c>
       <c r="T28">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="U28">
         <v>1.78</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="W28">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="X28">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7622,13 +7631,13 @@
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BR28">
         <v>1000</v>
@@ -7640,7 +7649,7 @@
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7661,12 +7670,12 @@
         <v>1.04</v>
       </c>
       <c r="CB28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -7675,240 +7684,240 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F29">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G29">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I29">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="J29">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K29">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L29">
+        <v>1.6</v>
+      </c>
+      <c r="M29">
+        <v>1.12</v>
+      </c>
+      <c r="N29">
+        <v>2.6</v>
+      </c>
+      <c r="O29">
+        <v>1.57</v>
+      </c>
+      <c r="P29">
+        <v>1.56</v>
+      </c>
+      <c r="Q29">
+        <v>2.68</v>
+      </c>
+      <c r="R29">
+        <v>1.2</v>
+      </c>
+      <c r="S29">
+        <v>5.3</v>
+      </c>
+      <c r="T29">
+        <v>2.16</v>
+      </c>
+      <c r="U29">
+        <v>1.78</v>
+      </c>
+      <c r="V29">
         <v>1.39</v>
       </c>
-      <c r="M29">
-        <v>1.07</v>
-      </c>
-      <c r="N29">
-        <v>3.8</v>
-      </c>
-      <c r="O29">
-        <v>1.32</v>
-      </c>
-      <c r="P29">
-        <v>1.96</v>
-      </c>
-      <c r="Q29">
-        <v>1.93</v>
-      </c>
-      <c r="R29">
-        <v>1.38</v>
-      </c>
-      <c r="S29">
-        <v>3.4</v>
-      </c>
-      <c r="T29">
-        <v>1.74</v>
-      </c>
-      <c r="U29">
-        <v>2.2</v>
-      </c>
-      <c r="V29">
-        <v>1.46</v>
-      </c>
       <c r="W29">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X29">
-        <v>17</v>
+        <v>8.6</v>
       </c>
       <c r="Y29">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="Z29">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA29">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AB29">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AC29">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD29">
         <v>15.5</v>
       </c>
       <c r="AE29">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AF29">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG29">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH29">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AI29">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ29">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK29">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL29">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AM29">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="AN29">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AO29">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AP29">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AR29">
         <v>18.5</v>
       </c>
       <c r="AS29">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AT29">
+        <v>7</v>
+      </c>
+      <c r="AU29">
+        <v>6.8</v>
+      </c>
+      <c r="AV29">
+        <v>14</v>
+      </c>
+      <c r="AW29">
+        <v>22</v>
+      </c>
+      <c r="AX29">
+        <v>13</v>
+      </c>
+      <c r="AY29">
+        <v>12</v>
+      </c>
+      <c r="AZ29">
+        <v>21</v>
+      </c>
+      <c r="BA29">
+        <v>11.5</v>
+      </c>
+      <c r="BB29">
+        <v>34</v>
+      </c>
+      <c r="BC29">
+        <v>15</v>
+      </c>
+      <c r="BD29">
+        <v>11.5</v>
+      </c>
+      <c r="BE29">
+        <v>12</v>
+      </c>
+      <c r="BF29">
+        <v>10</v>
+      </c>
+      <c r="BG29">
+        <v>11</v>
+      </c>
+      <c r="BH29">
+        <v>2.66</v>
+      </c>
+      <c r="BI29">
+        <v>2.52</v>
+      </c>
+      <c r="BJ29">
+        <v>11.5</v>
+      </c>
+      <c r="BK29">
+        <v>7.2</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>16</v>
+      </c>
+      <c r="BN29">
+        <v>5.1</v>
+      </c>
+      <c r="BO29">
+        <v>4.6</v>
+      </c>
+      <c r="BP29">
+        <v>22</v>
+      </c>
+      <c r="BQ29">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU29">
-        <v>7.2</v>
-      </c>
-      <c r="AV29">
+      <c r="BR29">
+        <v>920</v>
+      </c>
+      <c r="BS29">
+        <v>12.5</v>
+      </c>
+      <c r="BT29">
+        <v>6.6</v>
+      </c>
+      <c r="BU29">
+        <v>5.8</v>
+      </c>
+      <c r="BV29">
+        <v>920</v>
+      </c>
+      <c r="BW29">
         <v>11.5</v>
       </c>
-      <c r="AW29">
-        <v>6.2</v>
-      </c>
-      <c r="AX29">
-        <v>14</v>
-      </c>
-      <c r="AY29">
-        <v>10.5</v>
-      </c>
-      <c r="AZ29">
-        <v>14.5</v>
-      </c>
-      <c r="BA29">
-        <v>6.4</v>
-      </c>
-      <c r="BB29">
-        <v>6.2</v>
-      </c>
-      <c r="BC29">
-        <v>5.9</v>
-      </c>
-      <c r="BD29">
-        <v>6.2</v>
-      </c>
-      <c r="BE29">
-        <v>6.8</v>
-      </c>
-      <c r="BF29">
-        <v>18</v>
-      </c>
-      <c r="BG29">
-        <v>6</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.15</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
-        <v>1.66</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>1.15</v>
-      </c>
-      <c r="BN29">
-        <v>1000</v>
-      </c>
-      <c r="BO29">
-        <v>1.38</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>1.15</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>1.15</v>
-      </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
-        <v>1.15</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>1.15</v>
-      </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.15</v>
+        <v>13.5</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.15</v>
+        <v>13</v>
       </c>
       <c r="CB29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
         <v>98</v>
@@ -7917,482 +7926,482 @@
         <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F30">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="G30">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="H30">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="J30">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K30">
         <v>3.65</v>
       </c>
       <c r="L30">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M30">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O30">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P30">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q30">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R30">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S30">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="T30">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="U30">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W30">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="X30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y30">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z30">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA30">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AC30">
+        <v>7.8</v>
+      </c>
+      <c r="AD30">
+        <v>14</v>
+      </c>
+      <c r="AE30">
+        <v>40</v>
+      </c>
+      <c r="AF30">
+        <v>17</v>
+      </c>
+      <c r="AG30">
+        <v>12</v>
+      </c>
+      <c r="AH30">
+        <v>18</v>
+      </c>
+      <c r="AI30">
+        <v>50</v>
+      </c>
+      <c r="AJ30">
+        <v>42</v>
+      </c>
+      <c r="AK30">
+        <v>29</v>
+      </c>
+      <c r="AL30">
+        <v>46</v>
+      </c>
+      <c r="AM30">
+        <v>110</v>
+      </c>
+      <c r="AN30">
+        <v>24</v>
+      </c>
+      <c r="AO30">
+        <v>36</v>
+      </c>
+      <c r="AP30">
+        <v>12.5</v>
+      </c>
+      <c r="AQ30">
+        <v>11</v>
+      </c>
+      <c r="AR30">
+        <v>17.5</v>
+      </c>
+      <c r="AS30">
+        <v>8.6</v>
+      </c>
+      <c r="AT30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU30">
+        <v>7.2</v>
+      </c>
+      <c r="AV30">
+        <v>11.5</v>
+      </c>
+      <c r="AW30">
         <v>8</v>
       </c>
-      <c r="AD30">
-        <v>16.5</v>
-      </c>
-      <c r="AE30">
-        <v>60</v>
-      </c>
-      <c r="AF30">
-        <v>13.5</v>
-      </c>
-      <c r="AG30">
-        <v>11</v>
-      </c>
-      <c r="AH30">
-        <v>19</v>
-      </c>
-      <c r="AI30">
-        <v>75</v>
-      </c>
-      <c r="AJ30">
-        <v>32</v>
-      </c>
-      <c r="AK30">
-        <v>25</v>
-      </c>
-      <c r="AL30">
-        <v>48</v>
-      </c>
-      <c r="AM30">
-        <v>130</v>
-      </c>
-      <c r="AN30">
-        <v>20</v>
-      </c>
-      <c r="AO30">
-        <v>70</v>
-      </c>
-      <c r="AP30">
-        <v>11</v>
-      </c>
-      <c r="AQ30">
-        <v>11.5</v>
-      </c>
-      <c r="AR30">
-        <v>8.4</v>
-      </c>
-      <c r="AS30">
-        <v>10</v>
-      </c>
-      <c r="AT30">
+      <c r="AX30">
+        <v>14</v>
+      </c>
+      <c r="AY30">
+        <v>10.5</v>
+      </c>
+      <c r="AZ30">
+        <v>15</v>
+      </c>
+      <c r="BA30">
+        <v>34</v>
+      </c>
+      <c r="BB30">
         <v>8</v>
-      </c>
-      <c r="AU30">
-        <v>7</v>
-      </c>
-      <c r="AV30">
-        <v>14</v>
-      </c>
-      <c r="AW30">
-        <v>9.6</v>
-      </c>
-      <c r="AX30">
-        <v>11.5</v>
-      </c>
-      <c r="AY30">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ30">
-        <v>16.5</v>
-      </c>
-      <c r="BA30">
-        <v>10</v>
-      </c>
-      <c r="BB30">
-        <v>8.199999999999999</v>
       </c>
       <c r="BC30">
         <v>21</v>
       </c>
       <c r="BD30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE30">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BE30">
-        <v>10</v>
       </c>
       <c r="BF30">
         <v>17</v>
       </c>
       <c r="BG30">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BH30">
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>2.34</v>
+        <v>1.15</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BN30">
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="CB30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F31">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G31">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H31">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="I31">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K31">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M31">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O31">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="P31">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="Q31">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="R31">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S31">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="T31">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="U31">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V31">
         <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB31">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="AC31">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF31">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="AG31">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN31">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP31">
-        <v>1.31</v>
+        <v>11</v>
       </c>
       <c r="AQ31">
-        <v>1.31</v>
+        <v>11.5</v>
       </c>
       <c r="AR31">
-        <v>1.31</v>
+        <v>20</v>
       </c>
       <c r="AS31">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="AT31">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU31">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV31">
-        <v>1.31</v>
+        <v>14</v>
       </c>
       <c r="AW31">
-        <v>1.31</v>
+        <v>9.4</v>
       </c>
       <c r="AX31">
-        <v>1.26</v>
+        <v>11.5</v>
       </c>
       <c r="AY31">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ31">
-        <v>1.31</v>
+        <v>16.5</v>
       </c>
       <c r="BA31">
-        <v>1.31</v>
+        <v>40</v>
       </c>
       <c r="BB31">
-        <v>1.31</v>
+        <v>20</v>
       </c>
       <c r="BC31">
-        <v>1.31</v>
+        <v>21</v>
       </c>
       <c r="BD31">
-        <v>1.31</v>
+        <v>30</v>
       </c>
       <c r="BE31">
-        <v>1.31</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF31">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BG31">
-        <v>1.31</v>
+        <v>9.6</v>
       </c>
       <c r="BH31">
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BN31">
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="BP31">
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.17</v>
+        <v>2.04</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="CB31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
@@ -8401,235 +8410,235 @@
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F32">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="G32">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="H32">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="I32">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="J32">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K32">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="L32">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="M32">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N32">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="O32">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="P32">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q32">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="R32">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S32">
-        <v>4.5</v>
+        <v>2.94</v>
       </c>
       <c r="T32">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="U32">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="V32">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="X32">
+        <v>21</v>
+      </c>
+      <c r="Y32">
+        <v>18.5</v>
+      </c>
+      <c r="Z32">
+        <v>34</v>
+      </c>
+      <c r="AA32">
+        <v>80</v>
+      </c>
+      <c r="AB32">
+        <v>11</v>
+      </c>
+      <c r="AC32">
+        <v>8.6</v>
+      </c>
+      <c r="AD32">
+        <v>18.5</v>
+      </c>
+      <c r="AE32">
+        <v>50</v>
+      </c>
+      <c r="AF32">
+        <v>17.5</v>
+      </c>
+      <c r="AG32">
+        <v>13.5</v>
+      </c>
+      <c r="AH32">
+        <v>21</v>
+      </c>
+      <c r="AI32">
+        <v>60</v>
+      </c>
+      <c r="AJ32">
+        <v>34</v>
+      </c>
+      <c r="AK32">
+        <v>27</v>
+      </c>
+      <c r="AL32">
+        <v>42</v>
+      </c>
+      <c r="AM32">
+        <v>100</v>
+      </c>
+      <c r="AN32">
+        <v>18</v>
+      </c>
+      <c r="AO32">
+        <v>46</v>
+      </c>
+      <c r="AP32">
+        <v>14.5</v>
+      </c>
+      <c r="AQ32">
+        <v>13</v>
+      </c>
+      <c r="AR32">
+        <v>19.5</v>
+      </c>
+      <c r="AS32">
+        <v>5.1</v>
+      </c>
+      <c r="AT32">
+        <v>9.4</v>
+      </c>
+      <c r="AU32">
+        <v>7.6</v>
+      </c>
+      <c r="AV32">
+        <v>13</v>
+      </c>
+      <c r="AW32">
+        <v>4.9</v>
+      </c>
+      <c r="AX32">
         <v>12</v>
       </c>
-      <c r="Y32">
-        <v>9</v>
-      </c>
-      <c r="Z32">
-        <v>18.5</v>
-      </c>
-      <c r="AA32">
-        <v>42</v>
-      </c>
-      <c r="AB32">
-        <v>12</v>
-      </c>
-      <c r="AC32">
-        <v>7.6</v>
-      </c>
-      <c r="AD32">
-        <v>13</v>
-      </c>
-      <c r="AE32">
-        <v>40</v>
-      </c>
-      <c r="AF32">
-        <v>24</v>
-      </c>
-      <c r="AG32">
-        <v>15</v>
-      </c>
-      <c r="AH32">
-        <v>24</v>
-      </c>
-      <c r="AI32">
-        <v>65</v>
-      </c>
-      <c r="AJ32">
-        <v>70</v>
-      </c>
-      <c r="AK32">
-        <v>50</v>
-      </c>
-      <c r="AL32">
-        <v>75</v>
-      </c>
-      <c r="AM32">
-        <v>170</v>
-      </c>
-      <c r="AN32">
-        <v>60</v>
-      </c>
-      <c r="AO32">
-        <v>40</v>
-      </c>
-      <c r="AP32">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ32">
-        <v>7.6</v>
-      </c>
-      <c r="AR32">
-        <v>13.5</v>
-      </c>
-      <c r="AS32">
-        <v>6</v>
-      </c>
-      <c r="AT32">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU32">
-        <v>6.4</v>
-      </c>
-      <c r="AV32">
-        <v>10.5</v>
-      </c>
-      <c r="AW32">
-        <v>6</v>
-      </c>
-      <c r="AX32">
-        <v>17</v>
-      </c>
       <c r="AY32">
+        <v>9.6</v>
+      </c>
+      <c r="AZ32">
+        <v>14.5</v>
+      </c>
+      <c r="BA32">
+        <v>5</v>
+      </c>
+      <c r="BB32">
+        <v>19.5</v>
+      </c>
+      <c r="BC32">
+        <v>16</v>
+      </c>
+      <c r="BD32">
+        <v>4.8</v>
+      </c>
+      <c r="BE32">
+        <v>5.2</v>
+      </c>
+      <c r="BF32">
         <v>12.5</v>
       </c>
-      <c r="AZ32">
-        <v>17.5</v>
-      </c>
-      <c r="BA32">
-        <v>6.2</v>
-      </c>
-      <c r="BB32">
-        <v>6.4</v>
-      </c>
-      <c r="BC32">
-        <v>6</v>
-      </c>
-      <c r="BD32">
-        <v>6.4</v>
-      </c>
-      <c r="BE32">
-        <v>6.4</v>
-      </c>
-      <c r="BF32">
-        <v>6.2</v>
-      </c>
       <c r="BG32">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BH32">
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="CB32" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8643,235 +8652,477 @@
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F33">
+        <v>3.1</v>
+      </c>
+      <c r="G33">
+        <v>3.3</v>
+      </c>
+      <c r="H33">
+        <v>2.52</v>
+      </c>
+      <c r="I33">
+        <v>2.68</v>
+      </c>
+      <c r="J33">
+        <v>3.2</v>
+      </c>
+      <c r="K33">
+        <v>3.3</v>
+      </c>
+      <c r="L33">
+        <v>1.46</v>
+      </c>
+      <c r="M33">
+        <v>1.1</v>
+      </c>
+      <c r="N33">
+        <v>2.98</v>
+      </c>
+      <c r="O33">
+        <v>1.45</v>
+      </c>
+      <c r="P33">
+        <v>1.66</v>
+      </c>
+      <c r="Q33">
+        <v>2.34</v>
+      </c>
+      <c r="R33">
+        <v>1.25</v>
+      </c>
+      <c r="S33">
+        <v>4.5</v>
+      </c>
+      <c r="T33">
+        <v>1.96</v>
+      </c>
+      <c r="U33">
+        <v>1.92</v>
+      </c>
+      <c r="V33">
+        <v>1.59</v>
+      </c>
+      <c r="W33">
+        <v>1.43</v>
+      </c>
+      <c r="X33">
+        <v>12</v>
+      </c>
+      <c r="Y33">
+        <v>9</v>
+      </c>
+      <c r="Z33">
+        <v>18.5</v>
+      </c>
+      <c r="AA33">
+        <v>46</v>
+      </c>
+      <c r="AB33">
+        <v>12</v>
+      </c>
+      <c r="AC33">
+        <v>7.6</v>
+      </c>
+      <c r="AD33">
+        <v>14.5</v>
+      </c>
+      <c r="AE33">
+        <v>40</v>
+      </c>
+      <c r="AF33">
+        <v>24</v>
+      </c>
+      <c r="AG33">
+        <v>17</v>
+      </c>
+      <c r="AH33">
+        <v>24</v>
+      </c>
+      <c r="AI33">
+        <v>65</v>
+      </c>
+      <c r="AJ33">
+        <v>70</v>
+      </c>
+      <c r="AK33">
+        <v>50</v>
+      </c>
+      <c r="AL33">
+        <v>75</v>
+      </c>
+      <c r="AM33">
+        <v>160</v>
+      </c>
+      <c r="AN33">
+        <v>60</v>
+      </c>
+      <c r="AO33">
+        <v>38</v>
+      </c>
+      <c r="AP33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ33">
+        <v>7.8</v>
+      </c>
+      <c r="AR33">
+        <v>13.5</v>
+      </c>
+      <c r="AS33">
+        <v>5.8</v>
+      </c>
+      <c r="AT33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU33">
+        <v>6.6</v>
+      </c>
+      <c r="AV33">
+        <v>10.5</v>
+      </c>
+      <c r="AW33">
+        <v>5.7</v>
+      </c>
+      <c r="AX33">
+        <v>17.5</v>
+      </c>
+      <c r="AY33">
+        <v>12.5</v>
+      </c>
+      <c r="AZ33">
+        <v>17.5</v>
+      </c>
+      <c r="BA33">
+        <v>6</v>
+      </c>
+      <c r="BB33">
+        <v>6</v>
+      </c>
+      <c r="BC33">
+        <v>34</v>
+      </c>
+      <c r="BD33">
+        <v>6</v>
+      </c>
+      <c r="BE33">
+        <v>5.7</v>
+      </c>
+      <c r="BF33">
+        <v>6</v>
+      </c>
+      <c r="BG33">
+        <v>5.6</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.04</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.49</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.49</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.49</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.49</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.49</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.49</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.49</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.49</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.49</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" t="s">
+        <v>148</v>
+      </c>
+      <c r="E34" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34">
         <v>1.84</v>
       </c>
-      <c r="G33">
+      <c r="G34">
         <v>1.88</v>
       </c>
-      <c r="H33">
+      <c r="H34">
         <v>5.5</v>
       </c>
-      <c r="I33">
+      <c r="I34">
         <v>5.9</v>
       </c>
-      <c r="J33">
+      <c r="J34">
         <v>3.4</v>
       </c>
-      <c r="K33">
-        <v>3.65</v>
-      </c>
-      <c r="L33">
+      <c r="K34">
+        <v>3.55</v>
+      </c>
+      <c r="L34">
         <v>1.53</v>
       </c>
-      <c r="M33">
+      <c r="M34">
         <v>1.11</v>
       </c>
-      <c r="N33">
-        <v>2.84</v>
-      </c>
-      <c r="O33">
-        <v>1.5</v>
-      </c>
-      <c r="P33">
-        <v>1.6</v>
-      </c>
-      <c r="Q33">
-        <v>2.42</v>
-      </c>
-      <c r="R33">
+      <c r="N34">
+        <v>2.8</v>
+      </c>
+      <c r="O34">
+        <v>1.51</v>
+      </c>
+      <c r="P34">
+        <v>1.61</v>
+      </c>
+      <c r="Q34">
+        <v>2.5</v>
+      </c>
+      <c r="R34">
         <v>1.22</v>
       </c>
-      <c r="S33">
+      <c r="S34">
         <v>4.7</v>
       </c>
-      <c r="T33">
-        <v>2.22</v>
-      </c>
-      <c r="U33">
-        <v>1.72</v>
-      </c>
-      <c r="V33">
+      <c r="T34">
+        <v>2.24</v>
+      </c>
+      <c r="U34">
+        <v>1.71</v>
+      </c>
+      <c r="V34">
         <v>1.21</v>
       </c>
-      <c r="W33">
+      <c r="W34">
         <v>2.12</v>
       </c>
-      <c r="X33">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y33">
-        <v>15</v>
-      </c>
-      <c r="Z33">
+      <c r="X34">
+        <v>9.6</v>
+      </c>
+      <c r="Y34">
+        <v>14.5</v>
+      </c>
+      <c r="Z34">
         <v>48</v>
       </c>
-      <c r="AA33">
+      <c r="AA34">
+        <v>230</v>
+      </c>
+      <c r="AB34">
+        <v>6.4</v>
+      </c>
+      <c r="AC34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD34">
+        <v>25</v>
+      </c>
+      <c r="AE34">
+        <v>140</v>
+      </c>
+      <c r="AF34">
+        <v>9.6</v>
+      </c>
+      <c r="AG34">
+        <v>11.5</v>
+      </c>
+      <c r="AH34">
+        <v>28</v>
+      </c>
+      <c r="AI34">
+        <v>150</v>
+      </c>
+      <c r="AJ34">
+        <v>22</v>
+      </c>
+      <c r="AK34">
+        <v>26</v>
+      </c>
+      <c r="AL34">
+        <v>65</v>
+      </c>
+      <c r="AM34">
+        <v>270</v>
+      </c>
+      <c r="AN34">
+        <v>19.5</v>
+      </c>
+      <c r="AO34">
         <v>240</v>
       </c>
-      <c r="AB33">
-        <v>6.6</v>
-      </c>
-      <c r="AC33">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD33">
-        <v>25</v>
-      </c>
-      <c r="AE33">
-        <v>140</v>
-      </c>
-      <c r="AF33">
+      <c r="AP34">
+        <v>8.6</v>
+      </c>
+      <c r="AQ34">
+        <v>12.5</v>
+      </c>
+      <c r="AR34">
         <v>9.6</v>
       </c>
-      <c r="AG33">
+      <c r="AS34">
+        <v>11</v>
+      </c>
+      <c r="AT34">
+        <v>5.7</v>
+      </c>
+      <c r="AU34">
+        <v>7.2</v>
+      </c>
+      <c r="AV34">
+        <v>21</v>
+      </c>
+      <c r="AW34">
+        <v>11</v>
+      </c>
+      <c r="AX34">
+        <v>8.6</v>
+      </c>
+      <c r="AY34">
+        <v>9.6</v>
+      </c>
+      <c r="AZ34">
+        <v>20</v>
+      </c>
+      <c r="BA34">
+        <v>11</v>
+      </c>
+      <c r="BB34">
+        <v>17.5</v>
+      </c>
+      <c r="BC34">
+        <v>21</v>
+      </c>
+      <c r="BD34">
+        <v>40</v>
+      </c>
+      <c r="BE34">
         <v>11.5</v>
       </c>
-      <c r="AH33">
-        <v>28</v>
-      </c>
-      <c r="AI33">
-        <v>150</v>
-      </c>
-      <c r="AJ33">
-        <v>21</v>
-      </c>
-      <c r="AK33">
-        <v>25</v>
-      </c>
-      <c r="AL33">
-        <v>60</v>
-      </c>
-      <c r="AM33">
-        <v>270</v>
-      </c>
-      <c r="AN33">
-        <v>19</v>
-      </c>
-      <c r="AO33">
-        <v>240</v>
-      </c>
-      <c r="AP33">
-        <v>8.6</v>
-      </c>
-      <c r="AQ33">
-        <v>12.5</v>
-      </c>
-      <c r="AR33">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS33">
-        <v>10.5</v>
-      </c>
-      <c r="AT33">
-        <v>5.7</v>
-      </c>
-      <c r="AU33">
-        <v>7.2</v>
-      </c>
-      <c r="AV33">
-        <v>21</v>
-      </c>
-      <c r="AW33">
-        <v>10.5</v>
-      </c>
-      <c r="AX33">
-        <v>8.4</v>
-      </c>
-      <c r="AY33">
-        <v>9.4</v>
-      </c>
-      <c r="AZ33">
-        <v>8</v>
-      </c>
-      <c r="BA33">
-        <v>10.5</v>
-      </c>
-      <c r="BB33">
-        <v>17.5</v>
-      </c>
-      <c r="BC33">
-        <v>21</v>
-      </c>
-      <c r="BD33">
-        <v>9.6</v>
-      </c>
-      <c r="BE33">
-        <v>10.5</v>
-      </c>
-      <c r="BF33">
-        <v>15.5</v>
-      </c>
-      <c r="BG33">
-        <v>10.5</v>
-      </c>
-      <c r="BH33">
-        <v>1000</v>
-      </c>
-      <c r="BI33">
-        <v>1.23</v>
-      </c>
-      <c r="BJ33">
-        <v>1000</v>
-      </c>
-      <c r="BK33">
-        <v>1.23</v>
-      </c>
-      <c r="BL33">
-        <v>1000</v>
-      </c>
-      <c r="BM33">
-        <v>1.23</v>
-      </c>
-      <c r="BN33">
-        <v>1000</v>
-      </c>
-      <c r="BO33">
-        <v>1.04</v>
-      </c>
-      <c r="BP33">
-        <v>1000</v>
-      </c>
-      <c r="BQ33">
-        <v>1.23</v>
-      </c>
-      <c r="BR33">
-        <v>1000</v>
-      </c>
-      <c r="BS33">
-        <v>1.23</v>
-      </c>
-      <c r="BT33">
-        <v>1000</v>
-      </c>
-      <c r="BU33">
-        <v>1.23</v>
-      </c>
-      <c r="BV33">
-        <v>1000</v>
-      </c>
-      <c r="BW33">
-        <v>1.23</v>
-      </c>
-      <c r="BX33">
-        <v>1000</v>
-      </c>
-      <c r="BY33">
-        <v>1.23</v>
-      </c>
-      <c r="BZ33">
-        <v>1000</v>
-      </c>
-      <c r="CA33">
-        <v>1.23</v>
-      </c>
-      <c r="CB33" t="s">
-        <v>179</v>
+      <c r="BF34">
+        <v>16.5</v>
+      </c>
+      <c r="BG34">
+        <v>11</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.21</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.04</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.04</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.04</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.04</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.04</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.04</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.04</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.04</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.04</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="186">
   <si>
     <t>League</t>
   </si>
@@ -346,6 +346,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -439,6 +442,9 @@
     <t>Helmond Sport</t>
   </si>
   <si>
+    <t>IRT Tanger</t>
+  </si>
+  <si>
     <t>Suriname</t>
   </si>
   <si>
@@ -538,6 +544,9 @@
     <t>Heracles</t>
   </si>
   <si>
+    <t>Moghreb Tetouan</t>
+  </si>
+  <si>
     <t>Guatemala</t>
   </si>
   <si>
@@ -562,7 +571,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 08:08:20</t>
+    <t>2026-10-01 10:21:32</t>
   </si>
 </sst>
 </file>
@@ -894,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB34"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1150,28 +1159,28 @@
         <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G2">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1180,34 +1189,34 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
         <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
         <v>1.87</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="X2">
         <v>14</v>
@@ -1234,7 +1243,7 @@
         <v>110</v>
       </c>
       <c r="AF2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1246,10 +1255,10 @@
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL2">
         <v>48</v>
@@ -1258,7 +1267,7 @@
         <v>190</v>
       </c>
       <c r="AN2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO2">
         <v>150</v>
@@ -1270,10 +1279,10 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
@@ -1285,7 +1294,7 @@
         <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AX2">
         <v>8.199999999999999</v>
@@ -1297,7 +1306,7 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
@@ -1306,16 +1315,16 @@
         <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG2">
         <v>10</v>
-      </c>
-      <c r="BG2">
-        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
@@ -1333,13 +1342,13 @@
         <v>190</v>
       </c>
       <c r="BM2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP2">
         <v>12</v>
@@ -1351,7 +1360,7 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
         <v>10</v>
@@ -1360,25 +1369,25 @@
         <v>7.8</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>70</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>27</v>
       </c>
       <c r="CA2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1392,25 +1401,25 @@
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F3">
         <v>3.5</v>
       </c>
       <c r="G3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I3">
         <v>2.14</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
         <v>4.2</v>
@@ -1422,31 +1431,31 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R3">
         <v>1.56</v>
       </c>
       <c r="S3">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T3">
         <v>1.6</v>
       </c>
       <c r="U3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V3">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W3">
         <v>1.37</v>
@@ -1467,7 +1476,7 @@
         <v>18.5</v>
       </c>
       <c r="AC3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3">
         <v>10.5</v>
@@ -1476,10 +1485,10 @@
         <v>19</v>
       </c>
       <c r="AF3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>15.5</v>
@@ -1491,19 +1500,19 @@
         <v>75</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AL3">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AN3">
         <v>32</v>
       </c>
       <c r="AO3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP3">
         <v>18</v>
@@ -1515,7 +1524,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AT3">
         <v>15.5</v>
@@ -1530,7 +1539,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AY3">
         <v>13.5</v>
@@ -1539,28 +1548,28 @@
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BB3">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BC3">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BD3">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BF3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG3">
         <v>10.5</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
         <v>3.35</v>
@@ -1569,31 +1578,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
         <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP3">
         <v>25</v>
       </c>
       <c r="BQ3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3">
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>5.3</v>
@@ -1605,22 +1614,22 @@
         <v>14</v>
       </c>
       <c r="BW3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
         <v>24</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
         <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1634,16 +1643,16 @@
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>34</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H4">
         <v>1.1</v>
@@ -1658,7 +1667,7 @@
         <v>15</v>
       </c>
       <c r="L4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M4">
         <v>1.02</v>
@@ -1673,7 +1682,7 @@
         <v>3.2</v>
       </c>
       <c r="Q4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R4">
         <v>1.9</v>
@@ -1682,13 +1691,13 @@
         <v>2.04</v>
       </c>
       <c r="T4">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="U4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W4">
         <v>1.02</v>
@@ -1700,10 +1709,10 @@
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AB4">
         <v>120</v>
@@ -1745,25 +1754,25 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>10</v>
       </c>
       <c r="AR4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS4">
         <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AU4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
@@ -1772,97 +1781,97 @@
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AY4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC4">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BD4">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BE4">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BF4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BG4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BH4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BI4">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4">
         <v>21</v>
       </c>
       <c r="BK4">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>34</v>
       </c>
       <c r="BO4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BU4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BV4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BW4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BX4">
         <v>29</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CA4">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="CB4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1876,28 +1885,28 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3.05</v>
+      </c>
+      <c r="H5">
+        <v>2.8</v>
+      </c>
+      <c r="I5">
         <v>2.94</v>
       </c>
-      <c r="G5">
-        <v>3.1</v>
-      </c>
-      <c r="H5">
-        <v>2.86</v>
-      </c>
-      <c r="I5">
-        <v>2.98</v>
-      </c>
       <c r="J5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
         <v>1.44</v>
@@ -1906,16 +1915,16 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
         <v>1.33</v>
@@ -1924,13 +1933,13 @@
         <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U5">
         <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
         <v>1.47</v>
@@ -1939,13 +1948,13 @@
         <v>12</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB5">
         <v>12.5</v>
@@ -1957,13 +1966,13 @@
         <v>13</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG5">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH5">
         <v>16.5</v>
@@ -1972,22 +1981,22 @@
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL5">
         <v>55</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1996,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="AR5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS5">
         <v>36</v>
@@ -2008,40 +2017,40 @@
         <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW5">
         <v>27</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BB5">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BC5">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BD5">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BG5">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BH5">
         <v>3.65</v>
@@ -2053,58 +2062,58 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BN5">
         <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP5">
         <v>26</v>
       </c>
       <c r="BQ5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BR5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BT5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW5">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2118,19 +2127,19 @@
         <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F6">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I6">
         <v>6.4</v>
@@ -2151,7 +2160,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P6">
         <v>3.4</v>
@@ -2169,19 +2178,19 @@
         <v>1.55</v>
       </c>
       <c r="U6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V6">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W6">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X6">
         <v>38</v>
       </c>
       <c r="Y6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z6">
         <v>65</v>
@@ -2190,7 +2199,7 @@
         <v>190</v>
       </c>
       <c r="AB6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC6">
         <v>13.5</v>
@@ -2205,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
         <v>17</v>
@@ -2229,7 +2238,7 @@
         <v>4.6</v>
       </c>
       <c r="AO6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP6">
         <v>32</v>
@@ -2259,10 +2268,10 @@
         <v>12.5</v>
       </c>
       <c r="AY6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
         <v>44</v>
@@ -2277,10 +2286,10 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG6">
         <v>36</v>
@@ -2301,7 +2310,7 @@
         <v>65</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
@@ -2319,7 +2328,7 @@
         <v>17</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT6">
         <v>10</v>
@@ -2331,22 +2340,22 @@
         <v>38</v>
       </c>
       <c r="BW6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CA6">
         <v>7.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2360,13 +2369,13 @@
         <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G7">
         <v>7.6</v>
@@ -2375,31 +2384,31 @@
         <v>1.54</v>
       </c>
       <c r="I7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
         <v>1.37</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
         <v>4.3</v>
       </c>
       <c r="O7">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R7">
         <v>1.44</v>
@@ -2408,25 +2417,25 @@
         <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U7">
         <v>1.95</v>
       </c>
       <c r="V7">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W7">
         <v>1.15</v>
       </c>
       <c r="X7">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Y7">
         <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA7">
         <v>14</v>
@@ -2441,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="AE7">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AF7">
         <v>65</v>
@@ -2501,94 +2510,94 @@
         <v>38</v>
       </c>
       <c r="AY7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ7">
         <v>7.4</v>
       </c>
       <c r="BA7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
+        <v>10.5</v>
+      </c>
+      <c r="BC7">
         <v>10</v>
       </c>
-      <c r="BC7">
-        <v>9.6</v>
-      </c>
       <c r="BD7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="BF7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
         <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BN7">
         <v>11</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BT7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BU7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BV7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2602,19 +2611,19 @@
         <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F8">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="G8">
         <v>3.3</v>
       </c>
       <c r="H8">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I8">
         <v>2.86</v>
@@ -2623,7 +2632,7 @@
         <v>3.15</v>
       </c>
       <c r="K8">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2632,7 +2641,7 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
         <v>1.28</v>
@@ -2641,7 +2650,7 @@
         <v>1.9</v>
       </c>
       <c r="Q8">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R8">
         <v>1.32</v>
@@ -2650,7 +2659,7 @@
         <v>2.86</v>
       </c>
       <c r="T8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U8">
         <v>2.04</v>
@@ -2830,7 +2839,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2844,28 +2853,28 @@
         <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F9">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G9">
         <v>1.96</v>
       </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
         <v>3.1</v>
       </c>
       <c r="K9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2874,19 +2883,19 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q9">
         <v>2.04</v>
       </c>
       <c r="R9">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
         <v>2.96</v>
@@ -2958,52 +2967,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3021,58 +3030,58 @@
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3086,16 +3095,16 @@
         <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F10">
         <v>2.46</v>
       </c>
       <c r="G10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H10">
         <v>2.16</v>
@@ -3116,7 +3125,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O10">
         <v>1.02</v>
@@ -3131,7 +3140,7 @@
         <v>1.39</v>
       </c>
       <c r="S10">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3143,7 +3152,7 @@
         <v>1.52</v>
       </c>
       <c r="W10">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3314,7 +3323,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3328,19 +3337,19 @@
         <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F11">
         <v>1.64</v>
       </c>
       <c r="G11">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -3355,19 +3364,19 @@
         <v>1.28</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P11">
         <v>1.65</v>
       </c>
       <c r="Q11">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R11">
         <v>1.26</v>
@@ -3376,22 +3385,22 @@
         <v>2.68</v>
       </c>
       <c r="T11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
         <v>1.17</v>
       </c>
       <c r="W11">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X11">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z11">
         <v>50</v>
@@ -3403,7 +3412,7 @@
         <v>8.4</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>25</v>
@@ -3418,13 +3427,13 @@
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI11">
         <v>95</v>
       </c>
       <c r="AJ11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK11">
         <v>23</v>
@@ -3442,64 +3451,64 @@
         <v>120</v>
       </c>
       <c r="AP11">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="AR11">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS11">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT11">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="AU11">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="AW11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY11">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB11">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BC11">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="BD11">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE11">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF11">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BG11">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
@@ -3556,7 +3565,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3570,10 +3579,10 @@
         <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F12">
         <v>2.4</v>
@@ -3585,7 +3594,7 @@
         <v>2.16</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J12">
         <v>3.25</v>
@@ -3600,10 +3609,10 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P12">
         <v>2.16</v>
@@ -3615,7 +3624,7 @@
         <v>1.42</v>
       </c>
       <c r="S12">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3624,7 +3633,7 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
         <v>1.42</v>
@@ -3798,7 +3807,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3812,16 +3821,16 @@
         <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H13">
         <v>3.1</v>
@@ -3869,7 +3878,7 @@
         <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X13">
         <v>50</v>
@@ -4007,7 +4016,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ13">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BR13">
         <v>20</v>
@@ -4040,7 +4049,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4054,10 +4063,10 @@
         <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F14">
         <v>2.14</v>
@@ -4087,7 +4096,7 @@
         <v>3.4</v>
       </c>
       <c r="O14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P14">
         <v>1.98</v>
@@ -4282,7 +4291,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4296,10 +4305,10 @@
         <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F15">
         <v>2.86</v>
@@ -4329,7 +4338,7 @@
         <v>3.25</v>
       </c>
       <c r="O15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
         <v>2.04</v>
@@ -4524,7 +4533,7 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4538,28 +4547,28 @@
         <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F16">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G16">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I16">
         <v>8.6</v>
       </c>
       <c r="J16">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="L16">
         <v>1.24</v>
@@ -4568,7 +4577,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="O16">
         <v>1.17</v>
@@ -4577,7 +4586,7 @@
         <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="R16">
         <v>1.65</v>
@@ -4592,28 +4601,28 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W16">
         <v>2.92</v>
       </c>
       <c r="X16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z16">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA16">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB16">
         <v>13.5</v>
       </c>
       <c r="AC16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD16">
         <v>32</v>
@@ -4622,13 +4631,13 @@
         <v>100</v>
       </c>
       <c r="AF16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG16">
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI16">
         <v>85</v>
@@ -4643,49 +4652,49 @@
         <v>32</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN16">
         <v>6.2</v>
       </c>
       <c r="AO16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP16">
         <v>21</v>
       </c>
       <c r="AQ16">
+        <v>4.6</v>
+      </c>
+      <c r="AR16">
         <v>4.9</v>
       </c>
-      <c r="AR16">
-        <v>5.2</v>
-      </c>
       <c r="AS16">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AT16">
         <v>9</v>
       </c>
       <c r="AU16">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW16">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AX16">
         <v>8.4</v>
       </c>
       <c r="AY16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA16">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB16">
         <v>10.5</v>
@@ -4697,13 +4706,13 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BF16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG16">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BH16">
         <v>4.7</v>
@@ -4766,7 +4775,7 @@
         <v>5.9</v>
       </c>
       <c r="CB16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4780,10 +4789,10 @@
         <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F17">
         <v>2.82</v>
@@ -4795,7 +4804,7 @@
         <v>3.2</v>
       </c>
       <c r="I17">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J17">
         <v>2.78</v>
@@ -4825,7 +4834,7 @@
         <v>1.18</v>
       </c>
       <c r="S17">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="T17">
         <v>2.16</v>
@@ -4834,7 +4843,7 @@
         <v>1.71</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W17">
         <v>1.5</v>
@@ -4858,7 +4867,7 @@
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE17">
         <v>65</v>
@@ -4867,7 +4876,7 @@
         <v>19.5</v>
       </c>
       <c r="AG17">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH17">
         <v>29</v>
@@ -4894,58 +4903,58 @@
         <v>90</v>
       </c>
       <c r="AP17">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AQ17">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AR17">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS17">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AT17">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU17">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AV17">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AW17">
+        <v>6</v>
+      </c>
+      <c r="AX17">
+        <v>4.9</v>
+      </c>
+      <c r="AY17">
+        <v>4.7</v>
+      </c>
+      <c r="AZ17">
+        <v>5.4</v>
+      </c>
+      <c r="BA17">
+        <v>6.2</v>
+      </c>
+      <c r="BB17">
+        <v>5.9</v>
+      </c>
+      <c r="BC17">
+        <v>5.9</v>
+      </c>
+      <c r="BD17">
+        <v>6.2</v>
+      </c>
+      <c r="BE17">
         <v>6.4</v>
       </c>
-      <c r="AX17">
-        <v>5.3</v>
-      </c>
-      <c r="AY17">
-        <v>4.8</v>
-      </c>
-      <c r="AZ17">
-        <v>5.8</v>
-      </c>
-      <c r="BA17">
-        <v>6.8</v>
-      </c>
-      <c r="BB17">
-        <v>6.4</v>
-      </c>
-      <c r="BC17">
-        <v>6.4</v>
-      </c>
-      <c r="BD17">
-        <v>6.6</v>
-      </c>
-      <c r="BE17">
-        <v>7</v>
-      </c>
       <c r="BF17">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG17">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5008,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5022,10 +5031,10 @@
         <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F18">
         <v>2.86</v>
@@ -5055,7 +5064,7 @@
         <v>2.88</v>
       </c>
       <c r="O18">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P18">
         <v>1.6</v>
@@ -5079,7 +5088,7 @@
         <v>1.51</v>
       </c>
       <c r="W18">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X18">
         <v>9.6</v>
@@ -5148,7 +5157,7 @@
         <v>23</v>
       </c>
       <c r="AT18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU18">
         <v>6.6</v>
@@ -5160,7 +5169,7 @@
         <v>10.5</v>
       </c>
       <c r="AX18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY18">
         <v>12.5</v>
@@ -5250,7 +5259,7 @@
         <v>2.94</v>
       </c>
       <c r="CB18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5264,13 +5273,13 @@
         <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G19">
         <v>1.81</v>
@@ -5279,7 +5288,7 @@
         <v>4.6</v>
       </c>
       <c r="I19">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19">
         <v>4.2</v>
@@ -5312,7 +5321,7 @@
         <v>2.42</v>
       </c>
       <c r="T19">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="U19">
         <v>2.28</v>
@@ -5390,7 +5399,7 @@
         <v>1.37</v>
       </c>
       <c r="AT19">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="AU19">
         <v>1.27</v>
@@ -5405,7 +5414,7 @@
         <v>1.31</v>
       </c>
       <c r="AY19">
-        <v>1.28</v>
+        <v>7.4</v>
       </c>
       <c r="AZ19">
         <v>1.37</v>
@@ -5492,7 +5501,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5506,13 +5515,13 @@
         <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F20">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="G20">
         <v>3.4</v>
@@ -5521,13 +5530,13 @@
         <v>2.16</v>
       </c>
       <c r="I20">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="J20">
         <v>3.9</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="L20">
         <v>1.31</v>
@@ -5551,7 +5560,7 @@
         <v>1.48</v>
       </c>
       <c r="S20">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T20">
         <v>1.55</v>
@@ -5560,10 +5569,10 @@
         <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5734,7 +5743,7 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5748,28 +5757,28 @@
         <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F21">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H21">
         <v>1.88</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="J21">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -5802,10 +5811,10 @@
         <v>2.06</v>
       </c>
       <c r="V21">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5976,7 +5985,7 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5990,10 +5999,10 @@
         <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F22">
         <v>1.89</v>
@@ -6008,7 +6017,7 @@
         <v>4.4</v>
       </c>
       <c r="J22">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
         <v>4.2</v>
@@ -6020,7 +6029,7 @@
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
         <v>1.26</v>
@@ -6077,7 +6086,7 @@
         <v>1000</v>
       </c>
       <c r="AG22">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH22">
         <v>1000</v>
@@ -6104,58 +6113,58 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AR22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AS22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT22">
-        <v>1.13</v>
+        <v>7.2</v>
       </c>
       <c r="AU22">
         <v>1.12</v>
       </c>
       <c r="AV22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AW22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AX22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AY22">
         <v>1.14</v>
       </c>
       <c r="AZ22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BA22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BB22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BC22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BD22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BE22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BF22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6218,7 +6227,7 @@
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6232,10 +6241,10 @@
         <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F23">
         <v>3.25</v>
@@ -6253,7 +6262,7 @@
         <v>3.85</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>1.27</v>
@@ -6268,7 +6277,7 @@
         <v>1.2</v>
       </c>
       <c r="P23">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q23">
         <v>1.59</v>
@@ -6286,7 +6295,7 @@
         <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W23">
         <v>1.35</v>
@@ -6322,7 +6331,7 @@
         <v>17.5</v>
       </c>
       <c r="AH23">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI23">
         <v>34</v>
@@ -6373,7 +6382,7 @@
         <v>21</v>
       </c>
       <c r="AY23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ23">
         <v>13</v>
@@ -6382,22 +6391,22 @@
         <v>21</v>
       </c>
       <c r="BB23">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD23">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE23">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF23">
         <v>18.5</v>
       </c>
       <c r="BG23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6460,7 +6469,7 @@
         <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6474,46 +6483,46 @@
         <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F24">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G24">
         <v>3.9</v>
       </c>
       <c r="H24">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I24">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J24">
+        <v>3.85</v>
+      </c>
+      <c r="K24">
         <v>4</v>
-      </c>
-      <c r="K24">
-        <v>4.3</v>
       </c>
       <c r="L24">
         <v>1.31</v>
       </c>
       <c r="M24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
         <v>5.3</v>
       </c>
       <c r="O24">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P24">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R24">
         <v>1.59</v>
@@ -6528,22 +6537,22 @@
         <v>2.48</v>
       </c>
       <c r="V24">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W24">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y24">
         <v>14</v>
       </c>
       <c r="Z24">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA24">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AB24">
         <v>21</v>
@@ -6558,13 +6567,13 @@
         <v>23</v>
       </c>
       <c r="AF24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG24">
         <v>17</v>
       </c>
       <c r="AH24">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI24">
         <v>34</v>
@@ -6582,13 +6591,13 @@
         <v>75</v>
       </c>
       <c r="AN24">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO24">
         <v>10</v>
       </c>
       <c r="AP24">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24">
         <v>11.5</v>
@@ -6600,10 +6609,10 @@
         <v>20</v>
       </c>
       <c r="AT24">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU24">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV24">
         <v>9.800000000000001</v>
@@ -6612,7 +6621,7 @@
         <v>16</v>
       </c>
       <c r="AX24">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AY24">
         <v>13.5</v>
@@ -6624,22 +6633,22 @@
         <v>20</v>
       </c>
       <c r="BB24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC24">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD24">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG24">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6657,7 +6666,7 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="BN24">
         <v>1000</v>
@@ -6669,13 +6678,13 @@
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="BT24">
         <v>1000</v>
@@ -6687,22 +6696,22 @@
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="CB24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6716,28 +6725,28 @@
         <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F25">
         <v>2.78</v>
       </c>
       <c r="G25">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I25">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="J25">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K25">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6752,7 +6761,7 @@
         <v>1.19</v>
       </c>
       <c r="P25">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q25">
         <v>1.56</v>
@@ -6761,7 +6770,7 @@
         <v>1.53</v>
       </c>
       <c r="S25">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T25">
         <v>1.51</v>
@@ -6770,10 +6779,10 @@
         <v>2.42</v>
       </c>
       <c r="V25">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X25">
         <v>25</v>
@@ -6824,7 +6833,7 @@
         <v>70</v>
       </c>
       <c r="AN25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO25">
         <v>15.5</v>
@@ -6839,7 +6848,7 @@
         <v>4.3</v>
       </c>
       <c r="AS25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT25">
         <v>4.2</v>
@@ -6860,22 +6869,22 @@
         <v>4</v>
       </c>
       <c r="AZ25">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BA25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB25">
         <v>5</v>
       </c>
       <c r="BC25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE25">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF25">
         <v>4.5</v>
@@ -6944,7 +6953,7 @@
         <v>1.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6958,10 +6967,10 @@
         <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F26">
         <v>7</v>
@@ -6991,19 +7000,19 @@
         <v>6.2</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P26">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q26">
         <v>1.46</v>
       </c>
       <c r="R26">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S26">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T26">
         <v>1.68</v>
@@ -7030,7 +7039,7 @@
         <v>14.5</v>
       </c>
       <c r="AB26">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AC26">
         <v>13.5</v>
@@ -7063,16 +7072,16 @@
         <v>80</v>
       </c>
       <c r="AM26">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN26">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO26">
         <v>5.4</v>
       </c>
       <c r="AP26">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ26">
         <v>11</v>
@@ -7084,7 +7093,7 @@
         <v>11.5</v>
       </c>
       <c r="AT26">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU26">
         <v>11</v>
@@ -7096,7 +7105,7 @@
         <v>12</v>
       </c>
       <c r="AX26">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY26">
         <v>21</v>
@@ -7105,19 +7114,19 @@
         <v>17.5</v>
       </c>
       <c r="BA26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC26">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD26">
         <v>22</v>
       </c>
       <c r="BE26">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BF26">
         <v>6.8</v>
@@ -7186,12 +7195,12 @@
         <v>1.04</v>
       </c>
       <c r="CB26" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
         <v>98</v>
@@ -7200,178 +7209,178 @@
         <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F27">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="G27">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="H27">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="I27">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="K27">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>3.65</v>
+        <v>2.14</v>
       </c>
       <c r="O27">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="P27">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="Q27">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="R27">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="T27">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="W27">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="X27">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
@@ -7428,254 +7437,254 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
         <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F28">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="G28">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="H28">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="I28">
-        <v>2.18</v>
+        <v>3.65</v>
       </c>
       <c r="J28">
+        <v>3.45</v>
+      </c>
+      <c r="K28">
+        <v>3.75</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.06</v>
+      </c>
+      <c r="N28">
+        <v>3.65</v>
+      </c>
+      <c r="O28">
+        <v>1.31</v>
+      </c>
+      <c r="P28">
+        <v>1.92</v>
+      </c>
+      <c r="Q28">
+        <v>1.86</v>
+      </c>
+      <c r="R28">
+        <v>1.32</v>
+      </c>
+      <c r="S28">
         <v>3.25</v>
       </c>
-      <c r="K28">
-        <v>4.4</v>
-      </c>
-      <c r="L28">
-        <v>1.01</v>
-      </c>
-      <c r="M28">
-        <v>1.04</v>
-      </c>
-      <c r="N28">
-        <v>3.1</v>
-      </c>
-      <c r="O28">
-        <v>1.4</v>
-      </c>
-      <c r="P28">
-        <v>1.7</v>
-      </c>
-      <c r="Q28">
-        <v>2.12</v>
-      </c>
-      <c r="R28">
-        <v>1.2</v>
-      </c>
-      <c r="S28">
-        <v>2.92</v>
-      </c>
       <c r="T28">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="U28">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="V28">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
@@ -7684,240 +7693,240 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F29">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="G29">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="H29">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="I29">
-        <v>3.55</v>
+        <v>2.16</v>
       </c>
       <c r="J29">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K29">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="L29">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
+        <v>1.04</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29">
+        <v>1.38</v>
+      </c>
+      <c r="P29">
+        <v>1.66</v>
+      </c>
+      <c r="Q29">
+        <v>2.16</v>
+      </c>
+      <c r="R29">
+        <v>1.21</v>
+      </c>
+      <c r="S29">
+        <v>3.2</v>
+      </c>
+      <c r="T29">
         <v>1.12</v>
       </c>
-      <c r="N29">
-        <v>2.6</v>
-      </c>
-      <c r="O29">
-        <v>1.57</v>
-      </c>
-      <c r="P29">
-        <v>1.56</v>
-      </c>
-      <c r="Q29">
-        <v>2.68</v>
-      </c>
-      <c r="R29">
-        <v>1.2</v>
-      </c>
-      <c r="S29">
-        <v>5.3</v>
-      </c>
-      <c r="T29">
-        <v>2.16</v>
-      </c>
       <c r="U29">
-        <v>1.78</v>
+        <v>1.12</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.86</v>
       </c>
       <c r="W29">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="X29">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR29">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU29">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV29">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW29">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA29">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF29">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
-        <v>920</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
-        <v>920</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s">
         <v>98</v>
@@ -7926,240 +7935,240 @@
         <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F30">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G30">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I30">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="J30">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K30">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="L30">
+        <v>1.6</v>
+      </c>
+      <c r="M30">
+        <v>1.12</v>
+      </c>
+      <c r="N30">
+        <v>2.64</v>
+      </c>
+      <c r="O30">
+        <v>1.58</v>
+      </c>
+      <c r="P30">
+        <v>1.56</v>
+      </c>
+      <c r="Q30">
+        <v>2.7</v>
+      </c>
+      <c r="R30">
+        <v>1.2</v>
+      </c>
+      <c r="S30">
+        <v>5.5</v>
+      </c>
+      <c r="T30">
+        <v>2.2</v>
+      </c>
+      <c r="U30">
+        <v>1.78</v>
+      </c>
+      <c r="V30">
         <v>1.39</v>
       </c>
-      <c r="M30">
-        <v>1.07</v>
-      </c>
-      <c r="N30">
-        <v>3.75</v>
-      </c>
-      <c r="O30">
-        <v>1.33</v>
-      </c>
-      <c r="P30">
-        <v>1.95</v>
-      </c>
-      <c r="Q30">
-        <v>1.96</v>
-      </c>
-      <c r="R30">
-        <v>1.37</v>
-      </c>
-      <c r="S30">
-        <v>3.5</v>
-      </c>
-      <c r="T30">
-        <v>1.76</v>
-      </c>
-      <c r="U30">
-        <v>2.18</v>
-      </c>
-      <c r="V30">
-        <v>1.46</v>
-      </c>
       <c r="W30">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X30">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="Y30">
+        <v>9.4</v>
+      </c>
+      <c r="Z30">
+        <v>22</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>7.6</v>
+      </c>
+      <c r="AC30">
+        <v>7.4</v>
+      </c>
+      <c r="AD30">
+        <v>15.5</v>
+      </c>
+      <c r="AE30">
+        <v>55</v>
+      </c>
+      <c r="AF30">
+        <v>14.5</v>
+      </c>
+      <c r="AG30">
+        <v>13.5</v>
+      </c>
+      <c r="AH30">
+        <v>24</v>
+      </c>
+      <c r="AI30">
+        <v>80</v>
+      </c>
+      <c r="AJ30">
+        <v>46</v>
+      </c>
+      <c r="AK30">
+        <v>40</v>
+      </c>
+      <c r="AL30">
+        <v>70</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>42</v>
+      </c>
+      <c r="AO30">
+        <v>80</v>
+      </c>
+      <c r="AP30">
+        <v>7.8</v>
+      </c>
+      <c r="AQ30">
+        <v>8.4</v>
+      </c>
+      <c r="AR30">
+        <v>18.5</v>
+      </c>
+      <c r="AS30">
+        <v>42</v>
+      </c>
+      <c r="AT30">
+        <v>7</v>
+      </c>
+      <c r="AU30">
+        <v>6.8</v>
+      </c>
+      <c r="AV30">
+        <v>14.5</v>
+      </c>
+      <c r="AW30">
+        <v>32</v>
+      </c>
+      <c r="AX30">
+        <v>13</v>
+      </c>
+      <c r="AY30">
+        <v>12</v>
+      </c>
+      <c r="AZ30">
+        <v>21</v>
+      </c>
+      <c r="BA30">
+        <v>48</v>
+      </c>
+      <c r="BB30">
+        <v>34</v>
+      </c>
+      <c r="BC30">
+        <v>24</v>
+      </c>
+      <c r="BD30">
+        <v>44</v>
+      </c>
+      <c r="BE30">
+        <v>55</v>
+      </c>
+      <c r="BF30">
+        <v>23</v>
+      </c>
+      <c r="BG30">
+        <v>32</v>
+      </c>
+      <c r="BH30">
+        <v>2.66</v>
+      </c>
+      <c r="BI30">
+        <v>2.52</v>
+      </c>
+      <c r="BJ30">
+        <v>11.5</v>
+      </c>
+      <c r="BK30">
+        <v>7.2</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>16</v>
+      </c>
+      <c r="BN30">
+        <v>5.1</v>
+      </c>
+      <c r="BO30">
+        <v>4.6</v>
+      </c>
+      <c r="BP30">
+        <v>22</v>
+      </c>
+      <c r="BQ30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR30">
+        <v>840</v>
+      </c>
+      <c r="BS30">
         <v>12.5</v>
       </c>
-      <c r="Z30">
-        <v>25</v>
-      </c>
-      <c r="AA30">
-        <v>60</v>
-      </c>
-      <c r="AB30">
+      <c r="BT30">
+        <v>6.6</v>
+      </c>
+      <c r="BU30">
+        <v>5.8</v>
+      </c>
+      <c r="BV30">
+        <v>840</v>
+      </c>
+      <c r="BW30">
         <v>11.5</v>
       </c>
-      <c r="AC30">
-        <v>7.8</v>
-      </c>
-      <c r="AD30">
-        <v>14</v>
-      </c>
-      <c r="AE30">
-        <v>40</v>
-      </c>
-      <c r="AF30">
-        <v>17</v>
-      </c>
-      <c r="AG30">
-        <v>12</v>
-      </c>
-      <c r="AH30">
-        <v>18</v>
-      </c>
-      <c r="AI30">
-        <v>50</v>
-      </c>
-      <c r="AJ30">
-        <v>42</v>
-      </c>
-      <c r="AK30">
-        <v>29</v>
-      </c>
-      <c r="AL30">
-        <v>46</v>
-      </c>
-      <c r="AM30">
-        <v>110</v>
-      </c>
-      <c r="AN30">
-        <v>24</v>
-      </c>
-      <c r="AO30">
-        <v>36</v>
-      </c>
-      <c r="AP30">
-        <v>12.5</v>
-      </c>
-      <c r="AQ30">
-        <v>11</v>
-      </c>
-      <c r="AR30">
-        <v>17.5</v>
-      </c>
-      <c r="AS30">
-        <v>8.6</v>
-      </c>
-      <c r="AT30">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU30">
-        <v>7.2</v>
-      </c>
-      <c r="AV30">
-        <v>11.5</v>
-      </c>
-      <c r="AW30">
-        <v>8</v>
-      </c>
-      <c r="AX30">
-        <v>14</v>
-      </c>
-      <c r="AY30">
-        <v>10.5</v>
-      </c>
-      <c r="AZ30">
-        <v>15</v>
-      </c>
-      <c r="BA30">
-        <v>34</v>
-      </c>
-      <c r="BB30">
-        <v>8</v>
-      </c>
-      <c r="BC30">
-        <v>21</v>
-      </c>
-      <c r="BD30">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE30">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF30">
-        <v>17</v>
-      </c>
-      <c r="BG30">
-        <v>7.8</v>
-      </c>
-      <c r="BH30">
-        <v>1000</v>
-      </c>
-      <c r="BI30">
-        <v>1.15</v>
-      </c>
-      <c r="BJ30">
-        <v>1000</v>
-      </c>
-      <c r="BK30">
-        <v>1.15</v>
-      </c>
-      <c r="BL30">
-        <v>1000</v>
-      </c>
-      <c r="BM30">
-        <v>1.15</v>
-      </c>
-      <c r="BN30">
-        <v>1000</v>
-      </c>
-      <c r="BO30">
-        <v>1.38</v>
-      </c>
-      <c r="BP30">
-        <v>1000</v>
-      </c>
-      <c r="BQ30">
-        <v>1.15</v>
-      </c>
-      <c r="BR30">
-        <v>1000</v>
-      </c>
-      <c r="BS30">
-        <v>1.15</v>
-      </c>
-      <c r="BT30">
-        <v>1000</v>
-      </c>
-      <c r="BU30">
-        <v>1.67</v>
-      </c>
-      <c r="BV30">
-        <v>1000</v>
-      </c>
-      <c r="BW30">
-        <v>1.15</v>
-      </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.15</v>
+        <v>13.5</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.15</v>
+        <v>13</v>
       </c>
       <c r="CB30" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
@@ -8168,482 +8177,482 @@
         <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F31">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="G31">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="H31">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="J31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K31">
         <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O31">
+        <v>1.32</v>
+      </c>
+      <c r="P31">
+        <v>1.96</v>
+      </c>
+      <c r="Q31">
+        <v>1.96</v>
+      </c>
+      <c r="R31">
         <v>1.37</v>
       </c>
-      <c r="P31">
-        <v>1.86</v>
-      </c>
-      <c r="Q31">
-        <v>2.08</v>
-      </c>
-      <c r="R31">
-        <v>1.31</v>
-      </c>
       <c r="S31">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="T31">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="U31">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W31">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="X31">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y31">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z31">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AA31">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
         <v>8</v>
       </c>
       <c r="AD31">
+        <v>14</v>
+      </c>
+      <c r="AE31">
+        <v>40</v>
+      </c>
+      <c r="AF31">
+        <v>17</v>
+      </c>
+      <c r="AG31">
+        <v>12.5</v>
+      </c>
+      <c r="AH31">
+        <v>18</v>
+      </c>
+      <c r="AI31">
+        <v>55</v>
+      </c>
+      <c r="AJ31">
+        <v>44</v>
+      </c>
+      <c r="AK31">
+        <v>29</v>
+      </c>
+      <c r="AL31">
+        <v>46</v>
+      </c>
+      <c r="AM31">
+        <v>110</v>
+      </c>
+      <c r="AN31">
+        <v>23</v>
+      </c>
+      <c r="AO31">
+        <v>36</v>
+      </c>
+      <c r="AP31">
+        <v>12.5</v>
+      </c>
+      <c r="AQ31">
+        <v>11</v>
+      </c>
+      <c r="AR31">
         <v>17.5</v>
       </c>
-      <c r="AE31">
-        <v>60</v>
-      </c>
-      <c r="AF31">
-        <v>13</v>
-      </c>
-      <c r="AG31">
-        <v>11</v>
-      </c>
-      <c r="AH31">
-        <v>19</v>
-      </c>
-      <c r="AI31">
-        <v>75</v>
-      </c>
-      <c r="AJ31">
-        <v>28</v>
-      </c>
-      <c r="AK31">
-        <v>25</v>
-      </c>
-      <c r="AL31">
-        <v>48</v>
-      </c>
-      <c r="AM31">
-        <v>130</v>
-      </c>
-      <c r="AN31">
-        <v>19</v>
-      </c>
-      <c r="AO31">
-        <v>70</v>
-      </c>
-      <c r="AP31">
-        <v>11</v>
-      </c>
-      <c r="AQ31">
-        <v>11.5</v>
-      </c>
-      <c r="AR31">
-        <v>20</v>
-      </c>
       <c r="AS31">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT31">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU31">
         <v>7.2</v>
       </c>
       <c r="AV31">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AW31">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX31">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AY31">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA31">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="BB31">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BC31">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BD31">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BE31">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF31">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG31">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH31">
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>2.7</v>
+        <v>1.38</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>2.32</v>
+        <v>1.38</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN31">
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="BP31">
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F32">
+        <v>2.14</v>
+      </c>
+      <c r="G32">
+        <v>2.22</v>
+      </c>
+      <c r="H32">
+        <v>3.8</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32">
+        <v>3.35</v>
+      </c>
+      <c r="K32">
+        <v>3.6</v>
+      </c>
+      <c r="L32">
+        <v>1.41</v>
+      </c>
+      <c r="M32">
+        <v>1.08</v>
+      </c>
+      <c r="N32">
+        <v>3.4</v>
+      </c>
+      <c r="O32">
+        <v>1.37</v>
+      </c>
+      <c r="P32">
+        <v>1.86</v>
+      </c>
+      <c r="Q32">
+        <v>2.1</v>
+      </c>
+      <c r="R32">
+        <v>1.32</v>
+      </c>
+      <c r="S32">
+        <v>3.85</v>
+      </c>
+      <c r="T32">
+        <v>1.87</v>
+      </c>
+      <c r="U32">
+        <v>2.04</v>
+      </c>
+      <c r="V32">
+        <v>1.33</v>
+      </c>
+      <c r="W32">
+        <v>1.83</v>
+      </c>
+      <c r="X32">
+        <v>13</v>
+      </c>
+      <c r="Y32">
+        <v>15</v>
+      </c>
+      <c r="Z32">
+        <v>29</v>
+      </c>
+      <c r="AA32">
+        <v>95</v>
+      </c>
+      <c r="AB32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC32">
+        <v>8</v>
+      </c>
+      <c r="AD32">
+        <v>16.5</v>
+      </c>
+      <c r="AE32">
+        <v>60</v>
+      </c>
+      <c r="AF32">
+        <v>13.5</v>
+      </c>
+      <c r="AG32">
+        <v>11</v>
+      </c>
+      <c r="AH32">
+        <v>19</v>
+      </c>
+      <c r="AI32">
+        <v>75</v>
+      </c>
+      <c r="AJ32">
+        <v>28</v>
+      </c>
+      <c r="AK32">
+        <v>25</v>
+      </c>
+      <c r="AL32">
+        <v>44</v>
+      </c>
+      <c r="AM32">
+        <v>130</v>
+      </c>
+      <c r="AN32">
+        <v>19</v>
+      </c>
+      <c r="AO32">
+        <v>70</v>
+      </c>
+      <c r="AP32">
+        <v>11</v>
+      </c>
+      <c r="AQ32">
+        <v>11.5</v>
+      </c>
+      <c r="AR32">
+        <v>24</v>
+      </c>
+      <c r="AS32">
+        <v>10</v>
+      </c>
+      <c r="AT32">
+        <v>8</v>
+      </c>
+      <c r="AU32">
+        <v>7.2</v>
+      </c>
+      <c r="AV32">
+        <v>14</v>
+      </c>
+      <c r="AW32">
+        <v>9.6</v>
+      </c>
+      <c r="AX32">
+        <v>11.5</v>
+      </c>
+      <c r="AY32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ32">
+        <v>16.5</v>
+      </c>
+      <c r="BA32">
+        <v>40</v>
+      </c>
+      <c r="BB32">
+        <v>19</v>
+      </c>
+      <c r="BC32">
+        <v>21</v>
+      </c>
+      <c r="BD32">
+        <v>30</v>
+      </c>
+      <c r="BE32">
+        <v>10.5</v>
+      </c>
+      <c r="BF32">
+        <v>16.5</v>
+      </c>
+      <c r="BG32">
+        <v>10</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>2.7</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>2.32</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>2.68</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.84</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>2.68</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>2.68</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
         <v>2.08</v>
       </c>
-      <c r="G32">
-        <v>2.26</v>
-      </c>
-      <c r="H32">
-        <v>3.5</v>
-      </c>
-      <c r="I32">
-        <v>3.85</v>
-      </c>
-      <c r="J32">
-        <v>3.6</v>
-      </c>
-      <c r="K32">
-        <v>3.95</v>
-      </c>
-      <c r="L32">
-        <v>1.33</v>
-      </c>
-      <c r="M32">
-        <v>1.06</v>
-      </c>
-      <c r="N32">
-        <v>4.1</v>
-      </c>
-      <c r="O32">
-        <v>1.26</v>
-      </c>
-      <c r="P32">
-        <v>2.02</v>
-      </c>
-      <c r="Q32">
-        <v>1.79</v>
-      </c>
-      <c r="R32">
-        <v>1.37</v>
-      </c>
-      <c r="S32">
-        <v>2.94</v>
-      </c>
-      <c r="T32">
-        <v>1.7</v>
-      </c>
-      <c r="U32">
-        <v>2.24</v>
-      </c>
-      <c r="V32">
-        <v>1.35</v>
-      </c>
-      <c r="W32">
-        <v>1.79</v>
-      </c>
-      <c r="X32">
-        <v>21</v>
-      </c>
-      <c r="Y32">
-        <v>18.5</v>
-      </c>
-      <c r="Z32">
-        <v>34</v>
-      </c>
-      <c r="AA32">
-        <v>80</v>
-      </c>
-      <c r="AB32">
-        <v>11</v>
-      </c>
-      <c r="AC32">
-        <v>8.6</v>
-      </c>
-      <c r="AD32">
-        <v>18.5</v>
-      </c>
-      <c r="AE32">
-        <v>50</v>
-      </c>
-      <c r="AF32">
-        <v>17.5</v>
-      </c>
-      <c r="AG32">
-        <v>13.5</v>
-      </c>
-      <c r="AH32">
-        <v>21</v>
-      </c>
-      <c r="AI32">
-        <v>60</v>
-      </c>
-      <c r="AJ32">
-        <v>34</v>
-      </c>
-      <c r="AK32">
-        <v>27</v>
-      </c>
-      <c r="AL32">
-        <v>42</v>
-      </c>
-      <c r="AM32">
-        <v>100</v>
-      </c>
-      <c r="AN32">
-        <v>18</v>
-      </c>
-      <c r="AO32">
-        <v>46</v>
-      </c>
-      <c r="AP32">
-        <v>14.5</v>
-      </c>
-      <c r="AQ32">
-        <v>13</v>
-      </c>
-      <c r="AR32">
-        <v>19.5</v>
-      </c>
-      <c r="AS32">
-        <v>5.1</v>
-      </c>
-      <c r="AT32">
-        <v>9.4</v>
-      </c>
-      <c r="AU32">
-        <v>7.6</v>
-      </c>
-      <c r="AV32">
-        <v>13</v>
-      </c>
-      <c r="AW32">
-        <v>4.9</v>
-      </c>
-      <c r="AX32">
-        <v>12</v>
-      </c>
-      <c r="AY32">
-        <v>9.6</v>
-      </c>
-      <c r="AZ32">
-        <v>14.5</v>
-      </c>
-      <c r="BA32">
-        <v>5</v>
-      </c>
-      <c r="BB32">
-        <v>19.5</v>
-      </c>
-      <c r="BC32">
-        <v>16</v>
-      </c>
-      <c r="BD32">
-        <v>4.8</v>
-      </c>
-      <c r="BE32">
-        <v>5.2</v>
-      </c>
-      <c r="BF32">
-        <v>12.5</v>
-      </c>
-      <c r="BG32">
-        <v>4.9</v>
-      </c>
-      <c r="BH32">
-        <v>1000</v>
-      </c>
-      <c r="BI32">
-        <v>1.2</v>
-      </c>
-      <c r="BJ32">
-        <v>1000</v>
-      </c>
-      <c r="BK32">
-        <v>1.2</v>
-      </c>
-      <c r="BL32">
-        <v>1000</v>
-      </c>
-      <c r="BM32">
-        <v>1.2</v>
-      </c>
-      <c r="BN32">
-        <v>1000</v>
-      </c>
-      <c r="BO32">
-        <v>1.33</v>
-      </c>
-      <c r="BP32">
-        <v>1000</v>
-      </c>
-      <c r="BQ32">
-        <v>1.2</v>
-      </c>
-      <c r="BR32">
-        <v>1000</v>
-      </c>
-      <c r="BS32">
-        <v>1.2</v>
-      </c>
-      <c r="BT32">
-        <v>1000</v>
-      </c>
-      <c r="BU32">
-        <v>1.2</v>
-      </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="CB32" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s">
         <v>98</v>
@@ -8652,235 +8661,235 @@
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F33">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="G33">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="H33">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="I33">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K33">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="L33">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="M33">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N33">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="O33">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="P33">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="Q33">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="R33">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S33">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="T33">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="U33">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="V33">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="X33">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="Z33">
+        <v>34</v>
+      </c>
+      <c r="AA33">
+        <v>85</v>
+      </c>
+      <c r="AB33">
+        <v>11</v>
+      </c>
+      <c r="AC33">
+        <v>8.6</v>
+      </c>
+      <c r="AD33">
         <v>18.5</v>
       </c>
-      <c r="AA33">
+      <c r="AE33">
+        <v>55</v>
+      </c>
+      <c r="AF33">
+        <v>15</v>
+      </c>
+      <c r="AG33">
+        <v>13.5</v>
+      </c>
+      <c r="AH33">
+        <v>21</v>
+      </c>
+      <c r="AI33">
+        <v>60</v>
+      </c>
+      <c r="AJ33">
+        <v>34</v>
+      </c>
+      <c r="AK33">
+        <v>27</v>
+      </c>
+      <c r="AL33">
+        <v>42</v>
+      </c>
+      <c r="AM33">
+        <v>100</v>
+      </c>
+      <c r="AN33">
+        <v>15</v>
+      </c>
+      <c r="AO33">
         <v>46</v>
       </c>
-      <c r="AB33">
-        <v>12</v>
-      </c>
-      <c r="AC33">
+      <c r="AP33">
+        <v>14</v>
+      </c>
+      <c r="AQ33">
+        <v>13</v>
+      </c>
+      <c r="AR33">
+        <v>19.5</v>
+      </c>
+      <c r="AS33">
+        <v>5.6</v>
+      </c>
+      <c r="AT33">
+        <v>9.4</v>
+      </c>
+      <c r="AU33">
         <v>7.6</v>
       </c>
-      <c r="AD33">
+      <c r="AV33">
+        <v>13</v>
+      </c>
+      <c r="AW33">
+        <v>5.4</v>
+      </c>
+      <c r="AX33">
+        <v>12.5</v>
+      </c>
+      <c r="AY33">
+        <v>9.6</v>
+      </c>
+      <c r="AZ33">
         <v>14.5</v>
       </c>
-      <c r="AE33">
-        <v>40</v>
-      </c>
-      <c r="AF33">
-        <v>24</v>
-      </c>
-      <c r="AG33">
-        <v>17</v>
-      </c>
-      <c r="AH33">
-        <v>24</v>
-      </c>
-      <c r="AI33">
-        <v>65</v>
-      </c>
-      <c r="AJ33">
-        <v>70</v>
-      </c>
-      <c r="AK33">
-        <v>50</v>
-      </c>
-      <c r="AL33">
-        <v>75</v>
-      </c>
-      <c r="AM33">
-        <v>160</v>
-      </c>
-      <c r="AN33">
-        <v>60</v>
-      </c>
-      <c r="AO33">
-        <v>38</v>
-      </c>
-      <c r="AP33">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ33">
-        <v>7.8</v>
-      </c>
-      <c r="AR33">
-        <v>13.5</v>
-      </c>
-      <c r="AS33">
-        <v>5.8</v>
-      </c>
-      <c r="AT33">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU33">
-        <v>6.6</v>
-      </c>
-      <c r="AV33">
-        <v>10.5</v>
-      </c>
-      <c r="AW33">
-        <v>5.7</v>
-      </c>
-      <c r="AX33">
-        <v>17.5</v>
-      </c>
-      <c r="AY33">
+      <c r="BA33">
+        <v>5.4</v>
+      </c>
+      <c r="BB33">
+        <v>19.5</v>
+      </c>
+      <c r="BC33">
+        <v>16</v>
+      </c>
+      <c r="BD33">
+        <v>5.2</v>
+      </c>
+      <c r="BE33">
+        <v>5.6</v>
+      </c>
+      <c r="BF33">
         <v>12.5</v>
       </c>
-      <c r="AZ33">
-        <v>17.5</v>
-      </c>
-      <c r="BA33">
-        <v>6</v>
-      </c>
-      <c r="BB33">
-        <v>6</v>
-      </c>
-      <c r="BC33">
-        <v>34</v>
-      </c>
-      <c r="BD33">
-        <v>6</v>
-      </c>
-      <c r="BE33">
-        <v>5.7</v>
-      </c>
-      <c r="BF33">
-        <v>6</v>
-      </c>
       <c r="BG33">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="CB33" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8894,235 +8903,477 @@
         <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F34">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="G34">
+        <v>3.3</v>
+      </c>
+      <c r="H34">
+        <v>2.56</v>
+      </c>
+      <c r="I34">
+        <v>2.66</v>
+      </c>
+      <c r="J34">
+        <v>3.2</v>
+      </c>
+      <c r="K34">
+        <v>3.3</v>
+      </c>
+      <c r="L34">
+        <v>1.51</v>
+      </c>
+      <c r="M34">
+        <v>1.1</v>
+      </c>
+      <c r="N34">
+        <v>2.98</v>
+      </c>
+      <c r="O34">
+        <v>1.46</v>
+      </c>
+      <c r="P34">
+        <v>1.66</v>
+      </c>
+      <c r="Q34">
+        <v>2.32</v>
+      </c>
+      <c r="R34">
+        <v>1.25</v>
+      </c>
+      <c r="S34">
+        <v>4.5</v>
+      </c>
+      <c r="T34">
+        <v>1.96</v>
+      </c>
+      <c r="U34">
+        <v>1.92</v>
+      </c>
+      <c r="V34">
+        <v>1.6</v>
+      </c>
+      <c r="W34">
+        <v>1.43</v>
+      </c>
+      <c r="X34">
+        <v>11</v>
+      </c>
+      <c r="Y34">
+        <v>9</v>
+      </c>
+      <c r="Z34">
+        <v>18.5</v>
+      </c>
+      <c r="AA34">
+        <v>46</v>
+      </c>
+      <c r="AB34">
+        <v>12</v>
+      </c>
+      <c r="AC34">
+        <v>7.6</v>
+      </c>
+      <c r="AD34">
+        <v>14.5</v>
+      </c>
+      <c r="AE34">
+        <v>40</v>
+      </c>
+      <c r="AF34">
+        <v>46</v>
+      </c>
+      <c r="AG34">
+        <v>17</v>
+      </c>
+      <c r="AH34">
+        <v>24</v>
+      </c>
+      <c r="AI34">
+        <v>65</v>
+      </c>
+      <c r="AJ34">
+        <v>70</v>
+      </c>
+      <c r="AK34">
+        <v>50</v>
+      </c>
+      <c r="AL34">
+        <v>75</v>
+      </c>
+      <c r="AM34">
+        <v>160</v>
+      </c>
+      <c r="AN34">
+        <v>60</v>
+      </c>
+      <c r="AO34">
+        <v>38</v>
+      </c>
+      <c r="AP34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ34">
+        <v>7.8</v>
+      </c>
+      <c r="AR34">
+        <v>13.5</v>
+      </c>
+      <c r="AS34">
+        <v>15.5</v>
+      </c>
+      <c r="AT34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU34">
+        <v>6.6</v>
+      </c>
+      <c r="AV34">
+        <v>10.5</v>
+      </c>
+      <c r="AW34">
+        <v>13.5</v>
+      </c>
+      <c r="AX34">
+        <v>17.5</v>
+      </c>
+      <c r="AY34">
+        <v>12.5</v>
+      </c>
+      <c r="AZ34">
+        <v>17.5</v>
+      </c>
+      <c r="BA34">
+        <v>6.6</v>
+      </c>
+      <c r="BB34">
+        <v>6.6</v>
+      </c>
+      <c r="BC34">
+        <v>6.4</v>
+      </c>
+      <c r="BD34">
+        <v>6.6</v>
+      </c>
+      <c r="BE34">
+        <v>6.6</v>
+      </c>
+      <c r="BF34">
+        <v>6.4</v>
+      </c>
+      <c r="BG34">
+        <v>6.2</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.16</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.16</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.16</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
         <v>1.88</v>
       </c>
-      <c r="H34">
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.16</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.16</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.5</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.16</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.16</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.16</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35">
+        <v>1.83</v>
+      </c>
+      <c r="G35">
+        <v>1.88</v>
+      </c>
+      <c r="H35">
         <v>5.5</v>
       </c>
-      <c r="I34">
-        <v>5.9</v>
-      </c>
-      <c r="J34">
+      <c r="I35">
+        <v>6</v>
+      </c>
+      <c r="J35">
         <v>3.4</v>
       </c>
-      <c r="K34">
+      <c r="K35">
         <v>3.55</v>
       </c>
-      <c r="L34">
+      <c r="L35">
         <v>1.53</v>
       </c>
-      <c r="M34">
-        <v>1.11</v>
-      </c>
-      <c r="N34">
-        <v>2.8</v>
-      </c>
-      <c r="O34">
+      <c r="M35">
+        <v>1.1</v>
+      </c>
+      <c r="N35">
+        <v>2.82</v>
+      </c>
+      <c r="O35">
         <v>1.51</v>
       </c>
-      <c r="P34">
+      <c r="P35">
         <v>1.61</v>
       </c>
-      <c r="Q34">
+      <c r="Q35">
         <v>2.5</v>
       </c>
-      <c r="R34">
-        <v>1.22</v>
-      </c>
-      <c r="S34">
-        <v>4.7</v>
-      </c>
-      <c r="T34">
+      <c r="R35">
+        <v>1.21</v>
+      </c>
+      <c r="S35">
+        <v>4.9</v>
+      </c>
+      <c r="T35">
         <v>2.24</v>
       </c>
-      <c r="U34">
-        <v>1.71</v>
-      </c>
-      <c r="V34">
+      <c r="U35">
+        <v>1.72</v>
+      </c>
+      <c r="V35">
+        <v>1.2</v>
+      </c>
+      <c r="W35">
+        <v>2.12</v>
+      </c>
+      <c r="X35">
+        <v>9.6</v>
+      </c>
+      <c r="Y35">
+        <v>14.5</v>
+      </c>
+      <c r="Z35">
+        <v>48</v>
+      </c>
+      <c r="AA35">
+        <v>230</v>
+      </c>
+      <c r="AB35">
+        <v>6.4</v>
+      </c>
+      <c r="AC35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD35">
+        <v>25</v>
+      </c>
+      <c r="AE35">
+        <v>140</v>
+      </c>
+      <c r="AF35">
+        <v>9.6</v>
+      </c>
+      <c r="AG35">
+        <v>11.5</v>
+      </c>
+      <c r="AH35">
+        <v>28</v>
+      </c>
+      <c r="AI35">
+        <v>150</v>
+      </c>
+      <c r="AJ35">
+        <v>21</v>
+      </c>
+      <c r="AK35">
+        <v>26</v>
+      </c>
+      <c r="AL35">
+        <v>65</v>
+      </c>
+      <c r="AM35">
+        <v>270</v>
+      </c>
+      <c r="AN35">
+        <v>19.5</v>
+      </c>
+      <c r="AO35">
+        <v>240</v>
+      </c>
+      <c r="AP35">
+        <v>8.6</v>
+      </c>
+      <c r="AQ35">
+        <v>12.5</v>
+      </c>
+      <c r="AR35">
+        <v>19.5</v>
+      </c>
+      <c r="AS35">
+        <v>11.5</v>
+      </c>
+      <c r="AT35">
+        <v>5.7</v>
+      </c>
+      <c r="AU35">
+        <v>7.2</v>
+      </c>
+      <c r="AV35">
+        <v>21</v>
+      </c>
+      <c r="AW35">
+        <v>11</v>
+      </c>
+      <c r="AX35">
+        <v>8.6</v>
+      </c>
+      <c r="AY35">
+        <v>9.6</v>
+      </c>
+      <c r="AZ35">
+        <v>8.4</v>
+      </c>
+      <c r="BA35">
+        <v>11</v>
+      </c>
+      <c r="BB35">
+        <v>18</v>
+      </c>
+      <c r="BC35">
+        <v>21</v>
+      </c>
+      <c r="BD35">
+        <v>26</v>
+      </c>
+      <c r="BE35">
+        <v>11.5</v>
+      </c>
+      <c r="BF35">
+        <v>16.5</v>
+      </c>
+      <c r="BG35">
+        <v>11.5</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.27</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
         <v>1.21</v>
       </c>
-      <c r="W34">
-        <v>2.12</v>
-      </c>
-      <c r="X34">
-        <v>9.6</v>
-      </c>
-      <c r="Y34">
-        <v>14.5</v>
-      </c>
-      <c r="Z34">
-        <v>48</v>
-      </c>
-      <c r="AA34">
-        <v>230</v>
-      </c>
-      <c r="AB34">
-        <v>6.4</v>
-      </c>
-      <c r="AC34">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD34">
-        <v>25</v>
-      </c>
-      <c r="AE34">
-        <v>140</v>
-      </c>
-      <c r="AF34">
-        <v>9.6</v>
-      </c>
-      <c r="AG34">
-        <v>11.5</v>
-      </c>
-      <c r="AH34">
-        <v>28</v>
-      </c>
-      <c r="AI34">
-        <v>150</v>
-      </c>
-      <c r="AJ34">
-        <v>22</v>
-      </c>
-      <c r="AK34">
-        <v>26</v>
-      </c>
-      <c r="AL34">
-        <v>65</v>
-      </c>
-      <c r="AM34">
-        <v>270</v>
-      </c>
-      <c r="AN34">
-        <v>19.5</v>
-      </c>
-      <c r="AO34">
-        <v>240</v>
-      </c>
-      <c r="AP34">
-        <v>8.6</v>
-      </c>
-      <c r="AQ34">
-        <v>12.5</v>
-      </c>
-      <c r="AR34">
-        <v>9.6</v>
-      </c>
-      <c r="AS34">
-        <v>11</v>
-      </c>
-      <c r="AT34">
-        <v>5.7</v>
-      </c>
-      <c r="AU34">
-        <v>7.2</v>
-      </c>
-      <c r="AV34">
-        <v>21</v>
-      </c>
-      <c r="AW34">
-        <v>11</v>
-      </c>
-      <c r="AX34">
-        <v>8.6</v>
-      </c>
-      <c r="AY34">
-        <v>9.6</v>
-      </c>
-      <c r="AZ34">
-        <v>20</v>
-      </c>
-      <c r="BA34">
-        <v>11</v>
-      </c>
-      <c r="BB34">
-        <v>17.5</v>
-      </c>
-      <c r="BC34">
-        <v>21</v>
-      </c>
-      <c r="BD34">
-        <v>40</v>
-      </c>
-      <c r="BE34">
-        <v>11.5</v>
-      </c>
-      <c r="BF34">
-        <v>16.5</v>
-      </c>
-      <c r="BG34">
-        <v>11</v>
-      </c>
-      <c r="BH34">
-        <v>1000</v>
-      </c>
-      <c r="BI34">
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
         <v>1.21</v>
       </c>
-      <c r="BJ34">
-        <v>1000</v>
-      </c>
-      <c r="BK34">
-        <v>1.04</v>
-      </c>
-      <c r="BL34">
-        <v>1000</v>
-      </c>
-      <c r="BM34">
-        <v>1.04</v>
-      </c>
-      <c r="BN34">
-        <v>1000</v>
-      </c>
-      <c r="BO34">
-        <v>1.04</v>
-      </c>
-      <c r="BP34">
-        <v>1000</v>
-      </c>
-      <c r="BQ34">
-        <v>1.04</v>
-      </c>
-      <c r="BR34">
-        <v>1000</v>
-      </c>
-      <c r="BS34">
-        <v>1.04</v>
-      </c>
-      <c r="BT34">
-        <v>1000</v>
-      </c>
-      <c r="BU34">
-        <v>1.04</v>
-      </c>
-      <c r="BV34">
-        <v>1000</v>
-      </c>
-      <c r="BW34">
-        <v>1.04</v>
-      </c>
-      <c r="BX34">
-        <v>1000</v>
-      </c>
-      <c r="BY34">
-        <v>1.04</v>
-      </c>
-      <c r="BZ34">
-        <v>1000</v>
-      </c>
-      <c r="CA34">
-        <v>1.04</v>
-      </c>
-      <c r="CB34" t="s">
-        <v>182</v>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.04</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.21</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.21</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.21</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.21</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.21</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.21</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -571,7 +571,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 10:21:32</t>
+    <t>2026-10-01 12:35:32</t>
   </si>
 </sst>
 </file>
@@ -1165,13 +1165,13 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>6.6</v>
@@ -1180,10 +1180,10 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -1192,13 +1192,13 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.33</v>
@@ -1207,22 +1207,22 @@
         <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>55</v>
@@ -1231,7 +1231,7 @@
         <v>210</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
@@ -1240,31 +1240,31 @@
         <v>25</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI2">
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AN2">
         <v>11.5</v>
@@ -1276,37 +1276,37 @@
         <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR2">
+        <v>42</v>
+      </c>
+      <c r="AS2">
+        <v>13.5</v>
+      </c>
+      <c r="AT2">
+        <v>7</v>
+      </c>
+      <c r="AU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2">
         <v>21</v>
       </c>
-      <c r="AS2">
-        <v>10</v>
-      </c>
-      <c r="AT2">
-        <v>6.8</v>
-      </c>
-      <c r="AU2">
-        <v>8</v>
-      </c>
-      <c r="AV2">
-        <v>19.5</v>
-      </c>
       <c r="AW2">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
@@ -1315,16 +1315,16 @@
         <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BE2">
+        <v>13.5</v>
+      </c>
+      <c r="BF2">
         <v>10</v>
       </c>
-      <c r="BF2">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG2">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
@@ -1336,7 +1336,7 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>190</v>
@@ -1363,7 +1363,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
         <v>7.8</v>
@@ -1407,16 +1407,16 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G3">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
         <v>3.95</v>
@@ -1428,70 +1428,70 @@
         <v>1.32</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R3">
+        <v>1.6</v>
+      </c>
+      <c r="S3">
+        <v>2.6</v>
+      </c>
+      <c r="T3">
         <v>1.56</v>
       </c>
-      <c r="S3">
-        <v>2.66</v>
-      </c>
-      <c r="T3">
-        <v>1.6</v>
-      </c>
       <c r="U3">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="W3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB3">
+        <v>19.5</v>
+      </c>
+      <c r="AC3">
+        <v>10</v>
+      </c>
+      <c r="AD3">
+        <v>11</v>
+      </c>
+      <c r="AE3">
         <v>18.5</v>
       </c>
-      <c r="AC3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD3">
-        <v>10.5</v>
-      </c>
-      <c r="AE3">
-        <v>19</v>
-      </c>
       <c r="AF3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG3">
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3">
         <v>27</v>
@@ -1500,52 +1500,52 @@
         <v>75</v>
       </c>
       <c r="AK3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AM3">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS3">
         <v>20</v>
       </c>
       <c r="AT3">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3">
         <v>9.4</v>
       </c>
       <c r="AW3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX3">
         <v>24</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA3">
         <v>23</v>
@@ -1554,31 +1554,31 @@
         <v>42</v>
       </c>
       <c r="BC3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>19.5</v>
       </c>
       <c r="BG3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH3">
         <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1593,10 +1593,10 @@
         <v>5.6</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR3">
         <v>32</v>
@@ -1617,13 +1617,13 @@
         <v>7.2</v>
       </c>
       <c r="BX3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA3">
         <v>8</v>
@@ -1655,49 +1655,49 @@
         <v>55</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I4">
         <v>1.11</v>
       </c>
       <c r="J4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="K4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O4">
         <v>1.13</v>
       </c>
       <c r="P4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R4">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="U4">
         <v>1.41</v>
       </c>
       <c r="V4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="W4">
         <v>1.02</v>
@@ -1769,10 +1769,10 @@
         <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AU4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
@@ -1781,28 +1781,28 @@
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AZ4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BB4">
         <v>11</v>
       </c>
       <c r="BC4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BE4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BF4">
         <v>11</v>
@@ -1814,58 +1814,58 @@
         <v>5.8</v>
       </c>
       <c r="BI4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ4">
         <v>21</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN4">
         <v>34</v>
       </c>
       <c r="BO4">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BU4">
         <v>3.25</v>
       </c>
       <c r="BV4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BW4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX4">
         <v>29</v>
       </c>
       <c r="BY4">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CA4">
         <v>5</v>
@@ -1891,22 +1891,22 @@
         <v>154</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G5">
         <v>3.05</v>
       </c>
       <c r="H5">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="I5">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.44</v>
@@ -1915,97 +1915,97 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
         <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X5">
         <v>12</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z5">
+        <v>18</v>
+      </c>
+      <c r="AA5">
+        <v>42</v>
+      </c>
+      <c r="AB5">
+        <v>11.5</v>
+      </c>
+      <c r="AC5">
+        <v>7.2</v>
+      </c>
+      <c r="AD5">
+        <v>12.5</v>
+      </c>
+      <c r="AE5">
+        <v>32</v>
+      </c>
+      <c r="AF5">
         <v>19.5</v>
       </c>
-      <c r="AA5">
+      <c r="AG5">
+        <v>13.5</v>
+      </c>
+      <c r="AH5">
+        <v>17</v>
+      </c>
+      <c r="AI5">
+        <v>48</v>
+      </c>
+      <c r="AJ5">
+        <v>55</v>
+      </c>
+      <c r="AK5">
+        <v>36</v>
+      </c>
+      <c r="AL5">
         <v>50</v>
       </c>
-      <c r="AB5">
-        <v>12.5</v>
-      </c>
-      <c r="AC5">
-        <v>6.8</v>
-      </c>
-      <c r="AD5">
-        <v>13</v>
-      </c>
-      <c r="AE5">
-        <v>36</v>
-      </c>
-      <c r="AF5">
-        <v>21</v>
-      </c>
-      <c r="AG5">
-        <v>15.5</v>
-      </c>
-      <c r="AH5">
-        <v>16.5</v>
-      </c>
-      <c r="AI5">
-        <v>55</v>
-      </c>
-      <c r="AJ5">
-        <v>60</v>
-      </c>
-      <c r="AK5">
-        <v>44</v>
-      </c>
-      <c r="AL5">
-        <v>55</v>
-      </c>
       <c r="AM5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
         <v>10</v>
       </c>
       <c r="AR5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS5">
         <v>36</v>
@@ -2014,7 +2014,7 @@
         <v>10.5</v>
       </c>
       <c r="AU5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
         <v>11</v>
@@ -2023,34 +2023,34 @@
         <v>27</v>
       </c>
       <c r="AX5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB5">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BC5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE5">
         <v>65</v>
       </c>
       <c r="BF5">
+        <v>26</v>
+      </c>
+      <c r="BG5">
         <v>23</v>
-      </c>
-      <c r="BG5">
-        <v>22</v>
       </c>
       <c r="BH5">
         <v>3.65</v>
@@ -2059,7 +2059,7 @@
         <v>2.7</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
         <v>7.4</v>
@@ -2074,16 +2074,16 @@
         <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
         <v>26</v>
       </c>
       <c r="BQ5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BS5">
         <v>5.6</v>
@@ -2092,22 +2092,22 @@
         <v>6.2</v>
       </c>
       <c r="BU5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
         <v>24</v>
       </c>
       <c r="BW5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BX5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY5">
         <v>5.5</v>
       </c>
       <c r="BZ5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA5">
         <v>5.4</v>
@@ -2142,13 +2142,13 @@
         <v>5.9</v>
       </c>
       <c r="I6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
         <v>5.1</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.23</v>
@@ -2166,7 +2166,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R6">
         <v>1.97</v>
@@ -2175,10 +2175,10 @@
         <v>2.02</v>
       </c>
       <c r="T6">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U6">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V6">
         <v>1.19</v>
@@ -2202,13 +2202,13 @@
         <v>17</v>
       </c>
       <c r="AC6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -2223,7 +2223,7 @@
         <v>50</v>
       </c>
       <c r="AJ6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK6">
         <v>14</v>
@@ -2235,7 +2235,7 @@
         <v>55</v>
       </c>
       <c r="AN6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO6">
         <v>40</v>
@@ -2244,7 +2244,7 @@
         <v>32</v>
       </c>
       <c r="AQ6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR6">
         <v>55</v>
@@ -2253,19 +2253,19 @@
         <v>42</v>
       </c>
       <c r="AT6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU6">
         <v>12</v>
       </c>
       <c r="AV6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>10</v>
@@ -2277,16 +2277,16 @@
         <v>44</v>
       </c>
       <c r="BB6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC6">
         <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF6">
         <v>4.4</v>
@@ -2304,7 +2304,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BL6">
         <v>65</v>
@@ -2322,7 +2322,7 @@
         <v>9</v>
       </c>
       <c r="BQ6">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
         <v>17</v>
@@ -2334,7 +2334,7 @@
         <v>10</v>
       </c>
       <c r="BU6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV6">
         <v>38</v>
@@ -2352,7 +2352,7 @@
         <v>9.4</v>
       </c>
       <c r="CA6">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="s">
         <v>185</v>
@@ -2378,19 +2378,19 @@
         <v>7.2</v>
       </c>
       <c r="G7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H7">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="I7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="J7">
         <v>4.5</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2402,25 +2402,25 @@
         <v>4.3</v>
       </c>
       <c r="O7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P7">
         <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S7">
         <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
         <v>2.78</v>
@@ -2429,7 +2429,7 @@
         <v>1.15</v>
       </c>
       <c r="X7">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="Y7">
         <v>8.6</v>
@@ -2438,7 +2438,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB7">
         <v>25</v>
@@ -2450,16 +2450,16 @@
         <v>10</v>
       </c>
       <c r="AE7">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AF7">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AG7">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AH7">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>44</v>
@@ -2480,10 +2480,10 @@
         <v>170</v>
       </c>
       <c r="AO7">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7">
         <v>7.8</v>
@@ -2507,34 +2507,34 @@
         <v>14.5</v>
       </c>
       <c r="AX7">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AY7">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AZ7">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BB7">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC7">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="BD7">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH7">
         <v>3.75</v>
@@ -2552,7 +2552,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="BN7">
         <v>11</v>
@@ -2576,7 +2576,7 @@
         <v>4</v>
       </c>
       <c r="BU7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV7">
         <v>9.4</v>
@@ -2617,22 +2617,22 @@
         <v>157</v>
       </c>
       <c r="F8">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G8">
         <v>3.3</v>
       </c>
       <c r="H8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I8">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2641,31 +2641,31 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
         <v>1.28</v>
       </c>
       <c r="P8">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="Q8">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="U8">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
         <v>1.45</v>
@@ -2686,7 +2686,7 @@
         <v>1000</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2725,58 +2725,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU8">
         <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2862,19 +2862,19 @@
         <v>1.55</v>
       </c>
       <c r="G9">
-        <v>1.96</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>1.13</v>
       </c>
       <c r="I9">
-        <v>9.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="K9">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2883,22 +2883,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>1.24</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P9">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>2.96</v>
+        <v>1.42</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2907,10 +2907,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>2.04</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3021,64 +3021,64 @@
         <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>185</v>
@@ -3101,22 +3101,22 @@
         <v>159</v>
       </c>
       <c r="F10">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="G10">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="H10">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="I10">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="J10">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3125,7 +3125,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
         <v>1.02</v>
@@ -3149,10 +3149,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="W10">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3343,46 +3343,46 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>1.64</v>
+        <v>1.1</v>
       </c>
       <c r="G11">
-        <v>1.94</v>
+        <v>990</v>
       </c>
       <c r="H11">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L11">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
         <v>1.03</v>
       </c>
       <c r="P11">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="R11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
-        <v>2.68</v>
+        <v>1.08</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3391,124 +3391,124 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Y11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Z11">
         <v>50</v>
       </c>
       <c r="AA11">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB11">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD11">
         <v>25</v>
       </c>
       <c r="AE11">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
         <v>22</v>
       </c>
       <c r="AK11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL11">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM11">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AO11">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AP11">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ11">
         <v>14</v>
       </c>
       <c r="AR11">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS11">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT11">
         <v>6.8</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW11">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX11">
+        <v>8.4</v>
+      </c>
+      <c r="AY11">
         <v>8</v>
       </c>
-      <c r="AY11">
-        <v>8.6</v>
-      </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC11">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BD11">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE11">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BG11">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
@@ -3827,7 +3827,7 @@
         <v>162</v>
       </c>
       <c r="F13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G13">
         <v>2.18</v>
@@ -3836,13 +3836,13 @@
         <v>3.1</v>
       </c>
       <c r="I13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J13">
         <v>4.4</v>
       </c>
       <c r="K13">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L13">
         <v>1.18</v>
@@ -3854,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P13">
         <v>3.4</v>
@@ -3866,7 +3866,7 @@
         <v>1.98</v>
       </c>
       <c r="S13">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="T13">
         <v>1.4</v>
@@ -3875,10 +3875,10 @@
         <v>3.15</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X13">
         <v>50</v>
@@ -3944,7 +3944,7 @@
         <v>5.6</v>
       </c>
       <c r="AS13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT13">
         <v>18.5</v>
@@ -3977,10 +3977,10 @@
         <v>16</v>
       </c>
       <c r="BD13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BE13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF13">
         <v>6.4</v>
@@ -3989,7 +3989,7 @@
         <v>11.5</v>
       </c>
       <c r="BH13">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BI13">
         <v>5</v>
@@ -4004,7 +4004,7 @@
         <v>55</v>
       </c>
       <c r="BM13">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BN13">
         <v>6.2</v>
@@ -4016,13 +4016,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ13">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BR13">
         <v>20</v>
       </c>
       <c r="BS13">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT13">
         <v>7.8</v>
@@ -4034,13 +4034,13 @@
         <v>23</v>
       </c>
       <c r="BW13">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BX13">
         <v>25</v>
       </c>
       <c r="BY13">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BZ13">
         <v>12</v>
@@ -4069,7 +4069,7 @@
         <v>163</v>
       </c>
       <c r="F14">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G14">
         <v>2.6</v>
@@ -4078,16 +4078,16 @@
         <v>2.86</v>
       </c>
       <c r="I14">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K14">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M14">
         <v>1.01</v>
@@ -4096,7 +4096,7 @@
         <v>3.4</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P14">
         <v>1.98</v>
@@ -4117,10 +4117,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W14">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4314,16 +4314,16 @@
         <v>2.86</v>
       </c>
       <c r="G15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H15">
         <v>1.86</v>
       </c>
       <c r="I15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J15">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -4335,7 +4335,7 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O15">
         <v>1.01</v>
@@ -4359,10 +4359,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="W15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4571,7 +4571,7 @@
         <v>5.7</v>
       </c>
       <c r="L16">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.01</v>
@@ -4586,7 +4586,7 @@
         <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R16">
         <v>1.65</v>
@@ -4664,10 +4664,10 @@
         <v>21</v>
       </c>
       <c r="AQ16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS16">
         <v>5</v>
@@ -4682,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="AW16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX16">
         <v>8.4</v>
@@ -4694,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="BA16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB16">
         <v>10.5</v>
@@ -4706,13 +4706,13 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF16">
         <v>4.2</v>
       </c>
       <c r="BG16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH16">
         <v>4.7</v>
@@ -4798,7 +4798,7 @@
         <v>2.82</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H17">
         <v>3.2</v>
@@ -4807,7 +4807,7 @@
         <v>3.45</v>
       </c>
       <c r="J17">
-        <v>2.78</v>
+        <v>1.12</v>
       </c>
       <c r="K17">
         <v>3</v>
@@ -4816,10 +4816,10 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N17">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O17">
         <v>1.6</v>
@@ -4831,7 +4831,7 @@
         <v>2.88</v>
       </c>
       <c r="R17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S17">
         <v>1.05</v>
@@ -4843,16 +4843,16 @@
         <v>1.71</v>
       </c>
       <c r="V17">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>24</v>
@@ -4861,7 +4861,7 @@
         <v>80</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC17">
         <v>7.2</v>
@@ -4873,10 +4873,10 @@
         <v>65</v>
       </c>
       <c r="AF17">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH17">
         <v>29</v>
@@ -4903,58 +4903,58 @@
         <v>90</v>
       </c>
       <c r="AP17">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AQ17">
         <v>3.75</v>
       </c>
       <c r="AR17">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AS17">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT17">
         <v>3.6</v>
       </c>
       <c r="AU17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AW17">
+        <v>5.8</v>
+      </c>
+      <c r="AX17">
+        <v>4.7</v>
+      </c>
+      <c r="AY17">
+        <v>4.6</v>
+      </c>
+      <c r="AZ17">
+        <v>5.2</v>
+      </c>
+      <c r="BA17">
         <v>6</v>
       </c>
-      <c r="AX17">
-        <v>4.9</v>
-      </c>
-      <c r="AY17">
-        <v>4.7</v>
-      </c>
-      <c r="AZ17">
-        <v>5.4</v>
-      </c>
-      <c r="BA17">
+      <c r="BB17">
+        <v>5.8</v>
+      </c>
+      <c r="BC17">
+        <v>5.7</v>
+      </c>
+      <c r="BD17">
+        <v>6</v>
+      </c>
+      <c r="BE17">
         <v>6.2</v>
       </c>
-      <c r="BB17">
+      <c r="BF17">
         <v>5.9</v>
       </c>
-      <c r="BC17">
-        <v>5.9</v>
-      </c>
-      <c r="BD17">
-        <v>6.2</v>
-      </c>
-      <c r="BE17">
-        <v>6.4</v>
-      </c>
-      <c r="BF17">
+      <c r="BG17">
         <v>6</v>
-      </c>
-      <c r="BG17">
-        <v>6.2</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5043,10 +5043,10 @@
         <v>2.98</v>
       </c>
       <c r="H18">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I18">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J18">
         <v>3.15</v>
@@ -5061,52 +5061,52 @@
         <v>1.11</v>
       </c>
       <c r="N18">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O18">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P18">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q18">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S18">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T18">
         <v>2.06</v>
       </c>
       <c r="U18">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
         <v>1.51</v>
       </c>
       <c r="X18">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z18">
         <v>17.5</v>
       </c>
       <c r="AA18">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD18">
         <v>14</v>
@@ -5115,49 +5115,49 @@
         <v>42</v>
       </c>
       <c r="AF18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG18">
         <v>14.5</v>
       </c>
       <c r="AH18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI18">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ18">
         <v>55</v>
       </c>
       <c r="AK18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL18">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM18">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN18">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO18">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ18">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR18">
         <v>14.5</v>
       </c>
       <c r="AS18">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AT18">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU18">
         <v>6.6</v>
@@ -5166,16 +5166,16 @@
         <v>12</v>
       </c>
       <c r="AW18">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AX18">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ18">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA18">
         <v>50</v>
@@ -5193,13 +5193,13 @@
         <v>12.5</v>
       </c>
       <c r="BF18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG18">
         <v>36</v>
       </c>
       <c r="BH18">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI18">
         <v>2.46</v>
@@ -5208,31 +5208,31 @@
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BT18">
         <v>1000</v>
@@ -5244,19 +5244,19 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="CB18" t="s">
         <v>185</v>
@@ -5279,7 +5279,7 @@
         <v>168</v>
       </c>
       <c r="F19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G19">
         <v>1.81</v>
@@ -5306,25 +5306,25 @@
         <v>5.3</v>
       </c>
       <c r="O19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P19">
         <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R19">
         <v>1.55</v>
       </c>
       <c r="S19">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T19">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
         <v>1.24</v>
@@ -5399,7 +5399,7 @@
         <v>1.37</v>
       </c>
       <c r="AT19">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="AU19">
         <v>1.27</v>
@@ -5411,10 +5411,10 @@
         <v>1.37</v>
       </c>
       <c r="AX19">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AY19">
-        <v>7.4</v>
+        <v>1.28</v>
       </c>
       <c r="AZ19">
         <v>1.37</v>
@@ -5521,13 +5521,13 @@
         <v>169</v>
       </c>
       <c r="F20">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="G20">
         <v>3.4</v>
       </c>
       <c r="H20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I20">
         <v>2.24</v>
@@ -5536,10 +5536,10 @@
         <v>3.9</v>
       </c>
       <c r="K20">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
         <v>1.02</v>
@@ -5560,13 +5560,13 @@
         <v>1.48</v>
       </c>
       <c r="S20">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T20">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U20">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V20">
         <v>1.8</v>
@@ -5578,7 +5578,7 @@
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
         <v>1000</v>
@@ -5626,61 +5626,61 @@
         <v>1000</v>
       </c>
       <c r="AO20">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP20">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AQ20">
         <v>1.15</v>
       </c>
       <c r="AR20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AS20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AT20">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AU20">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="AV20">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AW20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AX20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AY20">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AZ20">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BA20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BB20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BD20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BE20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BF20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BG20">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5763,10 +5763,10 @@
         <v>170</v>
       </c>
       <c r="F21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H21">
         <v>1.88</v>
@@ -5775,10 +5775,10 @@
         <v>1.96</v>
       </c>
       <c r="J21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -5790,10 +5790,10 @@
         <v>4.2</v>
       </c>
       <c r="O21">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q21">
         <v>1.74</v>
@@ -5802,19 +5802,19 @@
         <v>1.38</v>
       </c>
       <c r="S21">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T21">
         <v>1.71</v>
       </c>
       <c r="U21">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V21">
         <v>2.04</v>
       </c>
       <c r="W21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5823,7 +5823,7 @@
         <v>970</v>
       </c>
       <c r="Z21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5871,58 +5871,58 @@
         <v>26</v>
       </c>
       <c r="AP21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21">
         <v>1.22</v>
       </c>
       <c r="AR21">
+        <v>1.25</v>
+      </c>
+      <c r="AS21">
+        <v>1.3</v>
+      </c>
+      <c r="AT21">
+        <v>1.3</v>
+      </c>
+      <c r="AU21">
+        <v>1.2</v>
+      </c>
+      <c r="AV21">
         <v>1.24</v>
       </c>
-      <c r="AS21">
-        <v>1.28</v>
-      </c>
-      <c r="AT21">
-        <v>1.28</v>
-      </c>
-      <c r="AU21">
-        <v>1.18</v>
-      </c>
-      <c r="AV21">
-        <v>1.22</v>
-      </c>
       <c r="AW21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AX21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AZ21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BA21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BB21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BD21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BE21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BF21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BG21">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6005,19 +6005,19 @@
         <v>171</v>
       </c>
       <c r="F22">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G22">
         <v>2.04</v>
       </c>
       <c r="H22">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I22">
         <v>4.4</v>
       </c>
       <c r="J22">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K22">
         <v>4.2</v>
@@ -6029,7 +6029,7 @@
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O22">
         <v>1.26</v>
@@ -6038,19 +6038,19 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R22">
         <v>1.38</v>
       </c>
       <c r="S22">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T22">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V22">
         <v>1.29</v>
@@ -6113,58 +6113,58 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AQ22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AR22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AT22">
+        <v>1.15</v>
+      </c>
+      <c r="AU22">
+        <v>6.4</v>
+      </c>
+      <c r="AV22">
+        <v>1.23</v>
+      </c>
+      <c r="AW22">
+        <v>1.23</v>
+      </c>
+      <c r="AX22">
+        <v>1.23</v>
+      </c>
+      <c r="AY22">
         <v>7.2</v>
       </c>
-      <c r="AU22">
-        <v>1.12</v>
-      </c>
-      <c r="AV22">
-        <v>1.22</v>
-      </c>
-      <c r="AW22">
-        <v>1.22</v>
-      </c>
-      <c r="AX22">
-        <v>1.22</v>
-      </c>
-      <c r="AY22">
-        <v>1.14</v>
-      </c>
       <c r="AZ22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BA22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BB22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BD22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BE22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6250,19 +6250,19 @@
         <v>3.25</v>
       </c>
       <c r="G23">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I23">
         <v>2.26</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L23">
         <v>1.27</v>
@@ -6274,7 +6274,7 @@
         <v>5.1</v>
       </c>
       <c r="O23">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P23">
         <v>2.42</v>
@@ -6283,13 +6283,13 @@
         <v>1.59</v>
       </c>
       <c r="R23">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S23">
         <v>2.48</v>
       </c>
       <c r="T23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U23">
         <v>2.48</v>
@@ -6298,10 +6298,10 @@
         <v>1.8</v>
       </c>
       <c r="W23">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X23">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y23">
         <v>16</v>
@@ -6331,7 +6331,7 @@
         <v>17.5</v>
       </c>
       <c r="AH23">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI23">
         <v>34</v>
@@ -6349,13 +6349,13 @@
         <v>70</v>
       </c>
       <c r="AN23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AP23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ23">
         <v>11.5</v>
@@ -6376,7 +6376,7 @@
         <v>9.6</v>
       </c>
       <c r="AW23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX23">
         <v>21</v>
@@ -6391,16 +6391,16 @@
         <v>21</v>
       </c>
       <c r="BB23">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC23">
+        <v>5.2</v>
+      </c>
+      <c r="BD23">
+        <v>5.2</v>
+      </c>
+      <c r="BE23">
         <v>5.5</v>
-      </c>
-      <c r="BD23">
-        <v>5.6</v>
-      </c>
-      <c r="BE23">
-        <v>5.8</v>
       </c>
       <c r="BF23">
         <v>18.5</v>
@@ -6489,7 +6489,7 @@
         <v>173</v>
       </c>
       <c r="F24">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G24">
         <v>3.9</v>
@@ -6498,13 +6498,13 @@
         <v>2.02</v>
       </c>
       <c r="I24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J24">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L24">
         <v>1.31</v>
@@ -6516,13 +6516,13 @@
         <v>5.3</v>
       </c>
       <c r="O24">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
         <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R24">
         <v>1.59</v>
@@ -6537,58 +6537,58 @@
         <v>2.48</v>
       </c>
       <c r="V24">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W24">
         <v>1.34</v>
       </c>
       <c r="X24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z24">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE24">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AF24">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG24">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH24">
         <v>16</v>
       </c>
       <c r="AI24">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AJ24">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK24">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL24">
         <v>50</v>
       </c>
       <c r="AM24">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN24">
         <v>30</v>
@@ -6597,7 +6597,7 @@
         <v>10</v>
       </c>
       <c r="AP24">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="AQ24">
         <v>11.5</v>
@@ -6606,46 +6606,46 @@
         <v>13</v>
       </c>
       <c r="AS24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV24">
         <v>9.800000000000001</v>
       </c>
       <c r="AW24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX24">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AY24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA24">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BB24">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BC24">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BD24">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BE24">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="BF24">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BG24">
         <v>8.800000000000001</v>
@@ -6654,19 +6654,19 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="BN24">
         <v>1000</v>
@@ -6678,37 +6678,37 @@
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="CB24" t="s">
         <v>185</v>
@@ -6743,10 +6743,10 @@
         <v>2.62</v>
       </c>
       <c r="J25">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6770,7 +6770,7 @@
         <v>1.53</v>
       </c>
       <c r="S25">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T25">
         <v>1.51</v>
@@ -6827,7 +6827,7 @@
         <v>36</v>
       </c>
       <c r="AL25">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM25">
         <v>70</v>
@@ -6839,13 +6839,13 @@
         <v>15.5</v>
       </c>
       <c r="AP25">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ25">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS25">
         <v>4.7</v>
@@ -6854,10 +6854,10 @@
         <v>4.2</v>
       </c>
       <c r="AU25">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AV25">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AW25">
         <v>4.5</v>
@@ -6866,7 +6866,7 @@
         <v>4.6</v>
       </c>
       <c r="AY25">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AZ25">
         <v>4</v>
@@ -6875,7 +6875,7 @@
         <v>4.7</v>
       </c>
       <c r="BB25">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC25">
         <v>4.7</v>
@@ -6887,7 +6887,7 @@
         <v>5</v>
       </c>
       <c r="BF25">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG25">
         <v>4</v>
@@ -6982,13 +6982,13 @@
         <v>1.43</v>
       </c>
       <c r="I26">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J26">
         <v>5.1</v>
       </c>
       <c r="K26">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7000,28 +7000,28 @@
         <v>6.2</v>
       </c>
       <c r="O26">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q26">
         <v>1.46</v>
       </c>
       <c r="R26">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S26">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="T26">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U26">
         <v>2.24</v>
       </c>
       <c r="V26">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W26">
         <v>1.14</v>
@@ -7030,7 +7030,7 @@
         <v>38</v>
       </c>
       <c r="Y26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z26">
         <v>13</v>
@@ -7039,10 +7039,10 @@
         <v>14.5</v>
       </c>
       <c r="AB26">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD26">
         <v>11.5</v>
@@ -7057,7 +7057,7 @@
         <v>32</v>
       </c>
       <c r="AH26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI26">
         <v>32</v>
@@ -7066,7 +7066,7 @@
         <v>220</v>
       </c>
       <c r="AK26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL26">
         <v>80</v>
@@ -7081,13 +7081,13 @@
         <v>5.4</v>
       </c>
       <c r="AP26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ26">
         <v>11</v>
       </c>
       <c r="AR26">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS26">
         <v>11.5</v>
@@ -7120,16 +7120,16 @@
         <v>7.4</v>
       </c>
       <c r="BC26">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD26">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="BE26">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="BF26">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG26">
         <v>4.3</v>
@@ -7215,28 +7215,28 @@
         <v>176</v>
       </c>
       <c r="F27">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="G27">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I27">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N27">
         <v>2.14</v>
@@ -7266,7 +7266,7 @@
         <v>1.18</v>
       </c>
       <c r="W27">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7457,22 +7457,22 @@
         <v>177</v>
       </c>
       <c r="F28">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G28">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H28">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I28">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J28">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K28">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7484,7 +7484,7 @@
         <v>3.65</v>
       </c>
       <c r="O28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P28">
         <v>1.92</v>
@@ -7496,7 +7496,7 @@
         <v>1.32</v>
       </c>
       <c r="S28">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T28">
         <v>1.63</v>
@@ -7505,7 +7505,7 @@
         <v>2.14</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.68</v>
@@ -7535,19 +7535,19 @@
         <v>44</v>
       </c>
       <c r="AF28">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AG28">
         <v>12</v>
       </c>
       <c r="AH28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI28">
         <v>55</v>
       </c>
       <c r="AJ28">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK28">
         <v>29</v>
@@ -7562,61 +7562,61 @@
         <v>22</v>
       </c>
       <c r="AO28">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP28">
         <v>11.5</v>
       </c>
       <c r="AQ28">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU28">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV28">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW28">
+        <v>5.2</v>
+      </c>
+      <c r="AX28">
+        <v>12</v>
+      </c>
+      <c r="AY28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28">
+        <v>14.5</v>
+      </c>
+      <c r="BA28">
         <v>5.4</v>
       </c>
-      <c r="AX28">
-        <v>13</v>
-      </c>
-      <c r="AY28">
-        <v>9.6</v>
-      </c>
-      <c r="AZ28">
-        <v>14</v>
-      </c>
-      <c r="BA28">
-        <v>5.6</v>
-      </c>
       <c r="BB28">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BC28">
         <v>21</v>
       </c>
       <c r="BD28">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE28">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BF28">
         <v>14</v>
       </c>
       <c r="BG28">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7699,55 +7699,55 @@
         <v>178</v>
       </c>
       <c r="F29">
-        <v>3.85</v>
+        <v>1.12</v>
       </c>
       <c r="G29">
-        <v>5.1</v>
+        <v>990</v>
       </c>
       <c r="H29">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="I29">
-        <v>2.16</v>
+        <v>990</v>
       </c>
       <c r="J29">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="O29">
         <v>1.38</v>
       </c>
       <c r="P29">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="Q29">
-        <v>2.16</v>
+        <v>1.38</v>
       </c>
       <c r="R29">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S29">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="T29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V29">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="W29">
         <v>1.24</v>
@@ -7944,10 +7944,10 @@
         <v>2.5</v>
       </c>
       <c r="G30">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H30">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I30">
         <v>3.55</v>
@@ -7956,13 +7956,13 @@
         <v>3.1</v>
       </c>
       <c r="K30">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L30">
         <v>1.6</v>
       </c>
       <c r="M30">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N30">
         <v>2.64</v>
@@ -8025,25 +8025,25 @@
         <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI30">
         <v>80</v>
       </c>
       <c r="AJ30">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK30">
         <v>40</v>
       </c>
       <c r="AL30">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM30">
         <v>1000</v>
       </c>
       <c r="AN30">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO30">
         <v>80</v>
@@ -8052,7 +8052,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR30">
         <v>18.5</v>
@@ -8070,10 +8070,10 @@
         <v>14.5</v>
       </c>
       <c r="AW30">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY30">
         <v>12</v>
@@ -8082,19 +8082,19 @@
         <v>21</v>
       </c>
       <c r="BA30">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB30">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BC30">
         <v>24</v>
       </c>
       <c r="BD30">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE30">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BF30">
         <v>23</v>
@@ -8133,7 +8133,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BR30">
-        <v>840</v>
+        <v>750</v>
       </c>
       <c r="BS30">
         <v>12.5</v>
@@ -8145,13 +8145,13 @@
         <v>5.8</v>
       </c>
       <c r="BV30">
-        <v>840</v>
+        <v>36</v>
       </c>
       <c r="BW30">
         <v>11.5</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="BY30">
         <v>13.5</v>
@@ -8183,10 +8183,10 @@
         <v>180</v>
       </c>
       <c r="F31">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G31">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="H31">
         <v>3</v>
@@ -8213,37 +8213,37 @@
         <v>1.32</v>
       </c>
       <c r="P31">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
         <v>1.96</v>
       </c>
       <c r="R31">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S31">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="T31">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U31">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V31">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X31">
         <v>15</v>
       </c>
       <c r="Y31">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA31">
         <v>60</v>
@@ -8252,10 +8252,10 @@
         <v>11.5</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD31">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE31">
         <v>40</v>
@@ -8273,10 +8273,10 @@
         <v>55</v>
       </c>
       <c r="AJ31">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK31">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL31">
         <v>46</v>
@@ -8285,7 +8285,7 @@
         <v>110</v>
       </c>
       <c r="AN31">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO31">
         <v>36</v>
@@ -8303,7 +8303,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU31">
         <v>7.2</v>
@@ -8315,7 +8315,7 @@
         <v>7.6</v>
       </c>
       <c r="AX31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8330,7 +8330,7 @@
         <v>7.6</v>
       </c>
       <c r="BC31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD31">
         <v>7.8</v>
@@ -8339,7 +8339,7 @@
         <v>8.6</v>
       </c>
       <c r="BF31">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG31">
         <v>7.4</v>
@@ -8354,7 +8354,7 @@
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8366,7 +8366,7 @@
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="BP31">
         <v>1000</v>
@@ -8384,7 +8384,7 @@
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8437,13 +8437,13 @@
         <v>4</v>
       </c>
       <c r="J32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K32">
         <v>3.6</v>
       </c>
       <c r="L32">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M32">
         <v>1.08</v>
@@ -8452,7 +8452,7 @@
         <v>3.4</v>
       </c>
       <c r="O32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P32">
         <v>1.86</v>
@@ -8503,7 +8503,7 @@
         <v>60</v>
       </c>
       <c r="AF32">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG32">
         <v>11</v>
@@ -8539,10 +8539,10 @@
         <v>11.5</v>
       </c>
       <c r="AR32">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AS32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT32">
         <v>8</v>
@@ -8554,7 +8554,7 @@
         <v>14</v>
       </c>
       <c r="AW32">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX32">
         <v>11.5</v>
@@ -8587,7 +8587,7 @@
         <v>10</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI32">
         <v>2.7</v>
@@ -8596,13 +8596,13 @@
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BN32">
         <v>1000</v>
@@ -8614,37 +8614,37 @@
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CB32" t="s">
         <v>185</v>
@@ -8667,22 +8667,22 @@
         <v>182</v>
       </c>
       <c r="F33">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G33">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I33">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J33">
         <v>3.6</v>
       </c>
       <c r="K33">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L33">
         <v>1.33</v>
@@ -8697,16 +8697,16 @@
         <v>1.27</v>
       </c>
       <c r="P33">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q33">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="R33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S33">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T33">
         <v>1.7</v>
@@ -8721,7 +8721,7 @@
         <v>1.8</v>
       </c>
       <c r="X33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y33">
         <v>18.5</v>
@@ -8730,19 +8730,19 @@
         <v>34</v>
       </c>
       <c r="AA33">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB33">
         <v>11</v>
       </c>
       <c r="AC33">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD33">
         <v>18.5</v>
       </c>
       <c r="AE33">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF33">
         <v>15</v>
@@ -8769,7 +8769,7 @@
         <v>100</v>
       </c>
       <c r="AN33">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AO33">
         <v>46</v>
@@ -8784,7 +8784,7 @@
         <v>19.5</v>
       </c>
       <c r="AS33">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT33">
         <v>9.4</v>
@@ -8796,10 +8796,10 @@
         <v>13</v>
       </c>
       <c r="AW33">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY33">
         <v>9.6</v>
@@ -8808,7 +8808,7 @@
         <v>14.5</v>
       </c>
       <c r="BA33">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB33">
         <v>19.5</v>
@@ -8817,76 +8817,76 @@
         <v>16</v>
       </c>
       <c r="BD33">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE33">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BF33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG33">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
         <v>185</v>
@@ -8912,7 +8912,7 @@
         <v>3.1</v>
       </c>
       <c r="G34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H34">
         <v>2.56</v>
@@ -8924,7 +8924,7 @@
         <v>3.2</v>
       </c>
       <c r="K34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L34">
         <v>1.51</v>
@@ -8936,7 +8936,7 @@
         <v>2.98</v>
       </c>
       <c r="O34">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P34">
         <v>1.66</v>
@@ -8975,25 +8975,25 @@
         <v>46</v>
       </c>
       <c r="AB34">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC34">
         <v>7.6</v>
       </c>
       <c r="AD34">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE34">
         <v>40</v>
       </c>
       <c r="AF34">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AG34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI34">
         <v>65</v>
@@ -9026,7 +9026,7 @@
         <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT34">
         <v>9.199999999999999</v>
@@ -9038,7 +9038,7 @@
         <v>10.5</v>
       </c>
       <c r="AW34">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX34">
         <v>17.5</v>
@@ -9050,85 +9050,85 @@
         <v>17.5</v>
       </c>
       <c r="BA34">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB34">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC34">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BD34">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE34">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF34">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG34">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH34">
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="s">
         <v>185</v>
@@ -9160,7 +9160,7 @@
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J35">
         <v>3.4</v>
@@ -9181,28 +9181,28 @@
         <v>1.51</v>
       </c>
       <c r="P35">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q35">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S35">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T35">
         <v>2.24</v>
       </c>
       <c r="U35">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V35">
         <v>1.2</v>
       </c>
       <c r="W35">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X35">
         <v>9.6</v>
@@ -9211,7 +9211,7 @@
         <v>14.5</v>
       </c>
       <c r="Z35">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA35">
         <v>230</v>
@@ -9256,7 +9256,7 @@
         <v>19.5</v>
       </c>
       <c r="AO35">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP35">
         <v>8.6</v>
@@ -9265,13 +9265,13 @@
         <v>12.5</v>
       </c>
       <c r="AR35">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT35">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU35">
         <v>7.2</v>
@@ -9289,88 +9289,88 @@
         <v>9.6</v>
       </c>
       <c r="AZ35">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BA35">
         <v>11</v>
       </c>
       <c r="BB35">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC35">
         <v>21</v>
       </c>
       <c r="BD35">
-        <v>26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF35">
         <v>16.5</v>
       </c>
       <c r="BG35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH35">
         <v>1000</v>
       </c>
       <c r="BI35">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BJ35">
         <v>1000</v>
       </c>
       <c r="BK35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="BN35">
         <v>1000</v>
       </c>
       <c r="BO35">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BP35">
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="BT35">
         <v>1000</v>
       </c>
       <c r="BU35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="s">
         <v>185</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -571,7 +571,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 12:35:32</t>
+    <t>2026-10-01 14:51:46</t>
   </si>
 </sst>
 </file>
@@ -1165,25 +1165,25 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>6.6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -1195,28 +1195,28 @@
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q2">
         <v>2.08</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
         <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X2">
         <v>13.5</v>
@@ -1228,19 +1228,19 @@
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AB2">
         <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF2">
         <v>9.199999999999999</v>
@@ -1264,16 +1264,16 @@
         <v>42</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO2">
         <v>150</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
         <v>16.5</v>
@@ -1282,7 +1282,7 @@
         <v>42</v>
       </c>
       <c r="AS2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT2">
         <v>7</v>
@@ -1291,13 +1291,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW2">
         <v>13</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
@@ -1309,49 +1309,49 @@
         <v>13</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BL2">
         <v>190</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ2">
         <v>8.4</v>
@@ -1360,7 +1360,7 @@
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
         <v>10.5</v>
@@ -1372,19 +1372,19 @@
         <v>65</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>70</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
         <v>185</v>
@@ -1407,226 +1407,226 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="G3">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="I3">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
         <v>1.6</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T3">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V3">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="W3">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="X3">
+        <v>23</v>
+      </c>
+      <c r="Y3">
+        <v>12</v>
+      </c>
+      <c r="Z3">
+        <v>13</v>
+      </c>
+      <c r="AA3">
+        <v>19</v>
+      </c>
+      <c r="AB3">
+        <v>23</v>
+      </c>
+      <c r="AC3">
+        <v>10.5</v>
+      </c>
+      <c r="AD3">
+        <v>10.5</v>
+      </c>
+      <c r="AE3">
+        <v>16</v>
+      </c>
+      <c r="AF3">
+        <v>55</v>
+      </c>
+      <c r="AG3">
+        <v>19</v>
+      </c>
+      <c r="AH3">
+        <v>17.5</v>
+      </c>
+      <c r="AI3">
         <v>26</v>
       </c>
-      <c r="Y3">
-        <v>13.5</v>
-      </c>
-      <c r="Z3">
-        <v>16</v>
-      </c>
-      <c r="AA3">
-        <v>26</v>
-      </c>
-      <c r="AB3">
-        <v>19.5</v>
-      </c>
-      <c r="AC3">
-        <v>10</v>
-      </c>
-      <c r="AD3">
-        <v>11</v>
-      </c>
-      <c r="AE3">
-        <v>18.5</v>
-      </c>
-      <c r="AF3">
-        <v>32</v>
-      </c>
-      <c r="AG3">
-        <v>15.5</v>
-      </c>
-      <c r="AH3">
-        <v>15</v>
-      </c>
-      <c r="AI3">
-        <v>27</v>
-      </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AK3">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AM3">
         <v>70</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AO3">
+        <v>9.6</v>
+      </c>
+      <c r="AP3">
+        <v>20</v>
+      </c>
+      <c r="AQ3">
+        <v>10.5</v>
+      </c>
+      <c r="AR3">
+        <v>11.5</v>
+      </c>
+      <c r="AS3">
+        <v>17.5</v>
+      </c>
+      <c r="AT3">
+        <v>20</v>
+      </c>
+      <c r="AU3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW3">
+        <v>14</v>
+      </c>
+      <c r="AX3">
+        <v>34</v>
+      </c>
+      <c r="AY3">
+        <v>16.5</v>
+      </c>
+      <c r="AZ3">
+        <v>15</v>
+      </c>
+      <c r="BA3">
+        <v>22</v>
+      </c>
+      <c r="BB3">
+        <v>65</v>
+      </c>
+      <c r="BC3">
+        <v>42</v>
+      </c>
+      <c r="BD3">
+        <v>40</v>
+      </c>
+      <c r="BE3">
+        <v>55</v>
+      </c>
+      <c r="BF3">
+        <v>32</v>
+      </c>
+      <c r="BG3">
+        <v>7.6</v>
+      </c>
+      <c r="BH3">
+        <v>4.3</v>
+      </c>
+      <c r="BI3">
+        <v>3.85</v>
+      </c>
+      <c r="BJ3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK3">
+        <v>5.8</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>13</v>
+      </c>
+      <c r="BN3">
+        <v>8.4</v>
+      </c>
+      <c r="BO3">
+        <v>5.5</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>10.5</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
         <v>11</v>
       </c>
-      <c r="AP3">
-        <v>19.5</v>
-      </c>
-      <c r="AQ3">
+      <c r="BT3">
+        <v>4.8</v>
+      </c>
+      <c r="BU3">
+        <v>3.85</v>
+      </c>
+      <c r="BV3">
         <v>11.5</v>
       </c>
-      <c r="AR3">
-        <v>14</v>
-      </c>
-      <c r="AS3">
-        <v>20</v>
-      </c>
-      <c r="AT3">
-        <v>17.5</v>
-      </c>
-      <c r="AU3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3">
-        <v>9.4</v>
-      </c>
-      <c r="AW3">
-        <v>16</v>
-      </c>
-      <c r="AX3">
-        <v>24</v>
-      </c>
-      <c r="AY3">
-        <v>13</v>
-      </c>
-      <c r="AZ3">
-        <v>13</v>
-      </c>
-      <c r="BA3">
-        <v>23</v>
-      </c>
-      <c r="BB3">
-        <v>42</v>
-      </c>
-      <c r="BC3">
-        <v>26</v>
-      </c>
-      <c r="BD3">
-        <v>27</v>
-      </c>
-      <c r="BE3">
-        <v>50</v>
-      </c>
-      <c r="BF3">
-        <v>19.5</v>
-      </c>
-      <c r="BG3">
-        <v>10</v>
-      </c>
-      <c r="BH3">
-        <v>4.2</v>
-      </c>
-      <c r="BI3">
-        <v>3.4</v>
-      </c>
-      <c r="BJ3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK3">
-        <v>5.6</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>12.5</v>
-      </c>
-      <c r="BN3">
-        <v>7.2</v>
-      </c>
-      <c r="BO3">
-        <v>5.6</v>
-      </c>
-      <c r="BP3">
-        <v>26</v>
-      </c>
-      <c r="BQ3">
-        <v>9.6</v>
-      </c>
-      <c r="BR3">
-        <v>32</v>
-      </c>
-      <c r="BS3">
-        <v>10</v>
-      </c>
-      <c r="BT3">
-        <v>5.3</v>
-      </c>
-      <c r="BU3">
-        <v>4.2</v>
-      </c>
-      <c r="BV3">
-        <v>14</v>
-      </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BY3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CA3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="s">
         <v>185</v>
@@ -1661,13 +1661,13 @@
         <v>1.11</v>
       </c>
       <c r="J4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="K4">
         <v>16</v>
       </c>
       <c r="L4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M4">
         <v>1.01</v>
@@ -1685,19 +1685,19 @@
         <v>1.4</v>
       </c>
       <c r="R4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S4">
         <v>2</v>
       </c>
       <c r="T4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
         <v>1.41</v>
       </c>
       <c r="V4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>1.02</v>
@@ -1709,10 +1709,10 @@
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AB4">
         <v>120</v>
@@ -1757,7 +1757,7 @@
         <v>2.6</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AQ4">
         <v>10</v>
@@ -1769,10 +1769,10 @@
         <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU4">
-        <v>29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
@@ -1781,43 +1781,43 @@
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BB4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG4">
         <v>2.32</v>
       </c>
       <c r="BH4">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BI4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BK4">
         <v>8.4</v>
@@ -1829,7 +1829,7 @@
         <v>13</v>
       </c>
       <c r="BN4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BO4">
         <v>9.800000000000001</v>
@@ -1838,7 +1838,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1862,13 +1862,13 @@
         <v>29</v>
       </c>
       <c r="BY4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CA4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB4" t="s">
         <v>185</v>
@@ -1897,10 +1897,10 @@
         <v>3.05</v>
       </c>
       <c r="H5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I5">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J5">
         <v>3.2</v>
@@ -1915,13 +1915,13 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q5">
         <v>2.08</v>
@@ -1930,7 +1930,7 @@
         <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
         <v>1.79</v>
@@ -1939,13 +1939,13 @@
         <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
         <v>1.48</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
         <v>11</v>
@@ -1981,7 +1981,7 @@
         <v>48</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK5">
         <v>36</v>
@@ -1990,7 +1990,7 @@
         <v>50</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN5">
         <v>34</v>
@@ -2044,7 +2044,7 @@
         <v>40</v>
       </c>
       <c r="BE5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF5">
         <v>26</v>
@@ -2059,58 +2059,58 @@
         <v>2.7</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
+        <v>6.8</v>
+      </c>
+      <c r="BN5">
         <v>6.2</v>
       </c>
-      <c r="BN5">
-        <v>6.6</v>
-      </c>
       <c r="BO5">
+        <v>5.1</v>
+      </c>
+      <c r="BP5">
+        <v>27</v>
+      </c>
+      <c r="BQ5">
+        <v>5.7</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>6</v>
+      </c>
+      <c r="BT5">
+        <v>6.4</v>
+      </c>
+      <c r="BU5">
         <v>4.8</v>
       </c>
-      <c r="BP5">
-        <v>26</v>
-      </c>
-      <c r="BQ5">
-        <v>5.1</v>
-      </c>
-      <c r="BR5">
-        <v>44</v>
-      </c>
-      <c r="BS5">
-        <v>5.6</v>
-      </c>
-      <c r="BT5">
-        <v>6.2</v>
-      </c>
-      <c r="BU5">
-        <v>4.5</v>
-      </c>
       <c r="BV5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BX5">
         <v>40</v>
       </c>
       <c r="BY5">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CA5">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="CB5" t="s">
         <v>185</v>
@@ -2133,13 +2133,13 @@
         <v>155</v>
       </c>
       <c r="F6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I6">
         <v>6.2</v>
@@ -2148,7 +2148,7 @@
         <v>5.1</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L6">
         <v>1.23</v>
@@ -2157,7 +2157,7 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O6">
         <v>1.12</v>
@@ -2169,13 +2169,13 @@
         <v>1.39</v>
       </c>
       <c r="R6">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U6">
         <v>2.76</v>
@@ -2190,16 +2190,16 @@
         <v>38</v>
       </c>
       <c r="Y6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA6">
         <v>190</v>
       </c>
       <c r="AB6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC6">
         <v>13</v>
@@ -2220,10 +2220,10 @@
         <v>17</v>
       </c>
       <c r="AI6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK6">
         <v>14</v>
@@ -2238,16 +2238,16 @@
         <v>4.7</v>
       </c>
       <c r="AO6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP6">
         <v>32</v>
       </c>
       <c r="AQ6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AR6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS6">
         <v>42</v>
@@ -2283,7 +2283,7 @@
         <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE6">
         <v>46</v>
@@ -2292,28 +2292,28 @@
         <v>4.4</v>
       </c>
       <c r="BG6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH6">
         <v>5.4</v>
       </c>
       <c r="BI6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ6">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>65</v>
       </c>
       <c r="BM6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO6">
         <v>4.4</v>
@@ -2322,37 +2322,37 @@
         <v>9</v>
       </c>
       <c r="BQ6">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
         <v>17</v>
       </c>
       <c r="BS6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6">
         <v>10</v>
       </c>
       <c r="BU6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BV6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX6">
         <v>34</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>9.4</v>
       </c>
       <c r="CA6">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="s">
         <v>185</v>
@@ -2375,31 +2375,31 @@
         <v>156</v>
       </c>
       <c r="F7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="I7">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="J7">
         <v>4.5</v>
       </c>
       <c r="K7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
         <v>1.37</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O7">
         <v>1.28</v>
@@ -2408,7 +2408,7 @@
         <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R7">
         <v>1.43</v>
@@ -2420,28 +2420,28 @@
         <v>2</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="V7">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
@@ -2456,7 +2456,7 @@
         <v>75</v>
       </c>
       <c r="AG7">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AH7">
         <v>29</v>
@@ -2468,7 +2468,7 @@
         <v>260</v>
       </c>
       <c r="AK7">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AL7">
         <v>120</v>
@@ -2480,19 +2480,19 @@
         <v>170</v>
       </c>
       <c r="AO7">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AP7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
         <v>20</v>
@@ -2510,19 +2510,19 @@
         <v>46</v>
       </c>
       <c r="AY7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA7">
         <v>30</v>
       </c>
       <c r="BB7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BD7">
         <v>55</v>
@@ -2531,22 +2531,22 @@
         <v>85</v>
       </c>
       <c r="BF7">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
         <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2555,31 +2555,31 @@
         <v>3.15</v>
       </c>
       <c r="BN7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BU7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BV7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BW7">
         <v>6</v>
@@ -2588,7 +2588,7 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
@@ -2620,7 +2620,7 @@
         <v>2.7</v>
       </c>
       <c r="G8">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H8">
         <v>2.42</v>
@@ -2629,10 +2629,10 @@
         <v>2.82</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2641,28 +2641,28 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T8">
         <v>1.75</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
         <v>1.55</v>
@@ -2859,61 +2859,61 @@
         <v>158</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>1.91</v>
       </c>
       <c r="H9">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>1.11</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>1.24</v>
+        <v>2.72</v>
       </c>
       <c r="O9">
         <v>1.42</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q9">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>2.98</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y9">
         <v>1000</v>
@@ -2925,7 +2925,7 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC9">
         <v>1000</v>
@@ -2967,58 +2967,58 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3042,7 +3042,7 @@
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BP9">
         <v>1000</v>
@@ -3113,10 +3113,10 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3343,22 +3343,22 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>1.87</v>
       </c>
       <c r="H11">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3367,40 +3367,40 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q11">
-        <v>1.08</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
-        <v>1.08</v>
+        <v>2.42</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X11">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y11">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z11">
         <v>50</v>
@@ -3412,7 +3412,7 @@
         <v>10.5</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD11">
         <v>25</v>
@@ -3421,13 +3421,13 @@
         <v>80</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI11">
         <v>85</v>
@@ -3436,7 +3436,7 @@
         <v>22</v>
       </c>
       <c r="AK11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL11">
         <v>40</v>
@@ -3445,7 +3445,7 @@
         <v>130</v>
       </c>
       <c r="AN11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO11">
         <v>95</v>
@@ -3454,37 +3454,37 @@
         <v>12</v>
       </c>
       <c r="AQ11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR11">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS11">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT11">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV11">
         <v>16</v>
       </c>
       <c r="AW11">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AX11">
         <v>8.4</v>
       </c>
       <c r="AY11">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11">
         <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB11">
         <v>14.5</v>
@@ -3493,16 +3493,16 @@
         <v>14</v>
       </c>
       <c r="BD11">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE11">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF11">
         <v>8.4</v>
       </c>
       <c r="BG11">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3594,7 +3594,7 @@
         <v>2.16</v>
       </c>
       <c r="I12">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J12">
         <v>3.25</v>
@@ -3633,7 +3633,7 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
         <v>1.42</v>
@@ -3827,22 +3827,22 @@
         <v>162</v>
       </c>
       <c r="F13">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I13">
         <v>3.3</v>
       </c>
       <c r="J13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L13">
         <v>1.18</v>
@@ -3851,34 +3851,34 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O13">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P13">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q13">
         <v>1.36</v>
       </c>
       <c r="R13">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="T13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U13">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V13">
         <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="X13">
         <v>50</v>
@@ -3893,25 +3893,25 @@
         <v>65</v>
       </c>
       <c r="AB13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD13">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF13">
         <v>25</v>
       </c>
       <c r="AG13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI13">
         <v>32</v>
@@ -3923,28 +3923,28 @@
         <v>22</v>
       </c>
       <c r="AL13">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AM13">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AN13">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP13">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13">
         <v>20</v>
       </c>
       <c r="AR13">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS13">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT13">
         <v>18.5</v>
@@ -3953,7 +3953,7 @@
         <v>11</v>
       </c>
       <c r="AV13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW13">
         <v>21</v>
@@ -3968,34 +3968,34 @@
         <v>12</v>
       </c>
       <c r="BA13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB13">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC13">
         <v>16</v>
       </c>
       <c r="BD13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE13">
+        <v>7</v>
+      </c>
+      <c r="BF13">
+        <v>6.2</v>
+      </c>
+      <c r="BG13">
+        <v>11</v>
+      </c>
+      <c r="BH13">
         <v>5.8</v>
-      </c>
-      <c r="BF13">
-        <v>6.4</v>
-      </c>
-      <c r="BG13">
-        <v>11.5</v>
-      </c>
-      <c r="BH13">
-        <v>6.6</v>
       </c>
       <c r="BI13">
         <v>5</v>
       </c>
       <c r="BJ13">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK13">
         <v>6.4</v>
@@ -4016,16 +4016,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR13">
         <v>20</v>
       </c>
       <c r="BS13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT13">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU13">
         <v>6</v>
@@ -4034,10 +4034,10 @@
         <v>23</v>
       </c>
       <c r="BW13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BY13">
         <v>5.5</v>
@@ -4105,7 +4105,7 @@
         <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
         <v>2.68</v>
@@ -4120,7 +4120,7 @@
         <v>1.37</v>
       </c>
       <c r="W14">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4311,40 +4311,40 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>4.7</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I15">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="J15">
         <v>3.2</v>
       </c>
       <c r="K15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
         <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="R15">
         <v>1.41</v>
@@ -4353,16 +4353,16 @@
         <v>2.28</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V15">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W15">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4577,7 +4577,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="O16">
         <v>1.17</v>
@@ -4595,10 +4595,10 @@
         <v>2.28</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V16">
         <v>1.14</v>
@@ -4798,7 +4798,7 @@
         <v>2.82</v>
       </c>
       <c r="G17">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H17">
         <v>3.2</v>
@@ -4807,7 +4807,7 @@
         <v>3.45</v>
       </c>
       <c r="J17">
-        <v>1.12</v>
+        <v>2.64</v>
       </c>
       <c r="K17">
         <v>3</v>
@@ -4819,7 +4819,7 @@
         <v>1.15</v>
       </c>
       <c r="N17">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O17">
         <v>1.6</v>
@@ -4834,7 +4834,7 @@
         <v>1.17</v>
       </c>
       <c r="S17">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="T17">
         <v>2.16</v>
@@ -4843,10 +4843,10 @@
         <v>1.71</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X17">
         <v>8.6</v>
@@ -4861,10 +4861,10 @@
         <v>80</v>
       </c>
       <c r="AB17">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AD17">
         <v>18</v>
@@ -4873,13 +4873,13 @@
         <v>65</v>
       </c>
       <c r="AF17">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG17">
         <v>16.5</v>
       </c>
       <c r="AH17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI17">
         <v>100</v>
@@ -4903,58 +4903,58 @@
         <v>90</v>
       </c>
       <c r="AP17">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="AQ17">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="AR17">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AS17">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT17">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU17">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="AV17">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AW17">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX17">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AY17">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17">
+        <v>18.5</v>
+      </c>
+      <c r="BA17">
+        <v>5.3</v>
+      </c>
+      <c r="BB17">
         <v>5.2</v>
       </c>
-      <c r="BA17">
-        <v>6</v>
-      </c>
-      <c r="BB17">
-        <v>5.8</v>
-      </c>
       <c r="BC17">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD17">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BE17">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF17">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG17">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5043,10 +5043,10 @@
         <v>2.98</v>
       </c>
       <c r="H18">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I18">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J18">
         <v>3.15</v>
@@ -5058,70 +5058,70 @@
         <v>1.48</v>
       </c>
       <c r="M18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N18">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="O18">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P18">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S18">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T18">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U18">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="V18">
+        <v>1.51</v>
+      </c>
+      <c r="W18">
         <v>1.5</v>
       </c>
-      <c r="W18">
-        <v>1.51</v>
-      </c>
       <c r="X18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>17.5</v>
       </c>
       <c r="AA18">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB18">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE18">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG18">
         <v>14.5</v>
       </c>
       <c r="AH18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI18">
         <v>65</v>
@@ -5130,73 +5130,73 @@
         <v>55</v>
       </c>
       <c r="AK18">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AL18">
         <v>65</v>
       </c>
       <c r="AM18">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN18">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO18">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP18">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR18">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS18">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AT18">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU18">
         <v>6.6</v>
       </c>
       <c r="AV18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX18">
         <v>15</v>
       </c>
       <c r="AY18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA18">
         <v>50</v>
       </c>
       <c r="BB18">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BC18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD18">
         <v>50</v>
       </c>
       <c r="BE18">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG18">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH18">
         <v>3.1</v>
@@ -5208,7 +5208,7 @@
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>2.48</v>
+        <v>7.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5235,7 +5235,7 @@
         <v>2.88</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU18">
         <v>2.08</v>
@@ -5312,7 +5312,7 @@
         <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R19">
         <v>1.55</v>
@@ -5536,7 +5536,7 @@
         <v>3.9</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5545,10 +5545,10 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P20">
         <v>2.26</v>
@@ -5644,7 +5644,7 @@
         <v>1.15</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>1.08</v>
       </c>
       <c r="AV20">
         <v>1.11</v>
@@ -5763,13 +5763,13 @@
         <v>170</v>
       </c>
       <c r="F21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G21">
         <v>4.6</v>
       </c>
       <c r="H21">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I21">
         <v>1.96</v>
@@ -5778,7 +5778,7 @@
         <v>3.8</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -5802,7 +5802,7 @@
         <v>1.38</v>
       </c>
       <c r="S21">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T21">
         <v>1.71</v>
@@ -6011,13 +6011,13 @@
         <v>2.04</v>
       </c>
       <c r="H22">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I22">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J22">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K22">
         <v>4.2</v>
@@ -6038,13 +6038,13 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R22">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S22">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T22">
         <v>1.66</v>
@@ -6053,7 +6053,7 @@
         <v>2.08</v>
       </c>
       <c r="V22">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W22">
         <v>1.96</v>
@@ -6128,7 +6128,7 @@
         <v>1.15</v>
       </c>
       <c r="AU22">
-        <v>6.4</v>
+        <v>1.13</v>
       </c>
       <c r="AV22">
         <v>1.23</v>
@@ -6140,7 +6140,7 @@
         <v>1.23</v>
       </c>
       <c r="AY22">
-        <v>7.2</v>
+        <v>1.15</v>
       </c>
       <c r="AZ22">
         <v>1.23</v>
@@ -6247,22 +6247,22 @@
         <v>172</v>
       </c>
       <c r="F23">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I23">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J23">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>1.27</v>
@@ -6295,10 +6295,10 @@
         <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W23">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X23">
         <v>27</v>
@@ -6307,7 +6307,7 @@
         <v>16</v>
       </c>
       <c r="Z23">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA23">
         <v>32</v>
@@ -6331,7 +6331,7 @@
         <v>17.5</v>
       </c>
       <c r="AH23">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI23">
         <v>34</v>
@@ -6352,7 +6352,7 @@
         <v>29</v>
       </c>
       <c r="AO23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP23">
         <v>17.5</v>
@@ -6391,16 +6391,16 @@
         <v>21</v>
       </c>
       <c r="BB23">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC23">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD23">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE23">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF23">
         <v>18.5</v>
@@ -6489,25 +6489,25 @@
         <v>173</v>
       </c>
       <c r="F24">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G24">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H24">
         <v>2.02</v>
       </c>
       <c r="I24">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K24">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L24">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="M24">
         <v>1.04</v>
@@ -6522,25 +6522,25 @@
         <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R24">
         <v>1.59</v>
       </c>
       <c r="S24">
+        <v>2.54</v>
+      </c>
+      <c r="T24">
+        <v>1.58</v>
+      </c>
+      <c r="U24">
         <v>2.52</v>
       </c>
-      <c r="T24">
-        <v>1.59</v>
-      </c>
-      <c r="U24">
-        <v>2.48</v>
-      </c>
       <c r="V24">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W24">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X24">
         <v>23</v>
@@ -6552,7 +6552,7 @@
         <v>15.5</v>
       </c>
       <c r="AA24">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB24">
         <v>20</v>
@@ -6576,7 +6576,7 @@
         <v>16</v>
       </c>
       <c r="AI24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ24">
         <v>75</v>
@@ -6594,7 +6594,7 @@
         <v>30</v>
       </c>
       <c r="AO24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP24">
         <v>19</v>
@@ -6603,7 +6603,7 @@
         <v>11.5</v>
       </c>
       <c r="AR24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS24">
         <v>21</v>
@@ -6645,7 +6645,7 @@
         <v>50</v>
       </c>
       <c r="BF24">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BG24">
         <v>8.800000000000001</v>
@@ -6654,19 +6654,19 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="BN24">
         <v>1000</v>
@@ -6678,37 +6678,37 @@
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="CB24" t="s">
         <v>185</v>
@@ -6731,19 +6731,19 @@
         <v>174</v>
       </c>
       <c r="F25">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G25">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H25">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I25">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J25">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K25">
         <v>4.4</v>
@@ -6755,13 +6755,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="O25">
         <v>1.19</v>
       </c>
       <c r="P25">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
         <v>1.56</v>
@@ -6791,7 +6791,7 @@
         <v>16.5</v>
       </c>
       <c r="Z25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA25">
         <v>38</v>
@@ -6806,10 +6806,10 @@
         <v>13.5</v>
       </c>
       <c r="AE25">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF25">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG25">
         <v>15</v>
@@ -6827,37 +6827,37 @@
         <v>36</v>
       </c>
       <c r="AL25">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM25">
         <v>70</v>
       </c>
       <c r="AN25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT25">
         <v>4.2</v>
       </c>
       <c r="AU25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV25">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW25">
         <v>4.5</v>
@@ -6866,31 +6866,31 @@
         <v>4.6</v>
       </c>
       <c r="AY25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC25">
         <v>4.7</v>
       </c>
       <c r="BD25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE25">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF25">
         <v>4.4</v>
       </c>
       <c r="BG25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6973,82 +6973,82 @@
         <v>175</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="G26">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H26">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="I26">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="J26">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="K26">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N26">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P26">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="Q26">
         <v>1.46</v>
       </c>
       <c r="R26">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="S26">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="T26">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U26">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V26">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>38</v>
       </c>
       <c r="Y26">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z26">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA26">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB26">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AC26">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AD26">
         <v>11.5</v>
       </c>
       <c r="AE26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF26">
         <v>80</v>
@@ -7057,7 +7057,7 @@
         <v>32</v>
       </c>
       <c r="AH26">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI26">
         <v>32</v>
@@ -7075,37 +7075,37 @@
         <v>90</v>
       </c>
       <c r="AN26">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AO26">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AP26">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ26">
+        <v>11.5</v>
+      </c>
+      <c r="AR26">
+        <v>9.6</v>
+      </c>
+      <c r="AS26">
         <v>11</v>
       </c>
-      <c r="AR26">
-        <v>10</v>
-      </c>
-      <c r="AS26">
+      <c r="AT26">
+        <v>7.8</v>
+      </c>
+      <c r="AU26">
+        <v>12</v>
+      </c>
+      <c r="AV26">
+        <v>9.4</v>
+      </c>
+      <c r="AW26">
         <v>11.5</v>
       </c>
-      <c r="AT26">
-        <v>6.2</v>
-      </c>
-      <c r="AU26">
-        <v>11</v>
-      </c>
-      <c r="AV26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW26">
-        <v>12</v>
-      </c>
       <c r="AX26">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AY26">
         <v>21</v>
@@ -7117,22 +7117,22 @@
         <v>21</v>
       </c>
       <c r="BB26">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC26">
         <v>27</v>
       </c>
       <c r="BD26">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BE26">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BF26">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BG26">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7215,10 +7215,10 @@
         <v>176</v>
       </c>
       <c r="F27">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G27">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H27">
         <v>4.1</v>
@@ -7236,10 +7236,10 @@
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O27">
         <v>1.51</v>
@@ -7248,7 +7248,7 @@
         <v>1.4</v>
       </c>
       <c r="Q27">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R27">
         <v>1.18</v>
@@ -7263,10 +7263,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W27">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7457,22 +7457,22 @@
         <v>177</v>
       </c>
       <c r="F28">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G28">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H28">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I28">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J28">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K28">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7481,34 +7481,34 @@
         <v>1.06</v>
       </c>
       <c r="N28">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P28">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q28">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R28">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S28">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T28">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="U28">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X28">
         <v>17.5</v>
@@ -7523,7 +7523,7 @@
         <v>70</v>
       </c>
       <c r="AB28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC28">
         <v>8.6</v>
@@ -7547,7 +7547,7 @@
         <v>55</v>
       </c>
       <c r="AJ28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK28">
         <v>29</v>
@@ -7565,16 +7565,16 @@
         <v>40</v>
       </c>
       <c r="AP28">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR28">
         <v>19.5</v>
       </c>
       <c r="AS28">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AT28">
         <v>9.199999999999999</v>
@@ -7583,13 +7583,13 @@
         <v>7</v>
       </c>
       <c r="AV28">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW28">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY28">
         <v>9.800000000000001</v>
@@ -7598,25 +7598,25 @@
         <v>14.5</v>
       </c>
       <c r="BA28">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB28">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC28">
         <v>21</v>
       </c>
       <c r="BD28">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE28">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="BF28">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG28">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7699,22 +7699,22 @@
         <v>178</v>
       </c>
       <c r="F29">
-        <v>1.12</v>
+        <v>3.85</v>
       </c>
       <c r="G29">
-        <v>990</v>
+        <v>5.1</v>
       </c>
       <c r="H29">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="I29">
-        <v>990</v>
+        <v>2.16</v>
       </c>
       <c r="J29">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="K29">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L29">
         <v>1.02</v>
@@ -7723,22 +7723,22 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="O29">
         <v>1.38</v>
       </c>
       <c r="P29">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q29">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="R29">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S29">
-        <v>1.05</v>
+        <v>3.2</v>
       </c>
       <c r="T29">
         <v>1.11</v>
@@ -7747,7 +7747,7 @@
         <v>1.11</v>
       </c>
       <c r="V29">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="W29">
         <v>1.24</v>
@@ -7965,10 +7965,10 @@
         <v>1.13</v>
       </c>
       <c r="N30">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O30">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P30">
         <v>1.56</v>
@@ -7995,10 +7995,10 @@
         <v>1.62</v>
       </c>
       <c r="X30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y30">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z30">
         <v>22</v>
@@ -8025,7 +8025,7 @@
         <v>13.5</v>
       </c>
       <c r="AH30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI30">
         <v>80</v>
@@ -8034,7 +8034,7 @@
         <v>44</v>
       </c>
       <c r="AK30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL30">
         <v>65</v>
@@ -8046,13 +8046,13 @@
         <v>38</v>
       </c>
       <c r="AO30">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP30">
         <v>7.8</v>
       </c>
       <c r="AQ30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR30">
         <v>18.5</v>
@@ -8070,7 +8070,7 @@
         <v>14.5</v>
       </c>
       <c r="AW30">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AX30">
         <v>12.5</v>
@@ -8082,16 +8082,16 @@
         <v>21</v>
       </c>
       <c r="BA30">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BB30">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC30">
         <v>24</v>
       </c>
       <c r="BD30">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE30">
         <v>48</v>
@@ -8118,7 +8118,7 @@
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN30">
         <v>5.1</v>
@@ -8130,16 +8130,16 @@
         <v>22</v>
       </c>
       <c r="BQ30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR30">
-        <v>750</v>
+        <v>660</v>
       </c>
       <c r="BS30">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT30">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU30">
         <v>5.8</v>
@@ -8148,19 +8148,19 @@
         <v>36</v>
       </c>
       <c r="BW30">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX30">
-        <v>910</v>
+        <v>820</v>
       </c>
       <c r="BY30">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CB30" t="s">
         <v>185</v>
@@ -8186,7 +8186,7 @@
         <v>2.5</v>
       </c>
       <c r="G31">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H31">
         <v>3</v>
@@ -8195,10 +8195,10 @@
         <v>3.15</v>
       </c>
       <c r="J31">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L31">
         <v>1.4</v>
@@ -8207,49 +8207,49 @@
         <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O31">
         <v>1.32</v>
       </c>
       <c r="P31">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q31">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S31">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T31">
         <v>1.75</v>
       </c>
       <c r="U31">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y31">
         <v>13</v>
       </c>
       <c r="Z31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA31">
         <v>60</v>
       </c>
       <c r="AB31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC31">
         <v>7.8</v>
@@ -8258,7 +8258,7 @@
         <v>13.5</v>
       </c>
       <c r="AE31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF31">
         <v>17</v>
@@ -8276,7 +8276,7 @@
         <v>42</v>
       </c>
       <c r="AK31">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL31">
         <v>46</v>
@@ -8285,10 +8285,10 @@
         <v>110</v>
       </c>
       <c r="AN31">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO31">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP31">
         <v>12.5</v>
@@ -8297,13 +8297,13 @@
         <v>11</v>
       </c>
       <c r="AR31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS31">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT31">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU31">
         <v>7.2</v>
@@ -8312,10 +8312,10 @@
         <v>11.5</v>
       </c>
       <c r="AW31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX31">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8324,25 +8324,25 @@
         <v>15</v>
       </c>
       <c r="BA31">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC31">
         <v>7.2</v>
       </c>
       <c r="BD31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE31">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF31">
         <v>16.5</v>
       </c>
       <c r="BG31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8360,7 +8360,7 @@
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BN31">
         <v>1000</v>
@@ -8372,13 +8372,13 @@
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BT31">
         <v>1000</v>
@@ -8390,19 +8390,19 @@
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="CB31" t="s">
         <v>185</v>
@@ -8443,7 +8443,7 @@
         <v>3.6</v>
       </c>
       <c r="L32">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M32">
         <v>1.08</v>
@@ -8476,13 +8476,13 @@
         <v>1.33</v>
       </c>
       <c r="W32">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X32">
         <v>13</v>
       </c>
       <c r="Y32">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z32">
         <v>29</v>
@@ -8503,7 +8503,7 @@
         <v>60</v>
       </c>
       <c r="AF32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG32">
         <v>11</v>
@@ -8542,7 +8542,7 @@
         <v>14</v>
       </c>
       <c r="AS32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT32">
         <v>8</v>
@@ -8554,7 +8554,7 @@
         <v>14</v>
       </c>
       <c r="AW32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX32">
         <v>11.5</v>
@@ -8578,13 +8578,13 @@
         <v>30</v>
       </c>
       <c r="BE32">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF32">
         <v>16.5</v>
       </c>
       <c r="BG32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH32">
         <v>3.5</v>
@@ -8667,7 +8667,7 @@
         <v>182</v>
       </c>
       <c r="F33">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G33">
         <v>2.26</v>
@@ -8682,7 +8682,7 @@
         <v>3.6</v>
       </c>
       <c r="K33">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L33">
         <v>1.33</v>
@@ -8694,16 +8694,16 @@
         <v>4.1</v>
       </c>
       <c r="O33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P33">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q33">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R33">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S33">
         <v>3.1</v>
@@ -8832,37 +8832,37 @@
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BT33">
         <v>1000</v>
@@ -8874,19 +8874,19 @@
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="CB33" t="s">
         <v>185</v>
@@ -8912,7 +8912,7 @@
         <v>3.1</v>
       </c>
       <c r="G34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H34">
         <v>2.56</v>
@@ -8987,7 +8987,7 @@
         <v>40</v>
       </c>
       <c r="AF34">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AG34">
         <v>15</v>
@@ -9026,7 +9026,7 @@
         <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AT34">
         <v>9.199999999999999</v>
@@ -9038,7 +9038,7 @@
         <v>10.5</v>
       </c>
       <c r="AW34">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AX34">
         <v>17.5</v>
@@ -9050,7 +9050,7 @@
         <v>17.5</v>
       </c>
       <c r="BA34">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BB34">
         <v>8.4</v>
@@ -9074,61 +9074,61 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="CB34" t="s">
         <v>185</v>
@@ -9160,7 +9160,7 @@
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>3.4</v>
@@ -9172,7 +9172,7 @@
         <v>1.53</v>
       </c>
       <c r="M35">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N35">
         <v>2.82</v>
@@ -9202,7 +9202,7 @@
         <v>1.2</v>
       </c>
       <c r="W35">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X35">
         <v>9.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -571,7 +571,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 14:51:46</t>
+    <t>2026-10-01 17:07:53</t>
   </si>
 </sst>
 </file>
@@ -1165,22 +1165,22 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="G2">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="H2">
+        <v>5.8</v>
+      </c>
+      <c r="I2">
         <v>6.2</v>
       </c>
-      <c r="I2">
-        <v>6.6</v>
-      </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1192,70 +1192,70 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
         <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="X2">
         <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
+        <v>9</v>
+      </c>
+      <c r="AD2">
+        <v>24</v>
+      </c>
+      <c r="AE2">
+        <v>150</v>
+      </c>
+      <c r="AF2">
         <v>9.4</v>
-      </c>
-      <c r="AD2">
-        <v>26</v>
-      </c>
-      <c r="AE2">
-        <v>110</v>
-      </c>
-      <c r="AF2">
-        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
         <v>19</v>
@@ -1264,25 +1264,25 @@
         <v>42</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO2">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
         <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT2">
         <v>7</v>
@@ -1291,16 +1291,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW2">
         <v>13</v>
       </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
         <v>21</v>
@@ -1309,25 +1309,25 @@
         <v>13</v>
       </c>
       <c r="BB2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD2">
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
         <v>3.05</v>
@@ -1342,34 +1342,34 @@
         <v>190</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO2">
         <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
         <v>8.4</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW2">
         <v>11</v>
@@ -1378,13 +1378,13 @@
         <v>70</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
         <v>25</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>185</v>
@@ -1407,22 +1407,22 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H3">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="I3">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
         <v>1.31</v>
@@ -1431,49 +1431,49 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S3">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T3">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U3">
         <v>2.4</v>
       </c>
       <c r="V3">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="W3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X3">
         <v>23</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
         <v>13</v>
       </c>
       <c r="AA3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC3">
         <v>10.5</v>
@@ -1482,13 +1482,13 @@
         <v>10.5</v>
       </c>
       <c r="AE3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF3">
         <v>55</v>
       </c>
       <c r="AG3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH3">
         <v>17.5</v>
@@ -1506,16 +1506,16 @@
         <v>48</v>
       </c>
       <c r="AM3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AP3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
@@ -1527,31 +1527,31 @@
         <v>17.5</v>
       </c>
       <c r="AT3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AU3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV3">
         <v>9.199999999999999</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
         <v>34</v>
       </c>
       <c r="AY3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ3">
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BC3">
         <v>42</v>
@@ -1563,10 +1563,10 @@
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH3">
         <v>4.3</v>
@@ -1649,55 +1649,55 @@
         <v>153</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="J4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L4">
         <v>1.22</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="O4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q4">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R4">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T4">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="U4">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="W4">
         <v>1.02</v>
@@ -1706,19 +1706,19 @@
         <v>46</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AB4">
         <v>120</v>
       </c>
       <c r="AC4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AD4">
         <v>20</v>
@@ -1754,73 +1754,73 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AP4">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU4">
         <v>8.800000000000001</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW4">
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BB4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BE4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="BH4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1829,10 +1829,10 @@
         <v>13</v>
       </c>
       <c r="BN4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BO4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1847,7 +1847,7 @@
         <v>13</v>
       </c>
       <c r="BT4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BU4">
         <v>3.25</v>
@@ -1859,16 +1859,16 @@
         <v>4.5</v>
       </c>
       <c r="BX4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY4">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="CA4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="CB4" t="s">
         <v>185</v>
@@ -1891,7 +1891,7 @@
         <v>154</v>
       </c>
       <c r="F5">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G5">
         <v>3.05</v>
@@ -1909,10 +1909,10 @@
         <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
         <v>3.65</v>
@@ -1921,10 +1921,10 @@
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
         <v>1.34</v>
@@ -1936,7 +1936,7 @@
         <v>1.79</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
         <v>1.55</v>
@@ -1945,13 +1945,13 @@
         <v>1.48</v>
       </c>
       <c r="X5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA5">
         <v>42</v>
@@ -1975,31 +1975,31 @@
         <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI5">
+        <v>46</v>
+      </c>
+      <c r="AJ5">
         <v>48</v>
-      </c>
-      <c r="AJ5">
-        <v>50</v>
       </c>
       <c r="AK5">
         <v>36</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5">
         <v>10</v>
@@ -2023,7 +2023,7 @@
         <v>27</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
@@ -2032,85 +2032,85 @@
         <v>15</v>
       </c>
       <c r="BA5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD5">
         <v>40</v>
       </c>
       <c r="BE5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI5">
         <v>2.7</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM5">
+        <v>5.7</v>
+      </c>
+      <c r="BN5">
         <v>6.8</v>
       </c>
-      <c r="BN5">
-        <v>6.2</v>
-      </c>
       <c r="BO5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
         <v>27</v>
       </c>
       <c r="BQ5">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BW5">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BX5">
         <v>40</v>
       </c>
       <c r="BY5">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BZ5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA5">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="s">
         <v>185</v>
@@ -2133,31 +2133,31 @@
         <v>155</v>
       </c>
       <c r="F6">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G6">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I6">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <v>5.1</v>
       </c>
-      <c r="K6">
-        <v>5.2</v>
-      </c>
       <c r="L6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O6">
         <v>1.12</v>
@@ -2166,7 +2166,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R6">
         <v>1.98</v>
@@ -2175,28 +2175,28 @@
         <v>2</v>
       </c>
       <c r="T6">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U6">
         <v>2.76</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="X6">
         <v>38</v>
       </c>
       <c r="Y6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z6">
         <v>60</v>
       </c>
       <c r="AA6">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="AB6">
         <v>16.5</v>
@@ -2205,10 +2205,10 @@
         <v>13</v>
       </c>
       <c r="AD6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF6">
         <v>14</v>
@@ -2217,13 +2217,13 @@
         <v>10.5</v>
       </c>
       <c r="AH6">
+        <v>16.5</v>
+      </c>
+      <c r="AI6">
+        <v>46</v>
+      </c>
+      <c r="AJ6">
         <v>17</v>
-      </c>
-      <c r="AI6">
-        <v>48</v>
-      </c>
-      <c r="AJ6">
-        <v>16.5</v>
       </c>
       <c r="AK6">
         <v>14</v>
@@ -2238,19 +2238,19 @@
         <v>4.7</v>
       </c>
       <c r="AO6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR6">
         <v>50</v>
       </c>
       <c r="AS6">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AT6">
         <v>15.5</v>
@@ -2259,7 +2259,7 @@
         <v>12</v>
       </c>
       <c r="AV6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW6">
         <v>50</v>
@@ -2274,13 +2274,13 @@
         <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB6">
         <v>15.5</v>
       </c>
       <c r="BC6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD6">
         <v>20</v>
@@ -2292,7 +2292,7 @@
         <v>4.4</v>
       </c>
       <c r="BG6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH6">
         <v>5.4</v>
@@ -2301,25 +2301,25 @@
         <v>5</v>
       </c>
       <c r="BJ6">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL6">
         <v>65</v>
       </c>
       <c r="BM6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
         <v>4.9</v>
       </c>
       <c r="BO6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ6">
         <v>8.199999999999999</v>
@@ -2328,25 +2328,25 @@
         <v>17</v>
       </c>
       <c r="BS6">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BT6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV6">
         <v>36</v>
       </c>
       <c r="BW6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX6">
         <v>34</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
         <v>9.4</v>
@@ -2375,22 +2375,22 @@
         <v>156</v>
       </c>
       <c r="F7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H7">
+        <v>1.48</v>
+      </c>
+      <c r="I7">
         <v>1.5</v>
       </c>
-      <c r="I7">
-        <v>1.53</v>
-      </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2405,70 +2405,70 @@
         <v>1.28</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V7">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y7">
         <v>8.4</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA7">
         <v>13</v>
       </c>
       <c r="AB7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AC7">
+        <v>11</v>
+      </c>
+      <c r="AD7">
         <v>10.5</v>
-      </c>
-      <c r="AD7">
-        <v>10</v>
       </c>
       <c r="AE7">
         <v>17</v>
       </c>
       <c r="AF7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG7">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7">
         <v>44</v>
       </c>
       <c r="AJ7">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="AK7">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AL7">
         <v>120</v>
@@ -2477,31 +2477,31 @@
         <v>150</v>
       </c>
       <c r="AN7">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AO7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP7">
         <v>15</v>
       </c>
       <c r="AQ7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS7">
         <v>11.5</v>
       </c>
       <c r="AT7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU7">
+        <v>9.6</v>
+      </c>
+      <c r="AV7">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AV7">
-        <v>8.800000000000001</v>
       </c>
       <c r="AW7">
         <v>14.5</v>
@@ -2519,7 +2519,7 @@
         <v>30</v>
       </c>
       <c r="BB7">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BC7">
         <v>65</v>
@@ -2531,55 +2531,55 @@
         <v>85</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7">
         <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BN7">
         <v>11.5</v>
       </c>
       <c r="BO7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BT7">
         <v>3.9</v>
       </c>
       <c r="BU7">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BV7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW7">
         <v>6</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="s">
         <v>185</v>
@@ -2617,22 +2617,22 @@
         <v>157</v>
       </c>
       <c r="F8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H8">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I8">
         <v>2.82</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2641,28 +2641,28 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
         <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
         <v>1.75</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V8">
         <v>1.55</v>
@@ -2859,25 +2859,25 @@
         <v>158</v>
       </c>
       <c r="F9">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G9">
         <v>1.91</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M9">
         <v>1.09</v>
@@ -2886,13 +2886,13 @@
         <v>2.72</v>
       </c>
       <c r="O9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P9">
         <v>1.6</v>
       </c>
       <c r="Q9">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2901,25 +2901,25 @@
         <v>2.98</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U9">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X9">
         <v>970</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2928,16 +2928,16 @@
         <v>970</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE9">
         <v>1000</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG9">
         <v>1000</v>
@@ -2967,58 +2967,58 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AR9">
-        <v>1.16</v>
+        <v>6.2</v>
       </c>
       <c r="AS9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AT9">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AU9">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AV9">
-        <v>1.16</v>
+        <v>2.86</v>
       </c>
       <c r="AW9">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="AX9">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AY9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AZ9">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="BA9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="BB9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="BC9">
-        <v>1.16</v>
+        <v>2.86</v>
       </c>
       <c r="BD9">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="BE9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="BF9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="BG9">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3101,58 +3101,58 @@
         <v>159</v>
       </c>
       <c r="F10">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G10">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H10">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="I10">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="P10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q10">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="R10">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S10">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3343,22 +3343,22 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="G11">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="H11">
+        <v>3.7</v>
+      </c>
+      <c r="I11">
+        <v>4.9</v>
+      </c>
+      <c r="J11">
+        <v>3.45</v>
+      </c>
+      <c r="K11">
         <v>4.3</v>
-      </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
-      <c r="J11">
-        <v>3.7</v>
-      </c>
-      <c r="K11">
-        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3370,7 +3370,7 @@
         <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="P11">
         <v>1.86</v>
@@ -3379,130 +3379,130 @@
         <v>1.8</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
         <v>2.42</v>
       </c>
       <c r="T11">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="U11">
-        <v>1.12</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="W11">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="X11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y11">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z11">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AA11">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE11">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AF11">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AK11">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AL11">
         <v>40</v>
       </c>
       <c r="AM11">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN11">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO11">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AP11">
         <v>12</v>
       </c>
       <c r="AQ11">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AR11">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="AS11">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW11">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AX11">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AY11">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA11">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BC11">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD11">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE11">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BF11">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BG11">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3585,58 +3585,58 @@
         <v>161</v>
       </c>
       <c r="F12">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="G12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H12">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="I12">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="J12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="P12">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="Q12">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="R12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U12">
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="W12">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3827,22 +3827,22 @@
         <v>162</v>
       </c>
       <c r="F13">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H13">
         <v>3.05</v>
       </c>
       <c r="I13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L13">
         <v>1.18</v>
@@ -3851,34 +3851,34 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P13">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="R13">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="S13">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="T13">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="U13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V13">
         <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X13">
         <v>50</v>
@@ -3893,10 +3893,10 @@
         <v>65</v>
       </c>
       <c r="AB13">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AC13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD13">
         <v>17</v>
@@ -3908,13 +3908,13 @@
         <v>25</v>
       </c>
       <c r="AG13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH13">
         <v>16</v>
       </c>
       <c r="AI13">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ13">
         <v>34</v>
@@ -3926,34 +3926,34 @@
         <v>22</v>
       </c>
       <c r="AM13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN13">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO13">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP13">
+        <v>7.6</v>
+      </c>
+      <c r="AQ13">
+        <v>25</v>
+      </c>
+      <c r="AR13">
         <v>7.2</v>
       </c>
-      <c r="AQ13">
-        <v>20</v>
-      </c>
-      <c r="AR13">
-        <v>6.8</v>
-      </c>
       <c r="AS13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT13">
         <v>18.5</v>
       </c>
       <c r="AU13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW13">
         <v>21</v>
@@ -3962,16 +3962,16 @@
         <v>18.5</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
         <v>12</v>
       </c>
       <c r="BA13">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="BB13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC13">
         <v>16</v>
@@ -3980,19 +3980,19 @@
         <v>19</v>
       </c>
       <c r="BE13">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BI13">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BJ13">
         <v>9.199999999999999</v>
@@ -4004,49 +4004,49 @@
         <v>55</v>
       </c>
       <c r="BM13">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BN13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ13">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BR13">
         <v>20</v>
       </c>
       <c r="BS13">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BT13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU13">
         <v>6</v>
       </c>
       <c r="BV13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW13">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BX13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY13">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ13">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA13">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="s">
         <v>185</v>
@@ -4090,13 +4090,13 @@
         <v>1.28</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="P14">
         <v>1.98</v>
@@ -4111,13 +4111,13 @@
         <v>2.68</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
         <v>1.63</v>
@@ -4311,13 +4311,13 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="H15">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>2.34</v>
@@ -4326,7 +4326,7 @@
         <v>3.2</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4335,7 +4335,7 @@
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>3.85</v>
+        <v>1.1</v>
       </c>
       <c r="O15">
         <v>1.02</v>
@@ -4344,7 +4344,7 @@
         <v>2.04</v>
       </c>
       <c r="Q15">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="R15">
         <v>1.41</v>
@@ -4359,10 +4359,10 @@
         <v>1.12</v>
       </c>
       <c r="V15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4562,7 +4562,7 @@
         <v>6.8</v>
       </c>
       <c r="I16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -4574,13 +4574,13 @@
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16">
         <v>5.7</v>
       </c>
       <c r="O16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P16">
         <v>2.62</v>
@@ -4598,13 +4598,13 @@
         <v>1.65</v>
       </c>
       <c r="U16">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="V16">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W16">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="X16">
         <v>34</v>
@@ -4655,7 +4655,7 @@
         <v>110</v>
       </c>
       <c r="AN16">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AO16">
         <v>95</v>
@@ -4664,13 +4664,13 @@
         <v>21</v>
       </c>
       <c r="AQ16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AR16">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS16">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT16">
         <v>9</v>
@@ -4682,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="AW16">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX16">
         <v>8.4</v>
@@ -4694,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="BA16">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB16">
         <v>10.5</v>
@@ -4706,13 +4706,13 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF16">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG16">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH16">
         <v>4.7</v>
@@ -4795,166 +4795,166 @@
         <v>166</v>
       </c>
       <c r="F17">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G17">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <v>3.2</v>
       </c>
       <c r="I17">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="J17">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>2.24</v>
+      </c>
+      <c r="O17">
+        <v>1.2</v>
+      </c>
+      <c r="P17">
+        <v>1.25</v>
+      </c>
+      <c r="Q17">
+        <v>2.72</v>
+      </c>
+      <c r="R17">
         <v>1.15</v>
       </c>
-      <c r="N17">
-        <v>2.38</v>
-      </c>
-      <c r="O17">
-        <v>1.6</v>
-      </c>
-      <c r="P17">
-        <v>1.46</v>
-      </c>
-      <c r="Q17">
-        <v>2.88</v>
-      </c>
-      <c r="R17">
-        <v>1.17</v>
-      </c>
       <c r="S17">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="T17">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V17">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X17">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="AR17">
-        <v>15.5</v>
+        <v>2.04</v>
       </c>
       <c r="AS17">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="AT17">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="AW17">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>13</v>
+        <v>1.02</v>
       </c>
       <c r="AY17">
-        <v>10.5</v>
+        <v>1.02</v>
       </c>
       <c r="AZ17">
-        <v>18.5</v>
+        <v>1.06</v>
       </c>
       <c r="BA17">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="BB17">
-        <v>5.2</v>
+        <v>1.06</v>
       </c>
       <c r="BC17">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="BD17">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="BE17">
-        <v>5.5</v>
+        <v>1.06</v>
       </c>
       <c r="BF17">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5037,16 +5037,16 @@
         <v>167</v>
       </c>
       <c r="F18">
+        <v>2.8</v>
+      </c>
+      <c r="G18">
         <v>2.86</v>
       </c>
-      <c r="G18">
-        <v>2.98</v>
-      </c>
       <c r="H18">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="J18">
         <v>3.15</v>
@@ -5058,106 +5058,106 @@
         <v>1.48</v>
       </c>
       <c r="M18">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N18">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O18">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P18">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q18">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R18">
         <v>1.21</v>
       </c>
       <c r="S18">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T18">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U18">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V18">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA18">
         <v>55</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC18">
         <v>7.2</v>
       </c>
       <c r="AD18">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE18">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>17</v>
       </c>
       <c r="AG18">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI18">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ18">
         <v>55</v>
       </c>
       <c r="AK18">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM18">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN18">
         <v>48</v>
       </c>
       <c r="AO18">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP18">
+        <v>7.8</v>
+      </c>
+      <c r="AQ18">
+        <v>8.4</v>
+      </c>
+      <c r="AR18">
+        <v>16</v>
+      </c>
+      <c r="AS18">
+        <v>42</v>
+      </c>
+      <c r="AT18">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AQ18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR18">
-        <v>15.5</v>
-      </c>
-      <c r="AS18">
-        <v>27</v>
-      </c>
-      <c r="AT18">
-        <v>8</v>
       </c>
       <c r="AU18">
         <v>6.6</v>
@@ -5172,7 +5172,7 @@
         <v>15</v>
       </c>
       <c r="AY18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ18">
         <v>20</v>
@@ -5181,7 +5181,7 @@
         <v>50</v>
       </c>
       <c r="BB18">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BC18">
         <v>36</v>
@@ -5279,22 +5279,22 @@
         <v>168</v>
       </c>
       <c r="F19">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G19">
         <v>1.81</v>
       </c>
       <c r="H19">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I19">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>4.2</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5312,133 +5312,133 @@
         <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R19">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="S19">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="T19">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U19">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W19">
         <v>2.22</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB19">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF19">
+        <v>16.5</v>
+      </c>
+      <c r="AG19">
+        <v>13</v>
+      </c>
+      <c r="AH19">
+        <v>21</v>
+      </c>
+      <c r="AI19">
+        <v>60</v>
+      </c>
+      <c r="AJ19">
+        <v>24</v>
+      </c>
+      <c r="AK19">
+        <v>21</v>
+      </c>
+      <c r="AL19">
         <v>34</v>
       </c>
-      <c r="AG19">
-        <v>970</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN19">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP19">
-        <v>1.37</v>
+        <v>18</v>
       </c>
       <c r="AQ19">
-        <v>1.37</v>
+        <v>16.5</v>
       </c>
       <c r="AR19">
-        <v>1.37</v>
+        <v>4.9</v>
       </c>
       <c r="AS19">
-        <v>1.37</v>
+        <v>5.2</v>
       </c>
       <c r="AT19">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="AU19">
-        <v>1.27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>1.37</v>
+        <v>16</v>
       </c>
       <c r="AW19">
-        <v>1.37</v>
+        <v>5</v>
       </c>
       <c r="AX19">
-        <v>1.32</v>
+        <v>11.5</v>
       </c>
       <c r="AY19">
-        <v>1.28</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>1.37</v>
+        <v>14.5</v>
       </c>
       <c r="BA19">
-        <v>1.37</v>
+        <v>5</v>
       </c>
       <c r="BB19">
-        <v>1.37</v>
+        <v>16.5</v>
       </c>
       <c r="BC19">
-        <v>1.37</v>
+        <v>14</v>
       </c>
       <c r="BD19">
-        <v>1.37</v>
+        <v>19.5</v>
       </c>
       <c r="BE19">
-        <v>1.37</v>
+        <v>5.1</v>
       </c>
       <c r="BF19">
-        <v>1.21</v>
+        <v>6.8</v>
       </c>
       <c r="BG19">
-        <v>1.37</v>
+        <v>4.9</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5521,10 +5521,10 @@
         <v>169</v>
       </c>
       <c r="F20">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H20">
         <v>2.18</v>
@@ -5533,10 +5533,10 @@
         <v>2.24</v>
       </c>
       <c r="J20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5545,40 +5545,40 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O20">
         <v>1.2</v>
       </c>
       <c r="P20">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q20">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R20">
         <v>1.48</v>
       </c>
       <c r="S20">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T20">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U20">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V20">
         <v>1.8</v>
       </c>
       <c r="W20">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X20">
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z20">
         <v>1000</v>
@@ -5626,61 +5626,61 @@
         <v>1000</v>
       </c>
       <c r="AO20">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20">
         <v>1.15</v>
       </c>
       <c r="AR20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AS20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AT20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AU20">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AV20">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AW20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AX20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AY20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AZ20">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BA20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BB20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BD20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BE20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BF20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BG20">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5781,7 +5781,7 @@
         <v>4.8</v>
       </c>
       <c r="L21">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M21">
         <v>1.05</v>
@@ -5793,7 +5793,7 @@
         <v>1.27</v>
       </c>
       <c r="P21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q21">
         <v>1.74</v>
@@ -5802,13 +5802,13 @@
         <v>1.38</v>
       </c>
       <c r="S21">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T21">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U21">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V21">
         <v>2.04</v>
@@ -5868,58 +5868,58 @@
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AP21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
+        <v>1.24</v>
+      </c>
+      <c r="AR21">
+        <v>1.28</v>
+      </c>
+      <c r="AS21">
+        <v>1.33</v>
+      </c>
+      <c r="AT21">
+        <v>1.33</v>
+      </c>
+      <c r="AU21">
         <v>1.22</v>
       </c>
-      <c r="AR21">
-        <v>1.25</v>
-      </c>
-      <c r="AS21">
-        <v>1.3</v>
-      </c>
-      <c r="AT21">
-        <v>1.3</v>
-      </c>
-      <c r="AU21">
-        <v>1.2</v>
-      </c>
       <c r="AV21">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AW21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AX21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AY21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AZ21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BA21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BB21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BD21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BE21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BF21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BG21">
         <v>1.24</v>
@@ -6005,31 +6005,31 @@
         <v>171</v>
       </c>
       <c r="F22">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H22">
         <v>3.75</v>
       </c>
       <c r="I22">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J22">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="L22">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M22">
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O22">
         <v>1.26</v>
@@ -6038,25 +6038,25 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="R22">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S22">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T22">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U22">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V22">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6086,7 +6086,7 @@
         <v>1000</v>
       </c>
       <c r="AG22">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
         <v>1000</v>
@@ -6107,64 +6107,64 @@
         <v>1000</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO22">
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AQ22">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AR22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AS22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT22">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AU22">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AV22">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AW22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AX22">
-        <v>1.23</v>
+        <v>8.4</v>
       </c>
       <c r="AY22">
-        <v>1.15</v>
+        <v>7.4</v>
       </c>
       <c r="AZ22">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="BA22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BB22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BC22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BD22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BE22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BF22">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BG22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6247,19 +6247,19 @@
         <v>172</v>
       </c>
       <c r="F23">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G23">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H23">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="I23">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K23">
         <v>4.3</v>
@@ -6280,13 +6280,13 @@
         <v>2.42</v>
       </c>
       <c r="Q23">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S23">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T23">
         <v>1.57</v>
@@ -6295,28 +6295,28 @@
         <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="W23">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X23">
         <v>27</v>
       </c>
       <c r="Y23">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA23">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB23">
         <v>22</v>
       </c>
       <c r="AC23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>13</v>
@@ -6328,13 +6328,13 @@
         <v>34</v>
       </c>
       <c r="AG23">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH23">
         <v>16.5</v>
       </c>
       <c r="AI23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ23">
         <v>70</v>
@@ -6349,10 +6349,10 @@
         <v>70</v>
       </c>
       <c r="AN23">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO23">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP23">
         <v>17.5</v>
@@ -6385,28 +6385,28 @@
         <v>13</v>
       </c>
       <c r="AZ23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA23">
         <v>21</v>
       </c>
       <c r="BB23">
+        <v>6.4</v>
+      </c>
+      <c r="BC23">
         <v>6</v>
       </c>
-      <c r="BC23">
-        <v>5.6</v>
-      </c>
       <c r="BD23">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE23">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF23">
         <v>18.5</v>
       </c>
       <c r="BG23">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6489,10 +6489,10 @@
         <v>173</v>
       </c>
       <c r="F24">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G24">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H24">
         <v>2.02</v>
@@ -6504,10 +6504,10 @@
         <v>3.85</v>
       </c>
       <c r="K24">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M24">
         <v>1.04</v>
@@ -6519,25 +6519,25 @@
         <v>1.2</v>
       </c>
       <c r="P24">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q24">
         <v>1.62</v>
       </c>
       <c r="R24">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S24">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T24">
         <v>1.58</v>
       </c>
       <c r="U24">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W24">
         <v>1.33</v>
@@ -6573,10 +6573,10 @@
         <v>16.5</v>
       </c>
       <c r="AH24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ24">
         <v>75</v>
@@ -6588,13 +6588,13 @@
         <v>50</v>
       </c>
       <c r="AM24">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN24">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP24">
         <v>19</v>
@@ -6603,13 +6603,13 @@
         <v>11.5</v>
       </c>
       <c r="AR24">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS24">
         <v>21</v>
       </c>
       <c r="AT24">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU24">
         <v>8.4</v>
@@ -6621,13 +6621,13 @@
         <v>16.5</v>
       </c>
       <c r="AX24">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AY24">
         <v>14</v>
       </c>
       <c r="AZ24">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA24">
         <v>24</v>
@@ -6708,7 +6708,7 @@
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="CB24" t="s">
         <v>185</v>
@@ -6731,22 +6731,22 @@
         <v>174</v>
       </c>
       <c r="F25">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="G25">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H25">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="I25">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="J25">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="K25">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6755,142 +6755,142 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q25">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R25">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S25">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="T25">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="U25">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="V25">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W25">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="X25">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z25">
         <v>21</v>
       </c>
       <c r="AA25">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB25">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC25">
         <v>10.5</v>
       </c>
       <c r="AD25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE25">
         <v>25</v>
       </c>
       <c r="AF25">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI25">
         <v>38</v>
       </c>
       <c r="AJ25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK25">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL25">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM25">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AN25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO25">
         <v>16</v>
       </c>
       <c r="AP25">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="AQ25">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AR25">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS25">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AT25">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AU25">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV25">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AW25">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX25">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="AY25">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AZ25">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="BA25">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB25">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="BC25">
-        <v>4.7</v>
+        <v>22</v>
       </c>
       <c r="BD25">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="BE25">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF25">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BG25">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6988,31 +6988,31 @@
         <v>5.8</v>
       </c>
       <c r="K26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O26">
         <v>1.15</v>
       </c>
       <c r="P26">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q26">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R26">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S26">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T26">
         <v>1.71</v>
@@ -7042,7 +7042,7 @@
         <v>46</v>
       </c>
       <c r="AC26">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD26">
         <v>11.5</v>
@@ -7081,7 +7081,7 @@
         <v>4.4</v>
       </c>
       <c r="AP26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26">
         <v>11.5</v>
@@ -7093,7 +7093,7 @@
         <v>11</v>
       </c>
       <c r="AT26">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU26">
         <v>12</v>
@@ -7108,7 +7108,7 @@
         <v>8.6</v>
       </c>
       <c r="AY26">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AZ26">
         <v>17.5</v>
@@ -7117,19 +7117,19 @@
         <v>21</v>
       </c>
       <c r="BB26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC26">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD26">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="BE26">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BF26">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG26">
         <v>3.9</v>
@@ -7218,160 +7218,160 @@
         <v>1.9</v>
       </c>
       <c r="G27">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H27">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I27">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J27">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N27">
+        <v>2.58</v>
+      </c>
+      <c r="O27">
+        <v>1.52</v>
+      </c>
+      <c r="P27">
+        <v>1.53</v>
+      </c>
+      <c r="Q27">
+        <v>2.54</v>
+      </c>
+      <c r="R27">
+        <v>1.19</v>
+      </c>
+      <c r="S27">
+        <v>5.2</v>
+      </c>
+      <c r="T27">
         <v>2.16</v>
       </c>
-      <c r="O27">
-        <v>1.51</v>
-      </c>
-      <c r="P27">
-        <v>1.4</v>
-      </c>
-      <c r="Q27">
-        <v>2.46</v>
-      </c>
-      <c r="R27">
-        <v>1.18</v>
-      </c>
-      <c r="S27">
-        <v>2.72</v>
-      </c>
-      <c r="T27">
-        <v>1.01</v>
-      </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V27">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP27">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG27">
         <v>1.01</v>
@@ -7457,7 +7457,7 @@
         <v>177</v>
       </c>
       <c r="F28">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G28">
         <v>2.44</v>
@@ -7484,7 +7484,7 @@
         <v>3.75</v>
       </c>
       <c r="O28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P28">
         <v>1.94</v>
@@ -7517,7 +7517,7 @@
         <v>15.5</v>
       </c>
       <c r="Z28">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA28">
         <v>70</v>
@@ -7586,7 +7586,7 @@
         <v>12</v>
       </c>
       <c r="AW28">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX28">
         <v>13</v>
@@ -7598,7 +7598,7 @@
         <v>14.5</v>
       </c>
       <c r="BA28">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB28">
         <v>5.8</v>
@@ -7607,7 +7607,7 @@
         <v>21</v>
       </c>
       <c r="BD28">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE28">
         <v>6.4</v>
@@ -7702,10 +7702,10 @@
         <v>3.85</v>
       </c>
       <c r="G29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H29">
-        <v>1.95</v>
+        <v>1.12</v>
       </c>
       <c r="I29">
         <v>2.16</v>
@@ -7714,7 +7714,7 @@
         <v>3.25</v>
       </c>
       <c r="K29">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
         <v>1.02</v>
@@ -7723,7 +7723,7 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="O29">
         <v>1.38</v>
@@ -7750,7 +7750,7 @@
         <v>1.86</v>
       </c>
       <c r="W29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7950,7 +7950,7 @@
         <v>3.3</v>
       </c>
       <c r="I30">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J30">
         <v>3.1</v>
@@ -7971,25 +7971,25 @@
         <v>1.57</v>
       </c>
       <c r="P30">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q30">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R30">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S30">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T30">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U30">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
         <v>1.62</v>
@@ -8007,7 +8007,7 @@
         <v>1000</v>
       </c>
       <c r="AB30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC30">
         <v>7.4</v>
@@ -8031,13 +8031,13 @@
         <v>80</v>
       </c>
       <c r="AJ30">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK30">
         <v>38</v>
       </c>
       <c r="AL30">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
         <v>1000</v>
@@ -8049,7 +8049,7 @@
         <v>75</v>
       </c>
       <c r="AP30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ30">
         <v>8.4</v>
@@ -8067,10 +8067,10 @@
         <v>6.8</v>
       </c>
       <c r="AV30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW30">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AX30">
         <v>12.5</v>
@@ -8082,22 +8082,22 @@
         <v>21</v>
       </c>
       <c r="BA30">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BB30">
         <v>26</v>
       </c>
       <c r="BC30">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD30">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE30">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG30">
         <v>32</v>
@@ -8133,7 +8133,7 @@
         <v>10</v>
       </c>
       <c r="BR30">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="BS30">
         <v>13.5</v>
@@ -8151,7 +8151,7 @@
         <v>12.5</v>
       </c>
       <c r="BX30">
-        <v>820</v>
+        <v>720</v>
       </c>
       <c r="BY30">
         <v>14.5</v>
@@ -8183,16 +8183,16 @@
         <v>180</v>
       </c>
       <c r="F31">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G31">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J31">
         <v>3.4</v>
@@ -8213,7 +8213,7 @@
         <v>1.32</v>
       </c>
       <c r="P31">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
         <v>1.98</v>
@@ -8222,19 +8222,19 @@
         <v>1.36</v>
       </c>
       <c r="S31">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T31">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U31">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V31">
         <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X31">
         <v>14.5</v>
@@ -8243,7 +8243,7 @@
         <v>13</v>
       </c>
       <c r="Z31">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA31">
         <v>60</v>
@@ -8258,25 +8258,25 @@
         <v>13.5</v>
       </c>
       <c r="AE31">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF31">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG31">
         <v>12.5</v>
       </c>
       <c r="AH31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI31">
         <v>55</v>
       </c>
       <c r="AJ31">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL31">
         <v>46</v>
@@ -8294,13 +8294,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR31">
         <v>17</v>
       </c>
       <c r="AS31">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT31">
         <v>9.800000000000001</v>
@@ -8312,10 +8312,10 @@
         <v>11.5</v>
       </c>
       <c r="AW31">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8324,25 +8324,25 @@
         <v>15</v>
       </c>
       <c r="BA31">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB31">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC31">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD31">
+        <v>8.6</v>
+      </c>
+      <c r="BE31">
+        <v>9.6</v>
+      </c>
+      <c r="BF31">
+        <v>19.5</v>
+      </c>
+      <c r="BG31">
         <v>8</v>
-      </c>
-      <c r="BE31">
-        <v>9</v>
-      </c>
-      <c r="BF31">
-        <v>16.5</v>
-      </c>
-      <c r="BG31">
-        <v>7.6</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8360,7 +8360,7 @@
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="BN31">
         <v>1000</v>
@@ -8372,13 +8372,13 @@
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="BT31">
         <v>1000</v>
@@ -8390,19 +8390,19 @@
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="s">
         <v>185</v>
@@ -8428,16 +8428,16 @@
         <v>2.14</v>
       </c>
       <c r="G32">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H32">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I32">
         <v>4</v>
       </c>
       <c r="J32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K32">
         <v>3.6</v>
@@ -8449,7 +8449,7 @@
         <v>1.08</v>
       </c>
       <c r="N32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O32">
         <v>1.38</v>
@@ -8458,7 +8458,7 @@
         <v>1.86</v>
       </c>
       <c r="Q32">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R32">
         <v>1.32</v>
@@ -8470,13 +8470,13 @@
         <v>1.87</v>
       </c>
       <c r="U32">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V32">
         <v>1.33</v>
       </c>
       <c r="W32">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X32">
         <v>13</v>
@@ -8488,7 +8488,7 @@
         <v>29</v>
       </c>
       <c r="AA32">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB32">
         <v>8.800000000000001</v>
@@ -8500,7 +8500,7 @@
         <v>16.5</v>
       </c>
       <c r="AE32">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF32">
         <v>13.5</v>
@@ -8545,7 +8545,7 @@
         <v>11</v>
       </c>
       <c r="AT32">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU32">
         <v>7.2</v>
@@ -8569,7 +8569,7 @@
         <v>40</v>
       </c>
       <c r="BB32">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC32">
         <v>21</v>
@@ -8578,7 +8578,7 @@
         <v>30</v>
       </c>
       <c r="BE32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF32">
         <v>16.5</v>
@@ -8682,7 +8682,7 @@
         <v>3.6</v>
       </c>
       <c r="K33">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L33">
         <v>1.33</v>
@@ -8694,7 +8694,7 @@
         <v>4.1</v>
       </c>
       <c r="O33">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P33">
         <v>2.04</v>
@@ -8933,7 +8933,7 @@
         <v>1.1</v>
       </c>
       <c r="N34">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O34">
         <v>1.45</v>
@@ -8987,13 +8987,13 @@
         <v>40</v>
       </c>
       <c r="AF34">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AG34">
         <v>15</v>
       </c>
       <c r="AH34">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI34">
         <v>65</v>
@@ -9026,7 +9026,7 @@
         <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT34">
         <v>9.199999999999999</v>
@@ -9038,7 +9038,7 @@
         <v>10.5</v>
       </c>
       <c r="AW34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX34">
         <v>17.5</v>
@@ -9154,19 +9154,19 @@
         <v>1.83</v>
       </c>
       <c r="G35">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H35">
         <v>5.5</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J35">
         <v>3.4</v>
       </c>
       <c r="K35">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L35">
         <v>1.53</v>
@@ -9184,13 +9184,13 @@
         <v>1.6</v>
       </c>
       <c r="Q35">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R35">
         <v>1.22</v>
       </c>
       <c r="S35">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>2.24</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -559,7 +559,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-01 19:24:15</t>
+    <t>2026-10-01 21:40:38</t>
   </si>
 </sst>
 </file>
@@ -1153,226 +1153,226 @@
         <v>148</v>
       </c>
       <c r="F2">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="G2">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="I2">
+        <v>32</v>
+      </c>
+      <c r="J2">
+        <v>7.2</v>
+      </c>
+      <c r="K2">
+        <v>7.6</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>6.4</v>
+      </c>
+      <c r="O2">
+        <v>1.17</v>
+      </c>
+      <c r="P2">
+        <v>2.1</v>
+      </c>
+      <c r="Q2">
+        <v>1.86</v>
+      </c>
+      <c r="R2">
+        <v>1.37</v>
+      </c>
+      <c r="S2">
+        <v>3.55</v>
+      </c>
+      <c r="T2">
+        <v>2.16</v>
+      </c>
+      <c r="U2">
+        <v>1.72</v>
+      </c>
+      <c r="V2">
+        <v>1.03</v>
+      </c>
+      <c r="W2">
+        <v>5.7</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
         <v>6.8</v>
       </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>4.2</v>
-      </c>
-      <c r="L2">
-        <v>1.44</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.6</v>
-      </c>
-      <c r="O2">
-        <v>1.37</v>
-      </c>
-      <c r="P2">
-        <v>1.88</v>
-      </c>
-      <c r="Q2">
-        <v>2.1</v>
-      </c>
-      <c r="R2">
-        <v>1.33</v>
-      </c>
-      <c r="S2">
-        <v>3.85</v>
-      </c>
-      <c r="T2">
-        <v>2.08</v>
-      </c>
-      <c r="U2">
-        <v>1.87</v>
-      </c>
-      <c r="V2">
-        <v>1.17</v>
-      </c>
-      <c r="W2">
-        <v>2.5</v>
-      </c>
-      <c r="X2">
-        <v>13.5</v>
-      </c>
-      <c r="Y2">
-        <v>19.5</v>
-      </c>
-      <c r="Z2">
-        <v>55</v>
-      </c>
-      <c r="AA2">
-        <v>210</v>
-      </c>
-      <c r="AB2">
+      <c r="AC2">
+        <v>11</v>
+      </c>
+      <c r="AD2">
+        <v>50</v>
+      </c>
+      <c r="AE2">
+        <v>330</v>
+      </c>
+      <c r="AF2">
+        <v>5.3</v>
+      </c>
+      <c r="AG2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AH2">
+        <v>34</v>
+      </c>
+      <c r="AI2">
+        <v>220</v>
+      </c>
+      <c r="AJ2">
+        <v>8</v>
+      </c>
+      <c r="AK2">
+        <v>15.5</v>
+      </c>
+      <c r="AL2">
+        <v>65</v>
+      </c>
+      <c r="AM2">
+        <v>340</v>
+      </c>
+      <c r="AN2">
+        <v>9</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>42</v>
+      </c>
+      <c r="AQ2">
+        <v>26</v>
+      </c>
+      <c r="AR2">
+        <v>26</v>
+      </c>
+      <c r="AS2">
+        <v>28</v>
+      </c>
+      <c r="AT2">
+        <v>6</v>
+      </c>
+      <c r="AU2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV2">
+        <v>38</v>
+      </c>
+      <c r="AW2">
+        <v>180</v>
+      </c>
+      <c r="AX2">
+        <v>4.6</v>
+      </c>
+      <c r="AY2">
+        <v>8</v>
+      </c>
+      <c r="AZ2">
+        <v>27</v>
+      </c>
+      <c r="BA2">
+        <v>150</v>
+      </c>
+      <c r="BB2">
+        <v>7.2</v>
+      </c>
+      <c r="BC2">
+        <v>13</v>
+      </c>
+      <c r="BD2">
+        <v>48</v>
+      </c>
+      <c r="BE2">
+        <v>190</v>
+      </c>
+      <c r="BF2">
         <v>7.6</v>
       </c>
-      <c r="AC2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>26</v>
-      </c>
-      <c r="AE2">
-        <v>110</v>
-      </c>
-      <c r="AF2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>120</v>
-      </c>
-      <c r="AJ2">
-        <v>16.5</v>
-      </c>
-      <c r="AK2">
-        <v>19</v>
-      </c>
-      <c r="AL2">
-        <v>44</v>
-      </c>
-      <c r="AM2">
-        <v>190</v>
-      </c>
-      <c r="AN2">
-        <v>11.5</v>
-      </c>
-      <c r="AO2">
-        <v>170</v>
-      </c>
-      <c r="AP2">
+      <c r="BG2">
+        <v>160</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>18</v>
+      </c>
+      <c r="BJ2">
         <v>12</v>
       </c>
-      <c r="AQ2">
+      <c r="BK2">
+        <v>11</v>
+      </c>
+      <c r="BL2">
+        <v>950</v>
+      </c>
+      <c r="BM2">
+        <v>20</v>
+      </c>
+      <c r="BN2">
+        <v>1.54</v>
+      </c>
+      <c r="BO2">
+        <v>1.51</v>
+      </c>
+      <c r="BP2">
+        <v>5.3</v>
+      </c>
+      <c r="BQ2">
+        <v>4.9</v>
+      </c>
+      <c r="BR2">
+        <v>60</v>
+      </c>
+      <c r="BS2">
+        <v>36</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>18</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>18</v>
+      </c>
+      <c r="BX2">
+        <v>300</v>
+      </c>
+      <c r="BY2">
+        <v>22</v>
+      </c>
+      <c r="BZ2">
+        <v>42</v>
+      </c>
+      <c r="CA2">
         <v>17.5</v>
-      </c>
-      <c r="AR2">
-        <v>40</v>
-      </c>
-      <c r="AS2">
-        <v>13.5</v>
-      </c>
-      <c r="AT2">
-        <v>6.8</v>
-      </c>
-      <c r="AU2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV2">
-        <v>22</v>
-      </c>
-      <c r="AW2">
-        <v>36</v>
-      </c>
-      <c r="AX2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>21</v>
-      </c>
-      <c r="BA2">
-        <v>40</v>
-      </c>
-      <c r="BB2">
-        <v>14</v>
-      </c>
-      <c r="BC2">
-        <v>16</v>
-      </c>
-      <c r="BD2">
-        <v>36</v>
-      </c>
-      <c r="BE2">
-        <v>100</v>
-      </c>
-      <c r="BF2">
-        <v>10</v>
-      </c>
-      <c r="BG2">
-        <v>95</v>
-      </c>
-      <c r="BH2">
-        <v>3.3</v>
-      </c>
-      <c r="BI2">
-        <v>3.1</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL2">
-        <v>190</v>
-      </c>
-      <c r="BM2">
-        <v>130</v>
-      </c>
-      <c r="BN2">
-        <v>4</v>
-      </c>
-      <c r="BO2">
-        <v>3.75</v>
-      </c>
-      <c r="BP2">
-        <v>11.5</v>
-      </c>
-      <c r="BQ2">
-        <v>9.6</v>
-      </c>
-      <c r="BR2">
-        <v>30</v>
-      </c>
-      <c r="BS2">
-        <v>10</v>
-      </c>
-      <c r="BT2">
-        <v>10.5</v>
-      </c>
-      <c r="BU2">
-        <v>8.4</v>
-      </c>
-      <c r="BV2">
-        <v>75</v>
-      </c>
-      <c r="BW2">
-        <v>12</v>
-      </c>
-      <c r="BX2">
-        <v>70</v>
-      </c>
-      <c r="BY2">
-        <v>11.5</v>
-      </c>
-      <c r="BZ2">
-        <v>24</v>
-      </c>
-      <c r="CA2">
-        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>181</v>
@@ -1395,226 +1395,226 @@
         <v>149</v>
       </c>
       <c r="F3">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="G3">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="I3">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="K3">
+        <v>5.7</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>12.5</v>
+      </c>
+      <c r="O3">
+        <v>1.08</v>
+      </c>
+      <c r="P3">
+        <v>3.65</v>
+      </c>
+      <c r="Q3">
+        <v>1.36</v>
+      </c>
+      <c r="R3">
+        <v>1.9</v>
+      </c>
+      <c r="S3">
+        <v>2.04</v>
+      </c>
+      <c r="T3">
+        <v>1.38</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>3.35</v>
+      </c>
+      <c r="W3">
+        <v>1.12</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>14.5</v>
+      </c>
+      <c r="Z3">
+        <v>11</v>
+      </c>
+      <c r="AA3">
+        <v>14.5</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>12.5</v>
+      </c>
+      <c r="AD3">
+        <v>8</v>
+      </c>
+      <c r="AE3">
+        <v>12</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>21</v>
+      </c>
+      <c r="AH3">
+        <v>15</v>
+      </c>
+      <c r="AI3">
+        <v>21</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>65</v>
+      </c>
+      <c r="AL3">
+        <v>40</v>
+      </c>
+      <c r="AM3">
+        <v>70</v>
+      </c>
+      <c r="AN3">
+        <v>55</v>
+      </c>
+      <c r="AO3">
+        <v>6.8</v>
+      </c>
+      <c r="AP3">
+        <v>10</v>
+      </c>
+      <c r="AQ3">
+        <v>12.5</v>
+      </c>
+      <c r="AR3">
+        <v>9</v>
+      </c>
+      <c r="AS3">
+        <v>11.5</v>
+      </c>
+      <c r="AT3">
+        <v>10</v>
+      </c>
+      <c r="AU3">
+        <v>11</v>
+      </c>
+      <c r="AV3">
+        <v>7.4</v>
+      </c>
+      <c r="AW3">
+        <v>10.5</v>
+      </c>
+      <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>17.5</v>
+      </c>
+      <c r="AZ3">
+        <v>13</v>
+      </c>
+      <c r="BA3">
+        <v>17</v>
+      </c>
+      <c r="BB3">
+        <v>10</v>
+      </c>
+      <c r="BC3">
+        <v>44</v>
+      </c>
+      <c r="BD3">
+        <v>32</v>
+      </c>
+      <c r="BE3">
+        <v>44</v>
+      </c>
+      <c r="BF3">
+        <v>34</v>
+      </c>
+      <c r="BG3">
+        <v>5.7</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>7.8</v>
+      </c>
+      <c r="BJ3">
+        <v>6.4</v>
+      </c>
+      <c r="BK3">
+        <v>5.5</v>
+      </c>
+      <c r="BL3">
+        <v>130</v>
+      </c>
+      <c r="BM3">
+        <v>80</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>7.8</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>7.8</v>
+      </c>
+      <c r="BR3">
+        <v>46</v>
+      </c>
+      <c r="BS3">
+        <v>36</v>
+      </c>
+      <c r="BT3">
+        <v>2.32</v>
+      </c>
+      <c r="BU3">
+        <v>2.14</v>
+      </c>
+      <c r="BV3">
+        <v>5</v>
+      </c>
+      <c r="BW3">
         <v>4.6</v>
       </c>
-      <c r="L3">
-        <v>1.31</v>
-      </c>
-      <c r="M3">
-        <v>1.04</v>
-      </c>
-      <c r="N3">
-        <v>5.3</v>
-      </c>
-      <c r="O3">
-        <v>1.22</v>
-      </c>
-      <c r="P3">
-        <v>2.48</v>
-      </c>
-      <c r="Q3">
-        <v>1.64</v>
-      </c>
-      <c r="R3">
-        <v>1.58</v>
-      </c>
-      <c r="S3">
-        <v>2.62</v>
-      </c>
-      <c r="T3">
-        <v>1.66</v>
-      </c>
-      <c r="U3">
-        <v>2.44</v>
-      </c>
-      <c r="V3">
-        <v>2.12</v>
-      </c>
-      <c r="W3">
-        <v>1.29</v>
-      </c>
-      <c r="X3">
-        <v>22</v>
-      </c>
-      <c r="Y3">
-        <v>12</v>
-      </c>
-      <c r="Z3">
-        <v>13.5</v>
-      </c>
-      <c r="AA3">
-        <v>20</v>
-      </c>
-      <c r="AB3">
-        <v>20</v>
-      </c>
-      <c r="AC3">
-        <v>10.5</v>
-      </c>
-      <c r="AD3">
-        <v>10</v>
-      </c>
-      <c r="AE3">
-        <v>17</v>
-      </c>
-      <c r="AF3">
-        <v>38</v>
-      </c>
-      <c r="AG3">
-        <v>17.5</v>
-      </c>
-      <c r="AH3">
-        <v>17.5</v>
-      </c>
-      <c r="AI3">
-        <v>26</v>
-      </c>
-      <c r="AJ3">
-        <v>960</v>
-      </c>
-      <c r="AK3">
-        <v>46</v>
-      </c>
-      <c r="AL3">
-        <v>46</v>
-      </c>
-      <c r="AM3">
-        <v>75</v>
-      </c>
-      <c r="AN3">
-        <v>36</v>
-      </c>
-      <c r="AO3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP3">
-        <v>19.5</v>
-      </c>
-      <c r="AQ3">
-        <v>11</v>
-      </c>
-      <c r="AR3">
-        <v>12</v>
-      </c>
-      <c r="AS3">
-        <v>17.5</v>
-      </c>
-      <c r="AT3">
-        <v>18</v>
-      </c>
-      <c r="AU3">
-        <v>9.4</v>
-      </c>
-      <c r="AV3">
-        <v>9.4</v>
-      </c>
-      <c r="AW3">
+      <c r="BX3">
+        <v>16.5</v>
+      </c>
+      <c r="BY3">
         <v>15</v>
       </c>
-      <c r="AX3">
-        <v>30</v>
-      </c>
-      <c r="AY3">
-        <v>15</v>
-      </c>
-      <c r="AZ3">
-        <v>15.5</v>
-      </c>
-      <c r="BA3">
-        <v>23</v>
-      </c>
-      <c r="BB3">
-        <v>55</v>
-      </c>
-      <c r="BC3">
-        <v>40</v>
-      </c>
-      <c r="BD3">
-        <v>38</v>
-      </c>
-      <c r="BE3">
-        <v>55</v>
-      </c>
-      <c r="BF3">
-        <v>30</v>
-      </c>
-      <c r="BG3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH3">
-        <v>4.3</v>
-      </c>
-      <c r="BI3">
-        <v>3.85</v>
-      </c>
-      <c r="BJ3">
-        <v>9</v>
-      </c>
-      <c r="BK3">
-        <v>5.8</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>65</v>
-      </c>
-      <c r="BN3">
-        <v>8</v>
-      </c>
-      <c r="BO3">
-        <v>7</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>10</v>
-      </c>
-      <c r="BR3">
-        <v>36</v>
-      </c>
-      <c r="BS3">
-        <v>10.5</v>
-      </c>
-      <c r="BT3">
-        <v>5</v>
-      </c>
-      <c r="BU3">
-        <v>4.4</v>
-      </c>
-      <c r="BV3">
-        <v>12</v>
-      </c>
-      <c r="BW3">
-        <v>7</v>
-      </c>
-      <c r="BX3">
-        <v>22</v>
-      </c>
-      <c r="BY3">
-        <v>9</v>
-      </c>
       <c r="BZ3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA3">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
         <v>181</v>
@@ -1637,94 +1637,94 @@
         <v>150</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="H4">
+        <v>1.05</v>
+      </c>
+      <c r="I4">
+        <v>1.06</v>
+      </c>
+      <c r="J4">
+        <v>22</v>
+      </c>
+      <c r="K4">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4">
         <v>1.1</v>
       </c>
-      <c r="I4">
-        <v>1.13</v>
-      </c>
-      <c r="J4">
-        <v>12.5</v>
-      </c>
-      <c r="K4">
-        <v>15</v>
-      </c>
-      <c r="L4">
-        <v>1.21</v>
-      </c>
-      <c r="M4">
-        <v>1.02</v>
-      </c>
-      <c r="N4">
-        <v>6.8</v>
-      </c>
-      <c r="O4">
-        <v>1.15</v>
-      </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="Q4">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R4">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="S4">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="T4">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V4">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AA4">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AB4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AD4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF4">
         <v>1000</v>
       </c>
       <c r="AG4">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>140</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
         <v>1000</v>
@@ -1742,121 +1742,121 @@
         <v>1000</v>
       </c>
       <c r="AO4">
-        <v>2.78</v>
+        <v>3.8</v>
       </c>
       <c r="AP4">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AS4">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT4">
+        <v>10</v>
+      </c>
+      <c r="AU4">
         <v>30</v>
       </c>
-      <c r="AU4">
-        <v>13</v>
-      </c>
       <c r="AV4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AW4">
         <v>15</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AZ4">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BA4">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BB4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC4">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BD4">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="BE4">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BG4">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="BH4">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BM4">
-        <v>230</v>
+        <v>3.05</v>
       </c>
       <c r="BN4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>9.800000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
+        <v>3.05</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>3.05</v>
+      </c>
+      <c r="BT4">
+        <v>1.82</v>
+      </c>
+      <c r="BU4">
+        <v>1.71</v>
+      </c>
+      <c r="BV4">
+        <v>3.6</v>
+      </c>
+      <c r="BW4">
+        <v>3.3</v>
+      </c>
+      <c r="BX4">
+        <v>60</v>
+      </c>
+      <c r="BY4">
+        <v>46</v>
+      </c>
+      <c r="BZ4">
+        <v>15</v>
+      </c>
+      <c r="CA4">
         <v>13.5</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>13</v>
-      </c>
-      <c r="BT4">
-        <v>3.55</v>
-      </c>
-      <c r="BU4">
-        <v>3.2</v>
-      </c>
-      <c r="BV4">
-        <v>5.3</v>
-      </c>
-      <c r="BW4">
-        <v>4.4</v>
-      </c>
-      <c r="BX4">
-        <v>29</v>
-      </c>
-      <c r="BY4">
-        <v>9.4</v>
-      </c>
-      <c r="BZ4">
-        <v>6.2</v>
-      </c>
-      <c r="CA4">
-        <v>5.4</v>
       </c>
       <c r="CB4" t="s">
         <v>181</v>
@@ -1879,127 +1879,127 @@
         <v>151</v>
       </c>
       <c r="F5">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M5">
         <v>1.02</v>
       </c>
       <c r="N5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="T5">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="U5">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="V5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="X5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Y5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE5">
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK5">
         <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AM5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN5">
         <v>4.8</v>
       </c>
       <c r="AO5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AQ5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR5">
         <v>50</v>
       </c>
       <c r="AS5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT5">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AU5">
         <v>12</v>
@@ -2008,97 +2008,97 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC5">
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE5">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BF5">
         <v>4.5</v>
       </c>
       <c r="BG5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BH5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BI5">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BJ5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK5">
         <v>7.8</v>
       </c>
       <c r="BL5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BM5">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
+        <v>9.6</v>
+      </c>
+      <c r="BQ5">
+        <v>8.6</v>
+      </c>
+      <c r="BR5">
+        <v>16</v>
+      </c>
+      <c r="BS5">
+        <v>10.5</v>
+      </c>
+      <c r="BT5">
         <v>9.4</v>
       </c>
-      <c r="BQ5">
-        <v>8.4</v>
-      </c>
-      <c r="BR5">
-        <v>17</v>
-      </c>
-      <c r="BS5">
-        <v>14</v>
-      </c>
-      <c r="BT5">
-        <v>9.6</v>
-      </c>
       <c r="BU5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BV5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW5">
         <v>13</v>
       </c>
       <c r="BX5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BY5">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BZ5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CA5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
         <v>181</v>
@@ -2121,214 +2121,214 @@
         <v>152</v>
       </c>
       <c r="F6">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H6">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="I6">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="J6">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="K6">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="Q6">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="R6">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="S6">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="T6">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U6">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="W6">
         <v>1.08</v>
       </c>
       <c r="X6">
+        <v>27</v>
+      </c>
+      <c r="Y6">
+        <v>10</v>
+      </c>
+      <c r="Z6">
+        <v>7.6</v>
+      </c>
+      <c r="AA6">
+        <v>9</v>
+      </c>
+      <c r="AB6">
+        <v>46</v>
+      </c>
+      <c r="AC6">
+        <v>16</v>
+      </c>
+      <c r="AD6">
+        <v>12</v>
+      </c>
+      <c r="AE6">
+        <v>14</v>
+      </c>
+      <c r="AF6">
+        <v>160</v>
+      </c>
+      <c r="AG6">
+        <v>55</v>
+      </c>
+      <c r="AH6">
+        <v>46</v>
+      </c>
+      <c r="AI6">
+        <v>60</v>
+      </c>
+      <c r="AJ6">
+        <v>630</v>
+      </c>
+      <c r="AK6">
+        <v>290</v>
+      </c>
+      <c r="AL6">
+        <v>200</v>
+      </c>
+      <c r="AM6">
+        <v>270</v>
+      </c>
+      <c r="AN6">
+        <v>430</v>
+      </c>
+      <c r="AO6">
+        <v>4.3</v>
+      </c>
+      <c r="AP6">
         <v>22</v>
       </c>
-      <c r="Y6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z6">
-        <v>7.8</v>
-      </c>
-      <c r="AA6">
-        <v>10.5</v>
-      </c>
-      <c r="AB6">
-        <v>38</v>
-      </c>
-      <c r="AC6">
-        <v>13.5</v>
-      </c>
-      <c r="AD6">
-        <v>11</v>
-      </c>
-      <c r="AE6">
-        <v>14.5</v>
-      </c>
-      <c r="AF6">
-        <v>120</v>
-      </c>
-      <c r="AG6">
-        <v>44</v>
-      </c>
-      <c r="AH6">
-        <v>32</v>
-      </c>
-      <c r="AI6">
-        <v>48</v>
-      </c>
-      <c r="AJ6">
-        <v>540</v>
-      </c>
-      <c r="AK6">
-        <v>220</v>
-      </c>
-      <c r="AL6">
-        <v>180</v>
-      </c>
-      <c r="AM6">
-        <v>260</v>
-      </c>
-      <c r="AN6">
-        <v>330</v>
-      </c>
-      <c r="AO6">
-        <v>5.3</v>
-      </c>
-      <c r="AP6">
-        <v>18.5</v>
-      </c>
       <c r="AQ6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS6">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT6">
         <v>32</v>
       </c>
       <c r="AU6">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AV6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX6">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="AY6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AZ6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="BB6">
+        <v>12</v>
+      </c>
+      <c r="BC6">
+        <v>18</v>
+      </c>
+      <c r="BD6">
+        <v>21</v>
+      </c>
+      <c r="BE6">
+        <v>130</v>
+      </c>
+      <c r="BF6">
+        <v>18.5</v>
+      </c>
+      <c r="BG6">
+        <v>4.1</v>
+      </c>
+      <c r="BH6">
+        <v>4.6</v>
+      </c>
+      <c r="BI6">
+        <v>4</v>
+      </c>
+      <c r="BJ6">
         <v>13.5</v>
       </c>
-      <c r="BC6">
-        <v>80</v>
-      </c>
-      <c r="BD6">
-        <v>15.5</v>
-      </c>
-      <c r="BE6">
-        <v>13.5</v>
-      </c>
-      <c r="BF6">
-        <v>16</v>
-      </c>
-      <c r="BG6">
-        <v>4.9</v>
-      </c>
-      <c r="BH6">
-        <v>4.1</v>
-      </c>
-      <c r="BI6">
-        <v>3.7</v>
-      </c>
-      <c r="BJ6">
-        <v>13</v>
-      </c>
       <c r="BK6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
+        <v>160</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>8.6</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>2.96</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
         <v>15</v>
       </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>7.8</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>7.4</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>7.2</v>
-      </c>
       <c r="BT6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BU6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV6">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BW6">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2337,10 +2337,10 @@
         <v>10</v>
       </c>
       <c r="BZ6">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="CA6">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="s">
         <v>181</v>
@@ -2363,22 +2363,22 @@
         <v>153</v>
       </c>
       <c r="F7">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="G7">
         <v>3.15</v>
       </c>
       <c r="H7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I7">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
         <v>1.39</v>
@@ -2387,10 +2387,10 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
         <v>1.89</v>
@@ -2405,16 +2405,16 @@
         <v>3.35</v>
       </c>
       <c r="T7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X7">
         <v>15</v>
@@ -2462,7 +2462,7 @@
         <v>46</v>
       </c>
       <c r="AM7">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN7">
         <v>36</v>
@@ -2477,7 +2477,7 @@
         <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS7">
         <v>25</v>
@@ -2489,7 +2489,7 @@
         <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW7">
         <v>21</v>
@@ -2534,7 +2534,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2605,19 +2605,19 @@
         <v>154</v>
       </c>
       <c r="F8">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G8">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H8">
         <v>4.8</v>
       </c>
       <c r="I8">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
         <v>3.8</v>
@@ -2629,13 +2629,13 @@
         <v>1.1</v>
       </c>
       <c r="N8">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="O8">
         <v>1.42</v>
       </c>
       <c r="P8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2653,7 +2653,7 @@
         <v>1.69</v>
       </c>
       <c r="V8">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W8">
         <v>2.02</v>
@@ -2662,10 +2662,10 @@
         <v>970</v>
       </c>
       <c r="Y8">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z8">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2674,10 +2674,10 @@
         <v>970</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD8">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AE8">
         <v>1000</v>
@@ -2686,22 +2686,22 @@
         <v>19.5</v>
       </c>
       <c r="AG8">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI8">
         <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM8">
         <v>1000</v>
@@ -2713,22 +2713,22 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AQ8">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AR8">
         <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AT8">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AU8">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV8">
         <v>12.5</v>
@@ -2737,19 +2737,19 @@
         <v>26</v>
       </c>
       <c r="AX8">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AY8">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BB8">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="BC8">
         <v>14</v>
@@ -2758,13 +2758,13 @@
         <v>22</v>
       </c>
       <c r="BE8">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BF8">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BG8">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2847,16 +2847,16 @@
         <v>155</v>
       </c>
       <c r="F9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G9">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H9">
         <v>7.6</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>5.4</v>
@@ -2871,7 +2871,7 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O9">
         <v>1.17</v>
@@ -2889,16 +2889,16 @@
         <v>2.26</v>
       </c>
       <c r="T9">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V9">
         <v>1.12</v>
       </c>
       <c r="W9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X9">
         <v>30</v>
@@ -2952,19 +2952,19 @@
         <v>5.1</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP9">
         <v>22</v>
       </c>
       <c r="AQ9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR9">
         <v>60</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT9">
         <v>10</v>
@@ -2976,7 +2976,7 @@
         <v>26</v>
       </c>
       <c r="AW9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX9">
         <v>9</v>
@@ -3006,7 +3006,7 @@
         <v>4.4</v>
       </c>
       <c r="BG9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BH9">
         <v>4.7</v>
@@ -3030,7 +3030,7 @@
         <v>4.4</v>
       </c>
       <c r="BO9">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP9">
         <v>8.800000000000001</v>
@@ -3095,7 +3095,7 @@
         <v>4.3</v>
       </c>
       <c r="H10">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>2.34</v>
@@ -3140,7 +3140,7 @@
         <v>1.75</v>
       </c>
       <c r="W10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3152,19 +3152,19 @@
         <v>1000</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB10">
         <v>1000</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD10">
         <v>1000</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF10">
         <v>1000</v>
@@ -3179,7 +3179,7 @@
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK10">
         <v>1000</v>
@@ -3197,58 +3197,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF10">
         <v>1.55</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3400,7 +3400,7 @@
         <v>1000</v>
       </c>
       <c r="AC11">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD11">
         <v>1000</v>
@@ -3573,22 +3573,22 @@
         <v>158</v>
       </c>
       <c r="F12">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="I12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3597,34 +3597,34 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>1.16</v>
+        <v>2.26</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q12">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="R12">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="T12">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3642,7 +3642,7 @@
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3681,55 +3681,55 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AT12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AU12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AV12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AW12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AX12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AY12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AZ12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BA12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BB12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BC12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BD12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BE12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BF12">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="BG12">
         <v>1.55</v>
@@ -3815,19 +3815,19 @@
         <v>159</v>
       </c>
       <c r="F13">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G13">
         <v>2.3</v>
       </c>
       <c r="H13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K13">
         <v>4.1</v>
@@ -3860,7 +3860,7 @@
         <v>1.68</v>
       </c>
       <c r="U13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
         <v>1.33</v>
@@ -3875,10 +3875,10 @@
         <v>15.5</v>
       </c>
       <c r="Z13">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA13">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB13">
         <v>11</v>
@@ -3890,7 +3890,7 @@
         <v>19.5</v>
       </c>
       <c r="AE13">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF13">
         <v>14.5</v>
@@ -3932,7 +3932,7 @@
         <v>19.5</v>
       </c>
       <c r="AS13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT13">
         <v>8.199999999999999</v>
@@ -3944,7 +3944,7 @@
         <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX13">
         <v>10.5</v>
@@ -3956,7 +3956,7 @@
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB13">
         <v>9</v>
@@ -3968,13 +3968,13 @@
         <v>20</v>
       </c>
       <c r="BE13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF13">
         <v>11.5</v>
       </c>
       <c r="BG13">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4060,49 +4060,49 @@
         <v>2.88</v>
       </c>
       <c r="G14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H14">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I14">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J14">
         <v>3.25</v>
       </c>
       <c r="K14">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L14">
         <v>1.32</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P14">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S14">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U14">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V14">
         <v>1.58</v>
@@ -4111,112 +4111,112 @@
         <v>1.45</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y14">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Z14">
+        <v>18</v>
+      </c>
+      <c r="AA14">
+        <v>95</v>
+      </c>
+      <c r="AB14">
+        <v>12</v>
+      </c>
+      <c r="AC14">
+        <v>8</v>
+      </c>
+      <c r="AD14">
+        <v>13</v>
+      </c>
+      <c r="AE14">
         <v>75</v>
       </c>
-      <c r="AA14">
-        <v>900</v>
-      </c>
-      <c r="AB14">
-        <v>950</v>
-      </c>
-      <c r="AC14">
-        <v>970</v>
-      </c>
-      <c r="AD14">
-        <v>950</v>
-      </c>
-      <c r="AE14">
-        <v>180</v>
-      </c>
       <c r="AF14">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="AG14">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AH14">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AI14">
         <v>250</v>
       </c>
       <c r="AJ14">
-        <v>900</v>
+        <v>210</v>
       </c>
       <c r="AK14">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="AL14">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP14">
-        <v>1.25</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14">
-        <v>1.22</v>
+        <v>8.6</v>
       </c>
       <c r="AR14">
-        <v>1.24</v>
+        <v>12</v>
       </c>
       <c r="AS14">
-        <v>1.25</v>
+        <v>6.6</v>
       </c>
       <c r="AT14">
-        <v>1.23</v>
+        <v>9.6</v>
       </c>
       <c r="AU14">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="AV14">
-        <v>1.23</v>
+        <v>10</v>
       </c>
       <c r="AW14">
-        <v>1.25</v>
+        <v>21</v>
       </c>
       <c r="AX14">
-        <v>1.24</v>
+        <v>17</v>
       </c>
       <c r="AY14">
-        <v>1.23</v>
+        <v>11</v>
       </c>
       <c r="AZ14">
-        <v>1.23</v>
+        <v>13</v>
       </c>
       <c r="BA14">
-        <v>1.25</v>
+        <v>6.6</v>
       </c>
       <c r="BB14">
-        <v>1.25</v>
+        <v>6.8</v>
       </c>
       <c r="BC14">
-        <v>1.25</v>
+        <v>6.6</v>
       </c>
       <c r="BD14">
-        <v>1.25</v>
+        <v>6.8</v>
       </c>
       <c r="BE14">
-        <v>1.26</v>
+        <v>7.4</v>
       </c>
       <c r="BF14">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG14">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4302,7 +4302,7 @@
         <v>2.06</v>
       </c>
       <c r="G15">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H15">
         <v>3.05</v>
@@ -4314,10 +4314,10 @@
         <v>4.4</v>
       </c>
       <c r="K15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M15">
         <v>1.02</v>
@@ -4338,10 +4338,10 @@
         <v>2.14</v>
       </c>
       <c r="S15">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="U15">
         <v>3.4</v>
@@ -4350,16 +4350,16 @@
         <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X15">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA15">
         <v>65</v>
@@ -4368,61 +4368,61 @@
         <v>28</v>
       </c>
       <c r="AC15">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD15">
         <v>17</v>
       </c>
       <c r="AE15">
+        <v>34</v>
+      </c>
+      <c r="AF15">
+        <v>28</v>
+      </c>
+      <c r="AG15">
+        <v>15.5</v>
+      </c>
+      <c r="AH15">
+        <v>16.5</v>
+      </c>
+      <c r="AI15">
         <v>32</v>
       </c>
-      <c r="AF15">
-        <v>25</v>
-      </c>
-      <c r="AG15">
-        <v>14</v>
-      </c>
-      <c r="AH15">
-        <v>16</v>
-      </c>
-      <c r="AI15">
-        <v>28</v>
-      </c>
       <c r="AJ15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK15">
         <v>22</v>
       </c>
       <c r="AL15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AM15">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AN15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO15">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AP15">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AQ15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AR15">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AS15">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="AT15">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AU15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV15">
         <v>14.5</v>
@@ -4431,7 +4431,7 @@
         <v>21</v>
       </c>
       <c r="AX15">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY15">
         <v>11.5</v>
@@ -4440,16 +4440,16 @@
         <v>12</v>
       </c>
       <c r="BA15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BB15">
         <v>16</v>
       </c>
       <c r="BC15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE15">
         <v>14.5</v>
@@ -4461,7 +4461,7 @@
         <v>10.5</v>
       </c>
       <c r="BH15">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BI15">
         <v>5.3</v>
@@ -4476,10 +4476,10 @@
         <v>55</v>
       </c>
       <c r="BM15">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN15">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BO15">
         <v>5.4</v>
@@ -4488,22 +4488,22 @@
         <v>15</v>
       </c>
       <c r="BQ15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS15">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BT15">
         <v>8.800000000000001</v>
       </c>
       <c r="BU15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW15">
         <v>5.1</v>
@@ -4512,7 +4512,7 @@
         <v>24</v>
       </c>
       <c r="BY15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BZ15">
         <v>9.800000000000001</v>
@@ -4544,7 +4544,7 @@
         <v>2.86</v>
       </c>
       <c r="G16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H16">
         <v>3.2</v>
@@ -4553,154 +4553,154 @@
         <v>3.7</v>
       </c>
       <c r="J16">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="K16">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="L16">
         <v>1.63</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N16">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O16">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="P16">
         <v>1.43</v>
       </c>
       <c r="Q16">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="R16">
         <v>1.15</v>
       </c>
       <c r="S16">
-        <v>1.05</v>
+        <v>3.05</v>
       </c>
       <c r="T16">
         <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V16">
         <v>1.37</v>
       </c>
       <c r="W16">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC16">
         <v>970</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP16">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AQ16">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AR16">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AS16">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AT16">
-        <v>1.15</v>
+        <v>7.4</v>
       </c>
       <c r="AU16">
-        <v>1.06</v>
+        <v>4.6</v>
       </c>
       <c r="AV16">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AW16">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AX16">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AY16">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AZ16">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="BA16">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BB16">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BC16">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BD16">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BE16">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BF16">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="BG16">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4807,7 +4807,7 @@
         <v>1.12</v>
       </c>
       <c r="N17">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O17">
         <v>1.53</v>
@@ -4825,10 +4825,10 @@
         <v>5.3</v>
       </c>
       <c r="T17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U17">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V17">
         <v>1.48</v>
@@ -4837,7 +4837,7 @@
         <v>1.52</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Y17">
         <v>9.199999999999999</v>
@@ -4855,13 +4855,13 @@
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE17">
         <v>44</v>
       </c>
       <c r="AF17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG17">
         <v>13.5</v>
@@ -4879,25 +4879,25 @@
         <v>42</v>
       </c>
       <c r="AL17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM17">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN17">
         <v>48</v>
       </c>
       <c r="AO17">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ17">
         <v>8.4</v>
       </c>
       <c r="AR17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS17">
         <v>42</v>
@@ -4924,7 +4924,7 @@
         <v>20</v>
       </c>
       <c r="BA17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB17">
         <v>42</v>
@@ -4936,13 +4936,13 @@
         <v>50</v>
       </c>
       <c r="BE17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF17">
         <v>38</v>
       </c>
       <c r="BG17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH17">
         <v>3.1</v>
@@ -4954,7 +4954,7 @@
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>2.48</v>
+        <v>7.2</v>
       </c>
       <c r="BL17">
         <v>1000</v>
@@ -4963,7 +4963,7 @@
         <v>2.88</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO17">
         <v>2.08</v>
@@ -5025,7 +5025,7 @@
         <v>164</v>
       </c>
       <c r="F18">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G18">
         <v>3.85</v>
@@ -5115,7 +5115,7 @@
         <v>32</v>
       </c>
       <c r="AJ18">
-        <v>470</v>
+        <v>160</v>
       </c>
       <c r="AK18">
         <v>40</v>
@@ -5169,7 +5169,7 @@
         <v>21</v>
       </c>
       <c r="BB18">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC18">
         <v>16</v>
@@ -5178,7 +5178,7 @@
         <v>18</v>
       </c>
       <c r="BE18">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF18">
         <v>18.5</v>
@@ -5273,7 +5273,7 @@
         <v>3.95</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I19">
         <v>2.04</v>
@@ -5297,7 +5297,7 @@
         <v>1.21</v>
       </c>
       <c r="P19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5333,7 +5333,7 @@
         <v>25</v>
       </c>
       <c r="AB19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC19">
         <v>9.4</v>
@@ -5357,40 +5357,40 @@
         <v>30</v>
       </c>
       <c r="AJ19">
-        <v>75</v>
+        <v>470</v>
       </c>
       <c r="AK19">
         <v>40</v>
       </c>
       <c r="AL19">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM19">
         <v>65</v>
       </c>
       <c r="AN19">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="AO19">
         <v>10</v>
       </c>
       <c r="AP19">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT19">
         <v>17.5</v>
       </c>
       <c r="AU19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV19">
         <v>9.800000000000001</v>
@@ -5423,7 +5423,7 @@
         <v>50</v>
       </c>
       <c r="BF19">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BG19">
         <v>8.800000000000001</v>
@@ -5462,7 +5462,7 @@
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="BT19">
         <v>1000</v>
@@ -5480,13 +5480,13 @@
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.43</v>
+        <v>1.1</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="CB19" t="s">
         <v>181</v>
@@ -5509,22 +5509,22 @@
         <v>166</v>
       </c>
       <c r="F20">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="G20">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H20">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I20">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5533,43 +5533,43 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O20">
+        <v>1.24</v>
+      </c>
+      <c r="P20">
+        <v>2.1</v>
+      </c>
+      <c r="Q20">
+        <v>1.73</v>
+      </c>
+      <c r="R20">
+        <v>1.41</v>
+      </c>
+      <c r="S20">
+        <v>2.72</v>
+      </c>
+      <c r="T20">
+        <v>1.69</v>
+      </c>
+      <c r="U20">
+        <v>2.04</v>
+      </c>
+      <c r="V20">
         <v>1.23</v>
       </c>
-      <c r="P20">
-        <v>2.04</v>
-      </c>
-      <c r="Q20">
-        <v>1.75</v>
-      </c>
-      <c r="R20">
-        <v>1.4</v>
-      </c>
-      <c r="S20">
-        <v>2.74</v>
-      </c>
-      <c r="T20">
-        <v>1.73</v>
-      </c>
-      <c r="U20">
-        <v>2.06</v>
-      </c>
-      <c r="V20">
-        <v>1.26</v>
-      </c>
       <c r="W20">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X20">
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA20">
         <v>900</v>
@@ -5581,16 +5581,16 @@
         <v>42</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE20">
         <v>1000</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH20">
         <v>950</v>
@@ -5599,13 +5599,13 @@
         <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM20">
         <v>580</v>
@@ -5617,55 +5617,55 @@
         <v>290</v>
       </c>
       <c r="AP20">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AR20">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AS20">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AT20">
-        <v>7.2</v>
+        <v>1.35</v>
       </c>
       <c r="AU20">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="AV20">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AW20">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AX20">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AY20">
         <v>7.4</v>
       </c>
       <c r="AZ20">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="BA20">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="BB20">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BC20">
-        <v>11</v>
+        <v>1.44</v>
       </c>
       <c r="BD20">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="BE20">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="BF20">
-        <v>2.6</v>
+        <v>1.35</v>
       </c>
       <c r="BG20">
         <v>1.55</v>
@@ -5757,7 +5757,7 @@
         <v>1.82</v>
       </c>
       <c r="H21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -5784,13 +5784,13 @@
         <v>2.52</v>
       </c>
       <c r="Q21">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S21">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="T21">
         <v>1.62</v>
@@ -5811,7 +5811,7 @@
         <v>28</v>
       </c>
       <c r="Z21">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA21">
         <v>120</v>
@@ -5823,7 +5823,7 @@
         <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE21">
         <v>60</v>
@@ -5856,19 +5856,19 @@
         <v>7.8</v>
       </c>
       <c r="AO21">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP21">
         <v>18</v>
       </c>
       <c r="AQ21">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AR21">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="AS21">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT21">
         <v>11</v>
@@ -5880,7 +5880,7 @@
         <v>16</v>
       </c>
       <c r="AW21">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX21">
         <v>11.5</v>
@@ -5892,7 +5892,7 @@
         <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BB21">
         <v>16.5</v>
@@ -5901,16 +5901,16 @@
         <v>14</v>
       </c>
       <c r="BD21">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE21">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF21">
         <v>6.8</v>
       </c>
       <c r="BG21">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5993,22 +5993,22 @@
         <v>168</v>
       </c>
       <c r="F22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <v>3.3</v>
       </c>
       <c r="H22">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I22">
         <v>2.24</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6017,28 +6017,28 @@
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
         <v>1.2</v>
       </c>
       <c r="P22">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q22">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S22">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="T22">
         <v>1.58</v>
       </c>
       <c r="U22">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V22">
         <v>1.8</v>
@@ -6053,106 +6053,106 @@
         <v>950</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC22">
         <v>42</v>
       </c>
       <c r="AD22">
+        <v>970</v>
+      </c>
+      <c r="AE22">
+        <v>150</v>
+      </c>
+      <c r="AF22">
+        <v>90</v>
+      </c>
+      <c r="AG22">
         <v>950</v>
-      </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>1000</v>
       </c>
       <c r="AH22">
         <v>950</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AM22">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN22">
         <v>1000</v>
       </c>
       <c r="AO22">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AP22">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AQ22">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AR22">
-        <v>1.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS22">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AT22">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AU22">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AV22">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AW22">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AX22">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AY22">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AZ22">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="BA22">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="BB22">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="BC22">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="BD22">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="BE22">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="BF22">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="BG22">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6238,7 +6238,7 @@
         <v>3.85</v>
       </c>
       <c r="G23">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H23">
         <v>1.94</v>
@@ -6250,7 +6250,7 @@
         <v>3.35</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L23">
         <v>1.3</v>
@@ -6259,46 +6259,46 @@
         <v>1.09</v>
       </c>
       <c r="N23">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O23">
         <v>1.36</v>
       </c>
       <c r="P23">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q23">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R23">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S23">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="T23">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="U23">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V23">
         <v>1.84</v>
       </c>
       <c r="W23">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X23">
         <v>1000</v>
       </c>
       <c r="Y23">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z23">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB23">
         <v>950</v>
@@ -6307,10 +6307,10 @@
         <v>42</v>
       </c>
       <c r="AD23">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF23">
         <v>1000</v>
@@ -6322,10 +6322,10 @@
         <v>950</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK23">
         <v>1000</v>
@@ -6334,67 +6334,67 @@
         <v>1000</v>
       </c>
       <c r="AM23">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AO23">
         <v>970</v>
       </c>
       <c r="AP23">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="AQ23">
-        <v>1.26</v>
+        <v>5.7</v>
       </c>
       <c r="AR23">
-        <v>1.34</v>
+        <v>6.4</v>
       </c>
       <c r="AS23">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="AT23">
-        <v>1.35</v>
+        <v>8.4</v>
       </c>
       <c r="AU23">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="AV23">
-        <v>1.33</v>
+        <v>6.2</v>
       </c>
       <c r="AW23">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AX23">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AY23">
-        <v>1.41</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="BA23">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="BB23">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="BC23">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="BD23">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="BE23">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="BF23">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="BG23">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6477,22 +6477,22 @@
         <v>170</v>
       </c>
       <c r="F24">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H24">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I24">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J24">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6507,19 +6507,19 @@
         <v>1.2</v>
       </c>
       <c r="P24">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R24">
+        <v>1.57</v>
+      </c>
+      <c r="S24">
+        <v>2.44</v>
+      </c>
+      <c r="T24">
         <v>1.56</v>
-      </c>
-      <c r="S24">
-        <v>2.48</v>
-      </c>
-      <c r="T24">
-        <v>1.57</v>
       </c>
       <c r="U24">
         <v>2.5</v>
@@ -6543,7 +6543,7 @@
         <v>34</v>
       </c>
       <c r="AB24">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC24">
         <v>9.800000000000001</v>
@@ -6555,7 +6555,7 @@
         <v>24</v>
       </c>
       <c r="AF24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG24">
         <v>14.5</v>
@@ -6570,19 +6570,19 @@
         <v>50</v>
       </c>
       <c r="AK24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM24">
         <v>200</v>
       </c>
       <c r="AN24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO24">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP24">
         <v>17</v>
@@ -6591,25 +6591,25 @@
         <v>12.5</v>
       </c>
       <c r="AR24">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AS24">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AT24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU24">
         <v>8.800000000000001</v>
       </c>
       <c r="AV24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY24">
         <v>12</v>
@@ -6618,25 +6618,25 @@
         <v>12</v>
       </c>
       <c r="BA24">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BB24">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="BC24">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BD24">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BE24">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="BF24">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BG24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6749,10 +6749,10 @@
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q25">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R25">
         <v>1.82</v>
@@ -6761,7 +6761,7 @@
         <v>2.12</v>
       </c>
       <c r="T25">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U25">
         <v>2.28</v>
@@ -6773,7 +6773,7 @@
         <v>1.12</v>
       </c>
       <c r="X25">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="Y25">
         <v>13.5</v>
@@ -6785,10 +6785,10 @@
         <v>13</v>
       </c>
       <c r="AB25">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AC25">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD25">
         <v>11.5</v>
@@ -6800,16 +6800,16 @@
         <v>540</v>
       </c>
       <c r="AG25">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AH25">
         <v>24</v>
       </c>
       <c r="AI25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ25">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AK25">
         <v>480</v>
@@ -6824,7 +6824,7 @@
         <v>500</v>
       </c>
       <c r="AO25">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AP25">
         <v>14.5</v>
@@ -6836,13 +6836,13 @@
         <v>9.6</v>
       </c>
       <c r="AS25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT25">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AU25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV25">
         <v>9.4</v>
@@ -6851,34 +6851,34 @@
         <v>11.5</v>
       </c>
       <c r="AX25">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AY25">
         <v>14.5</v>
       </c>
       <c r="AZ25">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA25">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BB25">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC25">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BD25">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BE25">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BF25">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BG25">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6976,10 +6976,10 @@
         <v>3.1</v>
       </c>
       <c r="K26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L26">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M26">
         <v>1.12</v>
@@ -6994,7 +6994,7 @@
         <v>1.54</v>
       </c>
       <c r="Q26">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R26">
         <v>1.19</v>
@@ -7012,13 +7012,13 @@
         <v>1.22</v>
       </c>
       <c r="W26">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X26">
         <v>9.4</v>
       </c>
       <c r="Y26">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z26">
         <v>40</v>
@@ -7045,7 +7045,7 @@
         <v>12</v>
       </c>
       <c r="AH26">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI26">
         <v>700</v>
@@ -7057,13 +7057,13 @@
         <v>65</v>
       </c>
       <c r="AL26">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AM26">
         <v>500</v>
       </c>
       <c r="AN26">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AO26">
         <v>700</v>
@@ -7075,10 +7075,10 @@
         <v>11</v>
       </c>
       <c r="AR26">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AS26">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT26">
         <v>5.7</v>
@@ -7090,7 +7090,7 @@
         <v>18</v>
       </c>
       <c r="AW26">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX26">
         <v>8</v>
@@ -7102,7 +7102,7 @@
         <v>21</v>
       </c>
       <c r="BA26">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB26">
         <v>18</v>
@@ -7111,16 +7111,16 @@
         <v>20</v>
       </c>
       <c r="BD26">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE26">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF26">
         <v>17.5</v>
       </c>
       <c r="BG26">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7203,34 +7203,34 @@
         <v>173</v>
       </c>
       <c r="F27">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G27">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="H27">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I27">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L27">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O27">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P27">
         <v>2</v>
@@ -7239,31 +7239,31 @@
         <v>1.89</v>
       </c>
       <c r="R27">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S27">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T27">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U27">
         <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="X27">
         <v>18</v>
       </c>
       <c r="Y27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA27">
         <v>65</v>
@@ -7275,37 +7275,37 @@
         <v>8.6</v>
       </c>
       <c r="AD27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF27">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG27">
         <v>12</v>
       </c>
       <c r="AH27">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI27">
         <v>55</v>
       </c>
       <c r="AJ27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK27">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM27">
         <v>200</v>
       </c>
       <c r="AN27">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO27">
         <v>40</v>
@@ -7320,19 +7320,19 @@
         <v>19.5</v>
       </c>
       <c r="AS27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT27">
         <v>9.199999999999999</v>
       </c>
       <c r="AU27">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW27">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AX27">
         <v>13</v>
@@ -7344,25 +7344,25 @@
         <v>15</v>
       </c>
       <c r="BA27">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BB27">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BC27">
         <v>21</v>
       </c>
       <c r="BD27">
+        <v>30</v>
+      </c>
+      <c r="BE27">
+        <v>30</v>
+      </c>
+      <c r="BF27">
         <v>14.5</v>
       </c>
-      <c r="BE27">
-        <v>29</v>
-      </c>
-      <c r="BF27">
-        <v>16</v>
-      </c>
       <c r="BG27">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7445,37 +7445,37 @@
         <v>174</v>
       </c>
       <c r="F28">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="G28">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H28">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="I28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J28">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K28">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L28">
         <v>1.02</v>
       </c>
       <c r="M28">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N28">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O28">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P28">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q28">
         <v>2.16</v>
@@ -7484,31 +7484,31 @@
         <v>1.28</v>
       </c>
       <c r="S28">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T28">
         <v>1.94</v>
       </c>
       <c r="U28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V28">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y28">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z28">
         <v>13</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28">
         <v>26</v>
@@ -7517,94 +7517,94 @@
         <v>8.6</v>
       </c>
       <c r="AD28">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH28">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP28">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AQ28">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AR28">
-        <v>8.800000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="AS28">
         <v>16</v>
       </c>
       <c r="AT28">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AU28">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AV28">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="AW28">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AX28">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY28">
         <v>16</v>
       </c>
       <c r="AZ28">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA28">
-        <v>1.85</v>
+        <v>22</v>
       </c>
       <c r="BB28">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="BC28">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="BD28">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="BE28">
-        <v>19.5</v>
+        <v>2.52</v>
       </c>
       <c r="BF28">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="BG28">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7690,10 +7690,10 @@
         <v>2.52</v>
       </c>
       <c r="G29">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H29">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I29">
         <v>3.5</v>
@@ -7702,10 +7702,10 @@
         <v>3.1</v>
       </c>
       <c r="K29">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L29">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M29">
         <v>1.13</v>
@@ -7714,19 +7714,19 @@
         <v>2.66</v>
       </c>
       <c r="O29">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P29">
         <v>1.56</v>
       </c>
       <c r="Q29">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S29">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T29">
         <v>2.18</v>
@@ -7741,7 +7741,7 @@
         <v>1.62</v>
       </c>
       <c r="X29">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y29">
         <v>9.199999999999999</v>
@@ -7750,16 +7750,16 @@
         <v>22</v>
       </c>
       <c r="AA29">
-        <v>490</v>
+        <v>150</v>
       </c>
       <c r="AB29">
         <v>7.8</v>
       </c>
       <c r="AC29">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE29">
         <v>55</v>
@@ -7768,22 +7768,22 @@
         <v>14.5</v>
       </c>
       <c r="AG29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI29">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AJ29">
         <v>44</v>
       </c>
       <c r="AK29">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL29">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AM29">
         <v>1000</v>
@@ -7798,13 +7798,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ29">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR29">
         <v>18.5</v>
       </c>
       <c r="AS29">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT29">
         <v>7.2</v>
@@ -7825,25 +7825,25 @@
         <v>12</v>
       </c>
       <c r="AZ29">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BA29">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB29">
+        <v>28</v>
+      </c>
+      <c r="BC29">
         <v>30</v>
       </c>
-      <c r="BC29">
-        <v>26</v>
-      </c>
       <c r="BD29">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BE29">
         <v>95</v>
       </c>
       <c r="BF29">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BG29">
         <v>32</v>
@@ -7864,7 +7864,7 @@
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN29">
         <v>5.1</v>
@@ -7876,13 +7876,13 @@
         <v>22</v>
       </c>
       <c r="BQ29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR29">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="BS29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT29">
         <v>6.4</v>
@@ -7894,19 +7894,19 @@
         <v>36</v>
       </c>
       <c r="BW29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX29">
-        <v>640</v>
+        <v>540</v>
       </c>
       <c r="BY29">
+        <v>15</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
         <v>14.5</v>
-      </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
-        <v>14</v>
       </c>
       <c r="CB29" t="s">
         <v>181</v>
@@ -7929,19 +7929,19 @@
         <v>176</v>
       </c>
       <c r="F30">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G30">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H30">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="I30">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K30">
         <v>3.6</v>
@@ -7962,13 +7962,13 @@
         <v>1.94</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R30">
         <v>1.37</v>
       </c>
       <c r="S30">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T30">
         <v>1.77</v>
@@ -7977,10 +7977,10 @@
         <v>2.22</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X30">
         <v>14.5</v>
@@ -7989,10 +7989,10 @@
         <v>12.5</v>
       </c>
       <c r="Z30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA30">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB30">
         <v>11</v>
@@ -8004,25 +8004,25 @@
         <v>13.5</v>
       </c>
       <c r="AE30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG30">
         <v>12.5</v>
       </c>
       <c r="AH30">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI30">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ30">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL30">
         <v>46</v>
@@ -8031,10 +8031,10 @@
         <v>320</v>
       </c>
       <c r="AN30">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP30">
         <v>12.5</v>
@@ -8043,13 +8043,13 @@
         <v>10.5</v>
       </c>
       <c r="AR30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS30">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU30">
         <v>7.2</v>
@@ -8064,13 +8064,13 @@
         <v>15</v>
       </c>
       <c r="AY30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
         <v>15</v>
       </c>
       <c r="BA30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB30">
         <v>16</v>
@@ -8082,13 +8082,13 @@
         <v>32</v>
       </c>
       <c r="BE30">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF30">
         <v>19.5</v>
       </c>
       <c r="BG30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8186,10 +8186,10 @@
         <v>3.45</v>
       </c>
       <c r="K31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M31">
         <v>1.08</v>
@@ -8198,7 +8198,7 @@
         <v>3.4</v>
       </c>
       <c r="O31">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P31">
         <v>1.86</v>
@@ -8207,10 +8207,10 @@
         <v>2.1</v>
       </c>
       <c r="R31">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S31">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T31">
         <v>1.87</v>
@@ -8219,7 +8219,7 @@
         <v>2.02</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
         <v>1.82</v>
@@ -8231,67 +8231,67 @@
         <v>13.5</v>
       </c>
       <c r="Z31">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB31">
         <v>8.800000000000001</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD31">
         <v>16.5</v>
       </c>
       <c r="AE31">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG31">
         <v>11</v>
       </c>
       <c r="AH31">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI31">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ31">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK31">
         <v>25</v>
       </c>
       <c r="AL31">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM31">
         <v>130</v>
       </c>
       <c r="AN31">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO31">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31">
         <v>11.5</v>
       </c>
       <c r="AR31">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AS31">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="AT31">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU31">
         <v>7.2</v>
@@ -8300,37 +8300,37 @@
         <v>14</v>
       </c>
       <c r="AW31">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AX31">
         <v>11.5</v>
       </c>
       <c r="AY31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA31">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB31">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BC31">
         <v>21</v>
       </c>
       <c r="BD31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE31">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BF31">
         <v>16.5</v>
       </c>
       <c r="BG31">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BH31">
         <v>3.5</v>
@@ -8416,10 +8416,10 @@
         <v>2.1</v>
       </c>
       <c r="G32">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H32">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I32">
         <v>3.85</v>
@@ -8428,10 +8428,10 @@
         <v>3.6</v>
       </c>
       <c r="K32">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L32">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M32">
         <v>1.06</v>
@@ -8440,22 +8440,22 @@
         <v>4.1</v>
       </c>
       <c r="O32">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P32">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q32">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R32">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S32">
         <v>3.1</v>
       </c>
       <c r="T32">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U32">
         <v>2.24</v>
@@ -8464,28 +8464,28 @@
         <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X32">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y32">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z32">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA32">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC32">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD32">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE32">
         <v>50</v>
@@ -8494,22 +8494,22 @@
         <v>15</v>
       </c>
       <c r="AG32">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH32">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI32">
         <v>60</v>
       </c>
       <c r="AJ32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK32">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL32">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM32">
         <v>100</v>
@@ -8521,19 +8521,19 @@
         <v>46</v>
       </c>
       <c r="AP32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ32">
         <v>13</v>
       </c>
       <c r="AR32">
-        <v>19.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS32">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT32">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU32">
         <v>7.6</v>
@@ -8542,10 +8542,10 @@
         <v>13</v>
       </c>
       <c r="AW32">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY32">
         <v>9.6</v>
@@ -8554,25 +8554,25 @@
         <v>14.5</v>
       </c>
       <c r="BA32">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB32">
-        <v>19.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC32">
         <v>16</v>
       </c>
       <c r="BD32">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BE32">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BF32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG32">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8664,10 +8664,10 @@
         <v>2.56</v>
       </c>
       <c r="I33">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K33">
         <v>3.35</v>
@@ -8679,7 +8679,7 @@
         <v>1.1</v>
       </c>
       <c r="N33">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O33">
         <v>1.46</v>
@@ -8688,16 +8688,16 @@
         <v>1.66</v>
       </c>
       <c r="Q33">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R33">
         <v>1.25</v>
       </c>
       <c r="S33">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T33">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U33">
         <v>1.92</v>
@@ -8712,10 +8712,10 @@
         <v>11</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AA33">
         <v>46</v>
@@ -8724,22 +8724,22 @@
         <v>10.5</v>
       </c>
       <c r="AC33">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD33">
         <v>12.5</v>
       </c>
       <c r="AE33">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF33">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AG33">
         <v>15</v>
       </c>
       <c r="AH33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI33">
         <v>65</v>
@@ -8766,13 +8766,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR33">
         <v>13.5</v>
       </c>
       <c r="AS33">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="AT33">
         <v>9.199999999999999</v>
@@ -8784,73 +8784,73 @@
         <v>10.5</v>
       </c>
       <c r="AW33">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="AX33">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY33">
         <v>12.5</v>
       </c>
       <c r="AZ33">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA33">
-        <v>26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC33">
+        <v>36</v>
+      </c>
+      <c r="BD33">
+        <v>9.4</v>
+      </c>
+      <c r="BE33">
+        <v>9.4</v>
+      </c>
+      <c r="BF33">
+        <v>9</v>
+      </c>
+      <c r="BG33">
         <v>8.4</v>
       </c>
-      <c r="BC33">
-        <v>8</v>
-      </c>
-      <c r="BD33">
-        <v>8.4</v>
-      </c>
-      <c r="BE33">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF33">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG33">
-        <v>7.6</v>
-      </c>
       <c r="BH33">
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
@@ -8862,19 +8862,19 @@
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
         <v>181</v>
@@ -8900,7 +8900,7 @@
         <v>1.83</v>
       </c>
       <c r="G34">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H34">
         <v>5.5</v>
@@ -8909,10 +8909,10 @@
         <v>5.9</v>
       </c>
       <c r="J34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K34">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L34">
         <v>1.53</v>
@@ -8930,7 +8930,7 @@
         <v>1.6</v>
       </c>
       <c r="Q34">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R34">
         <v>1.22</v>
@@ -8939,7 +8939,7 @@
         <v>5</v>
       </c>
       <c r="T34">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U34">
         <v>1.73</v>
@@ -8948,7 +8948,7 @@
         <v>1.2</v>
       </c>
       <c r="W34">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X34">
         <v>9.6</v>
@@ -8957,7 +8957,7 @@
         <v>14.5</v>
       </c>
       <c r="Z34">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA34">
         <v>230</v>
@@ -8975,7 +8975,7 @@
         <v>140</v>
       </c>
       <c r="AF34">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG34">
         <v>11.5</v>
@@ -9011,10 +9011,10 @@
         <v>12.5</v>
       </c>
       <c r="AR34">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS34">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT34">
         <v>5.8</v>
@@ -9026,7 +9026,7 @@
         <v>21</v>
       </c>
       <c r="AW34">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX34">
         <v>8.6</v>
@@ -9038,25 +9038,25 @@
         <v>20</v>
       </c>
       <c r="BA34">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB34">
         <v>18.5</v>
       </c>
       <c r="BC34">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD34">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE34">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF34">
         <v>16.5</v>
       </c>
       <c r="BG34">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH34">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="174">
   <si>
     <t>League</t>
   </si>
@@ -286,6 +286,9 @@
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>CONCACAF Nations League A</t>
   </si>
   <si>
@@ -331,6 +334,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -391,15 +397,15 @@
     <t>Wexford F.C</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
     <t>St Lucia</t>
   </si>
   <si>
@@ -409,6 +415,12 @@
     <t>IRT Tanger</t>
   </si>
   <si>
+    <t>San Antonio FC</t>
+  </si>
+  <si>
+    <t>CD Cuenca Juniors</t>
+  </si>
+  <si>
     <t>Suriname</t>
   </si>
   <si>
@@ -475,15 +487,15 @@
     <t>Longford</t>
   </si>
   <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
     <t>Kerry FC</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
     <t>Guadeloupe</t>
   </si>
   <si>
@@ -493,6 +505,12 @@
     <t>Moghreb Tetouan</t>
   </si>
   <si>
+    <t>Vinotinto Ecuador</t>
+  </si>
+  <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>Guatemala</t>
   </si>
   <si>
@@ -517,7 +535,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-02 02:12:51</t>
+    <t>2026-10-02 04:29:15</t>
   </si>
 </sst>
 </file>
@@ -849,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1099,28 +1117,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F2">
         <v>2.94</v>
       </c>
       <c r="G2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H2">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I2">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J2">
         <v>3.45</v>
@@ -1129,19 +1147,19 @@
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O2">
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
         <v>1.98</v>
@@ -1156,7 +1174,7 @@
         <v>1.76</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
         <v>1.6</v>
@@ -1165,22 +1183,22 @@
         <v>1.48</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB2">
         <v>12.5</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD2">
         <v>12.5</v>
@@ -1189,7 +1207,7 @@
         <v>29</v>
       </c>
       <c r="AF2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG2">
         <v>13.5</v>
@@ -1201,16 +1219,16 @@
         <v>42</v>
       </c>
       <c r="AJ2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK2">
         <v>36</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN2">
         <v>32</v>
@@ -1219,16 +1237,16 @@
         <v>24</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2">
         <v>14.5</v>
       </c>
       <c r="AS2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1240,16 +1258,16 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY2">
         <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2">
         <v>29</v>
@@ -1264,16 +1282,16 @@
         <v>32</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG2">
         <v>19</v>
       </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
         <v>3.05</v>
@@ -1282,58 +1300,58 @@
         <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
         <v>6.2</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>36</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>5.6</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>28</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1341,34 +1359,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G3">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
         <v>1.51</v>
@@ -1380,67 +1398,67 @@
         <v>3</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
         <v>1.2</v>
       </c>
       <c r="W3">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X3">
         <v>970</v>
       </c>
       <c r="Y3">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Z3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="AD3">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF3">
         <v>11.5</v>
       </c>
       <c r="AG3">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ3">
         <v>900</v>
@@ -1449,7 +1467,7 @@
         <v>150</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM3">
         <v>580</v>
@@ -1458,61 +1476,61 @@
         <v>600</v>
       </c>
       <c r="AO3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.75</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3">
-        <v>1.87</v>
+        <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>1.9</v>
+        <v>27</v>
       </c>
       <c r="AS3">
-        <v>1.96</v>
+        <v>70</v>
       </c>
       <c r="AT3">
-        <v>1.62</v>
+        <v>5.2</v>
       </c>
       <c r="AU3">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.93</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>1.96</v>
+        <v>42</v>
       </c>
       <c r="AX3">
-        <v>1.67</v>
+        <v>7.4</v>
       </c>
       <c r="AY3">
-        <v>1.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>1.96</v>
+        <v>42</v>
       </c>
       <c r="BB3">
-        <v>1.96</v>
+        <v>14</v>
       </c>
       <c r="BC3">
-        <v>1.91</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>1.96</v>
+        <v>30</v>
       </c>
       <c r="BE3">
-        <v>1.96</v>
+        <v>80</v>
       </c>
       <c r="BF3">
-        <v>1.9</v>
+        <v>12.5</v>
       </c>
       <c r="BG3">
-        <v>1.96</v>
+        <v>60</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1575,7 +1593,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1583,112 +1601,112 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F4">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
+        <v>1.43</v>
+      </c>
+      <c r="M4">
+        <v>1.07</v>
+      </c>
+      <c r="N4">
+        <v>3.65</v>
+      </c>
+      <c r="O4">
+        <v>1.32</v>
+      </c>
+      <c r="P4">
+        <v>1.92</v>
+      </c>
+      <c r="Q4">
+        <v>1.92</v>
+      </c>
+      <c r="R4">
         <v>1.37</v>
       </c>
-      <c r="M4">
-        <v>1.06</v>
-      </c>
-      <c r="N4">
-        <v>4.3</v>
-      </c>
-      <c r="O4">
-        <v>1.28</v>
-      </c>
-      <c r="P4">
+      <c r="S4">
+        <v>3.35</v>
+      </c>
+      <c r="T4">
+        <v>1.73</v>
+      </c>
+      <c r="U4">
         <v>2.14</v>
       </c>
-      <c r="Q4">
-        <v>1.82</v>
-      </c>
-      <c r="R4">
-        <v>1.44</v>
-      </c>
-      <c r="S4">
-        <v>3.05</v>
-      </c>
-      <c r="T4">
-        <v>1.64</v>
-      </c>
-      <c r="U4">
-        <v>2.28</v>
-      </c>
       <c r="V4">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X4">
+        <v>15.5</v>
+      </c>
+      <c r="Y4">
+        <v>12</v>
+      </c>
+      <c r="Z4">
+        <v>18</v>
+      </c>
+      <c r="AA4">
+        <v>95</v>
+      </c>
+      <c r="AB4">
+        <v>13</v>
+      </c>
+      <c r="AC4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>13</v>
+      </c>
+      <c r="AE4">
+        <v>34</v>
+      </c>
+      <c r="AF4">
+        <v>22</v>
+      </c>
+      <c r="AG4">
+        <v>14.5</v>
+      </c>
+      <c r="AH4">
         <v>17.5</v>
       </c>
-      <c r="Y4">
-        <v>13</v>
-      </c>
-      <c r="Z4">
-        <v>18.5</v>
-      </c>
-      <c r="AA4">
-        <v>900</v>
-      </c>
-      <c r="AB4">
-        <v>14.5</v>
-      </c>
-      <c r="AC4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD4">
-        <v>12.5</v>
-      </c>
-      <c r="AE4">
-        <v>75</v>
-      </c>
-      <c r="AF4">
-        <v>90</v>
-      </c>
-      <c r="AG4">
-        <v>13.5</v>
-      </c>
-      <c r="AH4">
-        <v>16.5</v>
-      </c>
       <c r="AI4">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="AJ4">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AK4">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="AL4">
         <v>290</v>
@@ -1697,64 +1715,64 @@
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP4">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
+        <v>9</v>
+      </c>
+      <c r="AR4">
+        <v>14</v>
+      </c>
+      <c r="AS4">
+        <v>12.5</v>
+      </c>
+      <c r="AT4">
+        <v>10</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
         <v>10.5</v>
       </c>
-      <c r="AR4">
-        <v>15</v>
-      </c>
-      <c r="AS4">
-        <v>6.8</v>
-      </c>
-      <c r="AT4">
-        <v>11.5</v>
-      </c>
-      <c r="AU4">
-        <v>7.2</v>
-      </c>
-      <c r="AV4">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AW4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX4">
         <v>17</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BB4">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1817,7 +1835,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1825,190 +1843,190 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F5">
         <v>2.08</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H5">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
         <v>3.9</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.38</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q5">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="R5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T5">
         <v>1.72</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="V5">
         <v>1.34</v>
       </c>
       <c r="W5">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X5">
+        <v>18</v>
+      </c>
+      <c r="Y5">
+        <v>18.5</v>
+      </c>
+      <c r="Z5">
+        <v>32</v>
+      </c>
+      <c r="AA5">
+        <v>75</v>
+      </c>
+      <c r="AB5">
+        <v>12</v>
+      </c>
+      <c r="AC5">
+        <v>9</v>
+      </c>
+      <c r="AD5">
         <v>16.5</v>
       </c>
-      <c r="Y5">
-        <v>16</v>
-      </c>
-      <c r="Z5">
-        <v>29</v>
-      </c>
-      <c r="AA5">
-        <v>170</v>
-      </c>
-      <c r="AB5">
-        <v>11</v>
-      </c>
-      <c r="AC5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD5">
-        <v>19.5</v>
-      </c>
       <c r="AE5">
+        <v>46</v>
+      </c>
+      <c r="AF5">
+        <v>16.5</v>
+      </c>
+      <c r="AG5">
+        <v>11.5</v>
+      </c>
+      <c r="AH5">
+        <v>18.5</v>
+      </c>
+      <c r="AI5">
         <v>55</v>
       </c>
-      <c r="AF5">
-        <v>14</v>
-      </c>
-      <c r="AG5">
-        <v>13</v>
-      </c>
-      <c r="AH5">
-        <v>20</v>
-      </c>
-      <c r="AI5">
-        <v>60</v>
-      </c>
       <c r="AJ5">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL5">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO5">
         <v>55</v>
       </c>
       <c r="AP5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AS5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW5">
+        <v>32</v>
+      </c>
+      <c r="AX5">
+        <v>12</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
+        <v>14</v>
+      </c>
+      <c r="BA5">
+        <v>36</v>
+      </c>
+      <c r="BB5">
+        <v>23</v>
+      </c>
+      <c r="BC5">
+        <v>16.5</v>
+      </c>
+      <c r="BD5">
+        <v>25</v>
+      </c>
+      <c r="BE5">
+        <v>55</v>
+      </c>
+      <c r="BF5">
+        <v>11.5</v>
+      </c>
+      <c r="BG5">
         <v>20</v>
       </c>
-      <c r="AX5">
-        <v>11.5</v>
-      </c>
-      <c r="AY5">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5">
-        <v>14.5</v>
-      </c>
-      <c r="BA5">
-        <v>6.8</v>
-      </c>
-      <c r="BB5">
-        <v>14.5</v>
-      </c>
-      <c r="BC5">
-        <v>18</v>
-      </c>
-      <c r="BD5">
-        <v>21</v>
-      </c>
-      <c r="BE5">
-        <v>7.2</v>
-      </c>
-      <c r="BF5">
-        <v>12</v>
-      </c>
-      <c r="BG5">
-        <v>18.5</v>
-      </c>
       <c r="BH5">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK5">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2017,10 +2035,10 @@
         <v>5.6</v>
       </c>
       <c r="BN5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP5">
         <v>17.5</v>
@@ -2032,34 +2050,34 @@
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BT5">
         <v>8</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BW5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BZ5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CA5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2067,76 +2085,76 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H6">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I6">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
         <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R6">
         <v>1.49</v>
       </c>
       <c r="S6">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T6">
         <v>1.61</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="V6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W6">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X6">
         <v>22</v>
       </c>
       <c r="Y6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z6">
         <v>19.5</v>
@@ -2145,163 +2163,163 @@
         <v>38</v>
       </c>
       <c r="AB6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AE6">
         <v>27</v>
       </c>
       <c r="AF6">
+        <v>25</v>
+      </c>
+      <c r="AG6">
+        <v>15.5</v>
+      </c>
+      <c r="AH6">
+        <v>18.5</v>
+      </c>
+      <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
+        <v>55</v>
+      </c>
+      <c r="AK6">
+        <v>34</v>
+      </c>
+      <c r="AL6">
+        <v>42</v>
+      </c>
+      <c r="AM6">
+        <v>85</v>
+      </c>
+      <c r="AN6">
+        <v>25</v>
+      </c>
+      <c r="AO6">
+        <v>18.5</v>
+      </c>
+      <c r="AP6">
+        <v>15</v>
+      </c>
+      <c r="AQ6">
+        <v>10</v>
+      </c>
+      <c r="AR6">
+        <v>14</v>
+      </c>
+      <c r="AS6">
         <v>23</v>
       </c>
-      <c r="AG6">
-        <v>14</v>
-      </c>
-      <c r="AH6">
-        <v>16.5</v>
-      </c>
-      <c r="AI6">
-        <v>36</v>
-      </c>
-      <c r="AJ6">
-        <v>900</v>
-      </c>
-      <c r="AK6">
-        <v>32</v>
-      </c>
-      <c r="AL6">
-        <v>38</v>
-      </c>
-      <c r="AM6">
-        <v>80</v>
-      </c>
-      <c r="AN6">
-        <v>23</v>
-      </c>
-      <c r="AO6">
-        <v>18</v>
-      </c>
-      <c r="AP6">
-        <v>16</v>
-      </c>
-      <c r="AQ6">
-        <v>11</v>
-      </c>
-      <c r="AR6">
-        <v>15.5</v>
-      </c>
-      <c r="AS6">
-        <v>22</v>
-      </c>
       <c r="AT6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY6">
         <v>11</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA6">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="BB6">
         <v>30</v>
       </c>
       <c r="BC6">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="BE6">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF6">
         <v>18</v>
       </c>
       <c r="BG6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI6">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK6">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BL6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BN6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO6">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ6">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BR6">
         <v>34</v>
       </c>
       <c r="BS6">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BW6">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY6">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BZ6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA6">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="CB6" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2309,31 +2327,31 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
         <v>2.06</v>
       </c>
-      <c r="G7">
-        <v>2.14</v>
-      </c>
       <c r="H7">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K7">
         <v>4.9</v>
@@ -2345,34 +2363,34 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O7">
         <v>1.09</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="T7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="X7">
         <v>55</v>
@@ -2381,19 +2399,19 @@
         <v>36</v>
       </c>
       <c r="Z7">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA7">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB7">
         <v>28</v>
       </c>
       <c r="AC7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE7">
         <v>34</v>
@@ -2402,13 +2420,13 @@
         <v>28</v>
       </c>
       <c r="AG7">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
         <v>14</v>
       </c>
       <c r="AI7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ7">
         <v>36</v>
@@ -2420,13 +2438,13 @@
         <v>21</v>
       </c>
       <c r="AM7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN7">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP7">
         <v>29</v>
@@ -2438,7 +2456,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AT7">
         <v>21</v>
@@ -2450,10 +2468,10 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX7">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AY7">
         <v>11.5</v>
@@ -2465,25 +2483,25 @@
         <v>20</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE7">
         <v>29</v>
       </c>
       <c r="BF7">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG7">
         <v>10</v>
       </c>
       <c r="BH7">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BI7">
         <v>5.3</v>
@@ -2495,10 +2513,10 @@
         <v>6.4</v>
       </c>
       <c r="BL7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BM7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BN7">
         <v>6.4</v>
@@ -2507,16 +2525,16 @@
         <v>5.4</v>
       </c>
       <c r="BP7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BR7">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BS7">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BT7">
         <v>8.800000000000001</v>
@@ -2525,25 +2543,25 @@
         <v>4.2</v>
       </c>
       <c r="BV7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BW7">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BX7">
         <v>21</v>
       </c>
       <c r="BY7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BZ7">
         <v>9</v>
       </c>
       <c r="CA7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2551,34 +2569,34 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G8">
         <v>2.44</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8">
         <v>3.35</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.36</v>
@@ -2590,7 +2608,7 @@
         <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
         <v>2.08</v>
@@ -2605,13 +2623,13 @@
         <v>3.1</v>
       </c>
       <c r="T8">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U8">
         <v>2.12</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
         <v>1.69</v>
@@ -2632,7 +2650,7 @@
         <v>950</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD8">
         <v>950</v>
@@ -2671,10 +2689,10 @@
         <v>600</v>
       </c>
       <c r="AP8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AQ8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AR8">
         <v>1.3</v>
@@ -2683,34 +2701,34 @@
         <v>1.31</v>
       </c>
       <c r="AT8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AU8">
         <v>5.1</v>
       </c>
       <c r="AV8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AW8">
         <v>1.31</v>
       </c>
       <c r="AX8">
+        <v>1.3</v>
+      </c>
+      <c r="AY8">
         <v>1.29</v>
       </c>
-      <c r="AY8">
-        <v>1.28</v>
-      </c>
       <c r="AZ8">
-        <v>1.25</v>
+        <v>9</v>
       </c>
       <c r="BA8">
         <v>1.31</v>
       </c>
       <c r="BB8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BC8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BD8">
         <v>1.31</v>
@@ -2785,7 +2803,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2793,31 +2811,31 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F9">
         <v>3.25</v>
       </c>
       <c r="G9">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H9">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="I9">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -2826,37 +2844,37 @@
         <v>1.31</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O9">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P9">
         <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S9">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T9">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U9">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X9">
         <v>24</v>
@@ -2916,7 +2934,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR9">
         <v>12</v>
@@ -2925,16 +2943,16 @@
         <v>20</v>
       </c>
       <c r="AT9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
       </c>
       <c r="AV9">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW9">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX9">
         <v>20</v>
@@ -2946,22 +2964,22 @@
         <v>12</v>
       </c>
       <c r="BA9">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BB9">
         <v>5.9</v>
       </c>
       <c r="BC9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE9">
         <v>6</v>
       </c>
       <c r="BF9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG9">
         <v>10</v>
@@ -2976,13 +2994,13 @@
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN9">
         <v>8</v>
@@ -2994,13 +3012,13 @@
         <v>29</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR9">
         <v>38</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT9">
         <v>6</v>
@@ -3012,22 +3030,22 @@
         <v>16.5</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX9">
         <v>28</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3035,16 +3053,16 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F10">
         <v>1.43</v>
@@ -3068,10 +3086,10 @@
         <v>1.26</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O10">
         <v>1.17</v>
@@ -3080,13 +3098,13 @@
         <v>2.72</v>
       </c>
       <c r="Q10">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S10">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T10">
         <v>1.75</v>
@@ -3179,10 +3197,10 @@
         <v>48</v>
       </c>
       <c r="AX10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
         <v>20</v>
@@ -3200,7 +3218,7 @@
         <v>23</v>
       </c>
       <c r="BE10">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF10">
         <v>4.6</v>
@@ -3230,7 +3248,7 @@
         <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
         <v>8.800000000000001</v>
@@ -3248,7 +3266,7 @@
         <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV10">
         <v>55</v>
@@ -3269,7 +3287,7 @@
         <v>5.8</v>
       </c>
       <c r="CB10" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3277,34 +3295,34 @@
         <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G11">
         <v>3.3</v>
       </c>
       <c r="H11">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J11">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="K11">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="L11">
         <v>1.65</v>
@@ -3313,31 +3331,31 @@
         <v>1.17</v>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O11">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P11">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R11">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
         <v>6</v>
       </c>
       <c r="T11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U11">
         <v>1.76</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
         <v>1.43</v>
@@ -3346,7 +3364,7 @@
         <v>970</v>
       </c>
       <c r="Y11">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z11">
         <v>500</v>
@@ -3358,7 +3376,7 @@
         <v>970</v>
       </c>
       <c r="AC11">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD11">
         <v>970</v>
@@ -3370,7 +3388,7 @@
         <v>970</v>
       </c>
       <c r="AG11">
-        <v>150</v>
+        <v>970</v>
       </c>
       <c r="AH11">
         <v>500</v>
@@ -3391,64 +3409,64 @@
         <v>500</v>
       </c>
       <c r="AN11">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
-        <v>7.4</v>
+        <v>1.88</v>
       </c>
       <c r="AR11">
-        <v>1.21</v>
+        <v>2.5</v>
       </c>
       <c r="AS11">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="AT11">
-        <v>7.4</v>
+        <v>1.87</v>
       </c>
       <c r="AU11">
-        <v>1.19</v>
+        <v>1.93</v>
       </c>
       <c r="AV11">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
       <c r="AW11">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="AX11">
-        <v>1.21</v>
+        <v>2.08</v>
       </c>
       <c r="AY11">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AZ11">
-        <v>1.29</v>
+        <v>2.66</v>
       </c>
       <c r="BA11">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="BB11">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="BC11">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="BD11">
-        <v>1.22</v>
+        <v>2.08</v>
       </c>
       <c r="BE11">
-        <v>1.23</v>
+        <v>2.32</v>
       </c>
       <c r="BF11">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="BG11">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3511,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3519,79 +3537,79 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F12">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="G12">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="H12">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="I12">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
+        <v>3.1</v>
+      </c>
+      <c r="K12">
         <v>3.15</v>
       </c>
-      <c r="K12">
-        <v>3.2</v>
-      </c>
       <c r="L12">
+        <v>1.59</v>
+      </c>
+      <c r="M12">
+        <v>1.13</v>
+      </c>
+      <c r="N12">
+        <v>2.7</v>
+      </c>
+      <c r="O12">
+        <v>1.57</v>
+      </c>
+      <c r="P12">
         <v>1.56</v>
       </c>
-      <c r="M12">
-        <v>1.12</v>
-      </c>
-      <c r="N12">
-        <v>2.82</v>
-      </c>
-      <c r="O12">
-        <v>1.53</v>
-      </c>
-      <c r="P12">
-        <v>1.6</v>
-      </c>
       <c r="Q12">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="R12">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S12">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T12">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U12">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="X12">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA12">
         <v>70</v>
@@ -3603,52 +3621,52 @@
         <v>7.2</v>
       </c>
       <c r="AD12">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE12">
         <v>55</v>
       </c>
       <c r="AF12">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ12">
+        <v>46</v>
+      </c>
+      <c r="AK12">
         <v>40</v>
       </c>
-      <c r="AK12">
-        <v>34</v>
-      </c>
       <c r="AL12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM12">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN12">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AO12">
         <v>75</v>
       </c>
       <c r="AP12">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ12">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR12">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS12">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AT12">
         <v>7.2</v>
@@ -3657,16 +3675,16 @@
         <v>6.6</v>
       </c>
       <c r="AV12">
+        <v>13.5</v>
+      </c>
+      <c r="AW12">
+        <v>36</v>
+      </c>
+      <c r="AX12">
         <v>14.5</v>
       </c>
-      <c r="AW12">
-        <v>46</v>
-      </c>
-      <c r="AX12">
-        <v>12.5</v>
-      </c>
       <c r="AY12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
         <v>20</v>
@@ -3675,85 +3693,85 @@
         <v>55</v>
       </c>
       <c r="BB12">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BC12">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD12">
         <v>50</v>
       </c>
       <c r="BE12">
-        <v>16.5</v>
+        <v>100</v>
       </c>
       <c r="BF12">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BG12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH12">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BI12">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>7.2</v>
+        <v>2.68</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BN12">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU12">
-        <v>2.14</v>
+        <v>4.1</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CB12" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3761,16 +3779,16 @@
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F13">
         <v>4</v>
@@ -3779,16 +3797,16 @@
         <v>4.2</v>
       </c>
       <c r="H13">
+        <v>1.94</v>
+      </c>
+      <c r="I13">
         <v>1.97</v>
       </c>
-      <c r="I13">
-        <v>1.99</v>
-      </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.29</v>
@@ -3806,7 +3824,7 @@
         <v>2.62</v>
       </c>
       <c r="Q13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R13">
         <v>1.67</v>
@@ -3815,22 +3833,22 @@
         <v>2.42</v>
       </c>
       <c r="T13">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U13">
         <v>2.58</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W13">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z13">
         <v>15</v>
@@ -3842,7 +3860,7 @@
         <v>23</v>
       </c>
       <c r="AC13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13">
         <v>11</v>
@@ -3851,7 +3869,7 @@
         <v>18.5</v>
       </c>
       <c r="AF13">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AG13">
         <v>17.5</v>
@@ -3878,7 +3896,7 @@
         <v>30</v>
       </c>
       <c r="AO13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP13">
         <v>20</v>
@@ -3890,10 +3908,10 @@
         <v>13.5</v>
       </c>
       <c r="AS13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU13">
         <v>8.800000000000001</v>
@@ -3905,7 +3923,7 @@
         <v>15.5</v>
       </c>
       <c r="AX13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AY13">
         <v>14.5</v>
@@ -3929,73 +3947,73 @@
         <v>48</v>
       </c>
       <c r="BF13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BG13">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI13">
-        <v>1.32</v>
+        <v>4</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK13">
-        <v>1.81</v>
+        <v>5.2</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM13">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO13">
-        <v>1.58</v>
+        <v>6.8</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.66</v>
+        <v>8.4</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.66</v>
+        <v>8.6</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU13">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW13">
-        <v>1.81</v>
+        <v>6.4</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY13">
-        <v>1.44</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA13">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4003,16 +4021,16 @@
         <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F14">
         <v>3.55</v>
@@ -4021,16 +4039,16 @@
         <v>3.8</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I14">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J14">
         <v>3.95</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14">
         <v>1.3</v>
@@ -4051,7 +4069,7 @@
         <v>1.64</v>
       </c>
       <c r="R14">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S14">
         <v>2.58</v>
@@ -4063,16 +4081,16 @@
         <v>2.48</v>
       </c>
       <c r="V14">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X14">
         <v>27</v>
       </c>
       <c r="Y14">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z14">
         <v>16.5</v>
@@ -4087,7 +4105,7 @@
         <v>10</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE14">
         <v>23</v>
@@ -4105,7 +4123,7 @@
         <v>32</v>
       </c>
       <c r="AJ14">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK14">
         <v>40</v>
@@ -4114,7 +4132,7 @@
         <v>44</v>
       </c>
       <c r="AM14">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AN14">
         <v>30</v>
@@ -4123,7 +4141,7 @@
         <v>10.5</v>
       </c>
       <c r="AP14">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ14">
         <v>11.5</v>
@@ -4147,7 +4165,7 @@
         <v>17</v>
       </c>
       <c r="AX14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY14">
         <v>13</v>
@@ -4156,22 +4174,22 @@
         <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB14">
-        <v>6.6</v>
+        <v>44</v>
       </c>
       <c r="BC14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BD14">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BE14">
-        <v>6.6</v>
+        <v>50</v>
       </c>
       <c r="BF14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG14">
         <v>8.800000000000001</v>
@@ -4186,13 +4204,13 @@
         <v>10</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BN14">
         <v>8.4</v>
@@ -4204,13 +4222,13 @@
         <v>30</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR14">
         <v>36</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT14">
         <v>5.9</v>
@@ -4222,22 +4240,22 @@
         <v>15.5</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX14">
         <v>26</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ14">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4245,28 +4263,28 @@
         <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F15">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G15">
         <v>1.88</v>
       </c>
       <c r="H15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4287,34 +4305,34 @@
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q15">
         <v>1.8</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T15">
         <v>1.69</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
         <v>1.27</v>
       </c>
       <c r="W15">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y15">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="Z15">
         <v>170</v>
@@ -4323,10 +4341,10 @@
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC15">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
         <v>950</v>
@@ -4335,19 +4353,19 @@
         <v>340</v>
       </c>
       <c r="AF15">
-        <v>120</v>
+        <v>14.5</v>
       </c>
       <c r="AG15">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH15">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI15">
         <v>460</v>
       </c>
       <c r="AJ15">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK15">
         <v>150</v>
@@ -4359,64 +4377,64 @@
         <v>580</v>
       </c>
       <c r="AN15">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="AO15">
-        <v>290</v>
+        <v>600</v>
       </c>
       <c r="AP15">
-        <v>1.57</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15">
-        <v>1.55</v>
+        <v>15</v>
       </c>
       <c r="AR15">
-        <v>1.56</v>
+        <v>26</v>
       </c>
       <c r="AS15">
-        <v>1.56</v>
+        <v>44</v>
       </c>
       <c r="AT15">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU15">
-        <v>1.41</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>1.55</v>
+        <v>14</v>
       </c>
       <c r="AW15">
-        <v>1.56</v>
+        <v>34</v>
       </c>
       <c r="AX15">
-        <v>1.51</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15">
-        <v>1.53</v>
+        <v>15.5</v>
       </c>
       <c r="BA15">
-        <v>1.57</v>
+        <v>36</v>
       </c>
       <c r="BB15">
-        <v>1.55</v>
+        <v>15</v>
       </c>
       <c r="BC15">
-        <v>1.53</v>
+        <v>14</v>
       </c>
       <c r="BD15">
-        <v>1.56</v>
+        <v>23</v>
       </c>
       <c r="BE15">
-        <v>1.56</v>
+        <v>44</v>
       </c>
       <c r="BF15">
-        <v>1.43</v>
+        <v>7.6</v>
       </c>
       <c r="BG15">
-        <v>1.56</v>
+        <v>20</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4479,7 +4497,7 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4487,178 +4505,178 @@
         <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F16">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="G16">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="H16">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="I16">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="K16">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
+        <v>1.32</v>
+      </c>
+      <c r="M16">
+        <v>1.04</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16">
+        <v>1.22</v>
+      </c>
+      <c r="P16">
+        <v>2.38</v>
+      </c>
+      <c r="Q16">
+        <v>1.68</v>
+      </c>
+      <c r="R16">
+        <v>1.55</v>
+      </c>
+      <c r="S16">
+        <v>2.72</v>
+      </c>
+      <c r="T16">
+        <v>1.6</v>
+      </c>
+      <c r="U16">
+        <v>2.44</v>
+      </c>
+      <c r="V16">
+        <v>1.75</v>
+      </c>
+      <c r="W16">
         <v>1.46</v>
       </c>
-      <c r="M16">
-        <v>1.08</v>
-      </c>
-      <c r="N16">
-        <v>3.4</v>
-      </c>
-      <c r="O16">
-        <v>1.38</v>
-      </c>
-      <c r="P16">
-        <v>1.83</v>
-      </c>
-      <c r="Q16">
-        <v>2.12</v>
-      </c>
-      <c r="R16">
-        <v>1.3</v>
-      </c>
-      <c r="S16">
-        <v>4</v>
-      </c>
-      <c r="T16">
-        <v>1.9</v>
-      </c>
-      <c r="U16">
-        <v>1.98</v>
-      </c>
-      <c r="V16">
-        <v>1.92</v>
-      </c>
-      <c r="W16">
-        <v>1.29</v>
-      </c>
       <c r="X16">
+        <v>26</v>
+      </c>
+      <c r="Y16">
         <v>14</v>
       </c>
-      <c r="Y16">
-        <v>9.4</v>
-      </c>
       <c r="Z16">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AA16">
+        <v>32</v>
+      </c>
+      <c r="AB16">
+        <v>17</v>
+      </c>
+      <c r="AC16">
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
+        <v>12</v>
+      </c>
+      <c r="AE16">
+        <v>23</v>
+      </c>
+      <c r="AF16">
         <v>26</v>
       </c>
-      <c r="AB16">
-        <v>15.5</v>
-      </c>
-      <c r="AC16">
+      <c r="AG16">
+        <v>14.5</v>
+      </c>
+      <c r="AH16">
+        <v>17</v>
+      </c>
+      <c r="AI16">
+        <v>32</v>
+      </c>
+      <c r="AJ16">
+        <v>60</v>
+      </c>
+      <c r="AK16">
+        <v>34</v>
+      </c>
+      <c r="AL16">
+        <v>38</v>
+      </c>
+      <c r="AM16">
+        <v>80</v>
+      </c>
+      <c r="AN16">
+        <v>24</v>
+      </c>
+      <c r="AO16">
+        <v>13.5</v>
+      </c>
+      <c r="AP16">
+        <v>19.5</v>
+      </c>
+      <c r="AQ16">
+        <v>11.5</v>
+      </c>
+      <c r="AR16">
+        <v>14</v>
+      </c>
+      <c r="AS16">
+        <v>22</v>
+      </c>
+      <c r="AT16">
+        <v>14</v>
+      </c>
+      <c r="AU16">
         <v>8.6</v>
       </c>
-      <c r="AD16">
+      <c r="AV16">
+        <v>10</v>
+      </c>
+      <c r="AW16">
+        <v>18</v>
+      </c>
+      <c r="AX16">
+        <v>20</v>
+      </c>
+      <c r="AY16">
+        <v>12</v>
+      </c>
+      <c r="AZ16">
+        <v>14</v>
+      </c>
+      <c r="BA16">
+        <v>23</v>
+      </c>
+      <c r="BB16">
+        <v>34</v>
+      </c>
+      <c r="BC16">
+        <v>23</v>
+      </c>
+      <c r="BD16">
+        <v>27</v>
+      </c>
+      <c r="BE16">
+        <v>55</v>
+      </c>
+      <c r="BF16">
+        <v>19</v>
+      </c>
+      <c r="BG16">
         <v>11</v>
-      </c>
-      <c r="AE16">
-        <v>25</v>
-      </c>
-      <c r="AF16">
-        <v>44</v>
-      </c>
-      <c r="AG16">
-        <v>19</v>
-      </c>
-      <c r="AH16">
-        <v>22</v>
-      </c>
-      <c r="AI16">
-        <v>50</v>
-      </c>
-      <c r="AJ16">
-        <v>900</v>
-      </c>
-      <c r="AK16">
-        <v>170</v>
-      </c>
-      <c r="AL16">
-        <v>210</v>
-      </c>
-      <c r="AM16">
-        <v>580</v>
-      </c>
-      <c r="AN16">
-        <v>270</v>
-      </c>
-      <c r="AO16">
-        <v>19.5</v>
-      </c>
-      <c r="AP16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ16">
-        <v>6.8</v>
-      </c>
-      <c r="AR16">
-        <v>10</v>
-      </c>
-      <c r="AS16">
-        <v>20</v>
-      </c>
-      <c r="AT16">
-        <v>11.5</v>
-      </c>
-      <c r="AU16">
-        <v>6.6</v>
-      </c>
-      <c r="AV16">
-        <v>8.6</v>
-      </c>
-      <c r="AW16">
-        <v>19.5</v>
-      </c>
-      <c r="AX16">
-        <v>23</v>
-      </c>
-      <c r="AY16">
-        <v>15</v>
-      </c>
-      <c r="AZ16">
-        <v>17</v>
-      </c>
-      <c r="BA16">
-        <v>28</v>
-      </c>
-      <c r="BB16">
-        <v>7</v>
-      </c>
-      <c r="BC16">
-        <v>42</v>
-      </c>
-      <c r="BD16">
-        <v>6.8</v>
-      </c>
-      <c r="BE16">
-        <v>7</v>
-      </c>
-      <c r="BF16">
-        <v>6.8</v>
-      </c>
-      <c r="BG16">
-        <v>15.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4721,7 +4739,7 @@
         <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4729,178 +4747,178 @@
         <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F17">
-        <v>3.05</v>
+        <v>1.77</v>
       </c>
       <c r="G17">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="H17">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="I17">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L17">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M17">
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O17">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P17">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="Q17">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="R17">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="S17">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="T17">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U17">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="W17">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="X17">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Y17">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Z17">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AA17">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB17">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AC17">
+        <v>10.5</v>
+      </c>
+      <c r="AD17">
+        <v>19.5</v>
+      </c>
+      <c r="AE17">
+        <v>60</v>
+      </c>
+      <c r="AF17">
+        <v>16.5</v>
+      </c>
+      <c r="AG17">
+        <v>11.5</v>
+      </c>
+      <c r="AH17">
+        <v>21</v>
+      </c>
+      <c r="AI17">
+        <v>60</v>
+      </c>
+      <c r="AJ17">
+        <v>21</v>
+      </c>
+      <c r="AK17">
+        <v>21</v>
+      </c>
+      <c r="AL17">
+        <v>34</v>
+      </c>
+      <c r="AM17">
+        <v>80</v>
+      </c>
+      <c r="AN17">
+        <v>7.8</v>
+      </c>
+      <c r="AO17">
         <v>42</v>
       </c>
-      <c r="AD17">
-        <v>970</v>
-      </c>
-      <c r="AE17">
-        <v>500</v>
-      </c>
-      <c r="AF17">
-        <v>500</v>
-      </c>
-      <c r="AG17">
-        <v>950</v>
-      </c>
-      <c r="AH17">
-        <v>950</v>
-      </c>
-      <c r="AI17">
-        <v>500</v>
-      </c>
-      <c r="AJ17">
-        <v>900</v>
-      </c>
-      <c r="AK17">
-        <v>500</v>
-      </c>
-      <c r="AL17">
-        <v>500</v>
-      </c>
-      <c r="AM17">
-        <v>580</v>
-      </c>
-      <c r="AN17">
-        <v>500</v>
-      </c>
-      <c r="AO17">
-        <v>500</v>
-      </c>
       <c r="AP17">
-        <v>1.6</v>
+        <v>21</v>
       </c>
       <c r="AQ17">
-        <v>1.49</v>
+        <v>19</v>
       </c>
       <c r="AR17">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AS17">
-        <v>1.59</v>
+        <v>6.8</v>
       </c>
       <c r="AT17">
-        <v>1.57</v>
+        <v>11</v>
       </c>
       <c r="AU17">
-        <v>1.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV17">
-        <v>1.46</v>
+        <v>16</v>
       </c>
       <c r="AW17">
-        <v>1.57</v>
+        <v>6.4</v>
       </c>
       <c r="AX17">
-        <v>1.58</v>
+        <v>12</v>
       </c>
       <c r="AY17">
-        <v>1.57</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>1.6</v>
+        <v>36</v>
       </c>
       <c r="BB17">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="BC17">
-        <v>1.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD17">
-        <v>1.6</v>
+        <v>22</v>
       </c>
       <c r="BE17">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="BF17">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG17">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4963,7 +4981,7 @@
         <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4971,178 +4989,178 @@
         <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F18">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="H18">
-        <v>4.5</v>
+        <v>1.98</v>
       </c>
       <c r="I18">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="J18">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K18">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="M18">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N18">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="P18">
-        <v>2.56</v>
+        <v>1.96</v>
       </c>
       <c r="Q18">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="R18">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="S18">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="T18">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="W18">
-        <v>2.22</v>
+        <v>1.3</v>
       </c>
       <c r="X18">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Y18">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="Z18">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AA18">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="AB18">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AC18">
+        <v>9</v>
+      </c>
+      <c r="AD18">
+        <v>11</v>
+      </c>
+      <c r="AE18">
+        <v>23</v>
+      </c>
+      <c r="AF18">
+        <v>34</v>
+      </c>
+      <c r="AG18">
+        <v>17.5</v>
+      </c>
+      <c r="AH18">
+        <v>19.5</v>
+      </c>
+      <c r="AI18">
+        <v>50</v>
+      </c>
+      <c r="AJ18">
+        <v>310</v>
+      </c>
+      <c r="AK18">
+        <v>70</v>
+      </c>
+      <c r="AL18">
+        <v>65</v>
+      </c>
+      <c r="AM18">
+        <v>580</v>
+      </c>
+      <c r="AN18">
+        <v>65</v>
+      </c>
+      <c r="AO18">
+        <v>16.5</v>
+      </c>
+      <c r="AP18">
+        <v>12</v>
+      </c>
+      <c r="AQ18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR18">
         <v>10.5</v>
       </c>
-      <c r="AD18">
-        <v>20</v>
-      </c>
-      <c r="AE18">
-        <v>60</v>
-      </c>
-      <c r="AF18">
-        <v>16.5</v>
-      </c>
-      <c r="AG18">
-        <v>11.5</v>
-      </c>
-      <c r="AH18">
-        <v>21</v>
-      </c>
-      <c r="AI18">
-        <v>60</v>
-      </c>
-      <c r="AJ18">
-        <v>24</v>
-      </c>
-      <c r="AK18">
-        <v>21</v>
-      </c>
-      <c r="AL18">
-        <v>34</v>
-      </c>
-      <c r="AM18">
-        <v>80</v>
-      </c>
-      <c r="AN18">
-        <v>7.8</v>
-      </c>
-      <c r="AO18">
-        <v>42</v>
-      </c>
-      <c r="AP18">
-        <v>18</v>
-      </c>
-      <c r="AQ18">
-        <v>19</v>
-      </c>
-      <c r="AR18">
-        <v>18</v>
-      </c>
       <c r="AS18">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="AT18">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU18">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AV18">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="AW18">
-        <v>5.7</v>
+        <v>17.5</v>
       </c>
       <c r="AX18">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AY18">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AZ18">
         <v>14.5</v>
       </c>
       <c r="BA18">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="BB18">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC18">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="BD18">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="BE18">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF18">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BG18">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5205,7 +5223,7 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5213,88 +5231,88 @@
         <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F19">
         <v>3</v>
       </c>
       <c r="G19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I19">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J19">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
         <v>4</v>
       </c>
       <c r="L19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O19">
         <v>1.2</v>
       </c>
       <c r="P19">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q19">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R19">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S19">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T19">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V19">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y19">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA19">
         <v>34</v>
       </c>
       <c r="AB19">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19">
         <v>13</v>
@@ -5315,43 +5333,43 @@
         <v>32</v>
       </c>
       <c r="AJ19">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AK19">
         <v>30</v>
       </c>
       <c r="AL19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM19">
         <v>200</v>
       </c>
       <c r="AN19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR19">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT19">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW19">
         <v>19</v>
@@ -5369,22 +5387,22 @@
         <v>25</v>
       </c>
       <c r="BB19">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD19">
         <v>16</v>
       </c>
       <c r="BE19">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF19">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BG19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5447,7 +5465,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5455,19 +5473,19 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F20">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="G20">
         <v>8.6</v>
@@ -5488,28 +5506,28 @@
         <v>1.25</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O20">
         <v>1.16</v>
       </c>
       <c r="P20">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R20">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S20">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T20">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U20">
         <v>2.26</v>
@@ -5521,10 +5539,10 @@
         <v>1.13</v>
       </c>
       <c r="X20">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="Y20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z20">
         <v>11</v>
@@ -5551,7 +5569,7 @@
         <v>950</v>
       </c>
       <c r="AH20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI20">
         <v>29</v>
@@ -5575,10 +5593,10 @@
         <v>4.6</v>
       </c>
       <c r="AP20">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR20">
         <v>9.6</v>
@@ -5587,7 +5605,7 @@
         <v>11</v>
       </c>
       <c r="AT20">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AU20">
         <v>12</v>
@@ -5599,25 +5617,25 @@
         <v>12</v>
       </c>
       <c r="AX20">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AY20">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AZ20">
         <v>19</v>
       </c>
       <c r="BA20">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB20">
         <v>12.5</v>
       </c>
       <c r="BC20">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BD20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE20">
         <v>22</v>
@@ -5626,70 +5644,70 @@
         <v>15</v>
       </c>
       <c r="BG20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU20">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB20" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5697,31 +5715,31 @@
         <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F21">
         <v>1.84</v>
       </c>
       <c r="G21">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I21">
         <v>6</v>
       </c>
       <c r="J21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K21">
         <v>3.6</v>
@@ -5760,13 +5778,13 @@
         <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X21">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z21">
         <v>85</v>
@@ -5799,7 +5817,7 @@
         <v>700</v>
       </c>
       <c r="AJ21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK21">
         <v>26</v>
@@ -5811,7 +5829,7 @@
         <v>500</v>
       </c>
       <c r="AN21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO21">
         <v>700</v>
@@ -5850,16 +5868,16 @@
         <v>22</v>
       </c>
       <c r="BA21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB21">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC21">
         <v>21</v>
       </c>
       <c r="BD21">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE21">
         <v>10.5</v>
@@ -5931,7 +5949,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5939,184 +5957,184 @@
         <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F22">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="G22">
-        <v>2.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H22">
-        <v>3.25</v>
+        <v>1.68</v>
       </c>
       <c r="I22">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="J22">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>2.92</v>
+      </c>
+      <c r="O22">
         <v>1.39</v>
       </c>
-      <c r="M22">
-        <v>1.06</v>
-      </c>
-      <c r="N22">
-        <v>4</v>
-      </c>
-      <c r="O22">
-        <v>1.31</v>
-      </c>
       <c r="P22">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="Q22">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S22">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="T22">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI22">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
@@ -6173,1701 +6191,2185 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F23">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="G23">
-        <v>4.6</v>
+        <v>2.86</v>
       </c>
       <c r="H23">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="I23">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="J23">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="K23">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L23">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="M23">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N23">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="O23">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="P23">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="Q23">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="R23">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="T23">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="U23">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="V23">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z23">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
         <v>900</v>
       </c>
       <c r="AB23">
+        <v>12.5</v>
+      </c>
+      <c r="AC23">
+        <v>42</v>
+      </c>
+      <c r="AD23">
         <v>26</v>
       </c>
-      <c r="AC23">
-        <v>8.6</v>
-      </c>
-      <c r="AD23">
-        <v>13</v>
-      </c>
       <c r="AE23">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AF23">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AJ23">
         <v>900</v>
       </c>
       <c r="AK23">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AL23">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM23">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AQ23">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AS23">
-        <v>16</v>
+        <v>1.57</v>
       </c>
       <c r="AT23">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="AU23">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="AV23">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="AW23">
-        <v>16</v>
+        <v>1.57</v>
       </c>
       <c r="AX23">
-        <v>16.5</v>
+        <v>1.58</v>
       </c>
       <c r="AY23">
-        <v>16</v>
+        <v>1.58</v>
       </c>
       <c r="AZ23">
-        <v>16.5</v>
+        <v>1.58</v>
       </c>
       <c r="BA23">
-        <v>22</v>
+        <v>1.57</v>
       </c>
       <c r="BB23">
-        <v>2.36</v>
+        <v>1.56</v>
       </c>
       <c r="BC23">
-        <v>2.36</v>
+        <v>1.56</v>
       </c>
       <c r="BD23">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="BE23">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="BF23">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="BG23">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F24">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="G24">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="H24">
+        <v>3.15</v>
+      </c>
+      <c r="I24">
         <v>3.3</v>
       </c>
-      <c r="I24">
-        <v>3.5</v>
-      </c>
       <c r="J24">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="K24">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="M24">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="N24">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="O24">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="P24">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="Q24">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="R24">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S24">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="T24">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="U24">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z24">
+        <v>25</v>
+      </c>
+      <c r="AA24">
+        <v>65</v>
+      </c>
+      <c r="AB24">
+        <v>11</v>
+      </c>
+      <c r="AC24">
+        <v>8.6</v>
+      </c>
+      <c r="AD24">
+        <v>14.5</v>
+      </c>
+      <c r="AE24">
+        <v>42</v>
+      </c>
+      <c r="AF24">
+        <v>18</v>
+      </c>
+      <c r="AG24">
+        <v>11.5</v>
+      </c>
+      <c r="AH24">
         <v>21</v>
       </c>
-      <c r="AA24">
-        <v>150</v>
-      </c>
-      <c r="AB24">
-        <v>7.6</v>
-      </c>
-      <c r="AC24">
-        <v>7</v>
-      </c>
-      <c r="AD24">
-        <v>15.5</v>
-      </c>
-      <c r="AE24">
-        <v>60</v>
-      </c>
-      <c r="AF24">
-        <v>15</v>
-      </c>
-      <c r="AG24">
+      <c r="AI24">
+        <v>55</v>
+      </c>
+      <c r="AJ24">
+        <v>34</v>
+      </c>
+      <c r="AK24">
+        <v>28</v>
+      </c>
+      <c r="AL24">
+        <v>38</v>
+      </c>
+      <c r="AM24">
+        <v>200</v>
+      </c>
+      <c r="AN24">
+        <v>19</v>
+      </c>
+      <c r="AO24">
+        <v>40</v>
+      </c>
+      <c r="AP24">
         <v>13</v>
       </c>
-      <c r="AH24">
-        <v>25</v>
-      </c>
-      <c r="AI24">
-        <v>450</v>
-      </c>
-      <c r="AJ24">
-        <v>46</v>
-      </c>
-      <c r="AK24">
-        <v>40</v>
-      </c>
-      <c r="AL24">
-        <v>120</v>
-      </c>
-      <c r="AM24">
-        <v>1000</v>
-      </c>
-      <c r="AN24">
-        <v>55</v>
-      </c>
-      <c r="AO24">
-        <v>200</v>
-      </c>
-      <c r="AP24">
-        <v>7.2</v>
-      </c>
       <c r="AQ24">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AR24">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS24">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AT24">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU24">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV24">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW24">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="AX24">
         <v>13</v>
       </c>
       <c r="AY24">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA24">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="BB24">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BC24">
+        <v>21</v>
+      </c>
+      <c r="BD24">
         <v>30</v>
       </c>
-      <c r="BD24">
-        <v>46</v>
-      </c>
       <c r="BE24">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="BF24">
+        <v>15</v>
+      </c>
+      <c r="BG24">
+        <v>6.8</v>
+      </c>
+      <c r="BH24">
+        <v>3.9</v>
+      </c>
+      <c r="BI24">
+        <v>2.88</v>
+      </c>
+      <c r="BJ24">
+        <v>11</v>
+      </c>
+      <c r="BK24">
+        <v>7.2</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>5.9</v>
+      </c>
+      <c r="BO24">
+        <v>4.2</v>
+      </c>
+      <c r="BP24">
+        <v>19.5</v>
+      </c>
+      <c r="BQ24">
+        <v>13</v>
+      </c>
+      <c r="BR24">
         <v>34</v>
       </c>
-      <c r="BG24">
-        <v>34</v>
-      </c>
-      <c r="BH24">
-        <v>2.58</v>
-      </c>
-      <c r="BI24">
-        <v>2.46</v>
-      </c>
-      <c r="BJ24">
-        <v>11.5</v>
-      </c>
-      <c r="BK24">
-        <v>7.8</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>15</v>
-      </c>
-      <c r="BN24">
-        <v>5.1</v>
-      </c>
-      <c r="BO24">
-        <v>4.7</v>
-      </c>
-      <c r="BP24">
-        <v>23</v>
-      </c>
-      <c r="BQ24">
-        <v>11.5</v>
-      </c>
-      <c r="BR24">
-        <v>48</v>
-      </c>
       <c r="BS24">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BT24">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU24">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV24">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BW24">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BX24">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BY24">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BZ24">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="CA24">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="CB24" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
         <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F25">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="G25">
-        <v>2.82</v>
+        <v>4.6</v>
       </c>
       <c r="H25">
-        <v>2.76</v>
+        <v>1.99</v>
       </c>
       <c r="I25">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K25">
         <v>3.6</v>
       </c>
       <c r="L25">
+        <v>1.48</v>
+      </c>
+      <c r="M25">
+        <v>1.09</v>
+      </c>
+      <c r="N25">
+        <v>3.2</v>
+      </c>
+      <c r="O25">
         <v>1.42</v>
       </c>
-      <c r="M25">
-        <v>1.07</v>
-      </c>
-      <c r="N25">
-        <v>3.9</v>
-      </c>
-      <c r="O25">
-        <v>1.32</v>
-      </c>
       <c r="P25">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="Q25">
+        <v>2.24</v>
+      </c>
+      <c r="R25">
+        <v>1.28</v>
+      </c>
+      <c r="S25">
+        <v>4.2</v>
+      </c>
+      <c r="T25">
         <v>1.98</v>
       </c>
-      <c r="R25">
-        <v>1.38</v>
-      </c>
-      <c r="S25">
+      <c r="U25">
+        <v>1.9</v>
+      </c>
+      <c r="V25">
+        <v>1.94</v>
+      </c>
+      <c r="W25">
+        <v>1.27</v>
+      </c>
+      <c r="X25">
+        <v>11.5</v>
+      </c>
+      <c r="Y25">
+        <v>8</v>
+      </c>
+      <c r="Z25">
+        <v>12</v>
+      </c>
+      <c r="AA25">
+        <v>26</v>
+      </c>
+      <c r="AB25">
+        <v>14</v>
+      </c>
+      <c r="AC25">
+        <v>8</v>
+      </c>
+      <c r="AD25">
+        <v>11</v>
+      </c>
+      <c r="AE25">
+        <v>26</v>
+      </c>
+      <c r="AF25">
+        <v>36</v>
+      </c>
+      <c r="AG25">
+        <v>19.5</v>
+      </c>
+      <c r="AH25">
+        <v>23</v>
+      </c>
+      <c r="AI25">
+        <v>48</v>
+      </c>
+      <c r="AJ25">
+        <v>900</v>
+      </c>
+      <c r="AK25">
+        <v>160</v>
+      </c>
+      <c r="AL25">
+        <v>190</v>
+      </c>
+      <c r="AM25">
+        <v>580</v>
+      </c>
+      <c r="AN25">
+        <v>120</v>
+      </c>
+      <c r="AO25">
+        <v>23</v>
+      </c>
+      <c r="AP25">
+        <v>10</v>
+      </c>
+      <c r="AQ25">
+        <v>6.8</v>
+      </c>
+      <c r="AR25">
+        <v>10</v>
+      </c>
+      <c r="AS25">
+        <v>20</v>
+      </c>
+      <c r="AT25">
+        <v>11.5</v>
+      </c>
+      <c r="AU25">
+        <v>7</v>
+      </c>
+      <c r="AV25">
+        <v>9.4</v>
+      </c>
+      <c r="AW25">
+        <v>20</v>
+      </c>
+      <c r="AX25">
+        <v>16.5</v>
+      </c>
+      <c r="AY25">
+        <v>15.5</v>
+      </c>
+      <c r="AZ25">
+        <v>18</v>
+      </c>
+      <c r="BA25">
+        <v>22</v>
+      </c>
+      <c r="BB25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC25">
+        <v>8.4</v>
+      </c>
+      <c r="BD25">
+        <v>8.4</v>
+      </c>
+      <c r="BE25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG25">
+        <v>16</v>
+      </c>
+      <c r="BH25">
+        <v>3.15</v>
+      </c>
+      <c r="BI25">
+        <v>2.46</v>
+      </c>
+      <c r="BJ25">
+        <v>11</v>
+      </c>
+      <c r="BK25">
+        <v>5.5</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>10.5</v>
+      </c>
+      <c r="BN25">
+        <v>8</v>
+      </c>
+      <c r="BO25">
+        <v>5.8</v>
+      </c>
+      <c r="BP25">
+        <v>44</v>
+      </c>
+      <c r="BQ25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR25">
+        <v>60</v>
+      </c>
+      <c r="BS25">
+        <v>9.4</v>
+      </c>
+      <c r="BT25">
+        <v>4.7</v>
+      </c>
+      <c r="BU25">
         <v>3.55</v>
       </c>
-      <c r="T25">
-        <v>1.76</v>
-      </c>
-      <c r="U25">
-        <v>2.22</v>
-      </c>
-      <c r="V25">
-        <v>1.56</v>
-      </c>
-      <c r="W25">
-        <v>1.54</v>
-      </c>
-      <c r="X25">
-        <v>14.5</v>
-      </c>
-      <c r="Y25">
-        <v>12</v>
-      </c>
-      <c r="Z25">
-        <v>19</v>
-      </c>
-      <c r="AA25">
-        <v>46</v>
-      </c>
-      <c r="AB25">
-        <v>12</v>
-      </c>
-      <c r="AC25">
-        <v>7.8</v>
-      </c>
-      <c r="AD25">
-        <v>13</v>
-      </c>
-      <c r="AE25">
+      <c r="BV25">
+        <v>16</v>
+      </c>
+      <c r="BW25">
+        <v>6.6</v>
+      </c>
+      <c r="BX25">
+        <v>36</v>
+      </c>
+      <c r="BY25">
+        <v>8.4</v>
+      </c>
+      <c r="BZ25">
         <v>34</v>
       </c>
-      <c r="AF25">
-        <v>19.5</v>
-      </c>
-      <c r="AG25">
-        <v>13</v>
-      </c>
-      <c r="AH25">
-        <v>17</v>
-      </c>
-      <c r="AI25">
-        <v>50</v>
-      </c>
-      <c r="AJ25">
-        <v>55</v>
-      </c>
-      <c r="AK25">
-        <v>34</v>
-      </c>
-      <c r="AL25">
-        <v>46</v>
-      </c>
-      <c r="AM25">
-        <v>320</v>
-      </c>
-      <c r="AN25">
-        <v>28</v>
-      </c>
-      <c r="AO25">
-        <v>29</v>
-      </c>
-      <c r="AP25">
-        <v>13</v>
-      </c>
-      <c r="AQ25">
-        <v>10</v>
-      </c>
-      <c r="AR25">
-        <v>16</v>
-      </c>
-      <c r="AS25">
-        <v>17.5</v>
-      </c>
-      <c r="AT25">
-        <v>10</v>
-      </c>
-      <c r="AU25">
-        <v>7.2</v>
-      </c>
-      <c r="AV25">
-        <v>11</v>
-      </c>
-      <c r="AW25">
-        <v>16</v>
-      </c>
-      <c r="AX25">
-        <v>15</v>
-      </c>
-      <c r="AY25">
-        <v>11</v>
-      </c>
-      <c r="AZ25">
-        <v>15</v>
-      </c>
-      <c r="BA25">
-        <v>32</v>
-      </c>
-      <c r="BB25">
-        <v>32</v>
-      </c>
-      <c r="BC25">
-        <v>26</v>
-      </c>
-      <c r="BD25">
-        <v>32</v>
-      </c>
-      <c r="BE25">
-        <v>36</v>
-      </c>
-      <c r="BF25">
-        <v>19.5</v>
-      </c>
-      <c r="BG25">
-        <v>21</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.4</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.16</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.16</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>1.68</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.16</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>1.16</v>
-      </c>
-      <c r="BT25">
-        <v>1000</v>
-      </c>
-      <c r="BU25">
-        <v>1.71</v>
-      </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
-        <v>1.16</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>1.16</v>
-      </c>
-      <c r="BZ25">
-        <v>1000</v>
-      </c>
       <c r="CA25">
-        <v>1.16</v>
+        <v>8.4</v>
       </c>
       <c r="CB25" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
         <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F26">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="G26">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="H26">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="I26">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J26">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="L26">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="M26">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="O26">
+        <v>1.61</v>
+      </c>
+      <c r="P26">
+        <v>1.51</v>
+      </c>
+      <c r="Q26">
+        <v>2.88</v>
+      </c>
+      <c r="R26">
+        <v>1.18</v>
+      </c>
+      <c r="S26">
+        <v>6.2</v>
+      </c>
+      <c r="T26">
+        <v>2.24</v>
+      </c>
+      <c r="U26">
+        <v>1.76</v>
+      </c>
+      <c r="V26">
         <v>1.4</v>
       </c>
-      <c r="P26">
-        <v>1.79</v>
-      </c>
-      <c r="Q26">
-        <v>2.22</v>
-      </c>
-      <c r="R26">
-        <v>1.3</v>
-      </c>
-      <c r="S26">
-        <v>4.2</v>
-      </c>
-      <c r="T26">
-        <v>1.94</v>
-      </c>
-      <c r="U26">
-        <v>2</v>
-      </c>
-      <c r="V26">
-        <v>1.34</v>
-      </c>
       <c r="W26">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="X26">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB26">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC26">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE26">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF26">
+        <v>15</v>
+      </c>
+      <c r="AG26">
         <v>13</v>
       </c>
-      <c r="AG26">
-        <v>11</v>
-      </c>
       <c r="AH26">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI26">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AJ26">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AK26">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AL26">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AM26">
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AO26">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AP26">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ26">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR26">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AS26">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT26">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AU26">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV26">
         <v>14</v>
       </c>
       <c r="AW26">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX26">
+        <v>13</v>
+      </c>
+      <c r="AY26">
+        <v>12</v>
+      </c>
+      <c r="AZ26">
+        <v>18.5</v>
+      </c>
+      <c r="BA26">
+        <v>48</v>
+      </c>
+      <c r="BB26">
+        <v>36</v>
+      </c>
+      <c r="BC26">
+        <v>30</v>
+      </c>
+      <c r="BD26">
+        <v>46</v>
+      </c>
+      <c r="BE26">
+        <v>95</v>
+      </c>
+      <c r="BF26">
+        <v>34</v>
+      </c>
+      <c r="BG26">
+        <v>34</v>
+      </c>
+      <c r="BH26">
+        <v>2.58</v>
+      </c>
+      <c r="BI26">
+        <v>2.46</v>
+      </c>
+      <c r="BJ26">
         <v>11.5</v>
       </c>
-      <c r="AY26">
-        <v>10</v>
-      </c>
-      <c r="AZ26">
-        <v>17.5</v>
-      </c>
-      <c r="BA26">
-        <v>40</v>
-      </c>
-      <c r="BB26">
+      <c r="BK26">
+        <v>7.8</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>15</v>
+      </c>
+      <c r="BN26">
+        <v>5.1</v>
+      </c>
+      <c r="BO26">
+        <v>4.7</v>
+      </c>
+      <c r="BP26">
         <v>23</v>
       </c>
-      <c r="BC26">
-        <v>21</v>
-      </c>
-      <c r="BD26">
-        <v>32</v>
-      </c>
-      <c r="BE26">
-        <v>65</v>
-      </c>
-      <c r="BF26">
-        <v>18</v>
-      </c>
-      <c r="BG26">
-        <v>28</v>
-      </c>
-      <c r="BH26">
-        <v>3.5</v>
-      </c>
-      <c r="BI26">
-        <v>2.7</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>2.34</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>2.7</v>
-      </c>
-      <c r="BN26">
-        <v>1000</v>
-      </c>
-      <c r="BO26">
-        <v>1.84</v>
-      </c>
-      <c r="BP26">
-        <v>1000</v>
-      </c>
       <c r="BQ26">
-        <v>2.7</v>
+        <v>11.5</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS26">
-        <v>2.7</v>
+        <v>16</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU26">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW26">
-        <v>2.7</v>
+        <v>14</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY26">
-        <v>2.7</v>
+        <v>17</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA26">
-        <v>2.7</v>
+        <v>16.5</v>
       </c>
       <c r="CB26" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F27">
-        <v>2.12</v>
+        <v>2.84</v>
       </c>
       <c r="G27">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="H27">
+        <v>2.76</v>
+      </c>
+      <c r="I27">
+        <v>2.82</v>
+      </c>
+      <c r="J27">
+        <v>3.35</v>
+      </c>
+      <c r="K27">
         <v>3.5</v>
       </c>
-      <c r="I27">
-        <v>3.75</v>
-      </c>
-      <c r="J27">
-        <v>3.65</v>
-      </c>
-      <c r="K27">
-        <v>3.9</v>
-      </c>
       <c r="L27">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="P27">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="Q27">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="R27">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S27">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="T27">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="U27">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="W27">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="X27">
+        <v>12</v>
+      </c>
+      <c r="Y27">
+        <v>10.5</v>
+      </c>
+      <c r="Z27">
         <v>18</v>
       </c>
-      <c r="Y27">
-        <v>15.5</v>
-      </c>
-      <c r="Z27">
-        <v>28</v>
-      </c>
       <c r="AA27">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AB27">
         <v>11</v>
       </c>
       <c r="AC27">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD27">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE27">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AF27">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AG27">
         <v>13</v>
       </c>
       <c r="AH27">
+        <v>19.5</v>
+      </c>
+      <c r="AI27">
+        <v>50</v>
+      </c>
+      <c r="AJ27">
+        <v>55</v>
+      </c>
+      <c r="AK27">
+        <v>42</v>
+      </c>
+      <c r="AL27">
+        <v>60</v>
+      </c>
+      <c r="AM27">
+        <v>500</v>
+      </c>
+      <c r="AN27">
+        <v>36</v>
+      </c>
+      <c r="AO27">
+        <v>32</v>
+      </c>
+      <c r="AP27">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27">
+        <v>15.5</v>
+      </c>
+      <c r="AS27">
         <v>17.5</v>
       </c>
-      <c r="AI27">
-        <v>55</v>
-      </c>
-      <c r="AJ27">
+      <c r="AT27">
+        <v>9.4</v>
+      </c>
+      <c r="AU27">
+        <v>6.8</v>
+      </c>
+      <c r="AV27">
+        <v>11</v>
+      </c>
+      <c r="AW27">
+        <v>25</v>
+      </c>
+      <c r="AX27">
+        <v>16</v>
+      </c>
+      <c r="AY27">
+        <v>11</v>
+      </c>
+      <c r="AZ27">
+        <v>16</v>
+      </c>
+      <c r="BA27">
+        <v>17</v>
+      </c>
+      <c r="BB27">
         <v>32</v>
       </c>
-      <c r="AK27">
-        <v>24</v>
-      </c>
-      <c r="AL27">
-        <v>40</v>
-      </c>
-      <c r="AM27">
-        <v>95</v>
-      </c>
-      <c r="AN27">
-        <v>15.5</v>
-      </c>
-      <c r="AO27">
-        <v>44</v>
-      </c>
-      <c r="AP27">
-        <v>14.5</v>
-      </c>
-      <c r="AQ27">
-        <v>13</v>
-      </c>
-      <c r="AR27">
-        <v>6.2</v>
-      </c>
-      <c r="AS27">
-        <v>7.4</v>
-      </c>
-      <c r="AT27">
-        <v>9.6</v>
-      </c>
-      <c r="AU27">
-        <v>7.6</v>
-      </c>
-      <c r="AV27">
-        <v>13</v>
-      </c>
-      <c r="AW27">
-        <v>7</v>
-      </c>
-      <c r="AX27">
-        <v>12.5</v>
-      </c>
-      <c r="AY27">
-        <v>9.6</v>
-      </c>
-      <c r="AZ27">
-        <v>14.5</v>
-      </c>
-      <c r="BA27">
-        <v>7</v>
-      </c>
-      <c r="BB27">
-        <v>6.4</v>
-      </c>
       <c r="BC27">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BD27">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BE27">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BF27">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG27">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>2.02</v>
+        <v>1.16</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="CB27" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F28">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="G28">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="H28">
-        <v>2.56</v>
+        <v>3.8</v>
       </c>
       <c r="I28">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K28">
+        <v>3.6</v>
+      </c>
+      <c r="L28">
+        <v>1.47</v>
+      </c>
+      <c r="M28">
+        <v>1.09</v>
+      </c>
+      <c r="N28">
         <v>3.35</v>
       </c>
-      <c r="L28">
-        <v>1.52</v>
-      </c>
-      <c r="M28">
-        <v>1.1</v>
-      </c>
-      <c r="N28">
-        <v>3</v>
-      </c>
       <c r="O28">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="P28">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q28">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="R28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S28">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="T28">
+        <v>1.92</v>
+      </c>
+      <c r="U28">
         <v>2</v>
       </c>
-      <c r="U28">
-        <v>1.92</v>
-      </c>
       <c r="V28">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="W28">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="X28">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y28">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="Z28">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AA28">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC28">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD28">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AE28">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AF28">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AG28">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH28">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI28">
         <v>65</v>
       </c>
       <c r="AJ28">
+        <v>28</v>
+      </c>
+      <c r="AK28">
+        <v>26</v>
+      </c>
+      <c r="AL28">
+        <v>46</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>21</v>
+      </c>
+      <c r="AO28">
+        <v>65</v>
+      </c>
+      <c r="AP28">
+        <v>10.5</v>
+      </c>
+      <c r="AQ28">
+        <v>11</v>
+      </c>
+      <c r="AR28">
+        <v>22</v>
+      </c>
+      <c r="AS28">
+        <v>65</v>
+      </c>
+      <c r="AT28">
+        <v>7.8</v>
+      </c>
+      <c r="AU28">
+        <v>7</v>
+      </c>
+      <c r="AV28">
+        <v>14.5</v>
+      </c>
+      <c r="AW28">
+        <v>44</v>
+      </c>
+      <c r="AX28">
+        <v>11.5</v>
+      </c>
+      <c r="AY28">
+        <v>10</v>
+      </c>
+      <c r="AZ28">
+        <v>17.5</v>
+      </c>
+      <c r="BA28">
+        <v>50</v>
+      </c>
+      <c r="BB28">
+        <v>23</v>
+      </c>
+      <c r="BC28">
+        <v>21</v>
+      </c>
+      <c r="BD28">
+        <v>36</v>
+      </c>
+      <c r="BE28">
         <v>70</v>
       </c>
-      <c r="AK28">
-        <v>50</v>
-      </c>
-      <c r="AL28">
-        <v>75</v>
-      </c>
-      <c r="AM28">
-        <v>160</v>
-      </c>
-      <c r="AN28">
+      <c r="BF28">
+        <v>18</v>
+      </c>
+      <c r="BG28">
+        <v>29</v>
+      </c>
+      <c r="BH28">
+        <v>3.1</v>
+      </c>
+      <c r="BI28">
+        <v>2.86</v>
+      </c>
+      <c r="BJ28">
+        <v>10.5</v>
+      </c>
+      <c r="BK28">
+        <v>9</v>
+      </c>
+      <c r="BL28">
+        <v>170</v>
+      </c>
+      <c r="BM28">
+        <v>14</v>
+      </c>
+      <c r="BN28">
+        <v>4.8</v>
+      </c>
+      <c r="BO28">
+        <v>4.3</v>
+      </c>
+      <c r="BP28">
+        <v>16.5</v>
+      </c>
+      <c r="BQ28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR28">
+        <v>34</v>
+      </c>
+      <c r="BS28">
+        <v>10.5</v>
+      </c>
+      <c r="BT28">
+        <v>7.2</v>
+      </c>
+      <c r="BU28">
+        <v>6.2</v>
+      </c>
+      <c r="BV28">
+        <v>36</v>
+      </c>
+      <c r="BW28">
+        <v>10.5</v>
+      </c>
+      <c r="BX28">
         <v>60</v>
       </c>
-      <c r="AO28">
-        <v>38</v>
-      </c>
-      <c r="AP28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ28">
-        <v>7.6</v>
-      </c>
-      <c r="AR28">
-        <v>13.5</v>
-      </c>
-      <c r="AS28">
-        <v>9</v>
-      </c>
-      <c r="AT28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU28">
-        <v>6.6</v>
-      </c>
-      <c r="AV28">
+      <c r="BY28">
+        <v>12</v>
+      </c>
+      <c r="BZ28">
+        <v>36</v>
+      </c>
+      <c r="CA28">
         <v>10.5</v>
       </c>
-      <c r="AW28">
-        <v>15.5</v>
-      </c>
-      <c r="AX28">
-        <v>18</v>
-      </c>
-      <c r="AY28">
-        <v>12.5</v>
-      </c>
-      <c r="AZ28">
-        <v>18</v>
-      </c>
-      <c r="BA28">
-        <v>9.6</v>
-      </c>
-      <c r="BB28">
-        <v>9.6</v>
-      </c>
-      <c r="BC28">
-        <v>36</v>
-      </c>
-      <c r="BD28">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE28">
-        <v>10</v>
-      </c>
-      <c r="BF28">
-        <v>9.4</v>
-      </c>
-      <c r="BG28">
-        <v>8.6</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>1.15</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>1.04</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>1.04</v>
-      </c>
-      <c r="BN28">
-        <v>1000</v>
-      </c>
-      <c r="BO28">
-        <v>1.15</v>
-      </c>
-      <c r="BP28">
-        <v>1000</v>
-      </c>
-      <c r="BQ28">
-        <v>1.04</v>
-      </c>
-      <c r="BR28">
-        <v>1000</v>
-      </c>
-      <c r="BS28">
-        <v>1.04</v>
-      </c>
-      <c r="BT28">
-        <v>1000</v>
-      </c>
-      <c r="BU28">
-        <v>1.48</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>1.04</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
-      <c r="BY28">
-        <v>1.04</v>
-      </c>
-      <c r="BZ28">
-        <v>1000</v>
-      </c>
-      <c r="CA28">
-        <v>1.04</v>
-      </c>
       <c r="CB28" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
         <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F29">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="G29">
+        <v>2.22</v>
+      </c>
+      <c r="H29">
+        <v>3.5</v>
+      </c>
+      <c r="I29">
+        <v>3.75</v>
+      </c>
+      <c r="J29">
+        <v>3.7</v>
+      </c>
+      <c r="K29">
+        <v>3.9</v>
+      </c>
+      <c r="L29">
+        <v>1.35</v>
+      </c>
+      <c r="M29">
+        <v>1.06</v>
+      </c>
+      <c r="N29">
+        <v>4.1</v>
+      </c>
+      <c r="O29">
+        <v>1.28</v>
+      </c>
+      <c r="P29">
+        <v>2.08</v>
+      </c>
+      <c r="Q29">
+        <v>1.83</v>
+      </c>
+      <c r="R29">
+        <v>1.42</v>
+      </c>
+      <c r="S29">
+        <v>3.05</v>
+      </c>
+      <c r="T29">
+        <v>1.7</v>
+      </c>
+      <c r="U29">
+        <v>2.24</v>
+      </c>
+      <c r="V29">
+        <v>1.36</v>
+      </c>
+      <c r="W29">
+        <v>1.82</v>
+      </c>
+      <c r="X29">
+        <v>21</v>
+      </c>
+      <c r="Y29">
+        <v>15.5</v>
+      </c>
+      <c r="Z29">
+        <v>28</v>
+      </c>
+      <c r="AA29">
+        <v>80</v>
+      </c>
+      <c r="AB29">
+        <v>11</v>
+      </c>
+      <c r="AC29">
+        <v>8.6</v>
+      </c>
+      <c r="AD29">
+        <v>15.5</v>
+      </c>
+      <c r="AE29">
+        <v>50</v>
+      </c>
+      <c r="AF29">
+        <v>15</v>
+      </c>
+      <c r="AG29">
+        <v>13</v>
+      </c>
+      <c r="AH29">
+        <v>17.5</v>
+      </c>
+      <c r="AI29">
+        <v>55</v>
+      </c>
+      <c r="AJ29">
+        <v>34</v>
+      </c>
+      <c r="AK29">
+        <v>24</v>
+      </c>
+      <c r="AL29">
+        <v>40</v>
+      </c>
+      <c r="AM29">
+        <v>95</v>
+      </c>
+      <c r="AN29">
+        <v>15.5</v>
+      </c>
+      <c r="AO29">
+        <v>44</v>
+      </c>
+      <c r="AP29">
+        <v>14.5</v>
+      </c>
+      <c r="AQ29">
+        <v>13</v>
+      </c>
+      <c r="AR29">
+        <v>6</v>
+      </c>
+      <c r="AS29">
+        <v>7.2</v>
+      </c>
+      <c r="AT29">
+        <v>9.6</v>
+      </c>
+      <c r="AU29">
+        <v>7.6</v>
+      </c>
+      <c r="AV29">
+        <v>13</v>
+      </c>
+      <c r="AW29">
+        <v>6.8</v>
+      </c>
+      <c r="AX29">
+        <v>12.5</v>
+      </c>
+      <c r="AY29">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29">
+        <v>14.5</v>
+      </c>
+      <c r="BA29">
+        <v>6.8</v>
+      </c>
+      <c r="BB29">
+        <v>6.2</v>
+      </c>
+      <c r="BC29">
+        <v>18.5</v>
+      </c>
+      <c r="BD29">
+        <v>6.4</v>
+      </c>
+      <c r="BE29">
+        <v>7.2</v>
+      </c>
+      <c r="BF29">
+        <v>12.5</v>
+      </c>
+      <c r="BG29">
+        <v>6.6</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.35</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
         <v>2.02</v>
       </c>
-      <c r="H29">
-        <v>4.9</v>
-      </c>
-      <c r="I29">
-        <v>5.1</v>
-      </c>
-      <c r="J29">
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.11</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.52</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.11</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.11</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.7</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.11</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.11</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.11</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30">
+        <v>3.15</v>
+      </c>
+      <c r="G30">
         <v>3.3</v>
       </c>
-      <c r="K29">
-        <v>3.4</v>
-      </c>
-      <c r="L29">
+      <c r="H30">
+        <v>2.56</v>
+      </c>
+      <c r="I30">
+        <v>2.62</v>
+      </c>
+      <c r="J30">
+        <v>3.25</v>
+      </c>
+      <c r="K30">
+        <v>3.35</v>
+      </c>
+      <c r="L30">
+        <v>1.52</v>
+      </c>
+      <c r="M30">
+        <v>1.1</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30">
+        <v>1.46</v>
+      </c>
+      <c r="P30">
+        <v>1.66</v>
+      </c>
+      <c r="Q30">
+        <v>2.4</v>
+      </c>
+      <c r="R30">
+        <v>1.25</v>
+      </c>
+      <c r="S30">
+        <v>4.7</v>
+      </c>
+      <c r="T30">
+        <v>2</v>
+      </c>
+      <c r="U30">
+        <v>1.92</v>
+      </c>
+      <c r="V30">
+        <v>1.61</v>
+      </c>
+      <c r="W30">
+        <v>1.43</v>
+      </c>
+      <c r="X30">
+        <v>10.5</v>
+      </c>
+      <c r="Y30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z30">
+        <v>15.5</v>
+      </c>
+      <c r="AA30">
+        <v>46</v>
+      </c>
+      <c r="AB30">
+        <v>10.5</v>
+      </c>
+      <c r="AC30">
+        <v>7.4</v>
+      </c>
+      <c r="AD30">
+        <v>12.5</v>
+      </c>
+      <c r="AE30">
+        <v>38</v>
+      </c>
+      <c r="AF30">
+        <v>20</v>
+      </c>
+      <c r="AG30">
+        <v>15</v>
+      </c>
+      <c r="AH30">
+        <v>21</v>
+      </c>
+      <c r="AI30">
+        <v>65</v>
+      </c>
+      <c r="AJ30">
+        <v>70</v>
+      </c>
+      <c r="AK30">
+        <v>50</v>
+      </c>
+      <c r="AL30">
+        <v>75</v>
+      </c>
+      <c r="AM30">
+        <v>160</v>
+      </c>
+      <c r="AN30">
+        <v>60</v>
+      </c>
+      <c r="AO30">
+        <v>38</v>
+      </c>
+      <c r="AP30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ30">
+        <v>7.6</v>
+      </c>
+      <c r="AR30">
+        <v>13.5</v>
+      </c>
+      <c r="AS30">
+        <v>9</v>
+      </c>
+      <c r="AT30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU30">
+        <v>6.6</v>
+      </c>
+      <c r="AV30">
+        <v>10.5</v>
+      </c>
+      <c r="AW30">
+        <v>8.6</v>
+      </c>
+      <c r="AX30">
+        <v>18</v>
+      </c>
+      <c r="AY30">
+        <v>12.5</v>
+      </c>
+      <c r="AZ30">
+        <v>18</v>
+      </c>
+      <c r="BA30">
+        <v>9.6</v>
+      </c>
+      <c r="BB30">
+        <v>9.6</v>
+      </c>
+      <c r="BC30">
+        <v>36</v>
+      </c>
+      <c r="BD30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE30">
+        <v>10</v>
+      </c>
+      <c r="BF30">
+        <v>9.4</v>
+      </c>
+      <c r="BG30">
+        <v>8.6</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>1.15</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.04</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.04</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>1.15</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.04</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.04</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.48</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.04</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.04</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.04</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31">
+        <v>2.12</v>
+      </c>
+      <c r="G31">
+        <v>2.16</v>
+      </c>
+      <c r="H31">
+        <v>4.5</v>
+      </c>
+      <c r="I31">
+        <v>4.6</v>
+      </c>
+      <c r="J31">
+        <v>3.2</v>
+      </c>
+      <c r="K31">
+        <v>3.25</v>
+      </c>
+      <c r="L31">
         <v>1.59</v>
       </c>
-      <c r="M29">
+      <c r="M31">
         <v>1.13</v>
       </c>
-      <c r="N29">
+      <c r="N31">
+        <v>2.76</v>
+      </c>
+      <c r="O31">
+        <v>1.56</v>
+      </c>
+      <c r="P31">
+        <v>1.57</v>
+      </c>
+      <c r="Q31">
         <v>2.68</v>
       </c>
-      <c r="O29">
-        <v>1.56</v>
-      </c>
-      <c r="P29">
-        <v>1.55</v>
-      </c>
-      <c r="Q29">
+      <c r="R31">
+        <v>1.2</v>
+      </c>
+      <c r="S31">
+        <v>5.6</v>
+      </c>
+      <c r="T31">
+        <v>2.26</v>
+      </c>
+      <c r="U31">
+        <v>1.75</v>
+      </c>
+      <c r="V31">
+        <v>1.27</v>
+      </c>
+      <c r="W31">
+        <v>1.87</v>
+      </c>
+      <c r="X31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y31">
+        <v>11.5</v>
+      </c>
+      <c r="Z31">
+        <v>34</v>
+      </c>
+      <c r="AA31">
+        <v>130</v>
+      </c>
+      <c r="AB31">
+        <v>6.8</v>
+      </c>
+      <c r="AC31">
+        <v>7.6</v>
+      </c>
+      <c r="AD31">
+        <v>20</v>
+      </c>
+      <c r="AE31">
+        <v>85</v>
+      </c>
+      <c r="AF31">
+        <v>11.5</v>
+      </c>
+      <c r="AG31">
+        <v>11.5</v>
+      </c>
+      <c r="AH31">
+        <v>26</v>
+      </c>
+      <c r="AI31">
+        <v>110</v>
+      </c>
+      <c r="AJ31">
+        <v>26</v>
+      </c>
+      <c r="AK31">
+        <v>29</v>
+      </c>
+      <c r="AL31">
+        <v>75</v>
+      </c>
+      <c r="AM31">
+        <v>200</v>
+      </c>
+      <c r="AN31">
+        <v>27</v>
+      </c>
+      <c r="AO31">
+        <v>130</v>
+      </c>
+      <c r="AP31">
+        <v>8</v>
+      </c>
+      <c r="AQ31">
+        <v>10.5</v>
+      </c>
+      <c r="AR31">
+        <v>27</v>
+      </c>
+      <c r="AS31">
+        <v>15</v>
+      </c>
+      <c r="AT31">
+        <v>6.2</v>
+      </c>
+      <c r="AU31">
+        <v>7</v>
+      </c>
+      <c r="AV31">
+        <v>17.5</v>
+      </c>
+      <c r="AW31">
+        <v>15</v>
+      </c>
+      <c r="AX31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY31">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31">
+        <v>23</v>
+      </c>
+      <c r="BA31">
+        <v>15.5</v>
+      </c>
+      <c r="BB31">
+        <v>23</v>
+      </c>
+      <c r="BC31">
+        <v>26</v>
+      </c>
+      <c r="BD31">
+        <v>50</v>
+      </c>
+      <c r="BE31">
+        <v>14.5</v>
+      </c>
+      <c r="BF31">
+        <v>23</v>
+      </c>
+      <c r="BG31">
+        <v>15</v>
+      </c>
+      <c r="BH31">
         <v>2.7</v>
       </c>
-      <c r="R29">
-        <v>1.19</v>
-      </c>
-      <c r="S29">
-        <v>5.6</v>
-      </c>
-      <c r="T29">
-        <v>2.3</v>
-      </c>
-      <c r="U29">
-        <v>1.71</v>
-      </c>
-      <c r="V29">
-        <v>1.24</v>
-      </c>
-      <c r="W29">
-        <v>1.98</v>
-      </c>
-      <c r="X29">
+      <c r="BI31">
+        <v>2.54</v>
+      </c>
+      <c r="BJ31">
+        <v>12</v>
+      </c>
+      <c r="BK31">
+        <v>7.2</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>15.5</v>
+      </c>
+      <c r="BN31">
+        <v>4.6</v>
+      </c>
+      <c r="BO31">
+        <v>4.2</v>
+      </c>
+      <c r="BP31">
+        <v>17.5</v>
+      </c>
+      <c r="BQ31">
         <v>8.6</v>
       </c>
-      <c r="Y29">
-        <v>13</v>
-      </c>
-      <c r="Z29">
-        <v>40</v>
-      </c>
-      <c r="AA29">
-        <v>190</v>
-      </c>
-      <c r="AB29">
-        <v>6.4</v>
-      </c>
-      <c r="AC29">
-        <v>7.6</v>
-      </c>
-      <c r="AD29">
-        <v>23</v>
-      </c>
-      <c r="AE29">
-        <v>120</v>
-      </c>
-      <c r="AF29">
-        <v>10.5</v>
-      </c>
-      <c r="AG29">
-        <v>11.5</v>
-      </c>
-      <c r="AH29">
-        <v>28</v>
-      </c>
-      <c r="AI29">
-        <v>140</v>
-      </c>
-      <c r="AJ29">
-        <v>26</v>
-      </c>
-      <c r="AK29">
-        <v>29</v>
-      </c>
-      <c r="AL29">
-        <v>65</v>
-      </c>
-      <c r="AM29">
-        <v>270</v>
-      </c>
-      <c r="AN29">
-        <v>26</v>
-      </c>
-      <c r="AO29">
-        <v>200</v>
-      </c>
-      <c r="AP29">
+      <c r="BR31">
+        <v>42</v>
+      </c>
+      <c r="BS31">
+        <v>12</v>
+      </c>
+      <c r="BT31">
         <v>7.8</v>
       </c>
-      <c r="AQ29">
-        <v>11</v>
-      </c>
-      <c r="AR29">
-        <v>27</v>
-      </c>
-      <c r="AS29">
+      <c r="BU31">
+        <v>5.3</v>
+      </c>
+      <c r="BV31">
+        <v>48</v>
+      </c>
+      <c r="BW31">
+        <v>12.5</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>13.5</v>
+      </c>
+      <c r="BZ31">
+        <v>46</v>
+      </c>
+      <c r="CA31">
         <v>12</v>
       </c>
-      <c r="AT29">
-        <v>5.8</v>
-      </c>
-      <c r="AU29">
-        <v>7</v>
-      </c>
-      <c r="AV29">
-        <v>19.5</v>
-      </c>
-      <c r="AW29">
-        <v>55</v>
-      </c>
-      <c r="AX29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY29">
-        <v>10</v>
-      </c>
-      <c r="AZ29">
-        <v>19</v>
-      </c>
-      <c r="BA29">
-        <v>12</v>
-      </c>
-      <c r="BB29">
-        <v>20</v>
-      </c>
-      <c r="BC29">
-        <v>20</v>
-      </c>
-      <c r="BD29">
-        <v>11</v>
-      </c>
-      <c r="BE29">
-        <v>12</v>
-      </c>
-      <c r="BF29">
-        <v>17.5</v>
-      </c>
-      <c r="BG29">
-        <v>12</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.26</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
-        <v>1.04</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>1.04</v>
-      </c>
-      <c r="BN29">
-        <v>1000</v>
-      </c>
-      <c r="BO29">
-        <v>1.53</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>1.04</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>1.04</v>
-      </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
-        <v>2.24</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>1.04</v>
-      </c>
-      <c r="BX29">
-        <v>1000</v>
-      </c>
-      <c r="BY29">
-        <v>1.04</v>
-      </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
-        <v>1.04</v>
-      </c>
-      <c r="CB29" t="s">
-        <v>167</v>
+      <c r="CB31" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -535,7 +535,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-02 04:29:15</t>
+    <t>2026-10-02 06:45:32</t>
   </si>
 </sst>
 </file>
@@ -1129,19 +1129,19 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="H2">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="I2">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
         <v>3.65</v>
@@ -1150,37 +1150,37 @@
         <v>1.43</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
         <v>3.9</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
         <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
         <v>3.55</v>
       </c>
       <c r="T2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="W2">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1189,28 +1189,28 @@
         <v>11</v>
       </c>
       <c r="Z2">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB2">
         <v>12.5</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
         <v>17.5</v>
@@ -1219,37 +1219,37 @@
         <v>42</v>
       </c>
       <c r="AJ2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AO2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AP2">
         <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1258,97 +1258,97 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX2">
+        <v>19.5</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>15.5</v>
+      </c>
+      <c r="BA2">
+        <v>34</v>
+      </c>
+      <c r="BB2">
+        <v>42</v>
+      </c>
+      <c r="BC2">
+        <v>32</v>
+      </c>
+      <c r="BD2">
+        <v>40</v>
+      </c>
+      <c r="BE2">
+        <v>80</v>
+      </c>
+      <c r="BF2">
+        <v>29</v>
+      </c>
+      <c r="BG2">
         <v>18</v>
       </c>
-      <c r="AY2">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>29</v>
-      </c>
-      <c r="BB2">
-        <v>32</v>
-      </c>
-      <c r="BC2">
-        <v>24</v>
-      </c>
-      <c r="BD2">
-        <v>32</v>
-      </c>
-      <c r="BE2">
-        <v>65</v>
-      </c>
-      <c r="BF2">
-        <v>22</v>
-      </c>
-      <c r="BG2">
-        <v>19</v>
-      </c>
       <c r="BH2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI2">
         <v>3.05</v>
       </c>
       <c r="BJ2">
+        <v>9.6</v>
+      </c>
+      <c r="BK2">
+        <v>8</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>100</v>
+      </c>
+      <c r="BN2">
+        <v>6.6</v>
+      </c>
+      <c r="BO2">
+        <v>5.5</v>
+      </c>
+      <c r="BP2">
+        <v>26</v>
+      </c>
+      <c r="BQ2">
+        <v>8.4</v>
+      </c>
+      <c r="BR2">
+        <v>38</v>
+      </c>
+      <c r="BS2">
         <v>9.4</v>
       </c>
-      <c r="BK2">
-        <v>5.7</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>12.5</v>
-      </c>
-      <c r="BN2">
-        <v>6.2</v>
-      </c>
-      <c r="BO2">
-        <v>5.4</v>
-      </c>
-      <c r="BP2">
-        <v>23</v>
-      </c>
-      <c r="BQ2">
+      <c r="BT2">
+        <v>5.5</v>
+      </c>
+      <c r="BU2">
+        <v>4.8</v>
+      </c>
+      <c r="BV2">
+        <v>18</v>
+      </c>
+      <c r="BW2">
+        <v>7.2</v>
+      </c>
+      <c r="BX2">
+        <v>32</v>
+      </c>
+      <c r="BY2">
+        <v>9</v>
+      </c>
+      <c r="BZ2">
+        <v>27</v>
+      </c>
+      <c r="CA2">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BR2">
-        <v>36</v>
-      </c>
-      <c r="BS2">
-        <v>10</v>
-      </c>
-      <c r="BT2">
-        <v>5.6</v>
-      </c>
-      <c r="BU2">
-        <v>4.9</v>
-      </c>
-      <c r="BV2">
-        <v>20</v>
-      </c>
-      <c r="BW2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX2">
-        <v>34</v>
-      </c>
-      <c r="BY2">
-        <v>10</v>
-      </c>
-      <c r="BZ2">
-        <v>28</v>
-      </c>
-      <c r="CA2">
-        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>173</v>
@@ -1371,52 +1371,52 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G3">
         <v>1.83</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
         <v>6.6</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
         <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
         <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
         <v>1.2</v>
@@ -1428,7 +1428,7 @@
         <v>970</v>
       </c>
       <c r="Y3">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="Z3">
         <v>120</v>
@@ -1437,7 +1437,7 @@
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>10</v>
@@ -1449,13 +1449,13 @@
         <v>170</v>
       </c>
       <c r="AF3">
+        <v>10.5</v>
+      </c>
+      <c r="AG3">
         <v>11.5</v>
       </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
       <c r="AH3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI3">
         <v>190</v>
@@ -1479,22 +1479,22 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR3">
         <v>27</v>
       </c>
       <c r="AS3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>16.5</v>
@@ -1515,22 +1515,22 @@
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3">
         <v>30</v>
       </c>
       <c r="BE3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1613,100 +1613,100 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="G4">
         <v>3.1</v>
       </c>
       <c r="H4">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="I4">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="R4">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="S4">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="U4">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="V4">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA4">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB4">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF4">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI4">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK4">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="AL4">
         <v>290</v>
@@ -1715,28 +1715,28 @@
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AO4">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS4">
+        <v>7.8</v>
+      </c>
+      <c r="AT4">
         <v>12.5</v>
       </c>
-      <c r="AT4">
-        <v>10</v>
-      </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
         <v>10.5</v>
@@ -1745,94 +1745,94 @@
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AY4">
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA4">
         <v>13.5</v>
       </c>
       <c r="BB4">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BE4">
         <v>8.199999999999999</v>
       </c>
       <c r="BF4">
+        <v>15</v>
+      </c>
+      <c r="BG4">
+        <v>12</v>
+      </c>
+      <c r="BH4">
+        <v>4.3</v>
+      </c>
+      <c r="BI4">
+        <v>3.2</v>
+      </c>
+      <c r="BJ4">
+        <v>9</v>
+      </c>
+      <c r="BK4">
+        <v>4.8</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>9.4</v>
+      </c>
+      <c r="BN4">
+        <v>6.6</v>
+      </c>
+      <c r="BO4">
+        <v>4.8</v>
+      </c>
+      <c r="BP4">
         <v>21</v>
       </c>
-      <c r="BG4">
-        <v>16</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.04</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.04</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.04</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="s">
         <v>173</v>
@@ -1855,124 +1855,124 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H5">
+        <v>3.15</v>
+      </c>
+      <c r="I5">
+        <v>3.8</v>
+      </c>
+      <c r="J5">
         <v>3.4</v>
       </c>
-      <c r="I5">
-        <v>3.9</v>
-      </c>
-      <c r="J5">
-        <v>3.65</v>
-      </c>
       <c r="K5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.38</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
         <v>2.06</v>
       </c>
       <c r="Q5">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
         <v>1.42</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y5">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AA5">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AB5">
         <v>12</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>90</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AP5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
         <v>13</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AS5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT5">
         <v>9.800000000000001</v>
@@ -1981,100 +1981,100 @@
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AX5">
+        <v>12.5</v>
+      </c>
+      <c r="AY5">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5">
+        <v>14.5</v>
+      </c>
+      <c r="BA5">
+        <v>34</v>
+      </c>
+      <c r="BB5">
         <v>12</v>
-      </c>
-      <c r="AY5">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5">
-        <v>14</v>
-      </c>
-      <c r="BA5">
-        <v>36</v>
-      </c>
-      <c r="BB5">
-        <v>23</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BT5">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BU5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BW5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BX5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BY5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BZ5">
         <v>25</v>
       </c>
       <c r="CA5">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="CB5" t="s">
         <v>173</v>
@@ -2097,94 +2097,94 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="G6">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="H6">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I6">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="R6">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T6">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V6">
         <v>1.63</v>
       </c>
       <c r="W6">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="X6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD6">
         <v>14</v>
       </c>
       <c r="AE6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG6">
         <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI6">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ6">
         <v>55</v>
@@ -2193,40 +2193,40 @@
         <v>34</v>
       </c>
       <c r="AL6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN6">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AO6">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AP6">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR6">
+        <v>13.5</v>
+      </c>
+      <c r="AS6">
+        <v>5.4</v>
+      </c>
+      <c r="AT6">
         <v>10</v>
       </c>
-      <c r="AR6">
-        <v>14</v>
-      </c>
-      <c r="AS6">
-        <v>23</v>
-      </c>
-      <c r="AT6">
-        <v>11.5</v>
-      </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
         <v>9.800000000000001</v>
       </c>
       <c r="AW6">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX6">
         <v>17</v>
@@ -2235,88 +2235,88 @@
         <v>11</v>
       </c>
       <c r="AZ6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="BB6">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="BC6">
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE6">
         <v>5.7</v>
       </c>
       <c r="BF6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG6">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
+        <v>4.1</v>
+      </c>
+      <c r="BI6">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6">
+        <v>10.5</v>
+      </c>
+      <c r="BK6">
+        <v>3.9</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>5.8</v>
+      </c>
+      <c r="BN6">
+        <v>7</v>
+      </c>
+      <c r="BO6">
+        <v>4.9</v>
+      </c>
+      <c r="BP6">
+        <v>25</v>
+      </c>
+      <c r="BQ6">
+        <v>4.9</v>
+      </c>
+      <c r="BR6">
+        <v>36</v>
+      </c>
+      <c r="BS6">
+        <v>5.2</v>
+      </c>
+      <c r="BT6">
+        <v>6.2</v>
+      </c>
+      <c r="BU6">
         <v>4.5</v>
       </c>
-      <c r="BI6">
-        <v>3.25</v>
-      </c>
-      <c r="BJ6">
-        <v>9.4</v>
-      </c>
-      <c r="BK6">
-        <v>3.85</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>6.2</v>
-      </c>
-      <c r="BN6">
-        <v>7.2</v>
-      </c>
-      <c r="BO6">
-        <v>5.3</v>
-      </c>
-      <c r="BP6">
-        <v>23</v>
-      </c>
-      <c r="BQ6">
-        <v>5.1</v>
-      </c>
-      <c r="BR6">
-        <v>34</v>
-      </c>
-      <c r="BS6">
-        <v>5.5</v>
-      </c>
-      <c r="BT6">
-        <v>5.9</v>
-      </c>
-      <c r="BU6">
+      <c r="BV6">
+        <v>21</v>
+      </c>
+      <c r="BW6">
+        <v>4.7</v>
+      </c>
+      <c r="BX6">
+        <v>32</v>
+      </c>
+      <c r="BY6">
+        <v>5.2</v>
+      </c>
+      <c r="BZ6">
+        <v>25</v>
+      </c>
+      <c r="CA6">
         <v>4.9</v>
-      </c>
-      <c r="BV6">
-        <v>19.5</v>
-      </c>
-      <c r="BW6">
-        <v>4.9</v>
-      </c>
-      <c r="BX6">
-        <v>30</v>
-      </c>
-      <c r="BY6">
-        <v>5.4</v>
-      </c>
-      <c r="BZ6">
-        <v>22</v>
-      </c>
-      <c r="CA6">
-        <v>5.1</v>
       </c>
       <c r="CB6" t="s">
         <v>173</v>
@@ -2339,19 +2339,19 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
         <v>3.45</v>
       </c>
       <c r="J7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K7">
         <v>4.9</v>
@@ -2360,7 +2360,7 @@
         <v>1.19</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
         <v>10.5</v>
@@ -2372,31 +2372,31 @@
         <v>4.1</v>
       </c>
       <c r="Q7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="T7">
         <v>1.34</v>
       </c>
       <c r="U7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.94</v>
       </c>
       <c r="X7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Y7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z7">
         <v>46</v>
@@ -2405,19 +2405,19 @@
         <v>75</v>
       </c>
       <c r="AB7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC7">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AD7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG7">
         <v>13.5</v>
@@ -2429,16 +2429,16 @@
         <v>26</v>
       </c>
       <c r="AJ7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
         <v>21</v>
       </c>
       <c r="AM7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AN7">
         <v>5.9</v>
@@ -2450,28 +2450,28 @@
         <v>29</v>
       </c>
       <c r="AQ7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AR7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU7">
         <v>12.5</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW7">
         <v>24</v>
       </c>
       <c r="AX7">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY7">
         <v>11.5</v>
@@ -2480,10 +2480,10 @@
         <v>12</v>
       </c>
       <c r="BA7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC7">
         <v>16</v>
@@ -2501,64 +2501,64 @@
         <v>10</v>
       </c>
       <c r="BH7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BI7">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BJ7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL7">
         <v>50</v>
       </c>
       <c r="BM7">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN7">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP7">
         <v>14.5</v>
       </c>
       <c r="BQ7">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="BR7">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BS7">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BT7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU7">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BV7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW7">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BX7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BY7">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BZ7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CA7">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="CB7" t="s">
         <v>173</v>
@@ -2581,31 +2581,31 @@
         <v>149</v>
       </c>
       <c r="F8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H8">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.36</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O8">
         <v>1.28</v>
@@ -2623,16 +2623,16 @@
         <v>3.1</v>
       </c>
       <c r="T8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U8">
         <v>2.12</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X8">
         <v>950</v>
@@ -2701,7 +2701,7 @@
         <v>1.31</v>
       </c>
       <c r="AT8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AU8">
         <v>5.1</v>
@@ -2826,7 +2826,7 @@
         <v>3.25</v>
       </c>
       <c r="G9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H9">
         <v>2.12</v>
@@ -2838,7 +2838,7 @@
         <v>3.7</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>1.31</v>
@@ -2850,7 +2850,7 @@
         <v>4.8</v>
       </c>
       <c r="O9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P9">
         <v>2.32</v>
@@ -2886,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="AA9">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AB9">
         <v>18</v>
@@ -2904,10 +2904,10 @@
         <v>85</v>
       </c>
       <c r="AG9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH9">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI9">
         <v>95</v>
@@ -2931,19 +2931,19 @@
         <v>13</v>
       </c>
       <c r="AP9">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS9">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AT9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
@@ -2952,34 +2952,34 @@
         <v>9.4</v>
       </c>
       <c r="AW9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX9">
         <v>20</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA9">
         <v>12</v>
       </c>
       <c r="BB9">
+        <v>6.6</v>
+      </c>
+      <c r="BC9">
+        <v>6.2</v>
+      </c>
+      <c r="BD9">
+        <v>6.4</v>
+      </c>
+      <c r="BE9">
+        <v>6.6</v>
+      </c>
+      <c r="BF9">
         <v>5.9</v>
-      </c>
-      <c r="BC9">
-        <v>5.6</v>
-      </c>
-      <c r="BD9">
-        <v>5.8</v>
-      </c>
-      <c r="BE9">
-        <v>6</v>
-      </c>
-      <c r="BF9">
-        <v>5.4</v>
       </c>
       <c r="BG9">
         <v>10</v>
@@ -3065,10 +3065,10 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H10">
         <v>7.6</v>
@@ -3080,46 +3080,46 @@
         <v>5.4</v>
       </c>
       <c r="K10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>1.26</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>1.17</v>
       </c>
       <c r="P10">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q10">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S10">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10">
         <v>1.13</v>
       </c>
       <c r="W10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y10">
         <v>36</v>
@@ -3128,7 +3128,7 @@
         <v>80</v>
       </c>
       <c r="AA10">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AB10">
         <v>12</v>
@@ -3149,7 +3149,7 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI10">
         <v>85</v>
@@ -3167,22 +3167,22 @@
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP10">
         <v>22</v>
       </c>
       <c r="AQ10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AR10">
         <v>60</v>
       </c>
       <c r="AS10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT10">
         <v>10</v>
@@ -3200,7 +3200,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
         <v>20</v>
@@ -3218,10 +3218,10 @@
         <v>23</v>
       </c>
       <c r="BE10">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG10">
         <v>60</v>
@@ -3236,13 +3236,13 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN10">
         <v>4.4</v>
@@ -3251,7 +3251,7 @@
         <v>3.85</v>
       </c>
       <c r="BP10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ10">
         <v>5</v>
@@ -3260,31 +3260,31 @@
         <v>20</v>
       </c>
       <c r="BS10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT10">
         <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
+        <v>10</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>9.6</v>
       </c>
       <c r="BZ10">
         <v>11.5</v>
       </c>
       <c r="CA10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB10" t="s">
         <v>173</v>
@@ -3307,7 +3307,7 @@
         <v>152</v>
       </c>
       <c r="F11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G11">
         <v>3.3</v>
@@ -3328,19 +3328,19 @@
         <v>1.65</v>
       </c>
       <c r="M11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N11">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O11">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P11">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q11">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R11">
         <v>1.18</v>
@@ -3349,10 +3349,10 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U11">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V11">
         <v>1.43</v>
@@ -3361,7 +3361,7 @@
         <v>1.43</v>
       </c>
       <c r="X11">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y11">
         <v>500</v>
@@ -3415,58 +3415,58 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="AQ11">
-        <v>1.88</v>
+        <v>3.85</v>
       </c>
       <c r="AR11">
+        <v>2.14</v>
+      </c>
+      <c r="AS11">
+        <v>2.18</v>
+      </c>
+      <c r="AT11">
+        <v>4.1</v>
+      </c>
+      <c r="AU11">
+        <v>2.9</v>
+      </c>
+      <c r="AV11">
+        <v>6.6</v>
+      </c>
+      <c r="AW11">
+        <v>2.22</v>
+      </c>
+      <c r="AX11">
         <v>2.5</v>
       </c>
-      <c r="AS11">
-        <v>2.12</v>
-      </c>
-      <c r="AT11">
-        <v>1.87</v>
-      </c>
-      <c r="AU11">
-        <v>1.93</v>
-      </c>
-      <c r="AV11">
-        <v>1.97</v>
-      </c>
-      <c r="AW11">
-        <v>2.12</v>
-      </c>
-      <c r="AX11">
-        <v>2.08</v>
-      </c>
       <c r="AY11">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AZ11">
-        <v>2.66</v>
+        <v>9.6</v>
       </c>
       <c r="BA11">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="BB11">
+        <v>2.22</v>
+      </c>
+      <c r="BC11">
+        <v>2.22</v>
+      </c>
+      <c r="BD11">
+        <v>2.2</v>
+      </c>
+      <c r="BE11">
+        <v>2.24</v>
+      </c>
+      <c r="BF11">
         <v>2.1</v>
       </c>
-      <c r="BC11">
+      <c r="BG11">
         <v>2.1</v>
-      </c>
-      <c r="BD11">
-        <v>2.08</v>
-      </c>
-      <c r="BE11">
-        <v>2.32</v>
-      </c>
-      <c r="BF11">
-        <v>2.04</v>
-      </c>
-      <c r="BG11">
-        <v>2.04</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3549,10 +3549,10 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G12">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H12">
         <v>3.15</v>
@@ -3570,61 +3570,61 @@
         <v>1.59</v>
       </c>
       <c r="M12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q12">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="R12">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S12">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T12">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U12">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V12">
         <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X12">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12">
         <v>19.5</v>
       </c>
       <c r="AA12">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD12">
         <v>15</v>
       </c>
       <c r="AE12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF12">
         <v>16</v>
@@ -3636,37 +3636,37 @@
         <v>22</v>
       </c>
       <c r="AI12">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK12">
         <v>40</v>
       </c>
       <c r="AL12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM12">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO12">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS12">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AT12">
         <v>7.2</v>
@@ -3678,7 +3678,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -3690,85 +3690,85 @@
         <v>20</v>
       </c>
       <c r="BA12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC12">
         <v>34</v>
       </c>
       <c r="BD12">
+        <v>55</v>
+      </c>
+      <c r="BE12">
+        <v>110</v>
+      </c>
+      <c r="BF12">
+        <v>36</v>
+      </c>
+      <c r="BG12">
         <v>50</v>
       </c>
-      <c r="BE12">
-        <v>100</v>
-      </c>
-      <c r="BF12">
-        <v>38</v>
-      </c>
-      <c r="BG12">
+      <c r="BH12">
+        <v>2.74</v>
+      </c>
+      <c r="BI12">
+        <v>2.56</v>
+      </c>
+      <c r="BJ12">
+        <v>11.5</v>
+      </c>
+      <c r="BK12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>14</v>
+      </c>
+      <c r="BN12">
+        <v>5.3</v>
+      </c>
+      <c r="BO12">
+        <v>4.9</v>
+      </c>
+      <c r="BP12">
+        <v>27</v>
+      </c>
+      <c r="BQ12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR12">
+        <v>48</v>
+      </c>
+      <c r="BS12">
+        <v>11</v>
+      </c>
+      <c r="BT12">
+        <v>6.2</v>
+      </c>
+      <c r="BU12">
+        <v>5.5</v>
+      </c>
+      <c r="BV12">
+        <v>32</v>
+      </c>
+      <c r="BW12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX12">
         <v>55</v>
       </c>
-      <c r="BH12">
-        <v>2.96</v>
-      </c>
-      <c r="BI12">
-        <v>2.3</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>2.68</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>2.98</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>3.75</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>2.98</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>2.98</v>
-      </c>
-      <c r="BT12">
-        <v>8.6</v>
-      </c>
-      <c r="BU12">
-        <v>4.1</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>2.98</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
       <c r="BY12">
-        <v>2.98</v>
+        <v>11</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA12">
-        <v>2.98</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="s">
         <v>173</v>
@@ -3794,19 +3794,19 @@
         <v>4</v>
       </c>
       <c r="G13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H13">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="I13">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>1.29</v>
@@ -3815,61 +3815,61 @@
         <v>1.04</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P13">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T13">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U13">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="V13">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="W13">
         <v>1.31</v>
       </c>
       <c r="X13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z13">
         <v>15</v>
       </c>
       <c r="AA13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC13">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF13">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG13">
         <v>17.5</v>
@@ -3878,7 +3878,7 @@
         <v>15</v>
       </c>
       <c r="AI13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ13">
         <v>470</v>
@@ -3890,16 +3890,16 @@
         <v>42</v>
       </c>
       <c r="AM13">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO13">
         <v>8.4</v>
       </c>
       <c r="AP13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ13">
         <v>12.5</v>
@@ -3908,43 +3908,43 @@
         <v>13.5</v>
       </c>
       <c r="AS13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT13">
         <v>20</v>
       </c>
       <c r="AU13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV13">
         <v>9.800000000000001</v>
       </c>
       <c r="AW13">
+        <v>16</v>
+      </c>
+      <c r="AX13">
+        <v>32</v>
+      </c>
+      <c r="AY13">
         <v>15.5</v>
       </c>
-      <c r="AX13">
-        <v>30</v>
-      </c>
-      <c r="AY13">
-        <v>14.5</v>
-      </c>
       <c r="AZ13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA13">
         <v>23</v>
       </c>
       <c r="BB13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF13">
         <v>25</v>
@@ -3953,43 +3953,43 @@
         <v>7.8</v>
       </c>
       <c r="BH13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL13">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BM13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO13">
         <v>6.8</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ13">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS13">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU13">
         <v>4.6</v>
@@ -3998,19 +3998,19 @@
         <v>13</v>
       </c>
       <c r="BW13">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BX13">
         <v>22</v>
       </c>
       <c r="BY13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13">
         <v>15</v>
       </c>
       <c r="CA13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="s">
         <v>173</v>
@@ -4033,22 +4033,22 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="G14">
+        <v>3.2</v>
+      </c>
+      <c r="H14">
+        <v>2.28</v>
+      </c>
+      <c r="I14">
+        <v>2.4</v>
+      </c>
+      <c r="J14">
         <v>3.8</v>
       </c>
-      <c r="H14">
-        <v>2.04</v>
-      </c>
-      <c r="I14">
-        <v>2.12</v>
-      </c>
-      <c r="J14">
-        <v>3.95</v>
-      </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
         <v>1.3</v>
@@ -4057,202 +4057,202 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O14">
         <v>1.21</v>
       </c>
       <c r="P14">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R14">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S14">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
         <v>1.57</v>
       </c>
       <c r="U14">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V14">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="W14">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="X14">
         <v>27</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z14">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AA14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AB14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AG14">
+        <v>15</v>
+      </c>
+      <c r="AH14">
         <v>16</v>
-      </c>
-      <c r="AH14">
-        <v>16.5</v>
       </c>
       <c r="AI14">
         <v>32</v>
       </c>
       <c r="AJ14">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AK14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM14">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AO14">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AP14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR14">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV14">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AY14">
+        <v>12</v>
+      </c>
+      <c r="AZ14">
         <v>13</v>
-      </c>
-      <c r="AZ14">
-        <v>13.5</v>
       </c>
       <c r="BA14">
         <v>23</v>
       </c>
       <c r="BB14">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BC14">
+        <v>16</v>
+      </c>
+      <c r="BD14">
+        <v>18</v>
+      </c>
+      <c r="BE14">
         <v>27</v>
       </c>
-      <c r="BD14">
-        <v>29</v>
-      </c>
-      <c r="BE14">
-        <v>50</v>
-      </c>
       <c r="BF14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG14">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH14">
         <v>4.8</v>
       </c>
       <c r="BI14">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BJ14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BN14">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO14">
+        <v>3.7</v>
+      </c>
+      <c r="BP14">
+        <v>26</v>
+      </c>
+      <c r="BQ14">
+        <v>5.9</v>
+      </c>
+      <c r="BR14">
+        <v>34</v>
+      </c>
+      <c r="BS14">
         <v>5.7</v>
       </c>
-      <c r="BP14">
-        <v>30</v>
-      </c>
-      <c r="BQ14">
+      <c r="BT14">
+        <v>5.8</v>
+      </c>
+      <c r="BU14">
+        <v>4.9</v>
+      </c>
+      <c r="BV14">
+        <v>16</v>
+      </c>
+      <c r="BW14">
         <v>4.8</v>
-      </c>
-      <c r="BR14">
-        <v>36</v>
-      </c>
-      <c r="BS14">
-        <v>4.9</v>
-      </c>
-      <c r="BT14">
-        <v>5.9</v>
-      </c>
-      <c r="BU14">
-        <v>4.2</v>
-      </c>
-      <c r="BV14">
-        <v>15.5</v>
-      </c>
-      <c r="BW14">
-        <v>4.1</v>
       </c>
       <c r="BX14">
         <v>26</v>
       </c>
       <c r="BY14">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BZ14">
         <v>18.5</v>
       </c>
       <c r="CA14">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="CB14" t="s">
         <v>173</v>
@@ -4275,115 +4275,115 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="G15">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
         <v>1.36</v>
       </c>
       <c r="M15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O15">
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R15">
         <v>1.46</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T15">
         <v>1.69</v>
       </c>
       <c r="U15">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="X15">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="Y15">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="Z15">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AA15">
         <v>900</v>
       </c>
       <c r="AB15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD15">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE15">
         <v>340</v>
       </c>
       <c r="AF15">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG15">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH15">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI15">
         <v>460</v>
       </c>
       <c r="AJ15">
+        <v>26</v>
+      </c>
+      <c r="AK15">
+        <v>25</v>
+      </c>
+      <c r="AL15">
         <v>130</v>
-      </c>
-      <c r="AK15">
-        <v>150</v>
-      </c>
-      <c r="AL15">
-        <v>180</v>
       </c>
       <c r="AM15">
         <v>580</v>
       </c>
       <c r="AN15">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="AO15">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP15">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ15">
         <v>15</v>
@@ -4392,49 +4392,49 @@
         <v>26</v>
       </c>
       <c r="AS15">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT15">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AX15">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY15">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD15">
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BF15">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BG15">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4517,19 +4517,19 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H16">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="I16">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="J16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K16">
         <v>4.3</v>
@@ -4541,37 +4541,37 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O16">
         <v>1.22</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S16">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T16">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W16">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y16">
         <v>14</v>
@@ -4580,19 +4580,19 @@
         <v>17.5</v>
       </c>
       <c r="AA16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD16">
         <v>12</v>
       </c>
       <c r="AE16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF16">
         <v>26</v>
@@ -4601,7 +4601,7 @@
         <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI16">
         <v>32</v>
@@ -4622,7 +4622,7 @@
         <v>24</v>
       </c>
       <c r="AO16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP16">
         <v>19.5</v>
@@ -4652,19 +4652,19 @@
         <v>20</v>
       </c>
       <c r="AY16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16">
         <v>14</v>
       </c>
       <c r="BA16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC16">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BD16">
         <v>27</v>
@@ -4759,100 +4759,100 @@
         <v>158</v>
       </c>
       <c r="F17">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="G17">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="H17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I17">
+        <v>5.2</v>
+      </c>
+      <c r="J17">
+        <v>4.4</v>
+      </c>
+      <c r="K17">
         <v>4.8</v>
-      </c>
-      <c r="J17">
-        <v>4.2</v>
-      </c>
-      <c r="K17">
-        <v>4.5</v>
       </c>
       <c r="L17">
         <v>1.29</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q17">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R17">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S17">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T17">
         <v>1.62</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V17">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W17">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="X17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z17">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA17">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB17">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AC17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD17">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE17">
         <v>60</v>
       </c>
       <c r="AF17">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK17">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL17">
         <v>34</v>
@@ -4861,124 +4861,124 @@
         <v>80</v>
       </c>
       <c r="AN17">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO17">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR17">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS17">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AT17">
         <v>11</v>
       </c>
       <c r="AU17">
+        <v>9.6</v>
+      </c>
+      <c r="AV17">
+        <v>17.5</v>
+      </c>
+      <c r="AW17">
+        <v>23</v>
+      </c>
+      <c r="AX17">
+        <v>11.5</v>
+      </c>
+      <c r="AY17">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV17">
+      <c r="AZ17">
+        <v>15.5</v>
+      </c>
+      <c r="BA17">
+        <v>23</v>
+      </c>
+      <c r="BB17">
         <v>16</v>
-      </c>
-      <c r="AW17">
-        <v>6.4</v>
-      </c>
-      <c r="AX17">
-        <v>12</v>
-      </c>
-      <c r="AY17">
-        <v>9.4</v>
-      </c>
-      <c r="AZ17">
-        <v>14.5</v>
-      </c>
-      <c r="BA17">
-        <v>36</v>
-      </c>
-      <c r="BB17">
-        <v>17</v>
       </c>
       <c r="BC17">
         <v>14.5</v>
       </c>
       <c r="BD17">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BE17">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BF17">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG17">
         <v>7</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI17">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB17" t="s">
         <v>173</v>
@@ -5001,103 +5001,103 @@
         <v>159</v>
       </c>
       <c r="F18">
+        <v>4.2</v>
+      </c>
+      <c r="G18">
+        <v>4.4</v>
+      </c>
+      <c r="H18">
+        <v>1.92</v>
+      </c>
+      <c r="I18">
+        <v>1.97</v>
+      </c>
+      <c r="J18">
+        <v>3.85</v>
+      </c>
+      <c r="K18">
         <v>4</v>
       </c>
-      <c r="G18">
-        <v>4.3</v>
-      </c>
-      <c r="H18">
-        <v>1.98</v>
-      </c>
-      <c r="I18">
-        <v>2.04</v>
-      </c>
-      <c r="J18">
-        <v>3.65</v>
-      </c>
-      <c r="K18">
-        <v>3.9</v>
-      </c>
       <c r="L18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M18">
         <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O18">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P18">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q18">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="R18">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S18">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T18">
         <v>1.81</v>
       </c>
       <c r="U18">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V18">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="W18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X18">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Y18">
         <v>10.5</v>
       </c>
       <c r="Z18">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA18">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AB18">
         <v>18</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF18">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AG18">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AH18">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI18">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ18">
         <v>310</v>
       </c>
       <c r="AK18">
+        <v>65</v>
+      </c>
+      <c r="AL18">
         <v>70</v>
-      </c>
-      <c r="AL18">
-        <v>65</v>
       </c>
       <c r="AM18">
         <v>580</v>
@@ -5106,61 +5106,61 @@
         <v>65</v>
       </c>
       <c r="AO18">
+        <v>13</v>
+      </c>
+      <c r="AP18">
+        <v>14</v>
+      </c>
+      <c r="AQ18">
+        <v>8.6</v>
+      </c>
+      <c r="AR18">
+        <v>11</v>
+      </c>
+      <c r="AS18">
+        <v>18</v>
+      </c>
+      <c r="AT18">
+        <v>14</v>
+      </c>
+      <c r="AU18">
+        <v>7.8</v>
+      </c>
+      <c r="AV18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW18">
         <v>16.5</v>
       </c>
-      <c r="AP18">
-        <v>12</v>
-      </c>
-      <c r="AQ18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR18">
-        <v>10.5</v>
-      </c>
-      <c r="AS18">
-        <v>19.5</v>
-      </c>
-      <c r="AT18">
-        <v>12.5</v>
-      </c>
-      <c r="AU18">
-        <v>7.2</v>
-      </c>
-      <c r="AV18">
-        <v>8.6</v>
-      </c>
-      <c r="AW18">
-        <v>17.5</v>
-      </c>
       <c r="AX18">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AY18">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AZ18">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB18">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC18">
         <v>40</v>
       </c>
       <c r="BD18">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BE18">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF18">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BG18">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5243,22 +5243,22 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G19">
         <v>3.1</v>
       </c>
       <c r="H19">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I19">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L19">
         <v>1.29</v>
@@ -5270,28 +5270,28 @@
         <v>5.5</v>
       </c>
       <c r="O19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P19">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q19">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S19">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T19">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U19">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W19">
         <v>1.47</v>
@@ -5300,7 +5300,7 @@
         <v>23</v>
       </c>
       <c r="Y19">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z19">
         <v>20</v>
@@ -5309,16 +5309,16 @@
         <v>34</v>
       </c>
       <c r="AB19">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC19">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19">
         <v>25</v>
@@ -5330,43 +5330,43 @@
         <v>15</v>
       </c>
       <c r="AI19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ19">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AK19">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL19">
         <v>34</v>
       </c>
       <c r="AM19">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN19">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP19">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR19">
         <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV19">
         <v>10.5</v>
@@ -5375,34 +5375,34 @@
         <v>19</v>
       </c>
       <c r="AX19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB19">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BC19">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BD19">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BE19">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BF19">
         <v>15</v>
       </c>
       <c r="BG19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5485,7 +5485,7 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G20">
         <v>8.6</v>
@@ -5518,16 +5518,16 @@
         <v>3</v>
       </c>
       <c r="Q20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R20">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S20">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T20">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U20">
         <v>2.26</v>
@@ -5539,10 +5539,10 @@
         <v>1.13</v>
       </c>
       <c r="X20">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="Y20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z20">
         <v>11</v>
@@ -5551,7 +5551,7 @@
         <v>13</v>
       </c>
       <c r="AB20">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AC20">
         <v>14</v>
@@ -5563,19 +5563,19 @@
         <v>14</v>
       </c>
       <c r="AF20">
-        <v>540</v>
+        <v>80</v>
       </c>
       <c r="AG20">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AH20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20">
         <v>29</v>
       </c>
       <c r="AJ20">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AK20">
         <v>480</v>
@@ -5587,25 +5587,25 @@
         <v>320</v>
       </c>
       <c r="AN20">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AO20">
         <v>4.6</v>
       </c>
       <c r="AP20">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="AQ20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS20">
         <v>11</v>
       </c>
       <c r="AT20">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AU20">
         <v>12</v>
@@ -5617,91 +5617,91 @@
         <v>12</v>
       </c>
       <c r="AX20">
+        <v>32</v>
+      </c>
+      <c r="AY20">
+        <v>26</v>
+      </c>
+      <c r="AZ20">
+        <v>19.5</v>
+      </c>
+      <c r="BA20">
+        <v>24</v>
+      </c>
+      <c r="BB20">
+        <v>12</v>
+      </c>
+      <c r="BC20">
+        <v>11.5</v>
+      </c>
+      <c r="BD20">
         <v>28</v>
       </c>
-      <c r="AY20">
-        <v>25</v>
-      </c>
-      <c r="AZ20">
-        <v>19</v>
-      </c>
-      <c r="BA20">
-        <v>15</v>
-      </c>
-      <c r="BB20">
-        <v>12.5</v>
-      </c>
-      <c r="BC20">
-        <v>40</v>
-      </c>
-      <c r="BD20">
-        <v>32</v>
-      </c>
       <c r="BE20">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BF20">
         <v>15</v>
       </c>
       <c r="BG20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH20">
         <v>4.9</v>
       </c>
       <c r="BI20">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ20">
         <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN20">
         <v>12</v>
       </c>
       <c r="BO20">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ20">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT20">
         <v>4.3</v>
       </c>
       <c r="BU20">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BV20">
+        <v>8</v>
+      </c>
+      <c r="BW20">
+        <v>5.1</v>
+      </c>
+      <c r="BX20">
+        <v>19.5</v>
+      </c>
+      <c r="BY20">
         <v>8.199999999999999</v>
       </c>
-      <c r="BW20">
-        <v>5.4</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>8.6</v>
-      </c>
       <c r="BZ20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA20">
         <v>6</v>
@@ -5727,7 +5727,7 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G21">
         <v>1.91</v>
@@ -5736,22 +5736,22 @@
         <v>5.4</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J21">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K21">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L21">
         <v>1.56</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N21">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O21">
         <v>1.52</v>
@@ -5760,133 +5760,133 @@
         <v>1.57</v>
       </c>
       <c r="Q21">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
         <v>1.2</v>
       </c>
       <c r="S21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T21">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U21">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V21">
         <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AA21">
         <v>900</v>
       </c>
       <c r="AB21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC21">
         <v>8.199999999999999</v>
       </c>
       <c r="AD21">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AE21">
         <v>700</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21">
         <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AI21">
         <v>700</v>
       </c>
       <c r="AJ21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK21">
         <v>26</v>
       </c>
       <c r="AL21">
-        <v>460</v>
+        <v>170</v>
       </c>
       <c r="AM21">
         <v>500</v>
       </c>
       <c r="AN21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO21">
-        <v>700</v>
+        <v>270</v>
       </c>
       <c r="AP21">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ21">
         <v>12</v>
       </c>
       <c r="AR21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AS21">
-        <v>10.5</v>
+        <v>110</v>
       </c>
       <c r="AT21">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW21">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AX21">
         <v>8.4</v>
       </c>
       <c r="AY21">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21">
         <v>22</v>
       </c>
       <c r="BA21">
-        <v>10.5</v>
+        <v>65</v>
       </c>
       <c r="BB21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD21">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="BE21">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5969,172 +5969,172 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="G22">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H22">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="I22">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="J22">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
+        <v>1.04</v>
+      </c>
+      <c r="N22">
+        <v>3.5</v>
+      </c>
+      <c r="O22">
+        <v>1.33</v>
+      </c>
+      <c r="P22">
+        <v>1.83</v>
+      </c>
+      <c r="Q22">
+        <v>1.89</v>
+      </c>
+      <c r="R22">
+        <v>1.33</v>
+      </c>
+      <c r="S22">
+        <v>3.4</v>
+      </c>
+      <c r="T22">
+        <v>1.9</v>
+      </c>
+      <c r="U22">
+        <v>1.84</v>
+      </c>
+      <c r="V22">
+        <v>2.28</v>
+      </c>
+      <c r="W22">
+        <v>1.15</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>970</v>
+      </c>
+      <c r="Z22">
+        <v>970</v>
+      </c>
+      <c r="AA22">
+        <v>900</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>42</v>
+      </c>
+      <c r="AD22">
+        <v>970</v>
+      </c>
+      <c r="AE22">
+        <v>85</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>160</v>
+      </c>
+      <c r="AI22">
+        <v>160</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>580</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>600</v>
+      </c>
+      <c r="AP22">
+        <v>1.59</v>
+      </c>
+      <c r="AQ22">
+        <v>1.39</v>
+      </c>
+      <c r="AR22">
+        <v>1.44</v>
+      </c>
+      <c r="AS22">
+        <v>1.56</v>
+      </c>
+      <c r="AT22">
+        <v>1.59</v>
+      </c>
+      <c r="AU22">
+        <v>2.52</v>
+      </c>
+      <c r="AV22">
+        <v>7.6</v>
+      </c>
+      <c r="AW22">
+        <v>1.55</v>
+      </c>
+      <c r="AX22">
+        <v>1.59</v>
+      </c>
+      <c r="AY22">
+        <v>1.59</v>
+      </c>
+      <c r="AZ22">
+        <v>1.55</v>
+      </c>
+      <c r="BA22">
+        <v>1.57</v>
+      </c>
+      <c r="BB22">
+        <v>1.59</v>
+      </c>
+      <c r="BC22">
+        <v>1.59</v>
+      </c>
+      <c r="BD22">
+        <v>1.59</v>
+      </c>
+      <c r="BE22">
+        <v>1.58</v>
+      </c>
+      <c r="BF22">
+        <v>1.59</v>
+      </c>
+      <c r="BG22">
+        <v>1.48</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
         <v>1.01</v>
-      </c>
-      <c r="N22">
-        <v>2.92</v>
-      </c>
-      <c r="O22">
-        <v>1.39</v>
-      </c>
-      <c r="P22">
-        <v>1.75</v>
-      </c>
-      <c r="Q22">
-        <v>2</v>
-      </c>
-      <c r="R22">
-        <v>1.27</v>
-      </c>
-      <c r="S22">
-        <v>3.05</v>
-      </c>
-      <c r="T22">
-        <v>1.89</v>
-      </c>
-      <c r="U22">
-        <v>1.78</v>
-      </c>
-      <c r="V22">
-        <v>1.01</v>
-      </c>
-      <c r="W22">
-        <v>1.01</v>
-      </c>
-      <c r="X22">
-        <v>1000</v>
-      </c>
-      <c r="Y22">
-        <v>1000</v>
-      </c>
-      <c r="Z22">
-        <v>1000</v>
-      </c>
-      <c r="AA22">
-        <v>1000</v>
-      </c>
-      <c r="AB22">
-        <v>1000</v>
-      </c>
-      <c r="AC22">
-        <v>1000</v>
-      </c>
-      <c r="AD22">
-        <v>1000</v>
-      </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>1000</v>
-      </c>
-      <c r="AH22">
-        <v>1000</v>
-      </c>
-      <c r="AI22">
-        <v>1000</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
-        <v>1000</v>
-      </c>
-      <c r="AP22">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22">
-        <v>1.03</v>
-      </c>
-      <c r="AR22">
-        <v>1.03</v>
-      </c>
-      <c r="AS22">
-        <v>1.03</v>
-      </c>
-      <c r="AT22">
-        <v>1.03</v>
-      </c>
-      <c r="AU22">
-        <v>1.03</v>
-      </c>
-      <c r="AV22">
-        <v>1.03</v>
-      </c>
-      <c r="AW22">
-        <v>1.03</v>
-      </c>
-      <c r="AX22">
-        <v>1.03</v>
-      </c>
-      <c r="AY22">
-        <v>1.03</v>
-      </c>
-      <c r="AZ22">
-        <v>1.03</v>
-      </c>
-      <c r="BA22">
-        <v>1.03</v>
-      </c>
-      <c r="BB22">
-        <v>1.03</v>
-      </c>
-      <c r="BC22">
-        <v>1.03</v>
-      </c>
-      <c r="BD22">
-        <v>1.03</v>
-      </c>
-      <c r="BE22">
-        <v>1.03</v>
-      </c>
-      <c r="BF22">
-        <v>1.01</v>
-      </c>
-      <c r="BG22">
-        <v>8</v>
-      </c>
-      <c r="BH22">
-        <v>3.8</v>
-      </c>
-      <c r="BI22">
-        <v>2.44</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
@@ -6211,13 +6211,13 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G23">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H23">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I23">
         <v>3.45</v>
@@ -6226,160 +6226,160 @@
         <v>2.88</v>
       </c>
       <c r="K23">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L23">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M23">
         <v>1.13</v>
       </c>
       <c r="N23">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q23">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="R23">
         <v>1.18</v>
       </c>
       <c r="S23">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U23">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X23">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA23">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB23">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AC23">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="AD23">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AE23">
         <v>150</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI23">
         <v>230</v>
       </c>
       <c r="AJ23">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK23">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AL23">
         <v>210</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP23">
-        <v>1.44</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>7.6</v>
       </c>
       <c r="AR23">
-        <v>1.58</v>
+        <v>14.5</v>
       </c>
       <c r="AS23">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="AT23">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU23">
-        <v>1.39</v>
+        <v>6</v>
       </c>
       <c r="AV23">
-        <v>1.49</v>
+        <v>13</v>
       </c>
       <c r="AW23">
-        <v>1.57</v>
+        <v>7</v>
       </c>
       <c r="AX23">
-        <v>1.58</v>
+        <v>13</v>
       </c>
       <c r="AY23">
-        <v>1.58</v>
+        <v>11.5</v>
       </c>
       <c r="AZ23">
-        <v>1.58</v>
+        <v>6.2</v>
       </c>
       <c r="BA23">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="BB23">
-        <v>1.56</v>
+        <v>34</v>
       </c>
       <c r="BC23">
-        <v>1.56</v>
+        <v>30</v>
       </c>
       <c r="BD23">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="BE23">
-        <v>1.58</v>
+        <v>7.8</v>
       </c>
       <c r="BF23">
-        <v>1.58</v>
+        <v>38</v>
       </c>
       <c r="BG23">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK23">
         <v>1.01</v>
@@ -6391,37 +6391,37 @@
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
@@ -6453,22 +6453,22 @@
         <v>165</v>
       </c>
       <c r="F24">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G24">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="H24">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J24">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K24">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
         <v>1.39</v>
@@ -6477,19 +6477,19 @@
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P24">
         <v>2.04</v>
       </c>
       <c r="Q24">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S24">
         <v>3.35</v>
@@ -6498,22 +6498,22 @@
         <v>1.73</v>
       </c>
       <c r="U24">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X24">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA24">
         <v>65</v>
@@ -6525,52 +6525,52 @@
         <v>8.6</v>
       </c>
       <c r="AD24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE24">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF24">
+        <v>16</v>
+      </c>
+      <c r="AG24">
+        <v>12</v>
+      </c>
+      <c r="AH24">
         <v>18</v>
       </c>
-      <c r="AG24">
-        <v>11.5</v>
-      </c>
-      <c r="AH24">
-        <v>21</v>
-      </c>
       <c r="AI24">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK24">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL24">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM24">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AN24">
         <v>19</v>
       </c>
       <c r="AO24">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24">
         <v>11.5</v>
       </c>
       <c r="AR24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT24">
         <v>9.4</v>
@@ -6579,16 +6579,16 @@
         <v>7.4</v>
       </c>
       <c r="AV24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW24">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AX24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY24">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ24">
         <v>15</v>
@@ -6597,22 +6597,22 @@
         <v>21</v>
       </c>
       <c r="BB24">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BC24">
         <v>21</v>
       </c>
       <c r="BD24">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="BE24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG24">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH24">
         <v>3.9</v>
@@ -6633,7 +6633,7 @@
         <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO24">
         <v>4.2</v>
@@ -6642,7 +6642,7 @@
         <v>19.5</v>
       </c>
       <c r="BQ24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BR24">
         <v>34</v>
@@ -6707,10 +6707,10 @@
         <v>2.06</v>
       </c>
       <c r="J25">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
         <v>1.48</v>
@@ -6719,115 +6719,115 @@
         <v>1.09</v>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O25">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P25">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q25">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S25">
         <v>4.2</v>
       </c>
       <c r="T25">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U25">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="V25">
         <v>1.94</v>
       </c>
       <c r="W25">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X25">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z25">
         <v>12</v>
       </c>
       <c r="AA25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC25">
         <v>8</v>
       </c>
       <c r="AD25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG25">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI25">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ25">
         <v>900</v>
       </c>
       <c r="AK25">
-        <v>160</v>
+        <v>310</v>
       </c>
       <c r="AL25">
-        <v>190</v>
+        <v>420</v>
       </c>
       <c r="AM25">
         <v>580</v>
       </c>
       <c r="AN25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AO25">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AP25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS25">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU25">
         <v>7</v>
       </c>
       <c r="AV25">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AX25">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY25">
         <v>15.5</v>
@@ -6836,31 +6836,31 @@
         <v>18</v>
       </c>
       <c r="BA25">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC25">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD25">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE25">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF25">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH25">
         <v>3.15</v>
       </c>
       <c r="BI25">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ25">
         <v>11</v>
@@ -6878,7 +6878,7 @@
         <v>8</v>
       </c>
       <c r="BO25">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP25">
         <v>44</v>
@@ -6896,13 +6896,13 @@
         <v>4.7</v>
       </c>
       <c r="BU25">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV25">
         <v>16</v>
       </c>
       <c r="BW25">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX25">
         <v>36</v>
@@ -6937,16 +6937,16 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G26">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H26">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J26">
         <v>3</v>
@@ -6964,7 +6964,7 @@
         <v>2.58</v>
       </c>
       <c r="O26">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P26">
         <v>1.51</v>
@@ -6985,22 +6985,22 @@
         <v>1.76</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y26">
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA26">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB26">
         <v>7.6</v>
@@ -7012,7 +7012,7 @@
         <v>15.5</v>
       </c>
       <c r="AE26">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF26">
         <v>15</v>
@@ -7021,10 +7021,10 @@
         <v>13</v>
       </c>
       <c r="AH26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI26">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ26">
         <v>42</v>
@@ -7036,7 +7036,7 @@
         <v>75</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN26">
         <v>46</v>
@@ -7048,19 +7048,19 @@
         <v>7.2</v>
       </c>
       <c r="AQ26">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR26">
         <v>18.5</v>
       </c>
       <c r="AS26">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT26">
         <v>7</v>
       </c>
       <c r="AU26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV26">
         <v>14</v>
@@ -7069,94 +7069,94 @@
         <v>44</v>
       </c>
       <c r="AX26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY26">
         <v>12</v>
       </c>
       <c r="AZ26">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BA26">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BB26">
         <v>36</v>
       </c>
       <c r="BC26">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BD26">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BE26">
         <v>95</v>
       </c>
       <c r="BF26">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BG26">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH26">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI26">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ26">
         <v>11.5</v>
       </c>
       <c r="BK26">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BN26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO26">
         <v>4.7</v>
       </c>
       <c r="BP26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR26">
         <v>48</v>
       </c>
       <c r="BS26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BT26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU26">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX26">
         <v>60</v>
       </c>
       <c r="BY26">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BZ26">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CA26">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="CB26" t="s">
         <v>173</v>
@@ -7179,16 +7179,16 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G27">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="H27">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="I27">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="J27">
         <v>3.35</v>
@@ -7197,49 +7197,49 @@
         <v>3.5</v>
       </c>
       <c r="L27">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P27">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q27">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R27">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T27">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U27">
         <v>2.06</v>
       </c>
       <c r="V27">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y27">
         <v>10.5</v>
       </c>
       <c r="Z27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA27">
         <v>48</v>
@@ -7248,13 +7248,13 @@
         <v>11</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD27">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE27">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF27">
         <v>19.5</v>
@@ -7266,13 +7266,13 @@
         <v>19.5</v>
       </c>
       <c r="AI27">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AJ27">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AK27">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL27">
         <v>60</v>
@@ -7281,22 +7281,22 @@
         <v>500</v>
       </c>
       <c r="AN27">
+        <v>40</v>
+      </c>
+      <c r="AO27">
         <v>36</v>
-      </c>
-      <c r="AO27">
-        <v>32</v>
       </c>
       <c r="AP27">
         <v>10.5</v>
       </c>
       <c r="AQ27">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR27">
         <v>15.5</v>
       </c>
       <c r="AS27">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AT27">
         <v>9.4</v>
@@ -7308,97 +7308,97 @@
         <v>11</v>
       </c>
       <c r="AW27">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AX27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY27">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA27">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BB27">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BC27">
         <v>26</v>
       </c>
       <c r="BD27">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BE27">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="BG27">
-        <v>19.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI27">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK27">
-        <v>1.16</v>
+        <v>8.6</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.16</v>
+        <v>7.8</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO27">
-        <v>1.72</v>
+        <v>5.3</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ27">
-        <v>1.16</v>
+        <v>6.2</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS27">
-        <v>1.16</v>
+        <v>6.8</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU27">
-        <v>1.76</v>
+        <v>5.1</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW27">
-        <v>1.16</v>
+        <v>6</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY27">
-        <v>1.16</v>
+        <v>6.8</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA27">
-        <v>1.16</v>
+        <v>6.8</v>
       </c>
       <c r="CB27" t="s">
         <v>173</v>
@@ -7421,61 +7421,61 @@
         <v>169</v>
       </c>
       <c r="F28">
+        <v>2.12</v>
+      </c>
+      <c r="G28">
         <v>2.16</v>
       </c>
-      <c r="G28">
-        <v>2.18</v>
-      </c>
       <c r="H28">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J28">
         <v>3.45</v>
       </c>
       <c r="K28">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L28">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M28">
         <v>1.09</v>
       </c>
       <c r="N28">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O28">
         <v>1.41</v>
       </c>
       <c r="P28">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q28">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S28">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T28">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V28">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W28">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y28">
         <v>12.5</v>
@@ -7484,46 +7484,46 @@
         <v>27</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB28">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28">
         <v>7.8</v>
       </c>
       <c r="AD28">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE28">
         <v>55</v>
       </c>
       <c r="AF28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG28">
         <v>11</v>
       </c>
       <c r="AH28">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI28">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL28">
         <v>46</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO28">
         <v>65</v>
@@ -7532,13 +7532,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR28">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS28">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT28">
         <v>7.8</v>
@@ -7547,46 +7547,46 @@
         <v>7</v>
       </c>
       <c r="AV28">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW28">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AX28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY28">
         <v>10</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA28">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB28">
+        <v>24</v>
+      </c>
+      <c r="BC28">
         <v>23</v>
       </c>
-      <c r="BC28">
-        <v>21</v>
-      </c>
       <c r="BD28">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE28">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="BF28">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG28">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BH28">
         <v>3.1</v>
       </c>
       <c r="BI28">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ28">
         <v>10.5</v>
@@ -7595,52 +7595,52 @@
         <v>9</v>
       </c>
       <c r="BL28">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM28">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BN28">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO28">
         <v>4.3</v>
       </c>
       <c r="BP28">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ28">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR28">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BS28">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT28">
         <v>7.2</v>
       </c>
       <c r="BU28">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV28">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BW28">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BX28">
         <v>60</v>
       </c>
       <c r="BY28">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BZ28">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA28">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB28" t="s">
         <v>173</v>
@@ -7663,13 +7663,13 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G29">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H29">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I29">
         <v>3.75</v>
@@ -7681,43 +7681,43 @@
         <v>3.9</v>
       </c>
       <c r="L29">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M29">
         <v>1.06</v>
       </c>
       <c r="N29">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O29">
         <v>1.28</v>
       </c>
       <c r="P29">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q29">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R29">
         <v>1.42</v>
       </c>
       <c r="S29">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T29">
         <v>1.7</v>
       </c>
       <c r="U29">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V29">
         <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X29">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y29">
         <v>15.5</v>
@@ -7735,7 +7735,7 @@
         <v>8.6</v>
       </c>
       <c r="AD29">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE29">
         <v>50</v>
@@ -7744,16 +7744,16 @@
         <v>15</v>
       </c>
       <c r="AG29">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH29">
         <v>17.5</v>
       </c>
       <c r="AI29">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK29">
         <v>24</v>
@@ -7765,10 +7765,10 @@
         <v>95</v>
       </c>
       <c r="AN29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO29">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP29">
         <v>14.5</v>
@@ -7777,10 +7777,10 @@
         <v>13</v>
       </c>
       <c r="AR29">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AS29">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT29">
         <v>9.6</v>
@@ -7792,37 +7792,37 @@
         <v>13</v>
       </c>
       <c r="AW29">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX29">
         <v>12.5</v>
       </c>
       <c r="AY29">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29">
         <v>14.5</v>
       </c>
       <c r="BA29">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB29">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC29">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BD29">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE29">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG29">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7938,10 +7938,10 @@
         <v>1.66</v>
       </c>
       <c r="Q30">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S30">
         <v>4.7</v>
@@ -7950,7 +7950,7 @@
         <v>2</v>
       </c>
       <c r="U30">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V30">
         <v>1.61</v>
@@ -7965,7 +7965,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z30">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA30">
         <v>46</v>
@@ -7980,13 +7980,13 @@
         <v>12.5</v>
       </c>
       <c r="AE30">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF30">
         <v>20</v>
       </c>
       <c r="AG30">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH30">
         <v>21</v>
@@ -8022,10 +8022,10 @@
         <v>13.5</v>
       </c>
       <c r="AS30">
+        <v>18.5</v>
+      </c>
+      <c r="AT30">
         <v>9</v>
-      </c>
-      <c r="AT30">
-        <v>9.199999999999999</v>
       </c>
       <c r="AU30">
         <v>6.6</v>
@@ -8037,25 +8037,25 @@
         <v>8.6</v>
       </c>
       <c r="AX30">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30">
         <v>12.5</v>
       </c>
       <c r="AZ30">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA30">
-        <v>9.6</v>
+        <v>25</v>
       </c>
       <c r="BB30">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BC30">
         <v>36</v>
       </c>
       <c r="BD30">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BE30">
         <v>10</v>
@@ -8070,37 +8070,37 @@
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BN30">
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BT30">
         <v>1000</v>
@@ -8112,19 +8112,19 @@
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="CB30" t="s">
         <v>173</v>
@@ -8147,13 +8147,13 @@
         <v>172</v>
       </c>
       <c r="F31">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G31">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H31">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I31">
         <v>4.6</v>
@@ -8162,7 +8162,7 @@
         <v>3.2</v>
       </c>
       <c r="K31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L31">
         <v>1.59</v>
@@ -8171,7 +8171,7 @@
         <v>1.13</v>
       </c>
       <c r="N31">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O31">
         <v>1.56</v>
@@ -8180,7 +8180,7 @@
         <v>1.57</v>
       </c>
       <c r="Q31">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
         <v>1.2</v>
@@ -8210,7 +8210,7 @@
         <v>34</v>
       </c>
       <c r="AA31">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB31">
         <v>6.8</v>
@@ -8231,19 +8231,19 @@
         <v>11.5</v>
       </c>
       <c r="AH31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI31">
         <v>110</v>
       </c>
       <c r="AJ31">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK31">
         <v>29</v>
       </c>
       <c r="AL31">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM31">
         <v>200</v>
@@ -8255,7 +8255,7 @@
         <v>130</v>
       </c>
       <c r="AP31">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ31">
         <v>10.5</v>
@@ -8264,22 +8264,22 @@
         <v>27</v>
       </c>
       <c r="AS31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT31">
         <v>6.2</v>
       </c>
       <c r="AU31">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV31">
         <v>17.5</v>
       </c>
       <c r="AW31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8288,10 +8288,10 @@
         <v>23</v>
       </c>
       <c r="BA31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC31">
         <v>26</v>
@@ -8300,70 +8300,70 @@
         <v>50</v>
       </c>
       <c r="BE31">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH31">
         <v>2.7</v>
       </c>
       <c r="BI31">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ31">
         <v>12</v>
       </c>
       <c r="BK31">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN31">
         <v>4.6</v>
       </c>
       <c r="BO31">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP31">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ31">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR31">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS31">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT31">
         <v>7.8</v>
       </c>
       <c r="BU31">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BV31">
         <v>48</v>
       </c>
       <c r="BW31">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ31">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="CA31">
         <v>12</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -523,7 +523,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-02 09:02:20</t>
+    <t>2026-10-02 11:19:20</t>
   </si>
 </sst>
 </file>
@@ -1117,13 +1117,13 @@
         <v>140</v>
       </c>
       <c r="F2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G2">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>6.2</v>
@@ -1138,28 +1138,28 @@
         <v>1.51</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
         <v>1.45</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q2">
         <v>2.36</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
         <v>4.7</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
         <v>1.75</v>
@@ -1171,172 +1171,172 @@
         <v>2.2</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AA2">
         <v>900</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AE2">
         <v>700</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>700</v>
       </c>
       <c r="AJ2">
-        <v>75</v>
+        <v>19.5</v>
       </c>
       <c r="AK2">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AM2">
         <v>580</v>
       </c>
       <c r="AN2">
+        <v>17</v>
+      </c>
+      <c r="AO2">
         <v>600</v>
       </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
       <c r="AP2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AS2">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AT2">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="CB2" t="s">
         <v>169</v>
@@ -1359,22 +1359,22 @@
         <v>141</v>
       </c>
       <c r="F3">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="G3">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="I3">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
         <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
         <v>1.4</v>
@@ -1401,52 +1401,52 @@
         <v>3.15</v>
       </c>
       <c r="T3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V3">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC3">
         <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
         <v>16</v>
       </c>
       <c r="AI3">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>210</v>
@@ -1461,124 +1461,124 @@
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AO3">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AP3">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="AT3">
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
+        <v>11.5</v>
+      </c>
+      <c r="AW3">
+        <v>23</v>
+      </c>
+      <c r="AX3">
+        <v>15</v>
+      </c>
+      <c r="AY3">
         <v>10.5</v>
       </c>
-      <c r="AW3">
+      <c r="AZ3">
+        <v>13.5</v>
+      </c>
+      <c r="BA3">
+        <v>27</v>
+      </c>
+      <c r="BB3">
+        <v>15.5</v>
+      </c>
+      <c r="BC3">
         <v>21</v>
-      </c>
-      <c r="AX3">
-        <v>17</v>
-      </c>
-      <c r="AY3">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3">
-        <v>12.5</v>
-      </c>
-      <c r="BA3">
-        <v>13.5</v>
-      </c>
-      <c r="BB3">
-        <v>7.6</v>
-      </c>
-      <c r="BC3">
-        <v>11.5</v>
       </c>
       <c r="BD3">
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="BG3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI3">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ3">
         <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>2.18</v>
+        <v>5.3</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.76</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
+        <v>5.7</v>
+      </c>
+      <c r="BO3">
+        <v>4.9</v>
+      </c>
+      <c r="BP3">
+        <v>18</v>
+      </c>
+      <c r="BQ3">
+        <v>7.2</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>8.4</v>
+      </c>
+      <c r="BT3">
         <v>6.4</v>
       </c>
-      <c r="BO3">
+      <c r="BU3">
         <v>5.2</v>
       </c>
-      <c r="BP3">
-        <v>22</v>
-      </c>
-      <c r="BQ3">
-        <v>2.52</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>2.6</v>
-      </c>
-      <c r="BT3">
-        <v>5.9</v>
-      </c>
-      <c r="BU3">
-        <v>4.8</v>
-      </c>
       <c r="BV3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BW3">
-        <v>2.46</v>
+        <v>7.8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>2.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>23</v>
       </c>
       <c r="CA3">
-        <v>2.52</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>169</v>
@@ -1601,154 +1601,154 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="H4">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="I4">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
         <v>3.05</v>
       </c>
       <c r="T4">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Z4">
+        <v>38</v>
+      </c>
+      <c r="AA4">
+        <v>110</v>
+      </c>
+      <c r="AB4">
+        <v>10.5</v>
+      </c>
+      <c r="AC4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>18.5</v>
+      </c>
+      <c r="AE4">
+        <v>60</v>
+      </c>
+      <c r="AF4">
+        <v>12.5</v>
+      </c>
+      <c r="AG4">
+        <v>10.5</v>
+      </c>
+      <c r="AH4">
+        <v>21</v>
+      </c>
+      <c r="AI4">
+        <v>60</v>
+      </c>
+      <c r="AJ4">
+        <v>21</v>
+      </c>
+      <c r="AK4">
+        <v>20</v>
+      </c>
+      <c r="AL4">
         <v>36</v>
       </c>
-      <c r="AA4">
-        <v>170</v>
-      </c>
-      <c r="AB4">
+      <c r="AM4">
+        <v>110</v>
+      </c>
+      <c r="AN4">
         <v>11</v>
       </c>
-      <c r="AC4">
-        <v>9.6</v>
-      </c>
-      <c r="AD4">
+      <c r="AO4">
+        <v>55</v>
+      </c>
+      <c r="AP4">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4">
+        <v>15.5</v>
+      </c>
+      <c r="AR4">
+        <v>30</v>
+      </c>
+      <c r="AS4">
+        <v>55</v>
+      </c>
+      <c r="AT4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU4">
+        <v>8.4</v>
+      </c>
+      <c r="AV4">
         <v>16.5</v>
       </c>
-      <c r="AE4">
-        <v>48</v>
-      </c>
-      <c r="AF4">
-        <v>15.5</v>
-      </c>
-      <c r="AG4">
-        <v>12.5</v>
-      </c>
-      <c r="AH4">
+      <c r="AW4">
+        <v>44</v>
+      </c>
+      <c r="AX4">
+        <v>10.5</v>
+      </c>
+      <c r="AY4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4">
+        <v>16</v>
+      </c>
+      <c r="BA4">
+        <v>46</v>
+      </c>
+      <c r="BB4">
         <v>18</v>
       </c>
-      <c r="AI4">
-        <v>50</v>
-      </c>
-      <c r="AJ4">
-        <v>27</v>
-      </c>
-      <c r="AK4">
-        <v>21</v>
-      </c>
-      <c r="AL4">
-        <v>34</v>
-      </c>
-      <c r="AM4">
-        <v>200</v>
-      </c>
-      <c r="AN4">
-        <v>13.5</v>
-      </c>
-      <c r="AO4">
-        <v>40</v>
-      </c>
-      <c r="AP4">
+      <c r="BC4">
         <v>15</v>
-      </c>
-      <c r="AQ4">
-        <v>14.5</v>
-      </c>
-      <c r="AR4">
-        <v>25</v>
-      </c>
-      <c r="AS4">
-        <v>32</v>
-      </c>
-      <c r="AT4">
-        <v>10</v>
-      </c>
-      <c r="AU4">
-        <v>7.6</v>
-      </c>
-      <c r="AV4">
-        <v>14</v>
-      </c>
-      <c r="AW4">
-        <v>34</v>
-      </c>
-      <c r="AX4">
-        <v>12</v>
-      </c>
-      <c r="AY4">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4">
-        <v>15</v>
-      </c>
-      <c r="BA4">
-        <v>40</v>
-      </c>
-      <c r="BB4">
-        <v>20</v>
-      </c>
-      <c r="BC4">
-        <v>17.5</v>
       </c>
       <c r="BD4">
         <v>26</v>
@@ -1757,19 +1757,19 @@
         <v>55</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG4">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
         <v>7.2</v>
@@ -1778,25 +1778,25 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BN4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BT4">
         <v>8.199999999999999</v>
@@ -1805,22 +1805,22 @@
         <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BW4">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
+        <v>6.2</v>
+      </c>
+      <c r="BZ4">
+        <v>21</v>
+      </c>
+      <c r="CA4">
         <v>5.4</v>
-      </c>
-      <c r="BZ4">
-        <v>25</v>
-      </c>
-      <c r="CA4">
-        <v>4.9</v>
       </c>
       <c r="CB4" t="s">
         <v>169</v>
@@ -1843,61 +1843,61 @@
         <v>143</v>
       </c>
       <c r="F5">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G5">
         <v>3.05</v>
       </c>
       <c r="H5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I5">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S5">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T5">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U5">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="W5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y5">
         <v>14</v>
@@ -1909,31 +1909,31 @@
         <v>38</v>
       </c>
       <c r="AB5">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
+        <v>13</v>
+      </c>
+      <c r="AE5">
+        <v>26</v>
+      </c>
+      <c r="AF5">
+        <v>23</v>
+      </c>
+      <c r="AG5">
         <v>14</v>
       </c>
-      <c r="AE5">
-        <v>27</v>
-      </c>
-      <c r="AF5">
-        <v>25</v>
-      </c>
-      <c r="AG5">
-        <v>15</v>
-      </c>
       <c r="AH5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI5">
         <v>36</v>
       </c>
       <c r="AJ5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK5">
         <v>30</v>
@@ -1942,64 +1942,64 @@
         <v>38</v>
       </c>
       <c r="AM5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN5">
         <v>22</v>
       </c>
       <c r="AO5">
+        <v>17</v>
+      </c>
+      <c r="AP5">
+        <v>17</v>
+      </c>
+      <c r="AQ5">
+        <v>11.5</v>
+      </c>
+      <c r="AR5">
+        <v>16</v>
+      </c>
+      <c r="AS5">
+        <v>17</v>
+      </c>
+      <c r="AT5">
+        <v>12.5</v>
+      </c>
+      <c r="AU5">
+        <v>7.8</v>
+      </c>
+      <c r="AV5">
+        <v>10</v>
+      </c>
+      <c r="AW5">
+        <v>21</v>
+      </c>
+      <c r="AX5">
         <v>18</v>
-      </c>
-      <c r="AP5">
-        <v>15</v>
-      </c>
-      <c r="AQ5">
-        <v>11</v>
-      </c>
-      <c r="AR5">
-        <v>15.5</v>
-      </c>
-      <c r="AS5">
-        <v>6.2</v>
-      </c>
-      <c r="AT5">
-        <v>12</v>
-      </c>
-      <c r="AU5">
-        <v>7.2</v>
-      </c>
-      <c r="AV5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5">
-        <v>20</v>
-      </c>
-      <c r="AX5">
-        <v>17</v>
       </c>
       <c r="AY5">
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA5">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BB5">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD5">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG5">
         <v>13.5</v>
@@ -2008,61 +2008,61 @@
         <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
         <v>10</v>
       </c>
       <c r="BK5">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BL5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BN5">
         <v>7.2</v>
       </c>
       <c r="BO5">
+        <v>5.4</v>
+      </c>
+      <c r="BP5">
+        <v>23</v>
+      </c>
+      <c r="BQ5">
+        <v>4.6</v>
+      </c>
+      <c r="BR5">
+        <v>32</v>
+      </c>
+      <c r="BS5">
         <v>4.9</v>
-      </c>
-      <c r="BP5">
-        <v>24</v>
-      </c>
-      <c r="BQ5">
-        <v>4.4</v>
-      </c>
-      <c r="BR5">
-        <v>34</v>
-      </c>
-      <c r="BS5">
-        <v>4.6</v>
       </c>
       <c r="BT5">
         <v>6.6</v>
       </c>
       <c r="BU5">
+        <v>5</v>
+      </c>
+      <c r="BV5">
+        <v>20</v>
+      </c>
+      <c r="BW5">
+        <v>4.5</v>
+      </c>
+      <c r="BX5">
+        <v>27</v>
+      </c>
+      <c r="BY5">
+        <v>4.8</v>
+      </c>
+      <c r="BZ5">
+        <v>22</v>
+      </c>
+      <c r="CA5">
         <v>4.6</v>
-      </c>
-      <c r="BV5">
-        <v>21</v>
-      </c>
-      <c r="BW5">
-        <v>4.3</v>
-      </c>
-      <c r="BX5">
-        <v>32</v>
-      </c>
-      <c r="BY5">
-        <v>4.6</v>
-      </c>
-      <c r="BZ5">
-        <v>23</v>
-      </c>
-      <c r="CA5">
-        <v>4.3</v>
       </c>
       <c r="CB5" t="s">
         <v>169</v>
@@ -2106,7 +2106,7 @@
         <v>1.19</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -2115,22 +2115,22 @@
         <v>1.09</v>
       </c>
       <c r="P6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S6">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="T6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U6">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="V6">
         <v>1.42</v>
@@ -2142,7 +2142,7 @@
         <v>60</v>
       </c>
       <c r="Y6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z6">
         <v>44</v>
@@ -2151,31 +2151,31 @@
         <v>70</v>
       </c>
       <c r="AB6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AC6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE6">
         <v>34</v>
       </c>
       <c r="AF6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH6">
         <v>14</v>
       </c>
       <c r="AI6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK6">
         <v>18</v>
@@ -2196,7 +2196,7 @@
         <v>42</v>
       </c>
       <c r="AQ6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR6">
         <v>32</v>
@@ -2205,7 +2205,7 @@
         <v>48</v>
       </c>
       <c r="AT6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU6">
         <v>12</v>
@@ -2241,16 +2241,16 @@
         <v>30</v>
       </c>
       <c r="BF6">
+        <v>5.6</v>
+      </c>
+      <c r="BG6">
+        <v>10.5</v>
+      </c>
+      <c r="BH6">
+        <v>7.4</v>
+      </c>
+      <c r="BI6">
         <v>5.7</v>
-      </c>
-      <c r="BG6">
-        <v>11</v>
-      </c>
-      <c r="BH6">
-        <v>7.2</v>
-      </c>
-      <c r="BI6">
-        <v>5.6</v>
       </c>
       <c r="BJ6">
         <v>9.4</v>
@@ -2259,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="BL6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BM6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BN6">
         <v>7.2</v>
@@ -2274,13 +2274,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ6">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="BR6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BS6">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BT6">
         <v>9</v>
@@ -2292,19 +2292,19 @@
         <v>23</v>
       </c>
       <c r="BW6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
         <v>24</v>
       </c>
       <c r="BY6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BZ6">
         <v>8.800000000000001</v>
       </c>
       <c r="CA6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="s">
         <v>169</v>
@@ -2327,28 +2327,28 @@
         <v>145</v>
       </c>
       <c r="F7">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G7">
         <v>2.5</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>1.36</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
         <v>4.2</v>
@@ -2357,13 +2357,13 @@
         <v>1.28</v>
       </c>
       <c r="P7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S7">
         <v>3.1</v>
@@ -2372,7 +2372,7 @@
         <v>1.66</v>
       </c>
       <c r="U7">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V7">
         <v>1.47</v>
@@ -2393,13 +2393,13 @@
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="AD7">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE7">
         <v>500</v>
@@ -2435,58 +2435,58 @@
         <v>600</v>
       </c>
       <c r="AP7">
-        <v>1.32</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>1.32</v>
+        <v>16</v>
       </c>
       <c r="AT7">
-        <v>1.29</v>
+        <v>8.4</v>
       </c>
       <c r="AU7">
         <v>5.1</v>
       </c>
       <c r="AV7">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="AW7">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AX7">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="AY7">
-        <v>1.29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA7">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="BB7">
-        <v>1.31</v>
+        <v>13</v>
       </c>
       <c r="BC7">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="BD7">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="BE7">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="BF7">
-        <v>1.55</v>
+        <v>11.5</v>
       </c>
       <c r="BG7">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2569,13 +2569,13 @@
         <v>146</v>
       </c>
       <c r="F8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I8">
         <v>2.22</v>
@@ -2584,10 +2584,10 @@
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2602,16 +2602,16 @@
         <v>2.32</v>
       </c>
       <c r="Q8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R8">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S8">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U8">
         <v>2.36</v>
@@ -2629,28 +2629,28 @@
         <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA8">
         <v>32</v>
       </c>
       <c r="AB8">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AC8">
         <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF8">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AG8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH8">
         <v>18.5</v>
@@ -2659,25 +2659,25 @@
         <v>95</v>
       </c>
       <c r="AJ8">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AK8">
         <v>250</v>
       </c>
       <c r="AL8">
-        <v>46</v>
+        <v>330</v>
       </c>
       <c r="AM8">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN8">
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="AO8">
         <v>13</v>
       </c>
       <c r="AP8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
@@ -2686,10 +2686,10 @@
         <v>13</v>
       </c>
       <c r="AS8">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AT8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU8">
         <v>7.8</v>
@@ -2698,13 +2698,13 @@
         <v>9.4</v>
       </c>
       <c r="AW8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX8">
         <v>20</v>
       </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
         <v>13</v>
@@ -2713,19 +2713,19 @@
         <v>12</v>
       </c>
       <c r="BB8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC8">
-        <v>5.6</v>
+        <v>27</v>
       </c>
       <c r="BD8">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE8">
+        <v>6.4</v>
+      </c>
+      <c r="BF8">
         <v>6</v>
-      </c>
-      <c r="BF8">
-        <v>5.5</v>
       </c>
       <c r="BG8">
         <v>10</v>
@@ -2752,7 +2752,7 @@
         <v>8</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BP8">
         <v>29</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="BU8">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV8">
         <v>16.5</v>
@@ -2814,19 +2814,19 @@
         <v>1.42</v>
       </c>
       <c r="G9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K9">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L9">
         <v>1.26</v>
@@ -2835,34 +2835,34 @@
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P9">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q9">
         <v>1.51</v>
       </c>
       <c r="R9">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X9">
         <v>29</v>
@@ -2877,16 +2877,16 @@
         <v>260</v>
       </c>
       <c r="AB9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC9">
         <v>13.5</v>
       </c>
       <c r="AD9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AF9">
         <v>11</v>
@@ -2895,28 +2895,28 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI9">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK9">
         <v>14</v>
       </c>
       <c r="AL9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9">
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP9">
         <v>22</v>
@@ -2931,31 +2931,31 @@
         <v>11.5</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU9">
         <v>11.5</v>
       </c>
       <c r="AV9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA9">
         <v>42</v>
       </c>
       <c r="BB9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC9">
         <v>12</v>
@@ -2964,25 +2964,25 @@
         <v>23</v>
       </c>
       <c r="BE9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH9">
         <v>4.8</v>
       </c>
       <c r="BI9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2994,16 +2994,16 @@
         <v>4.4</v>
       </c>
       <c r="BO9">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP9">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS9">
         <v>7.4</v>
@@ -3012,25 +3012,25 @@
         <v>11.5</v>
       </c>
       <c r="BU9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
+        <v>10</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>9.6</v>
       </c>
       <c r="BZ9">
         <v>11.5</v>
       </c>
       <c r="CA9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB9" t="s">
         <v>169</v>
@@ -3053,22 +3053,22 @@
         <v>148</v>
       </c>
       <c r="F10">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="I10">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J10">
         <v>2.58</v>
       </c>
       <c r="K10">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="L10">
         <v>1.7</v>
@@ -3077,16 +3077,16 @@
         <v>1.17</v>
       </c>
       <c r="N10">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O10">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P10">
         <v>1.46</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R10">
         <v>1.17</v>
@@ -3095,19 +3095,19 @@
         <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U10">
         <v>1.7</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="X10">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="Y10">
         <v>500</v>
@@ -3119,10 +3119,10 @@
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AC10">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>970</v>
@@ -3161,70 +3161,70 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AQ10">
         <v>3.85</v>
       </c>
       <c r="AR10">
-        <v>2.12</v>
+        <v>8.4</v>
       </c>
       <c r="AS10">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="AT10">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AU10">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="AV10">
         <v>6.6</v>
       </c>
       <c r="AW10">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AX10">
-        <v>2.06</v>
+        <v>9</v>
       </c>
       <c r="AY10">
         <v>5.5</v>
       </c>
       <c r="AZ10">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="BA10">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="BB10">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BC10">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BD10">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="BE10">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="BF10">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BG10">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3236,7 +3236,7 @@
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BP10">
         <v>1000</v>
@@ -3254,7 +3254,7 @@
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3301,7 +3301,7 @@
         <v>2.74</v>
       </c>
       <c r="H11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I11">
         <v>3.25</v>
@@ -3325,16 +3325,16 @@
         <v>1.53</v>
       </c>
       <c r="P11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R11">
         <v>1.21</v>
       </c>
       <c r="S11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T11">
         <v>2.1</v>
@@ -3352,7 +3352,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z11">
         <v>19</v>
@@ -3361,7 +3361,7 @@
         <v>60</v>
       </c>
       <c r="AB11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>7</v>
@@ -3382,7 +3382,7 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ11">
         <v>44</v>
@@ -3412,10 +3412,10 @@
         <v>17.5</v>
       </c>
       <c r="AS11">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
@@ -3436,7 +3436,7 @@
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB11">
         <v>38</v>
@@ -3448,16 +3448,16 @@
         <v>55</v>
       </c>
       <c r="BE11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG11">
         <v>50</v>
       </c>
       <c r="BH11">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI11">
         <v>2.58</v>
@@ -3472,7 +3472,7 @@
         <v>220</v>
       </c>
       <c r="BM11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN11">
         <v>5.3</v>
@@ -3484,13 +3484,13 @@
         <v>24</v>
       </c>
       <c r="BQ11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR11">
         <v>46</v>
       </c>
       <c r="BS11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT11">
         <v>6.2</v>
@@ -3508,13 +3508,13 @@
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11">
         <v>48</v>
       </c>
       <c r="CA11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="s">
         <v>169</v>
@@ -3537,22 +3537,22 @@
         <v>150</v>
       </c>
       <c r="F12">
+        <v>4.6</v>
+      </c>
+      <c r="G12">
+        <v>4.8</v>
+      </c>
+      <c r="H12">
+        <v>1.76</v>
+      </c>
+      <c r="I12">
+        <v>1.78</v>
+      </c>
+      <c r="J12">
+        <v>4.4</v>
+      </c>
+      <c r="K12">
         <v>4.5</v>
-      </c>
-      <c r="G12">
-        <v>4.6</v>
-      </c>
-      <c r="H12">
-        <v>1.81</v>
-      </c>
-      <c r="I12">
-        <v>1.83</v>
-      </c>
-      <c r="J12">
-        <v>4.3</v>
-      </c>
-      <c r="K12">
-        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.28</v>
@@ -3567,37 +3567,37 @@
         <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q12">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R12">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U12">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="W12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA12">
         <v>20</v>
@@ -3606,61 +3606,61 @@
         <v>25</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
         <v>10</v>
       </c>
       <c r="AE12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG12">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
         <v>26</v>
       </c>
       <c r="AJ12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK12">
+        <v>50</v>
+      </c>
+      <c r="AL12">
         <v>46</v>
-      </c>
-      <c r="AL12">
-        <v>44</v>
       </c>
       <c r="AM12">
         <v>60</v>
       </c>
       <c r="AN12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO12">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ12">
         <v>12.5</v>
       </c>
       <c r="AR12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT12">
         <v>23</v>
       </c>
       <c r="AU12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12">
         <v>9.6</v>
@@ -3669,43 +3669,43 @@
         <v>14.5</v>
       </c>
       <c r="AX12">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AY12">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ12">
         <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB12">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BC12">
+        <v>42</v>
+      </c>
+      <c r="BD12">
         <v>40</v>
-      </c>
-      <c r="BD12">
-        <v>38</v>
       </c>
       <c r="BE12">
         <v>50</v>
       </c>
       <c r="BF12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BI12">
         <v>4.2</v>
       </c>
       <c r="BJ12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK12">
         <v>7.8</v>
@@ -3714,49 +3714,49 @@
         <v>75</v>
       </c>
       <c r="BM12">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN12">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BO12">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BP12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR12">
         <v>34</v>
       </c>
       <c r="BS12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU12">
         <v>4.4</v>
       </c>
       <c r="BV12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY12">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB12" t="s">
         <v>169</v>
@@ -3791,7 +3791,7 @@
         <v>4.2</v>
       </c>
       <c r="J13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
         <v>4.1</v>
@@ -3803,7 +3803,7 @@
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
         <v>1.26</v>
@@ -3812,7 +3812,7 @@
         <v>2.2</v>
       </c>
       <c r="Q13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R13">
         <v>1.47</v>
@@ -3824,7 +3824,7 @@
         <v>1.68</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V13">
         <v>1.31</v>
@@ -3833,7 +3833,7 @@
         <v>2</v>
       </c>
       <c r="X13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y13">
         <v>18.5</v>
@@ -3842,22 +3842,22 @@
         <v>38</v>
       </c>
       <c r="AA13">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="AB13">
         <v>11</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE13">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="AF13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG13">
         <v>10.5</v>
@@ -3866,34 +3866,34 @@
         <v>18</v>
       </c>
       <c r="AI13">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="AJ13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN13">
         <v>11.5</v>
       </c>
       <c r="AO13">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AP13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ13">
         <v>15</v>
       </c>
       <c r="AR13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS13">
         <v>55</v>
@@ -3902,16 +3902,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW13">
         <v>32</v>
       </c>
       <c r="AX13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY13">
         <v>9.199999999999999</v>
@@ -3926,7 +3926,7 @@
         <v>20</v>
       </c>
       <c r="BC13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD13">
         <v>24</v>
@@ -4021,19 +4021,19 @@
         <v>152</v>
       </c>
       <c r="F14">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="G14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H14">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="I14">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="J14">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -4045,34 +4045,34 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O14">
         <v>1.2</v>
       </c>
       <c r="P14">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q14">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R14">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S14">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T14">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U14">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V14">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W14">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X14">
         <v>24</v>
@@ -4081,16 +4081,16 @@
         <v>15.5</v>
       </c>
       <c r="Z14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB14">
         <v>18</v>
       </c>
       <c r="AC14">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD14">
         <v>12</v>
@@ -4102,46 +4102,46 @@
         <v>25</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ14">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL14">
         <v>34</v>
       </c>
       <c r="AM14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN14">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO14">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP14">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AQ14">
         <v>13.5</v>
       </c>
       <c r="AR14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AT14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU14">
         <v>8.6</v>
@@ -4150,13 +4150,13 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
+        <v>19</v>
+      </c>
+      <c r="AX14">
         <v>20</v>
       </c>
-      <c r="AX14">
-        <v>21</v>
-      </c>
       <c r="AY14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14">
         <v>13</v>
@@ -4165,28 +4165,28 @@
         <v>25</v>
       </c>
       <c r="BB14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BC14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD14">
         <v>28</v>
       </c>
       <c r="BE14">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BF14">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG14">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH14">
         <v>4.9</v>
       </c>
       <c r="BI14">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ14">
         <v>8.800000000000001</v>
@@ -4198,49 +4198,49 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO14">
         <v>5.7</v>
       </c>
       <c r="BP14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ14">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR14">
         <v>30</v>
       </c>
       <c r="BS14">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT14">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU14">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV14">
         <v>16.5</v>
       </c>
       <c r="BW14">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BX14">
         <v>27</v>
       </c>
       <c r="BY14">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA14">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="CB14" t="s">
         <v>169</v>
@@ -4263,16 +4263,16 @@
         <v>153</v>
       </c>
       <c r="F15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G15">
         <v>3.25</v>
       </c>
       <c r="H15">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I15">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J15">
         <v>4.1</v>
@@ -4287,7 +4287,7 @@
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O15">
         <v>1.22</v>
@@ -4299,25 +4299,25 @@
         <v>1.68</v>
       </c>
       <c r="R15">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S15">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T15">
         <v>1.61</v>
       </c>
       <c r="U15">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W15">
         <v>1.44</v>
       </c>
       <c r="X15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y15">
         <v>14</v>
@@ -4326,34 +4326,34 @@
         <v>17.5</v>
       </c>
       <c r="AA15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE15">
         <v>22</v>
       </c>
       <c r="AF15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15">
         <v>14.5</v>
       </c>
       <c r="AH15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK15">
         <v>34</v>
@@ -4365,13 +4365,13 @@
         <v>75</v>
       </c>
       <c r="AN15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ15">
         <v>11.5</v>
@@ -4380,7 +4380,7 @@
         <v>14</v>
       </c>
       <c r="AS15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT15">
         <v>14</v>
@@ -4392,25 +4392,25 @@
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA15">
         <v>23</v>
       </c>
       <c r="BB15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD15">
         <v>28</v>
@@ -4419,7 +4419,7 @@
         <v>55</v>
       </c>
       <c r="BF15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG15">
         <v>11</v>
@@ -4508,13 +4508,13 @@
         <v>1.68</v>
       </c>
       <c r="G16">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I16">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J16">
         <v>4.5</v>
@@ -4529,34 +4529,34 @@
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O16">
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q16">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R16">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S16">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="T16">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V16">
         <v>1.23</v>
       </c>
       <c r="W16">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X16">
         <v>26</v>
@@ -4574,10 +4574,10 @@
         <v>12.5</v>
       </c>
       <c r="AC16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE16">
         <v>60</v>
@@ -4589,7 +4589,7 @@
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI16">
         <v>55</v>
@@ -4601,19 +4601,19 @@
         <v>16.5</v>
       </c>
       <c r="AL16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM16">
         <v>80</v>
       </c>
       <c r="AN16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO16">
         <v>46</v>
       </c>
       <c r="AP16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ16">
         <v>21</v>
@@ -4622,7 +4622,7 @@
         <v>38</v>
       </c>
       <c r="AS16">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AT16">
         <v>11</v>
@@ -4646,10 +4646,10 @@
         <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB16">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC16">
         <v>14</v>
@@ -4661,13 +4661,13 @@
         <v>55</v>
       </c>
       <c r="BF16">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG16">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI16">
         <v>4</v>
@@ -4700,7 +4700,7 @@
         <v>25</v>
       </c>
       <c r="BS16">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BT16">
         <v>10.5</v>
@@ -4709,19 +4709,19 @@
         <v>7.8</v>
       </c>
       <c r="BV16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW16">
         <v>4.4</v>
       </c>
       <c r="BX16">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BY16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA16">
         <v>4.2</v>
@@ -4747,226 +4747,226 @@
         <v>155</v>
       </c>
       <c r="F17">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="G17">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="H17">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="I17">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="J17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L17">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M17">
         <v>1.07</v>
       </c>
       <c r="N17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P17">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q17">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R17">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T17">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U17">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V17">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="W17">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X17">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y17">
         <v>10.5</v>
       </c>
       <c r="Z17">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA17">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AB17">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC17">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD17">
         <v>10.5</v>
       </c>
       <c r="AE17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF17">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AG17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH17">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI17">
         <v>44</v>
       </c>
       <c r="AJ17">
+        <v>160</v>
+      </c>
+      <c r="AK17">
+        <v>65</v>
+      </c>
+      <c r="AL17">
+        <v>60</v>
+      </c>
+      <c r="AM17">
         <v>200</v>
       </c>
-      <c r="AK17">
-        <v>60</v>
-      </c>
-      <c r="AL17">
-        <v>65</v>
-      </c>
-      <c r="AM17">
-        <v>500</v>
-      </c>
       <c r="AN17">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO17">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AP17">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR17">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS17">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT17">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AU17">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV17">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW17">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX17">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AY17">
+        <v>13.5</v>
+      </c>
+      <c r="AZ17">
         <v>15</v>
-      </c>
-      <c r="AZ17">
-        <v>15.5</v>
       </c>
       <c r="BA17">
         <v>16</v>
       </c>
       <c r="BB17">
+        <v>9.6</v>
+      </c>
+      <c r="BC17">
         <v>32</v>
-      </c>
-      <c r="BC17">
-        <v>40</v>
       </c>
       <c r="BD17">
         <v>38</v>
       </c>
       <c r="BE17">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BF17">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="BG17">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI17">
-        <v>1.05</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK17">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO17">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ17">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS17">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU17">
-        <v>1.38</v>
+        <v>4.4</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW17">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY17">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA17">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="CB17" t="s">
         <v>169</v>
@@ -4989,22 +4989,22 @@
         <v>156</v>
       </c>
       <c r="F18">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G18">
         <v>3.1</v>
       </c>
       <c r="H18">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I18">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
         <v>1.29</v>
@@ -5013,13 +5013,13 @@
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O18">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P18">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q18">
         <v>1.58</v>
@@ -5031,25 +5031,25 @@
         <v>2.48</v>
       </c>
       <c r="T18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U18">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V18">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W18">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y18">
         <v>17</v>
       </c>
       <c r="Z18">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA18">
         <v>34</v>
@@ -5091,16 +5091,16 @@
         <v>60</v>
       </c>
       <c r="AN18">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO18">
         <v>13</v>
       </c>
       <c r="AP18">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR18">
         <v>16.5</v>
@@ -5136,7 +5136,7 @@
         <v>40</v>
       </c>
       <c r="BC18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD18">
         <v>28</v>
@@ -5231,226 +5231,226 @@
         <v>157</v>
       </c>
       <c r="F19">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="G19">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="H19">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="I19">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="J19">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="K19">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="L19">
         <v>1.25</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="O19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P19">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="Q19">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R19">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="S19">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="T19">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U19">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="V19">
-        <v>3.55</v>
+        <v>2.84</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Y19">
         <v>14</v>
       </c>
       <c r="Z19">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AA19">
+        <v>15.5</v>
+      </c>
+      <c r="AB19">
+        <v>32</v>
+      </c>
+      <c r="AC19">
         <v>12.5</v>
       </c>
-      <c r="AB19">
-        <v>44</v>
-      </c>
-      <c r="AC19">
+      <c r="AD19">
+        <v>10.5</v>
+      </c>
+      <c r="AE19">
         <v>14.5</v>
       </c>
-      <c r="AD19">
-        <v>11</v>
-      </c>
-      <c r="AE19">
-        <v>13.5</v>
-      </c>
       <c r="AF19">
+        <v>60</v>
+      </c>
+      <c r="AG19">
+        <v>24</v>
+      </c>
+      <c r="AH19">
+        <v>19</v>
+      </c>
+      <c r="AI19">
+        <v>26</v>
+      </c>
+      <c r="AJ19">
         <v>170</v>
       </c>
-      <c r="AG19">
-        <v>32</v>
-      </c>
-      <c r="AH19">
-        <v>23</v>
-      </c>
-      <c r="AI19">
-        <v>28</v>
-      </c>
-      <c r="AJ19">
-        <v>250</v>
-      </c>
       <c r="AK19">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AL19">
         <v>170</v>
       </c>
       <c r="AM19">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AN19">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AO19">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AP19">
         <v>27</v>
       </c>
       <c r="AQ19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS19">
+        <v>14</v>
+      </c>
+      <c r="AT19">
+        <v>29</v>
+      </c>
+      <c r="AU19">
         <v>11</v>
       </c>
-      <c r="AT19">
-        <v>32</v>
-      </c>
-      <c r="AU19">
+      <c r="AV19">
+        <v>9.4</v>
+      </c>
+      <c r="AW19">
         <v>12.5</v>
       </c>
-      <c r="AV19">
-        <v>9.6</v>
-      </c>
-      <c r="AW19">
-        <v>12</v>
-      </c>
       <c r="AX19">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AY19">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ19">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC19">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="BD19">
+        <v>48</v>
+      </c>
+      <c r="BE19">
         <v>36</v>
       </c>
-      <c r="BE19">
-        <v>22</v>
-      </c>
       <c r="BF19">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BG19">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH19">
         <v>5</v>
       </c>
       <c r="BI19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ19">
+        <v>9.6</v>
+      </c>
+      <c r="BK19">
+        <v>7.4</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>12</v>
+      </c>
+      <c r="BN19">
         <v>10.5</v>
       </c>
-      <c r="BK19">
+      <c r="BO19">
         <v>7.8</v>
       </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
+      <c r="BP19">
+        <v>42</v>
+      </c>
+      <c r="BQ19">
+        <v>10.5</v>
+      </c>
+      <c r="BR19">
+        <v>40</v>
+      </c>
+      <c r="BS19">
+        <v>10.5</v>
+      </c>
+      <c r="BT19">
+        <v>4.6</v>
+      </c>
+      <c r="BU19">
+        <v>4.1</v>
+      </c>
+      <c r="BV19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BW19">
+        <v>7.2</v>
+      </c>
+      <c r="BX19">
+        <v>18.5</v>
+      </c>
+      <c r="BY19">
         <v>14</v>
       </c>
-      <c r="BN19">
-        <v>12.5</v>
-      </c>
-      <c r="BO19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BP19">
-        <v>65</v>
-      </c>
-      <c r="BQ19">
-        <v>13</v>
-      </c>
-      <c r="BR19">
-        <v>55</v>
-      </c>
-      <c r="BS19">
-        <v>12.5</v>
-      </c>
-      <c r="BT19">
-        <v>4.3</v>
-      </c>
-      <c r="BU19">
-        <v>3.85</v>
-      </c>
-      <c r="BV19">
-        <v>7.8</v>
-      </c>
-      <c r="BW19">
-        <v>6.2</v>
-      </c>
-      <c r="BX19">
-        <v>19</v>
-      </c>
-      <c r="BY19">
+      <c r="BZ19">
+        <v>11</v>
+      </c>
+      <c r="CA19">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BZ19">
-        <v>9.4</v>
-      </c>
-      <c r="CA19">
-        <v>7.8</v>
       </c>
       <c r="CB19" t="s">
         <v>169</v>
@@ -5473,226 +5473,226 @@
         <v>158</v>
       </c>
       <c r="F20">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="H20">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="I20">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J20">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K20">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L20">
+        <v>1.59</v>
+      </c>
+      <c r="M20">
+        <v>1.13</v>
+      </c>
+      <c r="N20">
+        <v>2.62</v>
+      </c>
+      <c r="O20">
         <v>1.56</v>
       </c>
-      <c r="M20">
-        <v>1.12</v>
-      </c>
-      <c r="N20">
+      <c r="P20">
+        <v>1.53</v>
+      </c>
+      <c r="Q20">
         <v>2.74</v>
       </c>
-      <c r="O20">
-        <v>1.53</v>
-      </c>
-      <c r="P20">
-        <v>1.58</v>
-      </c>
-      <c r="Q20">
-        <v>2.62</v>
-      </c>
       <c r="R20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S20">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T20">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U20">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V20">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="X20">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y20">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z20">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AA20">
         <v>900</v>
       </c>
       <c r="AB20">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD20">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AE20">
         <v>700</v>
       </c>
       <c r="AF20">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AG20">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AI20">
         <v>700</v>
       </c>
       <c r="AJ20">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AK20">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AL20">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AM20">
         <v>500</v>
       </c>
       <c r="AN20">
+        <v>44</v>
+      </c>
+      <c r="AO20">
+        <v>160</v>
+      </c>
+      <c r="AP20">
+        <v>7.4</v>
+      </c>
+      <c r="AQ20">
+        <v>9.4</v>
+      </c>
+      <c r="AR20">
         <v>22</v>
       </c>
-      <c r="AO20">
-        <v>270</v>
-      </c>
-      <c r="AP20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ20">
-        <v>12</v>
-      </c>
-      <c r="AR20">
-        <v>36</v>
-      </c>
       <c r="AS20">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AT20">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV20">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AW20">
+        <v>46</v>
+      </c>
+      <c r="AX20">
+        <v>10</v>
+      </c>
+      <c r="AY20">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20">
+        <v>21</v>
+      </c>
+      <c r="BA20">
         <v>55</v>
       </c>
-      <c r="AX20">
-        <v>8.6</v>
-      </c>
-      <c r="AY20">
-        <v>9.6</v>
-      </c>
-      <c r="AZ20">
-        <v>22</v>
-      </c>
-      <c r="BA20">
-        <v>70</v>
-      </c>
       <c r="BB20">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC20">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BD20">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE20">
         <v>65</v>
       </c>
       <c r="BF20">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BG20">
+        <v>80</v>
+      </c>
+      <c r="BH20">
+        <v>2.74</v>
+      </c>
+      <c r="BI20">
+        <v>2.44</v>
+      </c>
+      <c r="BJ20">
+        <v>12</v>
+      </c>
+      <c r="BK20">
+        <v>6.2</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>12.5</v>
+      </c>
+      <c r="BN20">
+        <v>4.8</v>
+      </c>
+      <c r="BO20">
+        <v>4</v>
+      </c>
+      <c r="BP20">
+        <v>19</v>
+      </c>
+      <c r="BQ20">
+        <v>7.8</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>10</v>
+      </c>
+      <c r="BT20">
+        <v>7.6</v>
+      </c>
+      <c r="BU20">
+        <v>5.6</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>10</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
         <v>11</v>
       </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.01</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.01</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.01</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.01</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.01</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.01</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.01</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.01</v>
-      </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="s">
         <v>169</v>
@@ -5715,19 +5715,19 @@
         <v>159</v>
       </c>
       <c r="F21">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="G21">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H21">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="I21">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="J21">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <v>4.3</v>
@@ -5742,43 +5742,43 @@
         <v>3.7</v>
       </c>
       <c r="O21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P21">
         <v>1.92</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R21">
         <v>1.34</v>
       </c>
       <c r="S21">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T21">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U21">
         <v>1.87</v>
       </c>
       <c r="V21">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X21">
         <v>17.5</v>
       </c>
       <c r="Y21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB21">
         <v>25</v>
@@ -5823,10 +5823,10 @@
         <v>11</v>
       </c>
       <c r="AP21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ21">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR21">
         <v>8.199999999999999</v>
@@ -5847,7 +5847,7 @@
         <v>15.5</v>
       </c>
       <c r="AX21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY21">
         <v>21</v>
@@ -5856,16 +5856,16 @@
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB21">
         <v>5.6</v>
       </c>
       <c r="BC21">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD21">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE21">
         <v>5.5</v>
@@ -5874,67 +5874,67 @@
         <v>5.5</v>
       </c>
       <c r="BG21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB21" t="s">
         <v>169</v>
@@ -5957,40 +5957,40 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G22">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H22">
         <v>3.15</v>
       </c>
       <c r="I22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J22">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K22">
         <v>3.05</v>
       </c>
       <c r="L22">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M22">
         <v>1.15</v>
       </c>
       <c r="N22">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O22">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P22">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q22">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
         <v>1.17</v>
@@ -6005,16 +6005,16 @@
         <v>1.72</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X22">
         <v>9.199999999999999</v>
       </c>
       <c r="Y22">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z22">
         <v>21</v>
@@ -6065,10 +6065,10 @@
         <v>95</v>
       </c>
       <c r="AP22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR22">
         <v>17</v>
@@ -6077,7 +6077,7 @@
         <v>25</v>
       </c>
       <c r="AT22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU22">
         <v>6.2</v>
@@ -6086,7 +6086,7 @@
         <v>13</v>
       </c>
       <c r="AW22">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AX22">
         <v>13</v>
@@ -6098,16 +6098,16 @@
         <v>21</v>
       </c>
       <c r="BA22">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB22">
         <v>34</v>
       </c>
       <c r="BC22">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD22">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE22">
         <v>7.6</v>
@@ -6116,13 +6116,13 @@
         <v>32</v>
       </c>
       <c r="BG22">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BH22">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BI22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ22">
         <v>14</v>
@@ -6134,7 +6134,7 @@
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN22">
         <v>6.6</v>
@@ -6146,13 +6146,13 @@
         <v>34</v>
       </c>
       <c r="BQ22">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR22">
         <v>65</v>
       </c>
       <c r="BS22">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT22">
         <v>7.2</v>
@@ -6161,7 +6161,7 @@
         <v>4.6</v>
       </c>
       <c r="BV22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW22">
         <v>4.5</v>
@@ -6199,22 +6199,22 @@
         <v>161</v>
       </c>
       <c r="F23">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G23">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I23">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J23">
         <v>3.85</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.39</v>
@@ -6223,40 +6223,40 @@
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P23">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q23">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T23">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U23">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X23">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y23">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z23">
         <v>24</v>
@@ -6268,10 +6268,10 @@
         <v>11</v>
       </c>
       <c r="AC23">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE23">
         <v>38</v>
@@ -6292,25 +6292,25 @@
         <v>32</v>
       </c>
       <c r="AK23">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM23">
         <v>100</v>
       </c>
       <c r="AN23">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO23">
         <v>38</v>
       </c>
       <c r="AP23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR23">
         <v>19.5</v>
@@ -6322,55 +6322,55 @@
         <v>9.4</v>
       </c>
       <c r="AU23">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV23">
         <v>12</v>
       </c>
       <c r="AW23">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AX23">
         <v>13</v>
       </c>
       <c r="AY23">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA23">
         <v>32</v>
       </c>
       <c r="BB23">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC23">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD23">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BE23">
         <v>65</v>
       </c>
       <c r="BF23">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH23">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI23">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BJ23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK23">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6385,16 +6385,16 @@
         <v>4.2</v>
       </c>
       <c r="BP23">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ23">
         <v>12.5</v>
       </c>
       <c r="BR23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT23">
         <v>7.6</v>
@@ -6409,16 +6409,16 @@
         <v>19.5</v>
       </c>
       <c r="BX23">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY23">
+        <v>26</v>
+      </c>
+      <c r="BZ23">
         <v>27</v>
       </c>
-      <c r="BZ23">
-        <v>29</v>
-      </c>
       <c r="CA23">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="CB23" t="s">
         <v>169</v>
@@ -6447,7 +6447,7 @@
         <v>4.6</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I24">
         <v>2.06</v>
@@ -6462,7 +6462,7 @@
         <v>1.48</v>
       </c>
       <c r="M24">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N24">
         <v>3.3</v>
@@ -6471,19 +6471,19 @@
         <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R24">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S24">
         <v>4.2</v>
       </c>
       <c r="T24">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U24">
         <v>1.93</v>
@@ -6495,7 +6495,7 @@
         <v>1.27</v>
       </c>
       <c r="X24">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y24">
         <v>8.199999999999999</v>
@@ -6537,7 +6537,7 @@
         <v>160</v>
       </c>
       <c r="AL24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM24">
         <v>580</v>
@@ -6576,7 +6576,7 @@
         <v>24</v>
       </c>
       <c r="AY24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ24">
         <v>19.5</v>
@@ -6594,7 +6594,7 @@
         <v>50</v>
       </c>
       <c r="BE24">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF24">
         <v>55</v>
@@ -6642,7 +6642,7 @@
         <v>4.7</v>
       </c>
       <c r="BU24">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BV24">
         <v>16</v>
@@ -6683,10 +6683,10 @@
         <v>163</v>
       </c>
       <c r="F25">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G25">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H25">
         <v>3.3</v>
@@ -6701,7 +6701,7 @@
         <v>3.1</v>
       </c>
       <c r="L25">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M25">
         <v>1.14</v>
@@ -6710,31 +6710,31 @@
         <v>2.58</v>
       </c>
       <c r="O25">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P25">
         <v>1.52</v>
       </c>
       <c r="Q25">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
         <v>1.18</v>
       </c>
       <c r="S25">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T25">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U25">
         <v>1.77</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -6746,7 +6746,7 @@
         <v>21</v>
       </c>
       <c r="AA25">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB25">
         <v>7.6</v>
@@ -6764,7 +6764,7 @@
         <v>15</v>
       </c>
       <c r="AG25">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH25">
         <v>24</v>
@@ -6782,7 +6782,7 @@
         <v>70</v>
       </c>
       <c r="AM25">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN25">
         <v>46</v>
@@ -6809,31 +6809,31 @@
         <v>6.6</v>
       </c>
       <c r="AV25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW25">
         <v>48</v>
       </c>
       <c r="AX25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY25">
         <v>12</v>
       </c>
       <c r="AZ25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA25">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC25">
         <v>36</v>
       </c>
       <c r="BD25">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BE25">
         <v>95</v>
@@ -6848,7 +6848,7 @@
         <v>2.56</v>
       </c>
       <c r="BI25">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ25">
         <v>11.5</v>
@@ -6860,25 +6860,25 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>22</v>
+        <v>2.3</v>
       </c>
       <c r="BN25">
         <v>5.2</v>
       </c>
       <c r="BO25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP25">
         <v>24</v>
       </c>
       <c r="BQ25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR25">
         <v>48</v>
       </c>
       <c r="BS25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BT25">
         <v>6.2</v>
@@ -6896,10 +6896,10 @@
         <v>60</v>
       </c>
       <c r="BY25">
-        <v>2.24</v>
+        <v>13.5</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA25">
         <v>17.5</v>
@@ -6925,61 +6925,61 @@
         <v>164</v>
       </c>
       <c r="F26">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G26">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H26">
+        <v>2.52</v>
+      </c>
+      <c r="I26">
         <v>2.58</v>
       </c>
-      <c r="I26">
-        <v>2.64</v>
-      </c>
       <c r="J26">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K26">
         <v>3.45</v>
       </c>
       <c r="L26">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M26">
         <v>1.08</v>
       </c>
       <c r="N26">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P26">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q26">
+        <v>2.08</v>
+      </c>
+      <c r="R26">
+        <v>1.34</v>
+      </c>
+      <c r="S26">
+        <v>3.75</v>
+      </c>
+      <c r="T26">
+        <v>1.81</v>
+      </c>
+      <c r="U26">
         <v>2.16</v>
       </c>
-      <c r="R26">
-        <v>1.32</v>
-      </c>
-      <c r="S26">
-        <v>3.95</v>
-      </c>
-      <c r="T26">
-        <v>1.85</v>
-      </c>
-      <c r="U26">
-        <v>2.1</v>
-      </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W26">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y26">
         <v>10.5</v>
@@ -6988,19 +6988,19 @@
         <v>17</v>
       </c>
       <c r="AA26">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD26">
         <v>12</v>
       </c>
       <c r="AE26">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AF26">
         <v>21</v>
@@ -7009,10 +7009,10 @@
         <v>13.5</v>
       </c>
       <c r="AH26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI26">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ26">
         <v>55</v>
@@ -7021,7 +7021,7 @@
         <v>44</v>
       </c>
       <c r="AL26">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM26">
         <v>110</v>
@@ -7030,31 +7030,31 @@
         <v>38</v>
       </c>
       <c r="AO26">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP26">
+        <v>12</v>
+      </c>
+      <c r="AQ26">
+        <v>9.6</v>
+      </c>
+      <c r="AR26">
+        <v>14.5</v>
+      </c>
+      <c r="AS26">
+        <v>32</v>
+      </c>
+      <c r="AT26">
         <v>11</v>
       </c>
-      <c r="AQ26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR26">
-        <v>15</v>
-      </c>
-      <c r="AS26">
-        <v>34</v>
-      </c>
-      <c r="AT26">
-        <v>10</v>
-      </c>
       <c r="AU26">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW26">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AX26">
         <v>18</v>
@@ -7063,88 +7063,88 @@
         <v>12</v>
       </c>
       <c r="AZ26">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB26">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC26">
         <v>32</v>
       </c>
       <c r="BD26">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BF26">
         <v>30</v>
       </c>
       <c r="BG26">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BH26">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BI26">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK26">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BN26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO26">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BP26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ26">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR26">
         <v>42</v>
       </c>
       <c r="BS26">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT26">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BU26">
         <v>4.9</v>
       </c>
       <c r="BV26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BW26">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX26">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BZ26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA26">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="CB26" t="s">
         <v>169</v>
@@ -7167,61 +7167,61 @@
         <v>165</v>
       </c>
       <c r="F27">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G27">
         <v>2.08</v>
       </c>
       <c r="H27">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J27">
+        <v>3.45</v>
+      </c>
+      <c r="K27">
         <v>3.5</v>
       </c>
-      <c r="K27">
-        <v>3.55</v>
-      </c>
       <c r="L27">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M27">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N27">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P27">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q27">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
+        <v>1.26</v>
+      </c>
+      <c r="S27">
+        <v>4.6</v>
+      </c>
+      <c r="T27">
+        <v>2.04</v>
+      </c>
+      <c r="U27">
+        <v>1.92</v>
+      </c>
+      <c r="V27">
         <v>1.28</v>
-      </c>
-      <c r="S27">
-        <v>4.3</v>
-      </c>
-      <c r="T27">
-        <v>1.96</v>
-      </c>
-      <c r="U27">
-        <v>2</v>
-      </c>
-      <c r="V27">
-        <v>1.3</v>
       </c>
       <c r="W27">
         <v>1.93</v>
       </c>
       <c r="X27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y27">
         <v>13</v>
@@ -7230,163 +7230,163 @@
         <v>30</v>
       </c>
       <c r="AA27">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AC27">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE27">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI27">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ27">
         <v>25</v>
       </c>
       <c r="AK27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM27">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO27">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP27">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR27">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS27">
+        <v>36</v>
+      </c>
+      <c r="AT27">
+        <v>7</v>
+      </c>
+      <c r="AU27">
+        <v>7</v>
+      </c>
+      <c r="AV27">
+        <v>16.5</v>
+      </c>
+      <c r="AW27">
         <v>55</v>
       </c>
-      <c r="AT27">
-        <v>7.4</v>
-      </c>
-      <c r="AU27">
-        <v>7.2</v>
-      </c>
-      <c r="AV27">
-        <v>16</v>
-      </c>
-      <c r="AW27">
-        <v>50</v>
-      </c>
       <c r="AX27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY27">
         <v>10</v>
       </c>
       <c r="AZ27">
+        <v>20</v>
+      </c>
+      <c r="BA27">
+        <v>65</v>
+      </c>
+      <c r="BB27">
+        <v>23</v>
+      </c>
+      <c r="BC27">
+        <v>23</v>
+      </c>
+      <c r="BD27">
+        <v>42</v>
+      </c>
+      <c r="BE27">
+        <v>44</v>
+      </c>
+      <c r="BF27">
         <v>18.5</v>
       </c>
-      <c r="BA27">
-        <v>60</v>
-      </c>
-      <c r="BB27">
-        <v>22</v>
-      </c>
-      <c r="BC27">
-        <v>22</v>
-      </c>
-      <c r="BD27">
-        <v>40</v>
-      </c>
-      <c r="BE27">
-        <v>42</v>
-      </c>
-      <c r="BF27">
-        <v>17.5</v>
-      </c>
       <c r="BG27">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BH27">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI27">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK27">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BL27">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BM27">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO27">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP27">
         <v>18</v>
       </c>
       <c r="BQ27">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR27">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS27">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU27">
         <v>6.6</v>
       </c>
       <c r="BV27">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BW27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX27">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY27">
+        <v>12</v>
+      </c>
+      <c r="BZ27">
+        <v>40</v>
+      </c>
+      <c r="CA27">
         <v>10.5</v>
-      </c>
-      <c r="BZ27">
-        <v>38</v>
-      </c>
-      <c r="CA27">
-        <v>9.6</v>
       </c>
       <c r="CB27" t="s">
         <v>169</v>
@@ -7409,64 +7409,64 @@
         <v>166</v>
       </c>
       <c r="F28">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G28">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H28">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I28">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J28">
+        <v>3.5</v>
+      </c>
+      <c r="K28">
         <v>3.7</v>
       </c>
-      <c r="K28">
-        <v>3.9</v>
-      </c>
       <c r="L28">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="O28">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P28">
+        <v>1.91</v>
+      </c>
+      <c r="Q28">
+        <v>2.04</v>
+      </c>
+      <c r="R28">
+        <v>1.35</v>
+      </c>
+      <c r="S28">
+        <v>3.65</v>
+      </c>
+      <c r="T28">
+        <v>1.81</v>
+      </c>
+      <c r="U28">
         <v>2.1</v>
       </c>
-      <c r="Q28">
-        <v>1.86</v>
-      </c>
-      <c r="R28">
-        <v>1.42</v>
-      </c>
-      <c r="S28">
-        <v>3.2</v>
-      </c>
-      <c r="T28">
-        <v>1.7</v>
-      </c>
-      <c r="U28">
-        <v>2.24</v>
-      </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X28">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Y28">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z28">
         <v>28</v>
@@ -7475,70 +7475,70 @@
         <v>80</v>
       </c>
       <c r="AB28">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC28">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE28">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AF28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG28">
         <v>11</v>
       </c>
       <c r="AH28">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI28">
         <v>55</v>
       </c>
       <c r="AJ28">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK28">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL28">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM28">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AN28">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AO28">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AP28">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AQ28">
+        <v>11.5</v>
+      </c>
+      <c r="AR28">
+        <v>8.6</v>
+      </c>
+      <c r="AS28">
+        <v>10</v>
+      </c>
+      <c r="AT28">
+        <v>8.6</v>
+      </c>
+      <c r="AU28">
+        <v>7.2</v>
+      </c>
+      <c r="AV28">
         <v>13</v>
       </c>
-      <c r="AR28">
-        <v>23</v>
-      </c>
-      <c r="AS28">
-        <v>8.6</v>
-      </c>
-      <c r="AT28">
-        <v>9.6</v>
-      </c>
-      <c r="AU28">
-        <v>7.6</v>
-      </c>
-      <c r="AV28">
-        <v>13.5</v>
-      </c>
       <c r="AW28">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AX28">
         <v>12.5</v>
@@ -7547,88 +7547,88 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA28">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BB28">
-        <v>23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC28">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD28">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE28">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BF28">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG28">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CB28" t="s">
         <v>169</v>
@@ -7651,7 +7651,7 @@
         <v>167</v>
       </c>
       <c r="F29">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G29">
         <v>3.3</v>
@@ -7675,13 +7675,13 @@
         <v>1.1</v>
       </c>
       <c r="N29">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P29">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q29">
         <v>2.42</v>
@@ -7690,7 +7690,7 @@
         <v>1.25</v>
       </c>
       <c r="S29">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T29">
         <v>2.02</v>
@@ -7717,13 +7717,13 @@
         <v>46</v>
       </c>
       <c r="AB29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>7.4</v>
       </c>
       <c r="AD29">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AE29">
         <v>40</v>
@@ -7768,7 +7768,7 @@
         <v>13.5</v>
       </c>
       <c r="AS29">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT29">
         <v>9</v>
@@ -7777,13 +7777,13 @@
         <v>6.6</v>
       </c>
       <c r="AV29">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW29">
         <v>24</v>
       </c>
       <c r="AX29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY29">
         <v>12.5</v>
@@ -7792,85 +7792,85 @@
         <v>18.5</v>
       </c>
       <c r="BA29">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB29">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC29">
         <v>36</v>
       </c>
       <c r="BD29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF29">
         <v>15.5</v>
       </c>
       <c r="BG29">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI29">
-        <v>1.16</v>
+        <v>2.68</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK29">
-        <v>1.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.16</v>
+        <v>5.8</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO29">
-        <v>1.16</v>
+        <v>5.6</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ29">
-        <v>1.16</v>
+        <v>5</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS29">
-        <v>1.16</v>
+        <v>5.3</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU29">
-        <v>1.48</v>
+        <v>4.7</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW29">
-        <v>1.16</v>
+        <v>4.8</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY29">
-        <v>1.16</v>
+        <v>5.2</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA29">
-        <v>1.16</v>
+        <v>5.2</v>
       </c>
       <c r="CB29" t="s">
         <v>169</v>
@@ -7893,223 +7893,223 @@
         <v>168</v>
       </c>
       <c r="F30">
+        <v>1.89</v>
+      </c>
+      <c r="G30">
+        <v>1.91</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>5.2</v>
+      </c>
+      <c r="J30">
+        <v>3.5</v>
+      </c>
+      <c r="K30">
+        <v>3.6</v>
+      </c>
+      <c r="L30">
+        <v>1.52</v>
+      </c>
+      <c r="M30">
+        <v>1.1</v>
+      </c>
+      <c r="N30">
+        <v>3.15</v>
+      </c>
+      <c r="O30">
+        <v>1.45</v>
+      </c>
+      <c r="P30">
+        <v>1.71</v>
+      </c>
+      <c r="Q30">
+        <v>2.34</v>
+      </c>
+      <c r="R30">
+        <v>1.27</v>
+      </c>
+      <c r="S30">
+        <v>4.5</v>
+      </c>
+      <c r="T30">
+        <v>2.12</v>
+      </c>
+      <c r="U30">
+        <v>1.84</v>
+      </c>
+      <c r="V30">
+        <v>1.23</v>
+      </c>
+      <c r="W30">
         <v>2.08</v>
       </c>
-      <c r="G30">
-        <v>2.1</v>
-      </c>
-      <c r="H30">
-        <v>4.5</v>
-      </c>
-      <c r="I30">
-        <v>4.7</v>
-      </c>
-      <c r="J30">
-        <v>3.25</v>
-      </c>
-      <c r="K30">
-        <v>3.3</v>
-      </c>
-      <c r="L30">
-        <v>1.59</v>
-      </c>
-      <c r="M30">
-        <v>1.13</v>
-      </c>
-      <c r="N30">
-        <v>2.74</v>
-      </c>
-      <c r="O30">
-        <v>1.55</v>
-      </c>
-      <c r="P30">
-        <v>1.56</v>
-      </c>
-      <c r="Q30">
-        <v>2.68</v>
-      </c>
-      <c r="R30">
-        <v>1.2</v>
-      </c>
-      <c r="S30">
-        <v>5.5</v>
-      </c>
-      <c r="T30">
-        <v>2.26</v>
-      </c>
-      <c r="U30">
-        <v>1.75</v>
-      </c>
-      <c r="V30">
-        <v>1.27</v>
-      </c>
-      <c r="W30">
-        <v>1.91</v>
-      </c>
       <c r="X30">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y30">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Z30">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA30">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AB30">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC30">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AE30">
         <v>85</v>
       </c>
       <c r="AF30">
+        <v>10.5</v>
+      </c>
+      <c r="AG30">
         <v>11</v>
       </c>
-      <c r="AG30">
+      <c r="AH30">
+        <v>23</v>
+      </c>
+      <c r="AI30">
+        <v>100</v>
+      </c>
+      <c r="AJ30">
+        <v>21</v>
+      </c>
+      <c r="AK30">
+        <v>23</v>
+      </c>
+      <c r="AL30">
+        <v>48</v>
+      </c>
+      <c r="AM30">
+        <v>160</v>
+      </c>
+      <c r="AN30">
+        <v>16.5</v>
+      </c>
+      <c r="AO30">
+        <v>120</v>
+      </c>
+      <c r="AP30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ30">
+        <v>13</v>
+      </c>
+      <c r="AR30">
+        <v>32</v>
+      </c>
+      <c r="AS30">
+        <v>20</v>
+      </c>
+      <c r="AT30">
+        <v>6.8</v>
+      </c>
+      <c r="AU30">
+        <v>7.2</v>
+      </c>
+      <c r="AV30">
+        <v>18.5</v>
+      </c>
+      <c r="AW30">
+        <v>60</v>
+      </c>
+      <c r="AX30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY30">
+        <v>10</v>
+      </c>
+      <c r="AZ30">
+        <v>21</v>
+      </c>
+      <c r="BA30">
+        <v>44</v>
+      </c>
+      <c r="BB30">
+        <v>18.5</v>
+      </c>
+      <c r="BC30">
+        <v>21</v>
+      </c>
+      <c r="BD30">
+        <v>42</v>
+      </c>
+      <c r="BE30">
+        <v>21</v>
+      </c>
+      <c r="BF30">
+        <v>15</v>
+      </c>
+      <c r="BG30">
+        <v>22</v>
+      </c>
+      <c r="BH30">
+        <v>3</v>
+      </c>
+      <c r="BI30">
+        <v>2.82</v>
+      </c>
+      <c r="BJ30">
         <v>11.5</v>
       </c>
-      <c r="AH30">
-        <v>25</v>
-      </c>
-      <c r="AI30">
-        <v>110</v>
-      </c>
-      <c r="AJ30">
-        <v>26</v>
-      </c>
-      <c r="AK30">
-        <v>29</v>
-      </c>
-      <c r="AL30">
-        <v>65</v>
-      </c>
-      <c r="AM30">
-        <v>210</v>
-      </c>
-      <c r="AN30">
-        <v>27</v>
-      </c>
-      <c r="AO30">
-        <v>130</v>
-      </c>
-      <c r="AP30">
+      <c r="BK30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>15.5</v>
+      </c>
+      <c r="BN30">
+        <v>4.3</v>
+      </c>
+      <c r="BO30">
+        <v>4</v>
+      </c>
+      <c r="BP30">
+        <v>14.5</v>
+      </c>
+      <c r="BQ30">
         <v>7.8</v>
       </c>
-      <c r="AQ30">
-        <v>10.5</v>
-      </c>
-      <c r="AR30">
-        <v>28</v>
-      </c>
-      <c r="AS30">
-        <v>19</v>
-      </c>
-      <c r="AT30">
-        <v>6.2</v>
-      </c>
-      <c r="AU30">
-        <v>7</v>
-      </c>
-      <c r="AV30">
-        <v>18</v>
-      </c>
-      <c r="AW30">
+      <c r="BR30">
         <v>36</v>
-      </c>
-      <c r="AX30">
-        <v>10</v>
-      </c>
-      <c r="AY30">
-        <v>10.5</v>
-      </c>
-      <c r="AZ30">
-        <v>23</v>
-      </c>
-      <c r="BA30">
-        <v>15.5</v>
-      </c>
-      <c r="BB30">
-        <v>23</v>
-      </c>
-      <c r="BC30">
-        <v>26</v>
-      </c>
-      <c r="BD30">
-        <v>50</v>
-      </c>
-      <c r="BE30">
-        <v>15.5</v>
-      </c>
-      <c r="BF30">
-        <v>23</v>
-      </c>
-      <c r="BG30">
-        <v>16</v>
-      </c>
-      <c r="BH30">
-        <v>2.7</v>
-      </c>
-      <c r="BI30">
-        <v>2.54</v>
-      </c>
-      <c r="BJ30">
-        <v>12</v>
-      </c>
-      <c r="BK30">
-        <v>6.8</v>
-      </c>
-      <c r="BL30">
-        <v>1000</v>
-      </c>
-      <c r="BM30">
-        <v>14.5</v>
-      </c>
-      <c r="BN30">
-        <v>4.6</v>
-      </c>
-      <c r="BO30">
-        <v>4.1</v>
-      </c>
-      <c r="BP30">
-        <v>18.5</v>
-      </c>
-      <c r="BQ30">
-        <v>8.4</v>
-      </c>
-      <c r="BR30">
-        <v>44</v>
       </c>
       <c r="BS30">
         <v>11.5</v>
       </c>
       <c r="BT30">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU30">
         <v>6.4</v>
       </c>
       <c r="BV30">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW30">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ30">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="CA30">
         <v>11.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-02.xlsx
@@ -523,7 +523,7 @@
     <t>Operario PR</t>
   </si>
   <si>
-    <t>2026-10-02 11:19:20</t>
+    <t>2026-10-02 13:37:51</t>
   </si>
 </sst>
 </file>
@@ -1117,226 +1117,226 @@
         <v>140</v>
       </c>
       <c r="F2">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="G2">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>6.2</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>3.6</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>4.9</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="S2">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="X2">
+        <v>6.2</v>
+      </c>
+      <c r="Y2">
         <v>11</v>
-      </c>
-      <c r="Y2">
-        <v>16</v>
       </c>
       <c r="Z2">
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AC2">
         <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AE2">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AH2">
+        <v>60</v>
+      </c>
+      <c r="AI2">
+        <v>400</v>
+      </c>
+      <c r="AJ2">
+        <v>32</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>210</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>65</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>4.6</v>
+      </c>
+      <c r="AQ2">
+        <v>9</v>
+      </c>
+      <c r="AR2">
+        <v>36</v>
+      </c>
+      <c r="AS2">
+        <v>190</v>
+      </c>
+      <c r="AT2">
+        <v>4.3</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
         <v>29</v>
       </c>
-      <c r="AI2">
-        <v>700</v>
-      </c>
-      <c r="AJ2">
-        <v>19.5</v>
-      </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
-      <c r="AL2">
-        <v>170</v>
-      </c>
-      <c r="AM2">
-        <v>580</v>
-      </c>
-      <c r="AN2">
-        <v>17</v>
-      </c>
-      <c r="AO2">
-        <v>600</v>
-      </c>
-      <c r="AP2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>13</v>
-      </c>
-      <c r="AR2">
-        <v>32</v>
-      </c>
-      <c r="AS2">
-        <v>90</v>
-      </c>
-      <c r="AT2">
-        <v>6</v>
-      </c>
-      <c r="AU2">
-        <v>7.2</v>
-      </c>
-      <c r="AV2">
-        <v>20</v>
-      </c>
       <c r="AW2">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="BB2">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="BE2">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BG2">
         <v>100</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>1.41</v>
       </c>
       <c r="BI2">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BK2">
-        <v>1.88</v>
+        <v>14</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.88</v>
+        <v>17.5</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO2">
-        <v>1.46</v>
+        <v>5.6</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.88</v>
+        <v>14.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.88</v>
+        <v>17.5</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU2">
-        <v>1.88</v>
+        <v>11.5</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.88</v>
+        <v>16.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.88</v>
+        <v>17.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.88</v>
+        <v>17.5</v>
       </c>
       <c r="CB2" t="s">
         <v>169</v>
@@ -1359,76 +1359,76 @@
         <v>141</v>
       </c>
       <c r="F3">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H3">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S3">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="T3">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
         <v>14</v>
@@ -1437,100 +1437,100 @@
         <v>36</v>
       </c>
       <c r="AF3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AJ3">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="AK3">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="AL3">
-        <v>290</v>
+        <v>36</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ3">
+        <v>14</v>
+      </c>
+      <c r="AR3">
+        <v>18.5</v>
+      </c>
+      <c r="AS3">
+        <v>27</v>
+      </c>
+      <c r="AT3">
         <v>12</v>
       </c>
-      <c r="AR3">
-        <v>17.5</v>
-      </c>
-      <c r="AS3">
-        <v>29</v>
-      </c>
-      <c r="AT3">
-        <v>10.5</v>
-      </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BB3">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="BC3">
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BG3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BH3">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BJ3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1539,13 +1539,13 @@
         <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
         <v>7.2</v>
@@ -1560,25 +1560,25 @@
         <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW3">
         <v>7.8</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="s">
         <v>169</v>
@@ -1601,22 +1601,22 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="G4">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H4">
+        <v>4.6</v>
+      </c>
+      <c r="I4">
+        <v>4.9</v>
+      </c>
+      <c r="J4">
+        <v>4.1</v>
+      </c>
+      <c r="K4">
         <v>4.3</v>
-      </c>
-      <c r="I4">
-        <v>4.6</v>
-      </c>
-      <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4">
-        <v>4.2</v>
       </c>
       <c r="L4">
         <v>1.37</v>
@@ -1625,7 +1625,7 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O4">
         <v>1.27</v>
@@ -1640,7 +1640,7 @@
         <v>1.45</v>
       </c>
       <c r="S4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T4">
         <v>1.74</v>
@@ -1649,43 +1649,43 @@
         <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z4">
         <v>38</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
         <v>60</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI4">
         <v>60</v>
@@ -1694,25 +1694,25 @@
         <v>21</v>
       </c>
       <c r="AK4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP4">
         <v>15.5</v>
       </c>
       <c r="AQ4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
         <v>30</v>
@@ -1721,7 +1721,7 @@
         <v>55</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4">
         <v>8.4</v>
@@ -1733,13 +1733,13 @@
         <v>44</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
         <v>46</v>
@@ -1748,79 +1748,79 @@
         <v>18</v>
       </c>
       <c r="BC4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BF4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH4">
         <v>4.2</v>
       </c>
       <c r="BI4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN4">
         <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BT4">
         <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BV4">
         <v>38</v>
       </c>
       <c r="BW4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB4" t="s">
         <v>169</v>
@@ -1846,79 +1846,79 @@
         <v>2.86</v>
       </c>
       <c r="G5">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H5">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I5">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.31</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="V5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
         <v>1.5</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>13</v>
       </c>
       <c r="AE5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF5">
         <v>23</v>
@@ -1927,34 +1927,34 @@
         <v>14</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ5">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AK5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN5">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AO5">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AP5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
         <v>16</v>
@@ -1963,16 +1963,16 @@
         <v>17</v>
       </c>
       <c r="AT5">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX5">
         <v>18</v>
@@ -1987,40 +1987,40 @@
         <v>15</v>
       </c>
       <c r="BB5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC5">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BD5">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF5">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BG5">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BI5">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BM5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN5">
         <v>7.2</v>
@@ -2029,13 +2029,13 @@
         <v>5.4</v>
       </c>
       <c r="BP5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BS5">
         <v>4.9</v>
@@ -2044,25 +2044,25 @@
         <v>6.6</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BW5">
         <v>4.5</v>
       </c>
       <c r="BX5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB5" t="s">
         <v>169</v>
@@ -2085,16 +2085,16 @@
         <v>144</v>
       </c>
       <c r="F6">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="G6">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="H6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I6">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="J6">
         <v>4.7</v>
@@ -2103,94 +2103,94 @@
         <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O6">
         <v>1.09</v>
       </c>
       <c r="P6">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R6">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="T6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U6">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="X6">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Z6">
         <v>44</v>
       </c>
       <c r="AA6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE6">
         <v>34</v>
       </c>
       <c r="AF6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG6">
+        <v>12.5</v>
+      </c>
+      <c r="AH6">
         <v>13.5</v>
-      </c>
-      <c r="AH6">
-        <v>14</v>
       </c>
       <c r="AI6">
         <v>28</v>
       </c>
       <c r="AJ6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL6">
         <v>21</v>
       </c>
       <c r="AM6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN6">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AO6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP6">
         <v>42</v>
@@ -2199,22 +2199,22 @@
         <v>30</v>
       </c>
       <c r="AR6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AT6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX6">
         <v>20</v>
@@ -2229,82 +2229,82 @@
         <v>24</v>
       </c>
       <c r="BB6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BE6">
         <v>30</v>
       </c>
       <c r="BF6">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH6">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BJ6">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL6">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BM6">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BN6">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
         <v>5.6</v>
       </c>
       <c r="BP6">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ6">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BS6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT6">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BU6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW6">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="BX6">
         <v>24</v>
       </c>
       <c r="BY6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BZ6">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CA6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
         <v>169</v>
@@ -2327,226 +2327,226 @@
         <v>145</v>
       </c>
       <c r="F7">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G7">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="H7">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S7">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="U7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="X7">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB7">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AC7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AF7">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AG7">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AK7">
         <v>500</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>600</v>
+        <v>21</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="AP7">
+        <v>13</v>
+      </c>
+      <c r="AQ7">
         <v>11</v>
       </c>
-      <c r="AQ7">
-        <v>9.4</v>
-      </c>
       <c r="AR7">
+        <v>18</v>
+      </c>
+      <c r="AS7">
+        <v>27</v>
+      </c>
+      <c r="AT7">
         <v>10.5</v>
       </c>
-      <c r="AS7">
-        <v>16</v>
-      </c>
-      <c r="AT7">
-        <v>8.4</v>
-      </c>
       <c r="AU7">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>1.62</v>
+        <v>20</v>
       </c>
       <c r="AX7">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AY7">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA7">
-        <v>1.63</v>
+        <v>32</v>
       </c>
       <c r="BB7">
         <v>13</v>
       </c>
       <c r="BC7">
-        <v>1.62</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>1.62</v>
+        <v>22</v>
       </c>
       <c r="BE7">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="BF7">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BG7">
-        <v>1.63</v>
+        <v>17</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="CB7" t="s">
         <v>169</v>
@@ -2569,124 +2569,124 @@
         <v>146</v>
       </c>
       <c r="F8">
+        <v>3.2</v>
+      </c>
+      <c r="G8">
         <v>3.35</v>
       </c>
-      <c r="G8">
-        <v>3.65</v>
-      </c>
       <c r="H8">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I8">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O8">
         <v>1.23</v>
       </c>
       <c r="P8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R8">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S8">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T8">
         <v>1.6</v>
       </c>
       <c r="U8">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V8">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AB8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
         <v>24</v>
       </c>
       <c r="AF8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH8">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI8">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="AJ8">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AK8">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="AL8">
-        <v>330</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AN8">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="AO8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP8">
         <v>17</v>
       </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS8">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AT8">
         <v>14</v>
@@ -2695,100 +2695,100 @@
         <v>7.8</v>
       </c>
       <c r="AV8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BB8">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BC8">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BE8">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BF8">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BG8">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH8">
         <v>4.6</v>
       </c>
       <c r="BI8">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK8">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BN8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BP8">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BQ8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR8">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BT8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV8">
         <v>16.5</v>
       </c>
       <c r="BW8">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
         <v>28</v>
       </c>
       <c r="BY8">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BZ8">
         <v>21</v>
       </c>
       <c r="CA8">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="CB8" t="s">
         <v>169</v>
@@ -2811,226 +2811,226 @@
         <v>147</v>
       </c>
       <c r="F9">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="G9">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="H9">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I9">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="K9">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L9">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M9">
         <v>1.03</v>
       </c>
       <c r="N9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O9">
+        <v>1.18</v>
+      </c>
+      <c r="P9">
+        <v>2.68</v>
+      </c>
+      <c r="Q9">
+        <v>1.54</v>
+      </c>
+      <c r="R9">
+        <v>1.67</v>
+      </c>
+      <c r="S9">
+        <v>2.36</v>
+      </c>
+      <c r="T9">
+        <v>1.64</v>
+      </c>
+      <c r="U9">
+        <v>2.3</v>
+      </c>
+      <c r="V9">
         <v>1.16</v>
       </c>
-      <c r="P9">
-        <v>2.78</v>
-      </c>
-      <c r="Q9">
-        <v>1.51</v>
-      </c>
-      <c r="R9">
-        <v>1.71</v>
-      </c>
-      <c r="S9">
-        <v>2.26</v>
-      </c>
-      <c r="T9">
-        <v>1.75</v>
-      </c>
-      <c r="U9">
-        <v>2.24</v>
-      </c>
-      <c r="V9">
-        <v>1.14</v>
-      </c>
       <c r="W9">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="X9">
         <v>29</v>
       </c>
       <c r="Y9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA9">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="AB9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
+        <v>12.5</v>
+      </c>
+      <c r="AD9">
+        <v>28</v>
+      </c>
+      <c r="AE9">
+        <v>230</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH9">
+        <v>21</v>
+      </c>
+      <c r="AI9">
+        <v>75</v>
+      </c>
+      <c r="AJ9">
+        <v>15.5</v>
+      </c>
+      <c r="AK9">
+        <v>14.5</v>
+      </c>
+      <c r="AL9">
+        <v>26</v>
+      </c>
+      <c r="AM9">
+        <v>95</v>
+      </c>
+      <c r="AN9">
+        <v>5.6</v>
+      </c>
+      <c r="AO9">
+        <v>500</v>
+      </c>
+      <c r="AP9">
+        <v>24</v>
+      </c>
+      <c r="AQ9">
+        <v>19.5</v>
+      </c>
+      <c r="AR9">
+        <v>29</v>
+      </c>
+      <c r="AS9">
         <v>13.5</v>
       </c>
-      <c r="AD9">
-        <v>30</v>
-      </c>
-      <c r="AE9">
-        <v>190</v>
-      </c>
-      <c r="AF9">
-        <v>11</v>
-      </c>
-      <c r="AG9">
+      <c r="AT9">
         <v>10.5</v>
       </c>
-      <c r="AH9">
+      <c r="AU9">
+        <v>10.5</v>
+      </c>
+      <c r="AV9">
+        <v>15</v>
+      </c>
+      <c r="AW9">
+        <v>12.5</v>
+      </c>
+      <c r="AX9">
+        <v>10</v>
+      </c>
+      <c r="AY9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>17.5</v>
+      </c>
+      <c r="BA9">
+        <v>29</v>
+      </c>
+      <c r="BB9">
+        <v>13.5</v>
+      </c>
+      <c r="BC9">
+        <v>12.5</v>
+      </c>
+      <c r="BD9">
         <v>22</v>
       </c>
-      <c r="AI9">
-        <v>80</v>
-      </c>
-      <c r="AJ9">
-        <v>14</v>
-      </c>
-      <c r="AK9">
-        <v>14</v>
-      </c>
-      <c r="AL9">
-        <v>27</v>
-      </c>
-      <c r="AM9">
-        <v>110</v>
-      </c>
-      <c r="AN9">
-        <v>5.1</v>
-      </c>
-      <c r="AO9">
-        <v>85</v>
-      </c>
-      <c r="AP9">
-        <v>22</v>
-      </c>
-      <c r="AQ9">
-        <v>29</v>
-      </c>
-      <c r="AR9">
-        <v>60</v>
-      </c>
-      <c r="AS9">
-        <v>11.5</v>
-      </c>
-      <c r="AT9">
-        <v>11</v>
-      </c>
-      <c r="AU9">
-        <v>11.5</v>
-      </c>
-      <c r="AV9">
-        <v>25</v>
-      </c>
-      <c r="AW9">
-        <v>46</v>
-      </c>
-      <c r="AX9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY9">
-        <v>9</v>
-      </c>
-      <c r="AZ9">
-        <v>18.5</v>
-      </c>
-      <c r="BA9">
-        <v>42</v>
-      </c>
-      <c r="BB9">
-        <v>11.5</v>
-      </c>
-      <c r="BC9">
-        <v>12</v>
-      </c>
-      <c r="BD9">
-        <v>23</v>
-      </c>
       <c r="BE9">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BF9">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG9">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="BH9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI9">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
+        <v>12</v>
+      </c>
+      <c r="BN9">
+        <v>4.5</v>
+      </c>
+      <c r="BO9">
+        <v>3.95</v>
+      </c>
+      <c r="BP9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ9">
+        <v>6.4</v>
+      </c>
+      <c r="BR9">
+        <v>19</v>
+      </c>
+      <c r="BS9">
+        <v>8</v>
+      </c>
+      <c r="BT9">
         <v>10.5</v>
       </c>
-      <c r="BN9">
-        <v>4.4</v>
-      </c>
-      <c r="BO9">
-        <v>3.85</v>
-      </c>
-      <c r="BP9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ9">
-        <v>5.1</v>
-      </c>
-      <c r="BR9">
-        <v>19.5</v>
-      </c>
-      <c r="BS9">
-        <v>7.4</v>
-      </c>
-      <c r="BT9">
-        <v>11.5</v>
-      </c>
       <c r="BU9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA9">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="s">
         <v>169</v>
@@ -3053,22 +3053,22 @@
         <v>148</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G10">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H10">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J10">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K10">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="L10">
         <v>1.7</v>
@@ -3083,10 +3083,10 @@
         <v>1.59</v>
       </c>
       <c r="P10">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q10">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R10">
         <v>1.17</v>
@@ -3095,49 +3095,49 @@
         <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X10">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="Z10">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AA10">
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>60</v>
+        <v>8.6</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AD10">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AE10">
         <v>500</v>
       </c>
       <c r="AF10">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG10">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AI10">
         <v>500</v>
@@ -3161,112 +3161,112 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="AR10">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AS10">
-        <v>2.24</v>
+        <v>5.8</v>
       </c>
       <c r="AT10">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU10">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AV10">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW10">
-        <v>2.32</v>
+        <v>5.5</v>
       </c>
       <c r="AX10">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
+        <v>5.3</v>
+      </c>
+      <c r="BA10">
         <v>5.5</v>
       </c>
-      <c r="AZ10">
-        <v>2.32</v>
-      </c>
-      <c r="BA10">
-        <v>2.26</v>
-      </c>
       <c r="BB10">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC10">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="BD10">
-        <v>2.26</v>
+        <v>5.3</v>
       </c>
       <c r="BE10">
-        <v>2.28</v>
+        <v>5.4</v>
       </c>
       <c r="BF10">
-        <v>2.14</v>
+        <v>5.4</v>
       </c>
       <c r="BG10">
-        <v>2.14</v>
+        <v>5.5</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI10">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.31</v>
+        <v>8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO10">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.15</v>
+        <v>5.2</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>149</v>
       </c>
       <c r="F11">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="G11">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H11">
         <v>3.2</v>
       </c>
       <c r="I11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J11">
         <v>3.1</v>
@@ -3313,43 +3313,43 @@
         <v>3.15</v>
       </c>
       <c r="L11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M11">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N11">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O11">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P11">
+        <v>1.57</v>
+      </c>
+      <c r="Q11">
+        <v>2.72</v>
+      </c>
+      <c r="R11">
+        <v>1.2</v>
+      </c>
+      <c r="S11">
+        <v>5.7</v>
+      </c>
+      <c r="T11">
+        <v>2.14</v>
+      </c>
+      <c r="U11">
+        <v>1.85</v>
+      </c>
+      <c r="V11">
+        <v>1.43</v>
+      </c>
+      <c r="W11">
         <v>1.59</v>
       </c>
-      <c r="Q11">
-        <v>2.64</v>
-      </c>
-      <c r="R11">
-        <v>1.21</v>
-      </c>
-      <c r="S11">
-        <v>5.4</v>
-      </c>
-      <c r="T11">
-        <v>2.1</v>
-      </c>
-      <c r="U11">
-        <v>1.87</v>
-      </c>
-      <c r="V11">
-        <v>1.45</v>
-      </c>
-      <c r="W11">
-        <v>1.57</v>
-      </c>
       <c r="X11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11">
         <v>9.199999999999999</v>
@@ -3367,13 +3367,13 @@
         <v>7</v>
       </c>
       <c r="AD11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE11">
         <v>48</v>
       </c>
       <c r="AF11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG11">
         <v>13</v>
@@ -3382,13 +3382,13 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
         <v>44</v>
       </c>
       <c r="AK11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL11">
         <v>65</v>
@@ -3397,10 +3397,10 @@
         <v>180</v>
       </c>
       <c r="AN11">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP11">
         <v>8.199999999999999</v>
@@ -3415,7 +3415,7 @@
         <v>50</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
@@ -3427,7 +3427,7 @@
         <v>42</v>
       </c>
       <c r="AX11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY11">
         <v>11.5</v>
@@ -3436,7 +3436,7 @@
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB11">
         <v>38</v>
@@ -3448,19 +3448,19 @@
         <v>55</v>
       </c>
       <c r="BE11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BF11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH11">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI11">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
@@ -3469,10 +3469,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BL11">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="BM11">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BN11">
         <v>5.3</v>
@@ -3490,7 +3490,7 @@
         <v>46</v>
       </c>
       <c r="BS11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT11">
         <v>6.2</v>
@@ -3502,19 +3502,19 @@
         <v>30</v>
       </c>
       <c r="BW11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX11">
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ11">
         <v>48</v>
       </c>
       <c r="CA11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB11" t="s">
         <v>169</v>
@@ -3537,22 +3537,22 @@
         <v>150</v>
       </c>
       <c r="F12">
+        <v>5.2</v>
+      </c>
+      <c r="G12">
+        <v>5.4</v>
+      </c>
+      <c r="H12">
+        <v>1.68</v>
+      </c>
+      <c r="I12">
+        <v>1.69</v>
+      </c>
+      <c r="J12">
+        <v>4.5</v>
+      </c>
+      <c r="K12">
         <v>4.6</v>
-      </c>
-      <c r="G12">
-        <v>4.8</v>
-      </c>
-      <c r="H12">
-        <v>1.76</v>
-      </c>
-      <c r="I12">
-        <v>1.78</v>
-      </c>
-      <c r="J12">
-        <v>4.4</v>
-      </c>
-      <c r="K12">
-        <v>4.5</v>
       </c>
       <c r="L12">
         <v>1.28</v>
@@ -3570,193 +3570,193 @@
         <v>2.72</v>
       </c>
       <c r="Q12">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R12">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S12">
         <v>2.38</v>
       </c>
       <c r="T12">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="W12">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA12">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AB12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC12">
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE12">
+        <v>15.5</v>
+      </c>
+      <c r="AF12">
+        <v>46</v>
+      </c>
+      <c r="AG12">
+        <v>21</v>
+      </c>
+      <c r="AH12">
         <v>16</v>
       </c>
-      <c r="AF12">
-        <v>40</v>
-      </c>
-      <c r="AG12">
-        <v>19.5</v>
-      </c>
-      <c r="AH12">
-        <v>15.5</v>
-      </c>
       <c r="AI12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ12">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AK12">
+        <v>55</v>
+      </c>
+      <c r="AL12">
         <v>50</v>
       </c>
-      <c r="AL12">
-        <v>46</v>
-      </c>
       <c r="AM12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN12">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AO12">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AP12">
         <v>23</v>
       </c>
       <c r="AQ12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS12">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AT12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX12">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AY12">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AZ12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA12">
         <v>23</v>
       </c>
       <c r="BB12">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BC12">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BD12">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BE12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF12">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BG12">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH12">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BI12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ12">
+        <v>9.4</v>
+      </c>
+      <c r="BK12">
+        <v>8</v>
+      </c>
+      <c r="BL12">
+        <v>80</v>
+      </c>
+      <c r="BM12">
+        <v>13.5</v>
+      </c>
+      <c r="BN12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO12">
+        <v>8</v>
+      </c>
+      <c r="BP12">
+        <v>36</v>
+      </c>
+      <c r="BQ12">
+        <v>11</v>
+      </c>
+      <c r="BR12">
+        <v>38</v>
+      </c>
+      <c r="BS12">
+        <v>11.5</v>
+      </c>
+      <c r="BT12">
+        <v>4.7</v>
+      </c>
+      <c r="BU12">
+        <v>4.3</v>
+      </c>
+      <c r="BV12">
+        <v>10.5</v>
+      </c>
+      <c r="BW12">
         <v>9</v>
-      </c>
-      <c r="BK12">
-        <v>7.8</v>
-      </c>
-      <c r="BL12">
-        <v>75</v>
-      </c>
-      <c r="BM12">
-        <v>12.5</v>
-      </c>
-      <c r="BN12">
-        <v>8.4</v>
-      </c>
-      <c r="BO12">
-        <v>7.6</v>
-      </c>
-      <c r="BP12">
-        <v>32</v>
-      </c>
-      <c r="BQ12">
-        <v>10</v>
-      </c>
-      <c r="BR12">
-        <v>34</v>
-      </c>
-      <c r="BS12">
-        <v>10.5</v>
-      </c>
-      <c r="BT12">
-        <v>4.9</v>
-      </c>
-      <c r="BU12">
-        <v>4.4</v>
-      </c>
-      <c r="BV12">
-        <v>11</v>
-      </c>
-      <c r="BW12">
-        <v>6.2</v>
       </c>
       <c r="BX12">
         <v>20</v>
       </c>
       <c r="BY12">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ12">
         <v>13</v>
       </c>
       <c r="CA12">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB12" t="s">
         <v>169</v>
@@ -3779,7 +3779,7 @@
         <v>151</v>
       </c>
       <c r="F13">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -3788,10 +3788,10 @@
         <v>4</v>
       </c>
       <c r="I13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K13">
         <v>4.1</v>
@@ -3800,205 +3800,205 @@
         <v>1.36</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P13">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="T13">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="U13">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
         <v>2</v>
       </c>
       <c r="X13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y13">
         <v>18.5</v>
       </c>
       <c r="Z13">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA13">
-        <v>340</v>
+        <v>170</v>
       </c>
       <c r="AB13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC13">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE13">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="AF13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG13">
         <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI13">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK13">
         <v>20</v>
       </c>
       <c r="AL13">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM13">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO13">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AP13">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AS13">
         <v>55</v>
       </c>
       <c r="AT13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX13">
         <v>12</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH13">
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="CB13" t="s">
         <v>169</v>
@@ -4021,19 +4021,19 @@
         <v>152</v>
       </c>
       <c r="F14">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G14">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H14">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="I14">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -4045,145 +4045,145 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P14">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="Q14">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R14">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="S14">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T14">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U14">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V14">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W14">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC14">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD14">
         <v>12</v>
       </c>
       <c r="AE14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG14">
+        <v>15</v>
+      </c>
+      <c r="AH14">
         <v>14.5</v>
       </c>
-      <c r="AH14">
-        <v>15</v>
-      </c>
       <c r="AI14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ14">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AK14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL14">
         <v>34</v>
       </c>
       <c r="AM14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN14">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO14">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AP14">
+        <v>22</v>
+      </c>
+      <c r="AQ14">
         <v>14</v>
-      </c>
-      <c r="AQ14">
-        <v>13.5</v>
       </c>
       <c r="AR14">
         <v>16</v>
       </c>
       <c r="AS14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV14">
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AX14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ14">
         <v>13</v>
       </c>
       <c r="BA14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BD14">
         <v>28</v>
       </c>
       <c r="BE14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BF14">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG14">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BI14">
         <v>3.95</v>
@@ -4198,49 +4198,49 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO14">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BP14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ14">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR14">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BT14">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BU14">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV14">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BX14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BY14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ14">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA14">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="CB14" t="s">
         <v>169</v>
@@ -4263,22 +4263,22 @@
         <v>153</v>
       </c>
       <c r="F15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I15">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J15">
         <v>4.1</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.32</v>
@@ -4299,7 +4299,7 @@
         <v>1.68</v>
       </c>
       <c r="R15">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S15">
         <v>2.76</v>
@@ -4311,25 +4311,25 @@
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
@@ -4347,7 +4347,7 @@
         <v>14.5</v>
       </c>
       <c r="AH15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI15">
         <v>30</v>
@@ -4371,7 +4371,7 @@
         <v>13</v>
       </c>
       <c r="AP15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ15">
         <v>11.5</v>
@@ -4389,7 +4389,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15">
         <v>18.5</v>
@@ -4407,10 +4407,10 @@
         <v>23</v>
       </c>
       <c r="BB15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD15">
         <v>28</v>
@@ -4425,64 +4425,64 @@
         <v>11</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB15" t="s">
         <v>169</v>
@@ -4505,13 +4505,13 @@
         <v>154</v>
       </c>
       <c r="F16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G16">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5.3</v>
@@ -4523,46 +4523,46 @@
         <v>4.8</v>
       </c>
       <c r="L16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P16">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S16">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="T16">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U16">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
         <v>1.23</v>
       </c>
       <c r="W16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X16">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y16">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z16">
         <v>46</v>
@@ -4571,76 +4571,76 @@
         <v>110</v>
       </c>
       <c r="AB16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC16">
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE16">
         <v>60</v>
       </c>
       <c r="AF16">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG16">
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI16">
         <v>55</v>
       </c>
       <c r="AJ16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK16">
         <v>16.5</v>
       </c>
       <c r="AL16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM16">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN16">
         <v>6.8</v>
       </c>
       <c r="AO16">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP16">
         <v>22</v>
       </c>
       <c r="AQ16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS16">
         <v>40</v>
       </c>
       <c r="AT16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV16">
         <v>18.5</v>
       </c>
       <c r="AW16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY16">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
         <v>15.5</v>
@@ -4652,22 +4652,22 @@
         <v>16.5</v>
       </c>
       <c r="BC16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE16">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BF16">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG16">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BH16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI16">
         <v>4</v>
@@ -4676,13 +4676,13 @@
         <v>11</v>
       </c>
       <c r="BK16">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BL16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM16">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BN16">
         <v>5.6</v>
@@ -4691,16 +4691,16 @@
         <v>4.3</v>
       </c>
       <c r="BP16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ16">
         <v>7</v>
       </c>
       <c r="BR16">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BS16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT16">
         <v>10.5</v>
@@ -4709,22 +4709,22 @@
         <v>7.8</v>
       </c>
       <c r="BV16">
+        <v>36</v>
+      </c>
+      <c r="BW16">
+        <v>4.9</v>
+      </c>
+      <c r="BX16">
         <v>38</v>
       </c>
-      <c r="BW16">
-        <v>4.4</v>
-      </c>
-      <c r="BX16">
-        <v>40</v>
-      </c>
       <c r="BY16">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BZ16">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA16">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="CB16" t="s">
         <v>169</v>
@@ -4747,22 +4747,22 @@
         <v>155</v>
       </c>
       <c r="F17">
+        <v>3.85</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>2.04</v>
+      </c>
+      <c r="I17">
+        <v>2.08</v>
+      </c>
+      <c r="J17">
         <v>3.75</v>
       </c>
-      <c r="G17">
-        <v>3.85</v>
-      </c>
-      <c r="H17">
-        <v>2.1</v>
-      </c>
-      <c r="I17">
-        <v>2.14</v>
-      </c>
-      <c r="J17">
-        <v>3.8</v>
-      </c>
       <c r="K17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
         <v>1.42</v>
@@ -4774,46 +4774,46 @@
         <v>4.1</v>
       </c>
       <c r="O17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P17">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q17">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T17">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U17">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V17">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="W17">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X17">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y17">
         <v>10.5</v>
       </c>
       <c r="Z17">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC17">
         <v>8.6</v>
@@ -4825,106 +4825,106 @@
         <v>22</v>
       </c>
       <c r="AF17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG17">
         <v>16</v>
       </c>
       <c r="AH17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI17">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AJ17">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AL17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM17">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AN17">
         <v>55</v>
       </c>
       <c r="AO17">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP17">
         <v>13.5</v>
       </c>
       <c r="AQ17">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17">
         <v>11.5</v>
       </c>
       <c r="AS17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU17">
         <v>7.6</v>
       </c>
       <c r="AV17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW17">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AY17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ17">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BB17">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC17">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BD17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE17">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BF17">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BG17">
         <v>12.5</v>
       </c>
       <c r="BH17">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BI17">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17">
         <v>11</v>
       </c>
       <c r="BK17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BN17">
         <v>8.199999999999999</v>
@@ -4936,37 +4936,37 @@
         <v>36</v>
       </c>
       <c r="BQ17">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR17">
         <v>48</v>
       </c>
       <c r="BS17">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BT17">
         <v>5.5</v>
       </c>
       <c r="BU17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW17">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BX17">
         <v>32</v>
       </c>
       <c r="BY17">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BZ17">
         <v>28</v>
       </c>
       <c r="CA17">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="CB17" t="s">
         <v>169</v>
@@ -4989,7 +4989,7 @@
         <v>156</v>
       </c>
       <c r="F18">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G18">
         <v>3.1</v>
@@ -5013,7 +5013,7 @@
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O18">
         <v>1.2</v>
@@ -5022,22 +5022,22 @@
         <v>2.58</v>
       </c>
       <c r="Q18">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R18">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S18">
         <v>2.48</v>
       </c>
       <c r="T18">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U18">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="V18">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
         <v>1.48</v>
@@ -5046,10 +5046,10 @@
         <v>24</v>
       </c>
       <c r="Y18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA18">
         <v>34</v>
@@ -5091,13 +5091,13 @@
         <v>60</v>
       </c>
       <c r="AN18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO18">
         <v>13</v>
       </c>
       <c r="AP18">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ18">
         <v>14</v>
@@ -5109,7 +5109,7 @@
         <v>28</v>
       </c>
       <c r="AT18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU18">
         <v>8.6</v>
@@ -5142,10 +5142,10 @@
         <v>28</v>
       </c>
       <c r="BE18">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG18">
         <v>11</v>
@@ -5231,187 +5231,187 @@
         <v>157</v>
       </c>
       <c r="F19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G19">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H19">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="I19">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="J19">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K19">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M19">
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O19">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P19">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R19">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="S19">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="T19">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U19">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="W19">
         <v>1.17</v>
       </c>
       <c r="X19">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z19">
         <v>12.5</v>
       </c>
       <c r="AA19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB19">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AC19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD19">
         <v>10.5</v>
       </c>
       <c r="AE19">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF19">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH19">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK19">
         <v>120</v>
       </c>
       <c r="AL19">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN19">
         <v>55</v>
       </c>
       <c r="AO19">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AP19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AQ19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT19">
         <v>29</v>
       </c>
       <c r="AU19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW19">
         <v>12.5</v>
       </c>
       <c r="AX19">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AY19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ19">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC19">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BD19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE19">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BF19">
         <v>42</v>
       </c>
       <c r="BG19">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BH19">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI19">
         <v>4.4</v>
       </c>
       <c r="BJ19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK19">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN19">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BO19">
         <v>7.8</v>
@@ -5420,37 +5420,37 @@
         <v>42</v>
       </c>
       <c r="BQ19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT19">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU19">
         <v>4.1</v>
       </c>
       <c r="BV19">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BW19">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BX19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY19">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA19">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="CB19" t="s">
         <v>169</v>
@@ -5473,19 +5473,19 @@
         <v>158</v>
       </c>
       <c r="F20">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G20">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I20">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K20">
         <v>3.25</v>
@@ -5497,13 +5497,13 @@
         <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q20">
         <v>2.74</v>
@@ -5515,43 +5515,43 @@
         <v>5.7</v>
       </c>
       <c r="T20">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U20">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V20">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W20">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y20">
         <v>11.5</v>
       </c>
       <c r="Z20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA20">
         <v>900</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC20">
         <v>7.6</v>
       </c>
       <c r="AD20">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE20">
         <v>700</v>
       </c>
       <c r="AF20">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG20">
         <v>12.5</v>
@@ -5563,46 +5563,46 @@
         <v>700</v>
       </c>
       <c r="AJ20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL20">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AM20">
         <v>500</v>
       </c>
       <c r="AN20">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AO20">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AP20">
         <v>7.4</v>
       </c>
       <c r="AQ20">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS20">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT20">
         <v>6</v>
       </c>
       <c r="AU20">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW20">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX20">
         <v>10</v>
@@ -5614,85 +5614,85 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC20">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BD20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE20">
         <v>65</v>
       </c>
       <c r="BF20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BH20">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BI20">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ20">
         <v>12</v>
       </c>
       <c r="BK20">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO20">
         <v>4</v>
       </c>
       <c r="BP20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ20">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT20">
         <v>7.6</v>
       </c>
       <c r="BU20">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB20" t="s">
         <v>169</v>
@@ -5721,7 +5721,7 @@
         <v>7.2</v>
       </c>
       <c r="H21">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I21">
         <v>1.66</v>
@@ -5733,19 +5733,19 @@
         <v>4.3</v>
       </c>
       <c r="L21">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M21">
         <v>1.07</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O21">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P21">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q21">
         <v>2.02</v>
@@ -5754,7 +5754,7 @@
         <v>1.34</v>
       </c>
       <c r="S21">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T21">
         <v>2.02</v>
@@ -5769,25 +5769,25 @@
         <v>1.16</v>
       </c>
       <c r="X21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA21">
         <v>19</v>
       </c>
       <c r="AB21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC21">
         <v>9.800000000000001</v>
       </c>
       <c r="AD21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE21">
         <v>22</v>
@@ -5796,10 +5796,10 @@
         <v>60</v>
       </c>
       <c r="AG21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI21">
         <v>48</v>
@@ -5853,28 +5853,28 @@
         <v>21</v>
       </c>
       <c r="AZ21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA21">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BB21">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE21">
         <v>5.5</v>
       </c>
       <c r="BF21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG21">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH21">
         <v>3.9</v>
@@ -5886,34 +5886,34 @@
         <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BN21">
         <v>10.5</v>
       </c>
       <c r="BO21">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="BP21">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BQ21">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BR21">
         <v>85</v>
       </c>
       <c r="BS21">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BT21">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BU21">
         <v>3.5</v>
@@ -5922,19 +5922,19 @@
         <v>13</v>
       </c>
       <c r="BW21">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX21">
         <v>34</v>
       </c>
       <c r="BY21">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BZ21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA21">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB21" t="s">
         <v>169</v>
@@ -5960,88 +5960,88 @@
         <v>2.76</v>
       </c>
       <c r="G22">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I22">
         <v>3.3</v>
       </c>
       <c r="J22">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K22">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L22">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M22">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N22">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="O22">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="P22">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Q22">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="R22">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S22">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="T22">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U22">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="V22">
         <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X22">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z22">
         <v>21</v>
       </c>
       <c r="AA22">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AB22">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD22">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE22">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AF22">
         <v>20</v>
       </c>
       <c r="AG22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH22">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI22">
         <v>230</v>
@@ -6050,7 +6050,7 @@
         <v>60</v>
       </c>
       <c r="AK22">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL22">
         <v>210</v>
@@ -6059,25 +6059,25 @@
         <v>500</v>
       </c>
       <c r="AN22">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AO22">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP22">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ22">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR22">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS22">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="AT22">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU22">
         <v>6.2</v>
@@ -6086,55 +6086,55 @@
         <v>13</v>
       </c>
       <c r="AW22">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX22">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY22">
         <v>11.5</v>
       </c>
       <c r="AZ22">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BA22">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB22">
-        <v>34</v>
+        <v>5.5</v>
       </c>
       <c r="BC22">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="BD22">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BE22">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF22">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="BG22">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH22">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BI22">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BJ22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK22">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN22">
         <v>6.6</v>
@@ -6143,16 +6143,16 @@
         <v>4.9</v>
       </c>
       <c r="BP22">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR22">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT22">
         <v>7.2</v>
@@ -6164,19 +6164,19 @@
         <v>38</v>
       </c>
       <c r="BW22">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY22">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA22">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="CB22" t="s">
         <v>169</v>
@@ -6199,67 +6199,67 @@
         <v>161</v>
       </c>
       <c r="F23">
+        <v>2.2</v>
+      </c>
+      <c r="G23">
         <v>2.22</v>
       </c>
-      <c r="G23">
-        <v>2.26</v>
-      </c>
       <c r="H23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I23">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>1.39</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
         <v>1.29</v>
       </c>
       <c r="P23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R23">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T23">
         <v>1.72</v>
       </c>
       <c r="U23">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
         <v>1.8</v>
       </c>
       <c r="X23">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA23">
         <v>65</v>
@@ -6268,88 +6268,88 @@
         <v>11</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF23">
         <v>15.5</v>
       </c>
       <c r="AG23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH23">
         <v>18</v>
       </c>
       <c r="AI23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL23">
         <v>40</v>
       </c>
       <c r="AM23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN23">
         <v>16.5</v>
       </c>
       <c r="AO23">
+        <v>32</v>
+      </c>
+      <c r="AP23">
+        <v>16</v>
+      </c>
+      <c r="AQ23">
+        <v>12.5</v>
+      </c>
+      <c r="AR23">
+        <v>22</v>
+      </c>
+      <c r="AS23">
+        <v>46</v>
+      </c>
+      <c r="AT23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV23">
+        <v>12.5</v>
+      </c>
+      <c r="AW23">
+        <v>30</v>
+      </c>
+      <c r="AX23">
+        <v>13.5</v>
+      </c>
+      <c r="AY23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23">
+        <v>16</v>
+      </c>
+      <c r="BA23">
         <v>38</v>
       </c>
-      <c r="AP23">
-        <v>15</v>
-      </c>
-      <c r="AQ23">
-        <v>12</v>
-      </c>
-      <c r="AR23">
-        <v>19.5</v>
-      </c>
-      <c r="AS23">
-        <v>44</v>
-      </c>
-      <c r="AT23">
-        <v>9.4</v>
-      </c>
-      <c r="AU23">
-        <v>7.8</v>
-      </c>
-      <c r="AV23">
-        <v>12</v>
-      </c>
-      <c r="AW23">
-        <v>28</v>
-      </c>
-      <c r="AX23">
-        <v>13</v>
-      </c>
-      <c r="AY23">
-        <v>9.6</v>
-      </c>
-      <c r="AZ23">
-        <v>15.5</v>
-      </c>
-      <c r="BA23">
-        <v>32</v>
-      </c>
       <c r="BB23">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC23">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD23">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE23">
         <v>65</v>
@@ -6358,67 +6358,67 @@
         <v>14</v>
       </c>
       <c r="BG23">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BH23">
         <v>4.1</v>
       </c>
       <c r="BI23">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ23">
         <v>10.5</v>
       </c>
       <c r="BK23">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BN23">
         <v>6</v>
       </c>
       <c r="BO23">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP23">
         <v>18.5</v>
       </c>
       <c r="BQ23">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR23">
         <v>32</v>
       </c>
       <c r="BS23">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BT23">
         <v>7.6</v>
       </c>
       <c r="BU23">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="BV23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW23">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="BX23">
         <v>40</v>
       </c>
       <c r="BY23">
+        <v>5.1</v>
+      </c>
+      <c r="BZ23">
         <v>26</v>
       </c>
-      <c r="BZ23">
-        <v>27</v>
-      </c>
       <c r="CA23">
-        <v>17.5</v>
+        <v>4.7</v>
       </c>
       <c r="CB23" t="s">
         <v>169</v>
@@ -6459,31 +6459,31 @@
         <v>3.65</v>
       </c>
       <c r="L24">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M24">
         <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P24">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q24">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R24">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S24">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T24">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U24">
         <v>1.93</v>
@@ -6492,10 +6492,10 @@
         <v>1.94</v>
       </c>
       <c r="W24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y24">
         <v>8.199999999999999</v>
@@ -6504,7 +6504,7 @@
         <v>12</v>
       </c>
       <c r="AA24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB24">
         <v>14.5</v>
@@ -6519,40 +6519,40 @@
         <v>25</v>
       </c>
       <c r="AF24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH24">
         <v>22</v>
       </c>
       <c r="AI24">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ24">
-        <v>310</v>
+        <v>900</v>
       </c>
       <c r="AK24">
         <v>160</v>
       </c>
       <c r="AL24">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM24">
         <v>580</v>
       </c>
       <c r="AN24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO24">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR24">
         <v>10</v>
@@ -6573,7 +6573,7 @@
         <v>20</v>
       </c>
       <c r="AX24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY24">
         <v>16</v>
@@ -6600,49 +6600,49 @@
         <v>55</v>
       </c>
       <c r="BG24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH24">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI24">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ24">
         <v>11</v>
       </c>
       <c r="BK24">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN24">
         <v>8</v>
       </c>
       <c r="BO24">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP24">
         <v>44</v>
       </c>
       <c r="BQ24">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR24">
         <v>60</v>
       </c>
       <c r="BS24">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT24">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV24">
         <v>16</v>
@@ -6651,16 +6651,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY24">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ24">
         <v>34</v>
       </c>
       <c r="CA24">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB24" t="s">
         <v>169</v>
@@ -6689,10 +6689,10 @@
         <v>2.7</v>
       </c>
       <c r="H25">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I25">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J25">
         <v>3.05</v>
@@ -6707,25 +6707,25 @@
         <v>1.14</v>
       </c>
       <c r="N25">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
         <v>1.6</v>
       </c>
       <c r="P25">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S25">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
         <v>1.77</v>
@@ -6737,7 +6737,7 @@
         <v>1.58</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -6746,7 +6746,7 @@
         <v>21</v>
       </c>
       <c r="AA25">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB25">
         <v>7.6</v>
@@ -6770,19 +6770,19 @@
         <v>24</v>
       </c>
       <c r="AI25">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ25">
         <v>42</v>
       </c>
       <c r="AK25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL25">
         <v>70</v>
       </c>
       <c r="AM25">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN25">
         <v>46</v>
@@ -6794,25 +6794,25 @@
         <v>7.6</v>
       </c>
       <c r="AQ25">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR25">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS25">
         <v>55</v>
       </c>
       <c r="AT25">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU25">
         <v>6.6</v>
       </c>
       <c r="AV25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW25">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX25">
         <v>14</v>
@@ -6821,16 +6821,16 @@
         <v>12</v>
       </c>
       <c r="AZ25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA25">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BB25">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BC25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD25">
         <v>55</v>
@@ -6839,10 +6839,10 @@
         <v>95</v>
       </c>
       <c r="BF25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG25">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BH25">
         <v>2.56</v>
@@ -6860,7 +6860,7 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.3</v>
+        <v>22</v>
       </c>
       <c r="BN25">
         <v>5.2</v>
@@ -6878,7 +6878,7 @@
         <v>48</v>
       </c>
       <c r="BS25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BT25">
         <v>6.2</v>
@@ -6890,19 +6890,19 @@
         <v>34</v>
       </c>
       <c r="BW25">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX25">
         <v>60</v>
       </c>
       <c r="BY25">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BZ25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CB25" t="s">
         <v>169</v>
@@ -6928,16 +6928,16 @@
         <v>3.1</v>
       </c>
       <c r="G26">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H26">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I26">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J26">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
         <v>3.45</v>
@@ -6952,19 +6952,19 @@
         <v>3.65</v>
       </c>
       <c r="O26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P26">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q26">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R26">
         <v>1.34</v>
       </c>
       <c r="S26">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T26">
         <v>1.81</v>
@@ -6973,22 +6973,22 @@
         <v>2.16</v>
       </c>
       <c r="V26">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W26">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y26">
         <v>10.5</v>
       </c>
       <c r="Z26">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA26">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB26">
         <v>12</v>
@@ -7000,7 +7000,7 @@
         <v>12</v>
       </c>
       <c r="AE26">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF26">
         <v>21</v>
@@ -7018,16 +7018,16 @@
         <v>55</v>
       </c>
       <c r="AK26">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM26">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN26">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO26">
         <v>25</v>
@@ -7075,13 +7075,13 @@
         <v>32</v>
       </c>
       <c r="BD26">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE26">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="BF26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG26">
         <v>21</v>
@@ -7093,58 +7093,58 @@
         <v>3</v>
       </c>
       <c r="BJ26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK26">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BN26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO26">
         <v>5.6</v>
       </c>
       <c r="BP26">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BQ26">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR26">
         <v>42</v>
       </c>
       <c r="BS26">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT26">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU26">
         <v>4.9</v>
       </c>
       <c r="BV26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW26">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX26">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BY26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BZ26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA26">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB26" t="s">
         <v>169</v>
@@ -7173,7 +7173,7 @@
         <v>2.08</v>
       </c>
       <c r="H27">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I27">
         <v>4.5</v>
@@ -7182,43 +7182,43 @@
         <v>3.45</v>
       </c>
       <c r="K27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L27">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M27">
         <v>1.1</v>
       </c>
       <c r="N27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O27">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P27">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R27">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T27">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U27">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V27">
         <v>1.28</v>
       </c>
       <c r="W27">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X27">
         <v>11</v>
@@ -7233,7 +7233,7 @@
         <v>110</v>
       </c>
       <c r="AB27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC27">
         <v>7.6</v>
@@ -7242,7 +7242,7 @@
         <v>18</v>
       </c>
       <c r="AE27">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF27">
         <v>11.5</v>
@@ -7254,31 +7254,31 @@
         <v>22</v>
       </c>
       <c r="AI27">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ27">
         <v>25</v>
       </c>
       <c r="AK27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL27">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM27">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN27">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO27">
         <v>90</v>
       </c>
       <c r="AP27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR27">
         <v>27</v>
@@ -7287,10 +7287,10 @@
         <v>36</v>
       </c>
       <c r="AT27">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU27">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV27">
         <v>16.5</v>
@@ -7299,7 +7299,7 @@
         <v>55</v>
       </c>
       <c r="AX27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY27">
         <v>10</v>
@@ -7314,46 +7314,46 @@
         <v>23</v>
       </c>
       <c r="BC27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD27">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE27">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BF27">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG27">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH27">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI27">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK27">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL27">
         <v>190</v>
       </c>
       <c r="BM27">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BN27">
         <v>4.5</v>
       </c>
       <c r="BO27">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP27">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BQ27">
         <v>9.199999999999999</v>
@@ -7362,31 +7362,31 @@
         <v>34</v>
       </c>
       <c r="BS27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BT27">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU27">
         <v>6.6</v>
       </c>
       <c r="BV27">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW27">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BX27">
         <v>65</v>
       </c>
       <c r="BY27">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BZ27">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="CA27">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="CB27" t="s">
         <v>169</v>
@@ -7409,136 +7409,136 @@
         <v>166</v>
       </c>
       <c r="F28">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G28">
+        <v>2.22</v>
+      </c>
+      <c r="H28">
+        <v>3.55</v>
+      </c>
+      <c r="I28">
+        <v>3.7</v>
+      </c>
+      <c r="J28">
+        <v>3.65</v>
+      </c>
+      <c r="K28">
+        <v>3.85</v>
+      </c>
+      <c r="L28">
+        <v>1.4</v>
+      </c>
+      <c r="M28">
+        <v>1.06</v>
+      </c>
+      <c r="N28">
+        <v>4.2</v>
+      </c>
+      <c r="O28">
+        <v>1.29</v>
+      </c>
+      <c r="P28">
+        <v>2.08</v>
+      </c>
+      <c r="Q28">
+        <v>1.88</v>
+      </c>
+      <c r="R28">
+        <v>1.43</v>
+      </c>
+      <c r="S28">
+        <v>3.2</v>
+      </c>
+      <c r="T28">
+        <v>1.72</v>
+      </c>
+      <c r="U28">
         <v>2.24</v>
       </c>
-      <c r="H28">
-        <v>3.6</v>
-      </c>
-      <c r="I28">
-        <v>3.8</v>
-      </c>
-      <c r="J28">
-        <v>3.5</v>
-      </c>
-      <c r="K28">
-        <v>3.7</v>
-      </c>
-      <c r="L28">
-        <v>1.44</v>
-      </c>
-      <c r="M28">
-        <v>1.07</v>
-      </c>
-      <c r="N28">
-        <v>3.7</v>
-      </c>
-      <c r="O28">
-        <v>1.35</v>
-      </c>
-      <c r="P28">
-        <v>1.91</v>
-      </c>
-      <c r="Q28">
-        <v>2.04</v>
-      </c>
-      <c r="R28">
-        <v>1.35</v>
-      </c>
-      <c r="S28">
-        <v>3.65</v>
-      </c>
-      <c r="T28">
+      <c r="V28">
+        <v>1.37</v>
+      </c>
+      <c r="W28">
         <v>1.81</v>
       </c>
-      <c r="U28">
-        <v>2.1</v>
-      </c>
-      <c r="V28">
-        <v>1.35</v>
-      </c>
-      <c r="W28">
-        <v>1.8</v>
-      </c>
       <c r="X28">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y28">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA28">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB28">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD28">
         <v>15.5</v>
       </c>
       <c r="AE28">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AF28">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG28">
         <v>11</v>
       </c>
       <c r="AH28">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI28">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ28">
         <v>29</v>
       </c>
       <c r="AK28">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL28">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM28">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AN28">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AO28">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AP28">
+        <v>14.5</v>
+      </c>
+      <c r="AQ28">
+        <v>13</v>
+      </c>
+      <c r="AR28">
         <v>12</v>
       </c>
-      <c r="AQ28">
-        <v>11.5</v>
-      </c>
-      <c r="AR28">
-        <v>8.6</v>
-      </c>
       <c r="AS28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT28">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AU28">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV28">
         <v>13</v>
       </c>
       <c r="AW28">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AX28">
         <v>12.5</v>
@@ -7547,88 +7547,88 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA28">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BB28">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BC28">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD28">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="BE28">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="BF28">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BG28">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="CB28" t="s">
         <v>169</v>
@@ -7654,13 +7654,13 @@
         <v>3.2</v>
       </c>
       <c r="G29">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H29">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I29">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J29">
         <v>3.25</v>
@@ -7672,7 +7672,7 @@
         <v>1.52</v>
       </c>
       <c r="M29">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N29">
         <v>3</v>
@@ -7693,13 +7693,13 @@
         <v>4.8</v>
       </c>
       <c r="T29">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U29">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V29">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W29">
         <v>1.43</v>
@@ -7744,7 +7744,7 @@
         <v>70</v>
       </c>
       <c r="AK29">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL29">
         <v>75</v>
@@ -7756,7 +7756,7 @@
         <v>60</v>
       </c>
       <c r="AO29">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP29">
         <v>9.199999999999999</v>
@@ -7777,13 +7777,13 @@
         <v>6.6</v>
       </c>
       <c r="AV29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW29">
         <v>24</v>
       </c>
       <c r="AX29">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY29">
         <v>12.5</v>
@@ -7804,13 +7804,13 @@
         <v>10.5</v>
       </c>
       <c r="BE29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF29">
-        <v>15.5</v>
+        <v>40</v>
       </c>
       <c r="BG29">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="BH29">
         <v>3.25</v>
@@ -7822,7 +7822,7 @@
         <v>12</v>
       </c>
       <c r="BK29">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BL29">
         <v>1000</v>
@@ -7893,22 +7893,22 @@
         <v>168</v>
       </c>
       <c r="F30">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="G30">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I30">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J30">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K30">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L30">
         <v>1.52</v>
@@ -7920,85 +7920,85 @@
         <v>3.15</v>
       </c>
       <c r="O30">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P30">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q30">
         <v>2.34</v>
       </c>
       <c r="R30">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S30">
         <v>4.5</v>
       </c>
       <c r="T30">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U30">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V30">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W30">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y30">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z30">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA30">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AB30">
         <v>7.2</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE30">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF30">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG30">
         <v>11</v>
       </c>
       <c r="AH30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI30">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ30">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK30">
         <v>23</v>
       </c>
       <c r="AL30">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM30">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN30">
         <v>16.5</v>
       </c>
       <c r="AO30">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP30">
         <v>9.800000000000001</v>
@@ -8007,25 +8007,25 @@
         <v>13</v>
       </c>
       <c r="AR30">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS30">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AT30">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU30">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV30">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW30">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX30">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY30">
         <v>10</v>
@@ -8034,25 +8034,25 @@
         <v>21</v>
       </c>
       <c r="BA30">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="BB30">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD30">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BE30">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BF30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG30">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="BH30">
         <v>3</v>
@@ -8070,49 +8070,49 @@
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN30">
         <v>4.3</v>
       </c>
       <c r="BO30">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BP30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ30">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS30">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT30">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU30">
         <v>6.4</v>
       </c>
       <c r="BV30">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BW30">
         <v>12.5</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA30">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB30" t="s">
         <v>169</v>
